--- a/data/ICEHLdelegacije.xlsx
+++ b/data/ICEHLdelegacije.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1484" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1486" uniqueCount="241">
   <si>
     <t>PiragicTr</t>
   </si>
@@ -252,24 +252,24 @@
     <t>2024-10-19</t>
   </si>
   <si>
+    <t>2024-10-26</t>
+  </si>
+  <si>
+    <t>2024-11-17</t>
+  </si>
+  <si>
+    <t>2024-11-29</t>
+  </si>
+  <si>
+    <t>2024-11-03</t>
+  </si>
+  <si>
+    <t>2024-11-02</t>
+  </si>
+  <si>
     <t>2024-10-23</t>
   </si>
   <si>
-    <t>2024-10-26</t>
-  </si>
-  <si>
-    <t>2024-11-17</t>
-  </si>
-  <si>
-    <t>2024-11-29</t>
-  </si>
-  <si>
-    <t>2024-11-03</t>
-  </si>
-  <si>
-    <t>2024-11-02</t>
-  </si>
-  <si>
     <t>2024-10-29</t>
   </si>
   <si>
@@ -345,10 +345,10 @@
     <t>Tiroler Wasserkraft Arena;HolzerTo;SternatCh;MoidlMa;ZacherlPa</t>
   </si>
   <si>
-    <t>Klagenfurter Stadthalle;GroznikBo;HronskyTo;JedlickaPe;KoncDa</t>
-  </si>
-  <si>
-    <t>Klagenfurter Stadthalle;GroznikBo;PiragicTr;BärnthalerCh;PuffWo</t>
+    <t>Klagenfurter Stadthalle;GroznikBo;HronskyTo;DurmisOt;KoncDa</t>
+  </si>
+  <si>
+    <t>Klagenfurter Stadthalle;OfnerCh;PiragicTr;BärnthalerCh;PuffWo</t>
   </si>
   <si>
     <t>Tiroler Wasserkraft Arena;HuberAn;SmetanaLa;MantovaniDa;NotheggerDa</t>
@@ -450,7 +450,7 @@
     <t>Gabor Ocskay Eisarena;FichtnerPa;PiragicTr;DurmisOt;VacziDa</t>
   </si>
   <si>
-    <t>Stadthalle Villach;OfnerCh;SiegelSt;BedynekSe;RieckenSi</t>
+    <t>Stadthalle Villach;GroznikBo;SiegelSt;BedynekSe;RieckenSi</t>
   </si>
   <si>
     <t>Eishalle Asiago;GroznikBo;SchauerJa;PardatscherUl;RigoniDa</t>
@@ -621,7 +621,7 @@
     <t>Eishalle Pustertal;HuberAn;SeewaldEl;MartinFl;SparerDa</t>
   </si>
   <si>
-    <t>Merkur Eisstadion Graz;HronskyTo;KainbergerJu;DurmisOt;JedlickaPe</t>
+    <t>Merkur Eisstadion Graz;HronskyTo;KainbergerJu;JedlickaPe;WimmlerAl</t>
   </si>
   <si>
     <t>Hala Tivoli;NagyAt;OfnerCh;MuzsikNo;VacziDa</t>
@@ -2115,10 +2115,10 @@
         <v>61</v>
       </c>
       <c r="AF8" t="s">
+        <v>59</v>
+      </c>
+      <c r="AG8" t="s">
         <v>78</v>
-      </c>
-      <c r="AG8" t="s">
-        <v>79</v>
       </c>
       <c r="AH8" t="s">
         <v>67</v>
@@ -2136,10 +2136,10 @@
         <v>71</v>
       </c>
       <c r="AM8" t="s">
+        <v>79</v>
+      </c>
+      <c r="AN8" t="s">
         <v>80</v>
-      </c>
-      <c r="AN8" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
@@ -2231,10 +2231,10 @@
         <v>71</v>
       </c>
       <c r="AD9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AE9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AF9" t="s">
         <v>61</v>
@@ -2246,10 +2246,10 @@
         <v>71</v>
       </c>
       <c r="AI9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AK9" t="s">
         <v>68</v>
@@ -2278,7 +2278,7 @@
         <v>54</v>
       </c>
       <c r="F10" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G10" t="s">
         <v>71</v>
@@ -2314,7 +2314,7 @@
         <v>63</v>
       </c>
       <c r="R10" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="S10" t="s">
         <v>61</v>
@@ -2329,7 +2329,7 @@
         <v>84</v>
       </c>
       <c r="W10" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="X10" t="s">
         <v>69</v>
@@ -2350,16 +2350,16 @@
         <v>84</v>
       </c>
       <c r="AD10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AG10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AH10" t="s">
         <v>63</v>
@@ -2371,7 +2371,7 @@
         <v>68</v>
       </c>
       <c r="AK10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL10" t="s">
         <v>75</v>
@@ -2403,7 +2403,7 @@
         <v>63</v>
       </c>
       <c r="I11" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J11" t="s">
         <v>64</v>
@@ -2433,7 +2433,7 @@
         <v>61</v>
       </c>
       <c r="S11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T11" t="s">
         <v>61</v>
@@ -2445,7 +2445,7 @@
         <v>64</v>
       </c>
       <c r="W11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X11" t="s">
         <v>64</v>
@@ -2484,7 +2484,7 @@
         <v>74</v>
       </c>
       <c r="AJ11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AK11" t="s">
         <v>72</v>
@@ -2519,10 +2519,10 @@
         <v>69</v>
       </c>
       <c r="I12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K12" t="s">
         <v>64</v>
@@ -2546,10 +2546,10 @@
         <v>72</v>
       </c>
       <c r="R12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="T12" t="s">
         <v>64</v>
@@ -2558,19 +2558,19 @@
         <v>64</v>
       </c>
       <c r="V12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="W12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="X12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Y12" t="s">
         <v>68</v>
       </c>
       <c r="Z12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA12" t="s">
         <v>72</v>
@@ -2635,16 +2635,16 @@
         <v>68</v>
       </c>
       <c r="I13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J13" t="s">
         <v>72</v>
       </c>
       <c r="K13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M13" t="s">
         <v>71</v>
@@ -2662,7 +2662,7 @@
         <v>74</v>
       </c>
       <c r="R13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="S13" t="s">
         <v>74</v>
@@ -2695,10 +2695,10 @@
         <v>73</v>
       </c>
       <c r="AC13" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD13" t="s">
         <v>80</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>81</v>
       </c>
       <c r="AE13" t="s">
         <v>75</v>
@@ -2713,10 +2713,10 @@
         <v>75</v>
       </c>
       <c r="AI13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AJ13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AK13" t="s">
         <v>85</v>
@@ -2727,7 +2727,7 @@
         <v>61</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C14" t="s">
         <v>84</v>
@@ -2739,10 +2739,10 @@
         <v>84</v>
       </c>
       <c r="F14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H14" t="s">
         <v>64</v>
@@ -2772,7 +2772,7 @@
         <v>87</v>
       </c>
       <c r="Q14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R14" t="s">
         <v>85</v>
@@ -2823,7 +2823,7 @@
         <v>86</v>
       </c>
       <c r="AH14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AI14" t="s">
         <v>88</v>
@@ -2832,7 +2832,7 @@
         <v>88</v>
       </c>
       <c r="AK14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
@@ -2846,7 +2846,7 @@
         <v>64</v>
       </c>
       <c r="D15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E15" t="s">
         <v>64</v>
@@ -2867,19 +2867,19 @@
         <v>87</v>
       </c>
       <c r="K15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L15" t="s">
         <v>75</v>
       </c>
       <c r="M15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="N15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P15" t="s">
         <v>73</v>
@@ -2900,7 +2900,7 @@
         <v>85</v>
       </c>
       <c r="V15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W15" t="s">
         <v>89</v>
@@ -2921,7 +2921,7 @@
         <v>70</v>
       </c>
       <c r="AC15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AD15" t="s">
         <v>76</v>
@@ -2944,7 +2944,7 @@
         <v>64</v>
       </c>
       <c r="C16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D16" t="s">
         <v>72</v>
@@ -2953,7 +2953,7 @@
         <v>72</v>
       </c>
       <c r="F16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G16" t="s">
         <v>74</v>
@@ -2965,7 +2965,7 @@
         <v>89</v>
       </c>
       <c r="J16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K16" t="s">
         <v>70</v>
@@ -3007,7 +3007,7 @@
         <v>75</v>
       </c>
       <c r="X16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Y16" t="s">
         <v>70</v>
@@ -3016,7 +3016,7 @@
         <v>75</v>
       </c>
       <c r="AA16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AB16" t="s">
         <v>86</v>
@@ -3024,13 +3024,16 @@
       <c r="AC16" t="s">
         <v>88</v>
       </c>
+      <c r="AD16" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>64</v>
       </c>
       <c r="B17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
         <v>72</v>
@@ -3063,7 +3066,7 @@
         <v>88</v>
       </c>
       <c r="M17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N17" t="s">
         <v>75</v>
@@ -3075,7 +3078,7 @@
         <v>70</v>
       </c>
       <c r="Q17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="R17" t="s">
         <v>86</v>
@@ -3084,7 +3087,7 @@
         <v>90</v>
       </c>
       <c r="T17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="U17" t="s">
         <v>76</v>
@@ -3093,16 +3096,16 @@
         <v>90</v>
       </c>
       <c r="W17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="X17" t="s">
         <v>76</v>
       </c>
       <c r="Y17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Z17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AA17" t="s">
         <v>88</v>
@@ -3134,10 +3137,10 @@
         <v>70</v>
       </c>
       <c r="I18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K18" t="s">
         <v>86</v>
@@ -3155,7 +3158,7 @@
         <v>70</v>
       </c>
       <c r="P18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Q18" t="s">
         <v>76</v>
@@ -3172,16 +3175,16 @@
         <v>87</v>
       </c>
       <c r="D19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E19" t="s">
         <v>70</v>
       </c>
       <c r="F19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H19" t="s">
         <v>88</v>
@@ -3207,7 +3210,7 @@
         <v>87</v>
       </c>
       <c r="C20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D20" t="s">
         <v>85</v>
@@ -3218,13 +3221,16 @@
       <c r="F20" t="s">
         <v>76</v>
       </c>
+      <c r="I20" t="s">
+        <v>83</v>
+      </c>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>85</v>
       </c>
       <c r="B21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C21" t="s">
         <v>73</v>
@@ -3255,7 +3261,7 @@
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B23" t="s">
         <v>75</v>
@@ -3264,7 +3270,7 @@
         <v>89</v>
       </c>
       <c r="D23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3286,10 +3292,10 @@
         <v>86</v>
       </c>
       <c r="B25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D25" t="s">
         <v>76</v>
@@ -3518,13 +3524,13 @@
         <v>69</v>
       </c>
       <c r="S3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="T3" t="s">
         <v>61</v>
       </c>
       <c r="U3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="V3" t="s">
         <v>68</v>
@@ -3536,10 +3542,10 @@
         <v>64</v>
       </c>
       <c r="Y3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AA3" t="s">
         <v>72</v>
@@ -3551,7 +3557,7 @@
         <v>87</v>
       </c>
       <c r="AD3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE3" t="s">
         <v>73</v>
@@ -3569,7 +3575,7 @@
         <v>70</v>
       </c>
       <c r="AJ3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AK3" t="s">
         <v>88</v>
@@ -3643,7 +3649,7 @@
         <v>5</v>
       </c>
       <c r="T4" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U4" t="s">
         <v>30</v>
@@ -3884,7 +3890,7 @@
         <v>38</v>
       </c>
       <c r="S6" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="T6" t="s">
         <v>20</v>
@@ -4113,7 +4119,7 @@
         <v>16</v>
       </c>
       <c r="T8" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="V8" t="s">
         <v>5</v>
@@ -4967,7 +4973,7 @@
         <v>14</v>
       </c>
       <c r="T18" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="V18" t="s">
         <v>25</v>
@@ -5041,7 +5047,7 @@
         <v>19</v>
       </c>
       <c r="T19" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="V19" t="s">
         <v>36</v>
@@ -5432,7 +5438,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="20:36" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="15" customHeight="1" spans="24:36" x14ac:dyDescent="0.25"/>
     <row r="29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5594,13 +5600,13 @@
         <v>69</v>
       </c>
       <c r="S3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="T3" t="s">
         <v>61</v>
       </c>
       <c r="U3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="V3" t="s">
         <v>68</v>
@@ -5612,10 +5618,10 @@
         <v>64</v>
       </c>
       <c r="Y3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AA3" t="s">
         <v>72</v>
@@ -5627,7 +5633,7 @@
         <v>87</v>
       </c>
       <c r="AD3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE3" t="s">
         <v>73</v>
@@ -5645,7 +5651,7 @@
         <v>70</v>
       </c>
       <c r="AJ3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AK3" t="s">
         <v>88</v>
@@ -6125,7 +6131,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="20:36" x14ac:dyDescent="0.25"/>
+    <row r="10" ht="15" customHeight="1" spans="24:36" x14ac:dyDescent="0.25"/>
     <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="13" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/data/ICEHLdelegacije.xlsx
+++ b/data/ICEHLdelegacije.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="ICEHL" state="visible" r:id="rId4"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1486" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1484" uniqueCount="240">
   <si>
     <t>PiragicTr</t>
   </si>
@@ -108,189 +108,186 @@
     <t>WimmlerAl</t>
   </si>
   <si>
+    <t>Huber aAn</t>
+  </si>
+  <si>
+    <t>JedlickaPe</t>
+  </si>
+  <si>
+    <t>NotheggerDa</t>
+  </si>
+  <si>
+    <t>NikolicKr</t>
+  </si>
+  <si>
+    <t>SoosDa</t>
+  </si>
+  <si>
+    <t>NagyAt</t>
+  </si>
+  <si>
+    <t>VacziDa</t>
+  </si>
+  <si>
+    <t>WeissAl</t>
+  </si>
+  <si>
+    <t>MoidlMa</t>
+  </si>
+  <si>
+    <t>SeewaldJe</t>
+  </si>
+  <si>
+    <t>VoicanCh</t>
+  </si>
+  <si>
+    <t>HolzerTo</t>
+  </si>
+  <si>
+    <t>KainbergerJu</t>
+  </si>
+  <si>
+    <t>ZacherlPa</t>
+  </si>
+  <si>
+    <t>JeramFi</t>
+  </si>
+  <si>
+    <t>FleischmannLu</t>
+  </si>
+  <si>
+    <t>SnojTa</t>
+  </si>
+  <si>
+    <t>StrimitzerDa</t>
+  </si>
+  <si>
+    <t>2024-09-20</t>
+  </si>
+  <si>
+    <t>2024-09-22</t>
+  </si>
+  <si>
+    <t>2024-09-24</t>
+  </si>
+  <si>
+    <t>2024-09-21</t>
+  </si>
+  <si>
+    <t>2024-09-27</t>
+  </si>
+  <si>
+    <t>2024-10-04</t>
+  </si>
+  <si>
+    <t>2024-09-29</t>
+  </si>
+  <si>
+    <t>2024-10-13</t>
+  </si>
+  <si>
+    <t>2024-10-12</t>
+  </si>
+  <si>
+    <t>2024-10-01</t>
+  </si>
+  <si>
+    <t>2024-10-25</t>
+  </si>
+  <si>
+    <t>2024-10-06</t>
+  </si>
+  <si>
+    <t>2024-10-20</t>
+  </si>
+  <si>
+    <t>2024-11-01</t>
+  </si>
+  <si>
+    <t>2024-10-05</t>
+  </si>
+  <si>
+    <t>2024-10-11</t>
+  </si>
+  <si>
+    <t>2024-10-02</t>
+  </si>
+  <si>
+    <t>2024-10-27</t>
+  </si>
+  <si>
+    <t>2024-10-22</t>
+  </si>
+  <si>
+    <t>2024-11-27</t>
+  </si>
+  <si>
+    <t>2024-10-18</t>
+  </si>
+  <si>
+    <t>2024-11-13</t>
+  </si>
+  <si>
+    <t>2024-11-20</t>
+  </si>
+  <si>
+    <t>2024-11-15</t>
+  </si>
+  <si>
+    <t>2024-11-24</t>
+  </si>
+  <si>
+    <t>2024-12-04</t>
+  </si>
+  <si>
+    <t>2024-10-19</t>
+  </si>
+  <si>
+    <t>2024-10-26</t>
+  </si>
+  <si>
+    <t>2024-11-17</t>
+  </si>
+  <si>
+    <t>2024-11-29</t>
+  </si>
+  <si>
+    <t>2024-11-03</t>
+  </si>
+  <si>
+    <t>2024-11-02</t>
+  </si>
+  <si>
+    <t>2024-10-23</t>
+  </si>
+  <si>
+    <t>2024-10-29</t>
+  </si>
+  <si>
+    <t>zbrisano</t>
+  </si>
+  <si>
+    <t>2024-11-22</t>
+  </si>
+  <si>
+    <t>2024-12-01</t>
+  </si>
+  <si>
+    <t>2024-11-16</t>
+  </si>
+  <si>
+    <t>2024-11-30</t>
+  </si>
+  <si>
+    <t>2024-11-23</t>
+  </si>
+  <si>
+    <t>2024-12-03</t>
+  </si>
+  <si>
     <t>HuberAn</t>
   </si>
   <si>
-    <t>JedlickaPe</t>
-  </si>
-  <si>
-    <t>NotheggerDa</t>
-  </si>
-  <si>
-    <t>NikolicKr</t>
-  </si>
-  <si>
-    <t>SoosDa</t>
-  </si>
-  <si>
-    <t>NagyAt</t>
-  </si>
-  <si>
-    <t>VacziDa</t>
-  </si>
-  <si>
-    <t>WeissAl</t>
-  </si>
-  <si>
-    <t>MoidlMa</t>
-  </si>
-  <si>
-    <t>SeewaldJe</t>
-  </si>
-  <si>
-    <t>VoicanCh</t>
-  </si>
-  <si>
-    <t>HolzerTo</t>
-  </si>
-  <si>
-    <t>KainbergerJu</t>
-  </si>
-  <si>
-    <t>ZacherlPa</t>
-  </si>
-  <si>
-    <t>JeramFi</t>
-  </si>
-  <si>
-    <t>FleischmannLu</t>
-  </si>
-  <si>
-    <t>SnojTa</t>
-  </si>
-  <si>
-    <t>LinesmanZw</t>
-  </si>
-  <si>
-    <t>LinesmanEi</t>
-  </si>
-  <si>
-    <t>StrimitzerDa</t>
-  </si>
-  <si>
-    <t>2024-09-20</t>
-  </si>
-  <si>
-    <t>2024-09-22</t>
-  </si>
-  <si>
-    <t>2024-09-24</t>
-  </si>
-  <si>
-    <t>2024-09-21</t>
-  </si>
-  <si>
-    <t>2024-09-27</t>
-  </si>
-  <si>
-    <t>2024-10-04</t>
-  </si>
-  <si>
-    <t>2024-09-29</t>
-  </si>
-  <si>
-    <t>2024-10-13</t>
-  </si>
-  <si>
-    <t>2024-10-12</t>
-  </si>
-  <si>
-    <t>zbrisano</t>
-  </si>
-  <si>
-    <t>2024-10-01</t>
-  </si>
-  <si>
-    <t>2024-10-25</t>
-  </si>
-  <si>
-    <t>2024-10-06</t>
-  </si>
-  <si>
-    <t>2024-10-20</t>
-  </si>
-  <si>
-    <t>2024-11-01</t>
-  </si>
-  <si>
-    <t>2024-10-05</t>
-  </si>
-  <si>
-    <t>2024-10-11</t>
-  </si>
-  <si>
-    <t>2024-10-02</t>
-  </si>
-  <si>
-    <t>2024-10-27</t>
-  </si>
-  <si>
-    <t>2024-10-22</t>
-  </si>
-  <si>
-    <t>2024-11-27</t>
-  </si>
-  <si>
-    <t>2024-10-18</t>
-  </si>
-  <si>
-    <t>2024-11-13</t>
-  </si>
-  <si>
-    <t>2024-11-20</t>
-  </si>
-  <si>
-    <t>2024-11-15</t>
-  </si>
-  <si>
-    <t>2024-11-24</t>
-  </si>
-  <si>
-    <t>2024-12-04</t>
-  </si>
-  <si>
-    <t>2024-10-19</t>
-  </si>
-  <si>
-    <t>2024-10-26</t>
-  </si>
-  <si>
-    <t>2024-11-17</t>
-  </si>
-  <si>
-    <t>2024-11-29</t>
-  </si>
-  <si>
-    <t>2024-11-03</t>
-  </si>
-  <si>
-    <t>2024-11-02</t>
-  </si>
-  <si>
-    <t>2024-10-23</t>
-  </si>
-  <si>
-    <t>2024-10-29</t>
-  </si>
-  <si>
-    <t>2024-11-22</t>
-  </si>
-  <si>
-    <t>2024-12-01</t>
-  </si>
-  <si>
-    <t>2024-11-16</t>
-  </si>
-  <si>
-    <t>2024-11-30</t>
-  </si>
-  <si>
-    <t>2024-11-23</t>
-  </si>
-  <si>
-    <t>2024-12-03</t>
-  </si>
-  <si>
     <t>Heidi Horten Arena Klagenfurt;GroznikBo;SternatCh;JedlickaPe;KoncDa</t>
   </si>
   <si>
@@ -309,7 +306,7 @@
     <t>Eisarena Salzburg;SeewaldEl;SternatCh;NotheggerDa;SeewaldJe</t>
   </si>
   <si>
-    <t>ZBRISANO</t>
+    <t>Heidi Horten Arena Klagenfurt;PiragicTr;SoosDa;MuzsikNo;VacziDa</t>
   </si>
   <si>
     <t>Tiroler Wasserkraft Arena;HuberAn;SeewaldEl;MoidlMa;NotheggerDa</t>
@@ -369,7 +366,7 @@
     <t>Merkur Eisstadion Graz;OfnerCh;SternatCh;NotheggerDa;RieckenSi</t>
   </si>
   <si>
-    <t>Tiroler Wasserkraft Arena;HuberAn;SeewaldEl;NotheggerDa;SeewaldJe</t>
+    <t>Tiroler Wasserkraft Arena;NikolicKr;SeewaldEl;NotheggerDa;SeewaldJe</t>
   </si>
   <si>
     <t>Gabor Ocskay Eisarena;FichtnerPa;SoosDa;JedlickaPe;MuzsikNo</t>
@@ -423,7 +420,7 @@
     <t>Heidi Horten Arena;RezekGr;SmetanaLa;PuffWo;ZgoncGa</t>
   </si>
   <si>
-    <t>Heidi Horten Arena Klagenfurt;PiragicTr;SoosDa;MuzsikNo;VacziDa</t>
+    <t>Linz AG Eisarena;NikolicMa;RezekGr;SparerDa;ZgoncGa</t>
   </si>
   <si>
     <t>Eishalle Wien-Kagran;FichtnerPa;PiragicTr;Gatol-schafranekMa;ZgoncGa</t>
@@ -462,10 +459,10 @@
     <t>Hala Tivoli;RezekGr;SternatCh;HribarMa;JeramFi</t>
   </si>
   <si>
-    <t>Sparkasse Arena Bozen;HronskyTo;HuberAn;DurmisOt;KoncDa</t>
-  </si>
-  <si>
-    <t>Eishalle Bruneck;HronskyTo;NikolicMa;DurmisOt;KoncDa</t>
+    <t>Sparkasse Arena Bozen;HronskyTo;Huber aAn;JedlickaPe;KoncDa</t>
+  </si>
+  <si>
+    <t>Eishalle Bruneck;HronskyTo;NikolicMa;JedlickaPe;KoncDa</t>
   </si>
   <si>
     <t>Gabor Ocskay Eisarena;FichtnerPa;SmetanaLa;RieckenSi;VacziDa</t>
@@ -480,7 +477,7 @@
     <t>Eisarena Salzburg;FichtnerPa;SiegelSt;Gatol-schafranekMa;MoidlMa</t>
   </si>
   <si>
-    <t>Eishalle Feldkirch;HolzerTo;HuberAn;MartinFl;SparerDa</t>
+    <t>Eishalle Feldkirch;HolzerTo;Huber aAn;MartinFl;SparerDa</t>
   </si>
   <si>
     <t>Hala Tivoli;GroznikBo;NagyAt;MuzsikNo;VacziDa</t>
@@ -516,9 +513,6 @@
     <t>Merkur Eisstadion Graz;OfnerCh;SiegelSt;BärnthalerCh;WeissAl</t>
   </si>
   <si>
-    <t>Linz AG Eisarena;NikolicMa;RezekGr;SparerDa;ZgoncGa</t>
-  </si>
-  <si>
     <t>Klagenfurter Stadthalle;HronskyTo;NagyAt;DurmisOt;JedlickaPe</t>
   </si>
   <si>
@@ -552,7 +546,7 @@
     <t>Linz AG Eisarena;SiegelSt;SmetanaLa;BedynekSe;NotheggerDa</t>
   </si>
   <si>
-    <t>Eishalle KagranEins;GroznikBo;SmetanaLa;JedlickaPe;PuffWo</t>
+    <t>Eishalle KagranEins;GroznikBo;SmetanaLa;MoidlMa;PuffWo</t>
   </si>
   <si>
     <t>Eishalle Feldkirch;NikolicMa;SchauerJa;MartinFl;SparerDa</t>
@@ -564,7 +558,7 @@
     <t>Tiroler Wasserkraft Arena;SeewaldEl;SmetanaLa;MartinFl;RieckenSi</t>
   </si>
   <si>
-    <t>Sparkasse Arena Bozen;BernekerTh;OfnerCh;PuffWo;RigoniDa</t>
+    <t>Sparkasse Arena Bozen;BernekerTh;NikolicKr;PuffWo;RigoniDa</t>
   </si>
   <si>
     <t>Gabor Ocskay Eisarena;HronskyTo;PiragicTr;HribarMa;JedlickaPe</t>
@@ -579,7 +573,7 @@
     <t>Eishalle Wien-Kagran;FichtnerPa;SmetanaLa;DurmisOt;KoncDa</t>
   </si>
   <si>
-    <t>Sparkasse Arena Bozen;HuberAn;ZrnicMi;MantovaniDa;RigoniDa</t>
+    <t>Sparkasse Arena Bozen;Huber aAn;ZrnicMi;MantovaniDa;RigoniDa</t>
   </si>
   <si>
     <t>Eishalle Wien-Kagran;HronskyTo;PiragicTr;HribarMa;ZgoncGa</t>
@@ -633,7 +627,10 @@
     <t>Stadthalle Villach;RezekGr;SiegelSt;MantovaniDa;WimmlerAl</t>
   </si>
   <si>
-    <t>Eishalle Wien-Kagran;OfnerCh;SternatCh;DurmisOt;KoncDa</t>
+    <t>Eishalle Asiago;PiragicTr;ZrnicMi;RigoniDa;ZgoncGa</t>
+  </si>
+  <si>
+    <t>Eishalle Wien-Kagran;OfnerCh;SternatCh;KoncDa;MoidlMa</t>
   </si>
   <si>
     <t>Hala Tivoli;GroznikBo;NagyAt;HribarMa;PuffWo</t>
@@ -699,7 +696,7 @@
     <t>Eishalle Feldkirch;BernekerTh;SchauerJa;DurmisOt;KoncDa</t>
   </si>
   <si>
-    <t>Linz AG Eisarena;HuberAn;SeewaldEl;NotheggerDa;ZacherlPa</t>
+    <t>Linz AG Eisarena;Huber aAn;SeewaldEl;NotheggerDa;ZacherlPa</t>
   </si>
   <si>
     <t>Tiroler Wasserkraft Arena;SchauerJa;SternatCh;MartinFl;SparerDa</t>
@@ -735,7 +732,7 @@
     <t>Eishalle Bruneck;NikolicMa;SternatCh;MantovaniDa;SparerDa</t>
   </si>
   <si>
-    <t>Eishalle Bruneck;GroznikBo;HuberAn;PardatscherUl;RigoniDa</t>
+    <t>Eishalle Bruneck;GroznikBo;Huber aAn;PardatscherUl;RigoniDa</t>
   </si>
   <si>
     <t>Sparkasse Arena Bozen;NikolicMa;SternatCh;SeewaldJe;SparerDa</t>
@@ -1056,7 +1053,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:AY134"/>
+  <dimension ref="A2:AW134"/>
   <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.28515625" customWidth="1"/>
@@ -1106,50 +1103,48 @@
     <col min="45" max="45" width="10.7109375" customWidth="1"/>
     <col min="46" max="46" width="11.140625" customWidth="1"/>
     <col min="47" max="47" width="11.7109375" customWidth="1"/>
-    <col min="48" max="48" width="15.5703125" customWidth="1"/>
-    <col min="49" max="49" width="12" customWidth="1"/>
-    <col min="50" max="50" width="15.140625" customWidth="1"/>
-    <col min="51" max="51" width="14.140625" customWidth="1"/>
-    <col min="52" max="53" width="16" customWidth="1"/>
-    <col min="55" max="55" width="20.140625" customWidth="1"/>
-    <col min="57" max="57" width="10.140625" customWidth="1"/>
+    <col min="48" max="48" width="15.140625" customWidth="1"/>
+    <col min="49" max="49" width="14.140625" customWidth="1"/>
+    <col min="50" max="51" width="16" customWidth="1"/>
+    <col min="53" max="53" width="20.140625" customWidth="1"/>
+    <col min="55" max="55" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" ht="14.45" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A2">
-        <f>COUNTIF(A4:A100,"&lt;&gt;")</f>
+        <f t="shared" ref="A2:H2" si="0">COUNTIF(A4:A100,"&lt;&gt;")</f>
         <v>24</v>
       </c>
       <c r="B2">
-        <f>COUNTIF(B4:B100,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="C2">
-        <f>COUNTIF(C4:C100,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="D2">
-        <f>COUNTIF(D4:D100,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="E2">
-        <f>COUNTIF(E4:E100,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="F2">
-        <f>COUNTIF(F4:F100,"&lt;&gt;")</f>
-        <v>17</v>
+        <f t="shared" si="0"/>
+        <v>18</v>
       </c>
       <c r="G2">
-        <f>COUNTIF(G4:G100,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="H2">
-        <f>COUNTIF(H4:H100,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="I2">
-        <f>COUNTIF(I4:I100,"&lt;&gt;")</f>
+        <f>COUNTIF(I4:I99,"&lt;&gt;")</f>
         <v>16</v>
       </c>
       <c r="J2">
@@ -1193,119 +1188,119 @@
         <v>14</v>
       </c>
       <c r="T2">
-        <f>COUNTIF(T4:T100,"&lt;&gt;")</f>
+        <f t="shared" ref="T2:AC2" si="1">COUNTIF(T4:T100,"&lt;&gt;")</f>
         <v>14</v>
       </c>
       <c r="U2">
-        <f>COUNTIF(U4:U100,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="V2">
-        <f>COUNTIF(V4:V100,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="W2">
-        <f>COUNTIF(W4:W100,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="X2">
-        <f>COUNTIF(X4:X100,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="Y2">
-        <f>COUNTIF(Y4:Y100,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="Z2">
-        <f>COUNTIF(Z4:Z100,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="AA2">
-        <f>COUNTIF(AA4:AA100,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="AB2">
-        <f>COUNTIF(AB4:AB100,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="AC2">
-        <f>COUNTIF(AC4:AC100,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="AD2">
         <f>COUNTIF(AD4:AD96,"&lt;&gt;")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE2">
         <f>COUNTIF(AE4:AE100,"&lt;&gt;")</f>
         <v>12</v>
       </c>
       <c r="AF2">
-        <f>COUNTIF(AF4:AF100,"&lt;&gt;")</f>
-        <v>12</v>
+        <f>COUNTIF(AF4:AF99,"&lt;&gt;")</f>
+        <v>11</v>
       </c>
       <c r="AG2">
         <f>COUNTIF(AG4:AG100,"&lt;&gt;")</f>
         <v>12</v>
       </c>
       <c r="AH2">
-        <f>COUNTIF(AH4:AH100,"&lt;&gt;")</f>
-        <v>11</v>
+        <f>COUNTIF(AH4:AH99,"&lt;&gt;")</f>
+        <v>10</v>
       </c>
       <c r="AI2">
         <f>COUNTIF(AI4:AI99,"&lt;&gt;")</f>
         <v>11</v>
       </c>
       <c r="AJ2">
-        <f>COUNTIF(AJ4:AJ100,"&lt;&gt;")</f>
+        <f t="shared" ref="AJ2:AU2" si="2">COUNTIF(AJ4:AJ100,"&lt;&gt;")</f>
         <v>11</v>
       </c>
       <c r="AK2">
-        <f>COUNTIF(AK4:AK100,"&lt;&gt;")</f>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="AL2">
-        <f>COUNTIF(AL4:AL100,"&lt;&gt;")</f>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="AM2">
-        <f>COUNTIF(AM4:AM100,"&lt;&gt;")</f>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="AN2">
-        <f>COUNTIF(AN4:AN100,"&lt;&gt;")</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="AO2">
-        <f>COUNTIF(AO4:AO100,"&lt;&gt;")</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="AP2">
-        <f>COUNTIF(AP4:AP100,"&lt;&gt;")</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="AQ2">
-        <f>COUNTIF(AQ4:AQ100,"&lt;&gt;")</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="AR2">
-        <f>COUNTIF(AR4:AR100,"&lt;&gt;")</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="AS2">
-        <f>COUNTIF(AS4:AS100,"&lt;&gt;")</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="AT2">
-        <f>COUNTIF(AT4:AT100,"&lt;&gt;")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AU2">
-        <f>COUNTIF(AU4:AU100,"&lt;&gt;")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -1450,1874 +1445,1871 @@
       <c r="AV3" t="s">
         <v>47</v>
       </c>
-      <c r="AW3" t="s">
+    </row>
+    <row r="4" ht="15" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>48</v>
       </c>
-      <c r="AX3" t="s">
+      <c r="B4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I4" t="s">
+        <v>48</v>
+      </c>
+      <c r="J4" t="s">
         <v>49</v>
       </c>
+      <c r="K4" t="s">
+        <v>50</v>
+      </c>
+      <c r="L4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M4" t="s">
+        <v>49</v>
+      </c>
+      <c r="N4" t="s">
+        <v>48</v>
+      </c>
+      <c r="O4" t="s">
+        <v>48</v>
+      </c>
+      <c r="P4" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R4" t="s">
+        <v>48</v>
+      </c>
+      <c r="S4" t="s">
+        <v>49</v>
+      </c>
+      <c r="T4" t="s">
+        <v>51</v>
+      </c>
+      <c r="U4" t="s">
+        <v>52</v>
+      </c>
+      <c r="V4" t="s">
+        <v>48</v>
+      </c>
+      <c r="W4" t="s">
+        <v>48</v>
+      </c>
+      <c r="X4" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>53</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>53</v>
+      </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="5" ht="15" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H5" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J5" t="s">
+        <v>53</v>
+      </c>
+      <c r="K5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L5" t="s">
+        <v>52</v>
+      </c>
+      <c r="M5" t="s">
         <v>50</v>
       </c>
-      <c r="B4" t="s">
+      <c r="N5" t="s">
+        <v>52</v>
+      </c>
+      <c r="O5" t="s">
+        <v>49</v>
+      </c>
+      <c r="P5" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q5" t="s">
         <v>50</v>
       </c>
-      <c r="C4" t="s">
+      <c r="R5" t="s">
+        <v>52</v>
+      </c>
+      <c r="S5" t="s">
+        <v>52</v>
+      </c>
+      <c r="T5" t="s">
+        <v>57</v>
+      </c>
+      <c r="U5" t="s">
+        <v>54</v>
+      </c>
+      <c r="V5" t="s">
+        <v>51</v>
+      </c>
+      <c r="W5" t="s">
+        <v>52</v>
+      </c>
+      <c r="X5" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>54</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>53</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>52</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>57</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>54</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>57</v>
+      </c>
+      <c r="AL5" t="s">
         <v>50</v>
       </c>
-      <c r="D4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F4" t="s">
-        <v>50</v>
-      </c>
-      <c r="G4" t="s">
-        <v>50</v>
-      </c>
-      <c r="H4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J4" t="s">
-        <v>51</v>
-      </c>
-      <c r="K4" t="s">
-        <v>52</v>
-      </c>
-      <c r="L4" t="s">
-        <v>50</v>
-      </c>
-      <c r="M4" t="s">
-        <v>51</v>
-      </c>
-      <c r="N4" t="s">
-        <v>50</v>
-      </c>
-      <c r="O4" t="s">
-        <v>50</v>
-      </c>
-      <c r="P4" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>51</v>
-      </c>
-      <c r="R4" t="s">
-        <v>50</v>
-      </c>
-      <c r="S4" t="s">
-        <v>51</v>
-      </c>
-      <c r="T4" t="s">
+      <c r="AM5" t="s">
+        <v>55</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>58</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>59</v>
+      </c>
+      <c r="AP5" t="s">
         <v>53</v>
       </c>
-      <c r="U4" t="s">
-        <v>54</v>
-      </c>
-      <c r="V4" t="s">
-        <v>50</v>
-      </c>
-      <c r="W4" t="s">
-        <v>50</v>
-      </c>
-      <c r="X4" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>54</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>55</v>
-      </c>
-      <c r="AN4" t="s">
+      <c r="AQ5" t="s">
         <v>56</v>
       </c>
-      <c r="AO4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>56</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS4" t="s">
-        <v>58</v>
-      </c>
-      <c r="AT4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AU4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>59</v>
-      </c>
-      <c r="AW4" t="s">
-        <v>59</v>
-      </c>
-      <c r="AX4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G5" t="s">
-        <v>54</v>
-      </c>
-      <c r="H5" t="s">
-        <v>51</v>
-      </c>
-      <c r="I5" t="s">
-        <v>54</v>
-      </c>
-      <c r="J5" t="s">
-        <v>55</v>
-      </c>
-      <c r="K5" t="s">
-        <v>56</v>
-      </c>
-      <c r="L5" t="s">
-        <v>54</v>
-      </c>
-      <c r="M5" t="s">
-        <v>52</v>
-      </c>
-      <c r="N5" t="s">
-        <v>54</v>
-      </c>
-      <c r="O5" t="s">
-        <v>51</v>
-      </c>
-      <c r="P5" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>52</v>
-      </c>
-      <c r="R5" t="s">
-        <v>54</v>
-      </c>
-      <c r="S5" t="s">
-        <v>54</v>
-      </c>
-      <c r="T5" t="s">
+      <c r="AR5" t="s">
         <v>60</v>
       </c>
-      <c r="U5" t="s">
-        <v>56</v>
-      </c>
-      <c r="V5" t="s">
-        <v>53</v>
-      </c>
-      <c r="W5" t="s">
-        <v>54</v>
-      </c>
-      <c r="X5" t="s">
-        <v>56</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>56</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>54</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>54</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>56</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>55</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>54</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>56</v>
-      </c>
-      <c r="AH5" t="s">
-        <v>54</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>60</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>56</v>
-      </c>
-      <c r="AK5" t="s">
-        <v>60</v>
-      </c>
-      <c r="AL5" t="s">
-        <v>52</v>
-      </c>
-      <c r="AM5" t="s">
-        <v>57</v>
-      </c>
-      <c r="AN5" t="s">
+      <c r="AS5" t="s">
         <v>61</v>
-      </c>
-      <c r="AO5" t="s">
-        <v>62</v>
-      </c>
-      <c r="AP5" t="s">
-        <v>55</v>
-      </c>
-      <c r="AQ5" t="s">
-        <v>58</v>
-      </c>
-      <c r="AR5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AS5" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" t="s">
         <v>54</v>
       </c>
-      <c r="C6" t="s">
+      <c r="F6" t="s">
+        <v>52</v>
+      </c>
+      <c r="G6" t="s">
         <v>54</v>
       </c>
-      <c r="D6" t="s">
+      <c r="H6" t="s">
         <v>54</v>
       </c>
-      <c r="E6" t="s">
-        <v>56</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="I6" t="s">
+        <v>53</v>
+      </c>
+      <c r="J6" t="s">
+        <v>62</v>
+      </c>
+      <c r="K6" t="s">
+        <v>59</v>
+      </c>
+      <c r="L6" t="s">
         <v>54</v>
       </c>
-      <c r="G6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H6" t="s">
-        <v>56</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="M6" t="s">
+        <v>54</v>
+      </c>
+      <c r="N6" t="s">
+        <v>54</v>
+      </c>
+      <c r="O6" t="s">
+        <v>53</v>
+      </c>
+      <c r="P6" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>54</v>
+      </c>
+      <c r="R6" t="s">
+        <v>53</v>
+      </c>
+      <c r="S6" t="s">
+        <v>54</v>
+      </c>
+      <c r="T6" t="s">
+        <v>53</v>
+      </c>
+      <c r="U6" t="s">
+        <v>59</v>
+      </c>
+      <c r="V6" t="s">
+        <v>52</v>
+      </c>
+      <c r="W6" t="s">
+        <v>59</v>
+      </c>
+      <c r="X6" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>59</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AK6" t="s">
         <v>55</v>
       </c>
-      <c r="J6" t="s">
+      <c r="AL6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AN6" t="s">
         <v>65</v>
       </c>
-      <c r="K6" t="s">
-        <v>62</v>
-      </c>
-      <c r="L6" t="s">
-        <v>56</v>
-      </c>
-      <c r="M6" t="s">
-        <v>56</v>
-      </c>
-      <c r="N6" t="s">
-        <v>56</v>
-      </c>
-      <c r="O6" t="s">
-        <v>55</v>
-      </c>
-      <c r="P6" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>56</v>
-      </c>
-      <c r="R6" t="s">
-        <v>55</v>
-      </c>
-      <c r="S6" t="s">
-        <v>56</v>
-      </c>
-      <c r="T6" t="s">
-        <v>55</v>
-      </c>
-      <c r="U6" t="s">
-        <v>62</v>
-      </c>
-      <c r="V6" t="s">
-        <v>54</v>
-      </c>
-      <c r="W6" t="s">
-        <v>62</v>
-      </c>
-      <c r="X6" t="s">
-        <v>60</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>55</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>55</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>55</v>
-      </c>
-      <c r="AD6" t="s">
+      <c r="AO6" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP6" t="s">
         <v>66</v>
       </c>
-      <c r="AE6" t="s">
+      <c r="AQ6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AS6" t="s">
         <v>67</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>55</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>66</v>
-      </c>
-      <c r="AH6" t="s">
-        <v>55</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>62</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>55</v>
-      </c>
-      <c r="AK6" t="s">
-        <v>57</v>
-      </c>
-      <c r="AL6" t="s">
-        <v>56</v>
-      </c>
-      <c r="AM6" t="s">
-        <v>63</v>
-      </c>
-      <c r="AN6" t="s">
-        <v>68</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>64</v>
-      </c>
-      <c r="AP6" t="s">
-        <v>69</v>
-      </c>
-      <c r="AQ6" t="s">
-        <v>61</v>
-      </c>
-      <c r="AR6" t="s">
-        <v>69</v>
-      </c>
-      <c r="AS6" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" t="s">
+        <v>57</v>
+      </c>
+      <c r="F7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G7" t="s">
+        <v>57</v>
+      </c>
+      <c r="H7" t="s">
+        <v>59</v>
+      </c>
+      <c r="I7" t="s">
+        <v>59</v>
+      </c>
+      <c r="J7" t="s">
+        <v>56</v>
+      </c>
+      <c r="K7" t="s">
+        <v>63</v>
+      </c>
+      <c r="L7" t="s">
+        <v>59</v>
+      </c>
+      <c r="M7" t="s">
+        <v>59</v>
+      </c>
+      <c r="N7" t="s">
+        <v>53</v>
+      </c>
+      <c r="O7" t="s">
+        <v>55</v>
+      </c>
+      <c r="P7" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>53</v>
+      </c>
+      <c r="R7" t="s">
+        <v>59</v>
+      </c>
+      <c r="S7" t="s">
+        <v>63</v>
+      </c>
+      <c r="T7" t="s">
+        <v>62</v>
+      </c>
+      <c r="U7" t="s">
+        <v>55</v>
+      </c>
+      <c r="V7" t="s">
+        <v>54</v>
+      </c>
+      <c r="W7" t="s">
+        <v>63</v>
+      </c>
+      <c r="X7" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>59</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>68</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG7" t="s">
         <v>60</v>
       </c>
-      <c r="B7" t="s">
+      <c r="AH7" t="s">
+        <v>55</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>55</v>
+      </c>
+      <c r="AJ7" t="s">
         <v>56</v>
       </c>
-      <c r="C7" t="s">
+      <c r="AK7" t="s">
+        <v>68</v>
+      </c>
+      <c r="AL7" t="s">
         <v>56</v>
       </c>
-      <c r="D7" t="s">
-        <v>56</v>
-      </c>
-      <c r="E7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F7" t="s">
-        <v>62</v>
-      </c>
-      <c r="G7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H7" t="s">
-        <v>62</v>
-      </c>
-      <c r="I7" t="s">
-        <v>62</v>
-      </c>
-      <c r="J7" t="s">
-        <v>58</v>
-      </c>
-      <c r="K7" t="s">
+      <c r="AM7" t="s">
         <v>66</v>
       </c>
-      <c r="L7" t="s">
-        <v>62</v>
-      </c>
-      <c r="M7" t="s">
-        <v>62</v>
-      </c>
-      <c r="N7" t="s">
-        <v>55</v>
-      </c>
-      <c r="O7" t="s">
-        <v>57</v>
-      </c>
-      <c r="P7" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>55</v>
-      </c>
-      <c r="R7" t="s">
-        <v>62</v>
-      </c>
-      <c r="S7" t="s">
-        <v>66</v>
-      </c>
-      <c r="T7" t="s">
-        <v>65</v>
-      </c>
-      <c r="U7" t="s">
-        <v>57</v>
-      </c>
-      <c r="V7" t="s">
-        <v>56</v>
-      </c>
-      <c r="W7" t="s">
-        <v>66</v>
-      </c>
-      <c r="X7" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>62</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>62</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>66</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD7" t="s">
+      <c r="AN7" t="s">
+        <v>69</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>67</v>
+      </c>
+      <c r="AP7" t="s">
+        <v>70</v>
+      </c>
+      <c r="AQ7" t="s">
         <v>71</v>
       </c>
-      <c r="AE7" t="s">
-        <v>69</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>66</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>63</v>
-      </c>
-      <c r="AH7" t="s">
-        <v>57</v>
-      </c>
-      <c r="AI7" t="s">
-        <v>57</v>
-      </c>
-      <c r="AJ7" t="s">
-        <v>58</v>
-      </c>
-      <c r="AK7" t="s">
-        <v>71</v>
-      </c>
-      <c r="AL7" t="s">
-        <v>58</v>
-      </c>
-      <c r="AM7" t="s">
-        <v>69</v>
-      </c>
-      <c r="AN7" t="s">
+      <c r="AR7" t="s">
         <v>72</v>
       </c>
-      <c r="AO7" t="s">
-        <v>70</v>
-      </c>
-      <c r="AP7" t="s">
+      <c r="AS7" t="s">
         <v>73</v>
-      </c>
-      <c r="AQ7" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR7" t="s">
-        <v>75</v>
-      </c>
-      <c r="AS7" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" t="s">
         <v>55</v>
       </c>
-      <c r="B8" t="s">
+      <c r="G8" t="s">
         <v>55</v>
       </c>
-      <c r="C8" t="s">
-        <v>62</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="H8" t="s">
+        <v>63</v>
+      </c>
+      <c r="I8" t="s">
+        <v>63</v>
+      </c>
+      <c r="J8" t="s">
         <v>55</v>
       </c>
-      <c r="E8" t="s">
+      <c r="K8" t="s">
         <v>55</v>
       </c>
-      <c r="F8" t="s">
-        <v>57</v>
-      </c>
-      <c r="G8" t="s">
-        <v>57</v>
-      </c>
-      <c r="H8" t="s">
+      <c r="L8" t="s">
+        <v>68</v>
+      </c>
+      <c r="M8" t="s">
+        <v>64</v>
+      </c>
+      <c r="N8" t="s">
+        <v>55</v>
+      </c>
+      <c r="O8" t="s">
+        <v>52</v>
+      </c>
+      <c r="P8" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>63</v>
+      </c>
+      <c r="R8" t="s">
+        <v>63</v>
+      </c>
+      <c r="S8" t="s">
+        <v>55</v>
+      </c>
+      <c r="T8" t="s">
+        <v>59</v>
+      </c>
+      <c r="U8" t="s">
+        <v>74</v>
+      </c>
+      <c r="V8" t="s">
+        <v>63</v>
+      </c>
+      <c r="W8" t="s">
+        <v>56</v>
+      </c>
+      <c r="X8" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA8" t="s">
         <v>66</v>
       </c>
-      <c r="I8" t="s">
+      <c r="AB8" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>75</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK8" t="s">
         <v>66</v>
       </c>
-      <c r="J8" t="s">
-        <v>57</v>
-      </c>
-      <c r="K8" t="s">
-        <v>57</v>
-      </c>
-      <c r="L8" t="s">
-        <v>71</v>
-      </c>
-      <c r="M8" t="s">
-        <v>67</v>
-      </c>
-      <c r="N8" t="s">
-        <v>57</v>
-      </c>
-      <c r="O8" t="s">
-        <v>54</v>
-      </c>
-      <c r="P8" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>66</v>
-      </c>
-      <c r="R8" t="s">
-        <v>66</v>
-      </c>
-      <c r="S8" t="s">
-        <v>57</v>
-      </c>
-      <c r="T8" t="s">
-        <v>62</v>
-      </c>
-      <c r="U8" t="s">
+      <c r="AL8" t="s">
+        <v>68</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>76</v>
+      </c>
+      <c r="AN8" t="s">
         <v>77</v>
-      </c>
-      <c r="V8" t="s">
-        <v>66</v>
-      </c>
-      <c r="W8" t="s">
-        <v>58</v>
-      </c>
-      <c r="X8" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>66</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>57</v>
-      </c>
-      <c r="AC8" t="s">
-        <v>67</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>61</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>59</v>
-      </c>
-      <c r="AG8" t="s">
-        <v>78</v>
-      </c>
-      <c r="AH8" t="s">
-        <v>67</v>
-      </c>
-      <c r="AI8" t="s">
-        <v>63</v>
-      </c>
-      <c r="AJ8" t="s">
-        <v>71</v>
-      </c>
-      <c r="AK8" t="s">
-        <v>69</v>
-      </c>
-      <c r="AL8" t="s">
-        <v>71</v>
-      </c>
-      <c r="AM8" t="s">
-        <v>79</v>
-      </c>
-      <c r="AN8" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F9" t="s">
+        <v>60</v>
+      </c>
+      <c r="G9" t="s">
+        <v>63</v>
+      </c>
+      <c r="H9" t="s">
+        <v>55</v>
+      </c>
+      <c r="I9" t="s">
+        <v>68</v>
+      </c>
+      <c r="J9" t="s">
         <v>66</v>
       </c>
-      <c r="B9" t="s">
+      <c r="K9" t="s">
+        <v>68</v>
+      </c>
+      <c r="L9" t="s">
+        <v>60</v>
+      </c>
+      <c r="M9" t="s">
+        <v>74</v>
+      </c>
+      <c r="N9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O9" t="s">
+        <v>68</v>
+      </c>
+      <c r="P9" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>68</v>
+      </c>
+      <c r="R9" t="s">
+        <v>68</v>
+      </c>
+      <c r="S9" t="s">
+        <v>60</v>
+      </c>
+      <c r="T9" t="s">
+        <v>68</v>
+      </c>
+      <c r="U9" t="s">
+        <v>60</v>
+      </c>
+      <c r="V9" t="s">
+        <v>60</v>
+      </c>
+      <c r="W9" t="s">
+        <v>68</v>
+      </c>
+      <c r="X9" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>68</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>68</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>75</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>68</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>79</v>
+      </c>
+      <c r="AK9" t="s">
         <v>65</v>
       </c>
-      <c r="C9" t="s">
-        <v>58</v>
-      </c>
-      <c r="D9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F9" t="s">
-        <v>63</v>
-      </c>
-      <c r="G9" t="s">
-        <v>66</v>
-      </c>
-      <c r="H9" t="s">
-        <v>57</v>
-      </c>
-      <c r="I9" t="s">
-        <v>71</v>
-      </c>
-      <c r="J9" t="s">
-        <v>69</v>
-      </c>
-      <c r="K9" t="s">
-        <v>71</v>
-      </c>
-      <c r="L9" t="s">
-        <v>63</v>
-      </c>
-      <c r="M9" t="s">
-        <v>77</v>
-      </c>
-      <c r="N9" t="s">
-        <v>71</v>
-      </c>
-      <c r="O9" t="s">
-        <v>71</v>
-      </c>
-      <c r="P9" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>71</v>
-      </c>
-      <c r="R9" t="s">
-        <v>71</v>
-      </c>
-      <c r="S9" t="s">
-        <v>63</v>
-      </c>
-      <c r="T9" t="s">
-        <v>71</v>
-      </c>
-      <c r="U9" t="s">
-        <v>63</v>
-      </c>
-      <c r="V9" t="s">
-        <v>63</v>
-      </c>
-      <c r="W9" t="s">
-        <v>71</v>
-      </c>
-      <c r="X9" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>71</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>71</v>
-      </c>
-      <c r="AA9" t="s">
+      <c r="AL9" t="s">
         <v>61</v>
       </c>
-      <c r="AB9" t="s">
-        <v>71</v>
-      </c>
-      <c r="AC9" t="s">
-        <v>71</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>81</v>
-      </c>
-      <c r="AE9" t="s">
-        <v>78</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>61</v>
-      </c>
-      <c r="AG9" t="s">
-        <v>64</v>
-      </c>
-      <c r="AH9" t="s">
-        <v>71</v>
-      </c>
-      <c r="AI9" t="s">
-        <v>82</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>82</v>
-      </c>
-      <c r="AK9" t="s">
-        <v>68</v>
-      </c>
-      <c r="AL9" t="s">
-        <v>64</v>
-      </c>
       <c r="AM9" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" t="s">
         <v>66</v>
       </c>
-      <c r="C10" t="s">
-        <v>63</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" t="s">
+        <v>80</v>
+      </c>
+      <c r="G10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H10" t="s">
+        <v>68</v>
+      </c>
+      <c r="I10" t="s">
+        <v>66</v>
+      </c>
+      <c r="J10" t="s">
+        <v>58</v>
+      </c>
+      <c r="K10" t="s">
+        <v>60</v>
+      </c>
+      <c r="L10" t="s">
+        <v>66</v>
+      </c>
+      <c r="M10" t="s">
+        <v>60</v>
+      </c>
+      <c r="N10" t="s">
+        <v>66</v>
+      </c>
+      <c r="O10" t="s">
+        <v>66</v>
+      </c>
+      <c r="P10" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>60</v>
+      </c>
+      <c r="R10" t="s">
+        <v>80</v>
+      </c>
+      <c r="S10" t="s">
+        <v>58</v>
+      </c>
+      <c r="T10" t="s">
+        <v>66</v>
+      </c>
+      <c r="U10" t="s">
+        <v>58</v>
+      </c>
+      <c r="V10" t="s">
+        <v>81</v>
+      </c>
+      <c r="W10" t="s">
+        <v>80</v>
+      </c>
+      <c r="X10" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>65</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>81</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>76</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>71</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>78</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>60</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AM10" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" t="s">
+        <v>68</v>
+      </c>
+      <c r="F11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11" t="s">
+        <v>74</v>
+      </c>
+      <c r="H11" t="s">
+        <v>60</v>
+      </c>
+      <c r="I11" t="s">
+        <v>82</v>
+      </c>
+      <c r="J11" t="s">
+        <v>61</v>
+      </c>
+      <c r="K11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L11" t="s">
+        <v>81</v>
+      </c>
+      <c r="M11" t="s">
+        <v>58</v>
+      </c>
+      <c r="N11" t="s">
+        <v>58</v>
+      </c>
+      <c r="O11" t="s">
+        <v>58</v>
+      </c>
+      <c r="P11" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>66</v>
+      </c>
+      <c r="R11" t="s">
+        <v>58</v>
+      </c>
+      <c r="S11" t="s">
+        <v>75</v>
+      </c>
+      <c r="T11" t="s">
+        <v>58</v>
+      </c>
+      <c r="U11" t="s">
+        <v>65</v>
+      </c>
+      <c r="V11" t="s">
+        <v>61</v>
+      </c>
+      <c r="W11" t="s">
+        <v>79</v>
+      </c>
+      <c r="X11" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>81</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>81</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>83</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>82</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>53</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>83</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>71</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK11" t="s">
         <v>69</v>
       </c>
-      <c r="E10" t="s">
-        <v>54</v>
-      </c>
-      <c r="F10" t="s">
-        <v>83</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="AL11" t="s">
+        <v>84</v>
+      </c>
+      <c r="AM11" t="s">
         <v>71</v>
       </c>
-      <c r="H10" t="s">
-        <v>71</v>
-      </c>
-      <c r="I10" t="s">
-        <v>69</v>
-      </c>
-      <c r="J10" t="s">
-        <v>61</v>
-      </c>
-      <c r="K10" t="s">
-        <v>63</v>
-      </c>
-      <c r="L10" t="s">
-        <v>69</v>
-      </c>
-      <c r="M10" t="s">
-        <v>63</v>
-      </c>
-      <c r="N10" t="s">
-        <v>69</v>
-      </c>
-      <c r="O10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>63</v>
-      </c>
-      <c r="R10" t="s">
-        <v>83</v>
-      </c>
-      <c r="S10" t="s">
-        <v>61</v>
-      </c>
-      <c r="T10" t="s">
-        <v>69</v>
-      </c>
-      <c r="U10" t="s">
-        <v>61</v>
-      </c>
-      <c r="V10" t="s">
-        <v>84</v>
-      </c>
-      <c r="W10" t="s">
-        <v>83</v>
-      </c>
-      <c r="X10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>68</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>68</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>77</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>84</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>79</v>
-      </c>
-      <c r="AE10" t="s">
-        <v>82</v>
-      </c>
-      <c r="AF10" t="s">
+    </row>
+    <row r="12" ht="15" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" t="s">
+        <v>60</v>
+      </c>
+      <c r="F12" t="s">
         <v>81</v>
       </c>
-      <c r="AG10" t="s">
-        <v>81</v>
-      </c>
-      <c r="AH10" t="s">
-        <v>63</v>
-      </c>
-      <c r="AI10" t="s">
-        <v>84</v>
-      </c>
-      <c r="AJ10" t="s">
-        <v>68</v>
-      </c>
-      <c r="AK10" t="s">
-        <v>82</v>
-      </c>
-      <c r="AL10" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>71</v>
-      </c>
-      <c r="B11" t="s">
-        <v>63</v>
-      </c>
-      <c r="C11" t="s">
-        <v>69</v>
-      </c>
-      <c r="D11" t="s">
-        <v>61</v>
-      </c>
-      <c r="E11" t="s">
-        <v>71</v>
-      </c>
-      <c r="F11" t="s">
-        <v>61</v>
-      </c>
-      <c r="G11" t="s">
-        <v>77</v>
-      </c>
-      <c r="H11" t="s">
-        <v>63</v>
-      </c>
-      <c r="I11" t="s">
-        <v>59</v>
-      </c>
-      <c r="J11" t="s">
-        <v>64</v>
-      </c>
-      <c r="K11" t="s">
-        <v>61</v>
-      </c>
-      <c r="L11" t="s">
-        <v>84</v>
-      </c>
-      <c r="M11" t="s">
-        <v>61</v>
-      </c>
-      <c r="N11" t="s">
-        <v>61</v>
-      </c>
-      <c r="O11" t="s">
-        <v>61</v>
-      </c>
-      <c r="P11" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>69</v>
-      </c>
-      <c r="R11" t="s">
-        <v>61</v>
-      </c>
-      <c r="S11" t="s">
-        <v>78</v>
-      </c>
-      <c r="T11" t="s">
-        <v>61</v>
-      </c>
-      <c r="U11" t="s">
-        <v>68</v>
-      </c>
-      <c r="V11" t="s">
-        <v>64</v>
-      </c>
-      <c r="W11" t="s">
-        <v>82</v>
-      </c>
-      <c r="X11" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>61</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>84</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>84</v>
-      </c>
-      <c r="AB11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AC11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>85</v>
-      </c>
-      <c r="AE11" t="s">
-        <v>72</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>74</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>55</v>
-      </c>
-      <c r="AH11" t="s">
-        <v>59</v>
-      </c>
-      <c r="AI11" t="s">
-        <v>74</v>
-      </c>
-      <c r="AJ11" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK11" t="s">
-        <v>72</v>
-      </c>
-      <c r="AL11" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>63</v>
-      </c>
-      <c r="B12" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" t="s">
-        <v>61</v>
-      </c>
-      <c r="D12" t="s">
-        <v>68</v>
-      </c>
-      <c r="E12" t="s">
-        <v>63</v>
-      </c>
-      <c r="F12" t="s">
-        <v>84</v>
-      </c>
       <c r="G12" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H12" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I12" t="s">
         <v>82</v>
       </c>
       <c r="J12" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K12" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="L12" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="M12" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="N12" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="O12" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="P12" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="Q12" t="s">
+        <v>69</v>
+      </c>
+      <c r="R12" t="s">
+        <v>79</v>
+      </c>
+      <c r="S12" t="s">
+        <v>78</v>
+      </c>
+      <c r="T12" t="s">
+        <v>61</v>
+      </c>
+      <c r="U12" t="s">
+        <v>61</v>
+      </c>
+      <c r="V12" t="s">
+        <v>78</v>
+      </c>
+      <c r="W12" t="s">
+        <v>78</v>
+      </c>
+      <c r="X12" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>71</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>67</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF12" t="s">
         <v>72</v>
       </c>
-      <c r="R12" t="s">
-        <v>82</v>
-      </c>
-      <c r="S12" t="s">
-        <v>81</v>
-      </c>
-      <c r="T12" t="s">
-        <v>64</v>
-      </c>
-      <c r="U12" t="s">
-        <v>64</v>
-      </c>
-      <c r="V12" t="s">
-        <v>81</v>
-      </c>
-      <c r="W12" t="s">
-        <v>81</v>
-      </c>
-      <c r="X12" t="s">
-        <v>81</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>68</v>
-      </c>
-      <c r="Z12" t="s">
-        <v>82</v>
-      </c>
-      <c r="AA12" t="s">
+      <c r="AG12" t="s">
+        <v>69</v>
+      </c>
+      <c r="AH12" t="s">
         <v>72</v>
       </c>
-      <c r="AB12" t="s">
+      <c r="AI12" t="s">
         <v>72</v>
       </c>
-      <c r="AC12" t="s">
-        <v>74</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>70</v>
-      </c>
-      <c r="AE12" t="s">
+      <c r="AJ12" t="s">
+        <v>83</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>85</v>
+      </c>
+      <c r="AL12" t="s">
         <v>73</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AG12" t="s">
-        <v>72</v>
-      </c>
-      <c r="AH12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AI12" t="s">
-        <v>75</v>
-      </c>
-      <c r="AJ12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AK12" t="s">
-        <v>87</v>
-      </c>
-      <c r="AL12" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" t="s">
+        <v>81</v>
+      </c>
+      <c r="E13" t="s">
+        <v>65</v>
+      </c>
+      <c r="F13" t="s">
+        <v>61</v>
+      </c>
+      <c r="G13" t="s">
+        <v>61</v>
+      </c>
+      <c r="H13" t="s">
+        <v>65</v>
+      </c>
+      <c r="I13" t="s">
+        <v>82</v>
+      </c>
+      <c r="J13" t="s">
         <v>69</v>
       </c>
-      <c r="B13" t="s">
+      <c r="K13" t="s">
+        <v>78</v>
+      </c>
+      <c r="L13" t="s">
+        <v>76</v>
+      </c>
+      <c r="M13" t="s">
+        <v>68</v>
+      </c>
+      <c r="N13" t="s">
         <v>61</v>
       </c>
-      <c r="C13" t="s">
-        <v>68</v>
-      </c>
-      <c r="D13" t="s">
-        <v>84</v>
-      </c>
-      <c r="E13" t="s">
-        <v>68</v>
-      </c>
-      <c r="F13" t="s">
-        <v>64</v>
-      </c>
-      <c r="G13" t="s">
-        <v>64</v>
-      </c>
-      <c r="H13" t="s">
-        <v>68</v>
-      </c>
-      <c r="I13" t="s">
-        <v>81</v>
-      </c>
-      <c r="J13" t="s">
+      <c r="O13" t="s">
+        <v>69</v>
+      </c>
+      <c r="P13" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>71</v>
+      </c>
+      <c r="R13" t="s">
+        <v>78</v>
+      </c>
+      <c r="S13" t="s">
+        <v>71</v>
+      </c>
+      <c r="T13" t="s">
+        <v>69</v>
+      </c>
+      <c r="U13" t="s">
+        <v>71</v>
+      </c>
+      <c r="V13" t="s">
+        <v>58</v>
+      </c>
+      <c r="W13" t="s">
+        <v>71</v>
+      </c>
+      <c r="X13" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>71</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>77</v>
+      </c>
+      <c r="AE13" t="s">
         <v>72</v>
       </c>
-      <c r="K13" t="s">
-        <v>81</v>
-      </c>
-      <c r="L13" t="s">
-        <v>79</v>
-      </c>
-      <c r="M13" t="s">
-        <v>71</v>
-      </c>
-      <c r="N13" t="s">
-        <v>64</v>
-      </c>
-      <c r="O13" t="s">
+      <c r="AF13" t="s">
+        <v>67</v>
+      </c>
+      <c r="AG13" t="s">
         <v>72</v>
       </c>
-      <c r="P13" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>74</v>
-      </c>
-      <c r="R13" t="s">
-        <v>81</v>
-      </c>
-      <c r="S13" t="s">
-        <v>74</v>
-      </c>
-      <c r="T13" t="s">
-        <v>72</v>
-      </c>
-      <c r="U13" t="s">
-        <v>74</v>
-      </c>
-      <c r="V13" t="s">
-        <v>61</v>
-      </c>
-      <c r="W13" t="s">
-        <v>74</v>
-      </c>
-      <c r="X13" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z13" t="s">
-        <v>74</v>
-      </c>
-      <c r="AA13" t="s">
-        <v>74</v>
-      </c>
-      <c r="AB13" t="s">
-        <v>73</v>
-      </c>
-      <c r="AC13" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>80</v>
-      </c>
-      <c r="AE13" t="s">
-        <v>75</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>75</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>75</v>
-      </c>
       <c r="AH13" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI13" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="AJ13" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="AK13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" t="s">
         <v>61</v>
       </c>
-      <c r="B14" t="s">
+      <c r="E14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F14" t="s">
         <v>78</v>
       </c>
-      <c r="C14" t="s">
+      <c r="G14" t="s">
+        <v>78</v>
+      </c>
+      <c r="H14" t="s">
+        <v>61</v>
+      </c>
+      <c r="I14" t="s">
+        <v>83</v>
+      </c>
+      <c r="J14" t="s">
+        <v>71</v>
+      </c>
+      <c r="K14" t="s">
+        <v>71</v>
+      </c>
+      <c r="L14" t="s">
+        <v>83</v>
+      </c>
+      <c r="M14" t="s">
+        <v>71</v>
+      </c>
+      <c r="N14" t="s">
+        <v>69</v>
+      </c>
+      <c r="O14" t="s">
+        <v>71</v>
+      </c>
+      <c r="P14" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>76</v>
+      </c>
+      <c r="R14" t="s">
+        <v>83</v>
+      </c>
+      <c r="S14" t="s">
+        <v>83</v>
+      </c>
+      <c r="T14" t="s">
+        <v>70</v>
+      </c>
+      <c r="U14" t="s">
+        <v>70</v>
+      </c>
+      <c r="V14" t="s">
+        <v>69</v>
+      </c>
+      <c r="W14" t="s">
+        <v>83</v>
+      </c>
+      <c r="X14" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>67</v>
+      </c>
+      <c r="AD14" t="s">
         <v>84</v>
       </c>
-      <c r="D14" t="s">
-        <v>64</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="AE14" t="s">
+        <v>67</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AG14" t="s">
         <v>84</v>
       </c>
-      <c r="F14" t="s">
-        <v>81</v>
-      </c>
-      <c r="G14" t="s">
-        <v>81</v>
-      </c>
-      <c r="H14" t="s">
-        <v>64</v>
-      </c>
-      <c r="I14" t="s">
-        <v>74</v>
-      </c>
-      <c r="J14" t="s">
-        <v>74</v>
-      </c>
-      <c r="K14" t="s">
-        <v>74</v>
-      </c>
-      <c r="L14" t="s">
-        <v>85</v>
-      </c>
-      <c r="M14" t="s">
-        <v>74</v>
-      </c>
-      <c r="N14" t="s">
-        <v>72</v>
-      </c>
-      <c r="O14" t="s">
-        <v>74</v>
-      </c>
-      <c r="P14" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>79</v>
-      </c>
-      <c r="R14" t="s">
-        <v>85</v>
-      </c>
-      <c r="S14" t="s">
-        <v>85</v>
-      </c>
-      <c r="T14" t="s">
-        <v>73</v>
-      </c>
-      <c r="U14" t="s">
-        <v>73</v>
-      </c>
-      <c r="V14" t="s">
-        <v>72</v>
-      </c>
-      <c r="W14" t="s">
-        <v>85</v>
-      </c>
-      <c r="X14" t="s">
-        <v>73</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>73</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB14" t="s">
-        <v>85</v>
-      </c>
-      <c r="AC14" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD14" t="s">
+      <c r="AH14" t="s">
+        <v>69</v>
+      </c>
+      <c r="AI14" t="s">
         <v>86</v>
       </c>
-      <c r="AE14" t="s">
-        <v>70</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG14" t="s">
+      <c r="AJ14" t="s">
         <v>86</v>
       </c>
-      <c r="AH14" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI14" t="s">
-        <v>88</v>
-      </c>
-      <c r="AJ14" t="s">
-        <v>88</v>
-      </c>
       <c r="AK14" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B15" t="s">
+        <v>81</v>
+      </c>
+      <c r="C15" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F15" t="s">
+        <v>71</v>
+      </c>
+      <c r="G15" t="s">
+        <v>69</v>
+      </c>
+      <c r="H15" t="s">
+        <v>71</v>
+      </c>
+      <c r="I15" t="s">
+        <v>87</v>
+      </c>
+      <c r="J15" t="s">
+        <v>85</v>
+      </c>
+      <c r="K15" t="s">
+        <v>76</v>
+      </c>
+      <c r="L15" t="s">
+        <v>72</v>
+      </c>
+      <c r="M15" t="s">
+        <v>76</v>
+      </c>
+      <c r="N15" t="s">
+        <v>76</v>
+      </c>
+      <c r="O15" t="s">
+        <v>76</v>
+      </c>
+      <c r="P15" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>83</v>
+      </c>
+      <c r="R15" t="s">
+        <v>72</v>
+      </c>
+      <c r="S15" t="s">
+        <v>72</v>
+      </c>
+      <c r="T15" t="s">
+        <v>83</v>
+      </c>
+      <c r="U15" t="s">
+        <v>83</v>
+      </c>
+      <c r="V15" t="s">
+        <v>76</v>
+      </c>
+      <c r="W15" t="s">
+        <v>87</v>
+      </c>
+      <c r="X15" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>83</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>73</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>86</v>
+      </c>
+      <c r="AF15" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>73</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>81</v>
+      </c>
+      <c r="B16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" t="s">
+        <v>69</v>
+      </c>
+      <c r="F16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G16" t="s">
+        <v>71</v>
+      </c>
+      <c r="H16" t="s">
+        <v>70</v>
+      </c>
+      <c r="I16" t="s">
+        <v>72</v>
+      </c>
+      <c r="J16" t="s">
+        <v>76</v>
+      </c>
+      <c r="K16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M16" t="s">
+        <v>83</v>
+      </c>
+      <c r="N16" t="s">
+        <v>70</v>
+      </c>
+      <c r="O16" t="s">
+        <v>70</v>
+      </c>
+      <c r="P16" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>72</v>
+      </c>
+      <c r="R16" t="s">
+        <v>67</v>
+      </c>
+      <c r="S16" t="s">
+        <v>86</v>
+      </c>
+      <c r="T16" t="s">
+        <v>67</v>
+      </c>
+      <c r="U16" t="s">
+        <v>67</v>
+      </c>
+      <c r="V16" t="s">
+        <v>70</v>
+      </c>
+      <c r="W16" t="s">
+        <v>72</v>
+      </c>
+      <c r="X16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB16" t="s">
         <v>84</v>
       </c>
-      <c r="C15" t="s">
-        <v>64</v>
-      </c>
-      <c r="D15" t="s">
-        <v>81</v>
-      </c>
-      <c r="E15" t="s">
-        <v>64</v>
-      </c>
-      <c r="F15" t="s">
-        <v>74</v>
-      </c>
-      <c r="G15" t="s">
-        <v>72</v>
-      </c>
-      <c r="H15" t="s">
-        <v>74</v>
-      </c>
-      <c r="I15" t="s">
-        <v>85</v>
-      </c>
-      <c r="J15" t="s">
-        <v>87</v>
-      </c>
-      <c r="K15" t="s">
-        <v>79</v>
-      </c>
-      <c r="L15" t="s">
-        <v>75</v>
-      </c>
-      <c r="M15" t="s">
-        <v>79</v>
-      </c>
-      <c r="N15" t="s">
-        <v>79</v>
-      </c>
-      <c r="O15" t="s">
-        <v>79</v>
-      </c>
-      <c r="P15" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>85</v>
-      </c>
-      <c r="R15" t="s">
-        <v>75</v>
-      </c>
-      <c r="S15" t="s">
-        <v>75</v>
-      </c>
-      <c r="T15" t="s">
-        <v>85</v>
-      </c>
-      <c r="U15" t="s">
-        <v>85</v>
-      </c>
-      <c r="V15" t="s">
-        <v>79</v>
-      </c>
-      <c r="W15" t="s">
-        <v>89</v>
-      </c>
-      <c r="X15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y15" t="s">
-        <v>85</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>85</v>
-      </c>
-      <c r="AA15" t="s">
-        <v>70</v>
-      </c>
-      <c r="AB15" t="s">
-        <v>70</v>
-      </c>
-      <c r="AC15" t="s">
-        <v>80</v>
-      </c>
-      <c r="AD15" t="s">
-        <v>76</v>
-      </c>
-      <c r="AE15" t="s">
-        <v>88</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>76</v>
-      </c>
-      <c r="AG15" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>84</v>
-      </c>
-      <c r="B16" t="s">
-        <v>64</v>
-      </c>
-      <c r="C16" t="s">
-        <v>81</v>
-      </c>
-      <c r="D16" t="s">
-        <v>72</v>
-      </c>
-      <c r="E16" t="s">
-        <v>72</v>
-      </c>
-      <c r="F16" t="s">
-        <v>79</v>
-      </c>
-      <c r="G16" t="s">
-        <v>74</v>
-      </c>
-      <c r="H16" t="s">
-        <v>73</v>
-      </c>
-      <c r="I16" t="s">
-        <v>89</v>
-      </c>
-      <c r="J16" t="s">
-        <v>79</v>
-      </c>
-      <c r="K16" t="s">
-        <v>70</v>
-      </c>
-      <c r="L16" t="s">
-        <v>70</v>
-      </c>
-      <c r="M16" t="s">
-        <v>85</v>
-      </c>
-      <c r="N16" t="s">
-        <v>73</v>
-      </c>
-      <c r="O16" t="s">
-        <v>73</v>
-      </c>
-      <c r="P16" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>75</v>
-      </c>
-      <c r="R16" t="s">
-        <v>70</v>
-      </c>
-      <c r="S16" t="s">
-        <v>88</v>
-      </c>
-      <c r="T16" t="s">
-        <v>70</v>
-      </c>
-      <c r="U16" t="s">
-        <v>70</v>
-      </c>
-      <c r="V16" t="s">
-        <v>73</v>
-      </c>
-      <c r="W16" t="s">
-        <v>75</v>
-      </c>
-      <c r="X16" t="s">
-        <v>80</v>
-      </c>
-      <c r="Y16" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z16" t="s">
-        <v>75</v>
-      </c>
-      <c r="AA16" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB16" t="s">
+      <c r="AC16" t="s">
         <v>86</v>
       </c>
-      <c r="AC16" t="s">
-        <v>88</v>
-      </c>
       <c r="AD16" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" t="s">
+        <v>71</v>
+      </c>
+      <c r="E17" t="s">
+        <v>71</v>
+      </c>
+      <c r="F17" t="s">
+        <v>83</v>
+      </c>
+      <c r="G17" t="s">
+        <v>83</v>
+      </c>
+      <c r="H17" t="s">
         <v>72</v>
       </c>
-      <c r="D17" t="s">
-        <v>74</v>
-      </c>
-      <c r="E17" t="s">
-        <v>74</v>
-      </c>
-      <c r="F17" t="s">
-        <v>85</v>
-      </c>
-      <c r="G17" t="s">
-        <v>85</v>
-      </c>
-      <c r="H17" t="s">
-        <v>75</v>
-      </c>
       <c r="I17" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J17" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="K17" t="s">
+        <v>86</v>
+      </c>
+      <c r="L17" t="s">
+        <v>86</v>
+      </c>
+      <c r="M17" t="s">
+        <v>77</v>
+      </c>
+      <c r="N17" t="s">
+        <v>72</v>
+      </c>
+      <c r="O17" t="s">
+        <v>83</v>
+      </c>
+      <c r="P17" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>77</v>
+      </c>
+      <c r="R17" t="s">
+        <v>84</v>
+      </c>
+      <c r="S17" t="s">
         <v>88</v>
       </c>
-      <c r="L17" t="s">
+      <c r="T17" t="s">
+        <v>77</v>
+      </c>
+      <c r="U17" t="s">
+        <v>73</v>
+      </c>
+      <c r="V17" t="s">
         <v>88</v>
       </c>
-      <c r="M17" t="s">
-        <v>80</v>
-      </c>
-      <c r="N17" t="s">
-        <v>75</v>
-      </c>
-      <c r="O17" t="s">
-        <v>85</v>
-      </c>
-      <c r="P17" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>80</v>
-      </c>
-      <c r="R17" t="s">
+      <c r="W17" t="s">
+        <v>77</v>
+      </c>
+      <c r="X17" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA17" t="s">
         <v>86</v>
-      </c>
-      <c r="S17" t="s">
-        <v>90</v>
-      </c>
-      <c r="T17" t="s">
-        <v>80</v>
-      </c>
-      <c r="U17" t="s">
-        <v>76</v>
-      </c>
-      <c r="V17" t="s">
-        <v>90</v>
-      </c>
-      <c r="W17" t="s">
-        <v>80</v>
-      </c>
-      <c r="X17" t="s">
-        <v>76</v>
-      </c>
-      <c r="Y17" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z17" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA17" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" t="s">
+        <v>85</v>
+      </c>
+      <c r="E18" t="s">
+        <v>70</v>
+      </c>
+      <c r="F18" t="s">
+        <v>67</v>
+      </c>
+      <c r="G18" t="s">
         <v>72</v>
       </c>
-      <c r="B18" t="s">
-        <v>72</v>
-      </c>
-      <c r="C18" t="s">
-        <v>74</v>
-      </c>
-      <c r="D18" t="s">
-        <v>87</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="H18" t="s">
+        <v>67</v>
+      </c>
+      <c r="I18" t="s">
         <v>73</v>
       </c>
-      <c r="F18" t="s">
-        <v>70</v>
-      </c>
-      <c r="G18" t="s">
-        <v>75</v>
-      </c>
-      <c r="H18" t="s">
-        <v>70</v>
-      </c>
-      <c r="I18" t="s">
-        <v>80</v>
-      </c>
       <c r="J18" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K18" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L18" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="M18" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="N18" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="O18" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="P18" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="Q18" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C19" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D19" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E19" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F19" t="s">
+        <v>77</v>
+      </c>
+      <c r="G19" t="s">
+        <v>77</v>
+      </c>
+      <c r="H19" t="s">
+        <v>86</v>
+      </c>
+      <c r="I19" t="s">
         <v>80</v>
       </c>
-      <c r="G19" t="s">
-        <v>80</v>
-      </c>
-      <c r="H19" t="s">
-        <v>88</v>
-      </c>
-      <c r="I19" t="s">
-        <v>76</v>
-      </c>
       <c r="J19" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K19" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="L19" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>85</v>
+      </c>
+      <c r="B20" t="s">
+        <v>85</v>
+      </c>
+      <c r="C20" t="s">
+        <v>76</v>
+      </c>
+      <c r="D20" t="s">
+        <v>83</v>
+      </c>
+      <c r="E20" t="s">
+        <v>86</v>
+      </c>
+      <c r="F20" t="s">
+        <v>73</v>
+      </c>
+      <c r="H20" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>83</v>
+      </c>
+      <c r="B21" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" t="s">
+        <v>82</v>
+      </c>
+      <c r="D21" t="s">
         <v>87</v>
       </c>
-      <c r="B20" t="s">
-        <v>87</v>
-      </c>
-      <c r="C20" t="s">
-        <v>79</v>
-      </c>
-      <c r="D20" t="s">
-        <v>85</v>
-      </c>
-      <c r="E20" t="s">
-        <v>88</v>
-      </c>
-      <c r="F20" t="s">
-        <v>76</v>
-      </c>
-      <c r="I20" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>85</v>
-      </c>
-      <c r="B21" t="s">
-        <v>79</v>
-      </c>
-      <c r="C21" t="s">
-        <v>73</v>
-      </c>
-      <c r="D21" t="s">
-        <v>89</v>
-      </c>
       <c r="E21" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F21" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C22" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D22" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B23" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C23" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D23" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>86</v>
+      </c>
+      <c r="B24" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24" t="s">
         <v>88</v>
-      </c>
-      <c r="B24" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D24" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B25" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C25" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D25" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B27" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25"/>
@@ -3470,124 +3462,124 @@
   <sheetData>
     <row r="3" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" t="s">
         <v>50</v>
       </c>
-      <c r="B3" t="s">
+      <c r="E3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" t="s">
         <v>53</v>
       </c>
-      <c r="C3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="I3" t="s">
+        <v>62</v>
+      </c>
+      <c r="J3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K3" t="s">
+        <v>63</v>
+      </c>
+      <c r="L3" t="s">
         <v>56</v>
       </c>
-      <c r="G3" t="s">
+      <c r="M3" t="s">
+        <v>55</v>
+      </c>
+      <c r="N3" t="s">
+        <v>64</v>
+      </c>
+      <c r="O3" t="s">
+        <v>68</v>
+      </c>
+      <c r="P3" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q3" t="s">
         <v>60</v>
       </c>
-      <c r="H3" t="s">
-        <v>55</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="R3" t="s">
+        <v>66</v>
+      </c>
+      <c r="S3" t="s">
+        <v>80</v>
+      </c>
+      <c r="T3" t="s">
+        <v>58</v>
+      </c>
+      <c r="U3" t="s">
+        <v>75</v>
+      </c>
+      <c r="V3" t="s">
         <v>65</v>
       </c>
-      <c r="J3" t="s">
-        <v>62</v>
-      </c>
-      <c r="K3" t="s">
-        <v>66</v>
-      </c>
-      <c r="L3" t="s">
-        <v>58</v>
-      </c>
-      <c r="M3" t="s">
-        <v>57</v>
-      </c>
-      <c r="N3" t="s">
+      <c r="W3" t="s">
+        <v>81</v>
+      </c>
+      <c r="X3" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>71</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>72</v>
+      </c>
+      <c r="AI3" t="s">
         <v>67</v>
       </c>
-      <c r="O3" t="s">
-        <v>71</v>
-      </c>
-      <c r="P3" t="s">
+      <c r="AJ3" t="s">
         <v>77</v>
       </c>
-      <c r="Q3" t="s">
-        <v>63</v>
-      </c>
-      <c r="R3" t="s">
-        <v>69</v>
-      </c>
-      <c r="S3" t="s">
-        <v>83</v>
-      </c>
-      <c r="T3" t="s">
-        <v>61</v>
-      </c>
-      <c r="U3" t="s">
-        <v>78</v>
-      </c>
-      <c r="V3" t="s">
-        <v>68</v>
-      </c>
-      <c r="W3" t="s">
+      <c r="AK3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL3" t="s">
         <v>84</v>
       </c>
-      <c r="X3" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>82</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>81</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>87</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AE3" t="s">
+      <c r="AM3" t="s">
+        <v>88</v>
+      </c>
+      <c r="AN3" t="s">
         <v>73</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>85</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>89</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>70</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>88</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>86</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>90</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
@@ -3613,7 +3605,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>30</v>
+        <v>89</v>
       </c>
       <c r="I4" t="s">
         <v>1</v>
@@ -3631,7 +3623,7 @@
         <v>13</v>
       </c>
       <c r="N4" t="s">
-        <v>30</v>
+        <v>89</v>
       </c>
       <c r="O4" t="s">
         <v>16</v>
@@ -3652,7 +3644,7 @@
         <v>2</v>
       </c>
       <c r="U4" t="s">
-        <v>30</v>
+        <v>89</v>
       </c>
       <c r="V4" t="s">
         <v>13</v>
@@ -3670,7 +3662,7 @@
         <v>2</v>
       </c>
       <c r="AA4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="AB4" t="s">
         <v>16</v>
@@ -4321,10 +4313,10 @@
         <v>11</v>
       </c>
       <c r="Y10" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="Z10" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="AA10" t="s">
         <v>9</v>
@@ -4493,7 +4485,7 @@
         <v>23</v>
       </c>
       <c r="T12" t="s">
-        <v>30</v>
+        <v>89</v>
       </c>
       <c r="V12" t="s">
         <v>0</v>
@@ -4600,7 +4592,7 @@
         <v>1</v>
       </c>
       <c r="AE13" t="s">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="AF13" t="s">
         <v>0</v>
@@ -4671,7 +4663,7 @@
         <v>12</v>
       </c>
       <c r="Z14" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="AA14" t="s">
         <v>14</v>
@@ -4822,7 +4814,7 @@
         <v>33</v>
       </c>
       <c r="R16" t="s">
-        <v>30</v>
+        <v>89</v>
       </c>
       <c r="T16" t="s">
         <v>17</v>
@@ -4837,7 +4829,7 @@
         <v>23</v>
       </c>
       <c r="AA16" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="s">
         <v>2</v>
@@ -4911,7 +4903,7 @@
         <v>10</v>
       </c>
       <c r="AA17" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AB17" t="s">
         <v>3</v>
@@ -4988,7 +4980,7 @@
         <v>26</v>
       </c>
       <c r="AB18" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="AD18" t="s">
         <v>11</v>
@@ -5062,7 +5054,7 @@
         <v>4</v>
       </c>
       <c r="AB19" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="AD19" t="s">
         <v>21</v>
@@ -5141,7 +5133,7 @@
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>89</v>
       </c>
       <c r="C21" t="s">
         <v>7</v>
@@ -5259,7 +5251,7 @@
         <v>29</v>
       </c>
       <c r="H23" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="K23" t="s">
         <v>29</v>
@@ -5438,7 +5430,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="24:36" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="15" customHeight="1" spans="28:36" x14ac:dyDescent="0.25"/>
     <row r="29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5546,592 +5538,589 @@
   <sheetData>
     <row r="3" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" t="s">
         <v>50</v>
       </c>
-      <c r="B3" t="s">
+      <c r="E3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" t="s">
         <v>53</v>
       </c>
-      <c r="C3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="I3" t="s">
+        <v>62</v>
+      </c>
+      <c r="J3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K3" t="s">
+        <v>63</v>
+      </c>
+      <c r="L3" t="s">
         <v>56</v>
       </c>
-      <c r="G3" t="s">
+      <c r="M3" t="s">
+        <v>55</v>
+      </c>
+      <c r="N3" t="s">
+        <v>64</v>
+      </c>
+      <c r="O3" t="s">
+        <v>68</v>
+      </c>
+      <c r="P3" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q3" t="s">
         <v>60</v>
       </c>
-      <c r="H3" t="s">
-        <v>55</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="R3" t="s">
+        <v>66</v>
+      </c>
+      <c r="S3" t="s">
+        <v>80</v>
+      </c>
+      <c r="T3" t="s">
+        <v>58</v>
+      </c>
+      <c r="U3" t="s">
+        <v>75</v>
+      </c>
+      <c r="V3" t="s">
         <v>65</v>
       </c>
-      <c r="J3" t="s">
-        <v>62</v>
-      </c>
-      <c r="K3" t="s">
-        <v>66</v>
-      </c>
-      <c r="L3" t="s">
-        <v>58</v>
-      </c>
-      <c r="M3" t="s">
-        <v>57</v>
-      </c>
-      <c r="N3" t="s">
+      <c r="W3" t="s">
+        <v>81</v>
+      </c>
+      <c r="X3" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>71</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>72</v>
+      </c>
+      <c r="AI3" t="s">
         <v>67</v>
       </c>
-      <c r="O3" t="s">
-        <v>71</v>
-      </c>
-      <c r="P3" t="s">
+      <c r="AJ3" t="s">
         <v>77</v>
       </c>
-      <c r="Q3" t="s">
-        <v>63</v>
-      </c>
-      <c r="R3" t="s">
-        <v>69</v>
-      </c>
-      <c r="S3" t="s">
-        <v>83</v>
-      </c>
-      <c r="T3" t="s">
-        <v>61</v>
-      </c>
-      <c r="U3" t="s">
-        <v>78</v>
-      </c>
-      <c r="V3" t="s">
-        <v>68</v>
-      </c>
-      <c r="W3" t="s">
+      <c r="AK3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL3" t="s">
         <v>84</v>
       </c>
-      <c r="X3" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>82</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>81</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>87</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AE3" t="s">
+      <c r="AM3" t="s">
+        <v>88</v>
+      </c>
+      <c r="AN3" t="s">
         <v>73</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>85</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>89</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>70</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>88</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>86</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>90</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" t="s">
         <v>91</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>92</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>93</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>94</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>95</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>96</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>97</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>98</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>99</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>100</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>101</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>102</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>103</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>104</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>105</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>106</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
         <v>107</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S4" t="s">
         <v>108</v>
       </c>
-      <c r="S4" t="s">
+      <c r="T4" t="s">
         <v>109</v>
       </c>
-      <c r="T4" t="s">
+      <c r="U4" t="s">
         <v>110</v>
       </c>
-      <c r="U4" t="s">
+      <c r="V4" t="s">
         <v>111</v>
       </c>
-      <c r="V4" t="s">
+      <c r="W4" t="s">
         <v>112</v>
       </c>
-      <c r="W4" t="s">
+      <c r="X4" t="s">
         <v>113</v>
       </c>
-      <c r="X4" t="s">
+      <c r="Y4" t="s">
         <v>114</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Z4" t="s">
         <v>115</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AA4" t="s">
         <v>116</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AB4" t="s">
         <v>117</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AC4" t="s">
         <v>118</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AD4" t="s">
         <v>119</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AE4" t="s">
         <v>120</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AF4" t="s">
         <v>121</v>
       </c>
-      <c r="AF4" t="s">
+      <c r="AG4" t="s">
         <v>122</v>
       </c>
-      <c r="AG4" t="s">
+      <c r="AH4" t="s">
         <v>123</v>
       </c>
-      <c r="AH4" t="s">
+      <c r="AI4" t="s">
         <v>124</v>
       </c>
-      <c r="AI4" t="s">
+      <c r="AJ4" t="s">
         <v>125</v>
       </c>
-      <c r="AJ4" t="s">
+      <c r="AK4" t="s">
         <v>126</v>
       </c>
-      <c r="AK4" t="s">
+      <c r="AL4" t="s">
         <v>127</v>
       </c>
-      <c r="AL4" t="s">
+      <c r="AM4" t="s">
         <v>128</v>
       </c>
-      <c r="AM4" t="s">
+      <c r="AN4" t="s">
         <v>129</v>
-      </c>
-      <c r="AN4" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C5" t="s">
         <v>131</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
         <v>132</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>133</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>134</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>135</v>
       </c>
-      <c r="H5" t="s">
+      <c r="J5" t="s">
         <v>136</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>137</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>138</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>139</v>
       </c>
-      <c r="M5" t="s">
+      <c r="O5" t="s">
         <v>140</v>
       </c>
-      <c r="O5" t="s">
+      <c r="Q5" t="s">
         <v>141</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="R5" t="s">
         <v>142</v>
       </c>
-      <c r="R5" t="s">
+      <c r="T5" t="s">
         <v>143</v>
       </c>
-      <c r="T5" t="s">
+      <c r="V5" t="s">
         <v>144</v>
       </c>
-      <c r="V5" t="s">
+      <c r="W5" t="s">
         <v>145</v>
       </c>
-      <c r="W5" t="s">
+      <c r="X5" t="s">
         <v>146</v>
       </c>
-      <c r="X5" t="s">
+      <c r="Y5" t="s">
         <v>147</v>
       </c>
-      <c r="Y5" t="s">
+      <c r="Z5" t="s">
         <v>148</v>
       </c>
-      <c r="Z5" t="s">
+      <c r="AA5" t="s">
         <v>149</v>
       </c>
-      <c r="AA5" t="s">
+      <c r="AB5" t="s">
         <v>150</v>
       </c>
-      <c r="AB5" t="s">
+      <c r="AC5" t="s">
         <v>151</v>
       </c>
-      <c r="AC5" t="s">
+      <c r="AD5" t="s">
         <v>152</v>
       </c>
-      <c r="AD5" t="s">
+      <c r="AE5" t="s">
         <v>153</v>
       </c>
-      <c r="AE5" t="s">
+      <c r="AF5" t="s">
         <v>154</v>
       </c>
-      <c r="AF5" t="s">
+      <c r="AH5" t="s">
         <v>155</v>
       </c>
-      <c r="AH5" t="s">
+      <c r="AI5" t="s">
         <v>156</v>
       </c>
-      <c r="AI5" t="s">
+      <c r="AJ5" t="s">
         <v>157</v>
       </c>
-      <c r="AJ5" t="s">
+      <c r="AK5" t="s">
         <v>158</v>
       </c>
-      <c r="AK5" t="s">
+      <c r="AL5" t="s">
         <v>159</v>
       </c>
-      <c r="AL5" t="s">
+      <c r="AN5" t="s">
         <v>160</v>
-      </c>
-      <c r="AN5" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C6" t="s">
         <v>162</v>
       </c>
-      <c r="C6" t="s">
+      <c r="E6" t="s">
         <v>163</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>164</v>
       </c>
-      <c r="F6" t="s">
+      <c r="H6" t="s">
         <v>165</v>
       </c>
-      <c r="G6" t="s">
+      <c r="J6" t="s">
         <v>166</v>
       </c>
-      <c r="H6" t="s">
+      <c r="K6" t="s">
         <v>167</v>
       </c>
-      <c r="J6" t="s">
+      <c r="M6" t="s">
         <v>168</v>
       </c>
-      <c r="K6" t="s">
+      <c r="O6" t="s">
         <v>169</v>
       </c>
-      <c r="M6" t="s">
+      <c r="Q6" t="s">
         <v>170</v>
       </c>
-      <c r="O6" t="s">
+      <c r="R6" t="s">
         <v>171</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="T6" t="s">
         <v>172</v>
       </c>
-      <c r="R6" t="s">
+      <c r="V6" t="s">
         <v>173</v>
       </c>
-      <c r="T6" t="s">
+      <c r="W6" t="s">
         <v>174</v>
       </c>
-      <c r="V6" t="s">
+      <c r="X6" t="s">
         <v>175</v>
       </c>
-      <c r="W6" t="s">
+      <c r="Z6" t="s">
         <v>176</v>
       </c>
-      <c r="X6" t="s">
+      <c r="AA6" t="s">
         <v>177</v>
       </c>
-      <c r="Z6" t="s">
+      <c r="AB6" t="s">
         <v>178</v>
       </c>
-      <c r="AA6" t="s">
+      <c r="AD6" t="s">
         <v>179</v>
       </c>
-      <c r="AB6" t="s">
+      <c r="AE6" t="s">
         <v>180</v>
       </c>
-      <c r="AD6" t="s">
+      <c r="AF6" t="s">
         <v>181</v>
       </c>
-      <c r="AE6" t="s">
+      <c r="AH6" t="s">
         <v>182</v>
       </c>
-      <c r="AF6" t="s">
+      <c r="AI6" t="s">
         <v>183</v>
       </c>
-      <c r="AH6" t="s">
+      <c r="AJ6" t="s">
         <v>184</v>
       </c>
-      <c r="AI6" t="s">
+      <c r="AK6" t="s">
         <v>185</v>
       </c>
-      <c r="AJ6" t="s">
+      <c r="AL6" t="s">
         <v>186</v>
       </c>
-      <c r="AK6" t="s">
+      <c r="AN6" t="s">
         <v>187</v>
-      </c>
-      <c r="AL6" t="s">
-        <v>188</v>
-      </c>
-      <c r="AN6" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>188</v>
+      </c>
+      <c r="C7" t="s">
+        <v>189</v>
+      </c>
+      <c r="E7" t="s">
         <v>190</v>
       </c>
-      <c r="C7" t="s">
+      <c r="F7" t="s">
         <v>191</v>
       </c>
-      <c r="E7" t="s">
+      <c r="H7" t="s">
         <v>192</v>
       </c>
-      <c r="F7" t="s">
+      <c r="J7" t="s">
         <v>193</v>
       </c>
-      <c r="H7" t="s">
+      <c r="K7" t="s">
         <v>194</v>
       </c>
-      <c r="J7" t="s">
+      <c r="M7" t="s">
         <v>195</v>
       </c>
-      <c r="K7" t="s">
+      <c r="O7" t="s">
         <v>196</v>
       </c>
-      <c r="M7" t="s">
+      <c r="Q7" t="s">
         <v>197</v>
       </c>
-      <c r="O7" t="s">
+      <c r="R7" t="s">
         <v>198</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="T7" t="s">
         <v>199</v>
       </c>
-      <c r="R7" t="s">
+      <c r="V7" t="s">
         <v>200</v>
       </c>
-      <c r="T7" t="s">
+      <c r="X7" t="s">
         <v>201</v>
       </c>
-      <c r="V7" t="s">
+      <c r="Z7" t="s">
         <v>202</v>
       </c>
-      <c r="X7" t="s">
+      <c r="AA7" t="s">
         <v>203</v>
       </c>
-      <c r="Z7" t="s">
+      <c r="AB7" t="s">
         <v>204</v>
       </c>
-      <c r="AA7" t="s">
-        <v>176</v>
-      </c>
-      <c r="AB7" t="s">
+      <c r="AD7" t="s">
         <v>205</v>
       </c>
-      <c r="AD7" t="s">
+      <c r="AE7" t="s">
         <v>206</v>
       </c>
-      <c r="AE7" t="s">
+      <c r="AF7" t="s">
         <v>207</v>
       </c>
-      <c r="AF7" t="s">
+      <c r="AH7" t="s">
         <v>208</v>
       </c>
-      <c r="AH7" t="s">
+      <c r="AI7" t="s">
         <v>209</v>
       </c>
-      <c r="AI7" t="s">
+      <c r="AJ7" t="s">
         <v>210</v>
       </c>
-      <c r="AJ7" t="s">
+      <c r="AN7" t="s">
         <v>211</v>
-      </c>
-      <c r="AN7" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>212</v>
+      </c>
+      <c r="C8" t="s">
         <v>213</v>
       </c>
-      <c r="C8" t="s">
+      <c r="E8" t="s">
         <v>214</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>215</v>
       </c>
-      <c r="F8" t="s">
+      <c r="H8" t="s">
         <v>216</v>
       </c>
-      <c r="H8" t="s">
+      <c r="K8" t="s">
         <v>217</v>
       </c>
-      <c r="K8" t="s">
+      <c r="O8" t="s">
         <v>218</v>
       </c>
-      <c r="O8" t="s">
+      <c r="Q8" t="s">
         <v>219</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="R8" t="s">
         <v>220</v>
       </c>
-      <c r="R8" t="s">
+      <c r="T8" t="s">
         <v>221</v>
       </c>
-      <c r="T8" t="s">
+      <c r="X8" t="s">
         <v>222</v>
       </c>
-      <c r="X8" t="s">
+      <c r="AA8" t="s">
         <v>223</v>
       </c>
-      <c r="AA8" t="s">
+      <c r="AB8" t="s">
         <v>224</v>
       </c>
-      <c r="AB8" t="s">
+      <c r="AF8" t="s">
         <v>225</v>
       </c>
-      <c r="AF8" t="s">
+      <c r="AH8" t="s">
         <v>226</v>
       </c>
-      <c r="AH8" t="s">
+      <c r="AI8" t="s">
         <v>227</v>
       </c>
-      <c r="AI8" t="s">
+      <c r="AJ8" t="s">
         <v>228</v>
-      </c>
-      <c r="AJ8" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>229</v>
+      </c>
+      <c r="E9" t="s">
         <v>230</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>231</v>
       </c>
-      <c r="F9" t="s">
+      <c r="H9" t="s">
         <v>232</v>
       </c>
-      <c r="H9" t="s">
+      <c r="O9" t="s">
         <v>233</v>
       </c>
-      <c r="O9" t="s">
+      <c r="T9" t="s">
         <v>234</v>
       </c>
-      <c r="T9" t="s">
+      <c r="X9" t="s">
         <v>235</v>
       </c>
-      <c r="X9" t="s">
+      <c r="AB9" t="s">
         <v>236</v>
       </c>
-      <c r="AB9" t="s">
+      <c r="AF9" t="s">
         <v>237</v>
       </c>
-      <c r="AF9" t="s">
+      <c r="AI9" t="s">
         <v>238</v>
       </c>
-      <c r="AI9" t="s">
+      <c r="AJ9" t="s">
         <v>239</v>
       </c>
-      <c r="AJ9" t="s">
-        <v>240</v>
-      </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="24:36" x14ac:dyDescent="0.25"/>
+    <row r="10" ht="15" customHeight="1" spans="28:36" x14ac:dyDescent="0.25"/>
     <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="13" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/data/ICEHLdelegacije.xlsx
+++ b/data/ICEHLdelegacije.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17640"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="ICEHL" state="visible" r:id="rId4"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1484" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1481" uniqueCount="241">
   <si>
     <t>PiragicTr</t>
   </si>
@@ -264,24 +264,24 @@
     <t>2024-10-29</t>
   </si>
   <si>
+    <t>2024-11-22</t>
+  </si>
+  <si>
     <t>zbrisano</t>
   </si>
   <si>
-    <t>2024-11-22</t>
-  </si>
-  <si>
     <t>2024-12-01</t>
   </si>
   <si>
+    <t>2024-11-23</t>
+  </si>
+  <si>
     <t>2024-11-16</t>
   </si>
   <si>
     <t>2024-11-30</t>
   </si>
   <si>
-    <t>2024-11-23</t>
-  </si>
-  <si>
     <t>2024-12-03</t>
   </si>
   <si>
@@ -366,7 +366,7 @@
     <t>Merkur Eisstadion Graz;OfnerCh;SternatCh;NotheggerDa;RieckenSi</t>
   </si>
   <si>
-    <t>Tiroler Wasserkraft Arena;NikolicKr;SeewaldEl;NotheggerDa;SeewaldJe</t>
+    <t>Tiroler Wasserkraft Arena;KainbergerJu;SeewaldEl;NotheggerDa;SeewaldJe</t>
   </si>
   <si>
     <t>Gabor Ocskay Eisarena;FichtnerPa;SoosDa;JedlickaPe;MuzsikNo</t>
@@ -636,7 +636,7 @@
     <t>Hala Tivoli;GroznikBo;NagyAt;HribarMa;PuffWo</t>
   </si>
   <si>
-    <t>Eishalle Asiago;RezekGr;SchauerJa;PardatscherUl;ZgoncGa</t>
+    <t>Eishalle Asiago;RezekGr;SchauerJa;HribarMa;PardatscherUl</t>
   </si>
   <si>
     <t>Tiroler Wasserkraft Arena;NikolicKr;OfnerCh;BedynekSe;MartinFl</t>
@@ -691,6 +691,9 @@
   </si>
   <si>
     <t>Tiroler Wasserkraft Arena;KainbergerJu;NikolicMa;MantovaniDa;MartinFl</t>
+  </si>
+  <si>
+    <t>ZBRISANO</t>
   </si>
   <si>
     <t>Eishalle Feldkirch;BernekerTh;SchauerJa;DurmisOt;KoncDa</t>
@@ -1120,16 +1123,16 @@
         <v>24</v>
       </c>
       <c r="C2">
-        <f t="shared" si="0"/>
-        <v>23</v>
+        <f>COUNTIF(C4:C98,"&lt;&gt;")</f>
+        <v>21</v>
       </c>
       <c r="D2">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="E2">
-        <f t="shared" si="0"/>
-        <v>18</v>
+        <f>COUNTIF(E4:E99,"&lt;&gt;")</f>
+        <v>17</v>
       </c>
       <c r="F2">
         <f t="shared" si="0"/>
@@ -1141,11 +1144,11 @@
       </c>
       <c r="H2">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I2">
-        <f>COUNTIF(I4:I99,"&lt;&gt;")</f>
-        <v>16</v>
+        <f>COUNTIF(I4:I96,"&lt;&gt;")</f>
+        <v>13</v>
       </c>
       <c r="J2">
         <f>COUNTIF(J4:J99,"&lt;&gt;")</f>
@@ -1157,7 +1160,7 @@
       </c>
       <c r="L2">
         <f>COUNTIF(L4:L100,"&lt;&gt;")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M2">
         <f>COUNTIF(M4:M99,"&lt;&gt;")</f>
@@ -1237,7 +1240,7 @@
       </c>
       <c r="AF2">
         <f>COUNTIF(AF4:AF99,"&lt;&gt;")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG2">
         <f>COUNTIF(AG4:AG100,"&lt;&gt;")</f>
@@ -1245,7 +1248,7 @@
       </c>
       <c r="AH2">
         <f>COUNTIF(AH4:AH99,"&lt;&gt;")</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AI2">
         <f>COUNTIF(AI4:AI99,"&lt;&gt;")</f>
@@ -1265,7 +1268,7 @@
       </c>
       <c r="AM2">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AN2">
         <f t="shared" si="2"/>
@@ -1281,7 +1284,7 @@
       </c>
       <c r="AQ2">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR2">
         <f t="shared" si="2"/>
@@ -2124,8 +2127,11 @@
       <c r="AN8" t="s">
         <v>77</v>
       </c>
+      <c r="AQ8" t="s">
+        <v>69</v>
+      </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>63</v>
       </c>
@@ -2452,19 +2458,19 @@
         <v>61</v>
       </c>
       <c r="AD11" t="s">
+        <v>82</v>
+      </c>
+      <c r="AE11" t="s">
         <v>83</v>
       </c>
-      <c r="AE11" t="s">
+      <c r="AF11" t="s">
         <v>82</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>83</v>
       </c>
       <c r="AG11" t="s">
         <v>53</v>
       </c>
       <c r="AH11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AI11" t="s">
         <v>71</v>
@@ -2508,7 +2514,7 @@
         <v>66</v>
       </c>
       <c r="I12" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J12" t="s">
         <v>78</v>
@@ -2589,10 +2595,10 @@
         <v>72</v>
       </c>
       <c r="AJ12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AK12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AL12" t="s">
         <v>73</v>
@@ -2624,7 +2630,7 @@
         <v>65</v>
       </c>
       <c r="I13" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="J13" t="s">
         <v>69</v>
@@ -2708,7 +2714,7 @@
         <v>77</v>
       </c>
       <c r="AK13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
@@ -2737,7 +2743,7 @@
         <v>61</v>
       </c>
       <c r="I14" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="J14" t="s">
         <v>71</v>
@@ -2746,7 +2752,7 @@
         <v>71</v>
       </c>
       <c r="L14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M14" t="s">
         <v>71</v>
@@ -2758,16 +2764,16 @@
         <v>71</v>
       </c>
       <c r="P14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q14" t="s">
         <v>76</v>
       </c>
       <c r="R14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T14" t="s">
         <v>70</v>
@@ -2779,7 +2785,7 @@
         <v>69</v>
       </c>
       <c r="W14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X14" t="s">
         <v>70</v>
@@ -2788,13 +2794,13 @@
         <v>70</v>
       </c>
       <c r="Z14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AA14" t="s">
         <v>70</v>
       </c>
       <c r="AB14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC14" t="s">
         <v>67</v>
@@ -2812,13 +2818,13 @@
         <v>84</v>
       </c>
       <c r="AH14" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="AI14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AJ14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AK14" t="s">
         <v>77</v>
@@ -2850,10 +2856,10 @@
         <v>71</v>
       </c>
       <c r="I15" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="J15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K15" t="s">
         <v>76</v>
@@ -2874,7 +2880,7 @@
         <v>70</v>
       </c>
       <c r="Q15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="R15" t="s">
         <v>72</v>
@@ -2883,25 +2889,25 @@
         <v>72</v>
       </c>
       <c r="T15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V15" t="s">
         <v>76</v>
       </c>
       <c r="W15" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="X15" t="s">
         <v>67</v>
       </c>
       <c r="Y15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA15" t="s">
         <v>67</v>
@@ -2916,7 +2922,7 @@
         <v>73</v>
       </c>
       <c r="AE15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AF15" t="s">
         <v>79</v>
@@ -2954,7 +2960,7 @@
         <v>70</v>
       </c>
       <c r="I16" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="J16" t="s">
         <v>76</v>
@@ -2966,7 +2972,7 @@
         <v>67</v>
       </c>
       <c r="M16" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N16" t="s">
         <v>70</v>
@@ -2984,7 +2990,7 @@
         <v>67</v>
       </c>
       <c r="S16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="T16" t="s">
         <v>67</v>
@@ -3014,7 +3020,7 @@
         <v>84</v>
       </c>
       <c r="AC16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AD16" t="s">
         <v>58</v>
@@ -3028,7 +3034,7 @@
         <v>78</v>
       </c>
       <c r="C17" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="D17" t="s">
         <v>71</v>
@@ -3037,25 +3043,22 @@
         <v>71</v>
       </c>
       <c r="F17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H17" t="s">
         <v>72</v>
       </c>
-      <c r="I17" t="s">
-        <v>77</v>
-      </c>
       <c r="J17" t="s">
         <v>67</v>
       </c>
       <c r="K17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M17" t="s">
         <v>77</v>
@@ -3064,7 +3067,7 @@
         <v>72</v>
       </c>
       <c r="O17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P17" t="s">
         <v>67</v>
@@ -3100,7 +3103,7 @@
         <v>77</v>
       </c>
       <c r="AA17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
@@ -3111,13 +3114,13 @@
         <v>69</v>
       </c>
       <c r="C18" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="D18" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E18" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F18" t="s">
         <v>67</v>
@@ -3127,9 +3130,6 @@
       </c>
       <c r="H18" t="s">
         <v>67</v>
-      </c>
-      <c r="I18" t="s">
-        <v>73</v>
       </c>
       <c r="J18" t="s">
         <v>77</v>
@@ -3164,13 +3164,13 @@
         <v>71</v>
       </c>
       <c r="C19" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="D19" t="s">
         <v>76</v>
       </c>
       <c r="E19" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="F19" t="s">
         <v>77</v>
@@ -3179,13 +3179,10 @@
         <v>77</v>
       </c>
       <c r="H19" t="s">
-        <v>86</v>
-      </c>
-      <c r="I19" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="J19" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K19" t="s">
         <v>73</v>
@@ -3196,19 +3193,19 @@
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C20" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E20" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F20" t="s">
         <v>73</v>
@@ -3216,22 +3213,22 @@
       <c r="H20" t="s">
         <v>69</v>
       </c>
+      <c r="L20" t="s">
+        <v>70</v>
+      </c>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B21" t="s">
         <v>76</v>
       </c>
       <c r="C21" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D21" t="s">
-        <v>87</v>
-      </c>
-      <c r="E21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F21" t="s">
         <v>65</v>
@@ -3242,10 +3239,10 @@
         <v>72</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="D22" t="s">
         <v>67</v>
@@ -3259,7 +3256,7 @@
         <v>72</v>
       </c>
       <c r="C23" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="D23" t="s">
         <v>77</v>
@@ -3267,13 +3264,13 @@
     </row>
     <row r="24" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B24" t="s">
         <v>67</v>
       </c>
       <c r="C24" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D24" t="s">
         <v>88</v>
@@ -3286,9 +3283,6 @@
       <c r="B25" t="s">
         <v>77</v>
       </c>
-      <c r="C25" t="s">
-        <v>77</v>
-      </c>
       <c r="D25" t="s">
         <v>73</v>
       </c>
@@ -3300,11 +3294,8 @@
       <c r="B26" t="s">
         <v>84</v>
       </c>
-      <c r="C26" t="s">
-        <v>73</v>
-      </c>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>73</v>
       </c>
@@ -3546,7 +3537,7 @@
         <v>71</v>
       </c>
       <c r="AC3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AD3" t="s">
         <v>76</v>
@@ -3555,10 +3546,10 @@
         <v>70</v>
       </c>
       <c r="AF3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AG3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AH3" t="s">
         <v>72</v>
@@ -3570,7 +3561,7 @@
         <v>77</v>
       </c>
       <c r="AK3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AL3" t="s">
         <v>84</v>
@@ -3662,7 +3653,7 @@
         <v>2</v>
       </c>
       <c r="AA4" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="AB4" t="s">
         <v>16</v>
@@ -4986,7 +4977,7 @@
         <v>11</v>
       </c>
       <c r="AE18" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AF18" t="s">
         <v>12</v>
@@ -5060,7 +5051,7 @@
         <v>21</v>
       </c>
       <c r="AE19" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="AF19" t="s">
         <v>14</v>
@@ -5622,7 +5613,7 @@
         <v>71</v>
       </c>
       <c r="AC3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AD3" t="s">
         <v>76</v>
@@ -5631,10 +5622,10 @@
         <v>70</v>
       </c>
       <c r="AF3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AG3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AH3" t="s">
         <v>72</v>
@@ -5646,7 +5637,7 @@
         <v>77</v>
       </c>
       <c r="AK3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AL3" t="s">
         <v>84</v>
@@ -6072,52 +6063,55 @@
       <c r="AB8" t="s">
         <v>224</v>
       </c>
+      <c r="AE8" t="s">
+        <v>225</v>
+      </c>
       <c r="AF8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AH8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AI8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AJ8" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="T9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="X9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AB9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AF9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AI9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AJ9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="28:36" x14ac:dyDescent="0.25"/>

--- a/data/ICEHLdelegacije.xlsx
+++ b/data/ICEHLdelegacije.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17640"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="ICEHL" state="visible" r:id="rId4"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1481" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2075" uniqueCount="318">
   <si>
     <t>PiragicTr</t>
   </si>
@@ -42,81 +42,84 @@
     <t>ZrnicMi</t>
   </si>
   <si>
+    <t>HribarMa</t>
+  </si>
+  <si>
+    <t>SiegelSt</t>
+  </si>
+  <si>
+    <t>BedynekSe</t>
+  </si>
+  <si>
+    <t>SeewaldEl</t>
+  </si>
+  <si>
+    <t>PardatscherUl</t>
+  </si>
+  <si>
+    <t>FichtnerPa</t>
+  </si>
+  <si>
+    <t>BärnthalerCh</t>
+  </si>
+  <si>
+    <t>KoncDa</t>
+  </si>
+  <si>
+    <t>RieckenSi</t>
+  </si>
+  <si>
+    <t>MartinFl</t>
+  </si>
+  <si>
+    <t>HronskyTo</t>
+  </si>
+  <si>
+    <t>MantovaniDa</t>
+  </si>
+  <si>
+    <t>SparerDa</t>
+  </si>
+  <si>
+    <t>PuffWo</t>
+  </si>
+  <si>
+    <t>Gatol-schafranekMa</t>
+  </si>
+  <si>
+    <t>RezekGr</t>
+  </si>
+  <si>
+    <t>SchauerJa</t>
+  </si>
+  <si>
+    <t>RigoniDa</t>
+  </si>
+  <si>
+    <t>JedlickaPe</t>
+  </si>
+  <si>
+    <t>MuzsikNo</t>
+  </si>
+  <si>
+    <t>BernekerTh</t>
+  </si>
+  <si>
+    <t>WimmlerAl</t>
+  </si>
+  <si>
+    <t>NotheggerDa</t>
+  </si>
+  <si>
+    <t>VacziDa</t>
+  </si>
+  <si>
     <t>DurmisOt</t>
   </si>
   <si>
-    <t>RieckenSi</t>
-  </si>
-  <si>
-    <t>SiegelSt</t>
-  </si>
-  <si>
-    <t>HribarMa</t>
-  </si>
-  <si>
-    <t>BedynekSe</t>
-  </si>
-  <si>
-    <t>SeewaldEl</t>
-  </si>
-  <si>
-    <t>MartinFl</t>
-  </si>
-  <si>
-    <t>PardatscherUl</t>
-  </si>
-  <si>
-    <t>FichtnerPa</t>
-  </si>
-  <si>
-    <t>HronskyTo</t>
-  </si>
-  <si>
-    <t>MantovaniDa</t>
-  </si>
-  <si>
-    <t>SparerDa</t>
-  </si>
-  <si>
-    <t>BärnthalerCh</t>
-  </si>
-  <si>
-    <t>PuffWo</t>
-  </si>
-  <si>
-    <t>KoncDa</t>
-  </si>
-  <si>
-    <t>RezekGr</t>
-  </si>
-  <si>
-    <t>SchauerJa</t>
-  </si>
-  <si>
-    <t>MuzsikNo</t>
-  </si>
-  <si>
-    <t>RigoniDa</t>
-  </si>
-  <si>
-    <t>BernekerTh</t>
-  </si>
-  <si>
-    <t>Gatol-schafranekMa</t>
-  </si>
-  <si>
-    <t>WimmlerAl</t>
-  </si>
-  <si>
     <t>Huber aAn</t>
   </si>
   <si>
-    <t>JedlickaPe</t>
-  </si>
-  <si>
-    <t>NotheggerDa</t>
-  </si>
-  <si>
     <t>NikolicKr</t>
   </si>
   <si>
@@ -126,9 +129,6 @@
     <t>NagyAt</t>
   </si>
   <si>
-    <t>VacziDa</t>
-  </si>
-  <si>
     <t>WeissAl</t>
   </si>
   <si>
@@ -138,45 +138,48 @@
     <t>SeewaldJe</t>
   </si>
   <si>
+    <t>KainbergerJu</t>
+  </si>
+  <si>
+    <t>ZacherlPa</t>
+  </si>
+  <si>
     <t>VoicanCh</t>
   </si>
   <si>
     <t>HolzerTo</t>
   </si>
   <si>
-    <t>KainbergerJu</t>
-  </si>
-  <si>
-    <t>ZacherlPa</t>
+    <t>FleischmannLu</t>
   </si>
   <si>
     <t>JeramFi</t>
   </si>
   <si>
-    <t>FleischmannLu</t>
-  </si>
-  <si>
     <t>SnojTa</t>
   </si>
   <si>
     <t>StrimitzerDa</t>
   </si>
   <si>
+    <t>HlavatyAl</t>
+  </si>
+  <si>
     <t>2024-09-20</t>
   </si>
   <si>
+    <t>2024-09-24</t>
+  </si>
+  <si>
     <t>2024-09-22</t>
   </si>
   <si>
-    <t>2024-09-24</t>
+    <t>2024-09-27</t>
   </si>
   <si>
     <t>2024-09-21</t>
   </si>
   <si>
-    <t>2024-09-27</t>
-  </si>
-  <si>
     <t>2024-10-04</t>
   </si>
   <si>
@@ -189,16 +192,22 @@
     <t>2024-10-12</t>
   </si>
   <si>
+    <t>2024-12-26</t>
+  </si>
+  <si>
     <t>2024-10-01</t>
   </si>
   <si>
     <t>2024-10-25</t>
   </si>
   <si>
+    <t>2024-10-20</t>
+  </si>
+  <si>
     <t>2024-10-06</t>
   </si>
   <si>
-    <t>2024-10-20</t>
+    <t>2024-12-06</t>
   </si>
   <si>
     <t>2024-11-01</t>
@@ -219,6 +228,9 @@
     <t>2024-10-22</t>
   </si>
   <si>
+    <t>2024-12-08</t>
+  </si>
+  <si>
     <t>2024-11-27</t>
   </si>
   <si>
@@ -228,13 +240,16 @@
     <t>2024-11-13</t>
   </si>
   <si>
+    <t>2024-11-15</t>
+  </si>
+  <si>
+    <t>2024-11-24</t>
+  </si>
+  <si>
     <t>2024-11-20</t>
   </si>
   <si>
-    <t>2024-11-15</t>
-  </si>
-  <si>
-    <t>2024-11-24</t>
+    <t>2024-12-18</t>
   </si>
   <si>
     <t>2024-12-04</t>
@@ -252,12 +267,18 @@
     <t>2024-11-29</t>
   </si>
   <si>
+    <t>2024-12-20</t>
+  </si>
+  <si>
     <t>2024-11-03</t>
   </si>
   <si>
     <t>2024-11-02</t>
   </si>
   <si>
+    <t>2024-12-28</t>
+  </si>
+  <si>
     <t>2024-10-23</t>
   </si>
   <si>
@@ -267,24 +288,45 @@
     <t>2024-11-22</t>
   </si>
   <si>
+    <t>2024-12-01</t>
+  </si>
+  <si>
+    <t>2025-01-01</t>
+  </si>
+  <si>
+    <t>2024-11-16</t>
+  </si>
+  <si>
+    <t>2024-12-13</t>
+  </si>
+  <si>
+    <t>2024-12-30</t>
+  </si>
+  <si>
+    <t>2024-12-22</t>
+  </si>
+  <si>
+    <t>2024-11-30</t>
+  </si>
+  <si>
     <t>zbrisano</t>
   </si>
   <si>
-    <t>2024-12-01</t>
-  </si>
-  <si>
     <t>2024-11-23</t>
   </si>
   <si>
-    <t>2024-11-16</t>
-  </si>
-  <si>
-    <t>2024-11-30</t>
-  </si>
-  <si>
     <t>2024-12-03</t>
   </si>
   <si>
+    <t>2024-12-15</t>
+  </si>
+  <si>
+    <t>2024-12-07</t>
+  </si>
+  <si>
+    <t>2024-12-14</t>
+  </si>
+  <si>
     <t>HuberAn</t>
   </si>
   <si>
@@ -369,10 +411,10 @@
     <t>Tiroler Wasserkraft Arena;KainbergerJu;SeewaldEl;NotheggerDa;SeewaldJe</t>
   </si>
   <si>
-    <t>Gabor Ocskay Eisarena;FichtnerPa;SoosDa;JedlickaPe;MuzsikNo</t>
-  </si>
-  <si>
-    <t>Eishalle Wien-Kagran;OfnerCh;SternatCh;MuzsikNo;VacziDa</t>
+    <t>Gabor Ocskay Eisarena;FichtnerPa;SoosDa;JedlickaPe;VacziDa</t>
+  </si>
+  <si>
+    <t>Eishalle Wien-Kagran;OfnerCh;SternatCh;Gatol-schafranekMa;VacziDa</t>
   </si>
   <si>
     <t>Linz AG Eisarena;OfnerCh;SternatCh;BedynekSe;WimmlerAl</t>
@@ -384,10 +426,10 @@
     <t>Merkur Eisstadion Graz;FichtnerPa;SmetanaLa;BärnthalerCh;WimmlerAl</t>
   </si>
   <si>
-    <t>Sparkasse Arena Bozen;OfnerCh;SternatCh;DurmisOt;KoncDa</t>
-  </si>
-  <si>
-    <t>Eisarena Salzburg;NikolicKr;SmetanaLa;DurmisOt;KoncDa</t>
+    <t>Sparkasse Arena Bozen;OfnerCh;SternatCh;JedlickaPe;KoncDa</t>
+  </si>
+  <si>
+    <t>Eisarena Salzburg;NikolicKr;SmetanaLa;JedlickaPe;KoncDa</t>
   </si>
   <si>
     <t>Merkur Eisstadion Graz;HronskyTo;OfnerCh;BärnthalerCh;JedlickaPe</t>
@@ -408,6 +450,45 @@
     <t>Merkur Eisstadion Graz;SiegelSt;SmetanaLa;BärnthalerCh;WimmlerAl</t>
   </si>
   <si>
+    <t>Merkur Eisstadion Graz;FichtnerPa;SmetanaLa;RieckenSi;WimmlerAl</t>
+  </si>
+  <si>
+    <t>Eishalle Bruneck;OfnerCh;PiragicTr;PuffWo;ZgoncGa</t>
+  </si>
+  <si>
+    <t>Linz AG Eisarena;KainbergerJu;SmetanaLa;Gatol-schafranekMa;SparerDa</t>
+  </si>
+  <si>
+    <t>Klagenfurter Stadthalle;HronskyTo;SiegelSt;JedlickaPe;KoncDa</t>
+  </si>
+  <si>
+    <t>Hala Tivoli;OfnerCh;SmetanaLa;RieckenSi;ZgoncGa</t>
+  </si>
+  <si>
+    <t>Linz AG Eisarena;BernekerTh;NikolicMa;DurmisOt;WimmlerAl</t>
+  </si>
+  <si>
+    <t>Tiroler Wasserkraft Arena;NikolicMa;SternatCh;PardatscherUl;SparerDa</t>
+  </si>
+  <si>
+    <t>Merkur Eisstadion Graz;SmetanaLa;SternatCh;JedlickaPe;KoncDa</t>
+  </si>
+  <si>
+    <t>Eishalle Asiago;Huber aAn;OfnerCh;MantovaniDa;WeissAl</t>
+  </si>
+  <si>
+    <t>Linz AG Eisarena;HlavatyAl;SmetanaLa;BärnthalerCh;ZacherlPa</t>
+  </si>
+  <si>
+    <t>Tiroler Wasserkraft Arena;Huber aAn;SternatCh;NotheggerDa;ZacherlPa</t>
+  </si>
+  <si>
+    <t>Klagenfurter Stadthalle;GroznikBo;SiegelSt;BedynekSe;PuffWo</t>
+  </si>
+  <si>
+    <t>Eishalle Wien-Kagran;SiegelSt;SmetanaLa;Gatol-schafranekMa;JedlickaPe</t>
+  </si>
+  <si>
     <t>Tiroler Wasserkraft Arena;NikolicMa;SeewaldEl;FleischmannLu;NotheggerDa</t>
   </si>
   <si>
@@ -483,7 +564,7 @@
     <t>Hala Tivoli;GroznikBo;NagyAt;MuzsikNo;VacziDa</t>
   </si>
   <si>
-    <t>Gabor Ocskay Eisarena;HronskyTo;SoosDa;JedlickaPe;MuzsikNo</t>
+    <t>Gabor Ocskay Eisarena;HronskyTo;SoosDa;DurmisOt;MuzsikNo</t>
   </si>
   <si>
     <t>Gabor Ocskay Eisarena;RezekGr;SmetanaLa;Gatol-schafranekMa;JeramFi</t>
@@ -501,6 +582,42 @@
     <t>Stadthalle Villach;PiragicTr;SternatCh;HribarMa;JeramFi</t>
   </si>
   <si>
+    <t>Eishalle;KainbergerJu;SternatCh;DurmisOt;JedlickaPe</t>
+  </si>
+  <si>
+    <t>Eishalle Feldkirch;NikolicMa;SeewaldEl;FleischmannLu;NotheggerDa</t>
+  </si>
+  <si>
+    <t>Eisarena Salzburg;NikolicKr;OfnerCh;BedynekSe;MoidlMa</t>
+  </si>
+  <si>
+    <t>Eishalle;HronskyTo;PiragicTr;JedlickaPe;KoncDa</t>
+  </si>
+  <si>
+    <t>w KagranK;FichtnerPa;PiragicTr;MuzsikNo;PuffWo</t>
+  </si>
+  <si>
+    <t>Gabor Ocskay Eisarena;SiegelSt;SmetanaLa;DurmisOt;KoncDa</t>
+  </si>
+  <si>
+    <t>Gabor Ocskay Eisarena;HronskyTo;NagyAt;DurmisOt;VacziDa</t>
+  </si>
+  <si>
+    <t>Eishalle KagranEins;SmetanaLa;ZrnicMi;MoidlMa;ZgoncGa</t>
+  </si>
+  <si>
+    <t>Stadthalle Villach;HronskyTo;PiragicTr;BedynekSe;KoncDa</t>
+  </si>
+  <si>
+    <t>Gabor Ocskay Eisarena;NagyAt;ZrnicMi;HribarMa;ZgoncGa</t>
+  </si>
+  <si>
+    <t>Hala Tivoli;PiragicTr;RezekGr;HribarMa;VacziDa</t>
+  </si>
+  <si>
+    <t>Merkur Eisstadion Graz;GroznikBo;SoosDa;BärnthalerCh;MuzsikNo</t>
+  </si>
+  <si>
     <t>Hala Tivoli;PiragicTr;ZrnicMi;HribarMa;SnojTa</t>
   </si>
   <si>
@@ -561,7 +678,7 @@
     <t>Sparkasse Arena Bozen;BernekerTh;NikolicKr;PuffWo;RigoniDa</t>
   </si>
   <si>
-    <t>Gabor Ocskay Eisarena;HronskyTo;PiragicTr;HribarMa;JedlickaPe</t>
+    <t>Gabor Ocskay Eisarena;HronskyTo;PiragicTr;DurmisOt;HribarMa</t>
   </si>
   <si>
     <t>Klagenfurter Stadthalle;FichtnerPa;PiragicTr;MantovaniDa;WeissAl</t>
@@ -582,6 +699,39 @@
     <t>Linz AG Eisarena;GroznikBo;RezekGr;NotheggerDa;WeissAl</t>
   </si>
   <si>
+    <t>Olympiastadion Innsbruck;BernekerTh;SchauerJa;MantovaniDa;MartinFl</t>
+  </si>
+  <si>
+    <t>Sparkasse Arena Bozen;Huber aAn;ZrnicMi;PardatscherUl;RigoniDa</t>
+  </si>
+  <si>
+    <t>Eishalle KagranEins;FichtnerPa;SeewaldEl;DurmisOt;WimmlerAl</t>
+  </si>
+  <si>
+    <t>Merkur Eisstadion Graz;OfnerCh;SeewaldEl;BärnthalerCh;Gatol-schafranekMa</t>
+  </si>
+  <si>
+    <t>Klagenfurter Stadthalle;FichtnerPa;ZrnicMi;BärnthalerCh;Gatol-schafranekMa</t>
+  </si>
+  <si>
+    <t>Tiroler Wasserkraft Arena;BernekerTh;HolzerTo;SparerDa;WeissAl</t>
+  </si>
+  <si>
+    <t>Eishalle;RezekGr;SeewaldEl;NotheggerDa;PuffWo</t>
+  </si>
+  <si>
+    <t>Hala Tivoli;GroznikBo;SoosDa;MuzsikNo;VacziDa</t>
+  </si>
+  <si>
+    <t>Merkur Eisstadion Graz;PiragicTr;SoosDa;BärnthalerCh;VacziDa</t>
+  </si>
+  <si>
+    <t>Gabor Ocskay Eisarena;FichtnerPa;SmetanaLa;KoncDa;MuzsikNo</t>
+  </si>
+  <si>
+    <t>Stadthalle Villach;NagyAt;PiragicTr;BedynekSe;VacziDa</t>
+  </si>
+  <si>
     <t>Eishalle Wien-Kagran;HronskyTo;SmetanaLa;DurmisOt;WeissAl</t>
   </si>
   <si>
@@ -654,6 +804,36 @@
     <t>Gabor Ocskay Eisarena;FichtnerPa;OfnerCh;DurmisOt;JedlickaPe</t>
   </si>
   <si>
+    <t>Linz AG Eisarena;NikolicKr;SiegelSt;FleischmannLu;Gatol-schafranekMa</t>
+  </si>
+  <si>
+    <t>Gabor Ocskay Eisarena;RezekGr;SoosDa;MuzsikNo;VacziDa</t>
+  </si>
+  <si>
+    <t>Stadthalle Villach;SmetanaLa;ZrnicMi;BärnthalerCh;RieckenSi</t>
+  </si>
+  <si>
+    <t>Eishalle Feldkirch;NikolicKr;SchauerJa;FleischmannLu;MartinFl</t>
+  </si>
+  <si>
+    <t>Eisarena Salzburg;PiragicTr;VoicanCh;BedynekSe;NotheggerDa</t>
+  </si>
+  <si>
+    <t>Linz AG Eisarena;SchauerJa;SiegelSt;BärnthalerCh;BedynekSe</t>
+  </si>
+  <si>
+    <t>Eishalle Feldkirch;NikolicMa;SchauerJa;FleischmannLu;SparerDa</t>
+  </si>
+  <si>
+    <t>Eisarena Salzburg;OfnerCh;SmetanaLa;SeewaldJe;WimmlerAl</t>
+  </si>
+  <si>
+    <t>Eisarena Salzburg;HronskyTo;SternatCh;JedlickaPe;SeewaldJe</t>
+  </si>
+  <si>
+    <t>Tiroler Wasserkraft Arena;NikolicKr;NikolicMa;MartinFl;SparerDa</t>
+  </si>
+  <si>
     <t>Eishalle Bruneck;BernekerTh;HuberAn;MartinFl;PardatscherUl</t>
   </si>
   <si>
@@ -696,7 +876,7 @@
     <t>ZBRISANO</t>
   </si>
   <si>
-    <t>Eishalle Feldkirch;BernekerTh;SchauerJa;DurmisOt;KoncDa</t>
+    <t>Eishalle Feldkirch;BernekerTh;SchauerJa;JedlickaPe;KoncDa</t>
   </si>
   <si>
     <t>Linz AG Eisarena;Huber aAn;SeewaldEl;NotheggerDa;ZacherlPa</t>
@@ -708,6 +888,36 @@
     <t>Eishalle Asiago;NikolicKr;SchauerJa;PardatscherUl;RigoniDa</t>
   </si>
   <si>
+    <t>Eishalle Feldkirch;OfnerCh;PiragicTr;NotheggerDa;ZgoncGa</t>
+  </si>
+  <si>
+    <t>Merkur Eisstadion Graz;GroznikBo;NagyAt;HribarMa;RieckenSi</t>
+  </si>
+  <si>
+    <t>Hala Tivoli;GroznikBo;RezekGr;HribarMa;ZgoncGa</t>
+  </si>
+  <si>
+    <t>Eishalle Asiago;OfnerCh;PiragicTr;PuffWo;RigoniDa</t>
+  </si>
+  <si>
+    <t>Eishalle Feldkirch;Huber aAn;NikolicMa;PardatscherUl;SeewaldJe</t>
+  </si>
+  <si>
+    <t>Heidi Horten Arena Klagenfurt;FichtnerPa;HronskyTo;Gatol-schafranekMa;KoncDa</t>
+  </si>
+  <si>
+    <t>Merkur Eisstadion Graz;SeewaldEl;SternatCh;PuffWo;WimmlerAl</t>
+  </si>
+  <si>
+    <t>Eishalle Bruneck;BernekerTh;SchauerJa;MartinFl;WeissAl</t>
+  </si>
+  <si>
+    <t>Eishalle Feldkirch;BernekerTh;NikolicKr;MartinFl;SparerDa</t>
+  </si>
+  <si>
+    <t>Linz AG Eisarena;Huber aAn;OfnerCh;NotheggerDa;SeewaldJe</t>
+  </si>
+  <si>
     <t>Eiswelle Bozen;OfnerCh;RezekGr;PuffWo;ZgoncGa</t>
   </si>
   <si>
@@ -739,6 +949,27 @@
   </si>
   <si>
     <t>Sparkasse Arena Bozen;NikolicMa;SternatCh;SeewaldJe;SparerDa</t>
+  </si>
+  <si>
+    <t>Eishalle Asiago;Huber aAn;ZrnicMi;HribarMa;PardatscherUl</t>
+  </si>
+  <si>
+    <t>Sparkasse Arena Bozen;GroznikBo;OfnerCh;MantovaniDa;RigoniDa</t>
+  </si>
+  <si>
+    <t>Hala Tivoli;PiragicTr;SoosDa;HribarMa;MuzsikNo</t>
+  </si>
+  <si>
+    <t>Sparkasse Arena Bozen;OfnerCh;ZrnicMi;MantovaniDa;PardatscherUl</t>
+  </si>
+  <si>
+    <t>Eishalle Asiago;NikolicKr;NikolicMa;MantovaniDa;RigoniDa</t>
+  </si>
+  <si>
+    <t>Sparkasse Arena Bozen;OfnerCh;SeewaldEl;MantovaniDa;PardatscherUl</t>
+  </si>
+  <si>
+    <t>Eishalle Bruneck;RezekGr;SternatCh;RigoniDa;ZgoncGa</t>
   </si>
 </sst>
 </file>
@@ -1056,7 +1287,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:AW134"/>
+  <dimension ref="A2:AX134"/>
   <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.28515625" customWidth="1"/>
@@ -1115,195 +1346,195 @@
   <sheetData>
     <row r="2" ht="14.45" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A2">
-        <f t="shared" ref="A2:H2" si="0">COUNTIF(A4:A100,"&lt;&gt;")</f>
-        <v>24</v>
+        <f>COUNTIF(A4:A100,"&lt;&gt;")</f>
+        <v>35</v>
       </c>
       <c r="B2">
-        <f t="shared" si="0"/>
-        <v>24</v>
+        <f>COUNTIF(B4:B100,"&lt;&gt;")</f>
+        <v>35</v>
       </c>
       <c r="C2">
         <f>COUNTIF(C4:C98,"&lt;&gt;")</f>
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="D2">
-        <f t="shared" si="0"/>
-        <v>22</v>
+        <f>COUNTIF(D4:D100,"&lt;&gt;")</f>
+        <v>30</v>
       </c>
       <c r="E2">
         <f>COUNTIF(E4:E99,"&lt;&gt;")</f>
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F2">
-        <f t="shared" si="0"/>
-        <v>18</v>
+        <f>COUNTIF(F4:F100,"&lt;&gt;")</f>
+        <v>24</v>
       </c>
       <c r="G2">
-        <f t="shared" si="0"/>
-        <v>16</v>
+        <f>COUNTIF(G4:G100,"&lt;&gt;")</f>
+        <v>23</v>
       </c>
       <c r="H2">
-        <f t="shared" si="0"/>
-        <v>17</v>
+        <f>COUNTIF(H4:H100,"&lt;&gt;")</f>
+        <v>23</v>
       </c>
       <c r="I2">
-        <f>COUNTIF(I4:I96,"&lt;&gt;")</f>
-        <v>13</v>
+        <f>COUNTIF(I4:I100,"&lt;&gt;")</f>
+        <v>23</v>
       </c>
       <c r="J2">
-        <f>COUNTIF(J4:J99,"&lt;&gt;")</f>
-        <v>16</v>
+        <f>COUNTIF(J4:J100,"&lt;&gt;")</f>
+        <v>22</v>
       </c>
       <c r="K2">
-        <f>COUNTIF(K4:K100,"&lt;&gt;")</f>
-        <v>16</v>
+        <f>COUNTIF(K4:K99,"&lt;&gt;")</f>
+        <v>21</v>
       </c>
       <c r="L2">
         <f>COUNTIF(L4:L100,"&lt;&gt;")</f>
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="M2">
-        <f>COUNTIF(M4:M99,"&lt;&gt;")</f>
-        <v>15</v>
+        <f>COUNTIF(M4:M100,"&lt;&gt;")</f>
+        <v>21</v>
       </c>
       <c r="N2">
         <f>COUNTIF(N4:N100,"&lt;&gt;")</f>
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="O2">
         <f>COUNTIF(O4:O100,"&lt;&gt;")</f>
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="P2">
         <f>COUNTIF(P4:P100,"&lt;&gt;")</f>
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="Q2">
-        <f>COUNTIF(Q4:Q100,"&lt;&gt;")</f>
-        <v>15</v>
+        <f>COUNTIF(Q4:Q99,"&lt;&gt;")</f>
+        <v>20</v>
       </c>
       <c r="R2">
         <f>COUNTIF(R4:R100,"&lt;&gt;")</f>
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="S2">
-        <f>COUNTIF(S4:S99,"&lt;&gt;")</f>
-        <v>14</v>
+        <f>COUNTIF(S4:S100,"&lt;&gt;")</f>
+        <v>20</v>
       </c>
       <c r="T2">
-        <f t="shared" ref="T2:AC2" si="1">COUNTIF(T4:T100,"&lt;&gt;")</f>
-        <v>14</v>
+        <f>COUNTIF(T4:T99,"&lt;&gt;")</f>
+        <v>20</v>
       </c>
       <c r="U2">
-        <f t="shared" si="1"/>
-        <v>14</v>
+        <f t="shared" ref="U2:Z2" si="0">COUNTIF(U4:U100,"&lt;&gt;")</f>
+        <v>20</v>
       </c>
       <c r="V2">
-        <f t="shared" si="1"/>
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>20</v>
       </c>
       <c r="W2">
-        <f t="shared" si="1"/>
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>20</v>
       </c>
       <c r="X2">
-        <f t="shared" si="1"/>
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>19</v>
       </c>
       <c r="Y2">
-        <f t="shared" si="1"/>
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>19</v>
       </c>
       <c r="Z2">
-        <f t="shared" si="1"/>
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>19</v>
       </c>
       <c r="AA2">
-        <f t="shared" si="1"/>
-        <v>14</v>
+        <f>COUNTIF(AA4:AA99,"&lt;&gt;")</f>
+        <v>19</v>
       </c>
       <c r="AB2">
-        <f t="shared" si="1"/>
-        <v>13</v>
+        <f>COUNTIF(AB4:AB98,"&lt;&gt;")</f>
+        <v>18</v>
       </c>
       <c r="AC2">
-        <f t="shared" si="1"/>
-        <v>13</v>
+        <f>COUNTIF(AC4:AC100,"&lt;&gt;")</f>
+        <v>18</v>
       </c>
       <c r="AD2">
         <f>COUNTIF(AD4:AD96,"&lt;&gt;")</f>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AE2">
         <f>COUNTIF(AE4:AE100,"&lt;&gt;")</f>
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AF2">
-        <f>COUNTIF(AF4:AF99,"&lt;&gt;")</f>
-        <v>12</v>
+        <f>COUNTIF(AF4:AF100,"&lt;&gt;")</f>
+        <v>18</v>
       </c>
       <c r="AG2">
-        <f>COUNTIF(AG4:AG100,"&lt;&gt;")</f>
-        <v>12</v>
+        <f>COUNTIF(AG4:AG95,"&lt;&gt;")</f>
+        <v>17</v>
       </c>
       <c r="AH2">
         <f>COUNTIF(AH4:AH99,"&lt;&gt;")</f>
+        <v>17</v>
+      </c>
+      <c r="AI2">
+        <f>COUNTIF(AI4:AI98,"&lt;&gt;")</f>
+        <v>17</v>
+      </c>
+      <c r="AJ2">
+        <f>COUNTIF(AJ4:AJ99,"&lt;&gt;")</f>
+        <v>16</v>
+      </c>
+      <c r="AK2">
+        <f t="shared" ref="AK2:AU2" si="1">COUNTIF(AK4:AK100,"&lt;&gt;")</f>
+        <v>15</v>
+      </c>
+      <c r="AL2">
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="AI2">
-        <f>COUNTIF(AI4:AI99,"&lt;&gt;")</f>
+      <c r="AM2">
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="AJ2">
-        <f t="shared" ref="AJ2:AU2" si="2">COUNTIF(AJ4:AJ100,"&lt;&gt;")</f>
-        <v>11</v>
-      </c>
-      <c r="AK2">
-        <f t="shared" si="2"/>
-        <v>11</v>
-      </c>
-      <c r="AL2">
-        <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
-      <c r="AM2">
-        <f t="shared" si="2"/>
+      <c r="AN2">
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="AN2">
-        <f t="shared" si="2"/>
+      <c r="AO2">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="AP2">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="AQ2">
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="AO2">
-        <f t="shared" si="2"/>
+      <c r="AR2">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="AS2">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="AT2">
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="AP2">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="AQ2">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="AR2">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="AS2">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="AT2">
-        <f t="shared" si="2"/>
+      <c r="AU2">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AU2">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -1448,61 +1679,64 @@
       <c r="AV3" t="s">
         <v>47</v>
       </c>
+      <c r="AW3" t="s">
+        <v>48</v>
+      </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J4" t="s">
+        <v>50</v>
+      </c>
+      <c r="K4" t="s">
+        <v>51</v>
+      </c>
+      <c r="L4" t="s">
         <v>49</v>
-      </c>
-      <c r="K4" t="s">
-        <v>50</v>
-      </c>
-      <c r="L4" t="s">
-        <v>48</v>
       </c>
       <c r="M4" t="s">
         <v>49</v>
       </c>
       <c r="N4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="O4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="P4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q4" t="s">
+        <v>51</v>
+      </c>
+      <c r="R4" t="s">
         <v>49</v>
-      </c>
-      <c r="R4" t="s">
-        <v>48</v>
       </c>
       <c r="S4" t="s">
         <v>49</v>
@@ -1511,230 +1745,236 @@
         <v>51</v>
       </c>
       <c r="U4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="V4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="W4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="X4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Y4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z4" t="s">
         <v>51</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>49</v>
       </c>
       <c r="AA4" t="s">
         <v>49</v>
       </c>
       <c r="AB4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="AC4" t="s">
         <v>49</v>
       </c>
       <c r="AD4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AE4" t="s">
         <v>49</v>
       </c>
-      <c r="AE4" t="s">
-        <v>48</v>
-      </c>
       <c r="AF4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="AG4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AH4" t="s">
         <v>49</v>
       </c>
       <c r="AI4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ4" t="s">
         <v>52</v>
       </c>
-      <c r="AJ4" t="s">
+      <c r="AK4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AL4" t="s">
         <v>49</v>
       </c>
-      <c r="AK4" t="s">
+      <c r="AM4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AS4" t="s">
         <v>49</v>
       </c>
-      <c r="AL4" t="s">
-        <v>48</v>
-      </c>
-      <c r="AM4" t="s">
+      <c r="AT4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" t="s">
         <v>53</v>
       </c>
-      <c r="AN4" t="s">
-        <v>54</v>
-      </c>
-      <c r="AO4" t="s">
-        <v>49</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>49</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>54</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>55</v>
-      </c>
-      <c r="AS4" t="s">
-        <v>56</v>
-      </c>
-      <c r="AT4" t="s">
-        <v>48</v>
-      </c>
-      <c r="AU4" t="s">
-        <v>48</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>51</v>
       </c>
-      <c r="D5" t="s">
-        <v>49</v>
-      </c>
       <c r="E5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G5" t="s">
         <v>52</v>
       </c>
       <c r="H5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I5" t="s">
         <v>52</v>
       </c>
       <c r="J5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K5" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="L5" t="s">
         <v>52</v>
       </c>
       <c r="M5" t="s">
+        <v>52</v>
+      </c>
+      <c r="N5" t="s">
         <v>50</v>
       </c>
-      <c r="N5" t="s">
-        <v>52</v>
-      </c>
       <c r="O5" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="P5" t="s">
         <v>52</v>
       </c>
       <c r="Q5" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="R5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="S5" t="s">
         <v>52</v>
       </c>
       <c r="T5" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="U5" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="V5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="W5" t="s">
         <v>52</v>
       </c>
       <c r="X5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Y5" t="s">
         <v>52</v>
       </c>
       <c r="Z5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="AA5" t="s">
         <v>52</v>
       </c>
       <c r="AB5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="AC5" t="s">
         <v>52</v>
       </c>
       <c r="AD5" t="s">
+        <v>55</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>55</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>59</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH5" t="s">
         <v>54</v>
       </c>
-      <c r="AE5" t="s">
-        <v>53</v>
-      </c>
-      <c r="AF5" t="s">
+      <c r="AI5" t="s">
         <v>52</v>
       </c>
-      <c r="AG5" t="s">
-        <v>54</v>
-      </c>
-      <c r="AH5" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>57</v>
-      </c>
       <c r="AJ5" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AK5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="AL5" t="s">
         <v>50</v>
       </c>
       <c r="AM5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>60</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>57</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>62</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>54</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>63</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>55</v>
-      </c>
-      <c r="AN5" t="s">
-        <v>58</v>
-      </c>
-      <c r="AO5" t="s">
-        <v>59</v>
-      </c>
-      <c r="AP5" t="s">
-        <v>53</v>
-      </c>
-      <c r="AQ5" t="s">
-        <v>56</v>
-      </c>
-      <c r="AR5" t="s">
-        <v>60</v>
-      </c>
-      <c r="AS5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>54</v>
       </c>
       <c r="B6" t="s">
         <v>52</v>
@@ -1746,1575 +1986,2336 @@
         <v>52</v>
       </c>
       <c r="E6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F6" t="s">
         <v>52</v>
       </c>
       <c r="G6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J6" t="s">
         <v>62</v>
       </c>
       <c r="K6" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="L6" t="s">
+        <v>55</v>
+      </c>
+      <c r="M6" t="s">
+        <v>55</v>
+      </c>
+      <c r="N6" t="s">
+        <v>55</v>
+      </c>
+      <c r="O6" t="s">
+        <v>62</v>
+      </c>
+      <c r="P6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>65</v>
+      </c>
+      <c r="R6" t="s">
         <v>54</v>
-      </c>
-      <c r="M6" t="s">
-        <v>54</v>
-      </c>
-      <c r="N6" t="s">
-        <v>54</v>
-      </c>
-      <c r="O6" t="s">
-        <v>53</v>
-      </c>
-      <c r="P6" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>54</v>
-      </c>
-      <c r="R6" t="s">
-        <v>53</v>
       </c>
       <c r="S6" t="s">
         <v>54</v>
       </c>
       <c r="T6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="U6" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="V6" t="s">
         <v>52</v>
       </c>
       <c r="W6" t="s">
+        <v>54</v>
+      </c>
+      <c r="X6" t="s">
         <v>59</v>
       </c>
-      <c r="X6" t="s">
+      <c r="Y6" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>67</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>62</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>68</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>69</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>69</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F7" t="s">
+        <v>62</v>
+      </c>
+      <c r="G7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H7" t="s">
+        <v>62</v>
+      </c>
+      <c r="I7" t="s">
+        <v>62</v>
+      </c>
+      <c r="J7" t="s">
+        <v>66</v>
+      </c>
+      <c r="K7" t="s">
+        <v>62</v>
+      </c>
+      <c r="L7" t="s">
+        <v>54</v>
+      </c>
+      <c r="M7" t="s">
+        <v>54</v>
+      </c>
+      <c r="N7" t="s">
+        <v>54</v>
+      </c>
+      <c r="O7" t="s">
+        <v>56</v>
+      </c>
+      <c r="P7" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q7" t="s">
         <v>57</v>
       </c>
-      <c r="Y6" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>57</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>53</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>53</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>53</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>64</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>53</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>63</v>
-      </c>
-      <c r="AH6" t="s">
-        <v>53</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>59</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>53</v>
-      </c>
-      <c r="AK6" t="s">
+      <c r="R7" t="s">
+        <v>56</v>
+      </c>
+      <c r="S7" t="s">
+        <v>62</v>
+      </c>
+      <c r="T7" t="s">
+        <v>66</v>
+      </c>
+      <c r="U7" t="s">
+        <v>65</v>
+      </c>
+      <c r="V7" t="s">
         <v>55</v>
       </c>
-      <c r="AL6" t="s">
-        <v>54</v>
-      </c>
-      <c r="AM6" t="s">
-        <v>60</v>
-      </c>
-      <c r="AN6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AO6" t="s">
+      <c r="W7" t="s">
+        <v>66</v>
+      </c>
+      <c r="X7" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>62</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AE7" t="s">
         <v>61</v>
       </c>
-      <c r="AP6" t="s">
-        <v>66</v>
-      </c>
-      <c r="AQ6" t="s">
-        <v>58</v>
-      </c>
-      <c r="AR6" t="s">
-        <v>66</v>
-      </c>
-      <c r="AS6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D7" t="s">
-        <v>54</v>
-      </c>
-      <c r="E7" t="s">
-        <v>57</v>
-      </c>
-      <c r="F7" t="s">
-        <v>59</v>
-      </c>
-      <c r="G7" t="s">
-        <v>57</v>
-      </c>
-      <c r="H7" t="s">
-        <v>59</v>
-      </c>
-      <c r="I7" t="s">
-        <v>59</v>
-      </c>
-      <c r="J7" t="s">
+      <c r="AF7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>62</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>69</v>
+      </c>
+      <c r="AI7" t="s">
         <v>56</v>
-      </c>
-      <c r="K7" t="s">
-        <v>63</v>
-      </c>
-      <c r="L7" t="s">
-        <v>59</v>
-      </c>
-      <c r="M7" t="s">
-        <v>59</v>
-      </c>
-      <c r="N7" t="s">
-        <v>53</v>
-      </c>
-      <c r="O7" t="s">
-        <v>55</v>
-      </c>
-      <c r="P7" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>53</v>
-      </c>
-      <c r="R7" t="s">
-        <v>59</v>
-      </c>
-      <c r="S7" t="s">
-        <v>63</v>
-      </c>
-      <c r="T7" t="s">
-        <v>62</v>
-      </c>
-      <c r="U7" t="s">
-        <v>55</v>
-      </c>
-      <c r="V7" t="s">
-        <v>54</v>
-      </c>
-      <c r="W7" t="s">
-        <v>63</v>
-      </c>
-      <c r="X7" t="s">
-        <v>59</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>59</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>63</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>68</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>66</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>63</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>60</v>
-      </c>
-      <c r="AH7" t="s">
-        <v>55</v>
-      </c>
-      <c r="AI7" t="s">
-        <v>55</v>
       </c>
       <c r="AJ7" t="s">
         <v>56</v>
       </c>
       <c r="AK7" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="AL7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AM7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="AN7" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="AO7" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="AP7" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AQ7" t="s">
         <v>71</v>
       </c>
       <c r="AR7" t="s">
+        <v>76</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>77</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I8" t="s">
         <v>72</v>
       </c>
-      <c r="AS7" t="s">
+      <c r="J8" t="s">
+        <v>56</v>
+      </c>
+      <c r="K8" t="s">
+        <v>67</v>
+      </c>
+      <c r="L8" t="s">
+        <v>56</v>
+      </c>
+      <c r="M8" t="s">
+        <v>56</v>
+      </c>
+      <c r="N8" t="s">
+        <v>66</v>
+      </c>
+      <c r="O8" t="s">
+        <v>79</v>
+      </c>
+      <c r="P8" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>56</v>
+      </c>
+      <c r="R8" t="s">
+        <v>52</v>
+      </c>
+      <c r="S8" t="s">
+        <v>66</v>
+      </c>
+      <c r="T8" t="s">
+        <v>56</v>
+      </c>
+      <c r="U8" t="s">
+        <v>62</v>
+      </c>
+      <c r="V8" t="s">
+        <v>66</v>
+      </c>
+      <c r="W8" t="s">
+        <v>67</v>
+      </c>
+      <c r="X8" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>56</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>69</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>66</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>60</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>72</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>72</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>81</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>82</v>
+      </c>
+      <c r="AO8" t="s">
         <v>73</v>
       </c>
+      <c r="AP8" t="s">
+        <v>58</v>
+      </c>
+      <c r="AQ8" t="s">
+        <v>83</v>
+      </c>
+      <c r="AR8" t="s">
+        <v>83</v>
+      </c>
+      <c r="AS8" t="s">
+        <v>58</v>
+      </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E8" t="s">
-        <v>53</v>
-      </c>
-      <c r="F8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G8" t="s">
-        <v>55</v>
-      </c>
-      <c r="H8" t="s">
+    <row r="9" ht="15" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" t="s">
+        <v>61</v>
+      </c>
+      <c r="G9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H9" t="s">
+        <v>56</v>
+      </c>
+      <c r="I9" t="s">
+        <v>61</v>
+      </c>
+      <c r="J9" t="s">
+        <v>72</v>
+      </c>
+      <c r="K9" t="s">
+        <v>79</v>
+      </c>
+      <c r="L9" t="s">
+        <v>72</v>
+      </c>
+      <c r="M9" t="s">
+        <v>61</v>
+      </c>
+      <c r="N9" t="s">
+        <v>72</v>
+      </c>
+      <c r="O9" t="s">
+        <v>61</v>
+      </c>
+      <c r="P9" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>69</v>
+      </c>
+      <c r="R9" t="s">
+        <v>72</v>
+      </c>
+      <c r="S9" t="s">
+        <v>72</v>
+      </c>
+      <c r="T9" t="s">
+        <v>61</v>
+      </c>
+      <c r="U9" t="s">
+        <v>72</v>
+      </c>
+      <c r="V9" t="s">
+        <v>61</v>
+      </c>
+      <c r="W9" t="s">
+        <v>72</v>
+      </c>
+      <c r="X9" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>72</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>84</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>68</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>72</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>85</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>85</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>76</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AO9" t="s">
         <v>63</v>
       </c>
-      <c r="I8" t="s">
-        <v>63</v>
-      </c>
-      <c r="J8" t="s">
-        <v>55</v>
-      </c>
-      <c r="K8" t="s">
-        <v>55</v>
-      </c>
-      <c r="L8" t="s">
-        <v>68</v>
-      </c>
-      <c r="M8" t="s">
-        <v>64</v>
-      </c>
-      <c r="N8" t="s">
-        <v>55</v>
-      </c>
-      <c r="O8" t="s">
-        <v>52</v>
-      </c>
-      <c r="P8" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>63</v>
-      </c>
-      <c r="R8" t="s">
-        <v>63</v>
-      </c>
-      <c r="S8" t="s">
-        <v>55</v>
-      </c>
-      <c r="T8" t="s">
-        <v>59</v>
-      </c>
-      <c r="U8" t="s">
-        <v>74</v>
-      </c>
-      <c r="V8" t="s">
-        <v>63</v>
-      </c>
-      <c r="W8" t="s">
-        <v>56</v>
-      </c>
-      <c r="X8" t="s">
-        <v>63</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>63</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>66</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>55</v>
-      </c>
-      <c r="AC8" t="s">
-        <v>64</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>61</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>58</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>58</v>
-      </c>
-      <c r="AG8" t="s">
-        <v>75</v>
-      </c>
-      <c r="AH8" t="s">
-        <v>64</v>
-      </c>
-      <c r="AI8" t="s">
-        <v>60</v>
-      </c>
-      <c r="AJ8" t="s">
-        <v>68</v>
-      </c>
-      <c r="AK8" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL8" t="s">
-        <v>68</v>
-      </c>
-      <c r="AM8" t="s">
-        <v>76</v>
-      </c>
-      <c r="AN8" t="s">
-        <v>77</v>
-      </c>
-      <c r="AQ8" t="s">
-        <v>69</v>
+      <c r="AP9" t="s">
+        <v>86</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D9" t="s">
-        <v>62</v>
-      </c>
-      <c r="E9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F9" t="s">
-        <v>60</v>
-      </c>
-      <c r="G9" t="s">
-        <v>63</v>
-      </c>
-      <c r="H9" t="s">
-        <v>55</v>
-      </c>
-      <c r="I9" t="s">
-        <v>68</v>
-      </c>
-      <c r="J9" t="s">
-        <v>66</v>
-      </c>
-      <c r="K9" t="s">
-        <v>68</v>
-      </c>
-      <c r="L9" t="s">
-        <v>60</v>
-      </c>
-      <c r="M9" t="s">
-        <v>74</v>
-      </c>
-      <c r="N9" t="s">
-        <v>68</v>
-      </c>
-      <c r="O9" t="s">
-        <v>68</v>
-      </c>
-      <c r="P9" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>68</v>
-      </c>
-      <c r="R9" t="s">
-        <v>68</v>
-      </c>
-      <c r="S9" t="s">
-        <v>60</v>
-      </c>
-      <c r="T9" t="s">
-        <v>68</v>
-      </c>
-      <c r="U9" t="s">
-        <v>60</v>
-      </c>
-      <c r="V9" t="s">
-        <v>60</v>
-      </c>
-      <c r="W9" t="s">
-        <v>68</v>
-      </c>
-      <c r="X9" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>68</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>68</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>58</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC9" t="s">
-        <v>68</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>78</v>
-      </c>
-      <c r="AE9" t="s">
-        <v>75</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>78</v>
-      </c>
-      <c r="AG9" t="s">
-        <v>61</v>
-      </c>
-      <c r="AH9" t="s">
-        <v>68</v>
-      </c>
-      <c r="AI9" t="s">
-        <v>79</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK9" t="s">
-        <v>65</v>
-      </c>
-      <c r="AL9" t="s">
-        <v>61</v>
-      </c>
-      <c r="AM9" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>52</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D10" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E10" t="s">
         <v>52</v>
       </c>
       <c r="F10" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="I10" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="J10" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K10" t="s">
+        <v>61</v>
+      </c>
+      <c r="L10" t="s">
+        <v>69</v>
+      </c>
+      <c r="M10" t="s">
+        <v>69</v>
+      </c>
+      <c r="N10" t="s">
+        <v>61</v>
+      </c>
+      <c r="O10" t="s">
         <v>60</v>
       </c>
-      <c r="L10" t="s">
-        <v>66</v>
-      </c>
-      <c r="M10" t="s">
-        <v>60</v>
-      </c>
-      <c r="N10" t="s">
-        <v>66</v>
-      </c>
-      <c r="O10" t="s">
-        <v>66</v>
-      </c>
       <c r="P10" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="Q10" t="s">
         <v>60</v>
       </c>
       <c r="R10" t="s">
+        <v>69</v>
+      </c>
+      <c r="S10" t="s">
+        <v>87</v>
+      </c>
+      <c r="T10" t="s">
+        <v>60</v>
+      </c>
+      <c r="U10" t="s">
+        <v>69</v>
+      </c>
+      <c r="V10" t="s">
+        <v>88</v>
+      </c>
+      <c r="W10" t="s">
+        <v>88</v>
+      </c>
+      <c r="X10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>74</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>68</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>81</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>85</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>69</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>85</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>68</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>75</v>
+      </c>
+      <c r="AM10" t="s">
+        <v>84</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>86</v>
+      </c>
+      <c r="AO10" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" t="s">
+        <v>72</v>
+      </c>
+      <c r="F11" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H11" t="s">
+        <v>61</v>
+      </c>
+      <c r="I11" t="s">
+        <v>88</v>
+      </c>
+      <c r="J11" t="s">
+        <v>60</v>
+      </c>
+      <c r="K11" t="s">
+        <v>60</v>
+      </c>
+      <c r="L11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M11" t="s">
+        <v>60</v>
+      </c>
+      <c r="N11" t="s">
+        <v>69</v>
+      </c>
+      <c r="O11" t="s">
+        <v>68</v>
+      </c>
+      <c r="P11" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>64</v>
+      </c>
+      <c r="R11" t="s">
+        <v>60</v>
+      </c>
+      <c r="S11" t="s">
+        <v>60</v>
+      </c>
+      <c r="T11" t="s">
         <v>80</v>
       </c>
-      <c r="S10" t="s">
-        <v>58</v>
-      </c>
-      <c r="T10" t="s">
-        <v>66</v>
-      </c>
-      <c r="U10" t="s">
-        <v>58</v>
-      </c>
-      <c r="V10" t="s">
+      <c r="U11" t="s">
+        <v>60</v>
+      </c>
+      <c r="V11" t="s">
+        <v>64</v>
+      </c>
+      <c r="W11" t="s">
+        <v>64</v>
+      </c>
+      <c r="X11" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>88</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>89</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>54</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>73</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>89</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>76</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>89</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK11" t="s">
         <v>81</v>
       </c>
-      <c r="W10" t="s">
-        <v>80</v>
-      </c>
-      <c r="X10" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y10" t="s">
+      <c r="AL11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AM11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" t="s">
         <v>60</v>
       </c>
-      <c r="Z10" t="s">
-        <v>65</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>65</v>
-      </c>
-      <c r="AB10" t="s">
+      <c r="D12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E12" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12" t="s">
+        <v>88</v>
+      </c>
+      <c r="G12" t="s">
+        <v>60</v>
+      </c>
+      <c r="H12" t="s">
+        <v>69</v>
+      </c>
+      <c r="I12" t="s">
+        <v>64</v>
+      </c>
+      <c r="J12" t="s">
+        <v>64</v>
+      </c>
+      <c r="K12" t="s">
+        <v>64</v>
+      </c>
+      <c r="L12" t="s">
+        <v>68</v>
+      </c>
+      <c r="M12" t="s">
+        <v>68</v>
+      </c>
+      <c r="N12" t="s">
+        <v>73</v>
+      </c>
+      <c r="O12" t="s">
+        <v>64</v>
+      </c>
+      <c r="P12" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>84</v>
+      </c>
+      <c r="R12" t="s">
+        <v>68</v>
+      </c>
+      <c r="S12" t="s">
+        <v>85</v>
+      </c>
+      <c r="T12" t="s">
+        <v>84</v>
+      </c>
+      <c r="U12" t="s">
+        <v>64</v>
+      </c>
+      <c r="V12" t="s">
+        <v>84</v>
+      </c>
+      <c r="W12" t="s">
         <v>74</v>
       </c>
-      <c r="AC10" t="s">
+      <c r="X12" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>73</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>71</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>73</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>92</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>75</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>75</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>89</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>78</v>
+      </c>
+      <c r="AM12" t="s">
+        <v>93</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E13" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13" t="s">
+        <v>64</v>
+      </c>
+      <c r="G13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H13" t="s">
+        <v>68</v>
+      </c>
+      <c r="I13" t="s">
         <v>81</v>
       </c>
-      <c r="AD10" t="s">
-        <v>76</v>
-      </c>
-      <c r="AE10" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>71</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>78</v>
-      </c>
-      <c r="AH10" t="s">
+      <c r="J13" t="s">
+        <v>84</v>
+      </c>
+      <c r="K13" t="s">
+        <v>72</v>
+      </c>
+      <c r="L13" t="s">
+        <v>64</v>
+      </c>
+      <c r="M13" t="s">
+        <v>73</v>
+      </c>
+      <c r="N13" t="s">
+        <v>74</v>
+      </c>
+      <c r="O13" t="s">
+        <v>74</v>
+      </c>
+      <c r="P13" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>73</v>
+      </c>
+      <c r="R13" t="s">
+        <v>73</v>
+      </c>
+      <c r="S13" t="s">
+        <v>84</v>
+      </c>
+      <c r="T13" t="s">
+        <v>74</v>
+      </c>
+      <c r="U13" t="s">
+        <v>73</v>
+      </c>
+      <c r="V13" t="s">
         <v>60</v>
       </c>
-      <c r="AI10" t="s">
+      <c r="W13" t="s">
         <v>81</v>
       </c>
-      <c r="AJ10" t="s">
-        <v>65</v>
-      </c>
-      <c r="AK10" t="s">
-        <v>79</v>
-      </c>
-      <c r="AL10" t="s">
-        <v>72</v>
-      </c>
-      <c r="AM10" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>68</v>
-      </c>
-      <c r="B11" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D11" t="s">
-        <v>58</v>
-      </c>
-      <c r="E11" t="s">
-        <v>68</v>
-      </c>
-      <c r="F11" t="s">
-        <v>58</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="X13" t="s">
         <v>74</v>
       </c>
-      <c r="H11" t="s">
-        <v>60</v>
-      </c>
-      <c r="I11" t="s">
-        <v>82</v>
-      </c>
-      <c r="J11" t="s">
-        <v>61</v>
-      </c>
-      <c r="K11" t="s">
-        <v>58</v>
-      </c>
-      <c r="L11" t="s">
-        <v>81</v>
-      </c>
-      <c r="M11" t="s">
-        <v>58</v>
-      </c>
-      <c r="N11" t="s">
-        <v>58</v>
-      </c>
-      <c r="O11" t="s">
-        <v>58</v>
-      </c>
-      <c r="P11" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>66</v>
-      </c>
-      <c r="R11" t="s">
-        <v>58</v>
-      </c>
-      <c r="S11" t="s">
-        <v>75</v>
-      </c>
-      <c r="T11" t="s">
-        <v>58</v>
-      </c>
-      <c r="U11" t="s">
-        <v>65</v>
-      </c>
-      <c r="V11" t="s">
-        <v>61</v>
-      </c>
-      <c r="W11" t="s">
-        <v>79</v>
-      </c>
-      <c r="X11" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>81</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>81</v>
-      </c>
-      <c r="AB11" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC11" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>82</v>
-      </c>
-      <c r="AE11" t="s">
-        <v>83</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>82</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>53</v>
-      </c>
-      <c r="AH11" t="s">
-        <v>82</v>
-      </c>
-      <c r="AI11" t="s">
-        <v>71</v>
-      </c>
-      <c r="AJ11" t="s">
-        <v>76</v>
-      </c>
-      <c r="AK11" t="s">
-        <v>69</v>
-      </c>
-      <c r="AL11" t="s">
-        <v>84</v>
-      </c>
-      <c r="AM11" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>60</v>
-      </c>
-      <c r="B12" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" t="s">
-        <v>58</v>
-      </c>
-      <c r="D12" t="s">
-        <v>65</v>
-      </c>
-      <c r="E12" t="s">
-        <v>60</v>
-      </c>
-      <c r="F12" t="s">
-        <v>81</v>
-      </c>
-      <c r="G12" t="s">
-        <v>58</v>
-      </c>
-      <c r="H12" t="s">
-        <v>66</v>
-      </c>
-      <c r="I12" t="s">
-        <v>85</v>
-      </c>
-      <c r="J12" t="s">
-        <v>78</v>
-      </c>
-      <c r="K12" t="s">
-        <v>61</v>
-      </c>
-      <c r="L12" t="s">
-        <v>61</v>
-      </c>
-      <c r="M12" t="s">
-        <v>61</v>
-      </c>
-      <c r="N12" t="s">
-        <v>65</v>
-      </c>
-      <c r="O12" t="s">
-        <v>65</v>
-      </c>
-      <c r="P12" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>69</v>
-      </c>
-      <c r="R12" t="s">
-        <v>79</v>
-      </c>
-      <c r="S12" t="s">
-        <v>78</v>
-      </c>
-      <c r="T12" t="s">
-        <v>61</v>
-      </c>
-      <c r="U12" t="s">
-        <v>61</v>
-      </c>
-      <c r="V12" t="s">
-        <v>78</v>
-      </c>
-      <c r="W12" t="s">
-        <v>78</v>
-      </c>
-      <c r="X12" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>65</v>
-      </c>
-      <c r="Z12" t="s">
-        <v>79</v>
-      </c>
-      <c r="AA12" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB12" t="s">
-        <v>69</v>
-      </c>
-      <c r="AC12" t="s">
-        <v>71</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>67</v>
-      </c>
-      <c r="AE12" t="s">
-        <v>70</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>72</v>
-      </c>
-      <c r="AG12" t="s">
-        <v>69</v>
-      </c>
-      <c r="AH12" t="s">
-        <v>72</v>
-      </c>
-      <c r="AI12" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJ12" t="s">
-        <v>82</v>
-      </c>
-      <c r="AK12" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL12" t="s">
+      <c r="Y13" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B13" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" t="s">
-        <v>65</v>
-      </c>
-      <c r="D13" t="s">
-        <v>81</v>
-      </c>
-      <c r="E13" t="s">
-        <v>65</v>
-      </c>
-      <c r="F13" t="s">
-        <v>61</v>
-      </c>
-      <c r="G13" t="s">
-        <v>61</v>
-      </c>
-      <c r="H13" t="s">
-        <v>65</v>
-      </c>
-      <c r="I13" t="s">
-        <v>72</v>
-      </c>
-      <c r="J13" t="s">
-        <v>69</v>
-      </c>
-      <c r="K13" t="s">
-        <v>78</v>
-      </c>
-      <c r="L13" t="s">
-        <v>76</v>
-      </c>
-      <c r="M13" t="s">
-        <v>68</v>
-      </c>
-      <c r="N13" t="s">
-        <v>61</v>
-      </c>
-      <c r="O13" t="s">
-        <v>69</v>
-      </c>
-      <c r="P13" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>71</v>
-      </c>
-      <c r="R13" t="s">
-        <v>78</v>
-      </c>
-      <c r="S13" t="s">
-        <v>71</v>
-      </c>
-      <c r="T13" t="s">
-        <v>69</v>
-      </c>
-      <c r="U13" t="s">
-        <v>71</v>
-      </c>
-      <c r="V13" t="s">
-        <v>58</v>
-      </c>
-      <c r="W13" t="s">
-        <v>71</v>
-      </c>
-      <c r="X13" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>69</v>
-      </c>
       <c r="Z13" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AA13" t="s">
         <v>71</v>
       </c>
       <c r="AB13" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="AC13" t="s">
         <v>76</v>
       </c>
       <c r="AD13" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AE13" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="AF13" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="AG13" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="AH13" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="AI13" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AJ13" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AK13" t="s">
         <v>82</v>
       </c>
+      <c r="AL13" t="s">
+        <v>83</v>
+      </c>
+      <c r="AM13" t="s">
+        <v>95</v>
+      </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E14" t="s">
+        <v>88</v>
+      </c>
+      <c r="F14" t="s">
+        <v>84</v>
+      </c>
+      <c r="G14" t="s">
+        <v>84</v>
+      </c>
+      <c r="H14" t="s">
+        <v>64</v>
+      </c>
+      <c r="I14" t="s">
+        <v>89</v>
+      </c>
+      <c r="J14" t="s">
+        <v>74</v>
+      </c>
+      <c r="K14" t="s">
+        <v>74</v>
+      </c>
+      <c r="L14" t="s">
+        <v>73</v>
+      </c>
+      <c r="M14" t="s">
+        <v>92</v>
+      </c>
+      <c r="N14" t="s">
+        <v>81</v>
+      </c>
+      <c r="O14" t="s">
+        <v>76</v>
+      </c>
+      <c r="P14" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>74</v>
+      </c>
+      <c r="R14" t="s">
+        <v>74</v>
+      </c>
+      <c r="S14" t="s">
+        <v>89</v>
+      </c>
+      <c r="T14" t="s">
+        <v>89</v>
+      </c>
+      <c r="U14" t="s">
+        <v>76</v>
+      </c>
+      <c r="V14" t="s">
+        <v>73</v>
+      </c>
+      <c r="W14" t="s">
+        <v>71</v>
+      </c>
+      <c r="X14" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB14" t="s">
         <v>75</v>
       </c>
-      <c r="C14" t="s">
+      <c r="AC14" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>82</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>96</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>96</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>96</v>
+      </c>
+      <c r="AL14" t="s">
+        <v>95</v>
+      </c>
+      <c r="AM14" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" t="s">
+        <v>84</v>
+      </c>
+      <c r="E15" t="s">
+        <v>64</v>
+      </c>
+      <c r="F15" t="s">
+        <v>74</v>
+      </c>
+      <c r="G15" t="s">
+        <v>73</v>
+      </c>
+      <c r="H15" t="s">
+        <v>74</v>
+      </c>
+      <c r="I15" t="s">
+        <v>75</v>
+      </c>
+      <c r="J15" t="s">
         <v>81</v>
       </c>
-      <c r="D14" t="s">
-        <v>61</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="K15" t="s">
         <v>81</v>
       </c>
-      <c r="F14" t="s">
-        <v>78</v>
-      </c>
-      <c r="G14" t="s">
-        <v>78</v>
-      </c>
-      <c r="H14" t="s">
-        <v>61</v>
-      </c>
-      <c r="I14" t="s">
-        <v>77</v>
-      </c>
-      <c r="J14" t="s">
-        <v>71</v>
-      </c>
-      <c r="K14" t="s">
-        <v>71</v>
-      </c>
-      <c r="L14" t="s">
-        <v>82</v>
-      </c>
-      <c r="M14" t="s">
-        <v>71</v>
-      </c>
-      <c r="N14" t="s">
-        <v>69</v>
-      </c>
-      <c r="O14" t="s">
-        <v>71</v>
-      </c>
-      <c r="P14" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>76</v>
-      </c>
-      <c r="R14" t="s">
-        <v>82</v>
-      </c>
-      <c r="S14" t="s">
-        <v>82</v>
-      </c>
-      <c r="T14" t="s">
-        <v>70</v>
-      </c>
-      <c r="U14" t="s">
-        <v>70</v>
-      </c>
-      <c r="V14" t="s">
-        <v>69</v>
-      </c>
-      <c r="W14" t="s">
-        <v>82</v>
-      </c>
-      <c r="X14" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>86</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>70</v>
-      </c>
-      <c r="AB14" t="s">
-        <v>82</v>
-      </c>
-      <c r="AC14" t="s">
-        <v>67</v>
-      </c>
-      <c r="AD14" t="s">
-        <v>84</v>
-      </c>
-      <c r="AE14" t="s">
-        <v>67</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH14" t="s">
-        <v>83</v>
-      </c>
-      <c r="AI14" t="s">
-        <v>87</v>
-      </c>
-      <c r="AJ14" t="s">
-        <v>87</v>
-      </c>
-      <c r="AK14" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>65</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="L15" t="s">
         <v>81</v>
-      </c>
-      <c r="C15" t="s">
-        <v>61</v>
-      </c>
-      <c r="D15" t="s">
-        <v>78</v>
-      </c>
-      <c r="E15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F15" t="s">
-        <v>71</v>
-      </c>
-      <c r="G15" t="s">
-        <v>69</v>
-      </c>
-      <c r="H15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I15" t="s">
-        <v>73</v>
-      </c>
-      <c r="J15" t="s">
-        <v>86</v>
-      </c>
-      <c r="K15" t="s">
-        <v>76</v>
-      </c>
-      <c r="L15" t="s">
-        <v>72</v>
       </c>
       <c r="M15" t="s">
         <v>76</v>
       </c>
       <c r="N15" t="s">
+        <v>89</v>
+      </c>
+      <c r="O15" t="s">
+        <v>89</v>
+      </c>
+      <c r="P15" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>92</v>
+      </c>
+      <c r="R15" t="s">
+        <v>81</v>
+      </c>
+      <c r="S15" t="s">
+        <v>75</v>
+      </c>
+      <c r="T15" t="s">
+        <v>75</v>
+      </c>
+      <c r="U15" t="s">
+        <v>89</v>
+      </c>
+      <c r="V15" t="s">
+        <v>81</v>
+      </c>
+      <c r="W15" t="s">
+        <v>82</v>
+      </c>
+      <c r="X15" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>71</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>85</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>82</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>71</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF15" t="s">
+        <v>74</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>87</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>63</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK15" t="s">
+        <v>70</v>
+      </c>
+      <c r="AL15" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>88</v>
+      </c>
+      <c r="B16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D16" t="s">
+        <v>73</v>
+      </c>
+      <c r="E16" t="s">
+        <v>73</v>
+      </c>
+      <c r="F16" t="s">
+        <v>81</v>
+      </c>
+      <c r="G16" t="s">
+        <v>74</v>
+      </c>
+      <c r="H16" t="s">
         <v>76</v>
       </c>
-      <c r="O15" t="s">
+      <c r="I16" t="s">
+        <v>71</v>
+      </c>
+      <c r="J16" t="s">
+        <v>71</v>
+      </c>
+      <c r="K16" t="s">
+        <v>89</v>
+      </c>
+      <c r="L16" t="s">
         <v>76</v>
       </c>
-      <c r="P15" t="s">
+      <c r="M16" t="s">
+        <v>75</v>
+      </c>
+      <c r="N16" t="s">
+        <v>75</v>
+      </c>
+      <c r="O16" t="s">
+        <v>71</v>
+      </c>
+      <c r="P16" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>81</v>
+      </c>
+      <c r="R16" t="s">
+        <v>76</v>
+      </c>
+      <c r="S16" t="s">
+        <v>71</v>
+      </c>
+      <c r="T16" t="s">
+        <v>96</v>
+      </c>
+      <c r="U16" t="s">
+        <v>71</v>
+      </c>
+      <c r="V16" t="s">
+        <v>76</v>
+      </c>
+      <c r="W16" t="s">
+        <v>96</v>
+      </c>
+      <c r="X16" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>82</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>98</v>
+      </c>
+      <c r="AB16" t="s">
         <v>70</v>
       </c>
-      <c r="Q15" t="s">
+      <c r="AC16" t="s">
+        <v>90</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>70</v>
+      </c>
+      <c r="AG16" t="s">
+        <v>63</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>70</v>
+      </c>
+      <c r="AI16" t="s">
+        <v>93</v>
+      </c>
+      <c r="AJ16" t="s">
+        <v>95</v>
+      </c>
+      <c r="AK16" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" t="s">
+        <v>74</v>
+      </c>
+      <c r="D17" t="s">
+        <v>74</v>
+      </c>
+      <c r="E17" t="s">
+        <v>74</v>
+      </c>
+      <c r="F17" t="s">
+        <v>89</v>
+      </c>
+      <c r="G17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H17" t="s">
+        <v>75</v>
+      </c>
+      <c r="I17" t="s">
+        <v>96</v>
+      </c>
+      <c r="J17" t="s">
+        <v>96</v>
+      </c>
+      <c r="K17" t="s">
         <v>82</v>
       </c>
-      <c r="R15" t="s">
-        <v>72</v>
-      </c>
-      <c r="S15" t="s">
-        <v>72</v>
-      </c>
-      <c r="T15" t="s">
+      <c r="L17" t="s">
+        <v>75</v>
+      </c>
+      <c r="M17" t="s">
+        <v>71</v>
+      </c>
+      <c r="N17" t="s">
         <v>82</v>
       </c>
-      <c r="U15" t="s">
+      <c r="O17" t="s">
+        <v>78</v>
+      </c>
+      <c r="P17" t="s">
         <v>82</v>
       </c>
-      <c r="V15" t="s">
+      <c r="Q17" t="s">
+        <v>71</v>
+      </c>
+      <c r="R17" t="s">
+        <v>89</v>
+      </c>
+      <c r="S17" t="s">
+        <v>90</v>
+      </c>
+      <c r="T17" t="s">
+        <v>99</v>
+      </c>
+      <c r="U17" t="s">
+        <v>82</v>
+      </c>
+      <c r="V17" t="s">
+        <v>99</v>
+      </c>
+      <c r="W17" t="s">
+        <v>92</v>
+      </c>
+      <c r="X17" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>96</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>63</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>100</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>63</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG17" t="s">
+        <v>93</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>83</v>
+      </c>
+      <c r="AI17" t="s">
+        <v>77</v>
+      </c>
+      <c r="AJ17" t="s">
+        <v>58</v>
+      </c>
+      <c r="AK17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" t="s">
+        <v>92</v>
+      </c>
+      <c r="D18" t="s">
+        <v>92</v>
+      </c>
+      <c r="E18" t="s">
+        <v>71</v>
+      </c>
+      <c r="F18" t="s">
+        <v>71</v>
+      </c>
+      <c r="G18" t="s">
+        <v>75</v>
+      </c>
+      <c r="H18" t="s">
+        <v>71</v>
+      </c>
+      <c r="I18" t="s">
+        <v>90</v>
+      </c>
+      <c r="J18" t="s">
+        <v>90</v>
+      </c>
+      <c r="K18" t="s">
+        <v>90</v>
+      </c>
+      <c r="L18" t="s">
+        <v>90</v>
+      </c>
+      <c r="M18" t="s">
+        <v>82</v>
+      </c>
+      <c r="N18" t="s">
+        <v>78</v>
+      </c>
+      <c r="O18" t="s">
+        <v>93</v>
+      </c>
+      <c r="P18" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>82</v>
+      </c>
+      <c r="R18" t="s">
+        <v>71</v>
+      </c>
+      <c r="S18" t="s">
+        <v>93</v>
+      </c>
+      <c r="T18" t="s">
+        <v>63</v>
+      </c>
+      <c r="U18" t="s">
+        <v>70</v>
+      </c>
+      <c r="V18" t="s">
+        <v>101</v>
+      </c>
+      <c r="W18" t="s">
+        <v>63</v>
+      </c>
+      <c r="X18" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>93</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>95</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>100</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE18" t="s">
+        <v>83</v>
+      </c>
+      <c r="AF18" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG18" t="s">
+        <v>100</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>95</v>
+      </c>
+      <c r="AI18" t="s">
+        <v>86</v>
+      </c>
+      <c r="AJ18" t="s">
+        <v>86</v>
+      </c>
+      <c r="AK18" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" t="s">
+        <v>81</v>
+      </c>
+      <c r="D19" t="s">
+        <v>81</v>
+      </c>
+      <c r="E19" t="s">
+        <v>96</v>
+      </c>
+      <c r="F19" t="s">
+        <v>82</v>
+      </c>
+      <c r="G19" t="s">
+        <v>82</v>
+      </c>
+      <c r="H19" t="s">
+        <v>96</v>
+      </c>
+      <c r="I19" t="s">
+        <v>78</v>
+      </c>
+      <c r="J19" t="s">
+        <v>78</v>
+      </c>
+      <c r="K19" t="s">
+        <v>93</v>
+      </c>
+      <c r="L19" t="s">
+        <v>70</v>
+      </c>
+      <c r="M19" t="s">
+        <v>63</v>
+      </c>
+      <c r="N19" t="s">
+        <v>63</v>
+      </c>
+      <c r="O19" t="s">
+        <v>100</v>
+      </c>
+      <c r="P19" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>96</v>
+      </c>
+      <c r="R19" t="s">
+        <v>63</v>
+      </c>
+      <c r="S19" t="s">
+        <v>102</v>
+      </c>
+      <c r="T19" t="s">
+        <v>83</v>
+      </c>
+      <c r="U19" t="s">
+        <v>77</v>
+      </c>
+      <c r="V19" t="s">
+        <v>100</v>
+      </c>
+      <c r="W19" t="s">
+        <v>70</v>
+      </c>
+      <c r="X19" t="s">
+        <v>93</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>102</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>83</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>100</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>95</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>86</v>
+      </c>
+      <c r="AG19" t="s">
+        <v>77</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>86</v>
+      </c>
+      <c r="AI19" t="s">
+        <v>94</v>
+      </c>
+      <c r="AJ19" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>92</v>
+      </c>
+      <c r="B20" t="s">
+        <v>92</v>
+      </c>
+      <c r="C20" t="s">
+        <v>89</v>
+      </c>
+      <c r="D20" t="s">
+        <v>89</v>
+      </c>
+      <c r="E20" t="s">
+        <v>90</v>
+      </c>
+      <c r="F20" t="s">
+        <v>78</v>
+      </c>
+      <c r="G20" t="s">
+        <v>70</v>
+      </c>
+      <c r="H20" t="s">
+        <v>73</v>
+      </c>
+      <c r="I20" t="s">
         <v>76</v>
       </c>
-      <c r="W15" t="s">
-        <v>85</v>
-      </c>
-      <c r="X15" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y15" t="s">
+      <c r="J20" t="s">
+        <v>63</v>
+      </c>
+      <c r="K20" t="s">
+        <v>83</v>
+      </c>
+      <c r="L20" t="s">
+        <v>93</v>
+      </c>
+      <c r="M20" t="s">
+        <v>70</v>
+      </c>
+      <c r="N20" t="s">
+        <v>93</v>
+      </c>
+      <c r="O20" t="s">
+        <v>77</v>
+      </c>
+      <c r="P20" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>63</v>
+      </c>
+      <c r="R20" t="s">
+        <v>77</v>
+      </c>
+      <c r="S20" t="s">
+        <v>83</v>
+      </c>
+      <c r="T20" t="s">
+        <v>95</v>
+      </c>
+      <c r="U20" t="s">
+        <v>83</v>
+      </c>
+      <c r="V20" t="s">
+        <v>77</v>
+      </c>
+      <c r="W20" t="s">
+        <v>100</v>
+      </c>
+      <c r="X20" t="s">
+        <v>95</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>95</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>83</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>83</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD20" t="s">
+        <v>58</v>
+      </c>
+      <c r="AE20" t="s">
+        <v>86</v>
+      </c>
+      <c r="AF20" t="s">
+        <v>94</v>
+      </c>
+      <c r="AG20" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>91</v>
+      </c>
+      <c r="AI20" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>89</v>
+      </c>
+      <c r="B21" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" t="s">
+        <v>98</v>
+      </c>
+      <c r="D21" t="s">
+        <v>98</v>
+      </c>
+      <c r="E21" t="s">
+        <v>63</v>
+      </c>
+      <c r="F21" t="s">
+        <v>68</v>
+      </c>
+      <c r="G21" t="s">
+        <v>100</v>
+      </c>
+      <c r="H21" t="s">
+        <v>63</v>
+      </c>
+      <c r="I21" t="s">
+        <v>63</v>
+      </c>
+      <c r="J21" t="s">
+        <v>93</v>
+      </c>
+      <c r="K21" t="s">
+        <v>95</v>
+      </c>
+      <c r="L21" t="s">
+        <v>100</v>
+      </c>
+      <c r="M21" t="s">
+        <v>77</v>
+      </c>
+      <c r="N21" t="s">
+        <v>100</v>
+      </c>
+      <c r="O21" t="s">
+        <v>95</v>
+      </c>
+      <c r="P21" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>70</v>
+      </c>
+      <c r="R21" t="s">
+        <v>86</v>
+      </c>
+      <c r="S21" t="s">
+        <v>95</v>
+      </c>
+      <c r="T21" t="s">
+        <v>58</v>
+      </c>
+      <c r="U21" t="s">
+        <v>58</v>
+      </c>
+      <c r="V21" t="s">
+        <v>95</v>
+      </c>
+      <c r="W21" t="s">
+        <v>77</v>
+      </c>
+      <c r="X21" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>94</v>
+      </c>
+      <c r="AD21" t="s">
+        <v>86</v>
+      </c>
+      <c r="AE21" t="s">
+        <v>91</v>
+      </c>
+      <c r="AF21" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" t="s">
+        <v>71</v>
+      </c>
+      <c r="D22" t="s">
+        <v>71</v>
+      </c>
+      <c r="E22" t="s">
+        <v>101</v>
+      </c>
+      <c r="F22" t="s">
+        <v>70</v>
+      </c>
+      <c r="G22" t="s">
+        <v>77</v>
+      </c>
+      <c r="H22" t="s">
+        <v>93</v>
+      </c>
+      <c r="I22" t="s">
+        <v>70</v>
+      </c>
+      <c r="J22" t="s">
+        <v>77</v>
+      </c>
+      <c r="K22" t="s">
+        <v>58</v>
+      </c>
+      <c r="L22" t="s">
+        <v>95</v>
+      </c>
+      <c r="M22" t="s">
+        <v>83</v>
+      </c>
+      <c r="N22" t="s">
+        <v>77</v>
+      </c>
+      <c r="O22" t="s">
+        <v>58</v>
+      </c>
+      <c r="P22" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>93</v>
+      </c>
+      <c r="R22" t="s">
+        <v>94</v>
+      </c>
+      <c r="S22" t="s">
+        <v>58</v>
+      </c>
+      <c r="T22" t="s">
+        <v>86</v>
+      </c>
+      <c r="U22" t="s">
+        <v>94</v>
+      </c>
+      <c r="V22" t="s">
+        <v>58</v>
+      </c>
+      <c r="W22" t="s">
+        <v>95</v>
+      </c>
+      <c r="X22" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>82</v>
       </c>
-      <c r="Z15" t="s">
+      <c r="B23" t="s">
+        <v>75</v>
+      </c>
+      <c r="C23" t="s">
         <v>82</v>
       </c>
-      <c r="AA15" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB15" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC15" t="s">
+      <c r="D23" t="s">
+        <v>82</v>
+      </c>
+      <c r="E23" t="s">
+        <v>93</v>
+      </c>
+      <c r="F23" t="s">
+        <v>93</v>
+      </c>
+      <c r="G23" t="s">
+        <v>83</v>
+      </c>
+      <c r="H23" t="s">
         <v>77</v>
       </c>
-      <c r="AD15" t="s">
-        <v>73</v>
-      </c>
-      <c r="AE15" t="s">
-        <v>87</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG15" t="s">
-        <v>73</v>
-      </c>
-      <c r="AH15" t="s">
+      <c r="I23" t="s">
+        <v>93</v>
+      </c>
+      <c r="J23" t="s">
+        <v>95</v>
+      </c>
+      <c r="K23" t="s">
+        <v>94</v>
+      </c>
+      <c r="L23" t="s">
+        <v>58</v>
+      </c>
+      <c r="M23" t="s">
+        <v>58</v>
+      </c>
+      <c r="N23" t="s">
+        <v>95</v>
+      </c>
+      <c r="O23" t="s">
+        <v>86</v>
+      </c>
+      <c r="P23" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>102</v>
+      </c>
+      <c r="R23" t="s">
+        <v>91</v>
+      </c>
+      <c r="S23" t="s">
+        <v>94</v>
+      </c>
+      <c r="T23" t="s">
+        <v>94</v>
+      </c>
+      <c r="U23" t="s">
+        <v>91</v>
+      </c>
+      <c r="V23" t="s">
+        <v>94</v>
+      </c>
+      <c r="W23" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>96</v>
+      </c>
+      <c r="B24" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24" t="s">
+        <v>78</v>
+      </c>
+      <c r="D24" t="s">
+        <v>99</v>
+      </c>
+      <c r="E24" t="s">
+        <v>102</v>
+      </c>
+      <c r="F24" t="s">
+        <v>83</v>
+      </c>
+      <c r="G24" t="s">
+        <v>58</v>
+      </c>
+      <c r="H24" t="s">
+        <v>95</v>
+      </c>
+      <c r="I24" t="s">
+        <v>95</v>
+      </c>
+      <c r="J24" t="s">
+        <v>94</v>
+      </c>
+      <c r="K24" t="s">
+        <v>91</v>
+      </c>
+      <c r="L24" t="s">
+        <v>94</v>
+      </c>
+      <c r="M24" t="s">
+        <v>94</v>
+      </c>
+      <c r="N24" t="s">
+        <v>94</v>
+      </c>
+      <c r="O24" t="s">
+        <v>91</v>
+      </c>
+      <c r="P24" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>90</v>
+      </c>
+      <c r="B25" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25" t="s">
+        <v>63</v>
+      </c>
+      <c r="D25" t="s">
+        <v>78</v>
+      </c>
+      <c r="E25" t="s">
+        <v>95</v>
+      </c>
+      <c r="F25" t="s">
+        <v>58</v>
+      </c>
+      <c r="G25" t="s">
+        <v>86</v>
+      </c>
+      <c r="H25" t="s">
+        <v>58</v>
+      </c>
+      <c r="I25" t="s">
+        <v>86</v>
+      </c>
+      <c r="J25" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>99</v>
+      </c>
+      <c r="B26" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" t="s">
+        <v>101</v>
+      </c>
+      <c r="D26" t="s">
+        <v>63</v>
+      </c>
+      <c r="E26" t="s">
+        <v>86</v>
+      </c>
+      <c r="F26" t="s">
+        <v>94</v>
+      </c>
+      <c r="G26" t="s">
+        <v>91</v>
+      </c>
+      <c r="H26" t="s">
+        <v>86</v>
+      </c>
+      <c r="I26" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" t="s">
+        <v>78</v>
+      </c>
+      <c r="C27" t="s">
+        <v>93</v>
+      </c>
+      <c r="D27" t="s">
+        <v>97</v>
+      </c>
+      <c r="E27" t="s">
+        <v>91</v>
+      </c>
+      <c r="F27" t="s">
+        <v>91</v>
+      </c>
+      <c r="H27" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>81</v>
-      </c>
-      <c r="B16" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" t="s">
-        <v>78</v>
-      </c>
-      <c r="D16" t="s">
-        <v>69</v>
-      </c>
-      <c r="E16" t="s">
-        <v>69</v>
-      </c>
-      <c r="F16" t="s">
-        <v>76</v>
-      </c>
-      <c r="G16" t="s">
-        <v>71</v>
-      </c>
-      <c r="H16" t="s">
+    <row r="28" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" t="s">
+        <v>102</v>
+      </c>
+      <c r="D28" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>101</v>
+      </c>
+      <c r="B29" t="s">
         <v>70</v>
       </c>
-      <c r="I16" t="s">
-        <v>80</v>
-      </c>
-      <c r="J16" t="s">
-        <v>76</v>
-      </c>
-      <c r="K16" t="s">
-        <v>67</v>
-      </c>
-      <c r="L16" t="s">
-        <v>67</v>
-      </c>
-      <c r="M16" t="s">
-        <v>82</v>
-      </c>
-      <c r="N16" t="s">
-        <v>70</v>
-      </c>
-      <c r="O16" t="s">
-        <v>70</v>
-      </c>
-      <c r="P16" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>72</v>
-      </c>
-      <c r="R16" t="s">
-        <v>67</v>
-      </c>
-      <c r="S16" t="s">
-        <v>87</v>
-      </c>
-      <c r="T16" t="s">
-        <v>67</v>
-      </c>
-      <c r="U16" t="s">
-        <v>67</v>
-      </c>
-      <c r="V16" t="s">
-        <v>70</v>
-      </c>
-      <c r="W16" t="s">
-        <v>72</v>
-      </c>
-      <c r="X16" t="s">
+      <c r="C29" t="s">
+        <v>100</v>
+      </c>
+      <c r="D29" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>102</v>
+      </c>
+      <c r="B30" t="s">
+        <v>93</v>
+      </c>
+      <c r="C30" t="s">
         <v>77</v>
       </c>
-      <c r="Y16" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z16" t="s">
-        <v>72</v>
-      </c>
-      <c r="AA16" t="s">
+      <c r="D30" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B31" t="s">
+        <v>102</v>
+      </c>
+      <c r="C31" t="s">
+        <v>83</v>
+      </c>
+      <c r="D31" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>77</v>
       </c>
-      <c r="AB16" t="s">
-        <v>84</v>
-      </c>
-      <c r="AC16" t="s">
-        <v>87</v>
-      </c>
-      <c r="AD16" t="s">
+      <c r="B32" t="s">
+        <v>77</v>
+      </c>
+      <c r="C32" t="s">
+        <v>95</v>
+      </c>
+      <c r="D32" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>83</v>
+      </c>
+      <c r="B33" t="s">
+        <v>83</v>
+      </c>
+      <c r="C33" t="s">
         <v>58</v>
       </c>
+      <c r="D33" t="s">
+        <v>91</v>
+      </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>61</v>
-      </c>
-      <c r="B17" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" t="s">
-        <v>71</v>
-      </c>
-      <c r="D17" t="s">
-        <v>71</v>
-      </c>
-      <c r="E17" t="s">
-        <v>71</v>
-      </c>
-      <c r="F17" t="s">
-        <v>82</v>
-      </c>
-      <c r="G17" t="s">
-        <v>82</v>
-      </c>
-      <c r="H17" t="s">
-        <v>72</v>
-      </c>
-      <c r="J17" t="s">
-        <v>67</v>
-      </c>
-      <c r="K17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L17" t="s">
-        <v>87</v>
-      </c>
-      <c r="M17" t="s">
-        <v>77</v>
-      </c>
-      <c r="N17" t="s">
-        <v>72</v>
-      </c>
-      <c r="O17" t="s">
-        <v>82</v>
-      </c>
-      <c r="P17" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>77</v>
-      </c>
-      <c r="R17" t="s">
-        <v>84</v>
-      </c>
-      <c r="S17" t="s">
-        <v>88</v>
-      </c>
-      <c r="T17" t="s">
-        <v>77</v>
-      </c>
-      <c r="U17" t="s">
-        <v>73</v>
-      </c>
-      <c r="V17" t="s">
-        <v>88</v>
-      </c>
-      <c r="W17" t="s">
-        <v>77</v>
-      </c>
-      <c r="X17" t="s">
-        <v>73</v>
-      </c>
-      <c r="Y17" t="s">
-        <v>77</v>
-      </c>
-      <c r="Z17" t="s">
-        <v>77</v>
-      </c>
-      <c r="AA17" t="s">
-        <v>87</v>
+    <row r="34" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>95</v>
+      </c>
+      <c r="B34" t="s">
+        <v>95</v>
+      </c>
+      <c r="C34" t="s">
+        <v>86</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>69</v>
-      </c>
-      <c r="B18" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" t="s">
+    <row r="35" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>58</v>
+      </c>
+      <c r="B35" t="s">
+        <v>58</v>
+      </c>
+      <c r="C35" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>86</v>
       </c>
-      <c r="D18" t="s">
+      <c r="B36" t="s">
         <v>86</v>
       </c>
-      <c r="E18" t="s">
-        <v>67</v>
-      </c>
-      <c r="F18" t="s">
-        <v>67</v>
-      </c>
-      <c r="G18" t="s">
-        <v>72</v>
-      </c>
-      <c r="H18" t="s">
-        <v>67</v>
-      </c>
-      <c r="J18" t="s">
-        <v>77</v>
-      </c>
-      <c r="K18" t="s">
-        <v>84</v>
-      </c>
-      <c r="L18" t="s">
-        <v>84</v>
-      </c>
-      <c r="M18" t="s">
-        <v>84</v>
-      </c>
-      <c r="N18" t="s">
-        <v>84</v>
-      </c>
-      <c r="O18" t="s">
-        <v>67</v>
-      </c>
-      <c r="P18" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>73</v>
+      <c r="C36" t="s">
+        <v>91</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>71</v>
-      </c>
-      <c r="B19" t="s">
-        <v>71</v>
-      </c>
-      <c r="C19" t="s">
-        <v>76</v>
-      </c>
-      <c r="D19" t="s">
-        <v>76</v>
-      </c>
-      <c r="E19" t="s">
-        <v>87</v>
-      </c>
-      <c r="F19" t="s">
-        <v>77</v>
-      </c>
-      <c r="G19" t="s">
-        <v>77</v>
-      </c>
-      <c r="H19" t="s">
-        <v>87</v>
-      </c>
-      <c r="J19" t="s">
-        <v>87</v>
-      </c>
-      <c r="K19" t="s">
-        <v>73</v>
-      </c>
-      <c r="L19" t="s">
-        <v>73</v>
+    <row r="37" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>94</v>
+      </c>
+      <c r="B37" t="s">
+        <v>94</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>86</v>
-      </c>
-      <c r="B20" t="s">
-        <v>86</v>
-      </c>
-      <c r="C20" t="s">
-        <v>82</v>
-      </c>
-      <c r="D20" t="s">
-        <v>82</v>
-      </c>
-      <c r="E20" t="s">
-        <v>84</v>
-      </c>
-      <c r="F20" t="s">
-        <v>73</v>
-      </c>
-      <c r="H20" t="s">
-        <v>69</v>
-      </c>
-      <c r="L20" t="s">
-        <v>70</v>
+    <row r="38" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>91</v>
+      </c>
+      <c r="B38" t="s">
+        <v>91</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>82</v>
-      </c>
-      <c r="B21" t="s">
-        <v>76</v>
-      </c>
-      <c r="C21" t="s">
-        <v>85</v>
-      </c>
-      <c r="D21" t="s">
-        <v>85</v>
-      </c>
-      <c r="F21" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>72</v>
-      </c>
-      <c r="B22" t="s">
-        <v>82</v>
-      </c>
-      <c r="C22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D22" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>77</v>
-      </c>
-      <c r="B23" t="s">
-        <v>72</v>
-      </c>
-      <c r="C23" t="s">
-        <v>77</v>
-      </c>
-      <c r="D23" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>87</v>
-      </c>
-      <c r="B24" t="s">
-        <v>67</v>
-      </c>
-      <c r="C24" t="s">
-        <v>73</v>
-      </c>
-      <c r="D24" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>84</v>
-      </c>
-      <c r="B25" t="s">
-        <v>77</v>
-      </c>
-      <c r="D25" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>88</v>
-      </c>
-      <c r="B26" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>73</v>
-      </c>
-      <c r="B27" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25"/>
-    <row r="29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25"/>
     <row r="40" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="41" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="42" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3418,7 +4419,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:AN42"/>
+  <dimension ref="A3:BA42"/>
   <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="17.85546875" customWidth="1"/>
@@ -3451,15 +4452,15 @@
     <col min="98" max="98" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" t="s">
         <v>51</v>
-      </c>
-      <c r="C3" t="s">
-        <v>49</v>
       </c>
       <c r="D3" t="s">
         <v>50</v>
@@ -3468,112 +4469,151 @@
         <v>52</v>
       </c>
       <c r="F3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H3" t="s">
         <v>54</v>
       </c>
-      <c r="G3" t="s">
+      <c r="I3" t="s">
+        <v>65</v>
+      </c>
+      <c r="J3" t="s">
+        <v>62</v>
+      </c>
+      <c r="K3" t="s">
+        <v>66</v>
+      </c>
+      <c r="L3" t="s">
         <v>57</v>
       </c>
-      <c r="H3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I3" t="s">
-        <v>62</v>
-      </c>
-      <c r="J3" t="s">
-        <v>59</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="M3" t="s">
+        <v>56</v>
+      </c>
+      <c r="N3" t="s">
+        <v>67</v>
+      </c>
+      <c r="O3" t="s">
+        <v>72</v>
+      </c>
+      <c r="P3" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>61</v>
+      </c>
+      <c r="R3" t="s">
+        <v>69</v>
+      </c>
+      <c r="S3" t="s">
+        <v>87</v>
+      </c>
+      <c r="T3" t="s">
+        <v>60</v>
+      </c>
+      <c r="U3" t="s">
+        <v>80</v>
+      </c>
+      <c r="V3" t="s">
+        <v>68</v>
+      </c>
+      <c r="W3" t="s">
+        <v>88</v>
+      </c>
+      <c r="X3" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>81</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>89</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>75</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>71</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>90</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AO3" t="s">
         <v>63</v>
       </c>
-      <c r="L3" t="s">
-        <v>56</v>
-      </c>
-      <c r="M3" t="s">
-        <v>55</v>
-      </c>
-      <c r="N3" t="s">
-        <v>64</v>
-      </c>
-      <c r="O3" t="s">
-        <v>68</v>
-      </c>
-      <c r="P3" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>60</v>
-      </c>
-      <c r="R3" t="s">
-        <v>66</v>
-      </c>
-      <c r="S3" t="s">
-        <v>80</v>
-      </c>
-      <c r="T3" t="s">
+      <c r="AP3" t="s">
+        <v>101</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>93</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>102</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>100</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>83</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>95</v>
+      </c>
+      <c r="AX3" t="s">
         <v>58</v>
       </c>
-      <c r="U3" t="s">
-        <v>75</v>
-      </c>
-      <c r="V3" t="s">
-        <v>65</v>
-      </c>
-      <c r="W3" t="s">
-        <v>81</v>
-      </c>
-      <c r="X3" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>71</v>
-      </c>
-      <c r="AC3" t="s">
+      <c r="AY3" t="s">
         <v>86</v>
       </c>
-      <c r="AD3" t="s">
-        <v>76</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>70</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>82</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>85</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>72</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>67</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>77</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>87</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>84</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>88</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>73</v>
+      <c r="AZ3" t="s">
+        <v>94</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>91</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -3581,22 +4621,22 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G4" t="s">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="I4" t="s">
         <v>1</v>
@@ -3608,25 +4648,25 @@
         <v>0</v>
       </c>
       <c r="L4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M4" t="s">
+        <v>11</v>
+      </c>
+      <c r="N4" t="s">
+        <v>103</v>
+      </c>
+      <c r="O4" t="s">
         <v>13</v>
       </c>
-      <c r="N4" t="s">
-        <v>89</v>
-      </c>
-      <c r="O4" t="s">
-        <v>16</v>
-      </c>
       <c r="P4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q4" t="s">
         <v>2</v>
       </c>
       <c r="R4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="S4" t="s">
         <v>5</v>
@@ -3635,10 +4675,10 @@
         <v>2</v>
       </c>
       <c r="U4" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="V4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="W4" t="s">
         <v>5</v>
@@ -3647,16 +4687,16 @@
         <v>5</v>
       </c>
       <c r="Y4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Z4" t="s">
         <v>2</v>
       </c>
       <c r="AA4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AB4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AC4" t="s">
         <v>2</v>
@@ -3665,19 +4705,19 @@
         <v>2</v>
       </c>
       <c r="AE4" t="s">
+        <v>11</v>
+      </c>
+      <c r="AF4" t="s">
         <v>13</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>16</v>
       </c>
       <c r="AG4" t="s">
         <v>2</v>
       </c>
       <c r="AH4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AI4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ4" t="s">
         <v>2</v>
@@ -3686,16 +4726,55 @@
         <v>0</v>
       </c>
       <c r="AL4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AM4" t="s">
         <v>0</v>
       </c>
       <c r="AN4" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>13</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>2</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>18</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>1</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>33</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AY4" t="s">
+        <v>33</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BA4" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -3706,7 +4785,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
@@ -3715,31 +4794,31 @@
         <v>3</v>
       </c>
       <c r="G5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I5" t="s">
         <v>3</v>
       </c>
       <c r="J5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
       </c>
       <c r="M5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P5" t="s">
         <v>6</v>
@@ -3751,7 +4830,7 @@
         <v>3</v>
       </c>
       <c r="S5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T5" t="s">
         <v>0</v>
@@ -3769,16 +4848,16 @@
         <v>6</v>
       </c>
       <c r="Y5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Z5" t="s">
         <v>3</v>
       </c>
       <c r="AA5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AB5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AC5" t="s">
         <v>3</v>
@@ -3805,7 +4884,7 @@
         <v>0</v>
       </c>
       <c r="AK5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL5" t="s">
         <v>1</v>
@@ -3816,216 +4895,294 @@
       <c r="AN5" t="s">
         <v>1</v>
       </c>
+      <c r="AO5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>9</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>6</v>
+      </c>
+      <c r="AU5" t="s">
+        <v>3</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>3</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>2</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY5" t="s">
+        <v>3</v>
+      </c>
+      <c r="AZ5" t="s">
+        <v>9</v>
+      </c>
+      <c r="BA5" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
         <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="F6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H6" t="s">
         <v>38</v>
       </c>
       <c r="I6" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K6" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="L6" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="M6" t="s">
         <v>38</v>
       </c>
       <c r="N6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O6" t="s">
+        <v>32</v>
+      </c>
+      <c r="P6" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q6" t="s">
         <v>8</v>
-      </c>
-      <c r="P6" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>11</v>
       </c>
       <c r="R6" t="s">
         <v>38</v>
       </c>
       <c r="S6" t="s">
+        <v>32</v>
+      </c>
+      <c r="T6" t="s">
+        <v>14</v>
+      </c>
+      <c r="U6" t="s">
+        <v>19</v>
+      </c>
+      <c r="V6" t="s">
+        <v>17</v>
+      </c>
+      <c r="W6" t="s">
+        <v>22</v>
+      </c>
+      <c r="X6" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>14</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK6" t="s">
         <v>8</v>
       </c>
-      <c r="T6" t="s">
+      <c r="AL6" t="s">
+        <v>30</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>19</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>21</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>22</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>26</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>12</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>26</v>
+      </c>
+      <c r="AW6" t="s">
+        <v>19</v>
+      </c>
+      <c r="AX6" t="s">
+        <v>14</v>
+      </c>
+      <c r="AY6" t="s">
+        <v>30</v>
+      </c>
+      <c r="AZ6" t="s">
+        <v>10</v>
+      </c>
+      <c r="BA6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
         <v>20</v>
       </c>
-      <c r="U6" t="s">
-        <v>18</v>
-      </c>
-      <c r="V6" t="s">
-        <v>14</v>
-      </c>
-      <c r="W6" t="s">
-        <v>28</v>
-      </c>
-      <c r="X6" t="s">
-        <v>20</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB6" t="s">
+      <c r="C7" t="s">
         <v>31</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>25</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>20</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>20</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH6" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>20</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>25</v>
-      </c>
-      <c r="AK6" t="s">
-        <v>11</v>
-      </c>
-      <c r="AL6" t="s">
-        <v>32</v>
-      </c>
-      <c r="AM6" t="s">
-        <v>18</v>
-      </c>
-      <c r="AN6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" t="s">
-        <v>36</v>
       </c>
       <c r="D7" t="s">
         <v>37</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F7" t="s">
         <v>39</v>
       </c>
       <c r="G7" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K7" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="L7" t="s">
         <v>37</v>
       </c>
       <c r="M7" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="N7" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="O7" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="P7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Q7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="R7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="S7" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="T7" t="s">
         <v>21</v>
       </c>
       <c r="U7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="V7" t="s">
         <v>39</v>
       </c>
       <c r="W7" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="X7" t="s">
         <v>4</v>
       </c>
       <c r="Y7" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="Z7" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AA7" t="s">
         <v>39</v>
       </c>
       <c r="AB7" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="AC7" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="AD7" t="s">
         <v>29</v>
@@ -4037,16 +5194,16 @@
         <v>29</v>
       </c>
       <c r="AG7" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AH7" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AI7" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ7" t="s">
         <v>31</v>
-      </c>
-      <c r="AJ7" t="s">
-        <v>36</v>
       </c>
       <c r="AK7" t="s">
         <v>4</v>
@@ -4060,13 +5217,52 @@
       <c r="AN7" t="s">
         <v>29</v>
       </c>
+      <c r="AO7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AP7" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AR7" t="s">
+        <v>15</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>4</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AU7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>15</v>
+      </c>
+      <c r="AW7" t="s">
+        <v>37</v>
+      </c>
+      <c r="AX7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AY7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AZ7" t="s">
+        <v>21</v>
+      </c>
+      <c r="BA7" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E8" t="s">
         <v>1</v>
@@ -4078,28 +5274,28 @@
         <v>6</v>
       </c>
       <c r="H8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="R8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="T8" t="s">
         <v>5</v>
@@ -4108,63 +5304,99 @@
         <v>5</v>
       </c>
       <c r="W8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="X8" t="s">
         <v>23</v>
       </c>
       <c r="Y8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AB8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC8" t="s">
         <v>0</v>
       </c>
       <c r="AD8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AF8" t="s">
         <v>5</v>
       </c>
       <c r="AH8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI8" t="s">
         <v>23</v>
       </c>
       <c r="AJ8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AK8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AL8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AN8" t="s">
         <v>0</v>
       </c>
+      <c r="AO8" t="s">
+        <v>40</v>
+      </c>
+      <c r="AQ8" t="s">
+        <v>6</v>
+      </c>
+      <c r="AR8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AS8" t="s">
+        <v>18</v>
+      </c>
+      <c r="AT8" t="s">
+        <v>13</v>
+      </c>
+      <c r="AU8" t="s">
+        <v>9</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>18</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>1</v>
+      </c>
+      <c r="AX8" t="s">
+        <v>18</v>
+      </c>
+      <c r="AY8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ8" t="s">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C9" t="s">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F9" t="s">
         <v>1</v>
@@ -4176,7 +5408,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K9" t="s">
         <v>24</v>
@@ -4197,7 +5429,7 @@
         <v>0</v>
       </c>
       <c r="T9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V9" t="s">
         <v>24</v>
@@ -4209,7 +5441,7 @@
         <v>3</v>
       </c>
       <c r="Y9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="Z9" t="s">
         <v>6</v>
@@ -4224,137 +5456,209 @@
         <v>1</v>
       </c>
       <c r="AD9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="AF9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH9" t="s">
         <v>35</v>
-      </c>
-      <c r="AH9" t="s">
-        <v>34</v>
       </c>
       <c r="AI9" t="s">
         <v>1</v>
       </c>
       <c r="AJ9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AK9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AL9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AN9" t="s">
         <v>3</v>
       </c>
+      <c r="AO9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AQ9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AR9" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS9" t="s">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="s">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="s">
+        <v>1</v>
+      </c>
+      <c r="AV9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW9" t="s">
+        <v>7</v>
+      </c>
+      <c r="AX9" t="s">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ9" t="s">
+        <v>23</v>
+      </c>
+      <c r="BA9" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E10" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F10" t="s">
         <v>21</v>
       </c>
       <c r="G10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H10" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J10" t="s">
+        <v>32</v>
+      </c>
+      <c r="K10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M10" t="s">
+        <v>14</v>
+      </c>
+      <c r="O10" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>10</v>
+      </c>
+      <c r="R10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T10" t="s">
+        <v>10</v>
+      </c>
+      <c r="V10" t="s">
+        <v>12</v>
+      </c>
+      <c r="W10" t="s">
+        <v>27</v>
+      </c>
+      <c r="X10" t="s">
         <v>8</v>
       </c>
-      <c r="K10" t="s">
-        <v>31</v>
-      </c>
-      <c r="L10" t="s">
+      <c r="Y10" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>17</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>22</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AQ10" t="s">
         <v>44</v>
       </c>
-      <c r="M10" t="s">
-        <v>20</v>
-      </c>
-      <c r="O10" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>12</v>
-      </c>
-      <c r="R10" t="s">
+      <c r="AR10" t="s">
+        <v>10</v>
+      </c>
+      <c r="AS10" t="s">
+        <v>26</v>
+      </c>
+      <c r="AT10" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AV10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AW10" t="s">
+        <v>38</v>
+      </c>
+      <c r="AX10" t="s">
+        <v>10</v>
+      </c>
+      <c r="AY10" t="s">
         <v>8</v>
       </c>
-      <c r="T10" t="s">
-        <v>12</v>
-      </c>
-      <c r="V10" t="s">
-        <v>15</v>
-      </c>
-      <c r="W10" t="s">
-        <v>25</v>
-      </c>
-      <c r="X10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>31</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>31</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>28</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>28</v>
-      </c>
-      <c r="AE10" t="s">
+      <c r="AZ10" t="s">
+        <v>8</v>
+      </c>
+      <c r="BA10" t="s">
         <v>14</v>
       </c>
-      <c r="AF10" t="s">
-        <v>25</v>
-      </c>
-      <c r="AH10" t="s">
-        <v>31</v>
-      </c>
-      <c r="AI10" t="s">
-        <v>28</v>
-      </c>
-      <c r="AJ10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AK10" t="s">
-        <v>28</v>
-      </c>
-      <c r="AL10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AN10" t="s">
-        <v>11</v>
-      </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F11" t="s">
         <v>4</v>
@@ -4366,82 +5670,118 @@
         <v>4</v>
       </c>
       <c r="J11" t="s">
+        <v>15</v>
+      </c>
+      <c r="K11" t="s">
+        <v>27</v>
+      </c>
+      <c r="L11" t="s">
+        <v>15</v>
+      </c>
+      <c r="M11" t="s">
+        <v>31</v>
+      </c>
+      <c r="O11" t="s">
         <v>22</v>
       </c>
-      <c r="K11" t="s">
+      <c r="Q11" t="s">
+        <v>30</v>
+      </c>
+      <c r="R11" t="s">
+        <v>31</v>
+      </c>
+      <c r="T11" t="s">
+        <v>16</v>
+      </c>
+      <c r="V11" t="s">
         <v>25</v>
-      </c>
-      <c r="L11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M11" t="s">
-        <v>36</v>
-      </c>
-      <c r="O11" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>32</v>
-      </c>
-      <c r="R11" t="s">
-        <v>36</v>
-      </c>
-      <c r="T11" t="s">
-        <v>9</v>
-      </c>
-      <c r="V11" t="s">
-        <v>26</v>
       </c>
       <c r="W11" t="s">
         <v>21</v>
       </c>
       <c r="X11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Y11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Z11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AA11" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="AB11" t="s">
         <v>4</v>
       </c>
       <c r="AC11" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AD11" t="s">
         <v>38</v>
       </c>
       <c r="AE11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF11" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="AH11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AI11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AJ11" t="s">
         <v>29</v>
       </c>
       <c r="AK11" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AL11" t="s">
         <v>29</v>
       </c>
       <c r="AN11" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="AO11" t="s">
+        <v>26</v>
+      </c>
+      <c r="AQ11" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR11" t="s">
+        <v>38</v>
+      </c>
+      <c r="AS11" t="s">
+        <v>15</v>
+      </c>
+      <c r="AT11" t="s">
+        <v>21</v>
+      </c>
+      <c r="AU11" t="s">
+        <v>15</v>
+      </c>
+      <c r="AV11" t="s">
+        <v>31</v>
+      </c>
+      <c r="AW11" t="s">
+        <v>4</v>
+      </c>
+      <c r="AX11" t="s">
+        <v>15</v>
+      </c>
+      <c r="AY11" t="s">
+        <v>4</v>
+      </c>
+      <c r="AZ11" t="s">
+        <v>31</v>
+      </c>
+      <c r="BA11" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>0</v>
       </c>
@@ -4455,28 +5795,28 @@
         <v>2</v>
       </c>
       <c r="H12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R12" t="s">
         <v>23</v>
       </c>
       <c r="T12" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="V12" t="s">
         <v>0</v>
@@ -4485,7 +5825,7 @@
         <v>2</v>
       </c>
       <c r="X12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z12" t="s">
         <v>5</v>
@@ -4497,48 +5837,81 @@
         <v>5</v>
       </c>
       <c r="AD12" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>18</v>
+      </c>
+      <c r="AH12" t="s">
         <v>13</v>
       </c>
-      <c r="AE12" t="s">
-        <v>27</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>17</v>
-      </c>
-      <c r="AH12" t="s">
-        <v>16</v>
-      </c>
       <c r="AI12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ12" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AK12" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="AL12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AN12" t="s">
         <v>5</v>
       </c>
+      <c r="AO12" t="s">
+        <v>28</v>
+      </c>
+      <c r="AQ12" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR12" t="s">
+        <v>13</v>
+      </c>
+      <c r="AT12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AU12" t="s">
+        <v>13</v>
+      </c>
+      <c r="AV12" t="s">
+        <v>28</v>
+      </c>
+      <c r="AW12" t="s">
+        <v>23</v>
+      </c>
+      <c r="AX12" t="s">
+        <v>5</v>
+      </c>
+      <c r="AY12" t="s">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="s">
+        <v>13</v>
+      </c>
+      <c r="BA12" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E13" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J13" t="s">
         <v>7</v>
@@ -4550,16 +5923,16 @@
         <v>6</v>
       </c>
       <c r="O13" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q13" t="s">
         <v>35</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>34</v>
       </c>
       <c r="R13" t="s">
         <v>1</v>
       </c>
       <c r="T13" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V13" t="s">
         <v>7</v>
@@ -4583,7 +5956,7 @@
         <v>1</v>
       </c>
       <c r="AE13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AF13" t="s">
         <v>0</v>
@@ -4592,7 +5965,7 @@
         <v>0</v>
       </c>
       <c r="AI13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ13" t="s">
         <v>1</v>
@@ -4606,91 +5979,157 @@
       <c r="AN13" t="s">
         <v>23</v>
       </c>
+      <c r="AO13" t="s">
+        <v>24</v>
+      </c>
+      <c r="AQ13" t="s">
+        <v>7</v>
+      </c>
+      <c r="AR13" t="s">
+        <v>11</v>
+      </c>
+      <c r="AT13" t="s">
+        <v>11</v>
+      </c>
+      <c r="AU13" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV13" t="s">
+        <v>43</v>
+      </c>
+      <c r="AW13" t="s">
+        <v>11</v>
+      </c>
+      <c r="AX13" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY13" t="s">
+        <v>35</v>
+      </c>
+      <c r="AZ13" t="s">
+        <v>1</v>
+      </c>
+      <c r="BA13" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E14" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H14" t="s">
+        <v>32</v>
+      </c>
+      <c r="J14" t="s">
+        <v>14</v>
+      </c>
+      <c r="K14" t="s">
+        <v>30</v>
+      </c>
+      <c r="M14" t="s">
+        <v>17</v>
+      </c>
+      <c r="O14" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>14</v>
+      </c>
+      <c r="R14" t="s">
         <v>8</v>
       </c>
-      <c r="J14" t="s">
-        <v>20</v>
-      </c>
-      <c r="K14" t="s">
-        <v>32</v>
-      </c>
-      <c r="M14" t="s">
+      <c r="T14" t="s">
+        <v>17</v>
+      </c>
+      <c r="V14" t="s">
         <v>14</v>
       </c>
-      <c r="O14" t="s">
+      <c r="W14" t="s">
         <v>25</v>
       </c>
-      <c r="Q14" t="s">
-        <v>20</v>
-      </c>
-      <c r="R14" t="s">
-        <v>11</v>
-      </c>
-      <c r="T14" t="s">
-        <v>14</v>
-      </c>
-      <c r="V14" t="s">
-        <v>20</v>
-      </c>
-      <c r="W14" t="s">
-        <v>26</v>
-      </c>
       <c r="X14" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z14" t="s">
         <v>38</v>
       </c>
       <c r="AA14" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB14" t="s">
         <v>14</v>
       </c>
-      <c r="AB14" t="s">
-        <v>20</v>
-      </c>
       <c r="AD14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AE14" t="s">
         <v>21</v>
       </c>
       <c r="AF14" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="AH14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI14" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AJ14" t="s">
+        <v>32</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>19</v>
+      </c>
+      <c r="AL14" t="s">
         <v>8</v>
       </c>
-      <c r="AK14" t="s">
-        <v>18</v>
-      </c>
-      <c r="AL14" t="s">
-        <v>11</v>
-      </c>
       <c r="AN14" t="s">
+        <v>30</v>
+      </c>
+      <c r="AO14" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ14" t="s">
+        <v>12</v>
+      </c>
+      <c r="AR14" t="s">
         <v>32</v>
       </c>
+      <c r="AT14" t="s">
+        <v>14</v>
+      </c>
+      <c r="AU14" t="s">
+        <v>14</v>
+      </c>
+      <c r="AV14" t="s">
+        <v>20</v>
+      </c>
+      <c r="AW14" t="s">
+        <v>30</v>
+      </c>
+      <c r="AX14" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY14" t="s">
+        <v>14</v>
+      </c>
+      <c r="AZ14" t="s">
+        <v>15</v>
+      </c>
+      <c r="BA14" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>46</v>
       </c>
@@ -4704,25 +6143,25 @@
         <v>37</v>
       </c>
       <c r="H15" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J15" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K15" t="s">
         <v>21</v>
       </c>
       <c r="M15" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="O15" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="Q15" t="s">
         <v>38</v>
       </c>
       <c r="R15" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="T15" t="s">
         <v>39</v>
@@ -4734,25 +6173,25 @@
         <v>4</v>
       </c>
       <c r="X15" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Z15" t="s">
         <v>21</v>
       </c>
       <c r="AA15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AB15" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AD15" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AE15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF15" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="AH15" t="s">
         <v>37</v>
@@ -4761,10 +6200,10 @@
         <v>29</v>
       </c>
       <c r="AJ15" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AK15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL15" t="s">
         <v>4</v>
@@ -4772,22 +6211,55 @@
       <c r="AN15" t="s">
         <v>37</v>
       </c>
+      <c r="AO15" t="s">
+        <v>17</v>
+      </c>
+      <c r="AQ15" t="s">
+        <v>25</v>
+      </c>
+      <c r="AR15" t="s">
+        <v>29</v>
+      </c>
+      <c r="AT15" t="s">
+        <v>22</v>
+      </c>
+      <c r="AU15" t="s">
+        <v>22</v>
+      </c>
+      <c r="AV15" t="s">
+        <v>37</v>
+      </c>
+      <c r="AW15" t="s">
+        <v>21</v>
+      </c>
+      <c r="AX15" t="s">
+        <v>31</v>
+      </c>
+      <c r="AY15" t="s">
+        <v>31</v>
+      </c>
+      <c r="AZ15" t="s">
+        <v>27</v>
+      </c>
+      <c r="BA15" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E16" t="s">
         <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J16" t="s">
         <v>5</v>
@@ -4799,22 +6271,22 @@
         <v>5</v>
       </c>
       <c r="O16" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R16" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="T16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="X16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z16" t="s">
         <v>23</v>
@@ -4832,36 +6304,66 @@
         <v>23</v>
       </c>
       <c r="AF16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AH16" t="s">
         <v>6</v>
       </c>
       <c r="AI16" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AJ16" t="s">
         <v>5</v>
       </c>
       <c r="AN16" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="AO16" t="s">
+        <v>34</v>
+      </c>
+      <c r="AQ16" t="s">
+        <v>23</v>
+      </c>
+      <c r="AR16" t="s">
+        <v>1</v>
+      </c>
+      <c r="AU16" t="s">
+        <v>34</v>
+      </c>
+      <c r="AV16" t="s">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="s">
+        <v>24</v>
+      </c>
+      <c r="AX16" t="s">
+        <v>6</v>
+      </c>
+      <c r="AY16" t="s">
+        <v>2</v>
+      </c>
+      <c r="AZ16" t="s">
+        <v>18</v>
+      </c>
+      <c r="BA16" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E17" t="s">
         <v>3</v>
       </c>
       <c r="F17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H17" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J17" t="s">
         <v>23</v>
@@ -4870,7 +6372,7 @@
         <v>7</v>
       </c>
       <c r="M17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O17" t="s">
         <v>7</v>
@@ -4879,19 +6381,19 @@
         <v>0</v>
       </c>
       <c r="R17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T17" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="V17" t="s">
         <v>2</v>
       </c>
       <c r="X17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA17" t="s">
         <v>7</v>
@@ -4900,7 +6402,7 @@
         <v>3</v>
       </c>
       <c r="AD17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AE17" t="s">
         <v>24</v>
@@ -4920,31 +6422,61 @@
       <c r="AN17" t="s">
         <v>2</v>
       </c>
+      <c r="AO17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AQ17" t="s">
+        <v>35</v>
+      </c>
+      <c r="AR17" t="s">
+        <v>7</v>
+      </c>
+      <c r="AU17" t="s">
+        <v>24</v>
+      </c>
+      <c r="AV17" t="s">
+        <v>42</v>
+      </c>
+      <c r="AW17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AX17" t="s">
+        <v>24</v>
+      </c>
+      <c r="AY17" t="s">
+        <v>1</v>
+      </c>
+      <c r="AZ17" t="s">
+        <v>3</v>
+      </c>
+      <c r="BA17" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" t="s">
         <v>14</v>
       </c>
-      <c r="E18" t="s">
-        <v>20</v>
-      </c>
       <c r="F18" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H18" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O18" t="s">
         <v>37</v>
@@ -4953,49 +6485,79 @@
         <v>21</v>
       </c>
       <c r="R18" t="s">
+        <v>17</v>
+      </c>
+      <c r="T18" t="s">
+        <v>26</v>
+      </c>
+      <c r="V18" t="s">
+        <v>27</v>
+      </c>
+      <c r="X18" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE18" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF18" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI18" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ18" t="s">
+        <v>22</v>
+      </c>
+      <c r="AN18" t="s">
+        <v>32</v>
+      </c>
+      <c r="AO18" t="s">
+        <v>44</v>
+      </c>
+      <c r="AQ18" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR18" t="s">
         <v>14</v>
       </c>
-      <c r="T18" t="s">
-        <v>31</v>
-      </c>
-      <c r="V18" t="s">
-        <v>25</v>
-      </c>
-      <c r="X18" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z18" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA18" t="s">
+      <c r="AU18" t="s">
+        <v>44</v>
+      </c>
+      <c r="AV18" t="s">
+        <v>10</v>
+      </c>
+      <c r="AW18" t="s">
+        <v>14</v>
+      </c>
+      <c r="AX18" t="s">
+        <v>44</v>
+      </c>
+      <c r="AY18" t="s">
+        <v>39</v>
+      </c>
+      <c r="AZ18" t="s">
         <v>26</v>
       </c>
-      <c r="AB18" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD18" t="s">
-        <v>11</v>
-      </c>
-      <c r="AE18" t="s">
-        <v>11</v>
-      </c>
-      <c r="AF18" t="s">
-        <v>12</v>
-      </c>
-      <c r="AH18" t="s">
-        <v>11</v>
-      </c>
-      <c r="AI18" t="s">
-        <v>11</v>
-      </c>
-      <c r="AJ18" t="s">
-        <v>28</v>
-      </c>
-      <c r="AN18" t="s">
-        <v>8</v>
+      <c r="BA18" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>37</v>
       </c>
@@ -5006,19 +6568,19 @@
         <v>21</v>
       </c>
       <c r="F19" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K19" t="s">
         <v>4</v>
       </c>
       <c r="M19" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="O19" t="s">
         <v>29</v>
@@ -5027,13 +6589,13 @@
         <v>4</v>
       </c>
       <c r="R19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T19" t="s">
         <v>29</v>
       </c>
       <c r="V19" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="X19" t="s">
         <v>29</v>
@@ -5051,45 +6613,75 @@
         <v>21</v>
       </c>
       <c r="AE19" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AF19" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AH19" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AI19" t="s">
         <v>4</v>
       </c>
       <c r="AJ19" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AN19" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO19" t="s">
+        <v>22</v>
+      </c>
+      <c r="AQ19" t="s">
         <v>31</v>
       </c>
+      <c r="AR19" t="s">
+        <v>16</v>
+      </c>
+      <c r="AU19" t="s">
+        <v>17</v>
+      </c>
+      <c r="AV19" t="s">
+        <v>30</v>
+      </c>
+      <c r="AW19" t="s">
+        <v>10</v>
+      </c>
+      <c r="AX19" t="s">
+        <v>20</v>
+      </c>
+      <c r="AY19" t="s">
+        <v>29</v>
+      </c>
+      <c r="AZ19" t="s">
+        <v>39</v>
+      </c>
+      <c r="BA19" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C20" t="s">
         <v>3</v>
       </c>
       <c r="E20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F20" t="s">
         <v>6</v>
       </c>
       <c r="H20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K20" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="O20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q20" t="s">
         <v>5</v>
@@ -5101,30 +6693,60 @@
         <v>6</v>
       </c>
       <c r="X20" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB20" t="s">
         <v>40</v>
       </c>
-      <c r="AA20" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB20" t="s">
-        <v>42</v>
-      </c>
       <c r="AF20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AH20" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="AI20" t="s">
         <v>24</v>
       </c>
       <c r="AJ20" t="s">
+        <v>34</v>
+      </c>
+      <c r="AO20" t="s">
+        <v>2</v>
+      </c>
+      <c r="AQ20" t="s">
+        <v>5</v>
+      </c>
+      <c r="AR20" t="s">
+        <v>5</v>
+      </c>
+      <c r="AU20" t="s">
+        <v>2</v>
+      </c>
+      <c r="AV20" t="s">
         <v>33</v>
       </c>
+      <c r="AW20" t="s">
+        <v>13</v>
+      </c>
+      <c r="AX20" t="s">
+        <v>11</v>
+      </c>
+      <c r="AY20" t="s">
+        <v>28</v>
+      </c>
+      <c r="AZ20" t="s">
+        <v>28</v>
+      </c>
+      <c r="BA20" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C21" t="s">
         <v>7</v>
@@ -5166,7 +6788,7 @@
         <v>24</v>
       </c>
       <c r="AH21" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AI21" t="s">
         <v>3</v>
@@ -5174,69 +6796,129 @@
       <c r="AJ21" t="s">
         <v>24</v>
       </c>
+      <c r="AO21" t="s">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR21" t="s">
+        <v>23</v>
+      </c>
+      <c r="AU21" t="s">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="s">
+        <v>6</v>
+      </c>
+      <c r="AW21" t="s">
+        <v>18</v>
+      </c>
+      <c r="AX21" t="s">
+        <v>3</v>
+      </c>
+      <c r="AY21" t="s">
+        <v>24</v>
+      </c>
+      <c r="AZ21" t="s">
+        <v>34</v>
+      </c>
+      <c r="BA21" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F22" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H22" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="K22" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="O22" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R22" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X22" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AA22" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AB22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF22" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>30</v>
+      </c>
+      <c r="AI22" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ22" t="s">
+        <v>12</v>
+      </c>
+      <c r="AO22" t="s">
+        <v>30</v>
+      </c>
+      <c r="AQ22" t="s">
         <v>8</v>
       </c>
-      <c r="AH22" t="s">
-        <v>32</v>
-      </c>
-      <c r="AI22" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ22" t="s">
-        <v>15</v>
+      <c r="AR22" t="s">
+        <v>8</v>
+      </c>
+      <c r="AU22" t="s">
+        <v>21</v>
+      </c>
+      <c r="AV22" t="s">
+        <v>12</v>
+      </c>
+      <c r="AW22" t="s">
+        <v>22</v>
+      </c>
+      <c r="AX22" t="s">
+        <v>21</v>
+      </c>
+      <c r="AY22" t="s">
+        <v>17</v>
+      </c>
+      <c r="AZ22" t="s">
+        <v>17</v>
+      </c>
+      <c r="BA22" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E23" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F23" t="s">
         <v>29</v>
@@ -5248,16 +6930,16 @@
         <v>29</v>
       </c>
       <c r="O23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q23" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="R23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T23" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="X23" t="s">
         <v>37</v>
@@ -5266,30 +6948,60 @@
         <v>21</v>
       </c>
       <c r="AB23" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AF23" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AH23" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AI23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ23" t="s">
-        <v>26</v>
+        <v>25</v>
+      </c>
+      <c r="AO23" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ23" t="s">
+        <v>16</v>
+      </c>
+      <c r="AR23" t="s">
+        <v>4</v>
+      </c>
+      <c r="AU23" t="s">
+        <v>25</v>
+      </c>
+      <c r="AV23" t="s">
+        <v>39</v>
+      </c>
+      <c r="AW23" t="s">
+        <v>15</v>
+      </c>
+      <c r="AX23" t="s">
+        <v>29</v>
+      </c>
+      <c r="AY23" t="s">
+        <v>37</v>
+      </c>
+      <c r="AZ23" t="s">
+        <v>20</v>
+      </c>
+      <c r="BA23" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>2</v>
       </c>
       <c r="E24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F24" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H24" t="s">
         <v>24</v>
@@ -5315,8 +7027,29 @@
       <c r="AJ24" t="s">
         <v>6</v>
       </c>
+      <c r="AO24" t="s">
+        <v>33</v>
+      </c>
+      <c r="AV24" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW24" t="s">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="s">
+        <v>2</v>
+      </c>
+      <c r="AY24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AZ24" t="s">
+        <v>2</v>
+      </c>
+      <c r="BA24" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -5345,83 +7078,146 @@
         <v>3</v>
       </c>
       <c r="AI25" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="AJ25" t="s">
         <v>3</v>
       </c>
+      <c r="AO25" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV25" t="s">
+        <v>2</v>
+      </c>
+      <c r="AW25" t="s">
+        <v>35</v>
+      </c>
+      <c r="AX25" t="s">
+        <v>7</v>
+      </c>
+      <c r="AY25" t="s">
+        <v>6</v>
+      </c>
+      <c r="AZ25" t="s">
+        <v>11</v>
+      </c>
+      <c r="BA25" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>21</v>
       </c>
       <c r="E26" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F26" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H26" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="O26" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="X26" t="s">
         <v>21</v>
       </c>
       <c r="AB26" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AF26" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI26" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AJ26" t="s">
         <v>39</v>
       </c>
+      <c r="AO26" t="s">
+        <v>8</v>
+      </c>
+      <c r="AV26" t="s">
+        <v>19</v>
+      </c>
+      <c r="AW26" t="s">
+        <v>8</v>
+      </c>
+      <c r="AX26" t="s">
+        <v>19</v>
+      </c>
+      <c r="AY26" t="s">
+        <v>19</v>
+      </c>
+      <c r="AZ26" t="s">
+        <v>19</v>
+      </c>
+      <c r="BA26" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>4</v>
       </c>
       <c r="E27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O27" t="s">
         <v>4</v>
       </c>
       <c r="T27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AB27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ27" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="AO27" t="s">
+        <v>12</v>
+      </c>
+      <c r="AV27" t="s">
+        <v>25</v>
+      </c>
+      <c r="AW27" t="s">
+        <v>27</v>
+      </c>
+      <c r="AX27" t="s">
+        <v>12</v>
+      </c>
+      <c r="AY27" t="s">
+        <v>25</v>
+      </c>
+      <c r="AZ27" t="s">
+        <v>12</v>
+      </c>
+      <c r="BA27" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="28:36" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="15" customHeight="1" spans="32:53" x14ac:dyDescent="0.25"/>
     <row r="29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5443,7 +7239,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:AN1898"/>
+  <dimension ref="A3:BA1898"/>
   <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="55.28515625" customWidth="1"/>
@@ -5527,15 +7323,15 @@
     <col min="99" max="99" width="47.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" t="s">
         <v>51</v>
-      </c>
-      <c r="C3" t="s">
-        <v>49</v>
       </c>
       <c r="D3" t="s">
         <v>50</v>
@@ -5544,577 +7340,805 @@
         <v>52</v>
       </c>
       <c r="F3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H3" t="s">
         <v>54</v>
       </c>
-      <c r="G3" t="s">
+      <c r="I3" t="s">
+        <v>65</v>
+      </c>
+      <c r="J3" t="s">
+        <v>62</v>
+      </c>
+      <c r="K3" t="s">
+        <v>66</v>
+      </c>
+      <c r="L3" t="s">
         <v>57</v>
       </c>
-      <c r="H3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I3" t="s">
-        <v>62</v>
-      </c>
-      <c r="J3" t="s">
-        <v>59</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="M3" t="s">
+        <v>56</v>
+      </c>
+      <c r="N3" t="s">
+        <v>67</v>
+      </c>
+      <c r="O3" t="s">
+        <v>72</v>
+      </c>
+      <c r="P3" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>61</v>
+      </c>
+      <c r="R3" t="s">
+        <v>69</v>
+      </c>
+      <c r="S3" t="s">
+        <v>87</v>
+      </c>
+      <c r="T3" t="s">
+        <v>60</v>
+      </c>
+      <c r="U3" t="s">
+        <v>80</v>
+      </c>
+      <c r="V3" t="s">
+        <v>68</v>
+      </c>
+      <c r="W3" t="s">
+        <v>88</v>
+      </c>
+      <c r="X3" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>81</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>89</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>75</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>71</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>90</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AO3" t="s">
         <v>63</v>
       </c>
-      <c r="L3" t="s">
-        <v>56</v>
-      </c>
-      <c r="M3" t="s">
-        <v>55</v>
-      </c>
-      <c r="N3" t="s">
-        <v>64</v>
-      </c>
-      <c r="O3" t="s">
-        <v>68</v>
-      </c>
-      <c r="P3" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>60</v>
-      </c>
-      <c r="R3" t="s">
-        <v>66</v>
-      </c>
-      <c r="S3" t="s">
-        <v>80</v>
-      </c>
-      <c r="T3" t="s">
+      <c r="AP3" t="s">
+        <v>101</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>93</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>102</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>100</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>83</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>95</v>
+      </c>
+      <c r="AX3" t="s">
         <v>58</v>
       </c>
-      <c r="U3" t="s">
-        <v>75</v>
-      </c>
-      <c r="V3" t="s">
-        <v>65</v>
-      </c>
-      <c r="W3" t="s">
-        <v>81</v>
-      </c>
-      <c r="X3" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>71</v>
-      </c>
-      <c r="AC3" t="s">
+      <c r="AY3" t="s">
         <v>86</v>
       </c>
-      <c r="AD3" t="s">
-        <v>76</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>70</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>82</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>85</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>72</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>67</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>77</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>87</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>84</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>88</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>73</v>
+      <c r="AZ3" t="s">
+        <v>94</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>91</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="E4" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="F4" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="G4" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="H4" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="I4" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="J4" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="K4" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="L4" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="M4" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="N4" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="O4" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="P4" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="Q4" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="R4" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="S4" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="T4" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="U4" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="V4" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="W4" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="X4" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="Y4" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="Z4" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="AA4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="AB4" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="AC4" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="AD4" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="AE4" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="AF4" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="AG4" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="AH4" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="AI4" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="AJ4" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="AK4" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="AL4" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="AM4" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="AN4" t="s">
-        <v>129</v>
+        <v>143</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>144</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>145</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>146</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>147</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>148</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>149</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>150</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>151</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>152</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>153</v>
+      </c>
+      <c r="AY4" t="s">
+        <v>154</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>155</v>
+      </c>
+      <c r="BA4" t="s">
+        <v>156</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="C5" t="s">
-        <v>131</v>
+        <v>158</v>
       </c>
       <c r="E5" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="F5" t="s">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="G5" t="s">
-        <v>134</v>
+        <v>161</v>
       </c>
       <c r="H5" t="s">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="J5" t="s">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="K5" t="s">
-        <v>137</v>
+        <v>164</v>
       </c>
       <c r="L5" t="s">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="M5" t="s">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="O5" t="s">
-        <v>140</v>
+        <v>167</v>
       </c>
       <c r="Q5" t="s">
-        <v>141</v>
+        <v>168</v>
       </c>
       <c r="R5" t="s">
-        <v>142</v>
+        <v>169</v>
       </c>
       <c r="T5" t="s">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="V5" t="s">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="W5" t="s">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="X5" t="s">
-        <v>146</v>
+        <v>173</v>
       </c>
       <c r="Y5" t="s">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="Z5" t="s">
-        <v>148</v>
+        <v>175</v>
       </c>
       <c r="AA5" t="s">
-        <v>149</v>
+        <v>176</v>
       </c>
       <c r="AB5" t="s">
-        <v>150</v>
+        <v>177</v>
       </c>
       <c r="AC5" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="AD5" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="AE5" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="AF5" t="s">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="AH5" t="s">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="AI5" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="AJ5" t="s">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="AK5" t="s">
-        <v>158</v>
+        <v>185</v>
       </c>
       <c r="AL5" t="s">
-        <v>159</v>
+        <v>186</v>
       </c>
       <c r="AN5" t="s">
-        <v>160</v>
+        <v>187</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>188</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>189</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>190</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>191</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>192</v>
+      </c>
+      <c r="AU5" t="s">
+        <v>193</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>194</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>195</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>196</v>
+      </c>
+      <c r="AY5" t="s">
+        <v>197</v>
+      </c>
+      <c r="AZ5" t="s">
+        <v>198</v>
+      </c>
+      <c r="BA5" t="s">
+        <v>199</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>161</v>
+        <v>200</v>
       </c>
       <c r="C6" t="s">
-        <v>162</v>
+        <v>201</v>
       </c>
       <c r="E6" t="s">
-        <v>163</v>
+        <v>202</v>
       </c>
       <c r="F6" t="s">
-        <v>164</v>
+        <v>203</v>
       </c>
       <c r="H6" t="s">
-        <v>165</v>
+        <v>204</v>
       </c>
       <c r="J6" t="s">
-        <v>166</v>
+        <v>205</v>
       </c>
       <c r="K6" t="s">
-        <v>167</v>
+        <v>206</v>
       </c>
       <c r="M6" t="s">
-        <v>168</v>
+        <v>207</v>
       </c>
       <c r="O6" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="Q6" t="s">
-        <v>170</v>
+        <v>209</v>
       </c>
       <c r="R6" t="s">
-        <v>171</v>
+        <v>210</v>
       </c>
       <c r="T6" t="s">
-        <v>172</v>
+        <v>211</v>
       </c>
       <c r="V6" t="s">
-        <v>173</v>
+        <v>212</v>
       </c>
       <c r="W6" t="s">
-        <v>174</v>
+        <v>213</v>
       </c>
       <c r="X6" t="s">
-        <v>175</v>
+        <v>214</v>
       </c>
       <c r="Z6" t="s">
-        <v>176</v>
+        <v>215</v>
       </c>
       <c r="AA6" t="s">
-        <v>177</v>
+        <v>216</v>
       </c>
       <c r="AB6" t="s">
-        <v>178</v>
+        <v>217</v>
       </c>
       <c r="AD6" t="s">
-        <v>179</v>
+        <v>218</v>
       </c>
       <c r="AE6" t="s">
-        <v>180</v>
+        <v>219</v>
       </c>
       <c r="AF6" t="s">
-        <v>181</v>
+        <v>220</v>
       </c>
       <c r="AH6" t="s">
-        <v>182</v>
+        <v>221</v>
       </c>
       <c r="AI6" t="s">
-        <v>183</v>
+        <v>222</v>
       </c>
       <c r="AJ6" t="s">
-        <v>184</v>
+        <v>223</v>
       </c>
       <c r="AK6" t="s">
-        <v>185</v>
+        <v>224</v>
       </c>
       <c r="AL6" t="s">
-        <v>186</v>
+        <v>225</v>
       </c>
       <c r="AN6" t="s">
-        <v>187</v>
+        <v>226</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>227</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>228</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>229</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>230</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>231</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>232</v>
+      </c>
+      <c r="AW6" t="s">
+        <v>233</v>
+      </c>
+      <c r="AX6" t="s">
+        <v>234</v>
+      </c>
+      <c r="AY6" t="s">
+        <v>235</v>
+      </c>
+      <c r="AZ6" t="s">
+        <v>236</v>
+      </c>
+      <c r="BA6" t="s">
+        <v>237</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>188</v>
+        <v>238</v>
       </c>
       <c r="C7" t="s">
-        <v>189</v>
+        <v>239</v>
       </c>
       <c r="E7" t="s">
-        <v>190</v>
+        <v>240</v>
       </c>
       <c r="F7" t="s">
-        <v>191</v>
+        <v>241</v>
       </c>
       <c r="H7" t="s">
-        <v>192</v>
+        <v>242</v>
       </c>
       <c r="J7" t="s">
-        <v>193</v>
+        <v>243</v>
       </c>
       <c r="K7" t="s">
-        <v>194</v>
+        <v>244</v>
       </c>
       <c r="M7" t="s">
-        <v>195</v>
+        <v>245</v>
       </c>
       <c r="O7" t="s">
-        <v>196</v>
+        <v>246</v>
       </c>
       <c r="Q7" t="s">
-        <v>197</v>
+        <v>247</v>
       </c>
       <c r="R7" t="s">
-        <v>198</v>
+        <v>248</v>
       </c>
       <c r="T7" t="s">
-        <v>199</v>
+        <v>249</v>
       </c>
       <c r="V7" t="s">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="X7" t="s">
-        <v>201</v>
+        <v>251</v>
       </c>
       <c r="Z7" t="s">
-        <v>202</v>
+        <v>252</v>
       </c>
       <c r="AA7" t="s">
-        <v>203</v>
+        <v>253</v>
       </c>
       <c r="AB7" t="s">
-        <v>204</v>
+        <v>254</v>
       </c>
       <c r="AD7" t="s">
-        <v>205</v>
+        <v>255</v>
       </c>
       <c r="AE7" t="s">
-        <v>206</v>
+        <v>256</v>
       </c>
       <c r="AF7" t="s">
-        <v>207</v>
+        <v>257</v>
       </c>
       <c r="AH7" t="s">
-        <v>208</v>
+        <v>258</v>
       </c>
       <c r="AI7" t="s">
-        <v>209</v>
+        <v>259</v>
       </c>
       <c r="AJ7" t="s">
-        <v>210</v>
+        <v>260</v>
       </c>
       <c r="AN7" t="s">
-        <v>211</v>
+        <v>261</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>262</v>
+      </c>
+      <c r="AQ7" t="s">
+        <v>263</v>
+      </c>
+      <c r="AR7" t="s">
+        <v>264</v>
+      </c>
+      <c r="AU7" t="s">
+        <v>265</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>266</v>
+      </c>
+      <c r="AW7" t="s">
+        <v>267</v>
+      </c>
+      <c r="AX7" t="s">
+        <v>268</v>
+      </c>
+      <c r="AY7" t="s">
+        <v>269</v>
+      </c>
+      <c r="AZ7" t="s">
+        <v>270</v>
+      </c>
+      <c r="BA7" t="s">
+        <v>271</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>212</v>
+        <v>272</v>
       </c>
       <c r="C8" t="s">
-        <v>213</v>
+        <v>273</v>
       </c>
       <c r="E8" t="s">
-        <v>214</v>
+        <v>274</v>
       </c>
       <c r="F8" t="s">
-        <v>215</v>
+        <v>275</v>
       </c>
       <c r="H8" t="s">
-        <v>216</v>
+        <v>276</v>
       </c>
       <c r="K8" t="s">
-        <v>217</v>
+        <v>277</v>
       </c>
       <c r="O8" t="s">
-        <v>218</v>
+        <v>278</v>
       </c>
       <c r="Q8" t="s">
-        <v>219</v>
+        <v>279</v>
       </c>
       <c r="R8" t="s">
-        <v>220</v>
+        <v>280</v>
       </c>
       <c r="T8" t="s">
-        <v>221</v>
+        <v>281</v>
       </c>
       <c r="X8" t="s">
-        <v>222</v>
+        <v>282</v>
       </c>
       <c r="AA8" t="s">
-        <v>223</v>
+        <v>283</v>
       </c>
       <c r="AB8" t="s">
-        <v>224</v>
+        <v>284</v>
       </c>
       <c r="AE8" t="s">
-        <v>225</v>
+        <v>285</v>
       </c>
       <c r="AF8" t="s">
-        <v>226</v>
+        <v>286</v>
       </c>
       <c r="AH8" t="s">
-        <v>227</v>
+        <v>287</v>
       </c>
       <c r="AI8" t="s">
-        <v>228</v>
+        <v>288</v>
       </c>
       <c r="AJ8" t="s">
-        <v>229</v>
+        <v>289</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>290</v>
+      </c>
+      <c r="AQ8" t="s">
+        <v>291</v>
+      </c>
+      <c r="AR8" t="s">
+        <v>292</v>
+      </c>
+      <c r="AU8" t="s">
+        <v>293</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>294</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>295</v>
+      </c>
+      <c r="AX8" t="s">
+        <v>296</v>
+      </c>
+      <c r="AY8" t="s">
+        <v>297</v>
+      </c>
+      <c r="AZ8" t="s">
+        <v>298</v>
+      </c>
+      <c r="BA8" t="s">
+        <v>299</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>230</v>
+        <v>300</v>
       </c>
       <c r="E9" t="s">
-        <v>231</v>
+        <v>301</v>
       </c>
       <c r="F9" t="s">
-        <v>232</v>
+        <v>302</v>
       </c>
       <c r="H9" t="s">
-        <v>233</v>
+        <v>303</v>
       </c>
       <c r="O9" t="s">
-        <v>234</v>
+        <v>304</v>
       </c>
       <c r="T9" t="s">
-        <v>235</v>
+        <v>305</v>
       </c>
       <c r="X9" t="s">
-        <v>236</v>
+        <v>306</v>
       </c>
       <c r="AB9" t="s">
-        <v>237</v>
+        <v>307</v>
       </c>
       <c r="AF9" t="s">
-        <v>238</v>
+        <v>308</v>
       </c>
       <c r="AI9" t="s">
-        <v>239</v>
+        <v>309</v>
       </c>
       <c r="AJ9" t="s">
-        <v>240</v>
+        <v>310</v>
+      </c>
+      <c r="AO9" t="s">
+        <v>311</v>
+      </c>
+      <c r="AV9" t="s">
+        <v>312</v>
+      </c>
+      <c r="AW9" t="s">
+        <v>313</v>
+      </c>
+      <c r="AX9" t="s">
+        <v>314</v>
+      </c>
+      <c r="AY9" t="s">
+        <v>315</v>
+      </c>
+      <c r="AZ9" t="s">
+        <v>316</v>
+      </c>
+      <c r="BA9" t="s">
+        <v>317</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="28:36" x14ac:dyDescent="0.25"/>
+    <row r="10" ht="15" customHeight="1" spans="32:53" x14ac:dyDescent="0.25"/>
     <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="13" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/data/ICEHLdelegacije.xlsx
+++ b/data/ICEHLdelegacije.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2075" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2076" uniqueCount="318">
   <si>
     <t>PiragicTr</t>
   </si>
@@ -675,7 +675,7 @@
     <t>Tiroler Wasserkraft Arena;SeewaldEl;SmetanaLa;MartinFl;RieckenSi</t>
   </si>
   <si>
-    <t>Sparkasse Arena Bozen;BernekerTh;NikolicKr;PuffWo;RigoniDa</t>
+    <t>Sparkasse Arena Bozen;BernekerTh;SchauerJa;PuffWo;RigoniDa</t>
   </si>
   <si>
     <t>Gabor Ocskay Eisarena;HronskyTo;PiragicTr;DurmisOt;HribarMa</t>
@@ -786,7 +786,7 @@
     <t>Hala Tivoli;GroznikBo;NagyAt;HribarMa;PuffWo</t>
   </si>
   <si>
-    <t>Eishalle Asiago;RezekGr;SchauerJa;HribarMa;PardatscherUl</t>
+    <t>Eishalle Asiago;GroznikBo;RezekGr;HribarMa;PardatscherUl</t>
   </si>
   <si>
     <t>Tiroler Wasserkraft Arena;NikolicKr;OfnerCh;BedynekSe;MartinFl</t>
@@ -831,7 +831,7 @@
     <t>Eisarena Salzburg;HronskyTo;SternatCh;JedlickaPe;SeewaldJe</t>
   </si>
   <si>
-    <t>Tiroler Wasserkraft Arena;NikolicKr;NikolicMa;MartinFl;SparerDa</t>
+    <t>Tiroler Wasserkraft Arena;NikolicMa;NikolicKr;MartinFl;SparerDa</t>
   </si>
   <si>
     <t>Eishalle Bruneck;BernekerTh;HuberAn;MartinFl;PardatscherUl</t>
@@ -3109,7 +3109,7 @@
         <v>96</v>
       </c>
       <c r="AI14" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="AJ14" t="s">
         <v>96</v>
@@ -4195,8 +4195,11 @@
       <c r="D28" t="s">
         <v>77</v>
       </c>
+      <c r="F28" t="s">
+        <v>76</v>
+      </c>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>101</v>
       </c>
@@ -5956,7 +5959,7 @@
         <v>1</v>
       </c>
       <c r="AE13" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="AF13" t="s">
         <v>0</v>
@@ -6301,7 +6304,7 @@
         <v>5</v>
       </c>
       <c r="AE16" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="AF16" t="s">
         <v>34</v>
@@ -6346,7 +6349,7 @@
         <v>18</v>
       </c>
       <c r="BA16" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
@@ -6405,7 +6408,7 @@
         <v>36</v>
       </c>
       <c r="AE17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF17" t="s">
         <v>2</v>
@@ -6450,7 +6453,7 @@
         <v>3</v>
       </c>
       <c r="BA17" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">

--- a/data/ICEHLdelegacije.xlsx
+++ b/data/ICEHLdelegacije.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2076" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2085" uniqueCount="318">
   <si>
     <t>PiragicTr</t>
   </si>
@@ -276,6 +276,9 @@
     <t>2024-11-02</t>
   </si>
   <si>
+    <t>zbrisano</t>
+  </si>
+  <si>
     <t>2024-12-28</t>
   </si>
   <si>
@@ -309,9 +312,6 @@
     <t>2024-11-30</t>
   </si>
   <si>
-    <t>zbrisano</t>
-  </si>
-  <si>
     <t>2024-11-23</t>
   </si>
   <si>
@@ -582,7 +582,7 @@
     <t>Stadthalle Villach;PiragicTr;SternatCh;HribarMa;JeramFi</t>
   </si>
   <si>
-    <t>Eishalle;KainbergerJu;SternatCh;DurmisOt;JedlickaPe</t>
+    <t>ZBRISANO</t>
   </si>
   <si>
     <t>Eishalle Feldkirch;NikolicMa;SeewaldEl;FleischmannLu;NotheggerDa</t>
@@ -831,7 +831,7 @@
     <t>Eisarena Salzburg;HronskyTo;SternatCh;JedlickaPe;SeewaldJe</t>
   </si>
   <si>
-    <t>Tiroler Wasserkraft Arena;NikolicMa;NikolicKr;MartinFl;SparerDa</t>
+    <t>Tiroler Wasserkraft Arena;NikolicKr;NikolicMa;MartinFl;SparerDa</t>
   </si>
   <si>
     <t>Eishalle Bruneck;BernekerTh;HuberAn;MartinFl;PardatscherUl</t>
@@ -873,9 +873,6 @@
     <t>Tiroler Wasserkraft Arena;KainbergerJu;NikolicMa;MantovaniDa;MartinFl</t>
   </si>
   <si>
-    <t>ZBRISANO</t>
-  </si>
-  <si>
     <t>Eishalle Feldkirch;BernekerTh;SchauerJa;JedlickaPe;KoncDa</t>
   </si>
   <si>
@@ -963,13 +960,16 @@
     <t>Sparkasse Arena Bozen;OfnerCh;ZrnicMi;MantovaniDa;PardatscherUl</t>
   </si>
   <si>
-    <t>Eishalle Asiago;NikolicKr;NikolicMa;MantovaniDa;RigoniDa</t>
+    <t>Eishalle Asiago;NikolicMa;NikolicKr;MantovaniDa;RigoniDa</t>
   </si>
   <si>
     <t>Sparkasse Arena Bozen;OfnerCh;SeewaldEl;MantovaniDa;PardatscherUl</t>
   </si>
   <si>
     <t>Eishalle Bruneck;RezekGr;SternatCh;RigoniDa;ZgoncGa</t>
+  </si>
+  <si>
+    <t>Stadthalle Villach;KainbergerJu;SternatCh;DurmisOt;JedlickaPe</t>
   </si>
 </sst>
 </file>
@@ -2511,10 +2511,10 @@
         <v>83</v>
       </c>
       <c r="AO9" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="AP9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
@@ -2534,7 +2534,7 @@
         <v>52</v>
       </c>
       <c r="F10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G10" t="s">
         <v>72</v>
@@ -2564,7 +2564,7 @@
         <v>60</v>
       </c>
       <c r="P10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q10" t="s">
         <v>60</v>
@@ -2573,7 +2573,7 @@
         <v>69</v>
       </c>
       <c r="S10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T10" t="s">
         <v>60</v>
@@ -2582,10 +2582,10 @@
         <v>69</v>
       </c>
       <c r="V10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="W10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="X10" t="s">
         <v>69</v>
@@ -2624,7 +2624,7 @@
         <v>61</v>
       </c>
       <c r="AJ10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AK10" t="s">
         <v>68</v>
@@ -2636,7 +2636,7 @@
         <v>84</v>
       </c>
       <c r="AN10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AO10" t="s">
         <v>70</v>
@@ -2668,7 +2668,7 @@
         <v>61</v>
       </c>
       <c r="I11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J11" t="s">
         <v>60</v>
@@ -2719,19 +2719,19 @@
         <v>60</v>
       </c>
       <c r="Z11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AA11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB11" t="s">
         <v>89</v>
-      </c>
-      <c r="AB11" t="s">
-        <v>88</v>
       </c>
       <c r="AC11" t="s">
         <v>64</v>
       </c>
       <c r="AD11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AE11" t="s">
         <v>54</v>
@@ -2740,13 +2740,13 @@
         <v>73</v>
       </c>
       <c r="AG11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AH11" t="s">
         <v>76</v>
       </c>
       <c r="AI11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AJ11" t="s">
         <v>74</v>
@@ -2755,16 +2755,19 @@
         <v>81</v>
       </c>
       <c r="AL11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AM11" t="s">
         <v>74</v>
       </c>
       <c r="AN11" t="s">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="AO11" t="s">
+        <v>86</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>61</v>
       </c>
@@ -2781,7 +2784,7 @@
         <v>61</v>
       </c>
       <c r="F12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G12" t="s">
         <v>60</v>
@@ -2859,7 +2862,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AG12" t="s">
         <v>75</v>
@@ -2874,19 +2877,22 @@
         <v>75</v>
       </c>
       <c r="AK12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AL12" t="s">
         <v>78</v>
       </c>
       <c r="AM12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN12" t="s">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="AO12" t="s">
+        <v>63</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>69</v>
       </c>
@@ -2897,7 +2903,7 @@
         <v>68</v>
       </c>
       <c r="D13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E13" t="s">
         <v>68</v>
@@ -2969,7 +2975,7 @@
         <v>71</v>
       </c>
       <c r="AB13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AC13" t="s">
         <v>76</v>
@@ -2981,7 +2987,7 @@
         <v>75</v>
       </c>
       <c r="AF13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AG13" t="s">
         <v>82</v>
@@ -3002,7 +3008,7 @@
         <v>83</v>
       </c>
       <c r="AM13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
@@ -3013,13 +3019,13 @@
         <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D14" t="s">
         <v>64</v>
       </c>
       <c r="E14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F14" t="s">
         <v>84</v>
@@ -3031,7 +3037,7 @@
         <v>64</v>
       </c>
       <c r="I14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J14" t="s">
         <v>74</v>
@@ -3043,7 +3049,7 @@
         <v>73</v>
       </c>
       <c r="M14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N14" t="s">
         <v>81</v>
@@ -3052,7 +3058,7 @@
         <v>76</v>
       </c>
       <c r="P14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q14" t="s">
         <v>74</v>
@@ -3061,10 +3067,10 @@
         <v>74</v>
       </c>
       <c r="S14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="T14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="U14" t="s">
         <v>76</v>
@@ -3091,13 +3097,13 @@
         <v>75</v>
       </c>
       <c r="AC14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AD14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AE14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AF14" t="s">
         <v>82</v>
@@ -3106,22 +3112,22 @@
         <v>78</v>
       </c>
       <c r="AH14" t="s">
+        <v>97</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>86</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>97</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>97</v>
+      </c>
+      <c r="AL14" t="s">
         <v>96</v>
       </c>
-      <c r="AI14" t="s">
-        <v>97</v>
-      </c>
-      <c r="AJ14" t="s">
-        <v>96</v>
-      </c>
-      <c r="AK14" t="s">
-        <v>96</v>
-      </c>
-      <c r="AL14" t="s">
-        <v>95</v>
-      </c>
       <c r="AM14" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
@@ -3129,7 +3135,7 @@
         <v>68</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C15" t="s">
         <v>64</v>
@@ -3165,16 +3171,16 @@
         <v>76</v>
       </c>
       <c r="N15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P15" t="s">
         <v>98</v>
       </c>
       <c r="Q15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R15" t="s">
         <v>81</v>
@@ -3186,7 +3192,7 @@
         <v>75</v>
       </c>
       <c r="U15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="V15" t="s">
         <v>81</v>
@@ -3198,7 +3204,7 @@
         <v>71</v>
       </c>
       <c r="Y15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Z15" t="s">
         <v>71</v>
@@ -3222,7 +3228,7 @@
         <v>74</v>
       </c>
       <c r="AG15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AH15" t="s">
         <v>63</v>
@@ -3237,12 +3243,12 @@
         <v>70</v>
       </c>
       <c r="AL15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B16" t="s">
         <v>64</v>
@@ -3272,7 +3278,7 @@
         <v>71</v>
       </c>
       <c r="K16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L16" t="s">
         <v>76</v>
@@ -3299,7 +3305,7 @@
         <v>71</v>
       </c>
       <c r="T16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="U16" t="s">
         <v>71</v>
@@ -3308,7 +3314,7 @@
         <v>76</v>
       </c>
       <c r="W16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="X16" t="s">
         <v>82</v>
@@ -3326,7 +3332,7 @@
         <v>70</v>
       </c>
       <c r="AC16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AD16" t="s">
         <v>60</v>
@@ -3338,16 +3344,16 @@
         <v>70</v>
       </c>
       <c r="AG16" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="AH16" t="s">
         <v>70</v>
       </c>
       <c r="AI16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AJ16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK16" t="s">
         <v>83</v>
@@ -3370,19 +3376,19 @@
         <v>74</v>
       </c>
       <c r="F17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H17" t="s">
         <v>75</v>
       </c>
       <c r="I17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K17" t="s">
         <v>82</v>
@@ -3406,10 +3412,10 @@
         <v>71</v>
       </c>
       <c r="R17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="S17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T17" t="s">
         <v>99</v>
@@ -3421,7 +3427,7 @@
         <v>99</v>
       </c>
       <c r="W17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="X17" t="s">
         <v>78</v>
@@ -3430,10 +3436,10 @@
         <v>82</v>
       </c>
       <c r="Z17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AA17" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="AB17" t="s">
         <v>100</v>
@@ -3451,7 +3457,7 @@
         <v>83</v>
       </c>
       <c r="AG17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH17" t="s">
         <v>83</v>
@@ -3463,7 +3469,7 @@
         <v>58</v>
       </c>
       <c r="AK17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
@@ -3474,10 +3480,10 @@
         <v>73</v>
       </c>
       <c r="C18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E18" t="s">
         <v>71</v>
@@ -3492,16 +3498,16 @@
         <v>71</v>
       </c>
       <c r="I18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M18" t="s">
         <v>82</v>
@@ -3510,10 +3516,10 @@
         <v>78</v>
       </c>
       <c r="O18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q18" t="s">
         <v>82</v>
@@ -3522,7 +3528,7 @@
         <v>71</v>
       </c>
       <c r="S18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T18" t="s">
         <v>63</v>
@@ -3546,16 +3552,16 @@
         <v>70</v>
       </c>
       <c r="AA18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AB18" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AC18" t="s">
         <v>100</v>
       </c>
       <c r="AD18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE18" t="s">
         <v>83</v>
@@ -3567,16 +3573,16 @@
         <v>100</v>
       </c>
       <c r="AH18" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AI18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AJ18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AK18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
@@ -3593,7 +3599,7 @@
         <v>81</v>
       </c>
       <c r="E19" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F19" t="s">
         <v>82</v>
@@ -3602,7 +3608,7 @@
         <v>82</v>
       </c>
       <c r="H19" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I19" t="s">
         <v>78</v>
@@ -3611,7 +3617,7 @@
         <v>78</v>
       </c>
       <c r="K19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L19" t="s">
         <v>70</v>
@@ -3629,7 +3635,7 @@
         <v>102</v>
       </c>
       <c r="Q19" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="R19" t="s">
         <v>63</v>
@@ -3650,7 +3656,7 @@
         <v>70</v>
       </c>
       <c r="X19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Y19" t="s">
         <v>77</v>
@@ -3671,39 +3677,39 @@
         <v>100</v>
       </c>
       <c r="AE19" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AF19" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AG19" t="s">
         <v>77</v>
       </c>
       <c r="AH19" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI19" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AJ19" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E20" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F20" t="s">
         <v>78</v>
@@ -3724,13 +3730,13 @@
         <v>83</v>
       </c>
       <c r="L20" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M20" t="s">
         <v>70</v>
       </c>
       <c r="N20" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O20" t="s">
         <v>77</v>
@@ -3748,7 +3754,7 @@
         <v>83</v>
       </c>
       <c r="T20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="U20" t="s">
         <v>83</v>
@@ -3760,10 +3766,10 @@
         <v>100</v>
       </c>
       <c r="X20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Y20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Z20" t="s">
         <v>83</v>
@@ -3772,33 +3778,33 @@
         <v>83</v>
       </c>
       <c r="AB20" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC20" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AD20" t="s">
         <v>58</v>
       </c>
       <c r="AE20" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AF20" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AG20" t="s">
         <v>83</v>
       </c>
       <c r="AH20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B21" t="s">
         <v>81</v>
@@ -3825,10 +3831,10 @@
         <v>63</v>
       </c>
       <c r="J21" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K21" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L21" t="s">
         <v>100</v>
@@ -3840,7 +3846,7 @@
         <v>100</v>
       </c>
       <c r="O21" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P21" t="s">
         <v>83</v>
@@ -3849,10 +3855,10 @@
         <v>70</v>
       </c>
       <c r="R21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="S21" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T21" t="s">
         <v>58</v>
@@ -3861,45 +3867,48 @@
         <v>58</v>
       </c>
       <c r="V21" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="W21" t="s">
         <v>77</v>
       </c>
       <c r="X21" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Y21" t="s">
         <v>58</v>
       </c>
       <c r="Z21" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>95</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD21" t="s">
+        <v>87</v>
+      </c>
+      <c r="AE21" t="s">
+        <v>92</v>
+      </c>
+      <c r="AF21" t="s">
+        <v>92</v>
+      </c>
+      <c r="AG21" t="s">
         <v>86</v>
       </c>
-      <c r="AA21" t="s">
-        <v>94</v>
-      </c>
-      <c r="AB21" t="s">
-        <v>91</v>
-      </c>
-      <c r="AC21" t="s">
-        <v>94</v>
-      </c>
-      <c r="AD21" t="s">
-        <v>86</v>
-      </c>
-      <c r="AE21" t="s">
-        <v>91</v>
-      </c>
-      <c r="AF21" t="s">
-        <v>91</v>
-      </c>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>75</v>
       </c>
       <c r="B22" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s">
         <v>71</v>
@@ -3917,7 +3926,7 @@
         <v>77</v>
       </c>
       <c r="H22" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I22" t="s">
         <v>70</v>
@@ -3929,7 +3938,7 @@
         <v>58</v>
       </c>
       <c r="L22" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M22" t="s">
         <v>83</v>
@@ -3941,43 +3950,46 @@
         <v>58</v>
       </c>
       <c r="P22" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>94</v>
+      </c>
+      <c r="R22" t="s">
         <v>95</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>93</v>
-      </c>
-      <c r="R22" t="s">
-        <v>94</v>
       </c>
       <c r="S22" t="s">
         <v>58</v>
       </c>
       <c r="T22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="U22" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="V22" t="s">
         <v>58</v>
       </c>
       <c r="W22" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="X22" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Z22" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AA22" t="s">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="AG22" t="s">
+        <v>63</v>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>82</v>
       </c>
@@ -3991,10 +4003,10 @@
         <v>82</v>
       </c>
       <c r="E23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G23" t="s">
         <v>83</v>
@@ -4003,13 +4015,13 @@
         <v>77</v>
       </c>
       <c r="I23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J23" t="s">
+        <v>96</v>
+      </c>
+      <c r="K23" t="s">
         <v>95</v>
-      </c>
-      <c r="K23" t="s">
-        <v>94</v>
       </c>
       <c r="L23" t="s">
         <v>58</v>
@@ -4018,10 +4030,10 @@
         <v>58</v>
       </c>
       <c r="N23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P23" t="s">
         <v>58</v>
@@ -4030,27 +4042,30 @@
         <v>102</v>
       </c>
       <c r="R23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="S23" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="T23" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="U23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V23" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="W23" t="s">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>86</v>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B24" t="s">
         <v>71</v>
@@ -4071,36 +4086,39 @@
         <v>58</v>
       </c>
       <c r="H24" t="s">
+        <v>96</v>
+      </c>
+      <c r="I24" t="s">
+        <v>96</v>
+      </c>
+      <c r="J24" t="s">
         <v>95</v>
       </c>
-      <c r="I24" t="s">
+      <c r="K24" t="s">
+        <v>92</v>
+      </c>
+      <c r="L24" t="s">
         <v>95</v>
       </c>
-      <c r="J24" t="s">
-        <v>94</v>
-      </c>
-      <c r="K24" t="s">
+      <c r="M24" t="s">
+        <v>95</v>
+      </c>
+      <c r="N24" t="s">
+        <v>95</v>
+      </c>
+      <c r="O24" t="s">
+        <v>92</v>
+      </c>
+      <c r="P24" t="s">
+        <v>95</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>91</v>
-      </c>
-      <c r="L24" t="s">
-        <v>94</v>
-      </c>
-      <c r="M24" t="s">
-        <v>94</v>
-      </c>
-      <c r="N24" t="s">
-        <v>94</v>
-      </c>
-      <c r="O24" t="s">
-        <v>91</v>
-      </c>
-      <c r="P24" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>90</v>
       </c>
       <c r="B25" t="s">
         <v>82</v>
@@ -4112,22 +4130,22 @@
         <v>78</v>
       </c>
       <c r="E25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F25" t="s">
         <v>58</v>
       </c>
       <c r="G25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H25" t="s">
         <v>58</v>
       </c>
       <c r="I25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4135,28 +4153,28 @@
         <v>99</v>
       </c>
       <c r="B26" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C26" t="s">
         <v>101</v>
       </c>
       <c r="D26" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="E26" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F26" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H26" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I26" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -4167,16 +4185,16 @@
         <v>78</v>
       </c>
       <c r="C27" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D27" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="E27" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F27" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H27" t="s">
         <v>70</v>
@@ -4218,7 +4236,7 @@
         <v>102</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C30" t="s">
         <v>77</v>
@@ -4238,7 +4256,7 @@
         <v>83</v>
       </c>
       <c r="D31" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -4249,10 +4267,10 @@
         <v>77</v>
       </c>
       <c r="C32" t="s">
+        <v>96</v>
+      </c>
+      <c r="D32" t="s">
         <v>95</v>
-      </c>
-      <c r="D32" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -4266,21 +4284,24 @@
         <v>58</v>
       </c>
       <c r="D33" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B34" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C34" t="s">
+        <v>87</v>
+      </c>
+      <c r="D34" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>58</v>
       </c>
@@ -4288,34 +4309,37 @@
         <v>58</v>
       </c>
       <c r="C35" t="s">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="D35" t="s">
+        <v>63</v>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B36" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C36" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B37" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B38" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25"/>
@@ -4511,7 +4535,7 @@
         <v>69</v>
       </c>
       <c r="S3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T3" t="s">
         <v>60</v>
@@ -4523,7 +4547,7 @@
         <v>68</v>
       </c>
       <c r="W3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="X3" t="s">
         <v>64</v>
@@ -4541,7 +4565,7 @@
         <v>74</v>
       </c>
       <c r="AC3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AD3" t="s">
         <v>81</v>
@@ -4550,7 +4574,7 @@
         <v>76</v>
       </c>
       <c r="AF3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AG3" t="s">
         <v>98</v>
@@ -4565,10 +4589,10 @@
         <v>82</v>
       </c>
       <c r="AK3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AL3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AM3" t="s">
         <v>99</v>
@@ -4586,7 +4610,7 @@
         <v>70</v>
       </c>
       <c r="AR3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AS3" t="s">
         <v>102</v>
@@ -4601,19 +4625,19 @@
         <v>83</v>
       </c>
       <c r="AW3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AX3" t="s">
         <v>58</v>
       </c>
       <c r="AY3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AZ3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="BA3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
@@ -5355,7 +5379,7 @@
         <v>0</v>
       </c>
       <c r="AO8" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AQ8" t="s">
         <v>6</v>
@@ -5486,7 +5510,7 @@
         <v>3</v>
       </c>
       <c r="AO9" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="AQ9" t="s">
         <v>11</v>
@@ -5617,7 +5641,7 @@
         <v>8</v>
       </c>
       <c r="AO10" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="AQ10" t="s">
         <v>44</v>
@@ -5748,7 +5772,7 @@
         <v>45</v>
       </c>
       <c r="AO11" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="AQ11" t="s">
         <v>30</v>
@@ -5867,7 +5891,7 @@
         <v>5</v>
       </c>
       <c r="AO12" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AQ12" t="s">
         <v>33</v>
@@ -5983,7 +6007,7 @@
         <v>23</v>
       </c>
       <c r="AO13" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="AQ13" t="s">
         <v>7</v>
@@ -6099,7 +6123,7 @@
         <v>30</v>
       </c>
       <c r="AO14" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="AQ14" t="s">
         <v>12</v>
@@ -6215,7 +6239,7 @@
         <v>37</v>
       </c>
       <c r="AO15" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AQ15" t="s">
         <v>25</v>
@@ -6322,7 +6346,7 @@
         <v>13</v>
       </c>
       <c r="AO16" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AQ16" t="s">
         <v>23</v>
@@ -6349,7 +6373,7 @@
         <v>18</v>
       </c>
       <c r="BA16" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
@@ -6426,7 +6450,7 @@
         <v>2</v>
       </c>
       <c r="AO17" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="s">
         <v>35</v>
@@ -6453,7 +6477,7 @@
         <v>3</v>
       </c>
       <c r="BA17" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
@@ -6530,7 +6554,7 @@
         <v>32</v>
       </c>
       <c r="AO18" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="AQ18" t="s">
         <v>27</v>
@@ -6634,7 +6658,7 @@
         <v>26</v>
       </c>
       <c r="AO19" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="AQ19" t="s">
         <v>31</v>
@@ -6717,7 +6741,7 @@
         <v>34</v>
       </c>
       <c r="AO20" t="s">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="AQ20" t="s">
         <v>5</v>
@@ -6800,7 +6824,7 @@
         <v>24</v>
       </c>
       <c r="AO21" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AQ21" t="s">
         <v>36</v>
@@ -6883,7 +6907,7 @@
         <v>12</v>
       </c>
       <c r="AO22" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="AQ22" t="s">
         <v>8</v>
@@ -6966,7 +6990,7 @@
         <v>25</v>
       </c>
       <c r="AO23" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AQ23" t="s">
         <v>16</v>
@@ -7031,7 +7055,7 @@
         <v>6</v>
       </c>
       <c r="AO24" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="AV24" t="s">
         <v>5</v>
@@ -7043,7 +7067,7 @@
         <v>2</v>
       </c>
       <c r="AY24" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="AZ24" t="s">
         <v>2</v>
@@ -7087,7 +7111,7 @@
         <v>3</v>
       </c>
       <c r="AO25" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AV25" t="s">
         <v>2</v>
@@ -7099,7 +7123,7 @@
         <v>7</v>
       </c>
       <c r="AY25" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="AZ25" t="s">
         <v>11</v>
@@ -7143,7 +7167,7 @@
         <v>39</v>
       </c>
       <c r="AO26" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="AV26" t="s">
         <v>19</v>
@@ -7199,7 +7223,7 @@
         <v>20</v>
       </c>
       <c r="AO27" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="AV27" t="s">
         <v>25</v>
@@ -7382,7 +7406,7 @@
         <v>69</v>
       </c>
       <c r="S3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T3" t="s">
         <v>60</v>
@@ -7394,7 +7418,7 @@
         <v>68</v>
       </c>
       <c r="W3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="X3" t="s">
         <v>64</v>
@@ -7412,7 +7436,7 @@
         <v>74</v>
       </c>
       <c r="AC3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AD3" t="s">
         <v>81</v>
@@ -7421,7 +7445,7 @@
         <v>76</v>
       </c>
       <c r="AF3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AG3" t="s">
         <v>98</v>
@@ -7436,10 +7460,10 @@
         <v>82</v>
       </c>
       <c r="AK3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AL3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AM3" t="s">
         <v>99</v>
@@ -7457,7 +7481,7 @@
         <v>70</v>
       </c>
       <c r="AR3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AS3" t="s">
         <v>102</v>
@@ -7472,19 +7496,19 @@
         <v>83</v>
       </c>
       <c r="AW3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AX3" t="s">
         <v>58</v>
       </c>
       <c r="AY3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AZ3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="BA3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
@@ -8040,109 +8064,113 @@
         <v>284</v>
       </c>
       <c r="AE8" t="s">
+        <v>188</v>
+      </c>
+      <c r="AF8" t="s">
         <v>285</v>
       </c>
-      <c r="AF8" t="s">
+      <c r="AH8" t="s">
         <v>286</v>
       </c>
-      <c r="AH8" t="s">
+      <c r="AI8" t="s">
         <v>287</v>
       </c>
-      <c r="AI8" t="s">
+      <c r="AJ8" t="s">
         <v>288</v>
       </c>
-      <c r="AJ8" t="s">
+      <c r="AO8" t="s">
         <v>289</v>
       </c>
-      <c r="AO8" t="s">
+      <c r="AQ8" t="s">
         <v>290</v>
       </c>
-      <c r="AQ8" t="s">
+      <c r="AR8" t="s">
         <v>291</v>
       </c>
-      <c r="AR8" t="s">
+      <c r="AU8" t="s">
         <v>292</v>
       </c>
-      <c r="AU8" t="s">
+      <c r="AV8" t="s">
         <v>293</v>
       </c>
-      <c r="AV8" t="s">
+      <c r="AW8" t="s">
         <v>294</v>
       </c>
-      <c r="AW8" t="s">
+      <c r="AX8" t="s">
         <v>295</v>
       </c>
-      <c r="AX8" t="s">
+      <c r="AY8" t="s">
         <v>296</v>
       </c>
-      <c r="AY8" t="s">
+      <c r="AZ8" t="s">
         <v>297</v>
       </c>
-      <c r="AZ8" t="s">
+      <c r="BA8" t="s">
         <v>298</v>
-      </c>
-      <c r="BA8" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>299</v>
+      </c>
+      <c r="E9" t="s">
         <v>300</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>301</v>
       </c>
-      <c r="F9" t="s">
+      <c r="H9" t="s">
         <v>302</v>
       </c>
-      <c r="H9" t="s">
+      <c r="O9" t="s">
         <v>303</v>
       </c>
-      <c r="O9" t="s">
+      <c r="T9" t="s">
         <v>304</v>
       </c>
-      <c r="T9" t="s">
+      <c r="X9" t="s">
         <v>305</v>
       </c>
-      <c r="X9" t="s">
+      <c r="AB9" t="s">
         <v>306</v>
       </c>
-      <c r="AB9" t="s">
+      <c r="AF9" t="s">
         <v>307</v>
       </c>
-      <c r="AF9" t="s">
+      <c r="AI9" t="s">
         <v>308</v>
       </c>
-      <c r="AI9" t="s">
+      <c r="AJ9" t="s">
         <v>309</v>
       </c>
-      <c r="AJ9" t="s">
+      <c r="AO9" t="s">
         <v>310</v>
       </c>
-      <c r="AO9" t="s">
+      <c r="AV9" t="s">
         <v>311</v>
       </c>
-      <c r="AV9" t="s">
+      <c r="AW9" t="s">
         <v>312</v>
       </c>
-      <c r="AW9" t="s">
+      <c r="AX9" t="s">
         <v>313</v>
       </c>
-      <c r="AX9" t="s">
+      <c r="AY9" t="s">
         <v>314</v>
       </c>
-      <c r="AY9" t="s">
+      <c r="AZ9" t="s">
         <v>315</v>
       </c>
-      <c r="AZ9" t="s">
+      <c r="BA9" t="s">
         <v>316</v>
       </c>
-      <c r="BA9" t="s">
+    </row>
+    <row r="10" ht="15" customHeight="1" spans="32:53" x14ac:dyDescent="0.25">
+      <c r="AO10" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="32:53" x14ac:dyDescent="0.25"/>
-    <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" ht="15" customHeight="1" spans="41:41" x14ac:dyDescent="0.25"/>
     <row r="12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="13" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="14" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/data/ICEHLdelegacije.xlsx
+++ b/data/ICEHLdelegacije.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2085" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2088" uniqueCount="318">
   <si>
     <t>PiragicTr</t>
   </si>
@@ -246,6 +246,9 @@
     <t>2024-11-24</t>
   </si>
   <si>
+    <t>zbrisano</t>
+  </si>
+  <si>
     <t>2024-11-20</t>
   </si>
   <si>
@@ -276,9 +279,6 @@
     <t>2024-11-02</t>
   </si>
   <si>
-    <t>zbrisano</t>
-  </si>
-  <si>
     <t>2024-12-28</t>
   </si>
   <si>
@@ -423,13 +423,13 @@
     <t>Stadthalle Villach;SeewaldEl;ZrnicMi;BärnthalerCh;MoidlMa</t>
   </si>
   <si>
-    <t>Merkur Eisstadion Graz;FichtnerPa;SmetanaLa;BärnthalerCh;WimmlerAl</t>
+    <t>Merkur Eisstadion Graz;FichtnerPa;SmetanaLa;BärnthalerCh;WeissAl</t>
   </si>
   <si>
     <t>Sparkasse Arena Bozen;OfnerCh;SternatCh;JedlickaPe;KoncDa</t>
   </si>
   <si>
-    <t>Eisarena Salzburg;NikolicKr;SmetanaLa;JedlickaPe;KoncDa</t>
+    <t>Eisarena Salzburg;SchauerJa;SmetanaLa;JedlickaPe;KoncDa</t>
   </si>
   <si>
     <t>Merkur Eisstadion Graz;HronskyTo;OfnerCh;BärnthalerCh;JedlickaPe</t>
@@ -795,7 +795,7 @@
     <t>Eishalle Asiago;NikolicMa;ZrnicMi;HribarMa;PardatscherUl</t>
   </si>
   <si>
-    <t>Stadthalle Villach;VoicanCh;ZrnicMi;HribarMa;ZgoncGa</t>
+    <t>Stadthalle Villach;KainbergerJu;ZrnicMi;HribarMa;ZgoncGa</t>
   </si>
   <si>
     <t>Eishalle Feldkirch;GroznikBo;RezekGr;Gatol-schafranekMa;RieckenSi</t>
@@ -2240,16 +2240,16 @@
         <v>75</v>
       </c>
       <c r="AQ7" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="AR7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AS7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AT7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
@@ -2296,7 +2296,7 @@
         <v>66</v>
       </c>
       <c r="O8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P8" t="s">
         <v>57</v>
@@ -2344,7 +2344,7 @@
         <v>64</v>
       </c>
       <c r="AE8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AF8" t="s">
         <v>69</v>
@@ -2368,10 +2368,10 @@
         <v>72</v>
       </c>
       <c r="AM8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AN8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO8" t="s">
         <v>73</v>
@@ -2380,10 +2380,10 @@
         <v>58</v>
       </c>
       <c r="AQ8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AR8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AS8" t="s">
         <v>58</v>
@@ -2421,7 +2421,7 @@
         <v>72</v>
       </c>
       <c r="K9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L9" t="s">
         <v>72</v>
@@ -2469,7 +2469,7 @@
         <v>60</v>
       </c>
       <c r="AA9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB9" t="s">
         <v>72</v>
@@ -2478,7 +2478,7 @@
         <v>72</v>
       </c>
       <c r="AD9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE9" t="s">
         <v>64</v>
@@ -2490,28 +2490,28 @@
         <v>72</v>
       </c>
       <c r="AH9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI9" t="s">
         <v>72</v>
       </c>
       <c r="AJ9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AK9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AL9" t="s">
         <v>64</v>
       </c>
       <c r="AM9" t="s">
+        <v>77</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>84</v>
+      </c>
+      <c r="AO9" t="s">
         <v>76</v>
-      </c>
-      <c r="AN9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AO9" t="s">
-        <v>86</v>
       </c>
       <c r="AP9" t="s">
         <v>87</v>
@@ -2603,22 +2603,22 @@
         <v>68</v>
       </c>
       <c r="AC10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG10" t="s">
         <v>69</v>
       </c>
       <c r="AH10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI10" t="s">
         <v>61</v>
@@ -2633,7 +2633,7 @@
         <v>75</v>
       </c>
       <c r="AM10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN10" t="s">
         <v>87</v>
@@ -2662,7 +2662,7 @@
         <v>60</v>
       </c>
       <c r="G11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H11" t="s">
         <v>61</v>
@@ -2689,7 +2689,7 @@
         <v>68</v>
       </c>
       <c r="P11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q11" t="s">
         <v>64</v>
@@ -2701,7 +2701,7 @@
         <v>60</v>
       </c>
       <c r="T11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="U11" t="s">
         <v>60</v>
@@ -2731,7 +2731,7 @@
         <v>64</v>
       </c>
       <c r="AD11" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="AE11" t="s">
         <v>54</v>
@@ -2743,7 +2743,7 @@
         <v>90</v>
       </c>
       <c r="AH11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI11" t="s">
         <v>90</v>
@@ -2752,7 +2752,7 @@
         <v>74</v>
       </c>
       <c r="AK11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL11" t="s">
         <v>91</v>
@@ -2764,7 +2764,7 @@
         <v>92</v>
       </c>
       <c r="AO11" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
@@ -2814,31 +2814,31 @@
         <v>64</v>
       </c>
       <c r="P12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="R12" t="s">
         <v>68</v>
       </c>
       <c r="S12" t="s">
+        <v>86</v>
+      </c>
+      <c r="T12" t="s">
         <v>85</v>
-      </c>
-      <c r="T12" t="s">
-        <v>84</v>
       </c>
       <c r="U12" t="s">
         <v>64</v>
       </c>
       <c r="V12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W12" t="s">
         <v>74</v>
       </c>
       <c r="X12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y12" t="s">
         <v>68</v>
@@ -2850,7 +2850,7 @@
         <v>75</v>
       </c>
       <c r="AB12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AC12" t="s">
         <v>73</v>
@@ -2871,7 +2871,7 @@
         <v>75</v>
       </c>
       <c r="AI12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AJ12" t="s">
         <v>75</v>
@@ -2880,7 +2880,7 @@
         <v>90</v>
       </c>
       <c r="AL12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AM12" t="s">
         <v>94</v>
@@ -2918,10 +2918,10 @@
         <v>68</v>
       </c>
       <c r="I13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K13" t="s">
         <v>72</v>
@@ -2948,7 +2948,7 @@
         <v>73</v>
       </c>
       <c r="S13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T13" t="s">
         <v>74</v>
@@ -2960,7 +2960,7 @@
         <v>60</v>
       </c>
       <c r="W13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X13" t="s">
         <v>74</v>
@@ -2978,10 +2978,10 @@
         <v>90</v>
       </c>
       <c r="AC13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE13" t="s">
         <v>75</v>
@@ -2990,33 +2990,36 @@
         <v>90</v>
       </c>
       <c r="AG13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH13" t="s">
         <v>71</v>
       </c>
       <c r="AI13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AK13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AM13" t="s">
         <v>96</v>
       </c>
+      <c r="AO13" t="s">
+        <v>71</v>
+      </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>60</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
         <v>89</v>
@@ -3028,10 +3031,10 @@
         <v>89</v>
       </c>
       <c r="F14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H14" t="s">
         <v>64</v>
@@ -3052,10 +3055,10 @@
         <v>93</v>
       </c>
       <c r="N14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O14" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P14" t="s">
         <v>90</v>
@@ -3073,7 +3076,7 @@
         <v>90</v>
       </c>
       <c r="U14" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V14" t="s">
         <v>73</v>
@@ -3082,16 +3085,16 @@
         <v>71</v>
       </c>
       <c r="X14" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Y14" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Z14" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AA14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AB14" t="s">
         <v>75</v>
@@ -3106,16 +3109,16 @@
         <v>91</v>
       </c>
       <c r="AF14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AG14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH14" t="s">
         <v>97</v>
       </c>
       <c r="AI14" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="AJ14" t="s">
         <v>97</v>
@@ -3127,7 +3130,7 @@
         <v>96</v>
       </c>
       <c r="AM14" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
@@ -3141,7 +3144,7 @@
         <v>64</v>
       </c>
       <c r="D15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E15" t="s">
         <v>64</v>
@@ -3159,16 +3162,16 @@
         <v>75</v>
       </c>
       <c r="J15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N15" t="s">
         <v>90</v>
@@ -3183,7 +3186,7 @@
         <v>93</v>
       </c>
       <c r="R15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S15" t="s">
         <v>75</v>
@@ -3195,10 +3198,10 @@
         <v>90</v>
       </c>
       <c r="V15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X15" t="s">
         <v>71</v>
@@ -3210,19 +3213,19 @@
         <v>71</v>
       </c>
       <c r="AA15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AB15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC15" t="s">
         <v>71</v>
       </c>
       <c r="AD15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AE15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AF15" t="s">
         <v>74</v>
@@ -3254,7 +3257,7 @@
         <v>64</v>
       </c>
       <c r="C16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D16" t="s">
         <v>73</v>
@@ -3263,13 +3266,13 @@
         <v>73</v>
       </c>
       <c r="F16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G16" t="s">
         <v>74</v>
       </c>
       <c r="H16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I16" t="s">
         <v>71</v>
@@ -3281,7 +3284,7 @@
         <v>90</v>
       </c>
       <c r="L16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M16" t="s">
         <v>75</v>
@@ -3296,10 +3299,10 @@
         <v>75</v>
       </c>
       <c r="Q16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S16" t="s">
         <v>71</v>
@@ -3311,19 +3314,19 @@
         <v>71</v>
       </c>
       <c r="V16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="W16" t="s">
         <v>97</v>
       </c>
       <c r="X16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y16" t="s">
         <v>71</v>
       </c>
       <c r="Z16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA16" t="s">
         <v>98</v>
@@ -3344,7 +3347,7 @@
         <v>70</v>
       </c>
       <c r="AG16" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="AH16" t="s">
         <v>70</v>
@@ -3356,15 +3359,18 @@
         <v>96</v>
       </c>
       <c r="AK16" t="s">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="AL16" t="s">
+        <v>90</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>64</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C17" t="s">
         <v>74</v>
@@ -3391,7 +3397,7 @@
         <v>97</v>
       </c>
       <c r="K17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L17" t="s">
         <v>75</v>
@@ -3400,13 +3406,13 @@
         <v>71</v>
       </c>
       <c r="N17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q17" t="s">
         <v>71</v>
@@ -3421,7 +3427,7 @@
         <v>99</v>
       </c>
       <c r="U17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V17" t="s">
         <v>99</v>
@@ -3430,16 +3436,16 @@
         <v>93</v>
       </c>
       <c r="X17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Y17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z17" t="s">
         <v>97</v>
       </c>
       <c r="AA17" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="AB17" t="s">
         <v>100</v>
@@ -3454,16 +3460,16 @@
         <v>70</v>
       </c>
       <c r="AF17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AG17" t="s">
         <v>94</v>
       </c>
       <c r="AH17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ17" t="s">
         <v>58</v>
@@ -3510,10 +3516,10 @@
         <v>91</v>
       </c>
       <c r="M18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="N18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O18" t="s">
         <v>94</v>
@@ -3522,7 +3528,7 @@
         <v>94</v>
       </c>
       <c r="Q18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="R18" t="s">
         <v>71</v>
@@ -3564,7 +3570,7 @@
         <v>94</v>
       </c>
       <c r="AE18" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AF18" t="s">
         <v>58</v>
@@ -3593,28 +3599,28 @@
         <v>74</v>
       </c>
       <c r="C19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E19" t="s">
         <v>97</v>
       </c>
       <c r="F19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H19" t="s">
         <v>97</v>
       </c>
       <c r="I19" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J19" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K19" t="s">
         <v>94</v>
@@ -3644,10 +3650,10 @@
         <v>102</v>
       </c>
       <c r="T19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V19" t="s">
         <v>100</v>
@@ -3659,10 +3665,10 @@
         <v>94</v>
       </c>
       <c r="Y19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA19" t="s">
         <v>102</v>
@@ -3671,7 +3677,7 @@
         <v>58</v>
       </c>
       <c r="AC19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AD19" t="s">
         <v>100</v>
@@ -3683,7 +3689,7 @@
         <v>87</v>
       </c>
       <c r="AG19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH19" t="s">
         <v>87</v>
@@ -3712,7 +3718,7 @@
         <v>91</v>
       </c>
       <c r="F20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G20" t="s">
         <v>70</v>
@@ -3721,13 +3727,13 @@
         <v>73</v>
       </c>
       <c r="I20" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J20" t="s">
         <v>63</v>
       </c>
       <c r="K20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L20" t="s">
         <v>94</v>
@@ -3739,28 +3745,28 @@
         <v>94</v>
       </c>
       <c r="O20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q20" t="s">
         <v>63</v>
       </c>
       <c r="R20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T20" t="s">
         <v>96</v>
       </c>
       <c r="U20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W20" t="s">
         <v>100</v>
@@ -3772,10 +3778,10 @@
         <v>96</v>
       </c>
       <c r="Z20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AA20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AB20" t="s">
         <v>95</v>
@@ -3793,7 +3799,7 @@
         <v>95</v>
       </c>
       <c r="AG20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AH20" t="s">
         <v>92</v>
@@ -3807,7 +3813,7 @@
         <v>90</v>
       </c>
       <c r="B21" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C21" t="s">
         <v>98</v>
@@ -3840,7 +3846,7 @@
         <v>100</v>
       </c>
       <c r="M21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N21" t="s">
         <v>100</v>
@@ -3849,7 +3855,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q21" t="s">
         <v>70</v>
@@ -3870,7 +3876,7 @@
         <v>96</v>
       </c>
       <c r="W21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X21" t="s">
         <v>95</v>
@@ -3900,7 +3906,7 @@
         <v>92</v>
       </c>
       <c r="AG21" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
@@ -3923,7 +3929,7 @@
         <v>70</v>
       </c>
       <c r="G22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H22" t="s">
         <v>94</v>
@@ -3932,7 +3938,7 @@
         <v>70</v>
       </c>
       <c r="J22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K22" t="s">
         <v>58</v>
@@ -3941,10 +3947,10 @@
         <v>96</v>
       </c>
       <c r="M22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O22" t="s">
         <v>58</v>
@@ -3991,16 +3997,16 @@
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B23" t="s">
         <v>75</v>
       </c>
       <c r="C23" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D23" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E23" t="s">
         <v>94</v>
@@ -4009,10 +4015,10 @@
         <v>94</v>
       </c>
       <c r="G23" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H23" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I23" t="s">
         <v>94</v>
@@ -4059,8 +4065,11 @@
       <c r="W23" t="s">
         <v>92</v>
       </c>
+      <c r="Y23" t="s">
+        <v>75</v>
+      </c>
       <c r="AA23" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
@@ -4071,7 +4080,7 @@
         <v>71</v>
       </c>
       <c r="C24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D24" t="s">
         <v>99</v>
@@ -4080,7 +4089,7 @@
         <v>102</v>
       </c>
       <c r="F24" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G24" t="s">
         <v>58</v>
@@ -4121,13 +4130,13 @@
         <v>91</v>
       </c>
       <c r="B25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C25" t="s">
         <v>63</v>
       </c>
       <c r="D25" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E25" t="s">
         <v>96</v>
@@ -4159,7 +4168,7 @@
         <v>101</v>
       </c>
       <c r="D26" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="E26" t="s">
         <v>87</v>
@@ -4179,16 +4188,16 @@
     </row>
     <row r="27" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B27" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C27" t="s">
         <v>94</v>
       </c>
       <c r="D27" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="E27" t="s">
         <v>92</v>
@@ -4211,10 +4220,10 @@
         <v>102</v>
       </c>
       <c r="D28" t="s">
+        <v>78</v>
+      </c>
+      <c r="F28" t="s">
         <v>77</v>
-      </c>
-      <c r="F28" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4228,7 +4237,7 @@
         <v>100</v>
       </c>
       <c r="D29" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -4239,7 +4248,7 @@
         <v>94</v>
       </c>
       <c r="C30" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D30" t="s">
         <v>58</v>
@@ -4253,7 +4262,7 @@
         <v>102</v>
       </c>
       <c r="C31" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D31" t="s">
         <v>87</v>
@@ -4261,10 +4270,10 @@
     </row>
     <row r="32" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B32" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C32" t="s">
         <v>96</v>
@@ -4275,10 +4284,10 @@
     </row>
     <row r="33" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B33" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C33" t="s">
         <v>58</v>
@@ -4298,7 +4307,7 @@
         <v>87</v>
       </c>
       <c r="D34" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -4526,7 +4535,7 @@
         <v>72</v>
       </c>
       <c r="P3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q3" t="s">
         <v>61</v>
@@ -4541,7 +4550,7 @@
         <v>60</v>
       </c>
       <c r="U3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="V3" t="s">
         <v>68</v>
@@ -4553,10 +4562,10 @@
         <v>64</v>
       </c>
       <c r="Y3" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z3" t="s">
         <v>85</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>84</v>
       </c>
       <c r="AA3" t="s">
         <v>73</v>
@@ -4568,10 +4577,10 @@
         <v>93</v>
       </c>
       <c r="AD3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF3" t="s">
         <v>90</v>
@@ -4586,7 +4595,7 @@
         <v>71</v>
       </c>
       <c r="AJ3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AK3" t="s">
         <v>97</v>
@@ -4598,7 +4607,7 @@
         <v>99</v>
       </c>
       <c r="AN3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AO3" t="s">
         <v>63</v>
@@ -4619,10 +4628,10 @@
         <v>100</v>
       </c>
       <c r="AU3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AV3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AW3" t="s">
         <v>96</v>
@@ -4741,7 +4750,7 @@
         <v>2</v>
       </c>
       <c r="AH4" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="AI4" t="s">
         <v>18</v>
@@ -5218,7 +5227,7 @@
         <v>38</v>
       </c>
       <c r="AF7" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="AG7" t="s">
         <v>15</v>
@@ -6337,7 +6346,7 @@
         <v>6</v>
       </c>
       <c r="AI16" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ16" t="s">
         <v>5</v>
@@ -7244,7 +7253,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="32:53" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="15" customHeight="1" spans="35:53" x14ac:dyDescent="0.25"/>
     <row r="29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -7397,7 +7406,7 @@
         <v>72</v>
       </c>
       <c r="P3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q3" t="s">
         <v>61</v>
@@ -7412,7 +7421,7 @@
         <v>60</v>
       </c>
       <c r="U3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="V3" t="s">
         <v>68</v>
@@ -7424,10 +7433,10 @@
         <v>64</v>
       </c>
       <c r="Y3" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z3" t="s">
         <v>85</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>84</v>
       </c>
       <c r="AA3" t="s">
         <v>73</v>
@@ -7439,10 +7448,10 @@
         <v>93</v>
       </c>
       <c r="AD3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF3" t="s">
         <v>90</v>
@@ -7457,7 +7466,7 @@
         <v>71</v>
       </c>
       <c r="AJ3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AK3" t="s">
         <v>97</v>
@@ -7469,7 +7478,7 @@
         <v>99</v>
       </c>
       <c r="AN3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AO3" t="s">
         <v>63</v>
@@ -7490,10 +7499,10 @@
         <v>100</v>
       </c>
       <c r="AU3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AV3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AW3" t="s">
         <v>96</v>
@@ -8165,7 +8174,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="32:53" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="35:53" x14ac:dyDescent="0.25">
       <c r="AO10" t="s">
         <v>317</v>
       </c>

--- a/data/ICEHLdelegacije.xlsx
+++ b/data/ICEHLdelegacije.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2088" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2107" uniqueCount="320">
   <si>
     <t>PiragicTr</t>
   </si>
@@ -207,105 +207,105 @@
     <t>2024-10-06</t>
   </si>
   <si>
+    <t>zbrisano</t>
+  </si>
+  <si>
+    <t>2024-11-01</t>
+  </si>
+  <si>
+    <t>2024-10-05</t>
+  </si>
+  <si>
+    <t>2024-10-11</t>
+  </si>
+  <si>
+    <t>2024-10-02</t>
+  </si>
+  <si>
+    <t>2024-10-27</t>
+  </si>
+  <si>
+    <t>2024-10-22</t>
+  </si>
+  <si>
+    <t>2024-12-08</t>
+  </si>
+  <si>
+    <t>2024-11-27</t>
+  </si>
+  <si>
+    <t>2024-10-18</t>
+  </si>
+  <si>
+    <t>2024-11-13</t>
+  </si>
+  <si>
+    <t>2024-11-15</t>
+  </si>
+  <si>
+    <t>2024-11-24</t>
+  </si>
+  <si>
+    <t>2024-11-20</t>
+  </si>
+  <si>
+    <t>2024-12-18</t>
+  </si>
+  <si>
+    <t>2024-10-19</t>
+  </si>
+  <si>
+    <t>2024-10-26</t>
+  </si>
+  <si>
+    <t>2024-11-17</t>
+  </si>
+  <si>
+    <t>2024-11-29</t>
+  </si>
+  <si>
+    <t>2024-12-20</t>
+  </si>
+  <si>
+    <t>2024-11-03</t>
+  </si>
+  <si>
+    <t>2024-11-02</t>
+  </si>
+  <si>
+    <t>2024-12-28</t>
+  </si>
+  <si>
+    <t>2024-10-23</t>
+  </si>
+  <si>
+    <t>2024-10-29</t>
+  </si>
+  <si>
+    <t>2024-11-22</t>
+  </si>
+  <si>
+    <t>2024-12-01</t>
+  </si>
+  <si>
+    <t>2025-01-01</t>
+  </si>
+  <si>
+    <t>2024-11-16</t>
+  </si>
+  <si>
+    <t>2024-12-04</t>
+  </si>
+  <si>
+    <t>2024-12-13</t>
+  </si>
+  <si>
+    <t>2024-12-30</t>
+  </si>
+  <si>
     <t>2024-12-06</t>
   </si>
   <si>
-    <t>2024-11-01</t>
-  </si>
-  <si>
-    <t>2024-10-05</t>
-  </si>
-  <si>
-    <t>2024-10-11</t>
-  </si>
-  <si>
-    <t>2024-10-02</t>
-  </si>
-  <si>
-    <t>2024-10-27</t>
-  </si>
-  <si>
-    <t>2024-10-22</t>
-  </si>
-  <si>
-    <t>2024-12-08</t>
-  </si>
-  <si>
-    <t>2024-11-27</t>
-  </si>
-  <si>
-    <t>2024-10-18</t>
-  </si>
-  <si>
-    <t>2024-11-13</t>
-  </si>
-  <si>
-    <t>2024-11-15</t>
-  </si>
-  <si>
-    <t>2024-11-24</t>
-  </si>
-  <si>
-    <t>zbrisano</t>
-  </si>
-  <si>
-    <t>2024-11-20</t>
-  </si>
-  <si>
-    <t>2024-12-18</t>
-  </si>
-  <si>
-    <t>2024-12-04</t>
-  </si>
-  <si>
-    <t>2024-10-19</t>
-  </si>
-  <si>
-    <t>2024-10-26</t>
-  </si>
-  <si>
-    <t>2024-11-17</t>
-  </si>
-  <si>
-    <t>2024-11-29</t>
-  </si>
-  <si>
-    <t>2024-12-20</t>
-  </si>
-  <si>
-    <t>2024-11-03</t>
-  </si>
-  <si>
-    <t>2024-11-02</t>
-  </si>
-  <si>
-    <t>2024-12-28</t>
-  </si>
-  <si>
-    <t>2024-10-23</t>
-  </si>
-  <si>
-    <t>2024-10-29</t>
-  </si>
-  <si>
-    <t>2024-11-22</t>
-  </si>
-  <si>
-    <t>2024-12-01</t>
-  </si>
-  <si>
-    <t>2025-01-01</t>
-  </si>
-  <si>
-    <t>2024-11-16</t>
-  </si>
-  <si>
-    <t>2024-12-13</t>
-  </si>
-  <si>
-    <t>2024-12-30</t>
-  </si>
-  <si>
     <t>2024-12-22</t>
   </si>
   <si>
@@ -327,6 +327,9 @@
     <t>2024-12-14</t>
   </si>
   <si>
+    <t>2024-12-10</t>
+  </si>
+  <si>
     <t>HuberAn</t>
   </si>
   <si>
@@ -489,6 +492,9 @@
     <t>Eishalle Wien-Kagran;SiegelSt;SmetanaLa;Gatol-schafranekMa;JedlickaPe</t>
   </si>
   <si>
+    <t>Stadthalle Villach;PiragicTr;SternatCh;HribarMa;ZgoncGa</t>
+  </si>
+  <si>
     <t>Tiroler Wasserkraft Arena;NikolicMa;SeewaldEl;FleischmannLu;NotheggerDa</t>
   </si>
   <si>
@@ -579,9 +585,6 @@
     <t>Eisarena Salzburg;BernekerTh;SiegelSt;BedynekSe;WimmlerAl</t>
   </si>
   <si>
-    <t>Stadthalle Villach;PiragicTr;SternatCh;HribarMa;JeramFi</t>
-  </si>
-  <si>
     <t>ZBRISANO</t>
   </si>
   <si>
@@ -804,7 +807,7 @@
     <t>Gabor Ocskay Eisarena;FichtnerPa;OfnerCh;DurmisOt;JedlickaPe</t>
   </si>
   <si>
-    <t>Linz AG Eisarena;NikolicKr;SiegelSt;FleischmannLu;Gatol-schafranekMa</t>
+    <t>Linz AG Eisarena;NikolicKr;SiegelSt;Gatol-schafranekMa;MoidlMa</t>
   </si>
   <si>
     <t>Gabor Ocskay Eisarena;RezekGr;SoosDa;MuzsikNo;VacziDa</t>
@@ -883,6 +886,9 @@
   </si>
   <si>
     <t>Eishalle Asiago;NikolicKr;SchauerJa;PardatscherUl;RigoniDa</t>
+  </si>
+  <si>
+    <t>Eishalle Asiago;PiragicTr;ZrnicMi;MantovaniDa;PuffWo</t>
   </si>
   <si>
     <t>Eishalle Feldkirch;OfnerCh;PiragicTr;NotheggerDa;ZgoncGa</t>
@@ -2240,16 +2246,16 @@
         <v>75</v>
       </c>
       <c r="AQ7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AR7" t="s">
         <v>76</v>
       </c>
-      <c r="AR7" t="s">
+      <c r="AS7" t="s">
         <v>77</v>
       </c>
-      <c r="AS7" t="s">
-        <v>78</v>
-      </c>
       <c r="AT7" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
@@ -2296,7 +2302,7 @@
         <v>66</v>
       </c>
       <c r="O8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="P8" t="s">
         <v>57</v>
@@ -2344,7 +2350,7 @@
         <v>64</v>
       </c>
       <c r="AE8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AF8" t="s">
         <v>69</v>
@@ -2368,10 +2374,10 @@
         <v>72</v>
       </c>
       <c r="AM8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AN8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AO8" t="s">
         <v>73</v>
@@ -2380,10 +2386,10 @@
         <v>58</v>
       </c>
       <c r="AQ8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="AR8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="AS8" t="s">
         <v>58</v>
@@ -2421,7 +2427,7 @@
         <v>72</v>
       </c>
       <c r="K9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L9" t="s">
         <v>72</v>
@@ -2469,7 +2475,7 @@
         <v>60</v>
       </c>
       <c r="AA9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="AB9" t="s">
         <v>72</v>
@@ -2478,7 +2484,7 @@
         <v>72</v>
       </c>
       <c r="AD9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="AE9" t="s">
         <v>64</v>
@@ -2490,31 +2496,31 @@
         <v>72</v>
       </c>
       <c r="AH9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AI9" t="s">
         <v>72</v>
       </c>
       <c r="AJ9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AK9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AL9" t="s">
         <v>64</v>
       </c>
       <c r="AM9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AN9" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="AO9" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="AP9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
@@ -2534,7 +2540,7 @@
         <v>52</v>
       </c>
       <c r="F10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G10" t="s">
         <v>72</v>
@@ -2564,7 +2570,7 @@
         <v>60</v>
       </c>
       <c r="P10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="Q10" t="s">
         <v>60</v>
@@ -2573,7 +2579,7 @@
         <v>69</v>
       </c>
       <c r="S10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="T10" t="s">
         <v>60</v>
@@ -2582,10 +2588,10 @@
         <v>69</v>
       </c>
       <c r="V10" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="W10" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="X10" t="s">
         <v>69</v>
@@ -2603,28 +2609,28 @@
         <v>68</v>
       </c>
       <c r="AC10" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD10" t="s">
         <v>80</v>
       </c>
-      <c r="AD10" t="s">
-        <v>82</v>
-      </c>
       <c r="AE10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="AF10" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AG10" t="s">
         <v>69</v>
       </c>
       <c r="AH10" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AI10" t="s">
         <v>61</v>
       </c>
       <c r="AJ10" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AK10" t="s">
         <v>68</v>
@@ -2633,10 +2639,10 @@
         <v>75</v>
       </c>
       <c r="AM10" t="s">
+        <v>83</v>
+      </c>
+      <c r="AN10" t="s">
         <v>85</v>
-      </c>
-      <c r="AN10" t="s">
-        <v>87</v>
       </c>
       <c r="AO10" t="s">
         <v>70</v>
@@ -2662,13 +2668,13 @@
         <v>60</v>
       </c>
       <c r="G11" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H11" t="s">
         <v>61</v>
       </c>
       <c r="I11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J11" t="s">
         <v>60</v>
@@ -2689,7 +2695,7 @@
         <v>68</v>
       </c>
       <c r="P11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="Q11" t="s">
         <v>64</v>
@@ -2701,7 +2707,7 @@
         <v>60</v>
       </c>
       <c r="T11" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="U11" t="s">
         <v>60</v>
@@ -2719,19 +2725,19 @@
         <v>60</v>
       </c>
       <c r="Z11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AA11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AB11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AC11" t="s">
         <v>64</v>
       </c>
       <c r="AD11" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="AE11" t="s">
         <v>54</v>
@@ -2740,31 +2746,31 @@
         <v>73</v>
       </c>
       <c r="AG11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AH11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AI11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AJ11" t="s">
         <v>74</v>
       </c>
       <c r="AK11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AL11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="AM11" t="s">
         <v>74</v>
       </c>
       <c r="AN11" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AO11" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
@@ -2784,7 +2790,7 @@
         <v>61</v>
       </c>
       <c r="F12" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G12" t="s">
         <v>60</v>
@@ -2814,31 +2820,31 @@
         <v>64</v>
       </c>
       <c r="P12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="Q12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="R12" t="s">
         <v>68</v>
       </c>
       <c r="S12" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="T12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="U12" t="s">
         <v>64</v>
       </c>
       <c r="V12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="W12" t="s">
         <v>74</v>
       </c>
       <c r="X12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="Y12" t="s">
         <v>68</v>
@@ -2850,7 +2856,7 @@
         <v>75</v>
       </c>
       <c r="AB12" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AC12" t="s">
         <v>73</v>
@@ -2862,7 +2868,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="AG12" t="s">
         <v>75</v>
@@ -2871,25 +2877,25 @@
         <v>75</v>
       </c>
       <c r="AI12" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="AJ12" t="s">
         <v>75</v>
       </c>
       <c r="AK12" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AL12" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="AM12" t="s">
+        <v>93</v>
+      </c>
+      <c r="AN12" t="s">
         <v>94</v>
       </c>
-      <c r="AN12" t="s">
+      <c r="AO12" t="s">
         <v>95</v>
-      </c>
-      <c r="AO12" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
@@ -2903,7 +2909,7 @@
         <v>68</v>
       </c>
       <c r="D13" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E13" t="s">
         <v>68</v>
@@ -2918,10 +2924,10 @@
         <v>68</v>
       </c>
       <c r="I13" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="K13" t="s">
         <v>72</v>
@@ -2948,7 +2954,7 @@
         <v>73</v>
       </c>
       <c r="S13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="T13" t="s">
         <v>74</v>
@@ -2960,7 +2966,7 @@
         <v>60</v>
       </c>
       <c r="W13" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="X13" t="s">
         <v>74</v>
@@ -2975,37 +2981,37 @@
         <v>71</v>
       </c>
       <c r="AB13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AC13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AD13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AE13" t="s">
         <v>75</v>
       </c>
       <c r="AF13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AG13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AH13" t="s">
         <v>71</v>
       </c>
       <c r="AI13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AJ13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AK13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AL13" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="AM13" t="s">
         <v>96</v>
@@ -3019,28 +3025,28 @@
         <v>60</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D14" t="s">
         <v>64</v>
       </c>
       <c r="E14" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F14" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G14" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H14" t="s">
         <v>64</v>
       </c>
       <c r="I14" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J14" t="s">
         <v>74</v>
@@ -3052,16 +3058,16 @@
         <v>73</v>
       </c>
       <c r="M14" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N14" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="O14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P14" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="Q14" t="s">
         <v>74</v>
@@ -3070,13 +3076,13 @@
         <v>74</v>
       </c>
       <c r="S14" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="T14" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="U14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="V14" t="s">
         <v>73</v>
@@ -3085,40 +3091,40 @@
         <v>71</v>
       </c>
       <c r="X14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Z14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AA14" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="AB14" t="s">
         <v>75</v>
       </c>
       <c r="AC14" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AD14" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="AE14" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="AF14" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AG14" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="AH14" t="s">
         <v>97</v>
       </c>
       <c r="AI14" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="AJ14" t="s">
         <v>97</v>
@@ -3130,7 +3136,7 @@
         <v>96</v>
       </c>
       <c r="AM14" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
@@ -3138,13 +3144,13 @@
         <v>68</v>
       </c>
       <c r="B15" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C15" t="s">
         <v>64</v>
       </c>
       <c r="D15" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E15" t="s">
         <v>64</v>
@@ -3162,31 +3168,31 @@
         <v>75</v>
       </c>
       <c r="J15" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="K15" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="L15" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="M15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N15" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="O15" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="P15" t="s">
         <v>98</v>
       </c>
       <c r="Q15" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="R15" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="S15" t="s">
         <v>75</v>
@@ -3195,49 +3201,49 @@
         <v>75</v>
       </c>
       <c r="U15" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="V15" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="W15" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="X15" t="s">
         <v>71</v>
       </c>
       <c r="Y15" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="Z15" t="s">
         <v>71</v>
       </c>
       <c r="AA15" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AB15" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AC15" t="s">
         <v>71</v>
       </c>
       <c r="AD15" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="AE15" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="AF15" t="s">
         <v>74</v>
       </c>
       <c r="AG15" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AH15" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="AI15" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="AJ15" t="s">
         <v>70</v>
@@ -3246,18 +3252,21 @@
         <v>70</v>
       </c>
       <c r="AL15" t="s">
+        <v>85</v>
+      </c>
+      <c r="AM15" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>87</v>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>89</v>
       </c>
       <c r="B16" t="s">
         <v>64</v>
       </c>
       <c r="C16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D16" t="s">
         <v>73</v>
@@ -3266,13 +3275,13 @@
         <v>73</v>
       </c>
       <c r="F16" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G16" t="s">
         <v>74</v>
       </c>
       <c r="H16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I16" t="s">
         <v>71</v>
@@ -3281,10 +3290,10 @@
         <v>71</v>
       </c>
       <c r="K16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M16" t="s">
         <v>75</v>
@@ -3299,10 +3308,10 @@
         <v>75</v>
       </c>
       <c r="Q16" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="R16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S16" t="s">
         <v>71</v>
@@ -3314,19 +3323,19 @@
         <v>71</v>
       </c>
       <c r="V16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W16" t="s">
         <v>97</v>
       </c>
       <c r="X16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="Y16" t="s">
         <v>71</v>
       </c>
       <c r="Z16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AA16" t="s">
         <v>98</v>
@@ -3335,34 +3344,34 @@
         <v>70</v>
       </c>
       <c r="AC16" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="AD16" t="s">
         <v>60</v>
       </c>
       <c r="AE16" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="AF16" t="s">
         <v>70</v>
       </c>
       <c r="AG16" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="AH16" t="s">
         <v>70</v>
       </c>
       <c r="AI16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AJ16" t="s">
         <v>96</v>
       </c>
       <c r="AK16" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="AL16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
@@ -3370,7 +3379,7 @@
         <v>64</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C17" t="s">
         <v>74</v>
@@ -3382,10 +3391,10 @@
         <v>74</v>
       </c>
       <c r="F17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H17" t="s">
         <v>75</v>
@@ -3397,7 +3406,7 @@
         <v>97</v>
       </c>
       <c r="K17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="L17" t="s">
         <v>75</v>
@@ -3406,76 +3415,76 @@
         <v>71</v>
       </c>
       <c r="N17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="O17" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="P17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="Q17" t="s">
         <v>71</v>
       </c>
       <c r="R17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S17" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="T17" t="s">
         <v>99</v>
       </c>
       <c r="U17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="V17" t="s">
         <v>99</v>
       </c>
       <c r="W17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="X17" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="Y17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="Z17" t="s">
         <v>97</v>
       </c>
       <c r="AA17" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="AB17" t="s">
         <v>100</v>
       </c>
       <c r="AC17" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="AD17" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="AE17" t="s">
         <v>70</v>
       </c>
       <c r="AF17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="AG17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="AI17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AJ17" t="s">
         <v>58</v>
       </c>
       <c r="AK17" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
@@ -3486,10 +3495,10 @@
         <v>73</v>
       </c>
       <c r="C18" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D18" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E18" t="s">
         <v>71</v>
@@ -3504,40 +3513,40 @@
         <v>71</v>
       </c>
       <c r="I18" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J18" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="K18" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="L18" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="M18" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="N18" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="O18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q18" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="R18" t="s">
         <v>71</v>
       </c>
       <c r="S18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T18" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="U18" t="s">
         <v>70</v>
@@ -3546,19 +3555,19 @@
         <v>101</v>
       </c>
       <c r="W18" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="X18" t="s">
         <v>70</v>
       </c>
       <c r="Y18" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="Z18" t="s">
         <v>70</v>
       </c>
       <c r="AA18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB18" t="s">
         <v>96</v>
@@ -3567,10 +3576,10 @@
         <v>100</v>
       </c>
       <c r="AD18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE18" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="AF18" t="s">
         <v>58</v>
@@ -3582,13 +3591,13 @@
         <v>96</v>
       </c>
       <c r="AI18" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AJ18" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AK18" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
@@ -3599,40 +3608,40 @@
         <v>74</v>
       </c>
       <c r="C19" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D19" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E19" t="s">
         <v>97</v>
       </c>
       <c r="F19" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G19" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H19" t="s">
         <v>97</v>
       </c>
       <c r="I19" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="J19" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L19" t="s">
         <v>70</v>
       </c>
       <c r="M19" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="N19" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="O19" t="s">
         <v>100</v>
@@ -3644,16 +3653,16 @@
         <v>97</v>
       </c>
       <c r="R19" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="S19" t="s">
         <v>102</v>
       </c>
       <c r="T19" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="U19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="V19" t="s">
         <v>100</v>
@@ -3662,13 +3671,13 @@
         <v>70</v>
       </c>
       <c r="X19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Z19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AA19" t="s">
         <v>102</v>
@@ -3677,7 +3686,7 @@
         <v>58</v>
       </c>
       <c r="AC19" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="AD19" t="s">
         <v>100</v>
@@ -3686,39 +3695,39 @@
         <v>96</v>
       </c>
       <c r="AF19" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AG19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH19" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AI19" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AJ19" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C20" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D20" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E20" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F20" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="G20" t="s">
         <v>70</v>
@@ -3727,46 +3736,46 @@
         <v>73</v>
       </c>
       <c r="I20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J20" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="K20" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M20" t="s">
         <v>70</v>
       </c>
       <c r="N20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Q20" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="R20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="S20" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="T20" t="s">
         <v>96</v>
       </c>
       <c r="U20" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="V20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="W20" t="s">
         <v>100</v>
@@ -3778,42 +3787,42 @@
         <v>96</v>
       </c>
       <c r="Z20" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="AA20" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="AB20" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AC20" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AD20" t="s">
         <v>58</v>
       </c>
       <c r="AE20" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AF20" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AG20" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="AH20" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AI20" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B21" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C21" t="s">
         <v>98</v>
@@ -3822,7 +3831,7 @@
         <v>98</v>
       </c>
       <c r="E21" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="F21" t="s">
         <v>68</v>
@@ -3831,13 +3840,13 @@
         <v>100</v>
       </c>
       <c r="H21" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="I21" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="J21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K21" t="s">
         <v>96</v>
@@ -3846,7 +3855,7 @@
         <v>100</v>
       </c>
       <c r="M21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N21" t="s">
         <v>100</v>
@@ -3855,13 +3864,13 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="Q21" t="s">
         <v>70</v>
       </c>
       <c r="R21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="S21" t="s">
         <v>96</v>
@@ -3876,37 +3885,37 @@
         <v>96</v>
       </c>
       <c r="W21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="X21" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Y21" t="s">
         <v>58</v>
       </c>
       <c r="Z21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AA21" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AB21" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AC21" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AD21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AE21" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AF21" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AG21" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
@@ -3914,7 +3923,7 @@
         <v>75</v>
       </c>
       <c r="B22" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
         <v>71</v>
@@ -3929,16 +3938,16 @@
         <v>70</v>
       </c>
       <c r="G22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H22" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I22" t="s">
         <v>70</v>
       </c>
       <c r="J22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K22" t="s">
         <v>58</v>
@@ -3947,10 +3956,10 @@
         <v>96</v>
       </c>
       <c r="M22" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="N22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O22" t="s">
         <v>58</v>
@@ -3959,19 +3968,19 @@
         <v>96</v>
       </c>
       <c r="Q22" t="s">
+        <v>93</v>
+      </c>
+      <c r="R22" t="s">
         <v>94</v>
-      </c>
-      <c r="R22" t="s">
-        <v>95</v>
       </c>
       <c r="S22" t="s">
         <v>58</v>
       </c>
       <c r="T22" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="U22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="V22" t="s">
         <v>58</v>
@@ -3980,54 +3989,54 @@
         <v>96</v>
       </c>
       <c r="X22" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="Y22" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="Z22" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AA22" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AG22" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B23" t="s">
         <v>75</v>
       </c>
       <c r="C23" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D23" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G23" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J23" t="s">
         <v>96</v>
       </c>
       <c r="K23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L23" t="s">
         <v>58</v>
@@ -4039,7 +4048,7 @@
         <v>96</v>
       </c>
       <c r="O23" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="P23" t="s">
         <v>58</v>
@@ -4048,28 +4057,28 @@
         <v>102</v>
       </c>
       <c r="R23" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="S23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="U23" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="V23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="W23" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="Y23" t="s">
         <v>75</v>
       </c>
       <c r="AA23" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
@@ -4080,7 +4089,7 @@
         <v>71</v>
       </c>
       <c r="C24" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="D24" t="s">
         <v>99</v>
@@ -4089,7 +4098,7 @@
         <v>102</v>
       </c>
       <c r="F24" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G24" t="s">
         <v>58</v>
@@ -4101,42 +4110,48 @@
         <v>96</v>
       </c>
       <c r="J24" t="s">
+        <v>94</v>
+      </c>
+      <c r="K24" t="s">
+        <v>90</v>
+      </c>
+      <c r="L24" t="s">
+        <v>94</v>
+      </c>
+      <c r="M24" t="s">
+        <v>94</v>
+      </c>
+      <c r="N24" t="s">
+        <v>94</v>
+      </c>
+      <c r="O24" t="s">
+        <v>90</v>
+      </c>
+      <c r="P24" t="s">
+        <v>94</v>
+      </c>
+      <c r="T24" t="s">
+        <v>92</v>
+      </c>
+      <c r="V24" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA24" t="s">
         <v>95</v>
-      </c>
-      <c r="K24" t="s">
-        <v>92</v>
-      </c>
-      <c r="L24" t="s">
-        <v>95</v>
-      </c>
-      <c r="M24" t="s">
-        <v>95</v>
-      </c>
-      <c r="N24" t="s">
-        <v>95</v>
-      </c>
-      <c r="O24" t="s">
-        <v>92</v>
-      </c>
-      <c r="P24" t="s">
-        <v>95</v>
-      </c>
-      <c r="AA24" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C25" t="s">
+        <v>95</v>
+      </c>
+      <c r="D25" t="s">
         <v>63</v>
-      </c>
-      <c r="D25" t="s">
-        <v>79</v>
       </c>
       <c r="E25" t="s">
         <v>96</v>
@@ -4145,16 +4160,16 @@
         <v>58</v>
       </c>
       <c r="G25" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H25" t="s">
         <v>58</v>
       </c>
       <c r="I25" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J25" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4162,71 +4177,80 @@
         <v>99</v>
       </c>
       <c r="B26" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s">
         <v>101</v>
       </c>
       <c r="D26" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="E26" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F26" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G26" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H26" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I26" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="B27" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="C27" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D27" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="E27" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F27" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H27" t="s">
         <v>70</v>
       </c>
+      <c r="I27" t="s">
+        <v>103</v>
+      </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="B28" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="C28" t="s">
         <v>102</v>
       </c>
       <c r="D28" t="s">
-        <v>78</v>
+        <v>77</v>
+      </c>
+      <c r="E28" t="s">
+        <v>63</v>
       </c>
       <c r="F28" t="s">
-        <v>77</v>
+        <v>76</v>
+      </c>
+      <c r="H28" t="s">
+        <v>92</v>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>101</v>
       </c>
@@ -4237,18 +4261,21 @@
         <v>100</v>
       </c>
       <c r="D29" t="s">
-        <v>84</v>
+        <v>82</v>
+      </c>
+      <c r="E29" t="s">
+        <v>103</v>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>102</v>
       </c>
       <c r="B30" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C30" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D30" t="s">
         <v>58</v>
@@ -4262,38 +4289,38 @@
         <v>102</v>
       </c>
       <c r="C31" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D31" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B32" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C32" t="s">
         <v>96</v>
       </c>
       <c r="D32" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B33" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C33" t="s">
         <v>58</v>
       </c>
       <c r="D33" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -4304,10 +4331,10 @@
         <v>96</v>
       </c>
       <c r="C34" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D34" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -4318,43 +4345,58 @@
         <v>58</v>
       </c>
       <c r="C35" t="s">
+        <v>94</v>
+      </c>
+      <c r="D35" t="s">
         <v>95</v>
-      </c>
-      <c r="D35" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B36" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C36" t="s">
-        <v>92</v>
+        <v>90</v>
+      </c>
+      <c r="D36" t="s">
+        <v>103</v>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B37" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>90</v>
+      </c>
+      <c r="B38" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>92</v>
       </c>
-      <c r="B38" t="s">
-        <v>92</v>
-      </c>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25"/>
-    <row r="40" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25"/>
     <row r="43" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="44" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="45" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4455,7 +4497,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:BA42"/>
+  <dimension ref="A3:BB42"/>
   <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="17.85546875" customWidth="1"/>
@@ -4488,7 +4530,7 @@
     <col min="98" max="98" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>49</v>
       </c>
@@ -4535,7 +4577,7 @@
         <v>72</v>
       </c>
       <c r="P3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="Q3" t="s">
         <v>61</v>
@@ -4544,28 +4586,28 @@
         <v>69</v>
       </c>
       <c r="S3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="T3" t="s">
         <v>60</v>
       </c>
       <c r="U3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="V3" t="s">
         <v>68</v>
       </c>
       <c r="W3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="X3" t="s">
         <v>64</v>
       </c>
       <c r="Y3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="Z3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="AA3" t="s">
         <v>73</v>
@@ -4574,16 +4616,16 @@
         <v>74</v>
       </c>
       <c r="AC3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="AD3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AE3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AF3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AG3" t="s">
         <v>98</v>
@@ -4595,22 +4637,22 @@
         <v>71</v>
       </c>
       <c r="AJ3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AK3" t="s">
         <v>97</v>
       </c>
       <c r="AL3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="AM3" t="s">
         <v>99</v>
       </c>
       <c r="AN3" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="AO3" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="AP3" t="s">
         <v>101</v>
@@ -4619,7 +4661,7 @@
         <v>70</v>
       </c>
       <c r="AR3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AS3" t="s">
         <v>102</v>
@@ -4628,10 +4670,10 @@
         <v>100</v>
       </c>
       <c r="AU3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AV3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="AW3" t="s">
         <v>96</v>
@@ -4640,16 +4682,19 @@
         <v>58</v>
       </c>
       <c r="AY3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AZ3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="BA3" t="s">
-        <v>92</v>
+        <v>90</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>103</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -4672,7 +4717,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I4" t="s">
         <v>1</v>
@@ -4690,7 +4735,7 @@
         <v>11</v>
       </c>
       <c r="N4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O4" t="s">
         <v>13</v>
@@ -4711,7 +4756,7 @@
         <v>2</v>
       </c>
       <c r="U4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V4" t="s">
         <v>11</v>
@@ -4809,8 +4854,11 @@
       <c r="BA4" t="s">
         <v>9</v>
       </c>
+      <c r="BB4" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -4970,8 +5018,11 @@
       <c r="BA5" t="s">
         <v>1</v>
       </c>
+      <c r="BB5" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -5131,8 +5182,11 @@
       <c r="BA6" t="s">
         <v>22</v>
       </c>
+      <c r="BB6" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -5292,8 +5346,11 @@
       <c r="BA7" t="s">
         <v>26</v>
       </c>
+      <c r="BB7" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -5385,7 +5442,7 @@
         <v>28</v>
       </c>
       <c r="AN8" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AO8" t="s">
         <v>28</v>
@@ -5516,7 +5573,7 @@
         <v>9</v>
       </c>
       <c r="AN9" t="s">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="AO9" t="s">
         <v>24</v>
@@ -5647,7 +5704,7 @@
         <v>10</v>
       </c>
       <c r="AN10" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="AO10" t="s">
         <v>19</v>
@@ -5778,7 +5835,7 @@
         <v>29</v>
       </c>
       <c r="AN11" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="AO11" t="s">
         <v>17</v>
@@ -5852,7 +5909,7 @@
         <v>23</v>
       </c>
       <c r="T12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V12" t="s">
         <v>0</v>
@@ -5897,7 +5954,7 @@
         <v>18</v>
       </c>
       <c r="AN12" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AO12" t="s">
         <v>34</v>
@@ -6013,7 +6070,7 @@
         <v>0</v>
       </c>
       <c r="AN13" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="AO13" t="s">
         <v>9</v>
@@ -6129,10 +6186,10 @@
         <v>8</v>
       </c>
       <c r="AN14" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AO14" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="AQ14" t="s">
         <v>12</v>
@@ -6245,10 +6302,10 @@
         <v>4</v>
       </c>
       <c r="AN15" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="AO15" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="AQ15" t="s">
         <v>25</v>
@@ -6313,7 +6370,7 @@
         <v>34</v>
       </c>
       <c r="R16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T16" t="s">
         <v>18</v>
@@ -6352,7 +6409,7 @@
         <v>5</v>
       </c>
       <c r="AN16" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="s">
         <v>2</v>
@@ -6456,7 +6513,7 @@
         <v>23</v>
       </c>
       <c r="AN17" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AO17" t="s">
         <v>0</v>
@@ -6560,7 +6617,7 @@
         <v>22</v>
       </c>
       <c r="AN18" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="AO18" t="s">
         <v>30</v>
@@ -6664,7 +6721,7 @@
         <v>16</v>
       </c>
       <c r="AN19" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AO19" t="s">
         <v>4</v>
@@ -6782,7 +6839,7 @@
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C21" t="s">
         <v>7</v>
@@ -7253,7 +7310,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="35:53" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="15" customHeight="1" spans="36:53" x14ac:dyDescent="0.25"/>
     <row r="29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -7275,7 +7332,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:BA1898"/>
+  <dimension ref="A3:BB1898"/>
   <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="55.28515625" customWidth="1"/>
@@ -7359,7 +7416,7 @@
     <col min="99" max="99" width="47.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>49</v>
       </c>
@@ -7406,7 +7463,7 @@
         <v>72</v>
       </c>
       <c r="P3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="Q3" t="s">
         <v>61</v>
@@ -7415,28 +7472,28 @@
         <v>69</v>
       </c>
       <c r="S3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="T3" t="s">
         <v>60</v>
       </c>
       <c r="U3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="V3" t="s">
         <v>68</v>
       </c>
       <c r="W3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="X3" t="s">
         <v>64</v>
       </c>
       <c r="Y3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="Z3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="AA3" t="s">
         <v>73</v>
@@ -7445,16 +7502,16 @@
         <v>74</v>
       </c>
       <c r="AC3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="AD3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AE3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AF3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AG3" t="s">
         <v>98</v>
@@ -7466,22 +7523,22 @@
         <v>71</v>
       </c>
       <c r="AJ3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AK3" t="s">
         <v>97</v>
       </c>
       <c r="AL3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="AM3" t="s">
         <v>99</v>
       </c>
       <c r="AN3" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="AO3" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="AP3" t="s">
         <v>101</v>
@@ -7490,7 +7547,7 @@
         <v>70</v>
       </c>
       <c r="AR3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AS3" t="s">
         <v>102</v>
@@ -7499,10 +7556,10 @@
         <v>100</v>
       </c>
       <c r="AU3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AV3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="AW3" t="s">
         <v>96</v>
@@ -7511,672 +7568,681 @@
         <v>58</v>
       </c>
       <c r="AY3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AZ3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="BA3" t="s">
-        <v>92</v>
+        <v>90</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>103</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="R4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="S4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="T4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="U4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="V4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="W4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="X4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Y4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Z4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AA4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AB4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AC4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AD4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AE4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AF4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AH4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AI4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AJ4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AK4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AL4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AM4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AN4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AO4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AP4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AQ4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AR4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AS4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AT4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AU4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AV4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AW4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AX4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AY4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AZ4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="BA4" t="s">
-        <v>156</v>
+        <v>157</v>
+      </c>
+      <c r="BB4" t="s">
+        <v>158</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="K5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="L5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="M5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="O5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="R5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="T5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="V5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="W5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="X5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Y5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Z5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AA5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AB5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AC5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AD5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AE5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="AF5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AH5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AI5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AJ5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AK5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="AL5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AN5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AO5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AQ5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AR5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AS5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AT5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AU5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AV5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AW5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AX5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AY5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AZ5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="BA5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="R6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="T6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="V6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="W6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="X6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Z6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AA6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AB6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AE6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AF6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AH6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AI6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AJ6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AK6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AL6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AN6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AO6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AQ6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AR6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AT6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AU6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AV6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AW6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AX6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AY6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AZ6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="BA6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="R7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="T7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="V7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="X7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Z7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AA7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AB7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AD7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AE7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AF7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AH7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AI7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AJ7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AN7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AO7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AQ7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AR7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AU7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AV7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AW7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AX7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AY7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AZ7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="BA7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E8" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="R8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="T8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X8" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AA8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AB8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AE8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AF8" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AH8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AI8" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AJ8" t="s">
-        <v>288</v>
+        <v>289</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>290</v>
       </c>
       <c r="AO8" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AQ8" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AR8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AU8" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AV8" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AW8" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AX8" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AY8" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AZ8" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="BA8" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F9" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="H9" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="O9" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="T9" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="X9" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AB9" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AF9" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AI9" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AJ9" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AO9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AV9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AW9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AX9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AY9" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AZ9" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="BA9" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="35:53" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="36:53" x14ac:dyDescent="0.25">
       <c r="AO10" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" spans="41:41" x14ac:dyDescent="0.25"/>

--- a/data/ICEHLdelegacije.xlsx
+++ b/data/ICEHLdelegacije.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2107" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2108" uniqueCount="320">
   <si>
     <t>PiragicTr</t>
   </si>
@@ -492,7 +492,7 @@
     <t>Eishalle Wien-Kagran;SiegelSt;SmetanaLa;Gatol-schafranekMa;JedlickaPe</t>
   </si>
   <si>
-    <t>Stadthalle Villach;PiragicTr;SternatCh;HribarMa;ZgoncGa</t>
+    <t>Stadthalle Villach;PiragicTr;SeewaldEl;HribarMa;ZgoncGa</t>
   </si>
   <si>
     <t>Tiroler Wasserkraft Arena;NikolicMa;SeewaldEl;FleischmannLu;NotheggerDa</t>
@@ -4171,8 +4171,11 @@
       <c r="J25" t="s">
         <v>90</v>
       </c>
+      <c r="L25" t="s">
+        <v>103</v>
+      </c>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>99</v>
       </c>
@@ -4362,7 +4365,7 @@
         <v>90</v>
       </c>
       <c r="D36" t="s">
-        <v>103</v>
+        <v>63</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -5019,7 +5022,7 @@
         <v>1</v>
       </c>
       <c r="BB5" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
@@ -7310,7 +7313,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="36:53" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="15" customHeight="1" spans="41:53" x14ac:dyDescent="0.25"/>
     <row r="29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -8240,7 +8243,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="36:53" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="41:53" x14ac:dyDescent="0.25">
       <c r="AO10" t="s">
         <v>319</v>
       </c>

--- a/data/ICEHLdelegacije.xlsx
+++ b/data/ICEHLdelegacije.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2108" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2112" uniqueCount="321">
   <si>
     <t>PiragicTr</t>
   </si>
@@ -165,6 +165,9 @@
     <t>HlavatyAl</t>
   </si>
   <si>
+    <t>HeadSc</t>
+  </si>
+  <si>
     <t>2024-09-20</t>
   </si>
   <si>
@@ -195,6 +198,9 @@
     <t>2024-12-26</t>
   </si>
   <si>
+    <t>2024-12-22</t>
+  </si>
+  <si>
     <t>2024-10-01</t>
   </si>
   <si>
@@ -306,9 +312,6 @@
     <t>2024-12-06</t>
   </si>
   <si>
-    <t>2024-12-22</t>
-  </si>
-  <si>
     <t>2024-11-30</t>
   </si>
   <si>
@@ -477,7 +480,7 @@
     <t>Merkur Eisstadion Graz;SmetanaLa;SternatCh;JedlickaPe;KoncDa</t>
   </si>
   <si>
-    <t>Eishalle Asiago;Huber aAn;OfnerCh;MantovaniDa;WeissAl</t>
+    <t>Eishalle Asiago;HeadSc;OfnerCh;MantovaniDa;WeissAl</t>
   </si>
   <si>
     <t>Linz AG Eisarena;HlavatyAl;SmetanaLa;BärnthalerCh;ZacherlPa</t>
@@ -810,7 +813,7 @@
     <t>Linz AG Eisarena;NikolicKr;SiegelSt;Gatol-schafranekMa;MoidlMa</t>
   </si>
   <si>
-    <t>Gabor Ocskay Eisarena;RezekGr;SoosDa;MuzsikNo;VacziDa</t>
+    <t>Gabor Ocskay Eisarena;NagyAt;RezekGr;MuzsikNo;VacziDa</t>
   </si>
   <si>
     <t>Stadthalle Villach;SmetanaLa;ZrnicMi;BärnthalerCh;RieckenSi</t>
@@ -834,7 +837,7 @@
     <t>Eisarena Salzburg;HronskyTo;SternatCh;JedlickaPe;SeewaldJe</t>
   </si>
   <si>
-    <t>Tiroler Wasserkraft Arena;NikolicKr;NikolicMa;MartinFl;SparerDa</t>
+    <t>Tiroler Wasserkraft Arena;NikolicMa;NikolicKr;MartinFl;SparerDa</t>
   </si>
   <si>
     <t>Eishalle Bruneck;BernekerTh;HuberAn;MartinFl;PardatscherUl</t>
@@ -894,7 +897,7 @@
     <t>Eishalle Feldkirch;OfnerCh;PiragicTr;NotheggerDa;ZgoncGa</t>
   </si>
   <si>
-    <t>Merkur Eisstadion Graz;GroznikBo;NagyAt;HribarMa;RieckenSi</t>
+    <t>Merkur Eisstadion Graz;GroznikBo;SoosDa;HribarMa;RieckenSi</t>
   </si>
   <si>
     <t>Hala Tivoli;GroznikBo;RezekGr;HribarMa;ZgoncGa</t>
@@ -903,7 +906,7 @@
     <t>Eishalle Asiago;OfnerCh;PiragicTr;PuffWo;RigoniDa</t>
   </si>
   <si>
-    <t>Eishalle Feldkirch;Huber aAn;NikolicMa;PardatscherUl;SeewaldJe</t>
+    <t>Eishalle Feldkirch;NikolicMa;SeewaldEl;PardatscherUl;SeewaldJe</t>
   </si>
   <si>
     <t>Heidi Horten Arena Klagenfurt;FichtnerPa;HronskyTo;Gatol-schafranekMa;KoncDa</t>
@@ -966,10 +969,10 @@
     <t>Sparkasse Arena Bozen;OfnerCh;ZrnicMi;MantovaniDa;PardatscherUl</t>
   </si>
   <si>
-    <t>Eishalle Asiago;NikolicMa;NikolicKr;MantovaniDa;RigoniDa</t>
-  </si>
-  <si>
-    <t>Sparkasse Arena Bozen;OfnerCh;SeewaldEl;MantovaniDa;PardatscherUl</t>
+    <t>Eishalle Asiago;NikolicKr;NikolicMa;MantovaniDa;RigoniDa</t>
+  </si>
+  <si>
+    <t>Sparkasse Arena Bozen;Huber aAn;OfnerCh;MantovaniDa;PardatscherUl</t>
   </si>
   <si>
     <t>Eishalle Bruneck;RezekGr;SternatCh;RigoniDa;ZgoncGa</t>
@@ -1293,7 +1296,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:AX134"/>
+  <dimension ref="A2:AY134"/>
   <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.28515625" customWidth="1"/>
@@ -1540,7 +1543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -1688,2715 +1691,2727 @@
       <c r="AW3" t="s">
         <v>48</v>
       </c>
+      <c r="AX3" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J4" t="s">
+        <v>51</v>
+      </c>
+      <c r="K4" t="s">
+        <v>52</v>
+      </c>
+      <c r="L4" t="s">
         <v>50</v>
       </c>
-      <c r="K4" t="s">
+      <c r="M4" t="s">
+        <v>50</v>
+      </c>
+      <c r="N4" t="s">
+        <v>52</v>
+      </c>
+      <c r="O4" t="s">
+        <v>53</v>
+      </c>
+      <c r="P4" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>52</v>
+      </c>
+      <c r="R4" t="s">
+        <v>50</v>
+      </c>
+      <c r="S4" t="s">
+        <v>50</v>
+      </c>
+      <c r="T4" t="s">
+        <v>52</v>
+      </c>
+      <c r="U4" t="s">
+        <v>54</v>
+      </c>
+      <c r="V4" t="s">
+        <v>50</v>
+      </c>
+      <c r="W4" t="s">
+        <v>52</v>
+      </c>
+      <c r="X4" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>53</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>58</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H5" t="s">
+        <v>52</v>
+      </c>
+      <c r="I5" t="s">
+        <v>53</v>
+      </c>
+      <c r="J5" t="s">
+        <v>56</v>
+      </c>
+      <c r="K5" t="s">
         <v>51</v>
       </c>
-      <c r="L4" t="s">
-        <v>49</v>
-      </c>
-      <c r="M4" t="s">
-        <v>49</v>
-      </c>
-      <c r="N4" t="s">
+      <c r="L5" t="s">
+        <v>53</v>
+      </c>
+      <c r="M5" t="s">
+        <v>53</v>
+      </c>
+      <c r="N5" t="s">
         <v>51</v>
       </c>
-      <c r="O4" t="s">
+      <c r="O5" t="s">
+        <v>56</v>
+      </c>
+      <c r="P5" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>55</v>
+      </c>
+      <c r="R5" t="s">
         <v>52</v>
       </c>
-      <c r="P4" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q4" t="s">
+      <c r="S5" t="s">
+        <v>53</v>
+      </c>
+      <c r="T5" t="s">
+        <v>53</v>
+      </c>
+      <c r="U5" t="s">
+        <v>61</v>
+      </c>
+      <c r="V5" t="s">
+        <v>54</v>
+      </c>
+      <c r="W5" t="s">
+        <v>53</v>
+      </c>
+      <c r="X5" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>53</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>53</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>55</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>53</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AL5" t="s">
         <v>51</v>
       </c>
-      <c r="R4" t="s">
-        <v>49</v>
-      </c>
-      <c r="S4" t="s">
-        <v>49</v>
-      </c>
-      <c r="T4" t="s">
-        <v>51</v>
-      </c>
-      <c r="U4" t="s">
-        <v>53</v>
-      </c>
-      <c r="V4" t="s">
-        <v>49</v>
-      </c>
-      <c r="W4" t="s">
-        <v>51</v>
-      </c>
-      <c r="X4" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>49</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>49</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>49</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>49</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>49</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>54</v>
-      </c>
-      <c r="AN4" t="s">
+      <c r="AM5" t="s">
+        <v>57</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>62</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>58</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>63</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AR5" t="s">
         <v>55</v>
       </c>
-      <c r="AO4" t="s">
-        <v>55</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>56</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AS4" t="s">
-        <v>49</v>
-      </c>
-      <c r="AT4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AU4" t="s">
-        <v>49</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>54</v>
-      </c>
-      <c r="AW4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G5" t="s">
-        <v>52</v>
-      </c>
-      <c r="H5" t="s">
-        <v>51</v>
-      </c>
-      <c r="I5" t="s">
-        <v>52</v>
-      </c>
-      <c r="J5" t="s">
-        <v>55</v>
-      </c>
-      <c r="K5" t="s">
-        <v>50</v>
-      </c>
-      <c r="L5" t="s">
-        <v>52</v>
-      </c>
-      <c r="M5" t="s">
-        <v>52</v>
-      </c>
-      <c r="N5" t="s">
-        <v>50</v>
-      </c>
-      <c r="O5" t="s">
-        <v>55</v>
-      </c>
-      <c r="P5" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>54</v>
-      </c>
-      <c r="R5" t="s">
-        <v>51</v>
-      </c>
-      <c r="S5" t="s">
-        <v>52</v>
-      </c>
-      <c r="T5" t="s">
-        <v>52</v>
-      </c>
-      <c r="U5" t="s">
-        <v>59</v>
-      </c>
-      <c r="V5" t="s">
-        <v>53</v>
-      </c>
-      <c r="W5" t="s">
-        <v>52</v>
-      </c>
-      <c r="X5" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>52</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>55</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>55</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>55</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>59</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>52</v>
-      </c>
-      <c r="AH5" t="s">
-        <v>54</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>52</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>59</v>
-      </c>
-      <c r="AK5" t="s">
-        <v>55</v>
-      </c>
-      <c r="AL5" t="s">
-        <v>50</v>
-      </c>
-      <c r="AM5" t="s">
-        <v>56</v>
-      </c>
-      <c r="AN5" t="s">
-        <v>60</v>
-      </c>
-      <c r="AO5" t="s">
-        <v>57</v>
-      </c>
-      <c r="AP5" t="s">
-        <v>61</v>
-      </c>
-      <c r="AQ5" t="s">
-        <v>62</v>
-      </c>
-      <c r="AR5" t="s">
-        <v>54</v>
-      </c>
       <c r="AS5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="AT5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H6" t="s">
+        <v>56</v>
+      </c>
+      <c r="I6" t="s">
+        <v>56</v>
+      </c>
+      <c r="J6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K6" t="s">
+        <v>56</v>
+      </c>
+      <c r="L6" t="s">
+        <v>56</v>
+      </c>
+      <c r="M6" t="s">
+        <v>56</v>
+      </c>
+      <c r="N6" t="s">
+        <v>56</v>
+      </c>
+      <c r="O6" t="s">
+        <v>64</v>
+      </c>
+      <c r="P6" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>67</v>
+      </c>
+      <c r="R6" t="s">
         <v>55</v>
       </c>
-      <c r="B6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="S6" t="s">
         <v>55</v>
       </c>
-      <c r="F6" t="s">
-        <v>52</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="T6" t="s">
+        <v>56</v>
+      </c>
+      <c r="U6" t="s">
         <v>55</v>
       </c>
-      <c r="H6" t="s">
+      <c r="V6" t="s">
+        <v>53</v>
+      </c>
+      <c r="W6" t="s">
         <v>55</v>
       </c>
-      <c r="I6" t="s">
+      <c r="X6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y6" t="s">
         <v>55</v>
       </c>
-      <c r="J6" t="s">
+      <c r="Z6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>68</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>68</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>69</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AO6" t="s">
         <v>62</v>
       </c>
-      <c r="K6" t="s">
-        <v>55</v>
-      </c>
-      <c r="L6" t="s">
-        <v>55</v>
-      </c>
-      <c r="M6" t="s">
-        <v>55</v>
-      </c>
-      <c r="N6" t="s">
-        <v>55</v>
-      </c>
-      <c r="O6" t="s">
-        <v>62</v>
-      </c>
-      <c r="P6" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>65</v>
-      </c>
-      <c r="R6" t="s">
-        <v>54</v>
-      </c>
-      <c r="S6" t="s">
-        <v>54</v>
-      </c>
-      <c r="T6" t="s">
-        <v>55</v>
-      </c>
-      <c r="U6" t="s">
-        <v>54</v>
-      </c>
-      <c r="V6" t="s">
-        <v>52</v>
-      </c>
-      <c r="W6" t="s">
-        <v>54</v>
-      </c>
-      <c r="X6" t="s">
-        <v>59</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>54</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>54</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>59</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>54</v>
-      </c>
-      <c r="AD6" t="s">
+      <c r="AP6" t="s">
+        <v>71</v>
+      </c>
+      <c r="AQ6" t="s">
         <v>66</v>
       </c>
-      <c r="AE6" t="s">
-        <v>66</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>56</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>54</v>
-      </c>
-      <c r="AH6" t="s">
-        <v>67</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>54</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>62</v>
-      </c>
-      <c r="AK6" t="s">
-        <v>54</v>
-      </c>
-      <c r="AL6" t="s">
-        <v>55</v>
-      </c>
-      <c r="AM6" t="s">
-        <v>61</v>
-      </c>
-      <c r="AN6" t="s">
-        <v>68</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>60</v>
-      </c>
-      <c r="AP6" t="s">
-        <v>69</v>
-      </c>
-      <c r="AQ6" t="s">
-        <v>64</v>
-      </c>
       <c r="AR6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AS6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="AT6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F7" t="s">
+        <v>64</v>
+      </c>
+      <c r="G7" t="s">
+        <v>61</v>
+      </c>
+      <c r="H7" t="s">
+        <v>64</v>
+      </c>
+      <c r="I7" t="s">
+        <v>64</v>
+      </c>
+      <c r="J7" t="s">
+        <v>68</v>
+      </c>
+      <c r="K7" t="s">
+        <v>64</v>
+      </c>
+      <c r="L7" t="s">
         <v>55</v>
       </c>
-      <c r="C7" t="s">
+      <c r="M7" t="s">
         <v>55</v>
       </c>
-      <c r="D7" t="s">
+      <c r="N7" t="s">
         <v>55</v>
       </c>
-      <c r="E7" t="s">
-        <v>59</v>
-      </c>
-      <c r="F7" t="s">
-        <v>62</v>
-      </c>
-      <c r="G7" t="s">
-        <v>59</v>
-      </c>
-      <c r="H7" t="s">
-        <v>62</v>
-      </c>
-      <c r="I7" t="s">
-        <v>62</v>
-      </c>
-      <c r="J7" t="s">
-        <v>66</v>
-      </c>
-      <c r="K7" t="s">
-        <v>62</v>
-      </c>
-      <c r="L7" t="s">
-        <v>54</v>
-      </c>
-      <c r="M7" t="s">
-        <v>54</v>
-      </c>
-      <c r="N7" t="s">
-        <v>54</v>
-      </c>
       <c r="O7" t="s">
+        <v>57</v>
+      </c>
+      <c r="P7" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>58</v>
+      </c>
+      <c r="R7" t="s">
+        <v>57</v>
+      </c>
+      <c r="S7" t="s">
+        <v>64</v>
+      </c>
+      <c r="T7" t="s">
+        <v>68</v>
+      </c>
+      <c r="U7" t="s">
+        <v>67</v>
+      </c>
+      <c r="V7" t="s">
         <v>56</v>
       </c>
-      <c r="P7" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q7" t="s">
+      <c r="W7" t="s">
+        <v>68</v>
+      </c>
+      <c r="X7" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>68</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>71</v>
+      </c>
+      <c r="AI7" t="s">
         <v>57</v>
       </c>
-      <c r="R7" t="s">
-        <v>56</v>
-      </c>
-      <c r="S7" t="s">
-        <v>62</v>
-      </c>
-      <c r="T7" t="s">
-        <v>66</v>
-      </c>
-      <c r="U7" t="s">
+      <c r="AJ7" t="s">
+        <v>57</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>58</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>58</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>71</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>75</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>76</v>
+      </c>
+      <c r="AP7" t="s">
+        <v>77</v>
+      </c>
+      <c r="AQ7" t="s">
         <v>65</v>
       </c>
-      <c r="V7" t="s">
-        <v>55</v>
-      </c>
-      <c r="W7" t="s">
-        <v>66</v>
-      </c>
-      <c r="X7" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>62</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>66</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>62</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>61</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>62</v>
-      </c>
-      <c r="AH7" t="s">
-        <v>69</v>
-      </c>
-      <c r="AI7" t="s">
-        <v>56</v>
-      </c>
-      <c r="AJ7" t="s">
-        <v>56</v>
-      </c>
-      <c r="AK7" t="s">
-        <v>57</v>
-      </c>
-      <c r="AL7" t="s">
-        <v>57</v>
-      </c>
-      <c r="AM7" t="s">
-        <v>69</v>
-      </c>
-      <c r="AN7" t="s">
-        <v>73</v>
-      </c>
-      <c r="AO7" t="s">
-        <v>74</v>
-      </c>
-      <c r="AP7" t="s">
-        <v>75</v>
-      </c>
-      <c r="AQ7" t="s">
-        <v>63</v>
-      </c>
       <c r="AR7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AS7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AT7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I8" t="s">
+        <v>74</v>
+      </c>
+      <c r="J8" t="s">
+        <v>57</v>
+      </c>
+      <c r="K8" t="s">
+        <v>69</v>
+      </c>
+      <c r="L8" t="s">
+        <v>57</v>
+      </c>
+      <c r="M8" t="s">
+        <v>57</v>
+      </c>
+      <c r="N8" t="s">
+        <v>68</v>
+      </c>
+      <c r="O8" t="s">
+        <v>80</v>
+      </c>
+      <c r="P8" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>57</v>
+      </c>
+      <c r="R8" t="s">
+        <v>53</v>
+      </c>
+      <c r="S8" t="s">
+        <v>68</v>
+      </c>
+      <c r="T8" t="s">
+        <v>57</v>
+      </c>
+      <c r="U8" t="s">
+        <v>64</v>
+      </c>
+      <c r="V8" t="s">
+        <v>68</v>
+      </c>
+      <c r="W8" t="s">
+        <v>69</v>
+      </c>
+      <c r="X8" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>71</v>
+      </c>
+      <c r="AA8" t="s">
         <v>62</v>
       </c>
-      <c r="D8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G8" t="s">
-        <v>56</v>
-      </c>
-      <c r="H8" t="s">
+      <c r="AB8" t="s">
+        <v>68</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>57</v>
+      </c>
+      <c r="AD8" t="s">
         <v>66</v>
       </c>
-      <c r="I8" t="s">
-        <v>72</v>
-      </c>
-      <c r="J8" t="s">
-        <v>56</v>
-      </c>
-      <c r="K8" t="s">
-        <v>67</v>
-      </c>
-      <c r="L8" t="s">
-        <v>56</v>
-      </c>
-      <c r="M8" t="s">
-        <v>56</v>
-      </c>
-      <c r="N8" t="s">
-        <v>66</v>
-      </c>
-      <c r="O8" t="s">
-        <v>78</v>
-      </c>
-      <c r="P8" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>56</v>
-      </c>
-      <c r="R8" t="s">
-        <v>52</v>
-      </c>
-      <c r="S8" t="s">
-        <v>66</v>
-      </c>
-      <c r="T8" t="s">
-        <v>56</v>
-      </c>
-      <c r="U8" t="s">
+      <c r="AE8" t="s">
+        <v>81</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>71</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>68</v>
+      </c>
+      <c r="AH8" t="s">
         <v>62</v>
       </c>
-      <c r="V8" t="s">
-        <v>66</v>
-      </c>
-      <c r="W8" t="s">
-        <v>67</v>
-      </c>
-      <c r="X8" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z8" t="s">
+      <c r="AI8" t="s">
         <v>69</v>
       </c>
-      <c r="AA8" t="s">
-        <v>60</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>66</v>
-      </c>
-      <c r="AC8" t="s">
-        <v>56</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>69</v>
-      </c>
-      <c r="AG8" t="s">
-        <v>66</v>
-      </c>
-      <c r="AH8" t="s">
-        <v>60</v>
-      </c>
-      <c r="AI8" t="s">
-        <v>67</v>
-      </c>
       <c r="AJ8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="AK8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AL8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AM8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AN8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AO8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="AP8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AQ8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AR8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AS8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F9" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I9" t="s">
+        <v>63</v>
+      </c>
+      <c r="J9" t="s">
+        <v>74</v>
+      </c>
+      <c r="K9" t="s">
+        <v>80</v>
+      </c>
+      <c r="L9" t="s">
+        <v>74</v>
+      </c>
+      <c r="M9" t="s">
+        <v>63</v>
+      </c>
+      <c r="N9" t="s">
+        <v>74</v>
+      </c>
+      <c r="O9" t="s">
+        <v>63</v>
+      </c>
+      <c r="P9" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>71</v>
+      </c>
+      <c r="R9" t="s">
+        <v>74</v>
+      </c>
+      <c r="S9" t="s">
+        <v>74</v>
+      </c>
+      <c r="T9" t="s">
+        <v>63</v>
+      </c>
+      <c r="U9" t="s">
+        <v>74</v>
+      </c>
+      <c r="V9" t="s">
+        <v>63</v>
+      </c>
+      <c r="W9" t="s">
+        <v>74</v>
+      </c>
+      <c r="X9" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>85</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE9" t="s">
         <v>66</v>
       </c>
-      <c r="B9" t="s">
+      <c r="AF9" t="s">
+        <v>70</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>74</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>81</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>74</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>86</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>78</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>84</v>
+      </c>
+      <c r="AO9" t="s">
         <v>65</v>
       </c>
-      <c r="C9" t="s">
-        <v>57</v>
-      </c>
-      <c r="D9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F9" t="s">
-        <v>61</v>
-      </c>
-      <c r="G9" t="s">
-        <v>66</v>
-      </c>
-      <c r="H9" t="s">
-        <v>56</v>
-      </c>
-      <c r="I9" t="s">
-        <v>61</v>
-      </c>
-      <c r="J9" t="s">
-        <v>72</v>
-      </c>
-      <c r="K9" t="s">
-        <v>78</v>
-      </c>
-      <c r="L9" t="s">
-        <v>72</v>
-      </c>
-      <c r="M9" t="s">
-        <v>61</v>
-      </c>
-      <c r="N9" t="s">
-        <v>72</v>
-      </c>
-      <c r="O9" t="s">
-        <v>61</v>
-      </c>
-      <c r="P9" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>69</v>
-      </c>
-      <c r="R9" t="s">
-        <v>72</v>
-      </c>
-      <c r="S9" t="s">
-        <v>72</v>
-      </c>
-      <c r="T9" t="s">
-        <v>61</v>
-      </c>
-      <c r="U9" t="s">
-        <v>72</v>
-      </c>
-      <c r="V9" t="s">
-        <v>61</v>
-      </c>
-      <c r="W9" t="s">
-        <v>72</v>
-      </c>
-      <c r="X9" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC9" t="s">
-        <v>72</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AE9" t="s">
-        <v>64</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>68</v>
-      </c>
-      <c r="AG9" t="s">
-        <v>72</v>
-      </c>
-      <c r="AH9" t="s">
-        <v>79</v>
-      </c>
-      <c r="AI9" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>84</v>
-      </c>
-      <c r="AK9" t="s">
-        <v>84</v>
-      </c>
-      <c r="AL9" t="s">
-        <v>64</v>
-      </c>
-      <c r="AM9" t="s">
-        <v>76</v>
-      </c>
-      <c r="AN9" t="s">
-        <v>82</v>
-      </c>
-      <c r="AO9" t="s">
-        <v>63</v>
-      </c>
       <c r="AP9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I10" t="s">
+        <v>71</v>
+      </c>
+      <c r="J10" t="s">
+        <v>63</v>
+      </c>
+      <c r="K10" t="s">
+        <v>63</v>
+      </c>
+      <c r="L10" t="s">
+        <v>71</v>
+      </c>
+      <c r="M10" t="s">
+        <v>71</v>
+      </c>
+      <c r="N10" t="s">
+        <v>63</v>
+      </c>
+      <c r="O10" t="s">
+        <v>62</v>
+      </c>
+      <c r="P10" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>62</v>
+      </c>
+      <c r="R10" t="s">
+        <v>71</v>
+      </c>
+      <c r="S10" t="s">
+        <v>88</v>
+      </c>
+      <c r="T10" t="s">
+        <v>62</v>
+      </c>
+      <c r="U10" t="s">
+        <v>71</v>
+      </c>
+      <c r="V10" t="s">
+        <v>89</v>
+      </c>
+      <c r="W10" t="s">
+        <v>89</v>
+      </c>
+      <c r="X10" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>82</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>85</v>
+      </c>
+      <c r="AF10" t="s">
         <v>86</v>
       </c>
-      <c r="G10" t="s">
+      <c r="AG10" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>86</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>89</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>70</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AM10" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO10" t="s">
         <v>72</v>
-      </c>
-      <c r="H10" t="s">
-        <v>72</v>
-      </c>
-      <c r="I10" t="s">
-        <v>69</v>
-      </c>
-      <c r="J10" t="s">
-        <v>61</v>
-      </c>
-      <c r="K10" t="s">
-        <v>61</v>
-      </c>
-      <c r="L10" t="s">
-        <v>69</v>
-      </c>
-      <c r="M10" t="s">
-        <v>69</v>
-      </c>
-      <c r="N10" t="s">
-        <v>61</v>
-      </c>
-      <c r="O10" t="s">
-        <v>60</v>
-      </c>
-      <c r="P10" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>60</v>
-      </c>
-      <c r="R10" t="s">
-        <v>69</v>
-      </c>
-      <c r="S10" t="s">
-        <v>86</v>
-      </c>
-      <c r="T10" t="s">
-        <v>60</v>
-      </c>
-      <c r="U10" t="s">
-        <v>69</v>
-      </c>
-      <c r="V10" t="s">
-        <v>87</v>
-      </c>
-      <c r="W10" t="s">
-        <v>87</v>
-      </c>
-      <c r="X10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>61</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>68</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>74</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>80</v>
-      </c>
-      <c r="AE10" t="s">
-        <v>83</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>84</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>69</v>
-      </c>
-      <c r="AH10" t="s">
-        <v>84</v>
-      </c>
-      <c r="AI10" t="s">
-        <v>61</v>
-      </c>
-      <c r="AJ10" t="s">
-        <v>87</v>
-      </c>
-      <c r="AK10" t="s">
-        <v>68</v>
-      </c>
-      <c r="AL10" t="s">
-        <v>75</v>
-      </c>
-      <c r="AM10" t="s">
-        <v>83</v>
-      </c>
-      <c r="AN10" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO10" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E11" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G11" t="s">
+        <v>80</v>
+      </c>
+      <c r="H11" t="s">
+        <v>63</v>
+      </c>
+      <c r="I11" t="s">
+        <v>89</v>
+      </c>
+      <c r="J11" t="s">
+        <v>62</v>
+      </c>
+      <c r="K11" t="s">
+        <v>62</v>
+      </c>
+      <c r="L11" t="s">
+        <v>62</v>
+      </c>
+      <c r="M11" t="s">
+        <v>62</v>
+      </c>
+      <c r="N11" t="s">
+        <v>71</v>
+      </c>
+      <c r="O11" t="s">
+        <v>70</v>
+      </c>
+      <c r="P11" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>66</v>
+      </c>
+      <c r="R11" t="s">
+        <v>62</v>
+      </c>
+      <c r="S11" t="s">
+        <v>62</v>
+      </c>
+      <c r="T11" t="s">
+        <v>81</v>
+      </c>
+      <c r="U11" t="s">
+        <v>62</v>
+      </c>
+      <c r="V11" t="s">
+        <v>66</v>
+      </c>
+      <c r="W11" t="s">
+        <v>66</v>
+      </c>
+      <c r="X11" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>55</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AH11" t="s">
         <v>78</v>
       </c>
-      <c r="H11" t="s">
-        <v>61</v>
-      </c>
-      <c r="I11" t="s">
-        <v>87</v>
-      </c>
-      <c r="J11" t="s">
-        <v>60</v>
-      </c>
-      <c r="K11" t="s">
-        <v>60</v>
-      </c>
-      <c r="L11" t="s">
-        <v>60</v>
-      </c>
-      <c r="M11" t="s">
-        <v>60</v>
-      </c>
-      <c r="N11" t="s">
-        <v>69</v>
-      </c>
-      <c r="O11" t="s">
-        <v>68</v>
-      </c>
-      <c r="P11" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>64</v>
-      </c>
-      <c r="R11" t="s">
-        <v>60</v>
-      </c>
-      <c r="S11" t="s">
-        <v>60</v>
-      </c>
-      <c r="T11" t="s">
-        <v>79</v>
-      </c>
-      <c r="U11" t="s">
-        <v>60</v>
-      </c>
-      <c r="V11" t="s">
-        <v>64</v>
-      </c>
-      <c r="W11" t="s">
-        <v>64</v>
-      </c>
-      <c r="X11" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>60</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>88</v>
-      </c>
-      <c r="AB11" t="s">
-        <v>87</v>
-      </c>
-      <c r="AC11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE11" t="s">
-        <v>54</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>73</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>88</v>
-      </c>
-      <c r="AH11" t="s">
+      <c r="AI11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AJ11" t="s">
         <v>76</v>
       </c>
-      <c r="AI11" t="s">
-        <v>88</v>
-      </c>
-      <c r="AJ11" t="s">
-        <v>74</v>
-      </c>
       <c r="AK11" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AL11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AM11" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AN11" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AO11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I12" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J12" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K12" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="N12" t="s">
+        <v>75</v>
+      </c>
+      <c r="O12" t="s">
+        <v>66</v>
+      </c>
+      <c r="P12" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>85</v>
+      </c>
+      <c r="R12" t="s">
+        <v>70</v>
+      </c>
+      <c r="S12" t="s">
+        <v>86</v>
+      </c>
+      <c r="T12" t="s">
+        <v>85</v>
+      </c>
+      <c r="U12" t="s">
+        <v>66</v>
+      </c>
+      <c r="V12" t="s">
+        <v>85</v>
+      </c>
+      <c r="W12" t="s">
+        <v>76</v>
+      </c>
+      <c r="X12" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>75</v>
+      </c>
+      <c r="AD12" t="s">
         <v>73</v>
       </c>
-      <c r="O12" t="s">
-        <v>64</v>
-      </c>
-      <c r="P12" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>83</v>
-      </c>
-      <c r="R12" t="s">
-        <v>68</v>
-      </c>
-      <c r="S12" t="s">
-        <v>84</v>
-      </c>
-      <c r="T12" t="s">
-        <v>83</v>
-      </c>
-      <c r="U12" t="s">
-        <v>64</v>
-      </c>
-      <c r="V12" t="s">
-        <v>83</v>
-      </c>
-      <c r="W12" t="s">
-        <v>74</v>
-      </c>
-      <c r="X12" t="s">
-        <v>83</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>68</v>
-      </c>
-      <c r="Z12" t="s">
-        <v>73</v>
-      </c>
-      <c r="AA12" t="s">
+      <c r="AE12" t="s">
         <v>75</v>
       </c>
-      <c r="AB12" t="s">
-        <v>84</v>
-      </c>
-      <c r="AC12" t="s">
-        <v>73</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>71</v>
-      </c>
-      <c r="AE12" t="s">
-        <v>73</v>
-      </c>
       <c r="AF12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AG12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AH12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI12" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="AJ12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AK12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AL12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AM12" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AN12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AO12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" t="s">
+        <v>89</v>
+      </c>
+      <c r="E13" t="s">
+        <v>70</v>
+      </c>
+      <c r="F13" t="s">
+        <v>66</v>
+      </c>
+      <c r="G13" t="s">
+        <v>66</v>
+      </c>
+      <c r="H13" t="s">
+        <v>70</v>
+      </c>
+      <c r="I13" t="s">
+        <v>82</v>
+      </c>
+      <c r="J13" t="s">
+        <v>85</v>
+      </c>
+      <c r="K13" t="s">
+        <v>74</v>
+      </c>
+      <c r="L13" t="s">
+        <v>66</v>
+      </c>
+      <c r="M13" t="s">
+        <v>75</v>
+      </c>
+      <c r="N13" t="s">
+        <v>76</v>
+      </c>
+      <c r="O13" t="s">
+        <v>76</v>
+      </c>
+      <c r="P13" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>75</v>
+      </c>
+      <c r="R13" t="s">
+        <v>75</v>
+      </c>
+      <c r="S13" t="s">
+        <v>85</v>
+      </c>
+      <c r="T13" t="s">
+        <v>76</v>
+      </c>
+      <c r="U13" t="s">
+        <v>75</v>
+      </c>
+      <c r="V13" t="s">
+        <v>62</v>
+      </c>
+      <c r="W13" t="s">
+        <v>82</v>
+      </c>
+      <c r="X13" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>83</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>77</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>90</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>83</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>83</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>83</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>84</v>
+      </c>
+      <c r="AM13" t="s">
         <v>60</v>
       </c>
-      <c r="C13" t="s">
-        <v>68</v>
-      </c>
-      <c r="D13" t="s">
-        <v>87</v>
-      </c>
-      <c r="E13" t="s">
-        <v>68</v>
-      </c>
-      <c r="F13" t="s">
-        <v>64</v>
-      </c>
-      <c r="G13" t="s">
-        <v>64</v>
-      </c>
-      <c r="H13" t="s">
-        <v>68</v>
-      </c>
-      <c r="I13" t="s">
-        <v>80</v>
-      </c>
-      <c r="J13" t="s">
-        <v>83</v>
-      </c>
-      <c r="K13" t="s">
-        <v>72</v>
-      </c>
-      <c r="L13" t="s">
-        <v>64</v>
-      </c>
-      <c r="M13" t="s">
+      <c r="AO13" t="s">
         <v>73</v>
-      </c>
-      <c r="N13" t="s">
-        <v>74</v>
-      </c>
-      <c r="O13" t="s">
-        <v>74</v>
-      </c>
-      <c r="P13" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>73</v>
-      </c>
-      <c r="R13" t="s">
-        <v>73</v>
-      </c>
-      <c r="S13" t="s">
-        <v>83</v>
-      </c>
-      <c r="T13" t="s">
-        <v>74</v>
-      </c>
-      <c r="U13" t="s">
-        <v>73</v>
-      </c>
-      <c r="V13" t="s">
-        <v>60</v>
-      </c>
-      <c r="W13" t="s">
-        <v>80</v>
-      </c>
-      <c r="X13" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>73</v>
-      </c>
-      <c r="Z13" t="s">
-        <v>74</v>
-      </c>
-      <c r="AA13" t="s">
-        <v>71</v>
-      </c>
-      <c r="AB13" t="s">
-        <v>88</v>
-      </c>
-      <c r="AC13" t="s">
-        <v>76</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>81</v>
-      </c>
-      <c r="AE13" t="s">
-        <v>75</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>88</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>81</v>
-      </c>
-      <c r="AH13" t="s">
-        <v>71</v>
-      </c>
-      <c r="AI13" t="s">
-        <v>81</v>
-      </c>
-      <c r="AJ13" t="s">
-        <v>81</v>
-      </c>
-      <c r="AK13" t="s">
-        <v>81</v>
-      </c>
-      <c r="AL13" t="s">
-        <v>82</v>
-      </c>
-      <c r="AM13" t="s">
-        <v>96</v>
-      </c>
-      <c r="AO13" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14" t="s">
+        <v>89</v>
+      </c>
+      <c r="D14" t="s">
+        <v>66</v>
+      </c>
+      <c r="E14" t="s">
+        <v>89</v>
+      </c>
+      <c r="F14" t="s">
+        <v>85</v>
+      </c>
+      <c r="G14" t="s">
+        <v>85</v>
+      </c>
+      <c r="H14" t="s">
+        <v>66</v>
+      </c>
+      <c r="I14" t="s">
+        <v>90</v>
+      </c>
+      <c r="J14" t="s">
+        <v>76</v>
+      </c>
+      <c r="K14" t="s">
+        <v>76</v>
+      </c>
+      <c r="L14" t="s">
+        <v>75</v>
+      </c>
+      <c r="M14" t="s">
+        <v>93</v>
+      </c>
+      <c r="N14" t="s">
+        <v>82</v>
+      </c>
+      <c r="O14" t="s">
+        <v>78</v>
+      </c>
+      <c r="P14" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>76</v>
+      </c>
+      <c r="R14" t="s">
+        <v>76</v>
+      </c>
+      <c r="S14" t="s">
+        <v>90</v>
+      </c>
+      <c r="T14" t="s">
+        <v>90</v>
+      </c>
+      <c r="U14" t="s">
+        <v>78</v>
+      </c>
+      <c r="V14" t="s">
+        <v>75</v>
+      </c>
+      <c r="W14" t="s">
+        <v>73</v>
+      </c>
+      <c r="X14" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>90</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>94</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>98</v>
+      </c>
+      <c r="AL14" t="s">
         <v>60</v>
       </c>
-      <c r="B14" t="s">
-        <v>79</v>
-      </c>
-      <c r="C14" t="s">
-        <v>87</v>
-      </c>
-      <c r="D14" t="s">
-        <v>64</v>
-      </c>
-      <c r="E14" t="s">
-        <v>87</v>
-      </c>
-      <c r="F14" t="s">
-        <v>83</v>
-      </c>
-      <c r="G14" t="s">
-        <v>83</v>
-      </c>
-      <c r="H14" t="s">
-        <v>64</v>
-      </c>
-      <c r="I14" t="s">
-        <v>88</v>
-      </c>
-      <c r="J14" t="s">
-        <v>74</v>
-      </c>
-      <c r="K14" t="s">
-        <v>74</v>
-      </c>
-      <c r="L14" t="s">
-        <v>73</v>
-      </c>
-      <c r="M14" t="s">
-        <v>91</v>
-      </c>
-      <c r="N14" t="s">
-        <v>80</v>
-      </c>
-      <c r="O14" t="s">
-        <v>76</v>
-      </c>
-      <c r="P14" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>74</v>
-      </c>
-      <c r="R14" t="s">
-        <v>74</v>
-      </c>
-      <c r="S14" t="s">
-        <v>88</v>
-      </c>
-      <c r="T14" t="s">
-        <v>88</v>
-      </c>
-      <c r="U14" t="s">
-        <v>76</v>
-      </c>
-      <c r="V14" t="s">
-        <v>73</v>
-      </c>
-      <c r="W14" t="s">
-        <v>71</v>
-      </c>
-      <c r="X14" t="s">
-        <v>76</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>76</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>76</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AC14" t="s">
-        <v>88</v>
-      </c>
-      <c r="AD14" t="s">
-        <v>89</v>
-      </c>
-      <c r="AE14" t="s">
-        <v>89</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>81</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AH14" t="s">
-        <v>97</v>
-      </c>
-      <c r="AI14" t="s">
-        <v>63</v>
-      </c>
-      <c r="AJ14" t="s">
-        <v>97</v>
-      </c>
-      <c r="AK14" t="s">
-        <v>97</v>
-      </c>
-      <c r="AL14" t="s">
-        <v>96</v>
-      </c>
       <c r="AM14" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" t="s">
+        <v>85</v>
+      </c>
+      <c r="E15" t="s">
+        <v>66</v>
+      </c>
+      <c r="F15" t="s">
+        <v>76</v>
+      </c>
+      <c r="G15" t="s">
+        <v>75</v>
+      </c>
+      <c r="H15" t="s">
+        <v>76</v>
+      </c>
+      <c r="I15" t="s">
+        <v>77</v>
+      </c>
+      <c r="J15" t="s">
+        <v>82</v>
+      </c>
+      <c r="K15" t="s">
+        <v>82</v>
+      </c>
+      <c r="L15" t="s">
+        <v>82</v>
+      </c>
+      <c r="M15" t="s">
+        <v>78</v>
+      </c>
+      <c r="N15" t="s">
+        <v>90</v>
+      </c>
+      <c r="O15" t="s">
+        <v>90</v>
+      </c>
+      <c r="P15" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>93</v>
+      </c>
+      <c r="R15" t="s">
+        <v>82</v>
+      </c>
+      <c r="S15" t="s">
+        <v>77</v>
+      </c>
+      <c r="T15" t="s">
+        <v>77</v>
+      </c>
+      <c r="U15" t="s">
+        <v>90</v>
+      </c>
+      <c r="V15" t="s">
+        <v>82</v>
+      </c>
+      <c r="W15" t="s">
+        <v>83</v>
+      </c>
+      <c r="X15" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>86</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>73</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>94</v>
+      </c>
+      <c r="AF15" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>88</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>97</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>97</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>72</v>
+      </c>
+      <c r="AK15" t="s">
+        <v>72</v>
+      </c>
+      <c r="AL15" t="s">
         <v>87</v>
       </c>
-      <c r="C15" t="s">
-        <v>64</v>
-      </c>
-      <c r="D15" t="s">
-        <v>83</v>
-      </c>
-      <c r="E15" t="s">
-        <v>64</v>
-      </c>
-      <c r="F15" t="s">
-        <v>74</v>
-      </c>
-      <c r="G15" t="s">
-        <v>73</v>
-      </c>
-      <c r="H15" t="s">
-        <v>74</v>
-      </c>
-      <c r="I15" t="s">
-        <v>75</v>
-      </c>
-      <c r="J15" t="s">
-        <v>80</v>
-      </c>
-      <c r="K15" t="s">
-        <v>80</v>
-      </c>
-      <c r="L15" t="s">
-        <v>80</v>
-      </c>
-      <c r="M15" t="s">
-        <v>76</v>
-      </c>
-      <c r="N15" t="s">
-        <v>88</v>
-      </c>
-      <c r="O15" t="s">
-        <v>88</v>
-      </c>
-      <c r="P15" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>91</v>
-      </c>
-      <c r="R15" t="s">
-        <v>80</v>
-      </c>
-      <c r="S15" t="s">
-        <v>75</v>
-      </c>
-      <c r="T15" t="s">
-        <v>75</v>
-      </c>
-      <c r="U15" t="s">
-        <v>88</v>
-      </c>
-      <c r="V15" t="s">
-        <v>80</v>
-      </c>
-      <c r="W15" t="s">
-        <v>81</v>
-      </c>
-      <c r="X15" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y15" t="s">
-        <v>88</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>71</v>
-      </c>
-      <c r="AA15" t="s">
-        <v>84</v>
-      </c>
-      <c r="AB15" t="s">
-        <v>81</v>
-      </c>
-      <c r="AC15" t="s">
-        <v>71</v>
-      </c>
-      <c r="AD15" t="s">
-        <v>92</v>
-      </c>
-      <c r="AE15" t="s">
-        <v>92</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>74</v>
-      </c>
-      <c r="AG15" t="s">
-        <v>86</v>
-      </c>
-      <c r="AH15" t="s">
-        <v>95</v>
-      </c>
-      <c r="AI15" t="s">
-        <v>95</v>
-      </c>
-      <c r="AJ15" t="s">
-        <v>70</v>
-      </c>
-      <c r="AK15" t="s">
-        <v>70</v>
-      </c>
-      <c r="AL15" t="s">
-        <v>85</v>
-      </c>
       <c r="AM15" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B16" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C16" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" t="s">
+        <v>75</v>
+      </c>
+      <c r="F16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G16" t="s">
+        <v>76</v>
+      </c>
+      <c r="H16" t="s">
+        <v>78</v>
+      </c>
+      <c r="I16" t="s">
+        <v>73</v>
+      </c>
+      <c r="J16" t="s">
+        <v>73</v>
+      </c>
+      <c r="K16" t="s">
+        <v>90</v>
+      </c>
+      <c r="L16" t="s">
+        <v>78</v>
+      </c>
+      <c r="M16" t="s">
+        <v>77</v>
+      </c>
+      <c r="N16" t="s">
+        <v>77</v>
+      </c>
+      <c r="O16" t="s">
+        <v>73</v>
+      </c>
+      <c r="P16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>82</v>
+      </c>
+      <c r="R16" t="s">
+        <v>78</v>
+      </c>
+      <c r="S16" t="s">
+        <v>73</v>
+      </c>
+      <c r="T16" t="s">
+        <v>98</v>
+      </c>
+      <c r="U16" t="s">
+        <v>73</v>
+      </c>
+      <c r="V16" t="s">
+        <v>78</v>
+      </c>
+      <c r="W16" t="s">
+        <v>98</v>
+      </c>
+      <c r="X16" t="s">
         <v>83</v>
       </c>
-      <c r="D16" t="s">
+      <c r="Y16" t="s">
         <v>73</v>
       </c>
-      <c r="E16" t="s">
-        <v>73</v>
-      </c>
-      <c r="F16" t="s">
-        <v>80</v>
-      </c>
-      <c r="G16" t="s">
-        <v>74</v>
-      </c>
-      <c r="H16" t="s">
-        <v>76</v>
-      </c>
-      <c r="I16" t="s">
-        <v>71</v>
-      </c>
-      <c r="J16" t="s">
-        <v>71</v>
-      </c>
-      <c r="K16" t="s">
-        <v>88</v>
-      </c>
-      <c r="L16" t="s">
-        <v>76</v>
-      </c>
-      <c r="M16" t="s">
-        <v>75</v>
-      </c>
-      <c r="N16" t="s">
-        <v>75</v>
-      </c>
-      <c r="O16" t="s">
-        <v>71</v>
-      </c>
-      <c r="P16" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>80</v>
-      </c>
-      <c r="R16" t="s">
-        <v>76</v>
-      </c>
-      <c r="S16" t="s">
-        <v>71</v>
-      </c>
-      <c r="T16" t="s">
+      <c r="Z16" t="s">
+        <v>83</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>99</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>91</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE16" t="s">
         <v>97</v>
       </c>
-      <c r="U16" t="s">
-        <v>71</v>
-      </c>
-      <c r="V16" t="s">
-        <v>76</v>
-      </c>
-      <c r="W16" t="s">
-        <v>97</v>
-      </c>
-      <c r="X16" t="s">
-        <v>81</v>
-      </c>
-      <c r="Y16" t="s">
-        <v>71</v>
-      </c>
-      <c r="Z16" t="s">
-        <v>81</v>
-      </c>
-      <c r="AA16" t="s">
-        <v>98</v>
-      </c>
-      <c r="AB16" t="s">
-        <v>70</v>
-      </c>
-      <c r="AC16" t="s">
-        <v>89</v>
-      </c>
-      <c r="AD16" t="s">
+      <c r="AF16" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG16" t="s">
+        <v>65</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>72</v>
+      </c>
+      <c r="AI16" t="s">
+        <v>95</v>
+      </c>
+      <c r="AJ16" t="s">
         <v>60</v>
       </c>
-      <c r="AE16" t="s">
-        <v>95</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG16" t="s">
-        <v>63</v>
-      </c>
-      <c r="AH16" t="s">
-        <v>70</v>
-      </c>
-      <c r="AI16" t="s">
-        <v>93</v>
-      </c>
-      <c r="AJ16" t="s">
-        <v>96</v>
-      </c>
       <c r="AK16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AL16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B17" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" t="s">
+        <v>76</v>
+      </c>
+      <c r="E17" t="s">
+        <v>76</v>
+      </c>
+      <c r="F17" t="s">
+        <v>90</v>
+      </c>
+      <c r="G17" t="s">
+        <v>90</v>
+      </c>
+      <c r="H17" t="s">
+        <v>77</v>
+      </c>
+      <c r="I17" t="s">
+        <v>98</v>
+      </c>
+      <c r="J17" t="s">
+        <v>98</v>
+      </c>
+      <c r="K17" t="s">
         <v>83</v>
       </c>
-      <c r="C17" t="s">
-        <v>74</v>
-      </c>
-      <c r="D17" t="s">
-        <v>74</v>
-      </c>
-      <c r="E17" t="s">
-        <v>74</v>
-      </c>
-      <c r="F17" t="s">
-        <v>88</v>
-      </c>
-      <c r="G17" t="s">
-        <v>88</v>
-      </c>
-      <c r="H17" t="s">
-        <v>75</v>
-      </c>
-      <c r="I17" t="s">
+      <c r="L17" t="s">
+        <v>77</v>
+      </c>
+      <c r="M17" t="s">
+        <v>73</v>
+      </c>
+      <c r="N17" t="s">
+        <v>83</v>
+      </c>
+      <c r="O17" t="s">
+        <v>94</v>
+      </c>
+      <c r="P17" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>73</v>
+      </c>
+      <c r="R17" t="s">
+        <v>90</v>
+      </c>
+      <c r="S17" t="s">
+        <v>91</v>
+      </c>
+      <c r="T17" t="s">
+        <v>100</v>
+      </c>
+      <c r="U17" t="s">
+        <v>83</v>
+      </c>
+      <c r="V17" t="s">
+        <v>100</v>
+      </c>
+      <c r="W17" t="s">
+        <v>93</v>
+      </c>
+      <c r="X17" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>65</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC17" t="s">
         <v>97</v>
       </c>
-      <c r="J17" t="s">
+      <c r="AD17" t="s">
         <v>97</v>
       </c>
-      <c r="K17" t="s">
-        <v>81</v>
-      </c>
-      <c r="L17" t="s">
-        <v>75</v>
-      </c>
-      <c r="M17" t="s">
-        <v>71</v>
-      </c>
-      <c r="N17" t="s">
-        <v>81</v>
-      </c>
-      <c r="O17" t="s">
-        <v>92</v>
-      </c>
-      <c r="P17" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>71</v>
-      </c>
-      <c r="R17" t="s">
-        <v>88</v>
-      </c>
-      <c r="S17" t="s">
-        <v>89</v>
-      </c>
-      <c r="T17" t="s">
-        <v>99</v>
-      </c>
-      <c r="U17" t="s">
-        <v>81</v>
-      </c>
-      <c r="V17" t="s">
-        <v>99</v>
-      </c>
-      <c r="W17" t="s">
-        <v>91</v>
-      </c>
-      <c r="X17" t="s">
-        <v>92</v>
-      </c>
-      <c r="Y17" t="s">
-        <v>81</v>
-      </c>
-      <c r="Z17" t="s">
-        <v>97</v>
-      </c>
-      <c r="AA17" t="s">
-        <v>63</v>
-      </c>
-      <c r="AB17" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC17" t="s">
+      <c r="AE17" t="s">
+        <v>72</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>84</v>
+      </c>
+      <c r="AG17" t="s">
         <v>95</v>
       </c>
-      <c r="AD17" t="s">
-        <v>95</v>
-      </c>
-      <c r="AE17" t="s">
-        <v>70</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>82</v>
-      </c>
-      <c r="AG17" t="s">
-        <v>93</v>
-      </c>
       <c r="AH17" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="AI17" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AJ17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AK17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" t="s">
+        <v>93</v>
+      </c>
+      <c r="D18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E18" t="s">
         <v>73</v>
       </c>
-      <c r="B18" t="s">
+      <c r="F18" t="s">
         <v>73</v>
       </c>
-      <c r="C18" t="s">
+      <c r="G18" t="s">
+        <v>77</v>
+      </c>
+      <c r="H18" t="s">
+        <v>73</v>
+      </c>
+      <c r="I18" t="s">
         <v>91</v>
       </c>
-      <c r="D18" t="s">
+      <c r="J18" t="s">
         <v>91</v>
       </c>
-      <c r="E18" t="s">
-        <v>71</v>
-      </c>
-      <c r="F18" t="s">
-        <v>71</v>
-      </c>
-      <c r="G18" t="s">
-        <v>75</v>
-      </c>
-      <c r="H18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I18" t="s">
-        <v>89</v>
-      </c>
-      <c r="J18" t="s">
-        <v>89</v>
-      </c>
       <c r="K18" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="L18" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M18" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="N18" t="s">
+        <v>94</v>
+      </c>
+      <c r="O18" t="s">
+        <v>95</v>
+      </c>
+      <c r="P18" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>83</v>
+      </c>
+      <c r="R18" t="s">
+        <v>73</v>
+      </c>
+      <c r="S18" t="s">
+        <v>95</v>
+      </c>
+      <c r="T18" t="s">
+        <v>97</v>
+      </c>
+      <c r="U18" t="s">
+        <v>72</v>
+      </c>
+      <c r="V18" t="s">
+        <v>102</v>
+      </c>
+      <c r="W18" t="s">
+        <v>97</v>
+      </c>
+      <c r="X18" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>95</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>101</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>95</v>
+      </c>
+      <c r="AE18" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF18" t="s">
+        <v>59</v>
+      </c>
+      <c r="AG18" t="s">
+        <v>101</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI18" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ18" t="s">
+        <v>87</v>
+      </c>
+      <c r="AK18" t="s">
         <v>92</v>
-      </c>
-      <c r="O18" t="s">
-        <v>93</v>
-      </c>
-      <c r="P18" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>81</v>
-      </c>
-      <c r="R18" t="s">
-        <v>71</v>
-      </c>
-      <c r="S18" t="s">
-        <v>93</v>
-      </c>
-      <c r="T18" t="s">
-        <v>95</v>
-      </c>
-      <c r="U18" t="s">
-        <v>70</v>
-      </c>
-      <c r="V18" t="s">
-        <v>101</v>
-      </c>
-      <c r="W18" t="s">
-        <v>95</v>
-      </c>
-      <c r="X18" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y18" t="s">
-        <v>95</v>
-      </c>
-      <c r="Z18" t="s">
-        <v>70</v>
-      </c>
-      <c r="AA18" t="s">
-        <v>93</v>
-      </c>
-      <c r="AB18" t="s">
-        <v>96</v>
-      </c>
-      <c r="AC18" t="s">
-        <v>100</v>
-      </c>
-      <c r="AD18" t="s">
-        <v>93</v>
-      </c>
-      <c r="AE18" t="s">
-        <v>82</v>
-      </c>
-      <c r="AF18" t="s">
-        <v>58</v>
-      </c>
-      <c r="AG18" t="s">
-        <v>100</v>
-      </c>
-      <c r="AH18" t="s">
-        <v>96</v>
-      </c>
-      <c r="AI18" t="s">
-        <v>85</v>
-      </c>
-      <c r="AJ18" t="s">
-        <v>85</v>
-      </c>
-      <c r="AK18" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C19" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D19" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E19" t="s">
+        <v>98</v>
+      </c>
+      <c r="F19" t="s">
+        <v>83</v>
+      </c>
+      <c r="G19" t="s">
+        <v>83</v>
+      </c>
+      <c r="H19" t="s">
+        <v>98</v>
+      </c>
+      <c r="I19" t="s">
+        <v>65</v>
+      </c>
+      <c r="J19" t="s">
+        <v>94</v>
+      </c>
+      <c r="K19" t="s">
+        <v>95</v>
+      </c>
+      <c r="L19" t="s">
+        <v>72</v>
+      </c>
+      <c r="M19" t="s">
         <v>97</v>
       </c>
-      <c r="F19" t="s">
-        <v>81</v>
-      </c>
-      <c r="G19" t="s">
-        <v>81</v>
-      </c>
-      <c r="H19" t="s">
+      <c r="N19" t="s">
         <v>97</v>
       </c>
-      <c r="I19" t="s">
-        <v>63</v>
-      </c>
-      <c r="J19" t="s">
+      <c r="O19" t="s">
+        <v>101</v>
+      </c>
+      <c r="P19" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>98</v>
+      </c>
+      <c r="R19" t="s">
+        <v>97</v>
+      </c>
+      <c r="S19" t="s">
+        <v>103</v>
+      </c>
+      <c r="T19" t="s">
+        <v>84</v>
+      </c>
+      <c r="U19" t="s">
+        <v>79</v>
+      </c>
+      <c r="V19" t="s">
+        <v>101</v>
+      </c>
+      <c r="W19" t="s">
+        <v>72</v>
+      </c>
+      <c r="X19" t="s">
+        <v>95</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>103</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>84</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>101</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>87</v>
+      </c>
+      <c r="AG19" t="s">
+        <v>79</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>87</v>
+      </c>
+      <c r="AI19" t="s">
+        <v>96</v>
+      </c>
+      <c r="AJ19" t="s">
         <v>92</v>
-      </c>
-      <c r="K19" t="s">
-        <v>93</v>
-      </c>
-      <c r="L19" t="s">
-        <v>70</v>
-      </c>
-      <c r="M19" t="s">
-        <v>95</v>
-      </c>
-      <c r="N19" t="s">
-        <v>95</v>
-      </c>
-      <c r="O19" t="s">
-        <v>100</v>
-      </c>
-      <c r="P19" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>97</v>
-      </c>
-      <c r="R19" t="s">
-        <v>95</v>
-      </c>
-      <c r="S19" t="s">
-        <v>102</v>
-      </c>
-      <c r="T19" t="s">
-        <v>82</v>
-      </c>
-      <c r="U19" t="s">
-        <v>77</v>
-      </c>
-      <c r="V19" t="s">
-        <v>100</v>
-      </c>
-      <c r="W19" t="s">
-        <v>70</v>
-      </c>
-      <c r="X19" t="s">
-        <v>93</v>
-      </c>
-      <c r="Y19" t="s">
-        <v>77</v>
-      </c>
-      <c r="Z19" t="s">
-        <v>77</v>
-      </c>
-      <c r="AA19" t="s">
-        <v>102</v>
-      </c>
-      <c r="AB19" t="s">
-        <v>58</v>
-      </c>
-      <c r="AC19" t="s">
-        <v>82</v>
-      </c>
-      <c r="AD19" t="s">
-        <v>100</v>
-      </c>
-      <c r="AE19" t="s">
-        <v>96</v>
-      </c>
-      <c r="AF19" t="s">
-        <v>85</v>
-      </c>
-      <c r="AG19" t="s">
-        <v>77</v>
-      </c>
-      <c r="AH19" t="s">
-        <v>85</v>
-      </c>
-      <c r="AI19" t="s">
-        <v>94</v>
-      </c>
-      <c r="AJ19" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>93</v>
+      </c>
+      <c r="B20" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D20" t="s">
+        <v>90</v>
+      </c>
+      <c r="E20" t="s">
         <v>91</v>
       </c>
-      <c r="B20" t="s">
-        <v>91</v>
-      </c>
-      <c r="C20" t="s">
-        <v>88</v>
-      </c>
-      <c r="D20" t="s">
-        <v>88</v>
-      </c>
-      <c r="E20" t="s">
-        <v>89</v>
-      </c>
       <c r="F20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G20" t="s">
+        <v>72</v>
+      </c>
+      <c r="H20" t="s">
+        <v>75</v>
+      </c>
+      <c r="I20" t="s">
+        <v>78</v>
+      </c>
+      <c r="J20" t="s">
+        <v>97</v>
+      </c>
+      <c r="K20" t="s">
+        <v>84</v>
+      </c>
+      <c r="L20" t="s">
+        <v>95</v>
+      </c>
+      <c r="M20" t="s">
+        <v>72</v>
+      </c>
+      <c r="N20" t="s">
+        <v>95</v>
+      </c>
+      <c r="O20" t="s">
+        <v>79</v>
+      </c>
+      <c r="P20" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>97</v>
+      </c>
+      <c r="R20" t="s">
+        <v>79</v>
+      </c>
+      <c r="S20" t="s">
+        <v>84</v>
+      </c>
+      <c r="T20" t="s">
+        <v>60</v>
+      </c>
+      <c r="U20" t="s">
+        <v>84</v>
+      </c>
+      <c r="V20" t="s">
+        <v>79</v>
+      </c>
+      <c r="W20" t="s">
+        <v>101</v>
+      </c>
+      <c r="X20" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>96</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD20" t="s">
+        <v>59</v>
+      </c>
+      <c r="AE20" t="s">
+        <v>87</v>
+      </c>
+      <c r="AF20" t="s">
+        <v>96</v>
+      </c>
+      <c r="AG20" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH20" t="s">
         <v>92</v>
       </c>
-      <c r="G20" t="s">
-        <v>70</v>
-      </c>
-      <c r="H20" t="s">
-        <v>73</v>
-      </c>
-      <c r="I20" t="s">
-        <v>76</v>
-      </c>
-      <c r="J20" t="s">
-        <v>95</v>
-      </c>
-      <c r="K20" t="s">
-        <v>82</v>
-      </c>
-      <c r="L20" t="s">
-        <v>93</v>
-      </c>
-      <c r="M20" t="s">
-        <v>70</v>
-      </c>
-      <c r="N20" t="s">
-        <v>93</v>
-      </c>
-      <c r="O20" t="s">
-        <v>77</v>
-      </c>
-      <c r="P20" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>95</v>
-      </c>
-      <c r="R20" t="s">
-        <v>77</v>
-      </c>
-      <c r="S20" t="s">
-        <v>82</v>
-      </c>
-      <c r="T20" t="s">
-        <v>96</v>
-      </c>
-      <c r="U20" t="s">
-        <v>82</v>
-      </c>
-      <c r="V20" t="s">
-        <v>77</v>
-      </c>
-      <c r="W20" t="s">
-        <v>100</v>
-      </c>
-      <c r="X20" t="s">
-        <v>96</v>
-      </c>
-      <c r="Y20" t="s">
-        <v>96</v>
-      </c>
-      <c r="Z20" t="s">
-        <v>82</v>
-      </c>
-      <c r="AA20" t="s">
-        <v>82</v>
-      </c>
-      <c r="AB20" t="s">
-        <v>94</v>
-      </c>
-      <c r="AC20" t="s">
-        <v>85</v>
-      </c>
-      <c r="AD20" t="s">
-        <v>58</v>
-      </c>
-      <c r="AE20" t="s">
-        <v>85</v>
-      </c>
-      <c r="AF20" t="s">
-        <v>94</v>
-      </c>
-      <c r="AG20" t="s">
-        <v>82</v>
-      </c>
-      <c r="AH20" t="s">
-        <v>90</v>
-      </c>
       <c r="AI20" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B21" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C21" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D21" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E21" t="s">
+        <v>97</v>
+      </c>
+      <c r="F21" t="s">
+        <v>70</v>
+      </c>
+      <c r="G21" t="s">
+        <v>101</v>
+      </c>
+      <c r="H21" t="s">
+        <v>97</v>
+      </c>
+      <c r="I21" t="s">
+        <v>97</v>
+      </c>
+      <c r="J21" t="s">
         <v>95</v>
       </c>
-      <c r="F21" t="s">
-        <v>68</v>
-      </c>
-      <c r="G21" t="s">
-        <v>100</v>
-      </c>
-      <c r="H21" t="s">
+      <c r="K21" t="s">
+        <v>60</v>
+      </c>
+      <c r="L21" t="s">
+        <v>101</v>
+      </c>
+      <c r="M21" t="s">
+        <v>79</v>
+      </c>
+      <c r="N21" t="s">
+        <v>101</v>
+      </c>
+      <c r="O21" t="s">
+        <v>60</v>
+      </c>
+      <c r="P21" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>72</v>
+      </c>
+      <c r="R21" t="s">
+        <v>87</v>
+      </c>
+      <c r="S21" t="s">
+        <v>60</v>
+      </c>
+      <c r="T21" t="s">
+        <v>59</v>
+      </c>
+      <c r="U21" t="s">
+        <v>59</v>
+      </c>
+      <c r="V21" t="s">
+        <v>60</v>
+      </c>
+      <c r="W21" t="s">
+        <v>79</v>
+      </c>
+      <c r="X21" t="s">
+        <v>96</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>96</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>96</v>
+      </c>
+      <c r="AD21" t="s">
+        <v>87</v>
+      </c>
+      <c r="AE21" t="s">
+        <v>92</v>
+      </c>
+      <c r="AF21" t="s">
+        <v>92</v>
+      </c>
+      <c r="AG21" t="s">
+        <v>65</v>
+      </c>
+      <c r="AH21" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>77</v>
+      </c>
+      <c r="B22" t="s">
+        <v>90</v>
+      </c>
+      <c r="C22" t="s">
+        <v>73</v>
+      </c>
+      <c r="D22" t="s">
+        <v>73</v>
+      </c>
+      <c r="E22" t="s">
+        <v>102</v>
+      </c>
+      <c r="F22" t="s">
+        <v>72</v>
+      </c>
+      <c r="G22" t="s">
+        <v>79</v>
+      </c>
+      <c r="H22" t="s">
         <v>95</v>
       </c>
-      <c r="I21" t="s">
+      <c r="I22" t="s">
+        <v>72</v>
+      </c>
+      <c r="J22" t="s">
+        <v>79</v>
+      </c>
+      <c r="K22" t="s">
+        <v>59</v>
+      </c>
+      <c r="L22" t="s">
+        <v>60</v>
+      </c>
+      <c r="M22" t="s">
+        <v>84</v>
+      </c>
+      <c r="N22" t="s">
+        <v>79</v>
+      </c>
+      <c r="O22" t="s">
+        <v>59</v>
+      </c>
+      <c r="P22" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q22" t="s">
         <v>95</v>
       </c>
-      <c r="J21" t="s">
-        <v>93</v>
-      </c>
-      <c r="K21" t="s">
+      <c r="R22" t="s">
         <v>96</v>
       </c>
-      <c r="L21" t="s">
-        <v>100</v>
-      </c>
-      <c r="M21" t="s">
-        <v>77</v>
-      </c>
-      <c r="N21" t="s">
-        <v>100</v>
-      </c>
-      <c r="O21" t="s">
+      <c r="S22" t="s">
+        <v>59</v>
+      </c>
+      <c r="T22" t="s">
+        <v>87</v>
+      </c>
+      <c r="U22" t="s">
         <v>96</v>
       </c>
-      <c r="P21" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>70</v>
-      </c>
-      <c r="R21" t="s">
-        <v>85</v>
-      </c>
-      <c r="S21" t="s">
-        <v>96</v>
-      </c>
-      <c r="T21" t="s">
-        <v>58</v>
-      </c>
-      <c r="U21" t="s">
-        <v>58</v>
-      </c>
-      <c r="V21" t="s">
-        <v>96</v>
-      </c>
-      <c r="W21" t="s">
-        <v>77</v>
-      </c>
-      <c r="X21" t="s">
-        <v>94</v>
-      </c>
-      <c r="Y21" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z21" t="s">
-        <v>85</v>
-      </c>
-      <c r="AA21" t="s">
-        <v>94</v>
-      </c>
-      <c r="AB21" t="s">
-        <v>90</v>
-      </c>
-      <c r="AC21" t="s">
-        <v>94</v>
-      </c>
-      <c r="AD21" t="s">
-        <v>85</v>
-      </c>
-      <c r="AE21" t="s">
-        <v>90</v>
-      </c>
-      <c r="AF21" t="s">
-        <v>90</v>
-      </c>
-      <c r="AG21" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>75</v>
-      </c>
-      <c r="B22" t="s">
-        <v>88</v>
-      </c>
-      <c r="C22" t="s">
-        <v>71</v>
-      </c>
-      <c r="D22" t="s">
-        <v>71</v>
-      </c>
-      <c r="E22" t="s">
-        <v>101</v>
-      </c>
-      <c r="F22" t="s">
-        <v>70</v>
-      </c>
-      <c r="G22" t="s">
-        <v>77</v>
-      </c>
-      <c r="H22" t="s">
-        <v>93</v>
-      </c>
-      <c r="I22" t="s">
-        <v>70</v>
-      </c>
-      <c r="J22" t="s">
-        <v>77</v>
-      </c>
-      <c r="K22" t="s">
-        <v>58</v>
-      </c>
-      <c r="L22" t="s">
-        <v>96</v>
-      </c>
-      <c r="M22" t="s">
-        <v>82</v>
-      </c>
-      <c r="N22" t="s">
-        <v>77</v>
-      </c>
-      <c r="O22" t="s">
-        <v>58</v>
-      </c>
-      <c r="P22" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>93</v>
-      </c>
-      <c r="R22" t="s">
-        <v>94</v>
-      </c>
-      <c r="S22" t="s">
-        <v>58</v>
-      </c>
-      <c r="T22" t="s">
-        <v>85</v>
-      </c>
-      <c r="U22" t="s">
-        <v>94</v>
-      </c>
       <c r="V22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="W22" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="X22" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="Y22" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="Z22" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AA22" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AG22" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B23" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C23" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D23" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E23" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F23" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G23" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H23" t="s">
+        <v>79</v>
+      </c>
+      <c r="I23" t="s">
+        <v>95</v>
+      </c>
+      <c r="J23" t="s">
+        <v>60</v>
+      </c>
+      <c r="K23" t="s">
+        <v>96</v>
+      </c>
+      <c r="L23" t="s">
+        <v>59</v>
+      </c>
+      <c r="M23" t="s">
+        <v>59</v>
+      </c>
+      <c r="N23" t="s">
+        <v>60</v>
+      </c>
+      <c r="O23" t="s">
+        <v>87</v>
+      </c>
+      <c r="P23" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>103</v>
+      </c>
+      <c r="R23" t="s">
+        <v>92</v>
+      </c>
+      <c r="S23" t="s">
+        <v>96</v>
+      </c>
+      <c r="T23" t="s">
+        <v>96</v>
+      </c>
+      <c r="U23" t="s">
+        <v>92</v>
+      </c>
+      <c r="V23" t="s">
+        <v>96</v>
+      </c>
+      <c r="W23" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y23" t="s">
         <v>77</v>
       </c>
-      <c r="I23" t="s">
-        <v>93</v>
-      </c>
-      <c r="J23" t="s">
-        <v>96</v>
-      </c>
-      <c r="K23" t="s">
-        <v>94</v>
-      </c>
-      <c r="L23" t="s">
-        <v>58</v>
-      </c>
-      <c r="M23" t="s">
-        <v>58</v>
-      </c>
-      <c r="N23" t="s">
-        <v>96</v>
-      </c>
-      <c r="O23" t="s">
-        <v>85</v>
-      </c>
-      <c r="P23" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>102</v>
-      </c>
-      <c r="R23" t="s">
-        <v>90</v>
-      </c>
-      <c r="S23" t="s">
-        <v>94</v>
-      </c>
-      <c r="T23" t="s">
-        <v>94</v>
-      </c>
-      <c r="U23" t="s">
-        <v>90</v>
-      </c>
-      <c r="V23" t="s">
-        <v>94</v>
-      </c>
-      <c r="W23" t="s">
-        <v>90</v>
-      </c>
-      <c r="Y23" t="s">
-        <v>75</v>
-      </c>
       <c r="AA23" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>98</v>
+      </c>
+      <c r="B24" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D24" t="s">
+        <v>100</v>
+      </c>
+      <c r="E24" t="s">
+        <v>103</v>
+      </c>
+      <c r="F24" t="s">
+        <v>84</v>
+      </c>
+      <c r="G24" t="s">
+        <v>59</v>
+      </c>
+      <c r="H24" t="s">
+        <v>60</v>
+      </c>
+      <c r="I24" t="s">
+        <v>60</v>
+      </c>
+      <c r="J24" t="s">
+        <v>96</v>
+      </c>
+      <c r="K24" t="s">
+        <v>92</v>
+      </c>
+      <c r="L24" t="s">
+        <v>65</v>
+      </c>
+      <c r="M24" t="s">
+        <v>96</v>
+      </c>
+      <c r="N24" t="s">
+        <v>96</v>
+      </c>
+      <c r="O24" t="s">
+        <v>92</v>
+      </c>
+      <c r="P24" t="s">
+        <v>96</v>
+      </c>
+      <c r="T24" t="s">
+        <v>94</v>
+      </c>
+      <c r="V24" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA24" t="s">
         <v>97</v>
-      </c>
-      <c r="B24" t="s">
-        <v>71</v>
-      </c>
-      <c r="C24" t="s">
-        <v>92</v>
-      </c>
-      <c r="D24" t="s">
-        <v>99</v>
-      </c>
-      <c r="E24" t="s">
-        <v>102</v>
-      </c>
-      <c r="F24" t="s">
-        <v>82</v>
-      </c>
-      <c r="G24" t="s">
-        <v>58</v>
-      </c>
-      <c r="H24" t="s">
-        <v>96</v>
-      </c>
-      <c r="I24" t="s">
-        <v>96</v>
-      </c>
-      <c r="J24" t="s">
-        <v>94</v>
-      </c>
-      <c r="K24" t="s">
-        <v>90</v>
-      </c>
-      <c r="L24" t="s">
-        <v>94</v>
-      </c>
-      <c r="M24" t="s">
-        <v>94</v>
-      </c>
-      <c r="N24" t="s">
-        <v>94</v>
-      </c>
-      <c r="O24" t="s">
-        <v>90</v>
-      </c>
-      <c r="P24" t="s">
-        <v>94</v>
-      </c>
-      <c r="T24" t="s">
-        <v>92</v>
-      </c>
-      <c r="V24" t="s">
-        <v>92</v>
-      </c>
-      <c r="AA24" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B25" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C25" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D25" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E25" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="F25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G25" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I25" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J25" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="L25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B26" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C26" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D26" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E26" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F26" t="s">
+        <v>96</v>
+      </c>
+      <c r="G26" t="s">
+        <v>92</v>
+      </c>
+      <c r="H26" t="s">
+        <v>87</v>
+      </c>
+      <c r="I26" t="s">
+        <v>96</v>
+      </c>
+      <c r="L26" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>65</v>
+      </c>
+      <c r="B27" t="s">
         <v>94</v>
       </c>
-      <c r="G26" t="s">
-        <v>90</v>
-      </c>
-      <c r="H26" t="s">
-        <v>85</v>
-      </c>
-      <c r="I26" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>63</v>
-      </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
+        <v>95</v>
+      </c>
+      <c r="D27" t="s">
+        <v>65</v>
+      </c>
+      <c r="E27" t="s">
         <v>92</v>
       </c>
-      <c r="C27" t="s">
-        <v>93</v>
-      </c>
-      <c r="D27" t="s">
-        <v>63</v>
-      </c>
-      <c r="E27" t="s">
-        <v>90</v>
-      </c>
       <c r="F27" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H27" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B28" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C28" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D28" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E28" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F28" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>102</v>
+      </c>
+      <c r="B29" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29" t="s">
         <v>101</v>
       </c>
-      <c r="B29" t="s">
-        <v>70</v>
-      </c>
-      <c r="C29" t="s">
-        <v>100</v>
-      </c>
       <c r="D29" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E29" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B31" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C31" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D31" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B32" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C32" t="s">
+        <v>60</v>
+      </c>
+      <c r="D32" t="s">
         <v>96</v>
-      </c>
-      <c r="D32" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B33" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C33" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D33" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="B34" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="C34" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D34" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B35" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C35" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D35" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B36" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C36" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D36" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B37" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B38" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25"/>
@@ -4535,166 +4550,166 @@
   <sheetData>
     <row r="3" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" t="s">
         <v>53</v>
       </c>
-      <c r="C3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E3" t="s">
-        <v>52</v>
-      </c>
       <c r="F3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H3" t="s">
         <v>55</v>
       </c>
-      <c r="G3" t="s">
+      <c r="I3" t="s">
+        <v>67</v>
+      </c>
+      <c r="J3" t="s">
+        <v>64</v>
+      </c>
+      <c r="K3" t="s">
+        <v>68</v>
+      </c>
+      <c r="L3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M3" t="s">
+        <v>57</v>
+      </c>
+      <c r="N3" t="s">
+        <v>69</v>
+      </c>
+      <c r="O3" t="s">
+        <v>74</v>
+      </c>
+      <c r="P3" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>63</v>
+      </c>
+      <c r="R3" t="s">
+        <v>71</v>
+      </c>
+      <c r="S3" t="s">
+        <v>88</v>
+      </c>
+      <c r="T3" t="s">
+        <v>62</v>
+      </c>
+      <c r="U3" t="s">
+        <v>81</v>
+      </c>
+      <c r="V3" t="s">
+        <v>70</v>
+      </c>
+      <c r="W3" t="s">
+        <v>89</v>
+      </c>
+      <c r="X3" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>93</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>82</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>90</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>73</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>83</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>98</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>100</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>97</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>102</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>72</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>95</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>103</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>101</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AX3" t="s">
         <v>59</v>
       </c>
-      <c r="H3" t="s">
-        <v>54</v>
-      </c>
-      <c r="I3" t="s">
-        <v>65</v>
-      </c>
-      <c r="J3" t="s">
-        <v>62</v>
-      </c>
-      <c r="K3" t="s">
-        <v>66</v>
-      </c>
-      <c r="L3" t="s">
-        <v>57</v>
-      </c>
-      <c r="M3" t="s">
-        <v>56</v>
-      </c>
-      <c r="N3" t="s">
-        <v>67</v>
-      </c>
-      <c r="O3" t="s">
-        <v>72</v>
-      </c>
-      <c r="P3" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>61</v>
-      </c>
-      <c r="R3" t="s">
-        <v>69</v>
-      </c>
-      <c r="S3" t="s">
-        <v>86</v>
-      </c>
-      <c r="T3" t="s">
-        <v>60</v>
-      </c>
-      <c r="U3" t="s">
-        <v>79</v>
-      </c>
-      <c r="V3" t="s">
-        <v>68</v>
-      </c>
-      <c r="W3" t="s">
+      <c r="AY3" t="s">
         <v>87</v>
       </c>
-      <c r="X3" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>84</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>83</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>91</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>76</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>88</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>98</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>71</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>81</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>97</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>89</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>99</v>
-      </c>
-      <c r="AN3" t="s">
+      <c r="AZ3" t="s">
+        <v>96</v>
+      </c>
+      <c r="BA3" t="s">
         <v>92</v>
       </c>
-      <c r="AO3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>101</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>70</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>93</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>102</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>100</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>77</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>82</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>96</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>58</v>
-      </c>
-      <c r="AY3" t="s">
-        <v>85</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>94</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>90</v>
-      </c>
       <c r="BB3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
@@ -4720,7 +4735,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I4" t="s">
         <v>1</v>
@@ -4738,7 +4753,7 @@
         <v>11</v>
       </c>
       <c r="N4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O4" t="s">
         <v>13</v>
@@ -4759,7 +4774,7 @@
         <v>2</v>
       </c>
       <c r="U4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="V4" t="s">
         <v>11</v>
@@ -4843,7 +4858,7 @@
         <v>1</v>
       </c>
       <c r="AW4" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="AX4" t="s">
         <v>48</v>
@@ -5912,7 +5927,7 @@
         <v>23</v>
       </c>
       <c r="T12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="V12" t="s">
         <v>0</v>
@@ -6373,7 +6388,7 @@
         <v>34</v>
       </c>
       <c r="R16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T16" t="s">
         <v>18</v>
@@ -6418,7 +6433,7 @@
         <v>2</v>
       </c>
       <c r="AQ16" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="AR16" t="s">
         <v>1</v>
@@ -6442,7 +6457,7 @@
         <v>18</v>
       </c>
       <c r="BA16" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
@@ -6522,7 +6537,7 @@
         <v>0</v>
       </c>
       <c r="AQ17" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="AR17" t="s">
         <v>7</v>
@@ -6546,7 +6561,7 @@
         <v>3</v>
       </c>
       <c r="BA17" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
@@ -6822,7 +6837,7 @@
         <v>2</v>
       </c>
       <c r="AV20" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="AW20" t="s">
         <v>13</v>
@@ -6842,7 +6857,7 @@
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C21" t="s">
         <v>7</v>
@@ -6896,7 +6911,7 @@
         <v>7</v>
       </c>
       <c r="AQ21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AR21" t="s">
         <v>23</v>
@@ -6905,7 +6920,7 @@
         <v>0</v>
       </c>
       <c r="AV21" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AW21" t="s">
         <v>18</v>
@@ -7136,10 +7151,10 @@
         <v>2</v>
       </c>
       <c r="AY24" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="AZ24" t="s">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="BA24" t="s">
         <v>23</v>
@@ -7192,10 +7207,10 @@
         <v>7</v>
       </c>
       <c r="AY25" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="AZ25" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="BA25" t="s">
         <v>3</v>
@@ -7421,831 +7436,831 @@
   <sheetData>
     <row r="3" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" t="s">
         <v>53</v>
       </c>
-      <c r="C3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E3" t="s">
-        <v>52</v>
-      </c>
       <c r="F3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H3" t="s">
         <v>55</v>
       </c>
-      <c r="G3" t="s">
+      <c r="I3" t="s">
+        <v>67</v>
+      </c>
+      <c r="J3" t="s">
+        <v>64</v>
+      </c>
+      <c r="K3" t="s">
+        <v>68</v>
+      </c>
+      <c r="L3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M3" t="s">
+        <v>57</v>
+      </c>
+      <c r="N3" t="s">
+        <v>69</v>
+      </c>
+      <c r="O3" t="s">
+        <v>74</v>
+      </c>
+      <c r="P3" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>63</v>
+      </c>
+      <c r="R3" t="s">
+        <v>71</v>
+      </c>
+      <c r="S3" t="s">
+        <v>88</v>
+      </c>
+      <c r="T3" t="s">
+        <v>62</v>
+      </c>
+      <c r="U3" t="s">
+        <v>81</v>
+      </c>
+      <c r="V3" t="s">
+        <v>70</v>
+      </c>
+      <c r="W3" t="s">
+        <v>89</v>
+      </c>
+      <c r="X3" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>93</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>82</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>90</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>73</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>83</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>98</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>100</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>97</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>102</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>72</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>95</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>103</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>101</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AX3" t="s">
         <v>59</v>
       </c>
-      <c r="H3" t="s">
-        <v>54</v>
-      </c>
-      <c r="I3" t="s">
-        <v>65</v>
-      </c>
-      <c r="J3" t="s">
-        <v>62</v>
-      </c>
-      <c r="K3" t="s">
-        <v>66</v>
-      </c>
-      <c r="L3" t="s">
-        <v>57</v>
-      </c>
-      <c r="M3" t="s">
-        <v>56</v>
-      </c>
-      <c r="N3" t="s">
-        <v>67</v>
-      </c>
-      <c r="O3" t="s">
-        <v>72</v>
-      </c>
-      <c r="P3" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>61</v>
-      </c>
-      <c r="R3" t="s">
-        <v>69</v>
-      </c>
-      <c r="S3" t="s">
-        <v>86</v>
-      </c>
-      <c r="T3" t="s">
-        <v>60</v>
-      </c>
-      <c r="U3" t="s">
-        <v>79</v>
-      </c>
-      <c r="V3" t="s">
-        <v>68</v>
-      </c>
-      <c r="W3" t="s">
+      <c r="AY3" t="s">
         <v>87</v>
       </c>
-      <c r="X3" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>84</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>83</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>91</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>76</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>88</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>98</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>71</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>81</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>97</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>89</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>99</v>
-      </c>
-      <c r="AN3" t="s">
+      <c r="AZ3" t="s">
+        <v>96</v>
+      </c>
+      <c r="BA3" t="s">
         <v>92</v>
       </c>
-      <c r="AO3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>101</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>70</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>93</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>102</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>100</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>77</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>82</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>96</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>58</v>
-      </c>
-      <c r="AY3" t="s">
-        <v>85</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>94</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>90</v>
-      </c>
       <c r="BB3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="R4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="S4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="T4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="U4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="V4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="W4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="X4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Y4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Z4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AA4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AB4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AC4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AD4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AE4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AF4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AG4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AH4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AI4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AJ4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AK4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AL4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AM4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AN4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AO4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AP4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AQ4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AR4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AS4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AT4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AU4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AV4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AW4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AX4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AY4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AZ4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="BA4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="BB4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="R5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="T5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="V5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="W5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="X5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Y5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Z5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AA5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AB5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AC5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AD5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AE5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AF5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AH5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AI5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AJ5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AK5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AL5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AN5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AO5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AQ5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AR5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AS5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AT5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AU5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AV5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AW5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AX5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AY5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AZ5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="BA5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="R6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="T6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="V6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="W6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="X6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Z6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AA6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AB6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AD6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AE6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AF6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AH6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AI6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AJ6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AK6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AL6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AN6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AQ6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AR6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AT6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AU6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AV6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AW6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AX6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AY6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AZ6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="BA6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="R7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="T7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="V7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="X7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Z7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AA7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AB7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AD7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AE7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AF7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AH7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AI7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AJ7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AO7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AQ7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AR7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AU7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AV7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AW7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AX7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AY7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AZ7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="BA7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C8" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="R8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="T8" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="X8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AA8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AB8" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AE8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AF8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AH8" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AI8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AJ8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AN8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AO8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AQ8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AR8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AU8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AV8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AW8" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AX8" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AY8" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AZ8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="BA8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="T9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="X9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AB9" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AF9" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AI9" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AJ9" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AO9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AV9" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AW9" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AX9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AY9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AZ9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="BA9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="41:53" x14ac:dyDescent="0.25">
       <c r="AO10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" spans="41:41" x14ac:dyDescent="0.25"/>

--- a/data/ICEHLdelegacije.xlsx
+++ b/data/ICEHLdelegacije.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2112" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2087" uniqueCount="320">
   <si>
     <t>PiragicTr</t>
   </si>
@@ -213,7 +213,7 @@
     <t>2024-10-06</t>
   </si>
   <si>
-    <t>zbrisano</t>
+    <t>2024-12-08</t>
   </si>
   <si>
     <t>2024-11-01</t>
@@ -234,7 +234,7 @@
     <t>2024-10-22</t>
   </si>
   <si>
-    <t>2024-12-08</t>
+    <t>2024-12-18</t>
   </si>
   <si>
     <t>2024-11-27</t>
@@ -252,12 +252,12 @@
     <t>2024-11-24</t>
   </si>
   <si>
+    <t>2024-12-20</t>
+  </si>
+  <si>
     <t>2024-11-20</t>
   </si>
   <si>
-    <t>2024-12-18</t>
-  </si>
-  <si>
     <t>2024-10-19</t>
   </si>
   <si>
@@ -270,9 +270,6 @@
     <t>2024-11-29</t>
   </si>
   <si>
-    <t>2024-12-20</t>
-  </si>
-  <si>
     <t>2024-11-03</t>
   </si>
   <si>
@@ -288,6 +285,9 @@
     <t>2024-10-29</t>
   </si>
   <si>
+    <t>2024-12-06</t>
+  </si>
+  <si>
     <t>2024-11-22</t>
   </si>
   <si>
@@ -309,9 +309,6 @@
     <t>2024-12-30</t>
   </si>
   <si>
-    <t>2024-12-06</t>
-  </si>
-  <si>
     <t>2024-11-30</t>
   </si>
   <si>
@@ -591,7 +588,7 @@
     <t>ZBRISANO</t>
   </si>
   <si>
-    <t>Eishalle Feldkirch;NikolicMa;SeewaldEl;FleischmannLu;NotheggerDa</t>
+    <t>Eishalle Feldkirch;NikolicMa;SeewaldEl;FleischmannLu;SeewaldJe</t>
   </si>
   <si>
     <t>Eisarena Salzburg;NikolicKr;OfnerCh;BedynekSe;MoidlMa</t>
@@ -615,7 +612,7 @@
     <t>Stadthalle Villach;HronskyTo;PiragicTr;BedynekSe;KoncDa</t>
   </si>
   <si>
-    <t>Gabor Ocskay Eisarena;NagyAt;ZrnicMi;HribarMa;ZgoncGa</t>
+    <t>Gabor Ocskay Eisarena;PiragicTr;ZrnicMi;HribarMa;ZgoncGa</t>
   </si>
   <si>
     <t>Hala Tivoli;PiragicTr;RezekGr;HribarMa;VacziDa</t>
@@ -723,13 +720,13 @@
     <t>Tiroler Wasserkraft Arena;BernekerTh;HolzerTo;SparerDa;WeissAl</t>
   </si>
   <si>
-    <t>Eishalle;RezekGr;SeewaldEl;NotheggerDa;PuffWo</t>
+    <t>Eishalle;SeewaldEl;SoosDa;MuzsikNo;NotheggerDa</t>
   </si>
   <si>
     <t>Hala Tivoli;GroznikBo;SoosDa;MuzsikNo;VacziDa</t>
   </si>
   <si>
-    <t>Merkur Eisstadion Graz;PiragicTr;SoosDa;BärnthalerCh;VacziDa</t>
+    <t>Merkur Eisstadion Graz;NagyAt;SoosDa;BärnthalerCh;VacziDa</t>
   </si>
   <si>
     <t>Gabor Ocskay Eisarena;FichtnerPa;SmetanaLa;KoncDa;MuzsikNo</t>
@@ -837,7 +834,7 @@
     <t>Eisarena Salzburg;HronskyTo;SternatCh;JedlickaPe;SeewaldJe</t>
   </si>
   <si>
-    <t>Tiroler Wasserkraft Arena;NikolicMa;NikolicKr;MartinFl;SparerDa</t>
+    <t>Tiroler Wasserkraft Arena;NikolicKr;NikolicMa;MartinFl;SparerDa</t>
   </si>
   <si>
     <t>Eishalle Bruneck;BernekerTh;HuberAn;MartinFl;PardatscherUl</t>
@@ -963,7 +960,7 @@
     <t>Sparkasse Arena Bozen;GroznikBo;OfnerCh;MantovaniDa;RigoniDa</t>
   </si>
   <si>
-    <t>Hala Tivoli;PiragicTr;SoosDa;HribarMa;MuzsikNo</t>
+    <t>Hala Tivoli;PiragicTr;RezekGr;HribarMa;PuffWo</t>
   </si>
   <si>
     <t>Sparkasse Arena Bozen;OfnerCh;ZrnicMi;MantovaniDa;PardatscherUl</t>
@@ -1355,8 +1352,8 @@
   <sheetData>
     <row r="2" ht="14.45" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A2">
-        <f>COUNTIF(A4:A100,"&lt;&gt;")</f>
-        <v>35</v>
+        <f>COUNTIF(A4:A98,"&lt;&gt;")</f>
+        <v>36</v>
       </c>
       <c r="B2">
         <f>COUNTIF(B4:B100,"&lt;&gt;")</f>
@@ -1367,16 +1364,16 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <f>COUNTIF(D4:D100,"&lt;&gt;")</f>
-        <v>30</v>
+        <f>COUNTIF(D4:D96,"&lt;&gt;")</f>
+        <v>28</v>
       </c>
       <c r="E2">
-        <f>COUNTIF(E4:E99,"&lt;&gt;")</f>
-        <v>24</v>
+        <f>COUNTIF(E4:E98,"&lt;&gt;")</f>
+        <v>25</v>
       </c>
       <c r="F2">
         <f>COUNTIF(F4:F100,"&lt;&gt;")</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2">
         <f>COUNTIF(G4:G100,"&lt;&gt;")</f>
@@ -1384,10 +1381,10 @@
       </c>
       <c r="H2">
         <f>COUNTIF(H4:H100,"&lt;&gt;")</f>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I2">
-        <f>COUNTIF(I4:I100,"&lt;&gt;")</f>
+        <f>COUNTIF(I4:I99,"&lt;&gt;")</f>
         <v>23</v>
       </c>
       <c r="J2">
@@ -1399,8 +1396,8 @@
         <v>21</v>
       </c>
       <c r="L2">
-        <f>COUNTIF(L4:L100,"&lt;&gt;")</f>
-        <v>21</v>
+        <f>COUNTIF(L4:L99,"&lt;&gt;")</f>
+        <v>22</v>
       </c>
       <c r="M2">
         <f>COUNTIF(M4:M100,"&lt;&gt;")</f>
@@ -1432,7 +1429,7 @@
       </c>
       <c r="T2">
         <f>COUNTIF(T4:T99,"&lt;&gt;")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U2">
         <f t="shared" ref="U2:Z2" si="0">COUNTIF(U4:U100,"&lt;&gt;")</f>
@@ -1440,7 +1437,7 @@
       </c>
       <c r="V2">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W2">
         <f t="shared" si="0"/>
@@ -1452,14 +1449,14 @@
       </c>
       <c r="Y2">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Z2">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="AA2">
-        <f>COUNTIF(AA4:AA99,"&lt;&gt;")</f>
+        <f>COUNTIF(AA4:AA97,"&lt;&gt;")</f>
         <v>19</v>
       </c>
       <c r="AB2">
@@ -1471,28 +1468,28 @@
         <v>18</v>
       </c>
       <c r="AD2">
-        <f>COUNTIF(AD4:AD96,"&lt;&gt;")</f>
-        <v>18</v>
+        <f>COUNTIF(AD4:AD95,"&lt;&gt;")</f>
+        <v>17</v>
       </c>
       <c r="AE2">
-        <f>COUNTIF(AE4:AE100,"&lt;&gt;")</f>
-        <v>18</v>
+        <f>COUNTIF(AE4:AE99,"&lt;&gt;")</f>
+        <v>17</v>
       </c>
       <c r="AF2">
         <f>COUNTIF(AF4:AF100,"&lt;&gt;")</f>
         <v>18</v>
       </c>
       <c r="AG2">
-        <f>COUNTIF(AG4:AG95,"&lt;&gt;")</f>
+        <f>COUNTIF(AG4:AG93,"&lt;&gt;")</f>
         <v>17</v>
       </c>
       <c r="AH2">
-        <f>COUNTIF(AH4:AH99,"&lt;&gt;")</f>
-        <v>17</v>
+        <f>COUNTIF(AH4:AH97,"&lt;&gt;")</f>
+        <v>16</v>
       </c>
       <c r="AI2">
-        <f>COUNTIF(AI4:AI98,"&lt;&gt;")</f>
-        <v>17</v>
+        <f>COUNTIF(AI4:AI96,"&lt;&gt;")</f>
+        <v>15</v>
       </c>
       <c r="AJ2">
         <f>COUNTIF(AJ4:AJ99,"&lt;&gt;")</f>
@@ -1504,39 +1501,39 @@
       </c>
       <c r="AL2">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AM2">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(AM4:AM99,"&lt;&gt;")</f>
         <v>11</v>
       </c>
       <c r="AN2">
         <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="AO2">
+        <f>COUNTIF(AO4:AO98,"&lt;&gt;")</f>
         <v>8</v>
-      </c>
-      <c r="AO2">
-        <f t="shared" si="1"/>
-        <v>7</v>
       </c>
       <c r="AP2">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="AQ2">
-        <f t="shared" si="1"/>
-        <v>5</v>
+        <f>COUNTIF(AQ4:AQ99,"&lt;&gt;")</f>
+        <v>4</v>
       </c>
       <c r="AR2">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="AS2">
-        <f t="shared" si="1"/>
-        <v>5</v>
+        <f>COUNTIF(AS4:AS99,"&lt;&gt;")</f>
+        <v>4</v>
       </c>
       <c r="AT2">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU2">
         <f t="shared" si="1"/>
@@ -2255,19 +2252,16 @@
         <v>77</v>
       </c>
       <c r="AQ7" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="AR7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AS7" t="s">
-        <v>79</v>
-      </c>
-      <c r="AT7" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>55</v>
       </c>
@@ -2394,17 +2388,11 @@
       <c r="AP8" t="s">
         <v>59</v>
       </c>
-      <c r="AQ8" t="s">
-        <v>84</v>
-      </c>
       <c r="AR8" t="s">
-        <v>84</v>
-      </c>
-      <c r="AS8" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>68</v>
       </c>
@@ -2484,7 +2472,7 @@
         <v>62</v>
       </c>
       <c r="AA9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB9" t="s">
         <v>74</v>
@@ -2493,7 +2481,7 @@
         <v>74</v>
       </c>
       <c r="AD9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE9" t="s">
         <v>66</v>
@@ -2511,25 +2499,25 @@
         <v>74</v>
       </c>
       <c r="AJ9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AK9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AL9" t="s">
         <v>66</v>
       </c>
       <c r="AM9" t="s">
+        <v>79</v>
+      </c>
+      <c r="AN9" t="s">
         <v>78</v>
-      </c>
-      <c r="AN9" t="s">
-        <v>84</v>
       </c>
       <c r="AO9" t="s">
         <v>65</v>
       </c>
       <c r="AP9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
@@ -2549,7 +2537,7 @@
         <v>53</v>
       </c>
       <c r="F10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G10" t="s">
         <v>74</v>
@@ -2579,7 +2567,7 @@
         <v>62</v>
       </c>
       <c r="P10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Q10" t="s">
         <v>62</v>
@@ -2588,7 +2576,7 @@
         <v>71</v>
       </c>
       <c r="S10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="T10" t="s">
         <v>62</v>
@@ -2597,10 +2585,10 @@
         <v>71</v>
       </c>
       <c r="V10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="W10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="X10" t="s">
         <v>71</v>
@@ -2624,22 +2612,22 @@
         <v>82</v>
       </c>
       <c r="AE10" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF10" t="s">
         <v>85</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>86</v>
       </c>
       <c r="AG10" t="s">
         <v>71</v>
       </c>
       <c r="AH10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI10" t="s">
         <v>63</v>
       </c>
       <c r="AJ10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AK10" t="s">
         <v>70</v>
@@ -2648,13 +2636,13 @@
         <v>77</v>
       </c>
       <c r="AM10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AO10" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
@@ -2683,7 +2671,7 @@
         <v>63</v>
       </c>
       <c r="I11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J11" t="s">
         <v>62</v>
@@ -2704,7 +2692,7 @@
         <v>70</v>
       </c>
       <c r="P11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Q11" t="s">
         <v>66</v>
@@ -2734,19 +2722,19 @@
         <v>62</v>
       </c>
       <c r="Z11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AA11" t="s">
         <v>90</v>
       </c>
       <c r="AB11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AC11" t="s">
         <v>66</v>
       </c>
       <c r="AD11" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="AE11" t="s">
         <v>55</v>
@@ -2758,7 +2746,7 @@
         <v>90</v>
       </c>
       <c r="AH11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI11" t="s">
         <v>90</v>
@@ -2779,7 +2767,7 @@
         <v>92</v>
       </c>
       <c r="AO11" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
@@ -2799,7 +2787,7 @@
         <v>63</v>
       </c>
       <c r="F12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G12" t="s">
         <v>62</v>
@@ -2829,31 +2817,31 @@
         <v>66</v>
       </c>
       <c r="P12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R12" t="s">
         <v>70</v>
       </c>
       <c r="S12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="T12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U12" t="s">
         <v>66</v>
       </c>
       <c r="V12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W12" t="s">
         <v>76</v>
       </c>
       <c r="X12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y12" t="s">
         <v>70</v>
@@ -2865,13 +2853,13 @@
         <v>77</v>
       </c>
       <c r="AB12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AC12" t="s">
         <v>75</v>
       </c>
       <c r="AD12" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AE12" t="s">
         <v>75</v>
@@ -2886,7 +2874,7 @@
         <v>77</v>
       </c>
       <c r="AI12" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="AJ12" t="s">
         <v>77</v>
@@ -2903,11 +2891,8 @@
       <c r="AN12" t="s">
         <v>96</v>
       </c>
-      <c r="AO12" t="s">
-        <v>97</v>
-      </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>71</v>
       </c>
@@ -2918,7 +2903,7 @@
         <v>70</v>
       </c>
       <c r="D13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E13" t="s">
         <v>70</v>
@@ -2936,7 +2921,7 @@
         <v>82</v>
       </c>
       <c r="J13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K13" t="s">
         <v>74</v>
@@ -2963,7 +2948,7 @@
         <v>75</v>
       </c>
       <c r="S13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T13" t="s">
         <v>76</v>
@@ -2993,10 +2978,10 @@
         <v>90</v>
       </c>
       <c r="AC13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AD13" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="AE13" t="s">
         <v>77</v>
@@ -3011,7 +2996,7 @@
         <v>73</v>
       </c>
       <c r="AI13" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="AJ13" t="s">
         <v>83</v>
@@ -3020,16 +3005,16 @@
         <v>83</v>
       </c>
       <c r="AL13" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="AM13" t="s">
         <v>60</v>
       </c>
-      <c r="AO13" t="s">
-        <v>73</v>
+      <c r="AN13" t="s">
+        <v>65</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>62</v>
       </c>
@@ -3037,19 +3022,19 @@
         <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D14" t="s">
         <v>66</v>
       </c>
       <c r="E14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H14" t="s">
         <v>66</v>
@@ -3073,7 +3058,7 @@
         <v>82</v>
       </c>
       <c r="O14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P14" t="s">
         <v>90</v>
@@ -3091,7 +3076,7 @@
         <v>90</v>
       </c>
       <c r="U14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="V14" t="s">
         <v>75</v>
@@ -3100,13 +3085,13 @@
         <v>73</v>
       </c>
       <c r="X14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Y14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Z14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AA14" t="s">
         <v>94</v>
@@ -3118,7 +3103,7 @@
         <v>90</v>
       </c>
       <c r="AD14" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AE14" t="s">
         <v>91</v>
@@ -3130,22 +3115,22 @@
         <v>94</v>
       </c>
       <c r="AH14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AI14" t="s">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="AJ14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AL14" t="s">
         <v>60</v>
       </c>
       <c r="AM14" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
@@ -3153,13 +3138,13 @@
         <v>70</v>
       </c>
       <c r="B15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C15" t="s">
         <v>66</v>
       </c>
       <c r="D15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E15" t="s">
         <v>66</v>
@@ -3186,7 +3171,7 @@
         <v>82</v>
       </c>
       <c r="M15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N15" t="s">
         <v>90</v>
@@ -3195,7 +3180,7 @@
         <v>90</v>
       </c>
       <c r="P15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q15" t="s">
         <v>93</v>
@@ -3228,7 +3213,7 @@
         <v>73</v>
       </c>
       <c r="AA15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AB15" t="s">
         <v>83</v>
@@ -3237,7 +3222,7 @@
         <v>73</v>
       </c>
       <c r="AD15" t="s">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="AE15" t="s">
         <v>94</v>
@@ -3246,36 +3231,33 @@
         <v>76</v>
       </c>
       <c r="AG15" t="s">
+        <v>87</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>72</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK15" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL15" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>88</v>
-      </c>
-      <c r="AH15" t="s">
-        <v>97</v>
-      </c>
-      <c r="AI15" t="s">
-        <v>97</v>
-      </c>
-      <c r="AJ15" t="s">
-        <v>72</v>
-      </c>
-      <c r="AK15" t="s">
-        <v>72</v>
-      </c>
-      <c r="AL15" t="s">
-        <v>87</v>
-      </c>
-      <c r="AM15" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>89</v>
       </c>
       <c r="B16" t="s">
         <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D16" t="s">
         <v>75</v>
@@ -3290,7 +3272,7 @@
         <v>76</v>
       </c>
       <c r="H16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I16" t="s">
         <v>73</v>
@@ -3302,7 +3284,7 @@
         <v>90</v>
       </c>
       <c r="L16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M16" t="s">
         <v>77</v>
@@ -3320,22 +3302,22 @@
         <v>82</v>
       </c>
       <c r="R16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S16" t="s">
         <v>73</v>
       </c>
       <c r="T16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="U16" t="s">
         <v>73</v>
       </c>
       <c r="V16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="W16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="X16" t="s">
         <v>83</v>
@@ -3347,37 +3329,37 @@
         <v>83</v>
       </c>
       <c r="AA16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AB16" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="AC16" t="s">
         <v>91</v>
       </c>
       <c r="AD16" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="AE16" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="AF16" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="AG16" t="s">
+        <v>95</v>
+      </c>
+      <c r="AH16" t="s">
         <v>65</v>
       </c>
-      <c r="AH16" t="s">
-        <v>72</v>
-      </c>
       <c r="AI16" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="AJ16" t="s">
         <v>60</v>
       </c>
       <c r="AK16" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="AL16" t="s">
         <v>90</v>
@@ -3388,7 +3370,7 @@
         <v>66</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C17" t="s">
         <v>76</v>
@@ -3409,10 +3391,10 @@
         <v>77</v>
       </c>
       <c r="I17" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J17" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K17" t="s">
         <v>83</v>
@@ -3442,13 +3424,13 @@
         <v>91</v>
       </c>
       <c r="T17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="U17" t="s">
         <v>83</v>
       </c>
       <c r="V17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="W17" t="s">
         <v>93</v>
@@ -3460,40 +3442,40 @@
         <v>83</v>
       </c>
       <c r="Z17" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AA17" t="s">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="AB17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AC17" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="AD17" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="AE17" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="AF17" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="AG17" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AH17" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="AI17" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="AJ17" t="s">
         <v>59</v>
       </c>
       <c r="AK17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
@@ -3555,55 +3537,55 @@
         <v>95</v>
       </c>
       <c r="T18" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="U18" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="V18" t="s">
+        <v>101</v>
+      </c>
+      <c r="W18" t="s">
+        <v>89</v>
+      </c>
+      <c r="X18" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA18" t="s">
         <v>102</v>
-      </c>
-      <c r="W18" t="s">
-        <v>97</v>
-      </c>
-      <c r="X18" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y18" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z18" t="s">
-        <v>72</v>
-      </c>
-      <c r="AA18" t="s">
-        <v>95</v>
       </c>
       <c r="AB18" t="s">
         <v>60</v>
       </c>
       <c r="AC18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AD18" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AE18" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="AF18" t="s">
         <v>59</v>
       </c>
       <c r="AG18" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="AH18" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="AI18" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="AJ18" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AK18" t="s">
         <v>92</v>
@@ -3623,7 +3605,7 @@
         <v>82</v>
       </c>
       <c r="E19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F19" t="s">
         <v>83</v>
@@ -3632,10 +3614,10 @@
         <v>83</v>
       </c>
       <c r="H19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I19" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="J19" t="s">
         <v>94</v>
@@ -3644,75 +3626,72 @@
         <v>95</v>
       </c>
       <c r="L19" t="s">
+        <v>65</v>
+      </c>
+      <c r="M19" t="s">
+        <v>89</v>
+      </c>
+      <c r="N19" t="s">
+        <v>89</v>
+      </c>
+      <c r="O19" t="s">
+        <v>100</v>
+      </c>
+      <c r="P19" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>97</v>
+      </c>
+      <c r="R19" t="s">
+        <v>89</v>
+      </c>
+      <c r="S19" t="s">
+        <v>102</v>
+      </c>
+      <c r="T19" t="s">
+        <v>78</v>
+      </c>
+      <c r="U19" t="s">
         <v>72</v>
       </c>
-      <c r="M19" t="s">
-        <v>97</v>
-      </c>
-      <c r="N19" t="s">
-        <v>97</v>
-      </c>
-      <c r="O19" t="s">
-        <v>101</v>
-      </c>
-      <c r="P19" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>98</v>
-      </c>
-      <c r="R19" t="s">
-        <v>97</v>
-      </c>
-      <c r="S19" t="s">
-        <v>103</v>
-      </c>
-      <c r="T19" t="s">
-        <v>84</v>
-      </c>
-      <c r="U19" t="s">
-        <v>79</v>
-      </c>
       <c r="V19" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="W19" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="X19" t="s">
         <v>95</v>
       </c>
       <c r="Y19" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="Z19" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="AA19" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="AB19" t="s">
         <v>59</v>
       </c>
       <c r="AC19" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="AD19" t="s">
-        <v>101</v>
+        <v>59</v>
       </c>
       <c r="AE19" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="AF19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AG19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AH19" t="s">
-        <v>87</v>
-      </c>
-      <c r="AI19" t="s">
         <v>96</v>
       </c>
       <c r="AJ19" t="s">
@@ -3739,55 +3718,55 @@
         <v>94</v>
       </c>
       <c r="G20" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="H20" t="s">
         <v>75</v>
       </c>
       <c r="I20" t="s">
+        <v>89</v>
+      </c>
+      <c r="J20" t="s">
+        <v>89</v>
+      </c>
+      <c r="K20" t="s">
         <v>78</v>
-      </c>
-      <c r="J20" t="s">
-        <v>97</v>
-      </c>
-      <c r="K20" t="s">
-        <v>84</v>
       </c>
       <c r="L20" t="s">
         <v>95</v>
       </c>
       <c r="M20" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="N20" t="s">
         <v>95</v>
       </c>
       <c r="O20" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="P20" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="Q20" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="R20" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="S20" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="T20" t="s">
         <v>60</v>
       </c>
       <c r="U20" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="V20" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="W20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="X20" t="s">
         <v>60</v>
@@ -3796,37 +3775,31 @@
         <v>60</v>
       </c>
       <c r="Z20" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="AA20" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="AB20" t="s">
         <v>96</v>
       </c>
       <c r="AC20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AD20" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="AE20" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="AF20" t="s">
         <v>96</v>
       </c>
       <c r="AG20" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH20" t="s">
-        <v>92</v>
-      </c>
-      <c r="AI20" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>90</v>
       </c>
@@ -3834,25 +3807,25 @@
         <v>82</v>
       </c>
       <c r="C21" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D21" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E21" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F21" t="s">
         <v>70</v>
       </c>
       <c r="G21" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H21" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="I21" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="J21" t="s">
         <v>95</v>
@@ -3861,25 +3834,25 @@
         <v>60</v>
       </c>
       <c r="L21" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M21" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="N21" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O21" t="s">
         <v>60</v>
       </c>
       <c r="P21" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="Q21" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="R21" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="S21" t="s">
         <v>60</v>
@@ -3894,7 +3867,7 @@
         <v>60</v>
       </c>
       <c r="W21" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="X21" t="s">
         <v>96</v>
@@ -3903,10 +3876,10 @@
         <v>59</v>
       </c>
       <c r="Z21" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AA21" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="AB21" t="s">
         <v>92</v>
@@ -3914,23 +3887,11 @@
       <c r="AC21" t="s">
         <v>96</v>
       </c>
-      <c r="AD21" t="s">
-        <v>87</v>
-      </c>
-      <c r="AE21" t="s">
-        <v>92</v>
-      </c>
       <c r="AF21" t="s">
         <v>92</v>
       </c>
-      <c r="AG21" t="s">
-        <v>65</v>
-      </c>
-      <c r="AH21" t="s">
-        <v>96</v>
-      </c>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>77</v>
       </c>
@@ -3944,22 +3905,22 @@
         <v>73</v>
       </c>
       <c r="E22" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F22" t="s">
+        <v>65</v>
+      </c>
+      <c r="G22" t="s">
         <v>72</v>
-      </c>
-      <c r="G22" t="s">
-        <v>79</v>
       </c>
       <c r="H22" t="s">
         <v>95</v>
       </c>
       <c r="I22" t="s">
+        <v>95</v>
+      </c>
+      <c r="J22" t="s">
         <v>72</v>
-      </c>
-      <c r="J22" t="s">
-        <v>79</v>
       </c>
       <c r="K22" t="s">
         <v>59</v>
@@ -3968,10 +3929,10 @@
         <v>60</v>
       </c>
       <c r="M22" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="N22" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="O22" t="s">
         <v>59</v>
@@ -3989,7 +3950,7 @@
         <v>59</v>
       </c>
       <c r="T22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="U22" t="s">
         <v>96</v>
@@ -4004,19 +3965,16 @@
         <v>92</v>
       </c>
       <c r="Y22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Z22" t="s">
         <v>92</v>
       </c>
       <c r="AA22" t="s">
-        <v>92</v>
-      </c>
-      <c r="AG22" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>83</v>
       </c>
@@ -4036,13 +3994,13 @@
         <v>95</v>
       </c>
       <c r="G23" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H23" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="I23" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="J23" t="s">
         <v>60</v>
@@ -4060,13 +4018,13 @@
         <v>60</v>
       </c>
       <c r="O23" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P23" t="s">
         <v>59</v>
       </c>
       <c r="Q23" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="R23" t="s">
         <v>92</v>
@@ -4089,13 +4047,10 @@
       <c r="Y23" t="s">
         <v>77</v>
       </c>
-      <c r="AA23" t="s">
-        <v>65</v>
-      </c>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B24" t="s">
         <v>73</v>
@@ -4104,13 +4059,13 @@
         <v>94</v>
       </c>
       <c r="D24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E24" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F24" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="G24" t="s">
         <v>59</v>
@@ -4119,7 +4074,7 @@
         <v>60</v>
       </c>
       <c r="I24" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="J24" t="s">
         <v>96</v>
@@ -4128,7 +4083,7 @@
         <v>92</v>
       </c>
       <c r="L24" t="s">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="M24" t="s">
         <v>96</v>
@@ -4148,11 +4103,8 @@
       <c r="V24" t="s">
         <v>94</v>
       </c>
-      <c r="AA24" t="s">
-        <v>97</v>
-      </c>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>91</v>
       </c>
@@ -4160,10 +4112,10 @@
         <v>83</v>
       </c>
       <c r="C25" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D25" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="E25" t="s">
         <v>60</v>
@@ -4172,36 +4124,36 @@
         <v>59</v>
       </c>
       <c r="G25" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H25" t="s">
         <v>59</v>
       </c>
       <c r="I25" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="J25" t="s">
         <v>92</v>
       </c>
       <c r="L25" t="s">
-        <v>104</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B26" t="s">
         <v>91</v>
       </c>
       <c r="C26" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D26" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="E26" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F26" t="s">
         <v>96</v>
@@ -4210,18 +4162,15 @@
         <v>92</v>
       </c>
       <c r="H26" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I26" t="s">
-        <v>96</v>
-      </c>
-      <c r="L26" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="B27" t="s">
         <v>94</v>
@@ -4230,7 +4179,7 @@
         <v>95</v>
       </c>
       <c r="D27" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E27" t="s">
         <v>92</v>
@@ -4239,30 +4188,27 @@
         <v>92</v>
       </c>
       <c r="H27" t="s">
-        <v>72</v>
-      </c>
-      <c r="I27" t="s">
-        <v>104</v>
+        <v>65</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B28" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C28" t="s">
+        <v>102</v>
+      </c>
+      <c r="D28" t="s">
+        <v>86</v>
+      </c>
+      <c r="E28" t="s">
         <v>103</v>
       </c>
-      <c r="D28" t="s">
+      <c r="F28" t="s">
         <v>79</v>
-      </c>
-      <c r="E28" t="s">
-        <v>65</v>
-      </c>
-      <c r="F28" t="s">
-        <v>78</v>
       </c>
       <c r="H28" t="s">
         <v>94</v>
@@ -4273,91 +4219,79 @@
         <v>102</v>
       </c>
       <c r="B29" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C29" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D29" t="s">
-        <v>84</v>
-      </c>
-      <c r="E29" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B30" t="s">
         <v>95</v>
       </c>
       <c r="C30" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D30" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="B31" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C31" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D31" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B32" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C32" t="s">
         <v>60</v>
       </c>
-      <c r="D32" t="s">
-        <v>96</v>
-      </c>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="B33" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C33" t="s">
         <v>59</v>
       </c>
-      <c r="D33" t="s">
-        <v>92</v>
-      </c>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B34" t="s">
         <v>60</v>
       </c>
       <c r="C34" t="s">
-        <v>87</v>
-      </c>
-      <c r="D34" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B35" t="s">
         <v>59</v>
@@ -4365,27 +4299,21 @@
       <c r="C35" t="s">
         <v>96</v>
       </c>
-      <c r="D35" t="s">
-        <v>97</v>
-      </c>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="B36" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C36" t="s">
         <v>92</v>
       </c>
-      <c r="D36" t="s">
-        <v>65</v>
-      </c>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B37" t="s">
         <v>96</v>
@@ -4393,7 +4321,7 @@
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="B38" t="s">
         <v>92</v>
@@ -4401,20 +4329,12 @@
     </row>
     <row r="39" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="43" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="44" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="45" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4604,7 +4524,7 @@
         <v>71</v>
       </c>
       <c r="S3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="T3" t="s">
         <v>62</v>
@@ -4616,16 +4536,16 @@
         <v>70</v>
       </c>
       <c r="W3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="X3" t="s">
         <v>66</v>
       </c>
       <c r="Y3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Z3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA3" t="s">
         <v>75</v>
@@ -4640,13 +4560,13 @@
         <v>82</v>
       </c>
       <c r="AE3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AF3" t="s">
         <v>90</v>
       </c>
       <c r="AG3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AH3" t="s">
         <v>77</v>
@@ -4658,40 +4578,40 @@
         <v>83</v>
       </c>
       <c r="AK3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AL3" t="s">
         <v>91</v>
       </c>
       <c r="AM3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AN3" t="s">
         <v>94</v>
       </c>
       <c r="AO3" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="AP3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AQ3" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="AR3" t="s">
         <v>95</v>
       </c>
       <c r="AS3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AT3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AU3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="AV3" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="AW3" t="s">
         <v>60</v>
@@ -4700,7 +4620,7 @@
         <v>59</v>
       </c>
       <c r="AY3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AZ3" t="s">
         <v>96</v>
@@ -4709,7 +4629,7 @@
         <v>92</v>
       </c>
       <c r="BB3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
@@ -4735,7 +4655,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I4" t="s">
         <v>1</v>
@@ -4753,7 +4673,7 @@
         <v>11</v>
       </c>
       <c r="N4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="O4" t="s">
         <v>13</v>
@@ -4774,7 +4694,7 @@
         <v>2</v>
       </c>
       <c r="U4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="V4" t="s">
         <v>11</v>
@@ -5490,7 +5410,7 @@
         <v>18</v>
       </c>
       <c r="AY8" t="s">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="s">
         <v>0</v>
@@ -5859,7 +5779,7 @@
         <v>17</v>
       </c>
       <c r="AQ11" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="AR11" t="s">
         <v>38</v>
@@ -5927,7 +5847,7 @@
         <v>23</v>
       </c>
       <c r="T12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="V12" t="s">
         <v>0</v>
@@ -5993,13 +5913,13 @@
         <v>28</v>
       </c>
       <c r="AW12" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="AX12" t="s">
         <v>5</v>
       </c>
       <c r="AY12" t="s">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AZ12" t="s">
         <v>13</v>
@@ -6109,7 +6029,7 @@
         <v>43</v>
       </c>
       <c r="AW13" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="AX13" t="s">
         <v>35</v>
@@ -6225,7 +6145,7 @@
         <v>20</v>
       </c>
       <c r="AW14" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AX14" t="s">
         <v>27</v>
@@ -6341,7 +6261,7 @@
         <v>37</v>
       </c>
       <c r="AW15" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="AX15" t="s">
         <v>31</v>
@@ -6388,7 +6308,7 @@
         <v>34</v>
       </c>
       <c r="R16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T16" t="s">
         <v>18</v>
@@ -6457,7 +6377,7 @@
         <v>18</v>
       </c>
       <c r="BA16" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
@@ -6561,7 +6481,7 @@
         <v>3</v>
       </c>
       <c r="BA17" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
@@ -6857,7 +6777,7 @@
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C21" t="s">
         <v>7</v>
@@ -7201,7 +7121,7 @@
         <v>2</v>
       </c>
       <c r="AW25" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="AX25" t="s">
         <v>7</v>
@@ -7313,7 +7233,7 @@
         <v>25</v>
       </c>
       <c r="AW27" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AX27" t="s">
         <v>12</v>
@@ -7328,7 +7248,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="41:53" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="15" customHeight="1" spans="48:53" x14ac:dyDescent="0.25"/>
     <row r="29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -7490,7 +7410,7 @@
         <v>71</v>
       </c>
       <c r="S3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="T3" t="s">
         <v>62</v>
@@ -7502,16 +7422,16 @@
         <v>70</v>
       </c>
       <c r="W3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="X3" t="s">
         <v>66</v>
       </c>
       <c r="Y3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Z3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA3" t="s">
         <v>75</v>
@@ -7526,13 +7446,13 @@
         <v>82</v>
       </c>
       <c r="AE3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AF3" t="s">
         <v>90</v>
       </c>
       <c r="AG3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AH3" t="s">
         <v>77</v>
@@ -7544,40 +7464,40 @@
         <v>83</v>
       </c>
       <c r="AK3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AL3" t="s">
         <v>91</v>
       </c>
       <c r="AM3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AN3" t="s">
         <v>94</v>
       </c>
       <c r="AO3" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="AP3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AQ3" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="AR3" t="s">
         <v>95</v>
       </c>
       <c r="AS3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AT3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AU3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="AV3" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="AW3" t="s">
         <v>60</v>
@@ -7586,7 +7506,7 @@
         <v>59</v>
       </c>
       <c r="AY3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AZ3" t="s">
         <v>96</v>
@@ -7595,675 +7515,675 @@
         <v>92</v>
       </c>
       <c r="BB3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B4" t="s">
         <v>106</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>107</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>108</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>109</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>110</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>111</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>112</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>113</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>114</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>115</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>116</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>117</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>118</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>119</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>120</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>121</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
         <v>122</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S4" t="s">
         <v>123</v>
       </c>
-      <c r="S4" t="s">
+      <c r="T4" t="s">
         <v>124</v>
       </c>
-      <c r="T4" t="s">
+      <c r="U4" t="s">
         <v>125</v>
       </c>
-      <c r="U4" t="s">
+      <c r="V4" t="s">
         <v>126</v>
       </c>
-      <c r="V4" t="s">
+      <c r="W4" t="s">
         <v>127</v>
       </c>
-      <c r="W4" t="s">
+      <c r="X4" t="s">
         <v>128</v>
       </c>
-      <c r="X4" t="s">
+      <c r="Y4" t="s">
         <v>129</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Z4" t="s">
         <v>130</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AA4" t="s">
         <v>131</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AB4" t="s">
         <v>132</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AC4" t="s">
         <v>133</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AD4" t="s">
         <v>134</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AE4" t="s">
         <v>135</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AF4" t="s">
         <v>136</v>
       </c>
-      <c r="AF4" t="s">
+      <c r="AG4" t="s">
         <v>137</v>
       </c>
-      <c r="AG4" t="s">
+      <c r="AH4" t="s">
         <v>138</v>
       </c>
-      <c r="AH4" t="s">
+      <c r="AI4" t="s">
         <v>139</v>
       </c>
-      <c r="AI4" t="s">
+      <c r="AJ4" t="s">
         <v>140</v>
       </c>
-      <c r="AJ4" t="s">
+      <c r="AK4" t="s">
         <v>141</v>
       </c>
-      <c r="AK4" t="s">
+      <c r="AL4" t="s">
         <v>142</v>
       </c>
-      <c r="AL4" t="s">
+      <c r="AM4" t="s">
         <v>143</v>
       </c>
-      <c r="AM4" t="s">
+      <c r="AN4" t="s">
         <v>144</v>
       </c>
-      <c r="AN4" t="s">
+      <c r="AO4" t="s">
         <v>145</v>
       </c>
-      <c r="AO4" t="s">
+      <c r="AP4" t="s">
         <v>146</v>
       </c>
-      <c r="AP4" t="s">
+      <c r="AQ4" t="s">
         <v>147</v>
       </c>
-      <c r="AQ4" t="s">
+      <c r="AR4" t="s">
         <v>148</v>
       </c>
-      <c r="AR4" t="s">
+      <c r="AS4" t="s">
         <v>149</v>
       </c>
-      <c r="AS4" t="s">
+      <c r="AT4" t="s">
         <v>150</v>
       </c>
-      <c r="AT4" t="s">
+      <c r="AU4" t="s">
         <v>151</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AV4" t="s">
         <v>152</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AW4" t="s">
         <v>153</v>
       </c>
-      <c r="AW4" t="s">
+      <c r="AX4" t="s">
         <v>154</v>
       </c>
-      <c r="AX4" t="s">
+      <c r="AY4" t="s">
         <v>155</v>
       </c>
-      <c r="AY4" t="s">
+      <c r="AZ4" t="s">
         <v>156</v>
       </c>
-      <c r="AZ4" t="s">
+      <c r="BA4" t="s">
         <v>157</v>
       </c>
-      <c r="BA4" t="s">
+      <c r="BB4" t="s">
         <v>158</v>
-      </c>
-      <c r="BB4" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C5" t="s">
         <v>160</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
         <v>161</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>162</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>163</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>164</v>
       </c>
-      <c r="H5" t="s">
+      <c r="J5" t="s">
         <v>165</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>166</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>167</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>168</v>
       </c>
-      <c r="M5" t="s">
+      <c r="O5" t="s">
         <v>169</v>
       </c>
-      <c r="O5" t="s">
+      <c r="Q5" t="s">
         <v>170</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="R5" t="s">
         <v>171</v>
       </c>
-      <c r="R5" t="s">
+      <c r="T5" t="s">
         <v>172</v>
       </c>
-      <c r="T5" t="s">
+      <c r="V5" t="s">
         <v>173</v>
       </c>
-      <c r="V5" t="s">
+      <c r="W5" t="s">
         <v>174</v>
       </c>
-      <c r="W5" t="s">
+      <c r="X5" t="s">
         <v>175</v>
       </c>
-      <c r="X5" t="s">
+      <c r="Y5" t="s">
         <v>176</v>
       </c>
-      <c r="Y5" t="s">
+      <c r="Z5" t="s">
         <v>177</v>
       </c>
-      <c r="Z5" t="s">
+      <c r="AA5" t="s">
         <v>178</v>
       </c>
-      <c r="AA5" t="s">
+      <c r="AB5" t="s">
         <v>179</v>
       </c>
-      <c r="AB5" t="s">
+      <c r="AC5" t="s">
         <v>180</v>
       </c>
-      <c r="AC5" t="s">
+      <c r="AD5" t="s">
         <v>181</v>
       </c>
-      <c r="AD5" t="s">
+      <c r="AE5" t="s">
         <v>182</v>
       </c>
-      <c r="AE5" t="s">
+      <c r="AF5" t="s">
         <v>183</v>
       </c>
-      <c r="AF5" t="s">
+      <c r="AH5" t="s">
         <v>184</v>
       </c>
-      <c r="AH5" t="s">
+      <c r="AI5" t="s">
         <v>185</v>
       </c>
-      <c r="AI5" t="s">
+      <c r="AJ5" t="s">
         <v>186</v>
       </c>
-      <c r="AJ5" t="s">
+      <c r="AK5" t="s">
         <v>187</v>
       </c>
-      <c r="AK5" t="s">
+      <c r="AL5" t="s">
         <v>188</v>
       </c>
-      <c r="AL5" t="s">
+      <c r="AN5" t="s">
         <v>189</v>
       </c>
-      <c r="AN5" t="s">
+      <c r="AO5" t="s">
+        <v>189</v>
+      </c>
+      <c r="AQ5" t="s">
         <v>190</v>
       </c>
-      <c r="AO5" t="s">
-        <v>190</v>
-      </c>
-      <c r="AQ5" t="s">
+      <c r="AR5" t="s">
         <v>191</v>
       </c>
-      <c r="AR5" t="s">
+      <c r="AS5" t="s">
         <v>192</v>
       </c>
-      <c r="AS5" t="s">
+      <c r="AT5" t="s">
         <v>193</v>
       </c>
-      <c r="AT5" t="s">
+      <c r="AU5" t="s">
         <v>194</v>
       </c>
-      <c r="AU5" t="s">
+      <c r="AV5" t="s">
         <v>195</v>
       </c>
-      <c r="AV5" t="s">
+      <c r="AW5" t="s">
         <v>196</v>
       </c>
-      <c r="AW5" t="s">
+      <c r="AX5" t="s">
         <v>197</v>
       </c>
-      <c r="AX5" t="s">
+      <c r="AY5" t="s">
         <v>198</v>
       </c>
-      <c r="AY5" t="s">
+      <c r="AZ5" t="s">
         <v>199</v>
       </c>
-      <c r="AZ5" t="s">
+      <c r="BA5" t="s">
         <v>200</v>
-      </c>
-      <c r="BA5" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>201</v>
+      </c>
+      <c r="C6" t="s">
         <v>202</v>
       </c>
-      <c r="C6" t="s">
+      <c r="E6" t="s">
         <v>203</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>204</v>
       </c>
-      <c r="F6" t="s">
+      <c r="H6" t="s">
         <v>205</v>
       </c>
-      <c r="H6" t="s">
+      <c r="J6" t="s">
         <v>206</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>207</v>
       </c>
-      <c r="K6" t="s">
+      <c r="M6" t="s">
         <v>208</v>
       </c>
-      <c r="M6" t="s">
+      <c r="O6" t="s">
         <v>209</v>
       </c>
-      <c r="O6" t="s">
+      <c r="Q6" t="s">
         <v>210</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="R6" t="s">
         <v>211</v>
       </c>
-      <c r="R6" t="s">
+      <c r="T6" t="s">
         <v>212</v>
       </c>
-      <c r="T6" t="s">
+      <c r="V6" t="s">
         <v>213</v>
       </c>
-      <c r="V6" t="s">
+      <c r="W6" t="s">
         <v>214</v>
       </c>
-      <c r="W6" t="s">
+      <c r="X6" t="s">
         <v>215</v>
       </c>
-      <c r="X6" t="s">
+      <c r="Z6" t="s">
         <v>216</v>
       </c>
-      <c r="Z6" t="s">
+      <c r="AA6" t="s">
         <v>217</v>
       </c>
-      <c r="AA6" t="s">
+      <c r="AB6" t="s">
         <v>218</v>
       </c>
-      <c r="AB6" t="s">
+      <c r="AD6" t="s">
         <v>219</v>
       </c>
-      <c r="AD6" t="s">
+      <c r="AE6" t="s">
         <v>220</v>
       </c>
-      <c r="AE6" t="s">
+      <c r="AF6" t="s">
         <v>221</v>
       </c>
-      <c r="AF6" t="s">
+      <c r="AH6" t="s">
         <v>222</v>
       </c>
-      <c r="AH6" t="s">
+      <c r="AI6" t="s">
         <v>223</v>
       </c>
-      <c r="AI6" t="s">
+      <c r="AJ6" t="s">
         <v>224</v>
       </c>
-      <c r="AJ6" t="s">
+      <c r="AK6" t="s">
         <v>225</v>
       </c>
-      <c r="AK6" t="s">
+      <c r="AL6" t="s">
         <v>226</v>
       </c>
-      <c r="AL6" t="s">
+      <c r="AN6" t="s">
         <v>227</v>
       </c>
-      <c r="AN6" t="s">
+      <c r="AO6" t="s">
         <v>228</v>
       </c>
-      <c r="AO6" t="s">
+      <c r="AQ6" t="s">
         <v>229</v>
       </c>
-      <c r="AQ6" t="s">
+      <c r="AR6" t="s">
         <v>230</v>
       </c>
-      <c r="AR6" t="s">
+      <c r="AT6" t="s">
         <v>231</v>
       </c>
-      <c r="AT6" t="s">
+      <c r="AU6" t="s">
         <v>232</v>
       </c>
-      <c r="AU6" t="s">
+      <c r="AV6" t="s">
         <v>233</v>
       </c>
-      <c r="AV6" t="s">
+      <c r="AW6" t="s">
         <v>234</v>
       </c>
-      <c r="AW6" t="s">
+      <c r="AX6" t="s">
         <v>235</v>
       </c>
-      <c r="AX6" t="s">
+      <c r="AY6" t="s">
         <v>236</v>
       </c>
-      <c r="AY6" t="s">
+      <c r="AZ6" t="s">
         <v>237</v>
       </c>
-      <c r="AZ6" t="s">
+      <c r="BA6" t="s">
         <v>238</v>
-      </c>
-      <c r="BA6" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>239</v>
+      </c>
+      <c r="C7" t="s">
         <v>240</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
         <v>241</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>242</v>
       </c>
-      <c r="F7" t="s">
+      <c r="H7" t="s">
         <v>243</v>
       </c>
-      <c r="H7" t="s">
+      <c r="J7" t="s">
         <v>244</v>
       </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
         <v>245</v>
       </c>
-      <c r="K7" t="s">
+      <c r="M7" t="s">
         <v>246</v>
       </c>
-      <c r="M7" t="s">
+      <c r="O7" t="s">
         <v>247</v>
       </c>
-      <c r="O7" t="s">
+      <c r="Q7" t="s">
         <v>248</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="R7" t="s">
         <v>249</v>
       </c>
-      <c r="R7" t="s">
+      <c r="T7" t="s">
         <v>250</v>
       </c>
-      <c r="T7" t="s">
+      <c r="V7" t="s">
         <v>251</v>
       </c>
-      <c r="V7" t="s">
+      <c r="X7" t="s">
         <v>252</v>
       </c>
-      <c r="X7" t="s">
+      <c r="Z7" t="s">
         <v>253</v>
       </c>
-      <c r="Z7" t="s">
+      <c r="AA7" t="s">
         <v>254</v>
       </c>
-      <c r="AA7" t="s">
+      <c r="AB7" t="s">
         <v>255</v>
       </c>
-      <c r="AB7" t="s">
+      <c r="AD7" t="s">
         <v>256</v>
       </c>
-      <c r="AD7" t="s">
+      <c r="AE7" t="s">
         <v>257</v>
       </c>
-      <c r="AE7" t="s">
+      <c r="AF7" t="s">
         <v>258</v>
       </c>
-      <c r="AF7" t="s">
+      <c r="AH7" t="s">
         <v>259</v>
       </c>
-      <c r="AH7" t="s">
+      <c r="AI7" t="s">
         <v>260</v>
       </c>
-      <c r="AI7" t="s">
+      <c r="AJ7" t="s">
         <v>261</v>
       </c>
-      <c r="AJ7" t="s">
+      <c r="AN7" t="s">
         <v>262</v>
       </c>
-      <c r="AN7" t="s">
+      <c r="AO7" t="s">
         <v>263</v>
       </c>
-      <c r="AO7" t="s">
+      <c r="AQ7" t="s">
         <v>264</v>
       </c>
-      <c r="AQ7" t="s">
+      <c r="AR7" t="s">
         <v>265</v>
       </c>
-      <c r="AR7" t="s">
+      <c r="AU7" t="s">
         <v>266</v>
       </c>
-      <c r="AU7" t="s">
+      <c r="AV7" t="s">
         <v>267</v>
       </c>
-      <c r="AV7" t="s">
+      <c r="AW7" t="s">
         <v>268</v>
       </c>
-      <c r="AW7" t="s">
+      <c r="AX7" t="s">
         <v>269</v>
       </c>
-      <c r="AX7" t="s">
+      <c r="AY7" t="s">
         <v>270</v>
       </c>
-      <c r="AY7" t="s">
+      <c r="AZ7" t="s">
         <v>271</v>
       </c>
-      <c r="AZ7" t="s">
+      <c r="BA7" t="s">
         <v>272</v>
-      </c>
-      <c r="BA7" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>273</v>
+      </c>
+      <c r="C8" t="s">
         <v>274</v>
       </c>
-      <c r="C8" t="s">
+      <c r="E8" t="s">
         <v>275</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>276</v>
       </c>
-      <c r="F8" t="s">
+      <c r="H8" t="s">
         <v>277</v>
       </c>
-      <c r="H8" t="s">
+      <c r="K8" t="s">
         <v>278</v>
       </c>
-      <c r="K8" t="s">
+      <c r="O8" t="s">
         <v>279</v>
       </c>
-      <c r="O8" t="s">
+      <c r="Q8" t="s">
         <v>280</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="R8" t="s">
         <v>281</v>
       </c>
-      <c r="R8" t="s">
+      <c r="T8" t="s">
         <v>282</v>
       </c>
-      <c r="T8" t="s">
+      <c r="X8" t="s">
         <v>283</v>
       </c>
-      <c r="X8" t="s">
+      <c r="AA8" t="s">
         <v>284</v>
       </c>
-      <c r="AA8" t="s">
+      <c r="AB8" t="s">
         <v>285</v>
       </c>
-      <c r="AB8" t="s">
+      <c r="AE8" t="s">
+        <v>189</v>
+      </c>
+      <c r="AF8" t="s">
         <v>286</v>
       </c>
-      <c r="AE8" t="s">
-        <v>190</v>
-      </c>
-      <c r="AF8" t="s">
+      <c r="AH8" t="s">
         <v>287</v>
       </c>
-      <c r="AH8" t="s">
+      <c r="AI8" t="s">
         <v>288</v>
       </c>
-      <c r="AI8" t="s">
+      <c r="AJ8" t="s">
         <v>289</v>
       </c>
-      <c r="AJ8" t="s">
+      <c r="AN8" t="s">
         <v>290</v>
       </c>
-      <c r="AN8" t="s">
+      <c r="AO8" t="s">
         <v>291</v>
       </c>
-      <c r="AO8" t="s">
+      <c r="AQ8" t="s">
         <v>292</v>
       </c>
-      <c r="AQ8" t="s">
+      <c r="AR8" t="s">
         <v>293</v>
       </c>
-      <c r="AR8" t="s">
+      <c r="AU8" t="s">
         <v>294</v>
       </c>
-      <c r="AU8" t="s">
+      <c r="AV8" t="s">
         <v>295</v>
       </c>
-      <c r="AV8" t="s">
+      <c r="AW8" t="s">
         <v>296</v>
       </c>
-      <c r="AW8" t="s">
+      <c r="AX8" t="s">
         <v>297</v>
       </c>
-      <c r="AX8" t="s">
+      <c r="AY8" t="s">
         <v>298</v>
       </c>
-      <c r="AY8" t="s">
+      <c r="AZ8" t="s">
         <v>299</v>
       </c>
-      <c r="AZ8" t="s">
+      <c r="BA8" t="s">
         <v>300</v>
-      </c>
-      <c r="BA8" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>301</v>
+      </c>
+      <c r="E9" t="s">
         <v>302</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>303</v>
       </c>
-      <c r="F9" t="s">
+      <c r="H9" t="s">
         <v>304</v>
       </c>
-      <c r="H9" t="s">
+      <c r="O9" t="s">
         <v>305</v>
       </c>
-      <c r="O9" t="s">
+      <c r="T9" t="s">
         <v>306</v>
       </c>
-      <c r="T9" t="s">
+      <c r="X9" t="s">
         <v>307</v>
       </c>
-      <c r="X9" t="s">
+      <c r="AB9" t="s">
         <v>308</v>
       </c>
-      <c r="AB9" t="s">
+      <c r="AF9" t="s">
         <v>309</v>
       </c>
-      <c r="AF9" t="s">
+      <c r="AI9" t="s">
         <v>310</v>
       </c>
-      <c r="AI9" t="s">
+      <c r="AJ9" t="s">
         <v>311</v>
       </c>
-      <c r="AJ9" t="s">
+      <c r="AO9" t="s">
         <v>312</v>
       </c>
-      <c r="AO9" t="s">
+      <c r="AV9" t="s">
         <v>313</v>
       </c>
-      <c r="AV9" t="s">
+      <c r="AW9" t="s">
         <v>314</v>
       </c>
-      <c r="AW9" t="s">
+      <c r="AX9" t="s">
         <v>315</v>
       </c>
-      <c r="AX9" t="s">
+      <c r="AY9" t="s">
         <v>316</v>
       </c>
-      <c r="AY9" t="s">
+      <c r="AZ9" t="s">
         <v>317</v>
       </c>
-      <c r="AZ9" t="s">
+      <c r="BA9" t="s">
         <v>318</v>
-      </c>
-      <c r="BA9" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="41:53" x14ac:dyDescent="0.25">
       <c r="AO10" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="41:41" x14ac:dyDescent="0.25"/>
+    <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="13" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="14" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/data/ICEHLdelegacije.xlsx
+++ b/data/ICEHLdelegacije.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2087" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2089" uniqueCount="322">
   <si>
     <t>PiragicTr</t>
   </si>
@@ -168,6 +168,9 @@
     <t>HeadSc</t>
   </si>
   <si>
+    <t>LazzeriAl</t>
+  </si>
+  <si>
     <t>2024-09-20</t>
   </si>
   <si>
@@ -198,6 +201,9 @@
     <t>2024-12-26</t>
   </si>
   <si>
+    <t>zbrisano</t>
+  </si>
+  <si>
     <t>2024-12-22</t>
   </si>
   <si>
@@ -477,7 +483,7 @@
     <t>Merkur Eisstadion Graz;SmetanaLa;SternatCh;JedlickaPe;KoncDa</t>
   </si>
   <si>
-    <t>Eishalle Asiago;HeadSc;OfnerCh;MantovaniDa;WeissAl</t>
+    <t>Eishalle Asiago;LazzeriAl;OfnerCh;MantovaniDa;WeissAl</t>
   </si>
   <si>
     <t>Linz AG Eisarena;HlavatyAl;SmetanaLa;BärnthalerCh;ZacherlPa</t>
@@ -1293,7 +1299,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:AY134"/>
+  <dimension ref="A2:AZ134"/>
   <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.28515625" customWidth="1"/>
@@ -1540,7 +1546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -1691,2645 +1697,2651 @@
       <c r="AX3" t="s">
         <v>49</v>
       </c>
+      <c r="AY3" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K4" t="s">
+        <v>53</v>
+      </c>
+      <c r="L4" t="s">
         <v>51</v>
       </c>
-      <c r="K4" t="s">
+      <c r="M4" t="s">
+        <v>51</v>
+      </c>
+      <c r="N4" t="s">
+        <v>53</v>
+      </c>
+      <c r="O4" t="s">
+        <v>54</v>
+      </c>
+      <c r="P4" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>53</v>
+      </c>
+      <c r="R4" t="s">
+        <v>51</v>
+      </c>
+      <c r="S4" t="s">
+        <v>51</v>
+      </c>
+      <c r="T4" t="s">
+        <v>53</v>
+      </c>
+      <c r="U4" t="s">
+        <v>55</v>
+      </c>
+      <c r="V4" t="s">
+        <v>51</v>
+      </c>
+      <c r="W4" t="s">
+        <v>53</v>
+      </c>
+      <c r="X4" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>53</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>53</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>53</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>53</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>58</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>53</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>61</v>
+      </c>
+      <c r="AY4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" t="s">
+        <v>54</v>
+      </c>
+      <c r="H5" t="s">
+        <v>53</v>
+      </c>
+      <c r="I5" t="s">
+        <v>54</v>
+      </c>
+      <c r="J5" t="s">
+        <v>57</v>
+      </c>
+      <c r="K5" t="s">
         <v>52</v>
       </c>
-      <c r="L4" t="s">
-        <v>50</v>
-      </c>
-      <c r="M4" t="s">
-        <v>50</v>
-      </c>
-      <c r="N4" t="s">
+      <c r="L5" t="s">
+        <v>54</v>
+      </c>
+      <c r="M5" t="s">
+        <v>54</v>
+      </c>
+      <c r="N5" t="s">
         <v>52</v>
       </c>
-      <c r="O4" t="s">
+      <c r="O5" t="s">
+        <v>57</v>
+      </c>
+      <c r="P5" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>56</v>
+      </c>
+      <c r="R5" t="s">
         <v>53</v>
       </c>
-      <c r="P4" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q4" t="s">
+      <c r="S5" t="s">
+        <v>54</v>
+      </c>
+      <c r="T5" t="s">
+        <v>54</v>
+      </c>
+      <c r="U5" t="s">
+        <v>63</v>
+      </c>
+      <c r="V5" t="s">
+        <v>55</v>
+      </c>
+      <c r="W5" t="s">
+        <v>54</v>
+      </c>
+      <c r="X5" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>54</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>57</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>63</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>57</v>
+      </c>
+      <c r="AL5" t="s">
         <v>52</v>
       </c>
-      <c r="R4" t="s">
-        <v>50</v>
-      </c>
-      <c r="S4" t="s">
-        <v>50</v>
-      </c>
-      <c r="T4" t="s">
-        <v>52</v>
-      </c>
-      <c r="U4" t="s">
-        <v>54</v>
-      </c>
-      <c r="V4" t="s">
-        <v>50</v>
-      </c>
-      <c r="W4" t="s">
-        <v>52</v>
-      </c>
-      <c r="X4" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>52</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>52</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>52</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>52</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>53</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>52</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>55</v>
-      </c>
-      <c r="AN4" t="s">
+      <c r="AM5" t="s">
+        <v>58</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>59</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>65</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AR5" t="s">
         <v>56</v>
       </c>
-      <c r="AO4" t="s">
-        <v>56</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>52</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>52</v>
-      </c>
-      <c r="AS4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AT4" t="s">
-        <v>58</v>
-      </c>
-      <c r="AU4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>55</v>
-      </c>
-      <c r="AW4" t="s">
-        <v>59</v>
-      </c>
-      <c r="AX4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D5" t="s">
-        <v>52</v>
-      </c>
-      <c r="E5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G5" t="s">
-        <v>53</v>
-      </c>
-      <c r="H5" t="s">
-        <v>52</v>
-      </c>
-      <c r="I5" t="s">
-        <v>53</v>
-      </c>
-      <c r="J5" t="s">
-        <v>56</v>
-      </c>
-      <c r="K5" t="s">
-        <v>51</v>
-      </c>
-      <c r="L5" t="s">
-        <v>53</v>
-      </c>
-      <c r="M5" t="s">
-        <v>53</v>
-      </c>
-      <c r="N5" t="s">
-        <v>51</v>
-      </c>
-      <c r="O5" t="s">
-        <v>56</v>
-      </c>
-      <c r="P5" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>55</v>
-      </c>
-      <c r="R5" t="s">
-        <v>52</v>
-      </c>
-      <c r="S5" t="s">
-        <v>53</v>
-      </c>
-      <c r="T5" t="s">
-        <v>53</v>
-      </c>
-      <c r="U5" t="s">
-        <v>61</v>
-      </c>
-      <c r="V5" t="s">
-        <v>54</v>
-      </c>
-      <c r="W5" t="s">
-        <v>53</v>
-      </c>
-      <c r="X5" t="s">
-        <v>56</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>53</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>53</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>56</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>53</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>56</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>56</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>61</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>53</v>
-      </c>
-      <c r="AH5" t="s">
-        <v>55</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>53</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>61</v>
-      </c>
-      <c r="AK5" t="s">
-        <v>56</v>
-      </c>
-      <c r="AL5" t="s">
-        <v>51</v>
-      </c>
-      <c r="AM5" t="s">
-        <v>57</v>
-      </c>
-      <c r="AN5" t="s">
-        <v>62</v>
-      </c>
-      <c r="AO5" t="s">
-        <v>58</v>
-      </c>
-      <c r="AP5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AQ5" t="s">
-        <v>64</v>
-      </c>
-      <c r="AR5" t="s">
-        <v>55</v>
-      </c>
       <c r="AS5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AT5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" t="s">
+        <v>57</v>
+      </c>
+      <c r="F6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G6" t="s">
+        <v>57</v>
+      </c>
+      <c r="H6" t="s">
+        <v>57</v>
+      </c>
+      <c r="I6" t="s">
+        <v>57</v>
+      </c>
+      <c r="J6" t="s">
+        <v>66</v>
+      </c>
+      <c r="K6" t="s">
+        <v>57</v>
+      </c>
+      <c r="L6" t="s">
+        <v>57</v>
+      </c>
+      <c r="M6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N6" t="s">
+        <v>57</v>
+      </c>
+      <c r="O6" t="s">
+        <v>66</v>
+      </c>
+      <c r="P6" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>69</v>
+      </c>
+      <c r="R6" t="s">
         <v>56</v>
       </c>
-      <c r="B6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="S6" t="s">
         <v>56</v>
       </c>
-      <c r="F6" t="s">
-        <v>53</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="T6" t="s">
+        <v>57</v>
+      </c>
+      <c r="U6" t="s">
         <v>56</v>
       </c>
-      <c r="H6" t="s">
+      <c r="V6" t="s">
+        <v>54</v>
+      </c>
+      <c r="W6" t="s">
         <v>56</v>
       </c>
-      <c r="I6" t="s">
+      <c r="X6" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y6" t="s">
         <v>56</v>
       </c>
-      <c r="J6" t="s">
+      <c r="Z6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>71</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AO6" t="s">
         <v>64</v>
       </c>
-      <c r="K6" t="s">
-        <v>56</v>
-      </c>
-      <c r="L6" t="s">
-        <v>56</v>
-      </c>
-      <c r="M6" t="s">
-        <v>56</v>
-      </c>
-      <c r="N6" t="s">
-        <v>56</v>
-      </c>
-      <c r="O6" t="s">
-        <v>64</v>
-      </c>
-      <c r="P6" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>67</v>
-      </c>
-      <c r="R6" t="s">
-        <v>55</v>
-      </c>
-      <c r="S6" t="s">
-        <v>55</v>
-      </c>
-      <c r="T6" t="s">
-        <v>56</v>
-      </c>
-      <c r="U6" t="s">
-        <v>55</v>
-      </c>
-      <c r="V6" t="s">
-        <v>53</v>
-      </c>
-      <c r="W6" t="s">
-        <v>55</v>
-      </c>
-      <c r="X6" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>55</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>55</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>55</v>
-      </c>
-      <c r="AD6" t="s">
+      <c r="AP6" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ6" t="s">
         <v>68</v>
       </c>
-      <c r="AE6" t="s">
-        <v>68</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>57</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>55</v>
-      </c>
-      <c r="AH6" t="s">
-        <v>69</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>55</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>64</v>
-      </c>
-      <c r="AK6" t="s">
-        <v>55</v>
-      </c>
-      <c r="AL6" t="s">
-        <v>56</v>
-      </c>
-      <c r="AM6" t="s">
-        <v>63</v>
-      </c>
-      <c r="AN6" t="s">
-        <v>70</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>62</v>
-      </c>
-      <c r="AP6" t="s">
-        <v>71</v>
-      </c>
-      <c r="AQ6" t="s">
-        <v>66</v>
-      </c>
       <c r="AR6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="AS6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AT6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F7" t="s">
+        <v>66</v>
+      </c>
+      <c r="G7" t="s">
+        <v>63</v>
+      </c>
+      <c r="H7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I7" t="s">
+        <v>66</v>
+      </c>
+      <c r="J7" t="s">
+        <v>70</v>
+      </c>
+      <c r="K7" t="s">
+        <v>66</v>
+      </c>
+      <c r="L7" t="s">
         <v>56</v>
       </c>
-      <c r="C7" t="s">
+      <c r="M7" t="s">
         <v>56</v>
       </c>
-      <c r="D7" t="s">
+      <c r="N7" t="s">
         <v>56</v>
       </c>
-      <c r="E7" t="s">
-        <v>61</v>
-      </c>
-      <c r="F7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G7" t="s">
-        <v>61</v>
-      </c>
-      <c r="H7" t="s">
-        <v>64</v>
-      </c>
-      <c r="I7" t="s">
-        <v>64</v>
-      </c>
-      <c r="J7" t="s">
-        <v>68</v>
-      </c>
-      <c r="K7" t="s">
-        <v>64</v>
-      </c>
-      <c r="L7" t="s">
-        <v>55</v>
-      </c>
-      <c r="M7" t="s">
-        <v>55</v>
-      </c>
-      <c r="N7" t="s">
-        <v>55</v>
-      </c>
       <c r="O7" t="s">
+        <v>58</v>
+      </c>
+      <c r="P7" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>59</v>
+      </c>
+      <c r="R7" t="s">
+        <v>58</v>
+      </c>
+      <c r="S7" t="s">
+        <v>66</v>
+      </c>
+      <c r="T7" t="s">
+        <v>70</v>
+      </c>
+      <c r="U7" t="s">
+        <v>69</v>
+      </c>
+      <c r="V7" t="s">
         <v>57</v>
       </c>
-      <c r="P7" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q7" t="s">
+      <c r="W7" t="s">
+        <v>70</v>
+      </c>
+      <c r="X7" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>66</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>70</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>76</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>65</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>66</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI7" t="s">
         <v>58</v>
       </c>
-      <c r="R7" t="s">
-        <v>57</v>
-      </c>
-      <c r="S7" t="s">
-        <v>64</v>
-      </c>
-      <c r="T7" t="s">
-        <v>68</v>
-      </c>
-      <c r="U7" t="s">
-        <v>67</v>
-      </c>
-      <c r="V7" t="s">
-        <v>56</v>
-      </c>
-      <c r="W7" t="s">
-        <v>68</v>
-      </c>
-      <c r="X7" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>68</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>64</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>68</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>64</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>68</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>74</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>63</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>74</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>64</v>
-      </c>
-      <c r="AH7" t="s">
-        <v>71</v>
-      </c>
-      <c r="AI7" t="s">
-        <v>57</v>
-      </c>
       <c r="AJ7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AL7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AM7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="AN7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AO7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AP7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AQ7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AR7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AS7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G8" t="s">
+        <v>58</v>
+      </c>
+      <c r="H8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I8" t="s">
+        <v>76</v>
+      </c>
+      <c r="J8" t="s">
+        <v>58</v>
+      </c>
+      <c r="K8" t="s">
+        <v>71</v>
+      </c>
+      <c r="L8" t="s">
+        <v>58</v>
+      </c>
+      <c r="M8" t="s">
+        <v>58</v>
+      </c>
+      <c r="N8" t="s">
+        <v>70</v>
+      </c>
+      <c r="O8" t="s">
+        <v>82</v>
+      </c>
+      <c r="P8" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>58</v>
+      </c>
+      <c r="R8" t="s">
+        <v>54</v>
+      </c>
+      <c r="S8" t="s">
+        <v>70</v>
+      </c>
+      <c r="T8" t="s">
+        <v>58</v>
+      </c>
+      <c r="U8" t="s">
+        <v>66</v>
+      </c>
+      <c r="V8" t="s">
+        <v>70</v>
+      </c>
+      <c r="W8" t="s">
+        <v>71</v>
+      </c>
+      <c r="X8" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA8" t="s">
         <v>64</v>
       </c>
-      <c r="D8" t="s">
-        <v>55</v>
-      </c>
-      <c r="E8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F8" t="s">
-        <v>57</v>
-      </c>
-      <c r="G8" t="s">
-        <v>57</v>
-      </c>
-      <c r="H8" t="s">
+      <c r="AB8" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD8" t="s">
         <v>68</v>
       </c>
-      <c r="I8" t="s">
-        <v>74</v>
-      </c>
-      <c r="J8" t="s">
-        <v>57</v>
-      </c>
-      <c r="K8" t="s">
-        <v>69</v>
-      </c>
-      <c r="L8" t="s">
-        <v>57</v>
-      </c>
-      <c r="M8" t="s">
-        <v>57</v>
-      </c>
-      <c r="N8" t="s">
-        <v>68</v>
-      </c>
-      <c r="O8" t="s">
+      <c r="AE8" t="s">
+        <v>83</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>73</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>70</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>71</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>76</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>76</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>84</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>77</v>
+      </c>
+      <c r="AP8" t="s">
+        <v>60</v>
+      </c>
+      <c r="AR8" t="s">
         <v>80</v>
-      </c>
-      <c r="P8" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>57</v>
-      </c>
-      <c r="R8" t="s">
-        <v>53</v>
-      </c>
-      <c r="S8" t="s">
-        <v>68</v>
-      </c>
-      <c r="T8" t="s">
-        <v>57</v>
-      </c>
-      <c r="U8" t="s">
-        <v>64</v>
-      </c>
-      <c r="V8" t="s">
-        <v>68</v>
-      </c>
-      <c r="W8" t="s">
-        <v>69</v>
-      </c>
-      <c r="X8" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>71</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>62</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC8" t="s">
-        <v>57</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>66</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>81</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>71</v>
-      </c>
-      <c r="AG8" t="s">
-        <v>68</v>
-      </c>
-      <c r="AH8" t="s">
-        <v>62</v>
-      </c>
-      <c r="AI8" t="s">
-        <v>69</v>
-      </c>
-      <c r="AJ8" t="s">
-        <v>63</v>
-      </c>
-      <c r="AK8" t="s">
-        <v>74</v>
-      </c>
-      <c r="AL8" t="s">
-        <v>74</v>
-      </c>
-      <c r="AM8" t="s">
-        <v>82</v>
-      </c>
-      <c r="AN8" t="s">
-        <v>83</v>
-      </c>
-      <c r="AO8" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP8" t="s">
-        <v>59</v>
-      </c>
-      <c r="AR8" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9" t="s">
+        <v>70</v>
+      </c>
+      <c r="H9" t="s">
+        <v>58</v>
+      </c>
+      <c r="I9" t="s">
+        <v>65</v>
+      </c>
+      <c r="J9" t="s">
+        <v>76</v>
+      </c>
+      <c r="K9" t="s">
+        <v>82</v>
+      </c>
+      <c r="L9" t="s">
+        <v>76</v>
+      </c>
+      <c r="M9" t="s">
+        <v>65</v>
+      </c>
+      <c r="N9" t="s">
+        <v>76</v>
+      </c>
+      <c r="O9" t="s">
+        <v>65</v>
+      </c>
+      <c r="P9" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>73</v>
+      </c>
+      <c r="R9" t="s">
+        <v>76</v>
+      </c>
+      <c r="S9" t="s">
+        <v>76</v>
+      </c>
+      <c r="T9" t="s">
+        <v>65</v>
+      </c>
+      <c r="U9" t="s">
+        <v>76</v>
+      </c>
+      <c r="V9" t="s">
+        <v>65</v>
+      </c>
+      <c r="W9" t="s">
+        <v>76</v>
+      </c>
+      <c r="X9" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>86</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>86</v>
+      </c>
+      <c r="AE9" t="s">
         <v>68</v>
       </c>
-      <c r="B9" t="s">
+      <c r="AF9" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>76</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>76</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>87</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>87</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>68</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>81</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>80</v>
+      </c>
+      <c r="AO9" t="s">
         <v>67</v>
       </c>
-      <c r="C9" t="s">
-        <v>58</v>
-      </c>
-      <c r="D9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E9" t="s">
-        <v>68</v>
-      </c>
-      <c r="F9" t="s">
-        <v>63</v>
-      </c>
-      <c r="G9" t="s">
-        <v>68</v>
-      </c>
-      <c r="H9" t="s">
-        <v>57</v>
-      </c>
-      <c r="I9" t="s">
-        <v>63</v>
-      </c>
-      <c r="J9" t="s">
-        <v>74</v>
-      </c>
-      <c r="K9" t="s">
-        <v>80</v>
-      </c>
-      <c r="L9" t="s">
-        <v>74</v>
-      </c>
-      <c r="M9" t="s">
-        <v>63</v>
-      </c>
-      <c r="N9" t="s">
-        <v>74</v>
-      </c>
-      <c r="O9" t="s">
-        <v>63</v>
-      </c>
-      <c r="P9" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>71</v>
-      </c>
-      <c r="R9" t="s">
-        <v>74</v>
-      </c>
-      <c r="S9" t="s">
-        <v>74</v>
-      </c>
-      <c r="T9" t="s">
-        <v>63</v>
-      </c>
-      <c r="U9" t="s">
-        <v>74</v>
-      </c>
-      <c r="V9" t="s">
-        <v>63</v>
-      </c>
-      <c r="W9" t="s">
-        <v>74</v>
-      </c>
-      <c r="X9" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>74</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>62</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>84</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC9" t="s">
-        <v>74</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>84</v>
-      </c>
-      <c r="AE9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG9" t="s">
-        <v>74</v>
-      </c>
-      <c r="AH9" t="s">
-        <v>81</v>
-      </c>
-      <c r="AI9" t="s">
-        <v>74</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>85</v>
-      </c>
-      <c r="AK9" t="s">
-        <v>85</v>
-      </c>
-      <c r="AL9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AM9" t="s">
-        <v>79</v>
-      </c>
-      <c r="AN9" t="s">
-        <v>78</v>
-      </c>
-      <c r="AO9" t="s">
-        <v>65</v>
-      </c>
       <c r="AP9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F10" t="s">
+        <v>89</v>
+      </c>
+      <c r="G10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H10" t="s">
+        <v>76</v>
+      </c>
+      <c r="I10" t="s">
+        <v>73</v>
+      </c>
+      <c r="J10" t="s">
+        <v>65</v>
+      </c>
+      <c r="K10" t="s">
+        <v>65</v>
+      </c>
+      <c r="L10" t="s">
+        <v>73</v>
+      </c>
+      <c r="M10" t="s">
+        <v>73</v>
+      </c>
+      <c r="N10" t="s">
+        <v>65</v>
+      </c>
+      <c r="O10" t="s">
+        <v>64</v>
+      </c>
+      <c r="P10" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>64</v>
+      </c>
+      <c r="R10" t="s">
+        <v>73</v>
+      </c>
+      <c r="S10" t="s">
+        <v>89</v>
+      </c>
+      <c r="T10" t="s">
+        <v>64</v>
+      </c>
+      <c r="U10" t="s">
+        <v>73</v>
+      </c>
+      <c r="V10" t="s">
+        <v>90</v>
+      </c>
+      <c r="W10" t="s">
+        <v>90</v>
+      </c>
+      <c r="X10" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>82</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>84</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>86</v>
+      </c>
+      <c r="AF10" t="s">
         <v>87</v>
       </c>
-      <c r="G10" t="s">
-        <v>74</v>
-      </c>
-      <c r="H10" t="s">
-        <v>74</v>
-      </c>
-      <c r="I10" t="s">
-        <v>71</v>
-      </c>
-      <c r="J10" t="s">
-        <v>63</v>
-      </c>
-      <c r="K10" t="s">
-        <v>63</v>
-      </c>
-      <c r="L10" t="s">
-        <v>71</v>
-      </c>
-      <c r="M10" t="s">
-        <v>71</v>
-      </c>
-      <c r="N10" t="s">
-        <v>63</v>
-      </c>
-      <c r="O10" t="s">
-        <v>62</v>
-      </c>
-      <c r="P10" t="s">
+      <c r="AG10" t="s">
+        <v>73</v>
+      </c>
+      <c r="AH10" t="s">
         <v>87</v>
       </c>
-      <c r="Q10" t="s">
-        <v>62</v>
-      </c>
-      <c r="R10" t="s">
-        <v>71</v>
-      </c>
-      <c r="S10" t="s">
-        <v>87</v>
-      </c>
-      <c r="T10" t="s">
-        <v>62</v>
-      </c>
-      <c r="U10" t="s">
-        <v>71</v>
-      </c>
-      <c r="V10" t="s">
+      <c r="AI10" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>90</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AM10" t="s">
+        <v>86</v>
+      </c>
+      <c r="AN10" t="s">
         <v>88</v>
       </c>
-      <c r="W10" t="s">
-        <v>88</v>
-      </c>
-      <c r="X10" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>70</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>70</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>80</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>82</v>
-      </c>
-      <c r="AE10" t="s">
-        <v>84</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>85</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>71</v>
-      </c>
-      <c r="AH10" t="s">
-        <v>85</v>
-      </c>
-      <c r="AI10" t="s">
-        <v>63</v>
-      </c>
-      <c r="AJ10" t="s">
-        <v>88</v>
-      </c>
-      <c r="AK10" t="s">
-        <v>70</v>
-      </c>
-      <c r="AL10" t="s">
-        <v>77</v>
-      </c>
-      <c r="AM10" t="s">
-        <v>84</v>
-      </c>
-      <c r="AN10" t="s">
-        <v>86</v>
-      </c>
       <c r="AO10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E11" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G11" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="N11" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="O11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="P11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="Q11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="R11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="S11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="T11" t="s">
+        <v>83</v>
+      </c>
+      <c r="U11" t="s">
+        <v>64</v>
+      </c>
+      <c r="V11" t="s">
+        <v>68</v>
+      </c>
+      <c r="W11" t="s">
+        <v>68</v>
+      </c>
+      <c r="X11" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>68</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>92</v>
+      </c>
+      <c r="AH11" t="s">
         <v>81</v>
       </c>
-      <c r="U11" t="s">
-        <v>62</v>
-      </c>
-      <c r="V11" t="s">
-        <v>66</v>
-      </c>
-      <c r="W11" t="s">
-        <v>66</v>
-      </c>
-      <c r="X11" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>88</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>90</v>
-      </c>
-      <c r="AB11" t="s">
-        <v>88</v>
-      </c>
-      <c r="AC11" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>73</v>
-      </c>
-      <c r="AE11" t="s">
-        <v>55</v>
-      </c>
-      <c r="AF11" t="s">
+      <c r="AI11" t="s">
+        <v>92</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>78</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>84</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM11" t="s">
+        <v>78</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO11" t="s">
         <v>75</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>90</v>
-      </c>
-      <c r="AH11" t="s">
-        <v>79</v>
-      </c>
-      <c r="AI11" t="s">
-        <v>90</v>
-      </c>
-      <c r="AJ11" t="s">
-        <v>76</v>
-      </c>
-      <c r="AK11" t="s">
-        <v>82</v>
-      </c>
-      <c r="AL11" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM11" t="s">
-        <v>76</v>
-      </c>
-      <c r="AN11" t="s">
-        <v>92</v>
-      </c>
-      <c r="AO11" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E12" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="L12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="N12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="O12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="P12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="Q12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="R12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="S12" t="s">
+        <v>87</v>
+      </c>
+      <c r="T12" t="s">
+        <v>86</v>
+      </c>
+      <c r="U12" t="s">
+        <v>68</v>
+      </c>
+      <c r="V12" t="s">
+        <v>86</v>
+      </c>
+      <c r="W12" t="s">
+        <v>78</v>
+      </c>
+      <c r="X12" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>87</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD12" t="s">
         <v>85</v>
       </c>
-      <c r="T12" t="s">
-        <v>84</v>
-      </c>
-      <c r="U12" t="s">
-        <v>66</v>
-      </c>
-      <c r="V12" t="s">
-        <v>84</v>
-      </c>
-      <c r="W12" t="s">
-        <v>76</v>
-      </c>
-      <c r="X12" t="s">
-        <v>84</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z12" t="s">
-        <v>75</v>
-      </c>
-      <c r="AA12" t="s">
+      <c r="AE12" t="s">
         <v>77</v>
       </c>
-      <c r="AB12" t="s">
+      <c r="AF12" t="s">
+        <v>95</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>79</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>79</v>
+      </c>
+      <c r="AI12" t="s">
         <v>85</v>
       </c>
-      <c r="AC12" t="s">
-        <v>75</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>83</v>
-      </c>
-      <c r="AE12" t="s">
-        <v>75</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>93</v>
-      </c>
-      <c r="AG12" t="s">
-        <v>77</v>
-      </c>
-      <c r="AH12" t="s">
-        <v>77</v>
-      </c>
-      <c r="AI12" t="s">
-        <v>83</v>
-      </c>
       <c r="AJ12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AK12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AL12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AM12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AN12" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" t="s">
+        <v>90</v>
+      </c>
+      <c r="E13" t="s">
+        <v>72</v>
+      </c>
+      <c r="F13" t="s">
+        <v>68</v>
+      </c>
+      <c r="G13" t="s">
+        <v>68</v>
+      </c>
+      <c r="H13" t="s">
+        <v>72</v>
+      </c>
+      <c r="I13" t="s">
+        <v>84</v>
+      </c>
+      <c r="J13" t="s">
+        <v>86</v>
+      </c>
+      <c r="K13" t="s">
+        <v>76</v>
+      </c>
+      <c r="L13" t="s">
+        <v>68</v>
+      </c>
+      <c r="M13" t="s">
+        <v>77</v>
+      </c>
+      <c r="N13" t="s">
+        <v>78</v>
+      </c>
+      <c r="O13" t="s">
+        <v>78</v>
+      </c>
+      <c r="P13" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>77</v>
+      </c>
+      <c r="R13" t="s">
+        <v>77</v>
+      </c>
+      <c r="S13" t="s">
+        <v>86</v>
+      </c>
+      <c r="T13" t="s">
+        <v>78</v>
+      </c>
+      <c r="U13" t="s">
+        <v>77</v>
+      </c>
+      <c r="V13" t="s">
+        <v>64</v>
+      </c>
+      <c r="W13" t="s">
+        <v>84</v>
+      </c>
+      <c r="X13" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>81</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>85</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>75</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>91</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>85</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>85</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>80</v>
+      </c>
+      <c r="AM13" t="s">
         <v>62</v>
       </c>
-      <c r="C13" t="s">
-        <v>70</v>
-      </c>
-      <c r="D13" t="s">
-        <v>88</v>
-      </c>
-      <c r="E13" t="s">
-        <v>70</v>
-      </c>
-      <c r="F13" t="s">
-        <v>66</v>
-      </c>
-      <c r="G13" t="s">
-        <v>66</v>
-      </c>
-      <c r="H13" t="s">
-        <v>70</v>
-      </c>
-      <c r="I13" t="s">
-        <v>82</v>
-      </c>
-      <c r="J13" t="s">
-        <v>84</v>
-      </c>
-      <c r="K13" t="s">
-        <v>74</v>
-      </c>
-      <c r="L13" t="s">
-        <v>66</v>
-      </c>
-      <c r="M13" t="s">
-        <v>75</v>
-      </c>
-      <c r="N13" t="s">
-        <v>76</v>
-      </c>
-      <c r="O13" t="s">
-        <v>76</v>
-      </c>
-      <c r="P13" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>75</v>
-      </c>
-      <c r="R13" t="s">
-        <v>75</v>
-      </c>
-      <c r="S13" t="s">
-        <v>84</v>
-      </c>
-      <c r="T13" t="s">
-        <v>76</v>
-      </c>
-      <c r="U13" t="s">
-        <v>75</v>
-      </c>
-      <c r="V13" t="s">
-        <v>62</v>
-      </c>
-      <c r="W13" t="s">
-        <v>82</v>
-      </c>
-      <c r="X13" t="s">
-        <v>76</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>75</v>
-      </c>
-      <c r="Z13" t="s">
-        <v>76</v>
-      </c>
-      <c r="AA13" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB13" t="s">
-        <v>90</v>
-      </c>
-      <c r="AC13" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE13" t="s">
-        <v>77</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>90</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>83</v>
-      </c>
-      <c r="AH13" t="s">
-        <v>73</v>
-      </c>
-      <c r="AI13" t="s">
-        <v>89</v>
-      </c>
-      <c r="AJ13" t="s">
-        <v>83</v>
-      </c>
-      <c r="AK13" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL13" t="s">
-        <v>78</v>
-      </c>
-      <c r="AM13" t="s">
-        <v>60</v>
-      </c>
       <c r="AN13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" t="s">
+        <v>90</v>
+      </c>
+      <c r="F14" t="s">
+        <v>86</v>
+      </c>
+      <c r="G14" t="s">
+        <v>86</v>
+      </c>
+      <c r="H14" t="s">
+        <v>68</v>
+      </c>
+      <c r="I14" t="s">
+        <v>92</v>
+      </c>
+      <c r="J14" t="s">
+        <v>78</v>
+      </c>
+      <c r="K14" t="s">
+        <v>78</v>
+      </c>
+      <c r="L14" t="s">
+        <v>77</v>
+      </c>
+      <c r="M14" t="s">
+        <v>95</v>
+      </c>
+      <c r="N14" t="s">
+        <v>84</v>
+      </c>
+      <c r="O14" t="s">
+        <v>81</v>
+      </c>
+      <c r="P14" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>78</v>
+      </c>
+      <c r="R14" t="s">
+        <v>78</v>
+      </c>
+      <c r="S14" t="s">
+        <v>92</v>
+      </c>
+      <c r="T14" t="s">
+        <v>92</v>
+      </c>
+      <c r="U14" t="s">
+        <v>81</v>
+      </c>
+      <c r="V14" t="s">
+        <v>77</v>
+      </c>
+      <c r="W14" t="s">
+        <v>75</v>
+      </c>
+      <c r="X14" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>81</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>81</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>96</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>93</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>85</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>96</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>99</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>97</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>99</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>99</v>
+      </c>
+      <c r="AL14" t="s">
         <v>62</v>
       </c>
-      <c r="B14" t="s">
-        <v>81</v>
-      </c>
-      <c r="C14" t="s">
-        <v>88</v>
-      </c>
-      <c r="D14" t="s">
-        <v>66</v>
-      </c>
-      <c r="E14" t="s">
-        <v>88</v>
-      </c>
-      <c r="F14" t="s">
-        <v>84</v>
-      </c>
-      <c r="G14" t="s">
-        <v>84</v>
-      </c>
-      <c r="H14" t="s">
-        <v>66</v>
-      </c>
-      <c r="I14" t="s">
-        <v>90</v>
-      </c>
-      <c r="J14" t="s">
-        <v>76</v>
-      </c>
-      <c r="K14" t="s">
-        <v>76</v>
-      </c>
-      <c r="L14" t="s">
-        <v>75</v>
-      </c>
-      <c r="M14" t="s">
-        <v>93</v>
-      </c>
-      <c r="N14" t="s">
-        <v>82</v>
-      </c>
-      <c r="O14" t="s">
-        <v>79</v>
-      </c>
-      <c r="P14" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>76</v>
-      </c>
-      <c r="R14" t="s">
-        <v>76</v>
-      </c>
-      <c r="S14" t="s">
-        <v>90</v>
-      </c>
-      <c r="T14" t="s">
-        <v>90</v>
-      </c>
-      <c r="U14" t="s">
-        <v>79</v>
-      </c>
-      <c r="V14" t="s">
-        <v>75</v>
-      </c>
-      <c r="W14" t="s">
-        <v>73</v>
-      </c>
-      <c r="X14" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>79</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>94</v>
-      </c>
-      <c r="AB14" t="s">
-        <v>77</v>
-      </c>
-      <c r="AC14" t="s">
-        <v>90</v>
-      </c>
-      <c r="AD14" t="s">
-        <v>94</v>
-      </c>
-      <c r="AE14" t="s">
+      <c r="AM14" t="s">
         <v>91</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>83</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>94</v>
-      </c>
-      <c r="AH14" t="s">
-        <v>97</v>
-      </c>
-      <c r="AI14" t="s">
-        <v>95</v>
-      </c>
-      <c r="AJ14" t="s">
-        <v>97</v>
-      </c>
-      <c r="AK14" t="s">
-        <v>97</v>
-      </c>
-      <c r="AL14" t="s">
-        <v>60</v>
-      </c>
-      <c r="AM14" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B15" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" t="s">
+        <v>86</v>
+      </c>
+      <c r="E15" t="s">
+        <v>68</v>
+      </c>
+      <c r="F15" t="s">
+        <v>78</v>
+      </c>
+      <c r="G15" t="s">
+        <v>77</v>
+      </c>
+      <c r="H15" t="s">
+        <v>78</v>
+      </c>
+      <c r="I15" t="s">
+        <v>79</v>
+      </c>
+      <c r="J15" t="s">
+        <v>84</v>
+      </c>
+      <c r="K15" t="s">
+        <v>84</v>
+      </c>
+      <c r="L15" t="s">
+        <v>84</v>
+      </c>
+      <c r="M15" t="s">
+        <v>81</v>
+      </c>
+      <c r="N15" t="s">
+        <v>92</v>
+      </c>
+      <c r="O15" t="s">
+        <v>92</v>
+      </c>
+      <c r="P15" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>95</v>
+      </c>
+      <c r="R15" t="s">
+        <v>84</v>
+      </c>
+      <c r="S15" t="s">
+        <v>79</v>
+      </c>
+      <c r="T15" t="s">
+        <v>79</v>
+      </c>
+      <c r="U15" t="s">
+        <v>92</v>
+      </c>
+      <c r="V15" t="s">
+        <v>84</v>
+      </c>
+      <c r="W15" t="s">
+        <v>85</v>
+      </c>
+      <c r="X15" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>75</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>96</v>
+      </c>
+      <c r="AF15" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>89</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>91</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>74</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>67</v>
+      </c>
+      <c r="AK15" t="s">
+        <v>67</v>
+      </c>
+      <c r="AL15" t="s">
         <v>88</v>
-      </c>
-      <c r="C15" t="s">
-        <v>66</v>
-      </c>
-      <c r="D15" t="s">
-        <v>84</v>
-      </c>
-      <c r="E15" t="s">
-        <v>66</v>
-      </c>
-      <c r="F15" t="s">
-        <v>76</v>
-      </c>
-      <c r="G15" t="s">
-        <v>75</v>
-      </c>
-      <c r="H15" t="s">
-        <v>76</v>
-      </c>
-      <c r="I15" t="s">
-        <v>77</v>
-      </c>
-      <c r="J15" t="s">
-        <v>82</v>
-      </c>
-      <c r="K15" t="s">
-        <v>82</v>
-      </c>
-      <c r="L15" t="s">
-        <v>82</v>
-      </c>
-      <c r="M15" t="s">
-        <v>79</v>
-      </c>
-      <c r="N15" t="s">
-        <v>90</v>
-      </c>
-      <c r="O15" t="s">
-        <v>90</v>
-      </c>
-      <c r="P15" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>93</v>
-      </c>
-      <c r="R15" t="s">
-        <v>82</v>
-      </c>
-      <c r="S15" t="s">
-        <v>77</v>
-      </c>
-      <c r="T15" t="s">
-        <v>77</v>
-      </c>
-      <c r="U15" t="s">
-        <v>90</v>
-      </c>
-      <c r="V15" t="s">
-        <v>82</v>
-      </c>
-      <c r="W15" t="s">
-        <v>83</v>
-      </c>
-      <c r="X15" t="s">
-        <v>73</v>
-      </c>
-      <c r="Y15" t="s">
-        <v>90</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>73</v>
-      </c>
-      <c r="AA15" t="s">
-        <v>85</v>
-      </c>
-      <c r="AB15" t="s">
-        <v>83</v>
-      </c>
-      <c r="AC15" t="s">
-        <v>73</v>
-      </c>
-      <c r="AD15" t="s">
-        <v>62</v>
-      </c>
-      <c r="AE15" t="s">
-        <v>94</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>76</v>
-      </c>
-      <c r="AG15" t="s">
-        <v>87</v>
-      </c>
-      <c r="AH15" t="s">
-        <v>89</v>
-      </c>
-      <c r="AI15" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJ15" t="s">
-        <v>65</v>
-      </c>
-      <c r="AK15" t="s">
-        <v>65</v>
-      </c>
-      <c r="AL15" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>90</v>
+      </c>
+      <c r="B16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" t="s">
+        <v>86</v>
+      </c>
+      <c r="D16" t="s">
+        <v>77</v>
+      </c>
+      <c r="E16" t="s">
+        <v>77</v>
+      </c>
+      <c r="F16" t="s">
+        <v>84</v>
+      </c>
+      <c r="G16" t="s">
+        <v>78</v>
+      </c>
+      <c r="H16" t="s">
+        <v>81</v>
+      </c>
+      <c r="I16" t="s">
+        <v>75</v>
+      </c>
+      <c r="J16" t="s">
+        <v>75</v>
+      </c>
+      <c r="K16" t="s">
+        <v>92</v>
+      </c>
+      <c r="L16" t="s">
+        <v>81</v>
+      </c>
+      <c r="M16" t="s">
+        <v>79</v>
+      </c>
+      <c r="N16" t="s">
+        <v>79</v>
+      </c>
+      <c r="O16" t="s">
+        <v>75</v>
+      </c>
+      <c r="P16" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>84</v>
+      </c>
+      <c r="R16" t="s">
+        <v>81</v>
+      </c>
+      <c r="S16" t="s">
+        <v>75</v>
+      </c>
+      <c r="T16" t="s">
+        <v>99</v>
+      </c>
+      <c r="U16" t="s">
+        <v>75</v>
+      </c>
+      <c r="V16" t="s">
+        <v>81</v>
+      </c>
+      <c r="W16" t="s">
+        <v>99</v>
+      </c>
+      <c r="X16" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>93</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>91</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>67</v>
+      </c>
+      <c r="AG16" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>67</v>
+      </c>
+      <c r="AI16" t="s">
         <v>88</v>
       </c>
-      <c r="B16" t="s">
-        <v>66</v>
-      </c>
-      <c r="C16" t="s">
-        <v>84</v>
-      </c>
-      <c r="D16" t="s">
-        <v>75</v>
-      </c>
-      <c r="E16" t="s">
-        <v>75</v>
-      </c>
-      <c r="F16" t="s">
-        <v>82</v>
-      </c>
-      <c r="G16" t="s">
-        <v>76</v>
-      </c>
-      <c r="H16" t="s">
-        <v>79</v>
-      </c>
-      <c r="I16" t="s">
-        <v>73</v>
-      </c>
-      <c r="J16" t="s">
-        <v>73</v>
-      </c>
-      <c r="K16" t="s">
-        <v>90</v>
-      </c>
-      <c r="L16" t="s">
-        <v>79</v>
-      </c>
-      <c r="M16" t="s">
-        <v>77</v>
-      </c>
-      <c r="N16" t="s">
-        <v>77</v>
-      </c>
-      <c r="O16" t="s">
-        <v>73</v>
-      </c>
-      <c r="P16" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>82</v>
-      </c>
-      <c r="R16" t="s">
-        <v>79</v>
-      </c>
-      <c r="S16" t="s">
-        <v>73</v>
-      </c>
-      <c r="T16" t="s">
-        <v>97</v>
-      </c>
-      <c r="U16" t="s">
-        <v>73</v>
-      </c>
-      <c r="V16" t="s">
-        <v>79</v>
-      </c>
-      <c r="W16" t="s">
-        <v>97</v>
-      </c>
-      <c r="X16" t="s">
-        <v>83</v>
-      </c>
-      <c r="Y16" t="s">
-        <v>73</v>
-      </c>
-      <c r="Z16" t="s">
-        <v>83</v>
-      </c>
-      <c r="AA16" t="s">
-        <v>98</v>
-      </c>
-      <c r="AB16" t="s">
-        <v>65</v>
-      </c>
-      <c r="AC16" t="s">
-        <v>91</v>
-      </c>
-      <c r="AD16" t="s">
-        <v>89</v>
-      </c>
-      <c r="AE16" t="s">
-        <v>89</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>65</v>
-      </c>
-      <c r="AG16" t="s">
-        <v>95</v>
-      </c>
-      <c r="AH16" t="s">
-        <v>65</v>
-      </c>
-      <c r="AI16" t="s">
-        <v>86</v>
-      </c>
       <c r="AJ16" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="AK16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AL16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C17" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D17" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E17" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F17" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G17" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H17" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I17" t="s">
+        <v>99</v>
+      </c>
+      <c r="J17" t="s">
+        <v>99</v>
+      </c>
+      <c r="K17" t="s">
+        <v>85</v>
+      </c>
+      <c r="L17" t="s">
+        <v>79</v>
+      </c>
+      <c r="M17" t="s">
+        <v>75</v>
+      </c>
+      <c r="N17" t="s">
+        <v>85</v>
+      </c>
+      <c r="O17" t="s">
+        <v>96</v>
+      </c>
+      <c r="P17" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>75</v>
+      </c>
+      <c r="R17" t="s">
+        <v>92</v>
+      </c>
+      <c r="S17" t="s">
+        <v>93</v>
+      </c>
+      <c r="T17" t="s">
+        <v>101</v>
+      </c>
+      <c r="U17" t="s">
+        <v>85</v>
+      </c>
+      <c r="V17" t="s">
+        <v>101</v>
+      </c>
+      <c r="W17" t="s">
+        <v>95</v>
+      </c>
+      <c r="X17" t="s">
+        <v>96</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA17" t="s">
         <v>97</v>
       </c>
-      <c r="J17" t="s">
+      <c r="AB17" t="s">
+        <v>102</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>91</v>
+      </c>
+      <c r="AD17" t="s">
         <v>97</v>
       </c>
-      <c r="K17" t="s">
-        <v>83</v>
-      </c>
-      <c r="L17" t="s">
-        <v>77</v>
-      </c>
-      <c r="M17" t="s">
-        <v>73</v>
-      </c>
-      <c r="N17" t="s">
-        <v>83</v>
-      </c>
-      <c r="O17" t="s">
-        <v>94</v>
-      </c>
-      <c r="P17" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>73</v>
-      </c>
-      <c r="R17" t="s">
-        <v>90</v>
-      </c>
-      <c r="S17" t="s">
-        <v>91</v>
-      </c>
-      <c r="T17" t="s">
-        <v>99</v>
-      </c>
-      <c r="U17" t="s">
-        <v>83</v>
-      </c>
-      <c r="V17" t="s">
-        <v>99</v>
-      </c>
-      <c r="W17" t="s">
-        <v>93</v>
-      </c>
-      <c r="X17" t="s">
-        <v>94</v>
-      </c>
-      <c r="Y17" t="s">
-        <v>83</v>
-      </c>
-      <c r="Z17" t="s">
-        <v>97</v>
-      </c>
-      <c r="AA17" t="s">
-        <v>95</v>
-      </c>
-      <c r="AB17" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC17" t="s">
-        <v>89</v>
-      </c>
-      <c r="AD17" t="s">
-        <v>95</v>
-      </c>
       <c r="AE17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AF17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AG17" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AH17" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AI17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AJ17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK17" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>77</v>
+      </c>
+      <c r="B18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" t="s">
+        <v>95</v>
+      </c>
+      <c r="D18" t="s">
+        <v>95</v>
+      </c>
+      <c r="E18" t="s">
         <v>75</v>
       </c>
-      <c r="B18" t="s">
+      <c r="F18" t="s">
         <v>75</v>
       </c>
-      <c r="C18" t="s">
+      <c r="G18" t="s">
+        <v>79</v>
+      </c>
+      <c r="H18" t="s">
+        <v>75</v>
+      </c>
+      <c r="I18" t="s">
         <v>93</v>
       </c>
-      <c r="D18" t="s">
+      <c r="J18" t="s">
         <v>93</v>
       </c>
-      <c r="E18" t="s">
-        <v>73</v>
-      </c>
-      <c r="F18" t="s">
-        <v>73</v>
-      </c>
-      <c r="G18" t="s">
-        <v>77</v>
-      </c>
-      <c r="H18" t="s">
-        <v>73</v>
-      </c>
-      <c r="I18" t="s">
+      <c r="K18" t="s">
+        <v>93</v>
+      </c>
+      <c r="L18" t="s">
+        <v>93</v>
+      </c>
+      <c r="M18" t="s">
+        <v>85</v>
+      </c>
+      <c r="N18" t="s">
+        <v>96</v>
+      </c>
+      <c r="O18" t="s">
+        <v>97</v>
+      </c>
+      <c r="P18" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>85</v>
+      </c>
+      <c r="R18" t="s">
+        <v>75</v>
+      </c>
+      <c r="S18" t="s">
+        <v>97</v>
+      </c>
+      <c r="T18" t="s">
         <v>91</v>
       </c>
-      <c r="J18" t="s">
+      <c r="U18" t="s">
+        <v>67</v>
+      </c>
+      <c r="V18" t="s">
+        <v>103</v>
+      </c>
+      <c r="W18" t="s">
         <v>91</v>
       </c>
-      <c r="K18" t="s">
+      <c r="X18" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y18" t="s">
         <v>91</v>
       </c>
-      <c r="L18" t="s">
-        <v>91</v>
-      </c>
-      <c r="M18" t="s">
-        <v>83</v>
-      </c>
-      <c r="N18" t="s">
+      <c r="Z18" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>62</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>102</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>102</v>
+      </c>
+      <c r="AE18" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF18" t="s">
+        <v>60</v>
+      </c>
+      <c r="AG18" t="s">
+        <v>74</v>
+      </c>
+      <c r="AH18" t="s">
         <v>94</v>
       </c>
-      <c r="O18" t="s">
-        <v>95</v>
-      </c>
-      <c r="P18" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>83</v>
-      </c>
-      <c r="R18" t="s">
-        <v>73</v>
-      </c>
-      <c r="S18" t="s">
-        <v>95</v>
-      </c>
-      <c r="T18" t="s">
-        <v>89</v>
-      </c>
-      <c r="U18" t="s">
-        <v>65</v>
-      </c>
-      <c r="V18" t="s">
-        <v>101</v>
-      </c>
-      <c r="W18" t="s">
-        <v>89</v>
-      </c>
-      <c r="X18" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y18" t="s">
-        <v>89</v>
-      </c>
-      <c r="Z18" t="s">
-        <v>65</v>
-      </c>
-      <c r="AA18" t="s">
-        <v>102</v>
-      </c>
-      <c r="AB18" t="s">
-        <v>60</v>
-      </c>
-      <c r="AC18" t="s">
-        <v>100</v>
-      </c>
-      <c r="AD18" t="s">
-        <v>100</v>
-      </c>
-      <c r="AE18" t="s">
-        <v>60</v>
-      </c>
-      <c r="AF18" t="s">
-        <v>59</v>
-      </c>
-      <c r="AG18" t="s">
-        <v>72</v>
-      </c>
-      <c r="AH18" t="s">
-        <v>92</v>
-      </c>
       <c r="AI18" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AJ18" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AK18" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C19" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D19" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E19" t="s">
+        <v>99</v>
+      </c>
+      <c r="F19" t="s">
+        <v>85</v>
+      </c>
+      <c r="G19" t="s">
+        <v>85</v>
+      </c>
+      <c r="H19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I19" t="s">
+        <v>81</v>
+      </c>
+      <c r="J19" t="s">
+        <v>96</v>
+      </c>
+      <c r="K19" t="s">
         <v>97</v>
       </c>
-      <c r="F19" t="s">
-        <v>83</v>
-      </c>
-      <c r="G19" t="s">
-        <v>83</v>
-      </c>
-      <c r="H19" t="s">
+      <c r="L19" t="s">
+        <v>67</v>
+      </c>
+      <c r="M19" t="s">
+        <v>91</v>
+      </c>
+      <c r="N19" t="s">
+        <v>91</v>
+      </c>
+      <c r="O19" t="s">
+        <v>102</v>
+      </c>
+      <c r="P19" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>99</v>
+      </c>
+      <c r="R19" t="s">
+        <v>91</v>
+      </c>
+      <c r="S19" t="s">
+        <v>104</v>
+      </c>
+      <c r="T19" t="s">
+        <v>80</v>
+      </c>
+      <c r="U19" t="s">
+        <v>74</v>
+      </c>
+      <c r="V19" t="s">
+        <v>102</v>
+      </c>
+      <c r="W19" t="s">
+        <v>67</v>
+      </c>
+      <c r="X19" t="s">
         <v>97</v>
       </c>
-      <c r="I19" t="s">
-        <v>79</v>
-      </c>
-      <c r="J19" t="s">
+      <c r="Y19" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>88</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>88</v>
+      </c>
+      <c r="AG19" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>98</v>
+      </c>
+      <c r="AJ19" t="s">
         <v>94</v>
-      </c>
-      <c r="K19" t="s">
-        <v>95</v>
-      </c>
-      <c r="L19" t="s">
-        <v>65</v>
-      </c>
-      <c r="M19" t="s">
-        <v>89</v>
-      </c>
-      <c r="N19" t="s">
-        <v>89</v>
-      </c>
-      <c r="O19" t="s">
-        <v>100</v>
-      </c>
-      <c r="P19" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>97</v>
-      </c>
-      <c r="R19" t="s">
-        <v>89</v>
-      </c>
-      <c r="S19" t="s">
-        <v>102</v>
-      </c>
-      <c r="T19" t="s">
-        <v>78</v>
-      </c>
-      <c r="U19" t="s">
-        <v>72</v>
-      </c>
-      <c r="V19" t="s">
-        <v>100</v>
-      </c>
-      <c r="W19" t="s">
-        <v>65</v>
-      </c>
-      <c r="X19" t="s">
-        <v>95</v>
-      </c>
-      <c r="Y19" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z19" t="s">
-        <v>72</v>
-      </c>
-      <c r="AA19" t="s">
-        <v>78</v>
-      </c>
-      <c r="AB19" t="s">
-        <v>59</v>
-      </c>
-      <c r="AC19" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD19" t="s">
-        <v>59</v>
-      </c>
-      <c r="AE19" t="s">
-        <v>86</v>
-      </c>
-      <c r="AF19" t="s">
-        <v>86</v>
-      </c>
-      <c r="AG19" t="s">
-        <v>78</v>
-      </c>
-      <c r="AH19" t="s">
-        <v>96</v>
-      </c>
-      <c r="AJ19" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B20" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20" t="s">
+        <v>92</v>
+      </c>
+      <c r="E20" t="s">
         <v>93</v>
       </c>
-      <c r="B20" t="s">
-        <v>93</v>
-      </c>
-      <c r="C20" t="s">
-        <v>90</v>
-      </c>
-      <c r="D20" t="s">
-        <v>90</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
+        <v>96</v>
+      </c>
+      <c r="G20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H20" t="s">
+        <v>77</v>
+      </c>
+      <c r="I20" t="s">
         <v>91</v>
       </c>
-      <c r="F20" t="s">
+      <c r="J20" t="s">
+        <v>91</v>
+      </c>
+      <c r="K20" t="s">
+        <v>80</v>
+      </c>
+      <c r="L20" t="s">
+        <v>97</v>
+      </c>
+      <c r="M20" t="s">
+        <v>67</v>
+      </c>
+      <c r="N20" t="s">
+        <v>97</v>
+      </c>
+      <c r="O20" t="s">
+        <v>74</v>
+      </c>
+      <c r="P20" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>91</v>
+      </c>
+      <c r="R20" t="s">
+        <v>74</v>
+      </c>
+      <c r="S20" t="s">
+        <v>80</v>
+      </c>
+      <c r="T20" t="s">
+        <v>62</v>
+      </c>
+      <c r="U20" t="s">
+        <v>80</v>
+      </c>
+      <c r="V20" t="s">
+        <v>74</v>
+      </c>
+      <c r="W20" t="s">
+        <v>102</v>
+      </c>
+      <c r="X20" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>98</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>98</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>88</v>
+      </c>
+      <c r="AD20" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE20" t="s">
         <v>94</v>
       </c>
-      <c r="G20" t="s">
-        <v>65</v>
-      </c>
-      <c r="H20" t="s">
-        <v>75</v>
-      </c>
-      <c r="I20" t="s">
-        <v>89</v>
-      </c>
-      <c r="J20" t="s">
-        <v>89</v>
-      </c>
-      <c r="K20" t="s">
-        <v>78</v>
-      </c>
-      <c r="L20" t="s">
-        <v>95</v>
-      </c>
-      <c r="M20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N20" t="s">
-        <v>95</v>
-      </c>
-      <c r="O20" t="s">
-        <v>72</v>
-      </c>
-      <c r="P20" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>89</v>
-      </c>
-      <c r="R20" t="s">
-        <v>72</v>
-      </c>
-      <c r="S20" t="s">
-        <v>78</v>
-      </c>
-      <c r="T20" t="s">
-        <v>60</v>
-      </c>
-      <c r="U20" t="s">
-        <v>78</v>
-      </c>
-      <c r="V20" t="s">
-        <v>72</v>
-      </c>
-      <c r="W20" t="s">
-        <v>100</v>
-      </c>
-      <c r="X20" t="s">
-        <v>60</v>
-      </c>
-      <c r="Y20" t="s">
-        <v>60</v>
-      </c>
-      <c r="Z20" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA20" t="s">
-        <v>96</v>
-      </c>
-      <c r="AB20" t="s">
-        <v>96</v>
-      </c>
-      <c r="AC20" t="s">
-        <v>86</v>
-      </c>
-      <c r="AD20" t="s">
-        <v>86</v>
-      </c>
-      <c r="AE20" t="s">
-        <v>92</v>
-      </c>
       <c r="AF20" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AG20" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B21" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
+        <v>100</v>
+      </c>
+      <c r="D21" t="s">
+        <v>100</v>
+      </c>
+      <c r="E21" t="s">
+        <v>91</v>
+      </c>
+      <c r="F21" t="s">
+        <v>72</v>
+      </c>
+      <c r="G21" t="s">
+        <v>102</v>
+      </c>
+      <c r="H21" t="s">
+        <v>91</v>
+      </c>
+      <c r="I21" t="s">
+        <v>67</v>
+      </c>
+      <c r="J21" t="s">
+        <v>97</v>
+      </c>
+      <c r="K21" t="s">
+        <v>62</v>
+      </c>
+      <c r="L21" t="s">
+        <v>102</v>
+      </c>
+      <c r="M21" t="s">
+        <v>74</v>
+      </c>
+      <c r="N21" t="s">
+        <v>102</v>
+      </c>
+      <c r="O21" t="s">
+        <v>62</v>
+      </c>
+      <c r="P21" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>67</v>
+      </c>
+      <c r="R21" t="s">
+        <v>88</v>
+      </c>
+      <c r="S21" t="s">
+        <v>62</v>
+      </c>
+      <c r="T21" t="s">
+        <v>60</v>
+      </c>
+      <c r="U21" t="s">
+        <v>60</v>
+      </c>
+      <c r="V21" t="s">
+        <v>62</v>
+      </c>
+      <c r="W21" t="s">
+        <v>74</v>
+      </c>
+      <c r="X21" t="s">
         <v>98</v>
       </c>
-      <c r="D21" t="s">
+      <c r="Y21" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC21" t="s">
         <v>98</v>
       </c>
-      <c r="E21" t="s">
-        <v>89</v>
-      </c>
-      <c r="F21" t="s">
-        <v>70</v>
-      </c>
-      <c r="G21" t="s">
-        <v>100</v>
-      </c>
-      <c r="H21" t="s">
-        <v>89</v>
-      </c>
-      <c r="I21" t="s">
-        <v>65</v>
-      </c>
-      <c r="J21" t="s">
-        <v>95</v>
-      </c>
-      <c r="K21" t="s">
-        <v>60</v>
-      </c>
-      <c r="L21" t="s">
-        <v>100</v>
-      </c>
-      <c r="M21" t="s">
-        <v>72</v>
-      </c>
-      <c r="N21" t="s">
-        <v>100</v>
-      </c>
-      <c r="O21" t="s">
-        <v>60</v>
-      </c>
-      <c r="P21" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>65</v>
-      </c>
-      <c r="R21" t="s">
-        <v>86</v>
-      </c>
-      <c r="S21" t="s">
-        <v>60</v>
-      </c>
-      <c r="T21" t="s">
-        <v>59</v>
-      </c>
-      <c r="U21" t="s">
-        <v>59</v>
-      </c>
-      <c r="V21" t="s">
-        <v>60</v>
-      </c>
-      <c r="W21" t="s">
-        <v>72</v>
-      </c>
-      <c r="X21" t="s">
-        <v>96</v>
-      </c>
-      <c r="Y21" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z21" t="s">
-        <v>86</v>
-      </c>
-      <c r="AA21" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB21" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC21" t="s">
-        <v>96</v>
-      </c>
       <c r="AF21" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B22" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E22" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F22" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G22" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H22" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I22" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="J22" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L22" t="s">
+        <v>62</v>
+      </c>
+      <c r="M22" t="s">
+        <v>80</v>
+      </c>
+      <c r="N22" t="s">
+        <v>74</v>
+      </c>
+      <c r="O22" t="s">
         <v>60</v>
       </c>
-      <c r="M22" t="s">
-        <v>78</v>
-      </c>
-      <c r="N22" t="s">
-        <v>72</v>
-      </c>
-      <c r="O22" t="s">
-        <v>59</v>
-      </c>
       <c r="P22" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>97</v>
+      </c>
+      <c r="R22" t="s">
+        <v>98</v>
+      </c>
+      <c r="S22" t="s">
         <v>60</v>
       </c>
-      <c r="Q22" t="s">
-        <v>95</v>
-      </c>
-      <c r="R22" t="s">
-        <v>96</v>
-      </c>
-      <c r="S22" t="s">
-        <v>59</v>
-      </c>
       <c r="T22" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="U22" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="V22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="W22" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="X22" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="Y22" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="Z22" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AA22" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B23" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C23" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D23" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E23" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F23" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G23" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H23" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I23" t="s">
+        <v>62</v>
+      </c>
+      <c r="J23" t="s">
+        <v>62</v>
+      </c>
+      <c r="K23" t="s">
+        <v>98</v>
+      </c>
+      <c r="L23" t="s">
         <v>60</v>
       </c>
-      <c r="J23" t="s">
+      <c r="M23" t="s">
         <v>60</v>
       </c>
-      <c r="K23" t="s">
-        <v>96</v>
-      </c>
-      <c r="L23" t="s">
-        <v>59</v>
-      </c>
-      <c r="M23" t="s">
-        <v>59</v>
-      </c>
       <c r="N23" t="s">
+        <v>62</v>
+      </c>
+      <c r="O23" t="s">
+        <v>88</v>
+      </c>
+      <c r="P23" t="s">
         <v>60</v>
       </c>
-      <c r="O23" t="s">
-        <v>86</v>
-      </c>
-      <c r="P23" t="s">
-        <v>59</v>
-      </c>
       <c r="Q23" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="R23" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="S23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="T23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="U23" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="V23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="W23" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="Y23" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B24" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C24" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24" t="s">
+        <v>101</v>
+      </c>
+      <c r="E24" t="s">
+        <v>104</v>
+      </c>
+      <c r="F24" t="s">
+        <v>80</v>
+      </c>
+      <c r="G24" t="s">
+        <v>60</v>
+      </c>
+      <c r="H24" t="s">
+        <v>62</v>
+      </c>
+      <c r="I24" t="s">
+        <v>88</v>
+      </c>
+      <c r="J24" t="s">
+        <v>98</v>
+      </c>
+      <c r="K24" t="s">
         <v>94</v>
       </c>
-      <c r="D24" t="s">
-        <v>99</v>
-      </c>
-      <c r="E24" t="s">
-        <v>102</v>
-      </c>
-      <c r="F24" t="s">
-        <v>78</v>
-      </c>
-      <c r="G24" t="s">
-        <v>59</v>
-      </c>
-      <c r="H24" t="s">
-        <v>60</v>
-      </c>
-      <c r="I24" t="s">
-        <v>86</v>
-      </c>
-      <c r="J24" t="s">
+      <c r="L24" t="s">
+        <v>105</v>
+      </c>
+      <c r="M24" t="s">
+        <v>98</v>
+      </c>
+      <c r="N24" t="s">
+        <v>98</v>
+      </c>
+      <c r="O24" t="s">
+        <v>94</v>
+      </c>
+      <c r="P24" t="s">
+        <v>98</v>
+      </c>
+      <c r="T24" t="s">
         <v>96</v>
       </c>
-      <c r="K24" t="s">
-        <v>92</v>
-      </c>
-      <c r="L24" t="s">
-        <v>103</v>
-      </c>
-      <c r="M24" t="s">
+      <c r="V24" t="s">
         <v>96</v>
-      </c>
-      <c r="N24" t="s">
-        <v>96</v>
-      </c>
-      <c r="O24" t="s">
-        <v>92</v>
-      </c>
-      <c r="P24" t="s">
-        <v>96</v>
-      </c>
-      <c r="T24" t="s">
-        <v>94</v>
-      </c>
-      <c r="V24" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>93</v>
+      </c>
+      <c r="B25" t="s">
+        <v>85</v>
+      </c>
+      <c r="C25" t="s">
         <v>91</v>
       </c>
-      <c r="B25" t="s">
-        <v>83</v>
-      </c>
-      <c r="C25" t="s">
-        <v>89</v>
-      </c>
       <c r="D25" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E25" t="s">
+        <v>62</v>
+      </c>
+      <c r="F25" t="s">
         <v>60</v>
       </c>
-      <c r="F25" t="s">
-        <v>59</v>
-      </c>
       <c r="G25" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H25" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I25" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J25" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="L25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B26" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C26" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D26" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E26" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F26" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G26" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H26" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I26" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B27" t="s">
+        <v>96</v>
+      </c>
+      <c r="C27" t="s">
+        <v>97</v>
+      </c>
+      <c r="D27" t="s">
+        <v>60</v>
+      </c>
+      <c r="E27" t="s">
         <v>94</v>
       </c>
-      <c r="C27" t="s">
-        <v>95</v>
-      </c>
-      <c r="D27" t="s">
-        <v>59</v>
-      </c>
-      <c r="E27" t="s">
-        <v>92</v>
-      </c>
       <c r="F27" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H27" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C28" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D28" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E28" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F28" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>104</v>
+      </c>
+      <c r="B29" t="s">
+        <v>67</v>
+      </c>
+      <c r="C29" t="s">
         <v>102</v>
       </c>
-      <c r="B29" t="s">
-        <v>65</v>
-      </c>
-      <c r="C29" t="s">
-        <v>100</v>
-      </c>
       <c r="D29" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B30" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C30" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D30" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B31" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C31" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D31" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B32" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C32" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>62</v>
+      </c>
+      <c r="B33" t="s">
+        <v>80</v>
+      </c>
+      <c r="C33" t="s">
         <v>60</v>
-      </c>
-      <c r="B33" t="s">
-        <v>78</v>
-      </c>
-      <c r="C33" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B34" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C34" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B35" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B36" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C36" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B37" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B38" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25"/>
@@ -4470,166 +4482,166 @@
   <sheetData>
     <row r="3" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" t="s">
         <v>54</v>
       </c>
-      <c r="C3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E3" t="s">
-        <v>53</v>
-      </c>
       <c r="F3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H3" t="s">
         <v>56</v>
       </c>
-      <c r="G3" t="s">
-        <v>61</v>
-      </c>
-      <c r="H3" t="s">
-        <v>55</v>
-      </c>
       <c r="I3" t="s">
+        <v>69</v>
+      </c>
+      <c r="J3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K3" t="s">
+        <v>70</v>
+      </c>
+      <c r="L3" t="s">
+        <v>59</v>
+      </c>
+      <c r="M3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N3" t="s">
+        <v>71</v>
+      </c>
+      <c r="O3" t="s">
+        <v>76</v>
+      </c>
+      <c r="P3" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>65</v>
+      </c>
+      <c r="R3" t="s">
+        <v>73</v>
+      </c>
+      <c r="S3" t="s">
+        <v>89</v>
+      </c>
+      <c r="T3" t="s">
+        <v>64</v>
+      </c>
+      <c r="U3" t="s">
+        <v>83</v>
+      </c>
+      <c r="V3" t="s">
+        <v>72</v>
+      </c>
+      <c r="W3" t="s">
+        <v>90</v>
+      </c>
+      <c r="X3" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>81</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>100</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>101</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>91</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>103</v>
+      </c>
+      <c r="AQ3" t="s">
         <v>67</v>
       </c>
-      <c r="J3" t="s">
-        <v>64</v>
-      </c>
-      <c r="K3" t="s">
-        <v>68</v>
-      </c>
-      <c r="L3" t="s">
-        <v>58</v>
-      </c>
-      <c r="M3" t="s">
-        <v>57</v>
-      </c>
-      <c r="N3" t="s">
-        <v>69</v>
-      </c>
-      <c r="O3" t="s">
+      <c r="AR3" t="s">
+        <v>97</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>104</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>102</v>
+      </c>
+      <c r="AU3" t="s">
         <v>74</v>
       </c>
-      <c r="P3" t="s">
+      <c r="AV3" t="s">
         <v>80</v>
       </c>
-      <c r="Q3" t="s">
-        <v>63</v>
-      </c>
-      <c r="R3" t="s">
-        <v>71</v>
-      </c>
-      <c r="S3" t="s">
-        <v>87</v>
-      </c>
-      <c r="T3" t="s">
+      <c r="AW3" t="s">
         <v>62</v>
       </c>
-      <c r="U3" t="s">
-        <v>81</v>
-      </c>
-      <c r="V3" t="s">
-        <v>70</v>
-      </c>
-      <c r="W3" t="s">
+      <c r="AX3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AY3" t="s">
         <v>88</v>
       </c>
-      <c r="X3" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>85</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>84</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>76</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>93</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>82</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>90</v>
-      </c>
-      <c r="AG3" t="s">
+      <c r="AZ3" t="s">
         <v>98</v>
       </c>
-      <c r="AH3" t="s">
-        <v>77</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>73</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>83</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>97</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>99</v>
-      </c>
-      <c r="AN3" t="s">
+      <c r="BA3" t="s">
         <v>94</v>
       </c>
-      <c r="AO3" t="s">
-        <v>89</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>101</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>65</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>102</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>100</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>72</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>60</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>59</v>
-      </c>
-      <c r="AY3" t="s">
-        <v>86</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>96</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>92</v>
-      </c>
       <c r="BB3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
@@ -4655,7 +4667,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I4" t="s">
         <v>1</v>
@@ -4673,7 +4685,7 @@
         <v>11</v>
       </c>
       <c r="N4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="O4" t="s">
         <v>13</v>
@@ -4694,7 +4706,7 @@
         <v>2</v>
       </c>
       <c r="U4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="V4" t="s">
         <v>11</v>
@@ -4778,7 +4790,7 @@
         <v>1</v>
       </c>
       <c r="AW4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AX4" t="s">
         <v>48</v>
@@ -5847,7 +5859,7 @@
         <v>23</v>
       </c>
       <c r="T12" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="V12" t="s">
         <v>0</v>
@@ -6308,7 +6320,7 @@
         <v>34</v>
       </c>
       <c r="R16" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="T16" t="s">
         <v>18</v>
@@ -6777,7 +6789,7 @@
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C21" t="s">
         <v>7</v>
@@ -7356,831 +7368,831 @@
   <sheetData>
     <row r="3" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" t="s">
         <v>54</v>
       </c>
-      <c r="C3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E3" t="s">
-        <v>53</v>
-      </c>
       <c r="F3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H3" t="s">
         <v>56</v>
       </c>
-      <c r="G3" t="s">
-        <v>61</v>
-      </c>
-      <c r="H3" t="s">
-        <v>55</v>
-      </c>
       <c r="I3" t="s">
+        <v>69</v>
+      </c>
+      <c r="J3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K3" t="s">
+        <v>70</v>
+      </c>
+      <c r="L3" t="s">
+        <v>59</v>
+      </c>
+      <c r="M3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N3" t="s">
+        <v>71</v>
+      </c>
+      <c r="O3" t="s">
+        <v>76</v>
+      </c>
+      <c r="P3" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>65</v>
+      </c>
+      <c r="R3" t="s">
+        <v>73</v>
+      </c>
+      <c r="S3" t="s">
+        <v>89</v>
+      </c>
+      <c r="T3" t="s">
+        <v>64</v>
+      </c>
+      <c r="U3" t="s">
+        <v>83</v>
+      </c>
+      <c r="V3" t="s">
+        <v>72</v>
+      </c>
+      <c r="W3" t="s">
+        <v>90</v>
+      </c>
+      <c r="X3" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>81</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>100</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>101</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>91</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>103</v>
+      </c>
+      <c r="AQ3" t="s">
         <v>67</v>
       </c>
-      <c r="J3" t="s">
-        <v>64</v>
-      </c>
-      <c r="K3" t="s">
-        <v>68</v>
-      </c>
-      <c r="L3" t="s">
-        <v>58</v>
-      </c>
-      <c r="M3" t="s">
-        <v>57</v>
-      </c>
-      <c r="N3" t="s">
-        <v>69</v>
-      </c>
-      <c r="O3" t="s">
+      <c r="AR3" t="s">
+        <v>97</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>104</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>102</v>
+      </c>
+      <c r="AU3" t="s">
         <v>74</v>
       </c>
-      <c r="P3" t="s">
+      <c r="AV3" t="s">
         <v>80</v>
       </c>
-      <c r="Q3" t="s">
-        <v>63</v>
-      </c>
-      <c r="R3" t="s">
-        <v>71</v>
-      </c>
-      <c r="S3" t="s">
-        <v>87</v>
-      </c>
-      <c r="T3" t="s">
+      <c r="AW3" t="s">
         <v>62</v>
       </c>
-      <c r="U3" t="s">
-        <v>81</v>
-      </c>
-      <c r="V3" t="s">
-        <v>70</v>
-      </c>
-      <c r="W3" t="s">
+      <c r="AX3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AY3" t="s">
         <v>88</v>
       </c>
-      <c r="X3" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>85</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>84</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>76</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>93</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>82</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>90</v>
-      </c>
-      <c r="AG3" t="s">
+      <c r="AZ3" t="s">
         <v>98</v>
       </c>
-      <c r="AH3" t="s">
-        <v>77</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>73</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>83</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>97</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>99</v>
-      </c>
-      <c r="AN3" t="s">
+      <c r="BA3" t="s">
         <v>94</v>
       </c>
-      <c r="AO3" t="s">
-        <v>89</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>101</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>65</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>102</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>100</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>72</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>60</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>59</v>
-      </c>
-      <c r="AY3" t="s">
-        <v>86</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>96</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>92</v>
-      </c>
       <c r="BB3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="K4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="M4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="O4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="P4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="Q4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="R4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="S4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="T4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="U4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="V4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="W4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="X4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="Y4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="Z4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AA4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AB4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AC4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AD4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AE4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AF4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AG4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AH4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AI4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AJ4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AL4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AM4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AN4" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="AO4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AP4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AQ4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="AR4" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AS4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AT4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AU4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AV4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AW4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AX4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AY4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AZ4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="BA4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BB4" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="K5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="M5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="R5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="T5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="V5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="W5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="X5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Y5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Z5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AA5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AB5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AC5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="AD5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AE5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AF5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AH5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AI5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="AJ5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AK5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AL5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AN5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AO5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AQ5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AR5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AS5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AT5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AU5" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AV5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AW5" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AX5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AY5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AZ5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="BA5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E6" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F6" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="J6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="K6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="M6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="O6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="R6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="T6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="V6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="W6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="X6" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Z6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AA6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AB6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AD6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AE6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AF6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AH6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AI6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AJ6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AK6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AL6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AN6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AO6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AQ6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AR6" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AT6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AU6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AV6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AW6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AX6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AY6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AZ6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="BA6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C7" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E7" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F7" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="H7" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="J7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K7" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="M7" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="O7" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q7" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="R7" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="T7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="V7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="X7" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Z7" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AA7" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AB7" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AD7" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AE7" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AF7" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AH7" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AI7" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AJ7" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AN7" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AO7" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AQ7" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AR7" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AU7" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AV7" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AW7" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AX7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AY7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AZ7" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="BA7" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C8" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E8" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F8" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="K8" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O8" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q8" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="R8" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="T8" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="X8" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AA8" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AB8" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AE8" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AF8" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AH8" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI8" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AJ8" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AN8" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AO8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AQ8" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AR8" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AU8" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AV8" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AW8" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AX8" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AY8" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AZ8" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="BA8" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E9" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F9" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="H9" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="O9" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="T9" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="X9" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AB9" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AF9" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AI9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AJ9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AO9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AV9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AW9" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AX9" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AY9" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AZ9" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="BA9" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="41:53" x14ac:dyDescent="0.25">
       <c r="AO10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/data/ICEHLdelegacije.xlsx
+++ b/data/ICEHLdelegacije.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2089" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2528" uniqueCount="377">
   <si>
     <t>PiragicTr</t>
   </si>
@@ -225,6 +225,9 @@
     <t>2024-11-01</t>
   </si>
   <si>
+    <t>2025-01-19</t>
+  </si>
+  <si>
     <t>2024-10-05</t>
   </si>
   <si>
@@ -264,6 +267,9 @@
     <t>2024-11-20</t>
   </si>
   <si>
+    <t>2025-01-05</t>
+  </si>
+  <si>
     <t>2024-10-19</t>
   </si>
   <si>
@@ -276,6 +282,9 @@
     <t>2024-11-29</t>
   </si>
   <si>
+    <t>2025-01-18</t>
+  </si>
+  <si>
     <t>2024-11-03</t>
   </si>
   <si>
@@ -285,6 +294,9 @@
     <t>2024-12-28</t>
   </si>
   <si>
+    <t>2025-01-12</t>
+  </si>
+  <si>
     <t>2024-10-23</t>
   </si>
   <si>
@@ -294,6 +306,12 @@
     <t>2024-12-06</t>
   </si>
   <si>
+    <t>2025-01-10</t>
+  </si>
+  <si>
+    <t>2025-01-15</t>
+  </si>
+  <si>
     <t>2024-11-22</t>
   </si>
   <si>
@@ -318,6 +336,9 @@
     <t>2024-11-30</t>
   </si>
   <si>
+    <t>2025-01-08</t>
+  </si>
+  <si>
     <t>2024-11-23</t>
   </si>
   <si>
@@ -327,15 +348,27 @@
     <t>2024-12-15</t>
   </si>
   <si>
+    <t>2025-01-03</t>
+  </si>
+  <si>
     <t>2024-12-07</t>
   </si>
   <si>
+    <t>2025-01-17</t>
+  </si>
+  <si>
     <t>2024-12-14</t>
   </si>
   <si>
     <t>2024-12-10</t>
   </si>
   <si>
+    <t>2025-01-21</t>
+  </si>
+  <si>
+    <t>2025-01-22</t>
+  </si>
+  <si>
     <t>HuberAn</t>
   </si>
   <si>
@@ -501,6 +534,39 @@
     <t>Stadthalle Villach;PiragicTr;SeewaldEl;HribarMa;ZgoncGa</t>
   </si>
   <si>
+    <t>Eisarena Salzburg;SternatCh;ZrnicMi;BedynekSe;PuffWo</t>
+  </si>
+  <si>
+    <t>Gabor Ocskay Eisarena;NikolicMa;ZrnicMi;NotheggerDa;VacziDa</t>
+  </si>
+  <si>
+    <t>Merkur Eisstadion Graz;Huber aAn;OfnerCh;JedlickaPe;KoncDa</t>
+  </si>
+  <si>
+    <t>Merkur Eisstadion Graz;SiegelSt;SternatCh;RieckenSi;WimmlerAl</t>
+  </si>
+  <si>
+    <t>Eisarena Salzburg;PiragicTr;SternatCh;NotheggerDa;ZgoncGa</t>
+  </si>
+  <si>
+    <t>Eishalle Bruneck;NikolicMa;SeewaldEl;PardatscherUl;RigoniDa</t>
+  </si>
+  <si>
+    <t>Heidi Horten Arena Klagenfurt;FichtnerPa;SmetanaLa;BedynekSe;RieckenSi</t>
+  </si>
+  <si>
+    <t>Merkur Eisstadion Graz;HlavatyAl;SoosDa;MuzsikNo;VacziDa</t>
+  </si>
+  <si>
+    <t>Merkur Eisstadion Graz;HronskyTo;OfnerCh;JedlickaPe;KoncDa</t>
+  </si>
+  <si>
+    <t>Hala Tivoli;HronskyTo;SternatCh;JedlickaPe;KoncDa</t>
+  </si>
+  <si>
+    <t>Eishalle Wien-Kagran;SmetanaLa;VoicanCh;BedynekSe;RieckenSi</t>
+  </si>
+  <si>
     <t>Tiroler Wasserkraft Arena;NikolicMa;SeewaldEl;FleischmannLu;NotheggerDa</t>
   </si>
   <si>
@@ -600,9 +666,6 @@
     <t>Eisarena Salzburg;NikolicKr;OfnerCh;BedynekSe;MoidlMa</t>
   </si>
   <si>
-    <t>Eishalle;HronskyTo;PiragicTr;JedlickaPe;KoncDa</t>
-  </si>
-  <si>
     <t>w KagranK;FichtnerPa;PiragicTr;MuzsikNo;PuffWo</t>
   </si>
   <si>
@@ -627,6 +690,33 @@
     <t>Merkur Eisstadion Graz;GroznikBo;SoosDa;BärnthalerCh;MuzsikNo</t>
   </si>
   <si>
+    <t>Gabor Ocskay Eisarena;NikolicMa;SiegelSt;Gatol-schafranekMa;WeissAl</t>
+  </si>
+  <si>
+    <t>Eishalle Feldkirch;HolzerTo;SchauerJa;FleischmannLu;MartinFl</t>
+  </si>
+  <si>
+    <t>Heidi Horten Arena Klagenfurt;FichtnerPa;SmetanaLa;BärnthalerCh;ZgoncGa</t>
+  </si>
+  <si>
+    <t>Tiroler Wasserkraft Arena;NikolicKr;NikolicMa;SparerDa;ZacherlPa</t>
+  </si>
+  <si>
+    <t>Eishalle Feldkirch;BernekerTh;NikolicKr;FleischmannLu;MartinFl</t>
+  </si>
+  <si>
+    <t>Sparkasse Arena Bozen;OfnerCh;SternatCh;FleischmannLu;MantovaniDa</t>
+  </si>
+  <si>
+    <t>Eishalle Wien-Kagran;NagyAt;SiegelSt;DurmisOt;WimmlerAl</t>
+  </si>
+  <si>
+    <t>Linz AG Eisarena;SmetanaLa;SternatCh;DurmisOt;WimmlerAl</t>
+  </si>
+  <si>
+    <t>Gabor Ocskay Eisarena;OfnerCh;SeewaldEl;Gatol-schafranekMa;MuzsikNo</t>
+  </si>
+  <si>
     <t>Hala Tivoli;PiragicTr;ZrnicMi;HribarMa;SnojTa</t>
   </si>
   <si>
@@ -717,6 +807,9 @@
     <t>Eishalle KagranEins;FichtnerPa;SeewaldEl;DurmisOt;WimmlerAl</t>
   </si>
   <si>
+    <t>Stadthalle Villach;HronskyTo;PiragicTr;JedlickaPe;KoncDa</t>
+  </si>
+  <si>
     <t>Merkur Eisstadion Graz;OfnerCh;SeewaldEl;BärnthalerCh;Gatol-schafranekMa</t>
   </si>
   <si>
@@ -726,9 +819,6 @@
     <t>Tiroler Wasserkraft Arena;BernekerTh;HolzerTo;SparerDa;WeissAl</t>
   </si>
   <si>
-    <t>Eishalle;SeewaldEl;SoosDa;MuzsikNo;NotheggerDa</t>
-  </si>
-  <si>
     <t>Hala Tivoli;GroznikBo;SoosDa;MuzsikNo;VacziDa</t>
   </si>
   <si>
@@ -741,6 +831,27 @@
     <t>Stadthalle Villach;NagyAt;PiragicTr;BedynekSe;VacziDa</t>
   </si>
   <si>
+    <t>Heidi Horten Arena Klagenfurt;SmetanaLa;SoosDa;BärnthalerCh;RieckenSi</t>
+  </si>
+  <si>
+    <t>Tiroler Wasserkraft Arena;KainbergerJu;OfnerCh;SeewaldJe;WimmlerAl</t>
+  </si>
+  <si>
+    <t>Eisarena Salzburg;SchauerJa;ZrnicMi;NotheggerDa;RieckenSi</t>
+  </si>
+  <si>
+    <t>Eishalle Wien-Kagran;FichtnerPa;KainbergerJu;Gatol-schafranekMa;MoidlMa</t>
+  </si>
+  <si>
+    <t>Eishalle Bruneck;GroznikBo;OfnerCh;PardatscherUl;SparerDa</t>
+  </si>
+  <si>
+    <t>Stadthalle Villach;GroznikBo;PiragicTr;HribarMa;ZgoncGa</t>
+  </si>
+  <si>
+    <t>Eishalle Bruneck;NikolicMa;NikolicKr;MantovaniDa;SparerDa</t>
+  </si>
+  <si>
     <t>Eishalle Wien-Kagran;HronskyTo;SmetanaLa;DurmisOt;WeissAl</t>
   </si>
   <si>
@@ -840,7 +951,25 @@
     <t>Eisarena Salzburg;HronskyTo;SternatCh;JedlickaPe;SeewaldJe</t>
   </si>
   <si>
-    <t>Tiroler Wasserkraft Arena;NikolicKr;NikolicMa;MartinFl;SparerDa</t>
+    <t>Tiroler Wasserkraft Arena;NikolicMa;NikolicKr;MartinFl;SparerDa</t>
+  </si>
+  <si>
+    <t>Sparkasse Arena Bozen;BernekerTh;SeewaldEl;RigoniDa;SparerDa</t>
+  </si>
+  <si>
+    <t>Eishalle Wien-Kagran;HronskyTo;SternatCh;JedlickaPe;KoncDa</t>
+  </si>
+  <si>
+    <t>Linz AG Eisarena;PiragicTr;SiegelSt;Gatol-schafranekMa;SeewaldJe</t>
+  </si>
+  <si>
+    <t>Linz AG Eisarena;Huber aAn;SmetanaLa;DurmisOt;NotheggerDa</t>
+  </si>
+  <si>
+    <t>Stadthalle Villach;RezekGr;SmetanaLa;HribarMa;RieckenSi</t>
+  </si>
+  <si>
+    <t>Gabor Ocskay Eisarena;OfnerCh;SeewaldEl;MuzsikNo;VacziDa</t>
   </si>
   <si>
     <t>Eishalle Bruneck;BernekerTh;HuberAn;MartinFl;PardatscherUl</t>
@@ -927,6 +1056,24 @@
     <t>Linz AG Eisarena;Huber aAn;OfnerCh;NotheggerDa;SeewaldJe</t>
   </si>
   <si>
+    <t>Eishalle Bruneck;Huber aAn;PiragicTr;MartinFl;PardatscherUl</t>
+  </si>
+  <si>
+    <t>Stadthalle Villach;FichtnerPa;SmetanaLa;JeramFi;ZgoncGa</t>
+  </si>
+  <si>
+    <t>Hala Tivoli;NagyAt;SternatCh;HribarMa;PuffWo</t>
+  </si>
+  <si>
+    <t>Hala Tivoli;GroznikBo;OfnerCh;MuzsikNo;VacziDa</t>
+  </si>
+  <si>
+    <t>Heidi Horten Arena Klagenfurt;HronskyTo;Huber aAn;BärnthalerCh;DurmisOt</t>
+  </si>
+  <si>
+    <t>Eishalle Asiago;NikolicKr;SternatCh;PardatscherUl;SparerDa</t>
+  </si>
+  <si>
     <t>Eiswelle Bozen;OfnerCh;RezekGr;PuffWo;ZgoncGa</t>
   </si>
   <si>
@@ -981,7 +1128,25 @@
     <t>Eishalle Bruneck;RezekGr;SternatCh;RigoniDa;ZgoncGa</t>
   </si>
   <si>
+    <t>Eishalle Asiago;GroznikBo;OfnerCh;HribarMa;MantovaniDa</t>
+  </si>
+  <si>
+    <t>Sparkasse Arena Bozen;NikolicKr;PiragicTr;MantovaniDa;PardatscherUl</t>
+  </si>
+  <si>
+    <t>Eishalle Asiago;GroznikBo;RezekGr;PardatscherUl;RigoniDa</t>
+  </si>
+  <si>
+    <t>Eishalle Bruneck;PiragicTr;SchauerJa;MantovaniDa;ZgoncGa</t>
+  </si>
+  <si>
+    <t>Eishalle Asiago;NikolicMa;SchauerJa;MantovaniDa;RigoniDa</t>
+  </si>
+  <si>
     <t>Stadthalle Villach;KainbergerJu;SternatCh;DurmisOt;JedlickaPe</t>
+  </si>
+  <si>
+    <t>Stadthalle Villach;SeewaldEl;SoosDa;MuzsikNo;NotheggerDa</t>
   </si>
 </sst>
 </file>
@@ -1995,8 +2160,11 @@
       <c r="AT5" t="s">
         <v>68</v>
       </c>
+      <c r="AW5" t="s">
+        <v>69</v>
+      </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>57</v>
       </c>
@@ -2046,7 +2214,7 @@
         <v>66</v>
       </c>
       <c r="Q6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R6" t="s">
         <v>56</v>
@@ -2085,10 +2253,10 @@
         <v>56</v>
       </c>
       <c r="AD6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AE6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AF6" t="s">
         <v>58</v>
@@ -2097,7 +2265,7 @@
         <v>56</v>
       </c>
       <c r="AH6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AI6" t="s">
         <v>56</v>
@@ -2115,25 +2283,25 @@
         <v>65</v>
       </c>
       <c r="AN6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AO6" t="s">
         <v>64</v>
       </c>
       <c r="AP6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ6" t="s">
         <v>68</v>
       </c>
       <c r="AR6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AS6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AT6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
@@ -2165,7 +2333,7 @@
         <v>66</v>
       </c>
       <c r="J7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K7" t="s">
         <v>66</v>
@@ -2183,7 +2351,7 @@
         <v>58</v>
       </c>
       <c r="P7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q7" t="s">
         <v>59</v>
@@ -2195,49 +2363,49 @@
         <v>66</v>
       </c>
       <c r="T7" t="s">
+        <v>71</v>
+      </c>
+      <c r="U7" t="s">
         <v>70</v>
-      </c>
-      <c r="U7" t="s">
-        <v>69</v>
       </c>
       <c r="V7" t="s">
         <v>57</v>
       </c>
       <c r="W7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="X7" t="s">
         <v>66</v>
       </c>
       <c r="Y7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Z7" t="s">
         <v>66</v>
       </c>
       <c r="AA7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AB7" t="s">
         <v>66</v>
       </c>
       <c r="AC7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AD7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AE7" t="s">
         <v>65</v>
       </c>
       <c r="AF7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG7" t="s">
         <v>66</v>
       </c>
       <c r="AH7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI7" t="s">
         <v>58</v>
@@ -2252,28 +2420,31 @@
         <v>59</v>
       </c>
       <c r="AM7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AO7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AP7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AR7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AS7" t="s">
         <v>60</v>
       </c>
+      <c r="AT7" t="s">
+        <v>83</v>
+      </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>56</v>
       </c>
@@ -2296,16 +2467,16 @@
         <v>58</v>
       </c>
       <c r="H8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J8" t="s">
         <v>58</v>
       </c>
       <c r="K8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L8" t="s">
         <v>58</v>
@@ -2314,10 +2485,10 @@
         <v>58</v>
       </c>
       <c r="N8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="P8" t="s">
         <v>59</v>
@@ -2329,7 +2500,7 @@
         <v>54</v>
       </c>
       <c r="S8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="T8" t="s">
         <v>58</v>
@@ -2338,25 +2509,25 @@
         <v>66</v>
       </c>
       <c r="V8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="W8" t="s">
+        <v>72</v>
+      </c>
+      <c r="X8" t="s">
         <v>71</v>
-      </c>
-      <c r="X8" t="s">
-        <v>70</v>
       </c>
       <c r="Y8" t="s">
         <v>59</v>
       </c>
       <c r="Z8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AA8" t="s">
         <v>64</v>
       </c>
       <c r="AB8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AC8" t="s">
         <v>58</v>
@@ -2365,66 +2536,72 @@
         <v>68</v>
       </c>
       <c r="AE8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AF8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AG8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AH8" t="s">
         <v>64</v>
       </c>
       <c r="AI8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ8" t="s">
         <v>65</v>
       </c>
       <c r="AK8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AL8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AM8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AN8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AO8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AP8" t="s">
         <v>60</v>
       </c>
+      <c r="AQ8" t="s">
+        <v>88</v>
+      </c>
       <c r="AR8" t="s">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="AS8" t="s">
+        <v>83</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B9" t="s">
         <v>70</v>
-      </c>
-      <c r="B9" t="s">
-        <v>69</v>
       </c>
       <c r="C9" t="s">
         <v>59</v>
       </c>
       <c r="D9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F9" t="s">
         <v>65</v>
       </c>
       <c r="G9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H9" t="s">
         <v>58</v>
@@ -2433,132 +2610,138 @@
         <v>65</v>
       </c>
       <c r="J9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="L9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M9" t="s">
         <v>65</v>
       </c>
       <c r="N9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O9" t="s">
         <v>65</v>
       </c>
       <c r="P9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T9" t="s">
         <v>65</v>
       </c>
       <c r="U9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V9" t="s">
         <v>65</v>
       </c>
       <c r="W9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Y9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Z9" t="s">
         <v>64</v>
       </c>
       <c r="AA9" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AB9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AC9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD9" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AE9" t="s">
         <v>68</v>
       </c>
       <c r="AF9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AG9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AI9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AJ9" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="AK9" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="AL9" t="s">
         <v>68</v>
       </c>
       <c r="AM9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AN9" t="s">
         <v>81</v>
-      </c>
-      <c r="AN9" t="s">
-        <v>80</v>
       </c>
       <c r="AO9" t="s">
         <v>67</v>
       </c>
       <c r="AP9" t="s">
-        <v>88</v>
+        <v>91</v>
+      </c>
+      <c r="AR9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AS9" t="s">
+        <v>92</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
         <v>65</v>
       </c>
       <c r="D10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E10" t="s">
         <v>54</v>
       </c>
       <c r="F10" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J10" t="s">
         <v>65</v>
@@ -2567,10 +2750,10 @@
         <v>65</v>
       </c>
       <c r="L10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N10" t="s">
         <v>65</v>
@@ -2579,111 +2762,117 @@
         <v>64</v>
       </c>
       <c r="P10" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="Q10" t="s">
         <v>64</v>
       </c>
       <c r="R10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S10" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="T10" t="s">
         <v>64</v>
       </c>
       <c r="U10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="V10" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="W10" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="X10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Y10" t="s">
         <v>65</v>
       </c>
       <c r="Z10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AA10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AB10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AC10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AD10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AE10" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AF10" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="AG10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH10" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="AI10" t="s">
         <v>65</v>
       </c>
       <c r="AJ10" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AK10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AL10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM10" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AN10" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="AO10" t="s">
-        <v>91</v>
+        <v>95</v>
+      </c>
+      <c r="AP10" t="s">
+        <v>96</v>
+      </c>
+      <c r="AS10" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B11" t="s">
         <v>65</v>
       </c>
       <c r="C11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D11" t="s">
         <v>64</v>
       </c>
       <c r="E11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F11" t="s">
         <v>64</v>
       </c>
       <c r="G11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H11" t="s">
         <v>65</v>
       </c>
       <c r="I11" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="J11" t="s">
         <v>64</v>
@@ -2698,13 +2887,13 @@
         <v>64</v>
       </c>
       <c r="N11" t="s">
+        <v>74</v>
+      </c>
+      <c r="O11" t="s">
         <v>73</v>
       </c>
-      <c r="O11" t="s">
-        <v>72</v>
-      </c>
       <c r="P11" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="Q11" t="s">
         <v>68</v>
@@ -2716,7 +2905,7 @@
         <v>64</v>
       </c>
       <c r="T11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="U11" t="s">
         <v>64</v>
@@ -2734,52 +2923,52 @@
         <v>64</v>
       </c>
       <c r="Z11" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AA11" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="AB11" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AC11" t="s">
         <v>68</v>
       </c>
       <c r="AD11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AE11" t="s">
         <v>56</v>
       </c>
       <c r="AF11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AG11" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="AH11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI11" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="AJ11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AK11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AL11" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="AM11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AN11" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="AO11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
@@ -2787,25 +2976,25 @@
         <v>65</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
         <v>64</v>
       </c>
       <c r="D12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E12" t="s">
         <v>65</v>
       </c>
       <c r="F12" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="G12" t="s">
         <v>64</v>
       </c>
       <c r="H12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I12" t="s">
         <v>68</v>
@@ -2817,108 +3006,111 @@
         <v>68</v>
       </c>
       <c r="L12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="N12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O12" t="s">
         <v>68</v>
       </c>
       <c r="P12" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Q12" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="R12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="S12" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="T12" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="U12" t="s">
         <v>68</v>
       </c>
       <c r="V12" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="W12" t="s">
+        <v>79</v>
+      </c>
+      <c r="X12" t="s">
+        <v>89</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z12" t="s">
         <v>78</v>
       </c>
-      <c r="X12" t="s">
-        <v>86</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z12" t="s">
-        <v>77</v>
-      </c>
       <c r="AA12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB12" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD12" t="s">
         <v>87</v>
       </c>
-      <c r="AC12" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>85</v>
-      </c>
       <c r="AE12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF12" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="AG12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AJ12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK12" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="AL12" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="AM12" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="AN12" t="s">
-        <v>98</v>
+        <v>104</v>
+      </c>
+      <c r="AO12" t="s">
+        <v>83</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B13" t="s">
         <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D13" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F13" t="s">
         <v>68</v>
@@ -2927,97 +3119,97 @@
         <v>68</v>
       </c>
       <c r="H13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J13" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L13" t="s">
         <v>68</v>
       </c>
       <c r="M13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N13" t="s">
+        <v>79</v>
+      </c>
+      <c r="O13" t="s">
+        <v>79</v>
+      </c>
+      <c r="P13" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q13" t="s">
         <v>78</v>
       </c>
-      <c r="O13" t="s">
+      <c r="R13" t="s">
         <v>78</v>
       </c>
-      <c r="P13" t="s">
+      <c r="S13" t="s">
+        <v>89</v>
+      </c>
+      <c r="T13" t="s">
+        <v>79</v>
+      </c>
+      <c r="U13" t="s">
         <v>78</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>77</v>
-      </c>
-      <c r="R13" t="s">
-        <v>77</v>
-      </c>
-      <c r="S13" t="s">
-        <v>86</v>
-      </c>
-      <c r="T13" t="s">
-        <v>78</v>
-      </c>
-      <c r="U13" t="s">
-        <v>77</v>
       </c>
       <c r="V13" t="s">
         <v>64</v>
       </c>
       <c r="W13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="X13" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y13" t="s">
         <v>78</v>
       </c>
-      <c r="Y13" t="s">
-        <v>77</v>
-      </c>
       <c r="Z13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AA13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AB13" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="AC13" t="s">
+        <v>82</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>99</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>98</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>87</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>76</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>95</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>87</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>87</v>
+      </c>
+      <c r="AL13" t="s">
         <v>81</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>93</v>
-      </c>
-      <c r="AE13" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>92</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>85</v>
-      </c>
-      <c r="AH13" t="s">
-        <v>75</v>
-      </c>
-      <c r="AI13" t="s">
-        <v>91</v>
-      </c>
-      <c r="AJ13" t="s">
-        <v>85</v>
-      </c>
-      <c r="AK13" t="s">
-        <v>85</v>
-      </c>
-      <c r="AL13" t="s">
-        <v>80</v>
       </c>
       <c r="AM13" t="s">
         <v>62</v>
@@ -3025,231 +3217,237 @@
       <c r="AN13" t="s">
         <v>67</v>
       </c>
+      <c r="AO13" t="s">
+        <v>96</v>
+      </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>64</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D14" t="s">
         <v>68</v>
       </c>
       <c r="E14" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F14" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G14" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H14" t="s">
         <v>68</v>
       </c>
       <c r="I14" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="J14" t="s">
+        <v>79</v>
+      </c>
+      <c r="K14" t="s">
+        <v>79</v>
+      </c>
+      <c r="L14" t="s">
         <v>78</v>
       </c>
-      <c r="K14" t="s">
+      <c r="M14" t="s">
+        <v>101</v>
+      </c>
+      <c r="N14" t="s">
+        <v>86</v>
+      </c>
+      <c r="O14" t="s">
+        <v>82</v>
+      </c>
+      <c r="P14" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>79</v>
+      </c>
+      <c r="R14" t="s">
+        <v>79</v>
+      </c>
+      <c r="S14" t="s">
+        <v>98</v>
+      </c>
+      <c r="T14" t="s">
+        <v>98</v>
+      </c>
+      <c r="U14" t="s">
+        <v>82</v>
+      </c>
+      <c r="V14" t="s">
         <v>78</v>
       </c>
-      <c r="L14" t="s">
-        <v>77</v>
-      </c>
-      <c r="M14" t="s">
-        <v>95</v>
-      </c>
-      <c r="N14" t="s">
-        <v>84</v>
-      </c>
-      <c r="O14" t="s">
-        <v>81</v>
-      </c>
-      <c r="P14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>78</v>
-      </c>
-      <c r="R14" t="s">
-        <v>78</v>
-      </c>
-      <c r="S14" t="s">
-        <v>92</v>
-      </c>
-      <c r="T14" t="s">
-        <v>92</v>
-      </c>
-      <c r="U14" t="s">
-        <v>81</v>
-      </c>
-      <c r="V14" t="s">
-        <v>77</v>
-      </c>
       <c r="W14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="X14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Y14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA14" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="AB14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC14" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="AD14" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="AE14" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="AF14" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AG14" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="AH14" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="AI14" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="AJ14" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="AK14" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="AL14" t="s">
         <v>62</v>
       </c>
       <c r="AM14" t="s">
-        <v>91</v>
+        <v>95</v>
+      </c>
+      <c r="AN14" t="s">
+        <v>106</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B15" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C15" t="s">
         <v>68</v>
       </c>
       <c r="D15" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E15" t="s">
         <v>68</v>
       </c>
       <c r="F15" t="s">
+        <v>79</v>
+      </c>
+      <c r="G15" t="s">
         <v>78</v>
       </c>
-      <c r="G15" t="s">
-        <v>77</v>
-      </c>
       <c r="H15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J15" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K15" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L15" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="M15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="O15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="P15" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="Q15" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="R15" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="S15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="V15" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="W15" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="X15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Y15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="Z15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AA15" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB15" t="s">
         <v>87</v>
       </c>
-      <c r="AB15" t="s">
-        <v>85</v>
-      </c>
       <c r="AC15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AD15" t="s">
         <v>64</v>
       </c>
       <c r="AE15" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="AF15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AG15" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="AH15" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="AI15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AJ15" t="s">
         <v>67</v>
@@ -3258,123 +3456,129 @@
         <v>67</v>
       </c>
       <c r="AL15" t="s">
-        <v>88</v>
+        <v>91</v>
+      </c>
+      <c r="AM15" t="s">
+        <v>96</v>
+      </c>
+      <c r="AN15" t="s">
+        <v>83</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B16" t="s">
         <v>68</v>
       </c>
       <c r="C16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" t="s">
+        <v>78</v>
+      </c>
+      <c r="E16" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" t="s">
         <v>86</v>
       </c>
-      <c r="D16" t="s">
-        <v>77</v>
-      </c>
-      <c r="E16" t="s">
-        <v>77</v>
-      </c>
-      <c r="F16" t="s">
-        <v>84</v>
-      </c>
       <c r="G16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K16" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="L16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q16" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="R16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T16" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="U16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="V16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W16" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="X16" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="Y16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z16" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AA16" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="AB16" t="s">
         <v>67</v>
       </c>
       <c r="AC16" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="AD16" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="AE16" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="AF16" t="s">
         <v>67</v>
       </c>
       <c r="AG16" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="AH16" t="s">
         <v>67</v>
       </c>
       <c r="AI16" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="AJ16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AK16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AL16" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
@@ -3382,403 +3586,412 @@
         <v>68</v>
       </c>
       <c r="B17" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="H17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I17" t="s">
+        <v>105</v>
+      </c>
+      <c r="J17" t="s">
+        <v>105</v>
+      </c>
+      <c r="K17" t="s">
+        <v>87</v>
+      </c>
+      <c r="L17" t="s">
+        <v>80</v>
+      </c>
+      <c r="M17" t="s">
+        <v>76</v>
+      </c>
+      <c r="N17" t="s">
+        <v>87</v>
+      </c>
+      <c r="O17" t="s">
+        <v>102</v>
+      </c>
+      <c r="P17" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>76</v>
+      </c>
+      <c r="R17" t="s">
+        <v>98</v>
+      </c>
+      <c r="S17" t="s">
         <v>99</v>
       </c>
-      <c r="J17" t="s">
-        <v>99</v>
-      </c>
-      <c r="K17" t="s">
-        <v>85</v>
-      </c>
-      <c r="L17" t="s">
-        <v>79</v>
-      </c>
-      <c r="M17" t="s">
-        <v>75</v>
-      </c>
-      <c r="N17" t="s">
-        <v>85</v>
-      </c>
-      <c r="O17" t="s">
-        <v>96</v>
-      </c>
-      <c r="P17" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>75</v>
-      </c>
-      <c r="R17" t="s">
-        <v>92</v>
-      </c>
-      <c r="S17" t="s">
-        <v>93</v>
-      </c>
       <c r="T17" t="s">
+        <v>108</v>
+      </c>
+      <c r="U17" t="s">
+        <v>87</v>
+      </c>
+      <c r="V17" t="s">
+        <v>108</v>
+      </c>
+      <c r="W17" t="s">
         <v>101</v>
       </c>
-      <c r="U17" t="s">
-        <v>85</v>
-      </c>
-      <c r="V17" t="s">
-        <v>101</v>
-      </c>
-      <c r="W17" t="s">
+      <c r="X17" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>105</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>103</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>109</v>
+      </c>
+      <c r="AC17" t="s">
         <v>95</v>
       </c>
-      <c r="X17" t="s">
-        <v>96</v>
-      </c>
-      <c r="Y17" t="s">
-        <v>85</v>
-      </c>
-      <c r="Z17" t="s">
-        <v>99</v>
-      </c>
-      <c r="AA17" t="s">
-        <v>97</v>
-      </c>
-      <c r="AB17" t="s">
-        <v>102</v>
-      </c>
-      <c r="AC17" t="s">
+      <c r="AD17" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>81</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>81</v>
+      </c>
+      <c r="AG17" t="s">
+        <v>109</v>
+      </c>
+      <c r="AH17" t="s">
         <v>91</v>
       </c>
-      <c r="AD17" t="s">
-        <v>97</v>
-      </c>
-      <c r="AE17" t="s">
-        <v>80</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>80</v>
-      </c>
-      <c r="AG17" t="s">
-        <v>102</v>
-      </c>
-      <c r="AH17" t="s">
-        <v>88</v>
-      </c>
       <c r="AI17" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="AJ17" t="s">
         <v>60</v>
       </c>
       <c r="AK17" t="s">
-        <v>88</v>
+        <v>91</v>
+      </c>
+      <c r="AL17" t="s">
+        <v>110</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s">
+        <v>101</v>
+      </c>
+      <c r="D18" t="s">
+        <v>101</v>
+      </c>
+      <c r="E18" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" t="s">
+        <v>80</v>
+      </c>
+      <c r="H18" t="s">
+        <v>76</v>
+      </c>
+      <c r="I18" t="s">
+        <v>99</v>
+      </c>
+      <c r="J18" t="s">
+        <v>99</v>
+      </c>
+      <c r="K18" t="s">
+        <v>99</v>
+      </c>
+      <c r="L18" t="s">
+        <v>99</v>
+      </c>
+      <c r="M18" t="s">
+        <v>87</v>
+      </c>
+      <c r="N18" t="s">
+        <v>102</v>
+      </c>
+      <c r="O18" t="s">
+        <v>103</v>
+      </c>
+      <c r="P18" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>87</v>
+      </c>
+      <c r="R18" t="s">
+        <v>76</v>
+      </c>
+      <c r="S18" t="s">
+        <v>103</v>
+      </c>
+      <c r="T18" t="s">
         <v>95</v>
-      </c>
-      <c r="D18" t="s">
-        <v>95</v>
-      </c>
-      <c r="E18" t="s">
-        <v>75</v>
-      </c>
-      <c r="F18" t="s">
-        <v>75</v>
-      </c>
-      <c r="G18" t="s">
-        <v>79</v>
-      </c>
-      <c r="H18" t="s">
-        <v>75</v>
-      </c>
-      <c r="I18" t="s">
-        <v>93</v>
-      </c>
-      <c r="J18" t="s">
-        <v>93</v>
-      </c>
-      <c r="K18" t="s">
-        <v>93</v>
-      </c>
-      <c r="L18" t="s">
-        <v>93</v>
-      </c>
-      <c r="M18" t="s">
-        <v>85</v>
-      </c>
-      <c r="N18" t="s">
-        <v>96</v>
-      </c>
-      <c r="O18" t="s">
-        <v>97</v>
-      </c>
-      <c r="P18" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>85</v>
-      </c>
-      <c r="R18" t="s">
-        <v>75</v>
-      </c>
-      <c r="S18" t="s">
-        <v>97</v>
-      </c>
-      <c r="T18" t="s">
-        <v>91</v>
       </c>
       <c r="U18" t="s">
         <v>67</v>
       </c>
       <c r="V18" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="W18" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="X18" t="s">
         <v>67</v>
       </c>
       <c r="Y18" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="Z18" t="s">
         <v>67</v>
       </c>
       <c r="AA18" t="s">
-        <v>104</v>
+        <v>61</v>
       </c>
       <c r="AB18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AC18" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="AD18" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="AE18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AF18" t="s">
         <v>60</v>
       </c>
       <c r="AG18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AH18" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="AI18" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="AJ18" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="AK18" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B19" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D19" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E19" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="F19" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G19" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H19" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="I19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J19" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="K19" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="L19" t="s">
         <v>67</v>
       </c>
       <c r="M19" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="N19" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="O19" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="P19" t="s">
-        <v>104</v>
+        <v>61</v>
       </c>
       <c r="Q19" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="R19" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="S19" t="s">
-        <v>104</v>
+        <v>61</v>
       </c>
       <c r="T19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="U19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="V19" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="W19" t="s">
         <v>67</v>
       </c>
       <c r="X19" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="Y19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Z19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AA19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AB19" t="s">
         <v>60</v>
       </c>
       <c r="AC19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AD19" t="s">
         <v>60</v>
       </c>
       <c r="AE19" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="AF19" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="AG19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH19" t="s">
+        <v>104</v>
+      </c>
+      <c r="AI19" t="s">
+        <v>83</v>
+      </c>
+      <c r="AJ19" t="s">
+        <v>100</v>
+      </c>
+      <c r="AK19" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>101</v>
+      </c>
+      <c r="B20" t="s">
+        <v>101</v>
+      </c>
+      <c r="C20" t="s">
         <v>98</v>
       </c>
-      <c r="AJ19" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>95</v>
-      </c>
-      <c r="B20" t="s">
-        <v>95</v>
-      </c>
-      <c r="C20" t="s">
-        <v>92</v>
-      </c>
       <c r="D20" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E20" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F20" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G20" t="s">
         <v>67</v>
       </c>
       <c r="H20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I20" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="J20" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="K20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L20" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="M20" t="s">
         <v>67</v>
       </c>
       <c r="N20" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="O20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q20" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="R20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="S20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T20" t="s">
         <v>62</v>
       </c>
       <c r="U20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="V20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="W20" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="X20" t="s">
         <v>62</v>
@@ -3787,84 +4000,96 @@
         <v>62</v>
       </c>
       <c r="Z20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AA20" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>91</v>
+      </c>
+      <c r="AD20" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE20" t="s">
+        <v>100</v>
+      </c>
+      <c r="AF20" t="s">
+        <v>104</v>
+      </c>
+      <c r="AG20" t="s">
+        <v>95</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>110</v>
+      </c>
+      <c r="AI20" t="s">
+        <v>96</v>
+      </c>
+      <c r="AJ20" t="s">
+        <v>110</v>
+      </c>
+      <c r="AK20" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>98</v>
       </c>
-      <c r="AB20" t="s">
-        <v>98</v>
-      </c>
-      <c r="AC20" t="s">
-        <v>88</v>
-      </c>
-      <c r="AD20" t="s">
-        <v>88</v>
-      </c>
-      <c r="AE20" t="s">
-        <v>94</v>
-      </c>
-      <c r="AF20" t="s">
-        <v>98</v>
-      </c>
-      <c r="AG20" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>92</v>
-      </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="D21" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="E21" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G21" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="H21" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="I21" t="s">
         <v>67</v>
       </c>
       <c r="J21" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="K21" t="s">
         <v>62</v>
       </c>
       <c r="L21" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="M21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N21" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="O21" t="s">
         <v>62</v>
       </c>
       <c r="P21" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q21" t="s">
         <v>67</v>
       </c>
       <c r="R21" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="S21" t="s">
         <v>62</v>
@@ -3879,72 +4104,90 @@
         <v>62</v>
       </c>
       <c r="W21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X21" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="Y21" t="s">
         <v>60</v>
       </c>
       <c r="Z21" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="AA21" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="AB21" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="AC21" t="s">
+        <v>104</v>
+      </c>
+      <c r="AD21" t="s">
+        <v>83</v>
+      </c>
+      <c r="AE21" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF21" t="s">
+        <v>100</v>
+      </c>
+      <c r="AG21" t="s">
+        <v>96</v>
+      </c>
+      <c r="AH21" t="s">
+        <v>106</v>
+      </c>
+      <c r="AI21" t="s">
+        <v>92</v>
+      </c>
+      <c r="AJ21" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" t="s">
         <v>98</v>
       </c>
-      <c r="AF21" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>79</v>
-      </c>
-      <c r="B22" t="s">
-        <v>92</v>
-      </c>
       <c r="C22" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D22" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E22" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="F22" t="s">
         <v>67</v>
       </c>
       <c r="G22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H22" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="I22" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="J22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K22" t="s">
         <v>60</v>
       </c>
       <c r="L22" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O22" t="s">
         <v>60</v>
@@ -3953,19 +4196,19 @@
         <v>62</v>
       </c>
       <c r="Q22" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="R22" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="S22" t="s">
         <v>60</v>
       </c>
       <c r="T22" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="U22" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="V22" t="s">
         <v>60</v>
@@ -3974,42 +4217,69 @@
         <v>62</v>
       </c>
       <c r="X22" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="Y22" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Z22" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="AA22" t="s">
-        <v>91</v>
+        <v>95</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>96</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD22" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE22" t="s">
+        <v>106</v>
+      </c>
+      <c r="AF22" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG22" t="s">
+        <v>92</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>96</v>
+      </c>
+      <c r="AI22" t="s">
+        <v>112</v>
+      </c>
+      <c r="AJ22" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C23" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D23" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E23" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="F23" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="G23" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H23" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I23" t="s">
         <v>62</v>
@@ -4018,7 +4288,7 @@
         <v>62</v>
       </c>
       <c r="K23" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="L23" t="s">
         <v>60</v>
@@ -4030,54 +4300,90 @@
         <v>62</v>
       </c>
       <c r="O23" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="P23" t="s">
         <v>60</v>
       </c>
       <c r="Q23" t="s">
+        <v>113</v>
+      </c>
+      <c r="R23" t="s">
+        <v>100</v>
+      </c>
+      <c r="S23" t="s">
         <v>104</v>
       </c>
-      <c r="R23" t="s">
-        <v>94</v>
-      </c>
-      <c r="S23" t="s">
-        <v>98</v>
-      </c>
       <c r="T23" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="U23" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="V23" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="W23" t="s">
-        <v>94</v>
+        <v>100</v>
+      </c>
+      <c r="X23" t="s">
+        <v>106</v>
       </c>
       <c r="Y23" t="s">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>110</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD23" t="s">
+        <v>112</v>
+      </c>
+      <c r="AE23" t="s">
+        <v>96</v>
+      </c>
+      <c r="AF23" t="s">
+        <v>96</v>
+      </c>
+      <c r="AG23" t="s">
+        <v>112</v>
+      </c>
+      <c r="AH23" t="s">
+        <v>92</v>
+      </c>
+      <c r="AI23" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ23" t="s">
+        <v>62</v>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B24" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C24" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="D24" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="E24" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="F24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G24" t="s">
         <v>60</v>
@@ -4086,48 +4392,90 @@
         <v>62</v>
       </c>
       <c r="I24" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="J24" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="K24" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="L24" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="M24" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="N24" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="O24" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>98</v>
+        <v>104</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>110</v>
+      </c>
+      <c r="R24" t="s">
+        <v>110</v>
+      </c>
+      <c r="S24" t="s">
+        <v>61</v>
       </c>
       <c r="T24" t="s">
-        <v>96</v>
+        <v>102</v>
+      </c>
+      <c r="U24" t="s">
+        <v>110</v>
       </c>
       <c r="V24" t="s">
-        <v>96</v>
+        <v>102</v>
+      </c>
+      <c r="W24" t="s">
+        <v>110</v>
+      </c>
+      <c r="X24" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>106</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD24" t="s">
+        <v>69</v>
+      </c>
+      <c r="AE24" t="s">
+        <v>92</v>
+      </c>
+      <c r="AF24" t="s">
+        <v>112</v>
+      </c>
+      <c r="AG24" t="s">
+        <v>69</v>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="B25" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D25" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E25" t="s">
         <v>62</v>
@@ -4136,161 +4484,467 @@
         <v>60</v>
       </c>
       <c r="G25" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="H25" t="s">
         <v>60</v>
       </c>
       <c r="I25" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="J25" t="s">
-        <v>94</v>
+        <v>100</v>
+      </c>
+      <c r="K25" t="s">
+        <v>110</v>
       </c>
       <c r="L25" t="s">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="M25" t="s">
+        <v>110</v>
+      </c>
+      <c r="N25" t="s">
+        <v>83</v>
+      </c>
+      <c r="O25" t="s">
+        <v>110</v>
+      </c>
+      <c r="P25" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>106</v>
+      </c>
+      <c r="R25" t="s">
+        <v>83</v>
+      </c>
+      <c r="S25" t="s">
+        <v>113</v>
+      </c>
+      <c r="T25" t="s">
+        <v>110</v>
+      </c>
+      <c r="U25" t="s">
+        <v>96</v>
+      </c>
+      <c r="V25" t="s">
+        <v>110</v>
+      </c>
+      <c r="W25" t="s">
+        <v>106</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>106</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>83</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE25" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF25" t="s">
+        <v>69</v>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C26" t="s">
+        <v>111</v>
+      </c>
+      <c r="D26" t="s">
+        <v>81</v>
+      </c>
+      <c r="E26" t="s">
+        <v>91</v>
+      </c>
+      <c r="F26" t="s">
+        <v>104</v>
+      </c>
+      <c r="G26" t="s">
+        <v>100</v>
+      </c>
+      <c r="H26" t="s">
+        <v>91</v>
+      </c>
+      <c r="I26" t="s">
+        <v>114</v>
+      </c>
+      <c r="J26" t="s">
+        <v>110</v>
+      </c>
+      <c r="K26" t="s">
+        <v>61</v>
+      </c>
+      <c r="L26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M26" t="s">
+        <v>83</v>
+      </c>
+      <c r="N26" t="s">
+        <v>106</v>
+      </c>
+      <c r="O26" t="s">
+        <v>106</v>
+      </c>
+      <c r="P26" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>96</v>
+      </c>
+      <c r="R26" t="s">
+        <v>92</v>
+      </c>
+      <c r="S26" t="s">
+        <v>83</v>
+      </c>
+      <c r="T26" t="s">
+        <v>83</v>
+      </c>
+      <c r="U26" t="s">
+        <v>92</v>
+      </c>
+      <c r="V26" t="s">
+        <v>106</v>
+      </c>
+      <c r="W26" t="s">
+        <v>96</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AA26" t="s">
+        <v>106</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE26" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>95</v>
+      </c>
+      <c r="B27" t="s">
+        <v>102</v>
+      </c>
+      <c r="C27" t="s">
         <v>103</v>
-      </c>
-      <c r="D26" t="s">
-        <v>80</v>
-      </c>
-      <c r="E26" t="s">
-        <v>88</v>
-      </c>
-      <c r="F26" t="s">
-        <v>98</v>
-      </c>
-      <c r="G26" t="s">
-        <v>94</v>
-      </c>
-      <c r="H26" t="s">
-        <v>88</v>
-      </c>
-      <c r="I26" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>91</v>
-      </c>
-      <c r="B27" t="s">
-        <v>96</v>
-      </c>
-      <c r="C27" t="s">
-        <v>97</v>
       </c>
       <c r="D27" t="s">
         <v>60</v>
       </c>
       <c r="E27" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F27" t="s">
-        <v>94</v>
+        <v>100</v>
+      </c>
+      <c r="G27" t="s">
+        <v>110</v>
       </c>
       <c r="H27" t="s">
         <v>67</v>
       </c>
+      <c r="I27" t="s">
+        <v>110</v>
+      </c>
+      <c r="J27" t="s">
+        <v>106</v>
+      </c>
+      <c r="K27" t="s">
+        <v>112</v>
+      </c>
+      <c r="L27" t="s">
+        <v>97</v>
+      </c>
+      <c r="M27" t="s">
+        <v>106</v>
+      </c>
+      <c r="N27" t="s">
+        <v>96</v>
+      </c>
+      <c r="O27" t="s">
+        <v>92</v>
+      </c>
+      <c r="P27" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>92</v>
+      </c>
+      <c r="S27" t="s">
+        <v>92</v>
+      </c>
+      <c r="T27" t="s">
+        <v>96</v>
+      </c>
+      <c r="U27" t="s">
+        <v>112</v>
+      </c>
+      <c r="W27" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>115</v>
+      </c>
+      <c r="AB27" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE27" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B28" t="s">
+        <v>95</v>
+      </c>
+      <c r="C28" t="s">
+        <v>113</v>
+      </c>
+      <c r="D28" t="s">
         <v>91</v>
       </c>
-      <c r="C28" t="s">
-        <v>104</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
+        <v>114</v>
+      </c>
+      <c r="F28" t="s">
+        <v>82</v>
+      </c>
+      <c r="G28" t="s">
+        <v>83</v>
+      </c>
+      <c r="H28" t="s">
+        <v>102</v>
+      </c>
+      <c r="I28" t="s">
+        <v>106</v>
+      </c>
+      <c r="J28" t="s">
+        <v>96</v>
+      </c>
+      <c r="K28" t="s">
         <v>88</v>
       </c>
-      <c r="E28" t="s">
-        <v>105</v>
-      </c>
-      <c r="F28" t="s">
-        <v>81</v>
-      </c>
-      <c r="H28" t="s">
-        <v>96</v>
+      <c r="L28" t="s">
+        <v>112</v>
+      </c>
+      <c r="M28" t="s">
+        <v>92</v>
+      </c>
+      <c r="N28" t="s">
+        <v>112</v>
+      </c>
+      <c r="P28" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>112</v>
+      </c>
+      <c r="S28" t="s">
+        <v>115</v>
+      </c>
+      <c r="T28" t="s">
+        <v>92</v>
+      </c>
+      <c r="U28" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>116</v>
+      </c>
+      <c r="AE28" t="s">
+        <v>62</v>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>104</v>
+        <v>61</v>
       </c>
       <c r="B29" t="s">
         <v>67</v>
       </c>
       <c r="C29" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="D29" t="s">
-        <v>98</v>
+        <v>104</v>
+      </c>
+      <c r="E29" t="s">
+        <v>83</v>
+      </c>
+      <c r="F29" t="s">
+        <v>110</v>
+      </c>
+      <c r="G29" t="s">
+        <v>96</v>
+      </c>
+      <c r="H29" t="s">
+        <v>110</v>
+      </c>
+      <c r="I29" t="s">
+        <v>92</v>
+      </c>
+      <c r="J29" t="s">
+        <v>112</v>
+      </c>
+      <c r="L29" t="s">
+        <v>61</v>
+      </c>
+      <c r="M29" t="s">
+        <v>97</v>
+      </c>
+      <c r="P29" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>88</v>
+      </c>
+      <c r="S29" t="s">
+        <v>116</v>
+      </c>
+      <c r="T29" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="B30" t="s">
+        <v>103</v>
+      </c>
+      <c r="C30" t="s">
+        <v>75</v>
+      </c>
+      <c r="D30" t="s">
+        <v>100</v>
+      </c>
+      <c r="E30" t="s">
+        <v>106</v>
+      </c>
+      <c r="F30" t="s">
+        <v>106</v>
+      </c>
+      <c r="G30" t="s">
+        <v>92</v>
+      </c>
+      <c r="H30" t="s">
+        <v>83</v>
+      </c>
+      <c r="I30" t="s">
+        <v>112</v>
+      </c>
+      <c r="L30" t="s">
+        <v>62</v>
+      </c>
+      <c r="M30" t="s">
+        <v>112</v>
+      </c>
+      <c r="P30" t="s">
+        <v>116</v>
+      </c>
+      <c r="T30" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>75</v>
+      </c>
+      <c r="B31" t="s">
+        <v>113</v>
+      </c>
+      <c r="C31" t="s">
+        <v>81</v>
+      </c>
+      <c r="D31" t="s">
+        <v>95</v>
+      </c>
+      <c r="E31" t="s">
+        <v>96</v>
+      </c>
+      <c r="F31" t="s">
+        <v>96</v>
+      </c>
+      <c r="G31" t="s">
         <v>97</v>
       </c>
-      <c r="C30" t="s">
-        <v>74</v>
-      </c>
-      <c r="D30" t="s">
-        <v>94</v>
+      <c r="H31" t="s">
+        <v>106</v>
+      </c>
+      <c r="L31" t="s">
+        <v>88</v>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>74</v>
-      </c>
-      <c r="B31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C31" t="s">
-        <v>80</v>
-      </c>
-      <c r="D31" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B32" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C32" t="s">
         <v>62</v>
       </c>
+      <c r="D32" t="s">
+        <v>110</v>
+      </c>
+      <c r="E32" t="s">
+        <v>92</v>
+      </c>
+      <c r="F32" t="s">
+        <v>92</v>
+      </c>
+      <c r="G32" t="s">
+        <v>69</v>
+      </c>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>62</v>
       </c>
       <c r="B33" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C33" t="s">
         <v>60</v>
       </c>
+      <c r="D33" t="s">
+        <v>83</v>
+      </c>
+      <c r="E33" t="s">
+        <v>112</v>
+      </c>
+      <c r="F33" t="s">
+        <v>112</v>
+      </c>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>60</v>
       </c>
@@ -4298,61 +4952,165 @@
         <v>62</v>
       </c>
       <c r="C34" t="s">
-        <v>88</v>
+        <v>91</v>
+      </c>
+      <c r="D34" t="s">
+        <v>106</v>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B35" t="s">
         <v>60</v>
       </c>
       <c r="C35" t="s">
-        <v>98</v>
+        <v>104</v>
+      </c>
+      <c r="D35" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B36" t="s">
+        <v>91</v>
+      </c>
+      <c r="C36" t="s">
+        <v>100</v>
+      </c>
+      <c r="D36" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>100</v>
+      </c>
+      <c r="B37" t="s">
+        <v>104</v>
+      </c>
+      <c r="C37" t="s">
+        <v>110</v>
+      </c>
+      <c r="D37" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>114</v>
+      </c>
+      <c r="B38" t="s">
+        <v>100</v>
+      </c>
+      <c r="C38" t="s">
+        <v>83</v>
+      </c>
+      <c r="D38" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>102</v>
+      </c>
+      <c r="B39" t="s">
+        <v>110</v>
+      </c>
+      <c r="C39" t="s">
+        <v>106</v>
+      </c>
+      <c r="D39" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>61</v>
+      </c>
+      <c r="B40" t="s">
+        <v>83</v>
+      </c>
+      <c r="C40" t="s">
+        <v>96</v>
+      </c>
+      <c r="D40" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>113</v>
+      </c>
+      <c r="B41" t="s">
+        <v>106</v>
+      </c>
+      <c r="C41" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>110</v>
+      </c>
+      <c r="B42" t="s">
+        <v>96</v>
+      </c>
+      <c r="C42" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>83</v>
+      </c>
+      <c r="B43" t="s">
+        <v>92</v>
+      </c>
+      <c r="C43" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>106</v>
+      </c>
+      <c r="B44" t="s">
+        <v>112</v>
+      </c>
+      <c r="C44" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>96</v>
+      </c>
+      <c r="B45" t="s">
+        <v>69</v>
+      </c>
+      <c r="C45" t="s">
         <v>88</v>
       </c>
-      <c r="C36" t="s">
-        <v>94</v>
-      </c>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>94</v>
-      </c>
-      <c r="B37" t="s">
-        <v>98</v>
+    <row r="46" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>92</v>
+      </c>
+      <c r="B46" t="s">
+        <v>88</v>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>105</v>
-      </c>
-      <c r="B38" t="s">
-        <v>94</v>
+    <row r="47" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>112</v>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25"/>
-    <row r="41" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25"/>
     <row r="49" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="50" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="51" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4447,7 +5205,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:BB42"/>
+  <dimension ref="A3:BM42"/>
   <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="17.85546875" customWidth="1"/>
@@ -4480,7 +5238,7 @@
     <col min="98" max="98" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>51</v>
       </c>
@@ -4506,13 +5264,13 @@
         <v>56</v>
       </c>
       <c r="I3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J3" t="s">
         <v>66</v>
       </c>
       <c r="K3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L3" t="s">
         <v>59</v>
@@ -4521,109 +5279,109 @@
         <v>58</v>
       </c>
       <c r="N3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="Q3" t="s">
         <v>65</v>
       </c>
       <c r="R3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="T3" t="s">
         <v>64</v>
       </c>
       <c r="U3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="V3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="W3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="X3" t="s">
         <v>68</v>
       </c>
       <c r="Y3" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>101</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>82</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>98</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>107</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AJ3" t="s">
         <v>87</v>
       </c>
-      <c r="Z3" t="s">
-        <v>86</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>77</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AC3" t="s">
+      <c r="AK3" t="s">
+        <v>105</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>108</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>102</v>
+      </c>
+      <c r="AO3" t="s">
         <v>95</v>
       </c>
-      <c r="AD3" t="s">
-        <v>84</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>81</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>92</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>100</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>85</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>99</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>93</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>101</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>96</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>91</v>
-      </c>
       <c r="AP3" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="AQ3" t="s">
         <v>67</v>
       </c>
       <c r="AR3" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="AS3" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="AT3" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="AU3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AV3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AW3" t="s">
         <v>62</v>
@@ -4632,19 +5390,52 @@
         <v>60</v>
       </c>
       <c r="AY3" t="s">
+        <v>91</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>104</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>100</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>110</v>
+      </c>
+      <c r="BD3" t="s">
+        <v>83</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>106</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>96</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>92</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>97</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>69</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>115</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>116</v>
+      </c>
+      <c r="BM3" t="s">
         <v>88</v>
       </c>
-      <c r="AZ3" t="s">
-        <v>98</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>94</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>105</v>
-      </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -4667,7 +5458,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="I4" t="s">
         <v>1</v>
@@ -4685,7 +5476,7 @@
         <v>11</v>
       </c>
       <c r="N4" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="O4" t="s">
         <v>13</v>
@@ -4706,7 +5497,7 @@
         <v>2</v>
       </c>
       <c r="U4" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="V4" t="s">
         <v>11</v>
@@ -4807,8 +5598,41 @@
       <c r="BB4" t="s">
         <v>0</v>
       </c>
+      <c r="BC4" t="s">
+        <v>3</v>
+      </c>
+      <c r="BD4" t="s">
+        <v>6</v>
+      </c>
+      <c r="BE4" t="s">
+        <v>33</v>
+      </c>
+      <c r="BF4" t="s">
+        <v>9</v>
+      </c>
+      <c r="BG4" t="s">
+        <v>0</v>
+      </c>
+      <c r="BH4" t="s">
+        <v>6</v>
+      </c>
+      <c r="BI4" t="s">
+        <v>13</v>
+      </c>
+      <c r="BJ4" t="s">
+        <v>48</v>
+      </c>
+      <c r="BK4" t="s">
+        <v>18</v>
+      </c>
+      <c r="BL4" t="s">
+        <v>18</v>
+      </c>
+      <c r="BM4" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -4971,8 +5795,41 @@
       <c r="BB5" t="s">
         <v>11</v>
       </c>
+      <c r="BC5" t="s">
+        <v>7</v>
+      </c>
+      <c r="BD5" t="s">
+        <v>7</v>
+      </c>
+      <c r="BE5" t="s">
+        <v>2</v>
+      </c>
+      <c r="BF5" t="s">
+        <v>3</v>
+      </c>
+      <c r="BG5" t="s">
+        <v>3</v>
+      </c>
+      <c r="BH5" t="s">
+        <v>11</v>
+      </c>
+      <c r="BI5" t="s">
+        <v>1</v>
+      </c>
+      <c r="BJ5" t="s">
+        <v>35</v>
+      </c>
+      <c r="BK5" t="s">
+        <v>2</v>
+      </c>
+      <c r="BL5" t="s">
+        <v>3</v>
+      </c>
+      <c r="BM5" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -5135,8 +5992,41 @@
       <c r="BB6" t="s">
         <v>8</v>
       </c>
+      <c r="BC6" t="s">
+        <v>10</v>
+      </c>
+      <c r="BD6" t="s">
+        <v>30</v>
+      </c>
+      <c r="BE6" t="s">
+        <v>26</v>
+      </c>
+      <c r="BF6" t="s">
+        <v>16</v>
+      </c>
+      <c r="BG6" t="s">
+        <v>30</v>
+      </c>
+      <c r="BH6" t="s">
+        <v>12</v>
+      </c>
+      <c r="BI6" t="s">
+        <v>10</v>
+      </c>
+      <c r="BJ6" t="s">
+        <v>27</v>
+      </c>
+      <c r="BK6" t="s">
+        <v>26</v>
+      </c>
+      <c r="BL6" t="s">
+        <v>26</v>
+      </c>
+      <c r="BM6" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -5299,8 +6189,41 @@
       <c r="BB7" t="s">
         <v>4</v>
       </c>
+      <c r="BC7" t="s">
+        <v>21</v>
+      </c>
+      <c r="BD7" t="s">
+        <v>31</v>
+      </c>
+      <c r="BE7" t="s">
+        <v>15</v>
+      </c>
+      <c r="BF7" t="s">
+        <v>29</v>
+      </c>
+      <c r="BG7" t="s">
+        <v>4</v>
+      </c>
+      <c r="BH7" t="s">
+        <v>25</v>
+      </c>
+      <c r="BI7" t="s">
+        <v>16</v>
+      </c>
+      <c r="BJ7" t="s">
+        <v>31</v>
+      </c>
+      <c r="BK7" t="s">
+        <v>15</v>
+      </c>
+      <c r="BL7" t="s">
+        <v>15</v>
+      </c>
+      <c r="BM7" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -5430,8 +6353,35 @@
       <c r="BA8" t="s">
         <v>5</v>
       </c>
+      <c r="BC8" t="s">
+        <v>6</v>
+      </c>
+      <c r="BD8" t="s">
+        <v>43</v>
+      </c>
+      <c r="BE8" t="s">
+        <v>13</v>
+      </c>
+      <c r="BF8" t="s">
+        <v>34</v>
+      </c>
+      <c r="BG8" t="s">
+        <v>28</v>
+      </c>
+      <c r="BH8" t="s">
+        <v>2</v>
+      </c>
+      <c r="BI8" t="s">
+        <v>36</v>
+      </c>
+      <c r="BJ8" t="s">
+        <v>1</v>
+      </c>
+      <c r="BM8" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -5561,8 +6511,35 @@
       <c r="BA9" t="s">
         <v>35</v>
       </c>
+      <c r="BC9" t="s">
+        <v>9</v>
+      </c>
+      <c r="BD9" t="s">
+        <v>24</v>
+      </c>
+      <c r="BE9" t="s">
+        <v>1</v>
+      </c>
+      <c r="BF9" t="s">
+        <v>6</v>
+      </c>
+      <c r="BG9" t="s">
+        <v>34</v>
+      </c>
+      <c r="BH9" t="s">
+        <v>3</v>
+      </c>
+      <c r="BI9" t="s">
+        <v>9</v>
+      </c>
+      <c r="BJ9" t="s">
+        <v>3</v>
+      </c>
+      <c r="BM9" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>44</v>
       </c>
@@ -5692,8 +6669,35 @@
       <c r="BA10" t="s">
         <v>14</v>
       </c>
+      <c r="BC10" t="s">
+        <v>22</v>
+      </c>
+      <c r="BD10" t="s">
+        <v>44</v>
+      </c>
+      <c r="BE10" t="s">
+        <v>14</v>
+      </c>
+      <c r="BF10" t="s">
+        <v>20</v>
+      </c>
+      <c r="BG10" t="s">
+        <v>44</v>
+      </c>
+      <c r="BH10" t="s">
+        <v>44</v>
+      </c>
+      <c r="BI10" t="s">
+        <v>32</v>
+      </c>
+      <c r="BJ10" t="s">
+        <v>32</v>
+      </c>
+      <c r="BM10" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -5823,8 +6827,35 @@
       <c r="BA11" t="s">
         <v>27</v>
       </c>
+      <c r="BC11" t="s">
+        <v>37</v>
+      </c>
+      <c r="BD11" t="s">
+        <v>17</v>
+      </c>
+      <c r="BE11" t="s">
+        <v>4</v>
+      </c>
+      <c r="BF11" t="s">
+        <v>41</v>
+      </c>
+      <c r="BG11" t="s">
+        <v>17</v>
+      </c>
+      <c r="BH11" t="s">
+        <v>19</v>
+      </c>
+      <c r="BI11" t="s">
+        <v>29</v>
+      </c>
+      <c r="BJ11" t="s">
+        <v>29</v>
+      </c>
+      <c r="BM11" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>0</v>
       </c>
@@ -5859,7 +6890,7 @@
         <v>23</v>
       </c>
       <c r="T12" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="V12" t="s">
         <v>0</v>
@@ -5925,7 +6956,7 @@
         <v>28</v>
       </c>
       <c r="AW12" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="AX12" t="s">
         <v>5</v>
@@ -5939,8 +6970,29 @@
       <c r="BA12" t="s">
         <v>36</v>
       </c>
+      <c r="BC12" t="s">
+        <v>1</v>
+      </c>
+      <c r="BD12" t="s">
+        <v>40</v>
+      </c>
+      <c r="BE12" t="s">
+        <v>24</v>
+      </c>
+      <c r="BF12" t="s">
+        <v>13</v>
+      </c>
+      <c r="BG12" t="s">
+        <v>5</v>
+      </c>
+      <c r="BI12" t="s">
+        <v>5</v>
+      </c>
+      <c r="BJ12" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -6041,7 +7093,7 @@
         <v>43</v>
       </c>
       <c r="AW13" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="AX13" t="s">
         <v>35</v>
@@ -6055,8 +7107,29 @@
       <c r="BA13" t="s">
         <v>0</v>
       </c>
+      <c r="BC13" t="s">
+        <v>35</v>
+      </c>
+      <c r="BD13" t="s">
+        <v>2</v>
+      </c>
+      <c r="BE13" t="s">
+        <v>7</v>
+      </c>
+      <c r="BF13" t="s">
+        <v>40</v>
+      </c>
+      <c r="BG13" t="s">
+        <v>2</v>
+      </c>
+      <c r="BI13" t="s">
+        <v>0</v>
+      </c>
+      <c r="BJ13" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>8</v>
       </c>
@@ -6157,7 +7230,7 @@
         <v>20</v>
       </c>
       <c r="AW14" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="AX14" t="s">
         <v>27</v>
@@ -6171,8 +7244,29 @@
       <c r="BA14" t="s">
         <v>10</v>
       </c>
+      <c r="BC14" t="s">
+        <v>14</v>
+      </c>
+      <c r="BD14" t="s">
+        <v>39</v>
+      </c>
+      <c r="BE14" t="s">
+        <v>30</v>
+      </c>
+      <c r="BF14" t="s">
+        <v>22</v>
+      </c>
+      <c r="BG14" t="s">
+        <v>12</v>
+      </c>
+      <c r="BI14" t="s">
+        <v>8</v>
+      </c>
+      <c r="BJ14" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>46</v>
       </c>
@@ -6273,7 +7367,7 @@
         <v>37</v>
       </c>
       <c r="AW15" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="AX15" t="s">
         <v>31</v>
@@ -6287,8 +7381,29 @@
       <c r="BA15" t="s">
         <v>31</v>
       </c>
+      <c r="BC15" t="s">
+        <v>16</v>
+      </c>
+      <c r="BD15" t="s">
+        <v>29</v>
+      </c>
+      <c r="BE15" t="s">
+        <v>16</v>
+      </c>
+      <c r="BF15" t="s">
+        <v>38</v>
+      </c>
+      <c r="BG15" t="s">
+        <v>20</v>
+      </c>
+      <c r="BI15" t="s">
+        <v>4</v>
+      </c>
+      <c r="BJ15" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -6320,7 +7435,7 @@
         <v>34</v>
       </c>
       <c r="R16" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="T16" t="s">
         <v>18</v>
@@ -6377,7 +7492,7 @@
         <v>0</v>
       </c>
       <c r="AW16" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="AX16" t="s">
         <v>6</v>
@@ -6389,10 +7504,28 @@
         <v>18</v>
       </c>
       <c r="BA16" t="s">
-        <v>34</v>
+        <v>6</v>
+      </c>
+      <c r="BC16" t="s">
+        <v>28</v>
+      </c>
+      <c r="BD16" t="s">
+        <v>18</v>
+      </c>
+      <c r="BE16" t="s">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="s">
+        <v>33</v>
+      </c>
+      <c r="BG16" t="s">
+        <v>23</v>
+      </c>
+      <c r="BI16" t="s">
+        <v>2</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>1</v>
       </c>
@@ -6481,7 +7614,7 @@
         <v>42</v>
       </c>
       <c r="AW17" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AX17" t="s">
         <v>24</v>
@@ -6493,10 +7626,28 @@
         <v>3</v>
       </c>
       <c r="BA17" t="s">
-        <v>6</v>
+        <v>34</v>
+      </c>
+      <c r="BC17" t="s">
+        <v>11</v>
+      </c>
+      <c r="BD17" t="s">
+        <v>3</v>
+      </c>
+      <c r="BE17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BF17" t="s">
+        <v>1</v>
+      </c>
+      <c r="BG17" t="s">
+        <v>1</v>
+      </c>
+      <c r="BI17" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>32</v>
       </c>
@@ -6585,7 +7736,7 @@
         <v>10</v>
       </c>
       <c r="AW18" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AX18" t="s">
         <v>44</v>
@@ -6599,8 +7750,26 @@
       <c r="BA18" t="s">
         <v>17</v>
       </c>
+      <c r="BC18" t="s">
+        <v>25</v>
+      </c>
+      <c r="BD18" t="s">
+        <v>26</v>
+      </c>
+      <c r="BE18" t="s">
+        <v>22</v>
+      </c>
+      <c r="BF18" t="s">
+        <v>32</v>
+      </c>
+      <c r="BG18" t="s">
+        <v>8</v>
+      </c>
+      <c r="BI18" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>37</v>
       </c>
@@ -6689,7 +7858,7 @@
         <v>30</v>
       </c>
       <c r="AW19" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AX19" t="s">
         <v>20</v>
@@ -6703,8 +7872,26 @@
       <c r="BA19" t="s">
         <v>20</v>
       </c>
+      <c r="BC19" t="s">
+        <v>20</v>
+      </c>
+      <c r="BD19" t="s">
+        <v>15</v>
+      </c>
+      <c r="BE19" t="s">
+        <v>39</v>
+      </c>
+      <c r="BF19" t="s">
+        <v>30</v>
+      </c>
+      <c r="BG19" t="s">
+        <v>16</v>
+      </c>
+      <c r="BI19" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -6772,7 +7959,7 @@
         <v>6</v>
       </c>
       <c r="AW20" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="s">
         <v>11</v>
@@ -6786,10 +7973,28 @@
       <c r="BA20" t="s">
         <v>33</v>
       </c>
+      <c r="BC20" t="s">
+        <v>33</v>
+      </c>
+      <c r="BD20" t="s">
+        <v>13</v>
+      </c>
+      <c r="BE20" t="s">
+        <v>36</v>
+      </c>
+      <c r="BF20" t="s">
+        <v>5</v>
+      </c>
+      <c r="BG20" t="s">
+        <v>18</v>
+      </c>
+      <c r="BI20" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="C21" t="s">
         <v>7</v>
@@ -6855,7 +8060,7 @@
         <v>11</v>
       </c>
       <c r="AW21" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AX21" t="s">
         <v>3</v>
@@ -6869,8 +8074,26 @@
       <c r="BA21" t="s">
         <v>2</v>
       </c>
+      <c r="BC21" t="s">
+        <v>0</v>
+      </c>
+      <c r="BD21" t="s">
+        <v>1</v>
+      </c>
+      <c r="BE21" t="s">
+        <v>3</v>
+      </c>
+      <c r="BF21" t="s">
+        <v>2</v>
+      </c>
+      <c r="BG21" t="s">
+        <v>33</v>
+      </c>
+      <c r="BI21" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>17</v>
       </c>
@@ -6938,7 +8161,7 @@
         <v>12</v>
       </c>
       <c r="AW22" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="AX22" t="s">
         <v>21</v>
@@ -6952,8 +8175,26 @@
       <c r="BA22" t="s">
         <v>30</v>
       </c>
+      <c r="BC22" t="s">
+        <v>17</v>
+      </c>
+      <c r="BD22" t="s">
+        <v>45</v>
+      </c>
+      <c r="BE22" t="s">
+        <v>8</v>
+      </c>
+      <c r="BF22" t="s">
+        <v>27</v>
+      </c>
+      <c r="BG22" t="s">
+        <v>14</v>
+      </c>
+      <c r="BI22" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -7021,7 +8262,7 @@
         <v>39</v>
       </c>
       <c r="AW23" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AX23" t="s">
         <v>29</v>
@@ -7035,8 +8276,26 @@
       <c r="BA23" t="s">
         <v>39</v>
       </c>
+      <c r="BC23" t="s">
+        <v>12</v>
+      </c>
+      <c r="BD23" t="s">
+        <v>4</v>
+      </c>
+      <c r="BE23" t="s">
+        <v>21</v>
+      </c>
+      <c r="BF23" t="s">
+        <v>31</v>
+      </c>
+      <c r="BG23" t="s">
+        <v>32</v>
+      </c>
+      <c r="BI23" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>2</v>
       </c>
@@ -7077,7 +8336,7 @@
         <v>5</v>
       </c>
       <c r="AW24" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AX24" t="s">
         <v>2</v>
@@ -7091,8 +8350,23 @@
       <c r="BA24" t="s">
         <v>23</v>
       </c>
+      <c r="BC24" t="s">
+        <v>5</v>
+      </c>
+      <c r="BD24" t="s">
+        <v>34</v>
+      </c>
+      <c r="BE24" t="s">
+        <v>5</v>
+      </c>
+      <c r="BF24" t="s">
+        <v>0</v>
+      </c>
+      <c r="BG24" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -7133,7 +8407,7 @@
         <v>2</v>
       </c>
       <c r="AW25" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="AX25" t="s">
         <v>7</v>
@@ -7147,8 +8421,23 @@
       <c r="BA25" t="s">
         <v>3</v>
       </c>
+      <c r="BC25" t="s">
+        <v>2</v>
+      </c>
+      <c r="BD25" t="s">
+        <v>0</v>
+      </c>
+      <c r="BE25" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF25" t="s">
+        <v>24</v>
+      </c>
+      <c r="BG25" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>21</v>
       </c>
@@ -7189,7 +8478,7 @@
         <v>19</v>
       </c>
       <c r="AW26" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AX26" t="s">
         <v>19</v>
@@ -7203,8 +8492,23 @@
       <c r="BA26" t="s">
         <v>25</v>
       </c>
+      <c r="BC26" t="s">
+        <v>8</v>
+      </c>
+      <c r="BD26" t="s">
+        <v>19</v>
+      </c>
+      <c r="BE26" t="s">
+        <v>12</v>
+      </c>
+      <c r="BF26" t="s">
+        <v>19</v>
+      </c>
+      <c r="BG26" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -7245,7 +8549,7 @@
         <v>25</v>
       </c>
       <c r="AW27" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="AX27" t="s">
         <v>12</v>
@@ -7259,8 +8563,23 @@
       <c r="BA27" t="s">
         <v>4</v>
       </c>
+      <c r="BC27" t="s">
+        <v>19</v>
+      </c>
+      <c r="BD27" t="s">
+        <v>12</v>
+      </c>
+      <c r="BE27" t="s">
+        <v>25</v>
+      </c>
+      <c r="BF27" t="s">
+        <v>4</v>
+      </c>
+      <c r="BG27" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="48:53" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="15" customHeight="1" spans="48:59" x14ac:dyDescent="0.25"/>
     <row r="29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -7282,7 +8601,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:BB1898"/>
+  <dimension ref="A3:BM1898"/>
   <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="55.28515625" customWidth="1"/>
@@ -7366,7 +8685,7 @@
     <col min="99" max="99" width="47.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>51</v>
       </c>
@@ -7392,13 +8711,13 @@
         <v>56</v>
       </c>
       <c r="I3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J3" t="s">
         <v>66</v>
       </c>
       <c r="K3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L3" t="s">
         <v>59</v>
@@ -7407,109 +8726,109 @@
         <v>58</v>
       </c>
       <c r="N3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="Q3" t="s">
         <v>65</v>
       </c>
       <c r="R3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="T3" t="s">
         <v>64</v>
       </c>
       <c r="U3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="V3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="W3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="X3" t="s">
         <v>68</v>
       </c>
       <c r="Y3" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>101</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>82</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>98</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>107</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AJ3" t="s">
         <v>87</v>
       </c>
-      <c r="Z3" t="s">
-        <v>86</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>77</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AC3" t="s">
+      <c r="AK3" t="s">
+        <v>105</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>108</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>102</v>
+      </c>
+      <c r="AO3" t="s">
         <v>95</v>
       </c>
-      <c r="AD3" t="s">
-        <v>84</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>81</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>92</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>100</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>85</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>99</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>93</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>101</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>96</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>91</v>
-      </c>
       <c r="AP3" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="AQ3" t="s">
         <v>67</v>
       </c>
       <c r="AR3" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="AS3" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="AT3" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="AU3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AV3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AW3" t="s">
         <v>62</v>
@@ -7518,684 +8837,855 @@
         <v>60</v>
       </c>
       <c r="AY3" t="s">
+        <v>91</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>104</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>100</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>110</v>
+      </c>
+      <c r="BD3" t="s">
+        <v>83</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>106</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>96</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>92</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>97</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>69</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>115</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>116</v>
+      </c>
+      <c r="BM3" t="s">
         <v>88</v>
       </c>
-      <c r="AZ3" t="s">
-        <v>98</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>94</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>105</v>
-      </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="B4" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="C4" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="D4" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="E4" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="F4" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="G4" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="H4" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="I4" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="J4" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="K4" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="L4" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="M4" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="N4" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="O4" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="P4" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="Q4" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="R4" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="S4" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="T4" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="U4" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="V4" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="W4" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="X4" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="Y4" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="Z4" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="AA4" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="AB4" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="AC4" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="AD4" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="AE4" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="AF4" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="AG4" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="AH4" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="AI4" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AJ4" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="AK4" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="AL4" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="AM4" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="AN4" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="AO4" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="AP4" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="AQ4" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="AR4" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="AS4" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="AT4" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="AU4" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="AV4" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="AW4" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="AX4" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="AY4" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="AZ4" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="BA4" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="BB4" t="s">
-        <v>160</v>
+        <v>171</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>172</v>
+      </c>
+      <c r="BD4" t="s">
+        <v>173</v>
+      </c>
+      <c r="BE4" t="s">
+        <v>174</v>
+      </c>
+      <c r="BF4" t="s">
+        <v>175</v>
+      </c>
+      <c r="BG4" t="s">
+        <v>176</v>
+      </c>
+      <c r="BH4" t="s">
+        <v>177</v>
+      </c>
+      <c r="BI4" t="s">
+        <v>178</v>
+      </c>
+      <c r="BJ4" t="s">
+        <v>179</v>
+      </c>
+      <c r="BK4" t="s">
+        <v>180</v>
+      </c>
+      <c r="BL4" t="s">
+        <v>181</v>
+      </c>
+      <c r="BM4" t="s">
+        <v>182</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="C5" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="E5" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="F5" t="s">
-        <v>164</v>
+        <v>186</v>
       </c>
       <c r="G5" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="H5" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="J5" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="K5" t="s">
-        <v>168</v>
+        <v>190</v>
       </c>
       <c r="L5" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="M5" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="O5" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="Q5" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="R5" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="T5" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
       <c r="V5" t="s">
-        <v>175</v>
+        <v>197</v>
       </c>
       <c r="W5" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="X5" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="Y5" t="s">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="Z5" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="AA5" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="AB5" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="AC5" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="AD5" t="s">
-        <v>183</v>
+        <v>205</v>
       </c>
       <c r="AE5" t="s">
-        <v>184</v>
+        <v>206</v>
       </c>
       <c r="AF5" t="s">
-        <v>185</v>
+        <v>207</v>
       </c>
       <c r="AH5" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="AI5" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="AJ5" t="s">
-        <v>188</v>
+        <v>210</v>
       </c>
       <c r="AK5" t="s">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="AL5" t="s">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="AN5" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="AO5" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="AQ5" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="AR5" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="AS5" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="AT5" t="s">
-        <v>195</v>
+        <v>216</v>
       </c>
       <c r="AU5" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="AV5" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="AW5" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="AX5" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="AY5" t="s">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="AZ5" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="BA5" t="s">
-        <v>202</v>
+        <v>223</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>224</v>
+      </c>
+      <c r="BD5" t="s">
+        <v>225</v>
+      </c>
+      <c r="BE5" t="s">
+        <v>226</v>
+      </c>
+      <c r="BF5" t="s">
+        <v>227</v>
+      </c>
+      <c r="BG5" t="s">
+        <v>228</v>
+      </c>
+      <c r="BH5" t="s">
+        <v>229</v>
+      </c>
+      <c r="BI5" t="s">
+        <v>230</v>
+      </c>
+      <c r="BJ5" t="s">
+        <v>231</v>
+      </c>
+      <c r="BM5" t="s">
+        <v>232</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>203</v>
+        <v>233</v>
       </c>
       <c r="C6" t="s">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="E6" t="s">
-        <v>205</v>
+        <v>235</v>
       </c>
       <c r="F6" t="s">
-        <v>206</v>
+        <v>236</v>
       </c>
       <c r="H6" t="s">
-        <v>207</v>
+        <v>237</v>
       </c>
       <c r="J6" t="s">
-        <v>208</v>
+        <v>238</v>
       </c>
       <c r="K6" t="s">
-        <v>209</v>
+        <v>239</v>
       </c>
       <c r="M6" t="s">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="O6" t="s">
-        <v>211</v>
+        <v>241</v>
       </c>
       <c r="Q6" t="s">
-        <v>212</v>
+        <v>242</v>
       </c>
       <c r="R6" t="s">
+        <v>243</v>
+      </c>
+      <c r="T6" t="s">
+        <v>244</v>
+      </c>
+      <c r="V6" t="s">
+        <v>245</v>
+      </c>
+      <c r="W6" t="s">
+        <v>246</v>
+      </c>
+      <c r="X6" t="s">
+        <v>247</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>248</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>249</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>250</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>251</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>252</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>253</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>254</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>255</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>256</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>257</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>258</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>259</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>260</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>261</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>262</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>263</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>264</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>265</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>266</v>
+      </c>
+      <c r="AW6" t="s">
         <v>213</v>
       </c>
-      <c r="T6" t="s">
-        <v>214</v>
-      </c>
-      <c r="V6" t="s">
-        <v>215</v>
-      </c>
-      <c r="W6" t="s">
-        <v>216</v>
-      </c>
-      <c r="X6" t="s">
-        <v>217</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>218</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>219</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>220</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>221</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>222</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>223</v>
-      </c>
-      <c r="AH6" t="s">
-        <v>224</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>225</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>226</v>
-      </c>
-      <c r="AK6" t="s">
-        <v>227</v>
-      </c>
-      <c r="AL6" t="s">
-        <v>228</v>
-      </c>
-      <c r="AN6" t="s">
-        <v>229</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>230</v>
-      </c>
-      <c r="AQ6" t="s">
-        <v>231</v>
-      </c>
-      <c r="AR6" t="s">
-        <v>232</v>
-      </c>
-      <c r="AT6" t="s">
-        <v>233</v>
-      </c>
-      <c r="AU6" t="s">
-        <v>234</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>235</v>
-      </c>
-      <c r="AW6" t="s">
-        <v>236</v>
-      </c>
       <c r="AX6" t="s">
-        <v>237</v>
+        <v>267</v>
       </c>
       <c r="AY6" t="s">
-        <v>238</v>
+        <v>268</v>
       </c>
       <c r="AZ6" t="s">
-        <v>239</v>
+        <v>269</v>
       </c>
       <c r="BA6" t="s">
-        <v>240</v>
+        <v>270</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>271</v>
+      </c>
+      <c r="BD6" t="s">
+        <v>272</v>
+      </c>
+      <c r="BE6" t="s">
+        <v>273</v>
+      </c>
+      <c r="BF6" t="s">
+        <v>274</v>
+      </c>
+      <c r="BG6" t="s">
+        <v>275</v>
+      </c>
+      <c r="BI6" t="s">
+        <v>276</v>
+      </c>
+      <c r="BJ6" t="s">
+        <v>277</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>241</v>
+        <v>278</v>
       </c>
       <c r="C7" t="s">
-        <v>242</v>
+        <v>279</v>
       </c>
       <c r="E7" t="s">
-        <v>243</v>
+        <v>280</v>
       </c>
       <c r="F7" t="s">
-        <v>244</v>
+        <v>281</v>
       </c>
       <c r="H7" t="s">
-        <v>245</v>
+        <v>282</v>
       </c>
       <c r="J7" t="s">
-        <v>246</v>
+        <v>283</v>
       </c>
       <c r="K7" t="s">
-        <v>247</v>
+        <v>284</v>
       </c>
       <c r="M7" t="s">
-        <v>248</v>
+        <v>285</v>
       </c>
       <c r="O7" t="s">
-        <v>249</v>
+        <v>286</v>
       </c>
       <c r="Q7" t="s">
-        <v>250</v>
+        <v>287</v>
       </c>
       <c r="R7" t="s">
-        <v>251</v>
+        <v>288</v>
       </c>
       <c r="T7" t="s">
-        <v>252</v>
+        <v>289</v>
       </c>
       <c r="V7" t="s">
-        <v>253</v>
+        <v>290</v>
       </c>
       <c r="X7" t="s">
-        <v>254</v>
+        <v>291</v>
       </c>
       <c r="Z7" t="s">
-        <v>255</v>
+        <v>292</v>
       </c>
       <c r="AA7" t="s">
-        <v>256</v>
+        <v>293</v>
       </c>
       <c r="AB7" t="s">
-        <v>257</v>
+        <v>294</v>
       </c>
       <c r="AD7" t="s">
-        <v>258</v>
+        <v>295</v>
       </c>
       <c r="AE7" t="s">
-        <v>259</v>
+        <v>296</v>
       </c>
       <c r="AF7" t="s">
-        <v>260</v>
+        <v>297</v>
       </c>
       <c r="AH7" t="s">
-        <v>261</v>
+        <v>298</v>
       </c>
       <c r="AI7" t="s">
-        <v>262</v>
+        <v>299</v>
       </c>
       <c r="AJ7" t="s">
-        <v>263</v>
+        <v>300</v>
       </c>
       <c r="AN7" t="s">
-        <v>264</v>
+        <v>301</v>
       </c>
       <c r="AO7" t="s">
-        <v>265</v>
+        <v>302</v>
       </c>
       <c r="AQ7" t="s">
-        <v>266</v>
+        <v>303</v>
       </c>
       <c r="AR7" t="s">
-        <v>267</v>
+        <v>304</v>
       </c>
       <c r="AU7" t="s">
-        <v>268</v>
+        <v>305</v>
       </c>
       <c r="AV7" t="s">
-        <v>269</v>
+        <v>306</v>
       </c>
       <c r="AW7" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="AX7" t="s">
-        <v>271</v>
+        <v>308</v>
       </c>
       <c r="AY7" t="s">
-        <v>272</v>
+        <v>309</v>
       </c>
       <c r="AZ7" t="s">
-        <v>273</v>
+        <v>310</v>
       </c>
       <c r="BA7" t="s">
-        <v>274</v>
+        <v>311</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>312</v>
+      </c>
+      <c r="BD7" t="s">
+        <v>313</v>
+      </c>
+      <c r="BE7" t="s">
+        <v>314</v>
+      </c>
+      <c r="BF7" t="s">
+        <v>315</v>
+      </c>
+      <c r="BG7" t="s">
+        <v>316</v>
+      </c>
+      <c r="BI7" t="s">
+        <v>317</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>275</v>
+        <v>318</v>
       </c>
       <c r="C8" t="s">
-        <v>276</v>
+        <v>319</v>
       </c>
       <c r="E8" t="s">
-        <v>277</v>
+        <v>320</v>
       </c>
       <c r="F8" t="s">
-        <v>278</v>
+        <v>321</v>
       </c>
       <c r="H8" t="s">
-        <v>279</v>
+        <v>322</v>
       </c>
       <c r="K8" t="s">
-        <v>280</v>
+        <v>323</v>
       </c>
       <c r="O8" t="s">
-        <v>281</v>
+        <v>324</v>
       </c>
       <c r="Q8" t="s">
-        <v>282</v>
+        <v>325</v>
       </c>
       <c r="R8" t="s">
-        <v>283</v>
+        <v>326</v>
       </c>
       <c r="T8" t="s">
-        <v>284</v>
+        <v>327</v>
       </c>
       <c r="X8" t="s">
-        <v>285</v>
+        <v>328</v>
       </c>
       <c r="AA8" t="s">
-        <v>286</v>
+        <v>329</v>
       </c>
       <c r="AB8" t="s">
-        <v>287</v>
+        <v>330</v>
       </c>
       <c r="AE8" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="AF8" t="s">
-        <v>288</v>
+        <v>331</v>
       </c>
       <c r="AH8" t="s">
-        <v>289</v>
+        <v>332</v>
       </c>
       <c r="AI8" t="s">
-        <v>290</v>
+        <v>333</v>
       </c>
       <c r="AJ8" t="s">
-        <v>291</v>
+        <v>334</v>
       </c>
       <c r="AN8" t="s">
-        <v>292</v>
+        <v>335</v>
       </c>
       <c r="AO8" t="s">
-        <v>293</v>
+        <v>336</v>
       </c>
       <c r="AQ8" t="s">
-        <v>294</v>
+        <v>337</v>
       </c>
       <c r="AR8" t="s">
-        <v>295</v>
+        <v>338</v>
       </c>
       <c r="AU8" t="s">
-        <v>296</v>
+        <v>339</v>
       </c>
       <c r="AV8" t="s">
-        <v>297</v>
+        <v>340</v>
       </c>
       <c r="AW8" t="s">
-        <v>298</v>
+        <v>341</v>
       </c>
       <c r="AX8" t="s">
-        <v>299</v>
+        <v>342</v>
       </c>
       <c r="AY8" t="s">
-        <v>300</v>
+        <v>343</v>
       </c>
       <c r="AZ8" t="s">
-        <v>301</v>
+        <v>344</v>
       </c>
       <c r="BA8" t="s">
-        <v>302</v>
+        <v>345</v>
+      </c>
+      <c r="BC8" t="s">
+        <v>346</v>
+      </c>
+      <c r="BD8" t="s">
+        <v>347</v>
+      </c>
+      <c r="BE8" t="s">
+        <v>348</v>
+      </c>
+      <c r="BF8" t="s">
+        <v>349</v>
+      </c>
+      <c r="BG8" t="s">
+        <v>350</v>
+      </c>
+      <c r="BI8" t="s">
+        <v>351</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>303</v>
+        <v>352</v>
       </c>
       <c r="E9" t="s">
-        <v>304</v>
+        <v>353</v>
       </c>
       <c r="F9" t="s">
-        <v>305</v>
+        <v>354</v>
       </c>
       <c r="H9" t="s">
-        <v>306</v>
+        <v>355</v>
       </c>
       <c r="O9" t="s">
-        <v>307</v>
+        <v>356</v>
       </c>
       <c r="T9" t="s">
-        <v>308</v>
+        <v>357</v>
       </c>
       <c r="X9" t="s">
-        <v>309</v>
+        <v>358</v>
       </c>
       <c r="AB9" t="s">
-        <v>310</v>
+        <v>359</v>
       </c>
       <c r="AF9" t="s">
-        <v>311</v>
+        <v>360</v>
       </c>
       <c r="AI9" t="s">
-        <v>312</v>
+        <v>361</v>
       </c>
       <c r="AJ9" t="s">
-        <v>313</v>
+        <v>362</v>
       </c>
       <c r="AO9" t="s">
-        <v>314</v>
+        <v>363</v>
       </c>
       <c r="AV9" t="s">
-        <v>315</v>
+        <v>364</v>
       </c>
       <c r="AW9" t="s">
-        <v>316</v>
+        <v>365</v>
       </c>
       <c r="AX9" t="s">
-        <v>317</v>
+        <v>366</v>
       </c>
       <c r="AY9" t="s">
-        <v>318</v>
+        <v>367</v>
       </c>
       <c r="AZ9" t="s">
-        <v>319</v>
+        <v>368</v>
       </c>
       <c r="BA9" t="s">
-        <v>320</v>
+        <v>369</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>370</v>
+      </c>
+      <c r="BD9" t="s">
+        <v>371</v>
+      </c>
+      <c r="BE9" t="s">
+        <v>372</v>
+      </c>
+      <c r="BF9" t="s">
+        <v>373</v>
+      </c>
+      <c r="BG9" t="s">
+        <v>374</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="41:53" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="41:59" x14ac:dyDescent="0.25">
       <c r="AO10" t="s">
-        <v>321</v>
+        <v>375</v>
+      </c>
+      <c r="AW10" t="s">
+        <v>376</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" ht="15" customHeight="1" spans="49:49" x14ac:dyDescent="0.25"/>
     <row r="12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="13" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="14" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/data/ICEHLdelegacije.xlsx
+++ b/data/ICEHLdelegacije.xlsx
@@ -16,14 +16,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2528" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2506" uniqueCount="375">
+  <si>
+    <t>SmetanaLa</t>
+  </si>
   <si>
     <t>PiragicTr</t>
   </si>
   <si>
-    <t>SmetanaLa</t>
-  </si>
-  <si>
     <t>OfnerCh</t>
   </si>
   <si>
@@ -45,78 +45,78 @@
     <t>HribarMa</t>
   </si>
   <si>
+    <t>PardatscherUl</t>
+  </si>
+  <si>
+    <t>MantovaniDa</t>
+  </si>
+  <si>
     <t>SiegelSt</t>
   </si>
   <si>
+    <t>SeewaldEl</t>
+  </si>
+  <si>
+    <t>RieckenSi</t>
+  </si>
+  <si>
+    <t>FichtnerPa</t>
+  </si>
+  <si>
+    <t>KoncDa</t>
+  </si>
+  <si>
+    <t>SparerDa</t>
+  </si>
+  <si>
     <t>BedynekSe</t>
   </si>
   <si>
-    <t>SeewaldEl</t>
-  </si>
-  <si>
-    <t>PardatscherUl</t>
-  </si>
-  <si>
-    <t>FichtnerPa</t>
-  </si>
-  <si>
     <t>BärnthalerCh</t>
   </si>
   <si>
-    <t>KoncDa</t>
-  </si>
-  <si>
-    <t>RieckenSi</t>
+    <t>HronskyTo</t>
+  </si>
+  <si>
+    <t>Gatol-schafranekMa</t>
+  </si>
+  <si>
+    <t>SchauerJa</t>
   </si>
   <si>
     <t>MartinFl</t>
   </si>
   <si>
-    <t>HronskyTo</t>
-  </si>
-  <si>
-    <t>MantovaniDa</t>
-  </si>
-  <si>
-    <t>SparerDa</t>
-  </si>
-  <si>
     <t>PuffWo</t>
   </si>
   <si>
-    <t>Gatol-schafranekMa</t>
+    <t>RigoniDa</t>
+  </si>
+  <si>
+    <t>JedlickaPe</t>
+  </si>
+  <si>
+    <t>MuzsikNo</t>
+  </si>
+  <si>
+    <t>VacziDa</t>
   </si>
   <si>
     <t>RezekGr</t>
   </si>
   <si>
-    <t>SchauerJa</t>
-  </si>
-  <si>
-    <t>RigoniDa</t>
-  </si>
-  <si>
-    <t>JedlickaPe</t>
-  </si>
-  <si>
-    <t>MuzsikNo</t>
+    <t>WimmlerAl</t>
+  </si>
+  <si>
+    <t>NotheggerDa</t>
+  </si>
+  <si>
+    <t>DurmisOt</t>
   </si>
   <si>
     <t>BernekerTh</t>
   </si>
   <si>
-    <t>WimmlerAl</t>
-  </si>
-  <si>
-    <t>NotheggerDa</t>
-  </si>
-  <si>
-    <t>VacziDa</t>
-  </si>
-  <si>
-    <t>DurmisOt</t>
-  </si>
-  <si>
     <t>Huber aAn</t>
   </si>
   <si>
@@ -144,15 +144,15 @@
     <t>ZacherlPa</t>
   </si>
   <si>
+    <t>FleischmannLu</t>
+  </si>
+  <si>
+    <t>HolzerTo</t>
+  </si>
+  <si>
     <t>VoicanCh</t>
   </si>
   <si>
-    <t>HolzerTo</t>
-  </si>
-  <si>
-    <t>FleischmannLu</t>
-  </si>
-  <si>
     <t>JeramFi</t>
   </si>
   <si>
@@ -174,18 +174,18 @@
     <t>2024-09-20</t>
   </si>
   <si>
+    <t>2024-09-22</t>
+  </si>
+  <si>
     <t>2024-09-24</t>
   </si>
   <si>
-    <t>2024-09-22</t>
+    <t>2024-09-21</t>
   </si>
   <si>
     <t>2024-09-27</t>
   </si>
   <si>
-    <t>2024-09-21</t>
-  </si>
-  <si>
     <t>2024-10-04</t>
   </si>
   <si>
@@ -216,12 +216,12 @@
     <t>2024-10-20</t>
   </si>
   <si>
+    <t>2024-12-08</t>
+  </si>
+  <si>
     <t>2024-10-06</t>
   </si>
   <si>
-    <t>2024-12-08</t>
-  </si>
-  <si>
     <t>2024-11-01</t>
   </si>
   <si>
@@ -261,12 +261,12 @@
     <t>2024-11-24</t>
   </si>
   <si>
+    <t>2024-11-20</t>
+  </si>
+  <si>
     <t>2024-12-20</t>
   </si>
   <si>
-    <t>2024-11-20</t>
-  </si>
-  <si>
     <t>2025-01-05</t>
   </si>
   <si>
@@ -669,9 +669,6 @@
     <t>w KagranK;FichtnerPa;PiragicTr;MuzsikNo;PuffWo</t>
   </si>
   <si>
-    <t>Gabor Ocskay Eisarena;SiegelSt;SmetanaLa;DurmisOt;KoncDa</t>
-  </si>
-  <si>
     <t>Gabor Ocskay Eisarena;HronskyTo;NagyAt;DurmisOt;VacziDa</t>
   </si>
   <si>
@@ -951,7 +948,7 @@
     <t>Eisarena Salzburg;HronskyTo;SternatCh;JedlickaPe;SeewaldJe</t>
   </si>
   <si>
-    <t>Tiroler Wasserkraft Arena;NikolicMa;NikolicKr;MartinFl;SparerDa</t>
+    <t>Tiroler Wasserkraft Arena;NikolicKr;NikolicMa;MartinFl;SparerDa</t>
   </si>
   <si>
     <t>Sparkasse Arena Bozen;BernekerTh;SeewaldEl;RigoniDa;SparerDa</t>
@@ -1035,9 +1032,6 @@
     <t>Hala Tivoli;GroznikBo;RezekGr;HribarMa;ZgoncGa</t>
   </si>
   <si>
-    <t>Eishalle Asiago;OfnerCh;PiragicTr;PuffWo;RigoniDa</t>
-  </si>
-  <si>
     <t>Eishalle Feldkirch;NikolicMa;SeewaldEl;PardatscherUl;SeewaldJe</t>
   </si>
   <si>
@@ -1119,7 +1113,7 @@
     <t>Sparkasse Arena Bozen;OfnerCh;ZrnicMi;MantovaniDa;PardatscherUl</t>
   </si>
   <si>
-    <t>Eishalle Asiago;NikolicKr;NikolicMa;MantovaniDa;RigoniDa</t>
+    <t>Eishalle Asiago;NikolicMa;NikolicKr;MantovaniDa;RigoniDa</t>
   </si>
   <si>
     <t>Sparkasse Arena Bozen;Huber aAn;OfnerCh;MantovaniDa;PardatscherUl</t>
@@ -1523,191 +1517,191 @@
   <sheetData>
     <row r="2" ht="14.45" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A2">
-        <f>COUNTIF(A4:A98,"&lt;&gt;")</f>
-        <v>36</v>
+        <f>COUNTIF(A4:A100,"&lt;&gt;")</f>
+        <v>43</v>
       </c>
       <c r="B2">
-        <f>COUNTIF(B4:B100,"&lt;&gt;")</f>
-        <v>35</v>
+        <f>COUNTIF(B4:B96,"&lt;&gt;")</f>
+        <v>42</v>
       </c>
       <c r="C2">
         <f>COUNTIF(C4:C98,"&lt;&gt;")</f>
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D2">
         <f>COUNTIF(D4:D96,"&lt;&gt;")</f>
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="E2">
         <f>COUNTIF(E4:E98,"&lt;&gt;")</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F2">
         <f>COUNTIF(F4:F100,"&lt;&gt;")</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G2">
         <f>COUNTIF(G4:G100,"&lt;&gt;")</f>
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="H2">
         <f>COUNTIF(H4:H100,"&lt;&gt;")</f>
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I2">
         <f>COUNTIF(I4:I99,"&lt;&gt;")</f>
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J2">
         <f>COUNTIF(J4:J100,"&lt;&gt;")</f>
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K2">
         <f>COUNTIF(K4:K99,"&lt;&gt;")</f>
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="L2">
-        <f>COUNTIF(L4:L99,"&lt;&gt;")</f>
-        <v>22</v>
+        <f>COUNTIF(L4:L100,"&lt;&gt;")</f>
+        <v>26</v>
       </c>
       <c r="M2">
-        <f>COUNTIF(M4:M100,"&lt;&gt;")</f>
-        <v>21</v>
+        <f>COUNTIF(M4:M97,"&lt;&gt;")</f>
+        <v>26</v>
       </c>
       <c r="N2">
-        <f>COUNTIF(N4:N100,"&lt;&gt;")</f>
-        <v>21</v>
+        <f>COUNTIF(N4:N99,"&lt;&gt;")</f>
+        <v>26</v>
       </c>
       <c r="O2">
         <f>COUNTIF(O4:O100,"&lt;&gt;")</f>
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="P2">
-        <f>COUNTIF(P4:P100,"&lt;&gt;")</f>
-        <v>21</v>
+        <f>COUNTIF(P4:P98,"&lt;&gt;")</f>
+        <v>25</v>
       </c>
       <c r="Q2">
-        <f>COUNTIF(Q4:Q99,"&lt;&gt;")</f>
-        <v>20</v>
+        <f>COUNTIF(Q4:Q100,"&lt;&gt;")</f>
+        <v>25</v>
       </c>
       <c r="R2">
-        <f>COUNTIF(R4:R100,"&lt;&gt;")</f>
-        <v>20</v>
+        <f>COUNTIF(R4:R98,"&lt;&gt;")</f>
+        <v>24</v>
       </c>
       <c r="S2">
         <f>COUNTIF(S4:S100,"&lt;&gt;")</f>
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="T2">
-        <f>COUNTIF(T4:T99,"&lt;&gt;")</f>
-        <v>21</v>
+        <f>COUNTIF(T4:T98,"&lt;&gt;")</f>
+        <v>24</v>
       </c>
       <c r="U2">
-        <f t="shared" ref="U2:Z2" si="0">COUNTIF(U4:U100,"&lt;&gt;")</f>
-        <v>20</v>
+        <f>COUNTIF(U4:U100,"&lt;&gt;")</f>
+        <v>24</v>
       </c>
       <c r="V2">
-        <f t="shared" si="0"/>
-        <v>21</v>
+        <f>COUNTIF(V4:V100,"&lt;&gt;")</f>
+        <v>24</v>
       </c>
       <c r="W2">
-        <f t="shared" si="0"/>
-        <v>20</v>
+        <f>COUNTIF(W4:W100,"&lt;&gt;")</f>
+        <v>23</v>
       </c>
       <c r="X2">
-        <f t="shared" si="0"/>
-        <v>19</v>
+        <f>COUNTIF(X4:X100,"&lt;&gt;")</f>
+        <v>23</v>
       </c>
       <c r="Y2">
-        <f t="shared" si="0"/>
-        <v>20</v>
+        <f>COUNTIF(Y4:Y100,"&lt;&gt;")</f>
+        <v>23</v>
       </c>
       <c r="Z2">
-        <f t="shared" si="0"/>
-        <v>19</v>
+        <f>COUNTIF(Z4:Z95,"&lt;&gt;")</f>
+        <v>23</v>
       </c>
       <c r="AA2">
-        <f>COUNTIF(AA4:AA97,"&lt;&gt;")</f>
-        <v>19</v>
+        <f>COUNTIF(AA4:AA96,"&lt;&gt;")</f>
+        <v>22</v>
       </c>
       <c r="AB2">
-        <f>COUNTIF(AB4:AB98,"&lt;&gt;")</f>
-        <v>18</v>
+        <f>COUNTIF(AB4:AB100,"&lt;&gt;")</f>
+        <v>22</v>
       </c>
       <c r="AC2">
         <f>COUNTIF(AC4:AC100,"&lt;&gt;")</f>
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AD2">
         <f>COUNTIF(AD4:AD95,"&lt;&gt;")</f>
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AE2">
-        <f>COUNTIF(AE4:AE99,"&lt;&gt;")</f>
-        <v>17</v>
+        <f>COUNTIF(AE4:AE95,"&lt;&gt;")</f>
+        <v>21</v>
       </c>
       <c r="AF2">
-        <f>COUNTIF(AF4:AF100,"&lt;&gt;")</f>
-        <v>18</v>
+        <f>COUNTIF(AF4:AF93,"&lt;&gt;")</f>
+        <v>21</v>
       </c>
       <c r="AG2">
-        <f>COUNTIF(AG4:AG93,"&lt;&gt;")</f>
-        <v>17</v>
+        <f>COUNTIF(AG4:AG100,"&lt;&gt;")</f>
+        <v>20</v>
       </c>
       <c r="AH2">
         <f>COUNTIF(AH4:AH97,"&lt;&gt;")</f>
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AI2">
         <f>COUNTIF(AI4:AI96,"&lt;&gt;")</f>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AJ2">
-        <f>COUNTIF(AJ4:AJ99,"&lt;&gt;")</f>
-        <v>16</v>
+        <f>COUNTIF(AJ4:AJ97,"&lt;&gt;")</f>
+        <v>18</v>
       </c>
       <c r="AK2">
-        <f t="shared" ref="AK2:AU2" si="1">COUNTIF(AK4:AK100,"&lt;&gt;")</f>
-        <v>15</v>
+        <f>COUNTIF(AK4:AK100,"&lt;&gt;")</f>
+        <v>17</v>
       </c>
       <c r="AL2">
-        <f t="shared" si="1"/>
-        <v>13</v>
+        <f>COUNTIF(AL4:AL100,"&lt;&gt;")</f>
+        <v>14</v>
       </c>
       <c r="AM2">
         <f>COUNTIF(AM4:AM99,"&lt;&gt;")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN2">
-        <f t="shared" si="1"/>
-        <v>10</v>
+        <f>COUNTIF(AN4:AN100,"&lt;&gt;")</f>
+        <v>12</v>
       </c>
       <c r="AO2">
         <f>COUNTIF(AO4:AO98,"&lt;&gt;")</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AP2">
-        <f t="shared" si="1"/>
-        <v>6</v>
+        <f>COUNTIF(AP4:AP100,"&lt;&gt;")</f>
+        <v>7</v>
       </c>
       <c r="AQ2">
         <f>COUNTIF(AQ4:AQ99,"&lt;&gt;")</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AR2">
-        <f t="shared" si="1"/>
-        <v>5</v>
+        <f>COUNTIF(AR4:AR100,"&lt;&gt;")</f>
+        <v>6</v>
       </c>
       <c r="AS2">
         <f>COUNTIF(AS4:AS99,"&lt;&gt;")</f>
+        <v>5</v>
+      </c>
+      <c r="AT2">
+        <f>COUNTIF(AT4:AT100,"&lt;&gt;")</f>
         <v>4</v>
       </c>
-      <c r="AT2">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
       <c r="AU2">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(AU4:AU100,"&lt;&gt;")</f>
         <v>1</v>
       </c>
     </row>
@@ -1895,73 +1889,73 @@
         <v>51</v>
       </c>
       <c r="J4" t="s">
+        <v>51</v>
+      </c>
+      <c r="K4" t="s">
         <v>52</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>53</v>
-      </c>
-      <c r="L4" t="s">
-        <v>51</v>
       </c>
       <c r="M4" t="s">
         <v>51</v>
       </c>
       <c r="N4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="P4" t="s">
         <v>51</v>
       </c>
       <c r="Q4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R4" t="s">
+        <v>52</v>
+      </c>
+      <c r="S4" t="s">
+        <v>55</v>
+      </c>
+      <c r="T4" t="s">
         <v>51</v>
       </c>
-      <c r="S4" t="s">
+      <c r="U4" t="s">
+        <v>52</v>
+      </c>
+      <c r="V4" t="s">
+        <v>54</v>
+      </c>
+      <c r="W4" t="s">
         <v>51</v>
-      </c>
-      <c r="T4" t="s">
-        <v>53</v>
-      </c>
-      <c r="U4" t="s">
-        <v>55</v>
-      </c>
-      <c r="V4" t="s">
-        <v>51</v>
-      </c>
-      <c r="W4" t="s">
-        <v>53</v>
       </c>
       <c r="X4" t="s">
         <v>51</v>
       </c>
       <c r="Y4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="Z4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="AA4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AB4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AC4" t="s">
         <v>51</v>
       </c>
       <c r="AD4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AE4" t="s">
         <v>51</v>
       </c>
       <c r="AF4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="AG4" t="s">
         <v>51</v>
@@ -1970,13 +1964,13 @@
         <v>51</v>
       </c>
       <c r="AI4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AJ4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AK4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AL4" t="s">
         <v>51</v>
@@ -1994,13 +1988,13 @@
         <v>58</v>
       </c>
       <c r="AQ4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="AR4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AS4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AT4" t="s">
         <v>59</v>
@@ -2023,91 +2017,91 @@
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H5" t="s">
+        <v>52</v>
+      </c>
+      <c r="I5" t="s">
+        <v>55</v>
+      </c>
+      <c r="J5" t="s">
+        <v>55</v>
+      </c>
+      <c r="K5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L5" t="s">
+        <v>57</v>
+      </c>
+      <c r="M5" t="s">
+        <v>55</v>
+      </c>
+      <c r="N5" t="s">
+        <v>56</v>
+      </c>
+      <c r="O5" t="s">
         <v>53</v>
       </c>
-      <c r="B5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="P5" t="s">
         <v>55</v>
       </c>
-      <c r="D5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E5" t="s">
-        <v>53</v>
-      </c>
-      <c r="F5" t="s">
-        <v>53</v>
-      </c>
-      <c r="G5" t="s">
-        <v>54</v>
-      </c>
-      <c r="H5" t="s">
-        <v>53</v>
-      </c>
-      <c r="I5" t="s">
-        <v>54</v>
-      </c>
-      <c r="J5" t="s">
-        <v>57</v>
-      </c>
-      <c r="K5" t="s">
-        <v>52</v>
-      </c>
-      <c r="L5" t="s">
-        <v>54</v>
-      </c>
-      <c r="M5" t="s">
-        <v>54</v>
-      </c>
-      <c r="N5" t="s">
-        <v>52</v>
-      </c>
-      <c r="O5" t="s">
-        <v>57</v>
-      </c>
-      <c r="P5" t="s">
-        <v>54</v>
-      </c>
       <c r="Q5" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="R5" t="s">
         <v>53</v>
       </c>
       <c r="S5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="T5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="U5" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="V5" t="s">
         <v>55</v>
       </c>
       <c r="W5" t="s">
+        <v>52</v>
+      </c>
+      <c r="X5" t="s">
         <v>54</v>
       </c>
-      <c r="X5" t="s">
+      <c r="Y5" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA5" t="s">
         <v>57</v>
       </c>
-      <c r="Y5" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>54</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>54</v>
-      </c>
       <c r="AB5" t="s">
+        <v>63</v>
+      </c>
+      <c r="AC5" t="s">
         <v>57</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>54</v>
       </c>
       <c r="AD5" t="s">
         <v>57</v>
@@ -2116,16 +2110,16 @@
         <v>57</v>
       </c>
       <c r="AF5" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="AG5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AH5" t="s">
         <v>56</v>
       </c>
       <c r="AI5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AJ5" t="s">
         <v>63</v>
@@ -2134,7 +2128,7 @@
         <v>57</v>
       </c>
       <c r="AL5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AM5" t="s">
         <v>58</v>
@@ -2166,22 +2160,22 @@
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" t="s">
         <v>57</v>
       </c>
-      <c r="B6" t="s">
-        <v>54</v>
-      </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E6" t="s">
         <v>57</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G6" t="s">
         <v>57</v>
@@ -2193,49 +2187,49 @@
         <v>57</v>
       </c>
       <c r="J6" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="K6" t="s">
         <v>57</v>
       </c>
       <c r="L6" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="M6" t="s">
         <v>57</v>
       </c>
       <c r="N6" t="s">
+        <v>70</v>
+      </c>
+      <c r="O6" t="s">
         <v>57</v>
       </c>
-      <c r="O6" t="s">
-        <v>66</v>
-      </c>
       <c r="P6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q6" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="R6" t="s">
+        <v>57</v>
+      </c>
+      <c r="S6" t="s">
+        <v>67</v>
+      </c>
+      <c r="T6" t="s">
         <v>56</v>
-      </c>
-      <c r="S6" t="s">
-        <v>56</v>
-      </c>
-      <c r="T6" t="s">
-        <v>57</v>
       </c>
       <c r="U6" t="s">
         <v>56</v>
       </c>
       <c r="V6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="W6" t="s">
         <v>56</v>
       </c>
       <c r="X6" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="Y6" t="s">
         <v>56</v>
@@ -2244,13 +2238,13 @@
         <v>56</v>
       </c>
       <c r="AA6" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="AB6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC6" t="s">
         <v>63</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>56</v>
       </c>
       <c r="AD6" t="s">
         <v>71</v>
@@ -2259,7 +2253,7 @@
         <v>71</v>
       </c>
       <c r="AF6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="AG6" t="s">
         <v>56</v>
@@ -2271,7 +2265,7 @@
         <v>56</v>
       </c>
       <c r="AJ6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AK6" t="s">
         <v>56</v>
@@ -2292,13 +2286,13 @@
         <v>74</v>
       </c>
       <c r="AQ6" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="AR6" t="s">
         <v>74</v>
       </c>
       <c r="AS6" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="AT6" t="s">
         <v>76</v>
@@ -2306,10 +2300,10 @@
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" t="s">
         <v>63</v>
-      </c>
-      <c r="B7" t="s">
-        <v>57</v>
       </c>
       <c r="C7" t="s">
         <v>57</v>
@@ -2321,76 +2315,76 @@
         <v>63</v>
       </c>
       <c r="F7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G7" t="s">
         <v>63</v>
       </c>
       <c r="H7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J7" t="s">
+        <v>56</v>
+      </c>
+      <c r="K7" t="s">
         <v>71</v>
       </c>
-      <c r="K7" t="s">
-        <v>66</v>
-      </c>
       <c r="L7" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="M7" t="s">
         <v>56</v>
       </c>
       <c r="N7" t="s">
+        <v>59</v>
+      </c>
+      <c r="O7" t="s">
         <v>56</v>
-      </c>
-      <c r="O7" t="s">
-        <v>58</v>
       </c>
       <c r="P7" t="s">
         <v>71</v>
       </c>
       <c r="Q7" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="R7" t="s">
+        <v>67</v>
+      </c>
+      <c r="S7" t="s">
         <v>58</v>
       </c>
-      <c r="S7" t="s">
-        <v>66</v>
-      </c>
       <c r="T7" t="s">
+        <v>67</v>
+      </c>
+      <c r="U7" t="s">
         <v>71</v>
       </c>
-      <c r="U7" t="s">
-        <v>70</v>
-      </c>
       <c r="V7" t="s">
+        <v>71</v>
+      </c>
+      <c r="W7" t="s">
+        <v>58</v>
+      </c>
+      <c r="X7" t="s">
         <v>57</v>
       </c>
-      <c r="W7" t="s">
+      <c r="Y7" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z7" t="s">
         <v>71</v>
       </c>
-      <c r="X7" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>71</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>66</v>
-      </c>
       <c r="AA7" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="AB7" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="AC7" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="AD7" t="s">
         <v>77</v>
@@ -2399,10 +2393,10 @@
         <v>65</v>
       </c>
       <c r="AF7" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="AG7" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="AH7" t="s">
         <v>74</v>
@@ -2432,13 +2426,13 @@
         <v>80</v>
       </c>
       <c r="AQ7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AR7" t="s">
         <v>81</v>
       </c>
-      <c r="AR7" t="s">
+      <c r="AS7" t="s">
         <v>82</v>
-      </c>
-      <c r="AS7" t="s">
-        <v>60</v>
       </c>
       <c r="AT7" t="s">
         <v>83</v>
@@ -2452,7 +2446,7 @@
         <v>56</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D8" t="s">
         <v>56</v>
@@ -2476,7 +2470,7 @@
         <v>58</v>
       </c>
       <c r="K8" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="L8" t="s">
         <v>58</v>
@@ -2485,52 +2479,52 @@
         <v>58</v>
       </c>
       <c r="N8" t="s">
+        <v>58</v>
+      </c>
+      <c r="O8" t="s">
         <v>71</v>
-      </c>
-      <c r="O8" t="s">
-        <v>84</v>
       </c>
       <c r="P8" t="s">
         <v>59</v>
       </c>
       <c r="Q8" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="R8" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="S8" t="s">
+        <v>84</v>
+      </c>
+      <c r="T8" t="s">
         <v>71</v>
       </c>
-      <c r="T8" t="s">
-        <v>58</v>
-      </c>
       <c r="U8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="V8" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="W8" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="X8" t="s">
         <v>71</v>
       </c>
       <c r="Y8" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="Z8" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB8" t="s">
         <v>74</v>
       </c>
-      <c r="AA8" t="s">
-        <v>64</v>
-      </c>
-      <c r="AB8" t="s">
+      <c r="AC8" t="s">
         <v>71</v>
-      </c>
-      <c r="AC8" t="s">
-        <v>58</v>
       </c>
       <c r="AD8" t="s">
         <v>68</v>
@@ -2539,10 +2533,10 @@
         <v>85</v>
       </c>
       <c r="AF8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="AG8" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="AH8" t="s">
         <v>64</v>
@@ -2572,21 +2566,21 @@
         <v>60</v>
       </c>
       <c r="AQ8" t="s">
+        <v>83</v>
+      </c>
+      <c r="AR8" t="s">
+        <v>82</v>
+      </c>
+      <c r="AS8" t="s">
         <v>88</v>
-      </c>
-      <c r="AR8" t="s">
-        <v>81</v>
-      </c>
-      <c r="AS8" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" t="s">
         <v>71</v>
-      </c>
-      <c r="B9" t="s">
-        <v>70</v>
       </c>
       <c r="C9" t="s">
         <v>59</v>
@@ -2610,61 +2604,61 @@
         <v>65</v>
       </c>
       <c r="J9" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="K9" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="L9" t="s">
         <v>77</v>
       </c>
       <c r="M9" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="N9" t="s">
+        <v>74</v>
+      </c>
+      <c r="O9" t="s">
         <v>77</v>
-      </c>
-      <c r="O9" t="s">
-        <v>65</v>
       </c>
       <c r="P9" t="s">
         <v>77</v>
       </c>
       <c r="Q9" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="R9" t="s">
+        <v>84</v>
+      </c>
+      <c r="S9" t="s">
+        <v>65</v>
+      </c>
+      <c r="T9" t="s">
         <v>77</v>
-      </c>
-      <c r="S9" t="s">
-        <v>77</v>
-      </c>
-      <c r="T9" t="s">
-        <v>65</v>
       </c>
       <c r="U9" t="s">
         <v>77</v>
       </c>
       <c r="V9" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="W9" t="s">
         <v>77</v>
       </c>
       <c r="X9" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA9" t="s">
         <v>77</v>
       </c>
-      <c r="Y9" t="s">
-        <v>77</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>64</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>89</v>
-      </c>
       <c r="AB9" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="AC9" t="s">
         <v>77</v>
@@ -2676,7 +2670,7 @@
         <v>68</v>
       </c>
       <c r="AF9" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="AG9" t="s">
         <v>77</v>
@@ -2697,30 +2691,30 @@
         <v>68</v>
       </c>
       <c r="AM9" t="s">
+        <v>81</v>
+      </c>
+      <c r="AN9" t="s">
         <v>82</v>
       </c>
-      <c r="AN9" t="s">
-        <v>81</v>
-      </c>
       <c r="AO9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AP9" t="s">
         <v>91</v>
       </c>
+      <c r="AQ9" t="s">
+        <v>92</v>
+      </c>
       <c r="AR9" t="s">
         <v>83</v>
       </c>
-      <c r="AS9" t="s">
-        <v>92</v>
-      </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="C10" t="s">
         <v>65</v>
@@ -2729,7 +2723,7 @@
         <v>74</v>
       </c>
       <c r="E10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F10" t="s">
         <v>93</v>
@@ -2744,64 +2738,64 @@
         <v>74</v>
       </c>
       <c r="J10" t="s">
+        <v>74</v>
+      </c>
+      <c r="K10" t="s">
+        <v>64</v>
+      </c>
+      <c r="L10" t="s">
         <v>65</v>
-      </c>
-      <c r="K10" t="s">
-        <v>65</v>
-      </c>
-      <c r="L10" t="s">
-        <v>74</v>
       </c>
       <c r="M10" t="s">
         <v>74</v>
       </c>
       <c r="N10" t="s">
+        <v>64</v>
+      </c>
+      <c r="O10" t="s">
         <v>65</v>
-      </c>
-      <c r="O10" t="s">
-        <v>64</v>
       </c>
       <c r="P10" t="s">
         <v>93</v>
       </c>
       <c r="Q10" t="s">
+        <v>74</v>
+      </c>
+      <c r="R10" t="s">
+        <v>65</v>
+      </c>
+      <c r="S10" t="s">
         <v>64</v>
       </c>
-      <c r="R10" t="s">
+      <c r="T10" t="s">
+        <v>93</v>
+      </c>
+      <c r="U10" t="s">
+        <v>94</v>
+      </c>
+      <c r="V10" t="s">
+        <v>65</v>
+      </c>
+      <c r="W10" t="s">
         <v>74</v>
       </c>
-      <c r="S10" t="s">
-        <v>93</v>
-      </c>
-      <c r="T10" t="s">
-        <v>64</v>
-      </c>
-      <c r="U10" t="s">
+      <c r="X10" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC10" t="s">
         <v>74</v>
-      </c>
-      <c r="V10" t="s">
-        <v>94</v>
-      </c>
-      <c r="W10" t="s">
-        <v>94</v>
-      </c>
-      <c r="X10" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>65</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>73</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>73</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>84</v>
       </c>
       <c r="AD10" t="s">
         <v>86</v>
@@ -2810,10 +2804,10 @@
         <v>89</v>
       </c>
       <c r="AF10" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AG10" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="AH10" t="s">
         <v>90</v>
@@ -2842,16 +2836,16 @@
       <c r="AP10" t="s">
         <v>96</v>
       </c>
-      <c r="AS10" t="s">
+      <c r="AQ10" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" t="s">
         <v>77</v>
-      </c>
-      <c r="B11" t="s">
-        <v>65</v>
       </c>
       <c r="C11" t="s">
         <v>74</v>
@@ -2878,7 +2872,7 @@
         <v>64</v>
       </c>
       <c r="K11" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="L11" t="s">
         <v>64</v>
@@ -2887,49 +2881,49 @@
         <v>64</v>
       </c>
       <c r="N11" t="s">
+        <v>68</v>
+      </c>
+      <c r="O11" t="s">
         <v>74</v>
-      </c>
-      <c r="O11" t="s">
-        <v>73</v>
       </c>
       <c r="P11" t="s">
         <v>90</v>
       </c>
       <c r="Q11" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="R11" t="s">
         <v>64</v>
       </c>
       <c r="S11" t="s">
+        <v>73</v>
+      </c>
+      <c r="T11" t="s">
         <v>64</v>
       </c>
-      <c r="T11" t="s">
-        <v>85</v>
-      </c>
       <c r="U11" t="s">
+        <v>68</v>
+      </c>
+      <c r="V11" t="s">
         <v>64</v>
       </c>
-      <c r="V11" t="s">
-        <v>68</v>
-      </c>
       <c r="W11" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="X11" t="s">
         <v>68</v>
       </c>
       <c r="Y11" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="Z11" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA11" t="s">
         <v>94</v>
       </c>
-      <c r="AA11" t="s">
-        <v>98</v>
-      </c>
       <c r="AB11" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="AC11" t="s">
         <v>68</v>
@@ -2941,13 +2935,13 @@
         <v>56</v>
       </c>
       <c r="AF11" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="AG11" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="AH11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AI11" t="s">
         <v>98</v>
@@ -2973,10 +2967,10 @@
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" t="s">
         <v>65</v>
-      </c>
-      <c r="B12" t="s">
-        <v>74</v>
       </c>
       <c r="C12" t="s">
         <v>64</v>
@@ -3000,64 +2994,64 @@
         <v>68</v>
       </c>
       <c r="J12" t="s">
+        <v>73</v>
+      </c>
+      <c r="K12" t="s">
+        <v>89</v>
+      </c>
+      <c r="L12" t="s">
         <v>68</v>
-      </c>
-      <c r="K12" t="s">
-        <v>68</v>
-      </c>
-      <c r="L12" t="s">
-        <v>73</v>
       </c>
       <c r="M12" t="s">
         <v>73</v>
       </c>
       <c r="N12" t="s">
+        <v>89</v>
+      </c>
+      <c r="O12" t="s">
         <v>78</v>
-      </c>
-      <c r="O12" t="s">
-        <v>68</v>
       </c>
       <c r="P12" t="s">
         <v>89</v>
       </c>
       <c r="Q12" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="R12" t="s">
+        <v>68</v>
+      </c>
+      <c r="S12" t="s">
+        <v>68</v>
+      </c>
+      <c r="T12" t="s">
+        <v>90</v>
+      </c>
+      <c r="U12" t="s">
+        <v>79</v>
+      </c>
+      <c r="V12" t="s">
         <v>73</v>
       </c>
-      <c r="S12" t="s">
-        <v>90</v>
-      </c>
-      <c r="T12" t="s">
-        <v>89</v>
-      </c>
-      <c r="U12" t="s">
-        <v>68</v>
-      </c>
-      <c r="V12" t="s">
-        <v>89</v>
-      </c>
       <c r="W12" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="X12" t="s">
         <v>89</v>
       </c>
       <c r="Y12" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="Z12" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AA12" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AB12" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="AC12" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AD12" t="s">
         <v>87</v>
@@ -3066,10 +3060,10 @@
         <v>78</v>
       </c>
       <c r="AF12" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="AG12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AH12" t="s">
         <v>80</v>
@@ -3098,10 +3092,10 @@
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" t="s">
         <v>74</v>
-      </c>
-      <c r="B13" t="s">
-        <v>64</v>
       </c>
       <c r="C13" t="s">
         <v>73</v>
@@ -3125,19 +3119,19 @@
         <v>86</v>
       </c>
       <c r="J13" t="s">
+        <v>78</v>
+      </c>
+      <c r="K13" t="s">
+        <v>79</v>
+      </c>
+      <c r="L13" t="s">
         <v>89</v>
       </c>
-      <c r="K13" t="s">
-        <v>77</v>
-      </c>
-      <c r="L13" t="s">
+      <c r="M13" t="s">
         <v>68</v>
       </c>
-      <c r="M13" t="s">
+      <c r="N13" t="s">
         <v>78</v>
-      </c>
-      <c r="N13" t="s">
-        <v>79</v>
       </c>
       <c r="O13" t="s">
         <v>79</v>
@@ -3149,40 +3143,40 @@
         <v>78</v>
       </c>
       <c r="R13" t="s">
+        <v>77</v>
+      </c>
+      <c r="S13" t="s">
+        <v>79</v>
+      </c>
+      <c r="T13" t="s">
+        <v>89</v>
+      </c>
+      <c r="U13" t="s">
+        <v>86</v>
+      </c>
+      <c r="V13" t="s">
         <v>78</v>
       </c>
-      <c r="S13" t="s">
-        <v>89</v>
-      </c>
-      <c r="T13" t="s">
+      <c r="W13" t="s">
+        <v>78</v>
+      </c>
+      <c r="X13" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y13" t="s">
         <v>79</v>
       </c>
-      <c r="U13" t="s">
-        <v>78</v>
-      </c>
-      <c r="V13" t="s">
-        <v>64</v>
-      </c>
-      <c r="W13" t="s">
-        <v>86</v>
-      </c>
-      <c r="X13" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>78</v>
-      </c>
       <c r="Z13" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AA13" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AB13" t="s">
         <v>98</v>
       </c>
       <c r="AC13" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AD13" t="s">
         <v>99</v>
@@ -3191,10 +3185,10 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="AG13" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="AH13" t="s">
         <v>76</v>
@@ -3209,13 +3203,13 @@
         <v>87</v>
       </c>
       <c r="AL13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM13" t="s">
         <v>62</v>
       </c>
       <c r="AN13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AO13" t="s">
         <v>96</v>
@@ -3223,10 +3217,10 @@
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" t="s">
         <v>64</v>
-      </c>
-      <c r="B14" t="s">
-        <v>85</v>
       </c>
       <c r="C14" t="s">
         <v>94</v>
@@ -3250,64 +3244,64 @@
         <v>98</v>
       </c>
       <c r="J14" t="s">
+        <v>101</v>
+      </c>
+      <c r="K14" t="s">
+        <v>98</v>
+      </c>
+      <c r="L14" t="s">
         <v>79</v>
       </c>
-      <c r="K14" t="s">
+      <c r="M14" t="s">
+        <v>78</v>
+      </c>
+      <c r="N14" t="s">
         <v>79</v>
       </c>
-      <c r="L14" t="s">
-        <v>78</v>
-      </c>
-      <c r="M14" t="s">
-        <v>101</v>
-      </c>
-      <c r="N14" t="s">
+      <c r="O14" t="s">
         <v>86</v>
-      </c>
-      <c r="O14" t="s">
-        <v>82</v>
       </c>
       <c r="P14" t="s">
         <v>98</v>
       </c>
       <c r="Q14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="R14" t="s">
         <v>79</v>
       </c>
       <c r="S14" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="T14" t="s">
         <v>98</v>
       </c>
       <c r="U14" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="V14" t="s">
+        <v>81</v>
+      </c>
+      <c r="W14" t="s">
+        <v>79</v>
+      </c>
+      <c r="X14" t="s">
         <v>78</v>
       </c>
-      <c r="W14" t="s">
-        <v>76</v>
-      </c>
-      <c r="X14" t="s">
-        <v>82</v>
-      </c>
       <c r="Y14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Z14" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AA14" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AB14" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AC14" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="AD14" t="s">
         <v>102</v>
@@ -3316,10 +3310,10 @@
         <v>99</v>
       </c>
       <c r="AF14" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="AG14" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="AH14" t="s">
         <v>105</v>
@@ -3345,10 +3339,10 @@
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B15" t="s">
         <v>73</v>
-      </c>
-      <c r="B15" t="s">
-        <v>94</v>
       </c>
       <c r="C15" t="s">
         <v>68</v>
@@ -3372,19 +3366,19 @@
         <v>80</v>
       </c>
       <c r="J15" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="K15" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="L15" t="s">
         <v>86</v>
       </c>
       <c r="M15" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="N15" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="O15" t="s">
         <v>98</v>
@@ -3393,40 +3387,40 @@
         <v>107</v>
       </c>
       <c r="Q15" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="R15" t="s">
         <v>86</v>
       </c>
       <c r="S15" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="T15" t="s">
         <v>80</v>
       </c>
       <c r="U15" t="s">
+        <v>87</v>
+      </c>
+      <c r="V15" t="s">
         <v>98</v>
       </c>
-      <c r="V15" t="s">
+      <c r="W15" t="s">
         <v>86</v>
       </c>
-      <c r="W15" t="s">
+      <c r="X15" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA15" t="s">
         <v>87</v>
       </c>
-      <c r="X15" t="s">
-        <v>76</v>
-      </c>
-      <c r="Y15" t="s">
-        <v>98</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>76</v>
-      </c>
-      <c r="AA15" t="s">
-        <v>90</v>
-      </c>
       <c r="AB15" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AC15" t="s">
         <v>76</v>
@@ -3438,10 +3432,10 @@
         <v>102</v>
       </c>
       <c r="AF15" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="AG15" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="AH15" t="s">
         <v>95</v>
@@ -3450,10 +3444,10 @@
         <v>75</v>
       </c>
       <c r="AJ15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AK15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AL15" t="s">
         <v>91</v>
@@ -3467,10 +3461,10 @@
     </row>
     <row r="16" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" t="s">
         <v>94</v>
-      </c>
-      <c r="B16" t="s">
-        <v>68</v>
       </c>
       <c r="C16" t="s">
         <v>89</v>
@@ -3488,70 +3482,70 @@
         <v>79</v>
       </c>
       <c r="H16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I16" t="s">
         <v>76</v>
       </c>
       <c r="J16" t="s">
+        <v>80</v>
+      </c>
+      <c r="K16" t="s">
+        <v>105</v>
+      </c>
+      <c r="L16" t="s">
         <v>76</v>
       </c>
-      <c r="K16" t="s">
-        <v>98</v>
-      </c>
-      <c r="L16" t="s">
-        <v>82</v>
-      </c>
       <c r="M16" t="s">
+        <v>81</v>
+      </c>
+      <c r="N16" t="s">
+        <v>86</v>
+      </c>
+      <c r="O16" t="s">
         <v>80</v>
-      </c>
-      <c r="N16" t="s">
-        <v>80</v>
-      </c>
-      <c r="O16" t="s">
-        <v>76</v>
       </c>
       <c r="P16" t="s">
         <v>80</v>
       </c>
       <c r="Q16" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="R16" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="S16" t="s">
         <v>76</v>
       </c>
       <c r="T16" t="s">
+        <v>76</v>
+      </c>
+      <c r="U16" t="s">
         <v>105</v>
       </c>
-      <c r="U16" t="s">
+      <c r="V16" t="s">
         <v>76</v>
       </c>
-      <c r="V16" t="s">
-        <v>82</v>
-      </c>
       <c r="W16" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="X16" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y16" t="s">
         <v>87</v>
       </c>
-      <c r="Y16" t="s">
-        <v>76</v>
-      </c>
       <c r="Z16" t="s">
+        <v>107</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC16" t="s">
         <v>87</v>
-      </c>
-      <c r="AA16" t="s">
-        <v>107</v>
-      </c>
-      <c r="AB16" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC16" t="s">
-        <v>99</v>
       </c>
       <c r="AD16" t="s">
         <v>95</v>
@@ -3560,22 +3554,22 @@
         <v>95</v>
       </c>
       <c r="AF16" t="s">
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="AG16" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AH16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AI16" t="s">
         <v>91</v>
       </c>
       <c r="AJ16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AK16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL16" t="s">
         <v>98</v>
@@ -3583,10 +3577,10 @@
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>89</v>
+      </c>
+      <c r="B17" t="s">
         <v>68</v>
-      </c>
-      <c r="B17" t="s">
-        <v>89</v>
       </c>
       <c r="C17" t="s">
         <v>79</v>
@@ -3610,76 +3604,76 @@
         <v>105</v>
       </c>
       <c r="J17" t="s">
+        <v>76</v>
+      </c>
+      <c r="K17" t="s">
+        <v>108</v>
+      </c>
+      <c r="L17" t="s">
         <v>105</v>
       </c>
-      <c r="K17" t="s">
+      <c r="M17" t="s">
+        <v>80</v>
+      </c>
+      <c r="N17" t="s">
+        <v>76</v>
+      </c>
+      <c r="O17" t="s">
         <v>87</v>
-      </c>
-      <c r="L17" t="s">
-        <v>80</v>
-      </c>
-      <c r="M17" t="s">
-        <v>76</v>
-      </c>
-      <c r="N17" t="s">
-        <v>87</v>
-      </c>
-      <c r="O17" t="s">
-        <v>102</v>
       </c>
       <c r="P17" t="s">
         <v>87</v>
       </c>
       <c r="Q17" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="R17" t="s">
+        <v>87</v>
+      </c>
+      <c r="S17" t="s">
+        <v>102</v>
+      </c>
+      <c r="T17" t="s">
+        <v>99</v>
+      </c>
+      <c r="U17" t="s">
+        <v>101</v>
+      </c>
+      <c r="V17" t="s">
+        <v>87</v>
+      </c>
+      <c r="W17" t="s">
         <v>98</v>
       </c>
-      <c r="S17" t="s">
-        <v>99</v>
-      </c>
-      <c r="T17" t="s">
+      <c r="X17" t="s">
         <v>108</v>
       </c>
-      <c r="U17" t="s">
-        <v>87</v>
-      </c>
-      <c r="V17" t="s">
-        <v>108</v>
-      </c>
-      <c r="W17" t="s">
-        <v>101</v>
-      </c>
-      <c r="X17" t="s">
+      <c r="Y17" t="s">
+        <v>105</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>103</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>82</v>
+      </c>
+      <c r="AC17" t="s">
         <v>102</v>
-      </c>
-      <c r="Y17" t="s">
-        <v>87</v>
-      </c>
-      <c r="Z17" t="s">
-        <v>105</v>
-      </c>
-      <c r="AA17" t="s">
-        <v>103</v>
-      </c>
-      <c r="AB17" t="s">
-        <v>109</v>
-      </c>
-      <c r="AC17" t="s">
-        <v>95</v>
       </c>
       <c r="AD17" t="s">
         <v>103</v>
       </c>
       <c r="AE17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF17" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="AG17" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="AH17" t="s">
         <v>91</v>
@@ -3688,7 +3682,7 @@
         <v>104</v>
       </c>
       <c r="AJ17" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="AK17" t="s">
         <v>91</v>
@@ -3726,76 +3720,76 @@
         <v>99</v>
       </c>
       <c r="J18" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="K18" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="L18" t="s">
         <v>99</v>
       </c>
       <c r="M18" t="s">
+        <v>99</v>
+      </c>
+      <c r="N18" t="s">
         <v>87</v>
       </c>
-      <c r="N18" t="s">
+      <c r="O18" t="s">
         <v>102</v>
-      </c>
-      <c r="O18" t="s">
-        <v>103</v>
       </c>
       <c r="P18" t="s">
         <v>103</v>
       </c>
       <c r="Q18" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="R18" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="S18" t="s">
         <v>103</v>
       </c>
       <c r="T18" t="s">
+        <v>103</v>
+      </c>
+      <c r="U18" t="s">
         <v>95</v>
       </c>
-      <c r="U18" t="s">
-        <v>67</v>
-      </c>
       <c r="V18" t="s">
+        <v>95</v>
+      </c>
+      <c r="W18" t="s">
+        <v>76</v>
+      </c>
+      <c r="X18" t="s">
         <v>111</v>
       </c>
-      <c r="W18" t="s">
-        <v>95</v>
-      </c>
-      <c r="X18" t="s">
-        <v>67</v>
-      </c>
       <c r="Y18" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="Z18" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="AA18" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AB18" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AC18" t="s">
-        <v>109</v>
+        <v>66</v>
       </c>
       <c r="AD18" t="s">
         <v>109</v>
       </c>
       <c r="AE18" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="AF18" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AG18" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="AH18" t="s">
         <v>100</v>
@@ -3804,7 +3798,7 @@
         <v>100</v>
       </c>
       <c r="AJ18" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="AK18" t="s">
         <v>100</v>
@@ -3836,79 +3830,79 @@
         <v>105</v>
       </c>
       <c r="I19" t="s">
+        <v>81</v>
+      </c>
+      <c r="J19" t="s">
+        <v>95</v>
+      </c>
+      <c r="K19" t="s">
         <v>82</v>
       </c>
-      <c r="J19" t="s">
+      <c r="L19" t="s">
         <v>102</v>
       </c>
-      <c r="K19" t="s">
+      <c r="M19" t="s">
+        <v>66</v>
+      </c>
+      <c r="N19" t="s">
+        <v>105</v>
+      </c>
+      <c r="O19" t="s">
+        <v>95</v>
+      </c>
+      <c r="P19" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>75</v>
+      </c>
+      <c r="R19" t="s">
         <v>103</v>
       </c>
-      <c r="L19" t="s">
-        <v>67</v>
-      </c>
-      <c r="M19" t="s">
+      <c r="S19" t="s">
+        <v>109</v>
+      </c>
+      <c r="T19" t="s">
+        <v>82</v>
+      </c>
+      <c r="U19" t="s">
+        <v>66</v>
+      </c>
+      <c r="V19" t="s">
+        <v>75</v>
+      </c>
+      <c r="W19" t="s">
         <v>95</v>
       </c>
-      <c r="N19" t="s">
-        <v>95</v>
-      </c>
-      <c r="O19" t="s">
+      <c r="X19" t="s">
         <v>109</v>
       </c>
-      <c r="P19" t="s">
+      <c r="Y19" t="s">
         <v>61</v>
       </c>
-      <c r="Q19" t="s">
-        <v>105</v>
-      </c>
-      <c r="R19" t="s">
-        <v>95</v>
-      </c>
-      <c r="S19" t="s">
-        <v>61</v>
-      </c>
-      <c r="T19" t="s">
-        <v>81</v>
-      </c>
-      <c r="U19" t="s">
-        <v>75</v>
-      </c>
-      <c r="V19" t="s">
-        <v>109</v>
-      </c>
-      <c r="W19" t="s">
-        <v>67</v>
-      </c>
-      <c r="X19" t="s">
+      <c r="Z19" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC19" t="s">
         <v>103</v>
-      </c>
-      <c r="Y19" t="s">
-        <v>75</v>
-      </c>
-      <c r="Z19" t="s">
-        <v>75</v>
-      </c>
-      <c r="AA19" t="s">
-        <v>81</v>
-      </c>
-      <c r="AB19" t="s">
-        <v>60</v>
-      </c>
-      <c r="AC19" t="s">
-        <v>81</v>
       </c>
       <c r="AD19" t="s">
         <v>60</v>
       </c>
       <c r="AE19" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="AF19" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AG19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH19" t="s">
         <v>104</v>
@@ -3917,7 +3911,7 @@
         <v>83</v>
       </c>
       <c r="AJ19" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AK19" t="s">
         <v>106</v>
@@ -3943,7 +3937,7 @@
         <v>102</v>
       </c>
       <c r="G20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H20" t="s">
         <v>78</v>
@@ -3952,76 +3946,76 @@
         <v>95</v>
       </c>
       <c r="J20" t="s">
+        <v>66</v>
+      </c>
+      <c r="K20" t="s">
+        <v>62</v>
+      </c>
+      <c r="L20" t="s">
         <v>95</v>
       </c>
-      <c r="K20" t="s">
-        <v>81</v>
-      </c>
-      <c r="L20" t="s">
+      <c r="M20" t="s">
         <v>103</v>
       </c>
-      <c r="M20" t="s">
-        <v>67</v>
-      </c>
       <c r="N20" t="s">
+        <v>95</v>
+      </c>
+      <c r="O20" t="s">
         <v>103</v>
       </c>
-      <c r="O20" t="s">
+      <c r="P20" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>82</v>
+      </c>
+      <c r="R20" t="s">
+        <v>82</v>
+      </c>
+      <c r="S20" t="s">
         <v>75</v>
-      </c>
-      <c r="P20" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>95</v>
-      </c>
-      <c r="R20" t="s">
-        <v>75</v>
-      </c>
-      <c r="S20" t="s">
-        <v>81</v>
       </c>
       <c r="T20" t="s">
         <v>62</v>
       </c>
       <c r="U20" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="V20" t="s">
+        <v>62</v>
+      </c>
+      <c r="W20" t="s">
         <v>75</v>
       </c>
-      <c r="W20" t="s">
-        <v>109</v>
-      </c>
       <c r="X20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Y20" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="Z20" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="AA20" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="AB20" t="s">
         <v>104</v>
       </c>
       <c r="AC20" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="AD20" t="s">
         <v>91</v>
       </c>
       <c r="AE20" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="AF20" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="AG20" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="AH20" t="s">
         <v>110</v>
@@ -4030,7 +4024,7 @@
         <v>96</v>
       </c>
       <c r="AJ20" t="s">
-        <v>110</v>
+        <v>69</v>
       </c>
       <c r="AK20" t="s">
         <v>112</v>
@@ -4038,10 +4032,10 @@
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>86</v>
+      </c>
+      <c r="B21" t="s">
         <v>98</v>
-      </c>
-      <c r="B21" t="s">
-        <v>86</v>
       </c>
       <c r="C21" t="s">
         <v>107</v>
@@ -4062,34 +4056,34 @@
         <v>95</v>
       </c>
       <c r="I21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J21" t="s">
+        <v>75</v>
+      </c>
+      <c r="K21" t="s">
+        <v>60</v>
+      </c>
+      <c r="L21" t="s">
         <v>103</v>
       </c>
-      <c r="K21" t="s">
+      <c r="M21" t="s">
+        <v>109</v>
+      </c>
+      <c r="N21" t="s">
+        <v>66</v>
+      </c>
+      <c r="O21" t="s">
+        <v>109</v>
+      </c>
+      <c r="P21" t="s">
         <v>62</v>
       </c>
-      <c r="L21" t="s">
-        <v>109</v>
-      </c>
-      <c r="M21" t="s">
-        <v>75</v>
-      </c>
-      <c r="N21" t="s">
-        <v>109</v>
-      </c>
-      <c r="O21" t="s">
+      <c r="Q21" t="s">
+        <v>60</v>
+      </c>
+      <c r="R21" t="s">
         <v>62</v>
-      </c>
-      <c r="P21" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>67</v>
-      </c>
-      <c r="R21" t="s">
-        <v>91</v>
       </c>
       <c r="S21" t="s">
         <v>62</v>
@@ -4098,25 +4092,25 @@
         <v>60</v>
       </c>
       <c r="U21" t="s">
+        <v>75</v>
+      </c>
+      <c r="V21" t="s">
         <v>60</v>
       </c>
-      <c r="V21" t="s">
+      <c r="W21" t="s">
+        <v>91</v>
+      </c>
+      <c r="X21" t="s">
         <v>62</v>
       </c>
-      <c r="W21" t="s">
-        <v>75</v>
-      </c>
-      <c r="X21" t="s">
-        <v>104</v>
-      </c>
       <c r="Y21" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="Z21" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="AA21" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="AB21" t="s">
         <v>100</v>
@@ -4128,13 +4122,13 @@
         <v>83</v>
       </c>
       <c r="AE21" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="AF21" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="AG21" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="AH21" t="s">
         <v>106</v>
@@ -4143,15 +4137,15 @@
         <v>92</v>
       </c>
       <c r="AJ21" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>98</v>
+      </c>
+      <c r="B22" t="s">
         <v>80</v>
-      </c>
-      <c r="B22" t="s">
-        <v>98</v>
       </c>
       <c r="C22" t="s">
         <v>76</v>
@@ -4163,7 +4157,7 @@
         <v>111</v>
       </c>
       <c r="F22" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G22" t="s">
         <v>75</v>
@@ -4175,76 +4169,76 @@
         <v>103</v>
       </c>
       <c r="J22" t="s">
+        <v>82</v>
+      </c>
+      <c r="K22" t="s">
+        <v>91</v>
+      </c>
+      <c r="L22" t="s">
         <v>75</v>
       </c>
-      <c r="K22" t="s">
+      <c r="M22" t="s">
         <v>60</v>
       </c>
-      <c r="L22" t="s">
-        <v>61</v>
-      </c>
-      <c r="M22" t="s">
-        <v>81</v>
-      </c>
       <c r="N22" t="s">
+        <v>103</v>
+      </c>
+      <c r="O22" t="s">
         <v>75</v>
       </c>
-      <c r="O22" t="s">
+      <c r="P22" t="s">
         <v>60</v>
       </c>
-      <c r="P22" t="s">
-        <v>62</v>
-      </c>
       <c r="Q22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R22" t="s">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="S22" t="s">
         <v>60</v>
       </c>
       <c r="T22" t="s">
+        <v>104</v>
+      </c>
+      <c r="U22" t="s">
+        <v>62</v>
+      </c>
+      <c r="V22" t="s">
         <v>91</v>
       </c>
-      <c r="U22" t="s">
+      <c r="W22" t="s">
         <v>104</v>
       </c>
-      <c r="V22" t="s">
+      <c r="X22" t="s">
         <v>60</v>
       </c>
-      <c r="W22" t="s">
-        <v>62</v>
-      </c>
-      <c r="X22" t="s">
+      <c r="Y22" t="s">
         <v>100</v>
       </c>
-      <c r="Y22" t="s">
-        <v>91</v>
-      </c>
       <c r="Z22" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>112</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC22" t="s">
         <v>100</v>
-      </c>
-      <c r="AA22" t="s">
-        <v>95</v>
-      </c>
-      <c r="AB22" t="s">
-        <v>96</v>
-      </c>
-      <c r="AC22" t="s">
-        <v>110</v>
       </c>
       <c r="AD22" t="s">
         <v>96</v>
       </c>
       <c r="AE22" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="AF22" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="AG22" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="AH22" t="s">
         <v>96</v>
@@ -4252,16 +4246,13 @@
       <c r="AI22" t="s">
         <v>112</v>
       </c>
-      <c r="AJ22" t="s">
-        <v>61</v>
-      </c>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>80</v>
+      </c>
+      <c r="B23" t="s">
         <v>87</v>
-      </c>
-      <c r="B23" t="s">
-        <v>80</v>
       </c>
       <c r="C23" t="s">
         <v>87</v>
@@ -4276,7 +4267,7 @@
         <v>103</v>
       </c>
       <c r="G23" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H23" t="s">
         <v>75</v>
@@ -4285,76 +4276,76 @@
         <v>62</v>
       </c>
       <c r="J23" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K23" t="s">
         <v>104</v>
       </c>
       <c r="L23" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M23" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="N23" t="s">
+        <v>113</v>
+      </c>
+      <c r="O23" t="s">
         <v>62</v>
       </c>
-      <c r="O23" t="s">
+      <c r="P23" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>100</v>
+      </c>
+      <c r="R23" t="s">
+        <v>104</v>
+      </c>
+      <c r="S23" t="s">
         <v>91</v>
       </c>
-      <c r="P23" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q23" t="s">
+      <c r="T23" t="s">
         <v>113</v>
-      </c>
-      <c r="R23" t="s">
-        <v>100</v>
-      </c>
-      <c r="S23" t="s">
-        <v>104</v>
-      </c>
-      <c r="T23" t="s">
-        <v>104</v>
       </c>
       <c r="U23" t="s">
         <v>100</v>
       </c>
       <c r="V23" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="W23" t="s">
         <v>100</v>
       </c>
       <c r="X23" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>83</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>96</v>
+      </c>
+      <c r="AC23" t="s">
         <v>106</v>
-      </c>
-      <c r="Y23" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z23" t="s">
-        <v>110</v>
-      </c>
-      <c r="AA23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB23" t="s">
-        <v>112</v>
-      </c>
-      <c r="AC23" t="s">
-        <v>92</v>
       </c>
       <c r="AD23" t="s">
         <v>112</v>
       </c>
       <c r="AE23" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="AF23" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AG23" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="AH23" t="s">
         <v>92</v>
@@ -4362,16 +4353,13 @@
       <c r="AI23" t="s">
         <v>69</v>
       </c>
-      <c r="AJ23" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>76</v>
+      </c>
+      <c r="B24" t="s">
         <v>105</v>
-      </c>
-      <c r="B24" t="s">
-        <v>76</v>
       </c>
       <c r="C24" t="s">
         <v>102</v>
@@ -4383,7 +4371,7 @@
         <v>113</v>
       </c>
       <c r="F24" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G24" t="s">
         <v>60</v>
@@ -4398,78 +4386,78 @@
         <v>104</v>
       </c>
       <c r="K24" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="L24" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="M24" t="s">
+        <v>82</v>
+      </c>
+      <c r="N24" t="s">
+        <v>110</v>
+      </c>
+      <c r="O24" t="s">
         <v>104</v>
       </c>
-      <c r="N24" t="s">
-        <v>104</v>
-      </c>
-      <c r="O24" t="s">
-        <v>100</v>
-      </c>
       <c r="P24" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="Q24" t="s">
         <v>110</v>
       </c>
       <c r="R24" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="S24" t="s">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="T24" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="U24" t="s">
         <v>110</v>
       </c>
       <c r="V24" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="W24" t="s">
         <v>110</v>
       </c>
       <c r="X24" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="Y24" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="Z24" t="s">
         <v>106</v>
       </c>
       <c r="AA24" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="AB24" t="s">
-        <v>69</v>
+        <v>112</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>92</v>
       </c>
       <c r="AD24" t="s">
         <v>69</v>
       </c>
       <c r="AE24" t="s">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="AF24" t="s">
-        <v>112</v>
-      </c>
-      <c r="AG24" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>87</v>
+      </c>
+      <c r="B25" t="s">
         <v>99</v>
-      </c>
-      <c r="B25" t="s">
-        <v>87</v>
       </c>
       <c r="C25" t="s">
         <v>95</v>
@@ -4493,78 +4481,75 @@
         <v>104</v>
       </c>
       <c r="J25" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="K25" t="s">
         <v>110</v>
       </c>
       <c r="L25" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="M25" t="s">
         <v>110</v>
       </c>
       <c r="N25" t="s">
+        <v>106</v>
+      </c>
+      <c r="O25" t="s">
         <v>83</v>
       </c>
-      <c r="O25" t="s">
+      <c r="P25" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>96</v>
+      </c>
+      <c r="R25" t="s">
         <v>110</v>
       </c>
-      <c r="P25" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q25" t="s">
+      <c r="S25" t="s">
+        <v>110</v>
+      </c>
+      <c r="T25" t="s">
+        <v>92</v>
+      </c>
+      <c r="U25" t="s">
         <v>106</v>
       </c>
-      <c r="R25" t="s">
+      <c r="V25" t="s">
+        <v>106</v>
+      </c>
+      <c r="W25" t="s">
         <v>83</v>
       </c>
-      <c r="S25" t="s">
-        <v>113</v>
-      </c>
-      <c r="T25" t="s">
+      <c r="X25" t="s">
         <v>110</v>
       </c>
-      <c r="U25" t="s">
-        <v>96</v>
-      </c>
-      <c r="V25" t="s">
-        <v>110</v>
-      </c>
-      <c r="W25" t="s">
-        <v>106</v>
-      </c>
       <c r="Y25" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="Z25" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="AA25" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AB25" t="s">
-        <v>61</v>
-      </c>
-      <c r="AE25" t="s">
-        <v>61</v>
-      </c>
-      <c r="AF25" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>99</v>
+      </c>
+      <c r="B26" t="s">
         <v>108</v>
-      </c>
-      <c r="B26" t="s">
-        <v>99</v>
       </c>
       <c r="C26" t="s">
         <v>111</v>
       </c>
       <c r="D26" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E26" t="s">
         <v>91</v>
@@ -4582,69 +4567,63 @@
         <v>114</v>
       </c>
       <c r="J26" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
       <c r="K26" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="L26" t="s">
         <v>110</v>
       </c>
       <c r="M26" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="N26" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="O26" t="s">
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="Q26" t="s">
+        <v>92</v>
+      </c>
+      <c r="R26" t="s">
+        <v>112</v>
+      </c>
+      <c r="S26" t="s">
+        <v>106</v>
+      </c>
+      <c r="T26" t="s">
+        <v>115</v>
+      </c>
+      <c r="U26" t="s">
         <v>96</v>
       </c>
-      <c r="R26" t="s">
+      <c r="V26" t="s">
+        <v>96</v>
+      </c>
+      <c r="W26" t="s">
         <v>92</v>
       </c>
-      <c r="S26" t="s">
-        <v>83</v>
-      </c>
-      <c r="T26" t="s">
-        <v>83</v>
-      </c>
-      <c r="U26" t="s">
-        <v>92</v>
-      </c>
-      <c r="V26" t="s">
+      <c r="X26" t="s">
         <v>106</v>
       </c>
-      <c r="W26" t="s">
-        <v>96</v>
-      </c>
       <c r="Y26" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Z26" t="s">
-        <v>97</v>
-      </c>
-      <c r="AA26" t="s">
-        <v>106</v>
-      </c>
-      <c r="AB26" t="s">
-        <v>62</v>
-      </c>
-      <c r="AE26" t="s">
-        <v>83</v>
+        <v>116</v>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>102</v>
+      </c>
+      <c r="B27" t="s">
         <v>95</v>
-      </c>
-      <c r="B27" t="s">
-        <v>102</v>
       </c>
       <c r="C27" t="s">
         <v>103</v>
@@ -4662,7 +4641,7 @@
         <v>110</v>
       </c>
       <c r="H27" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I27" t="s">
         <v>110</v>
@@ -4671,57 +4650,48 @@
         <v>106</v>
       </c>
       <c r="K27" t="s">
+        <v>96</v>
+      </c>
+      <c r="L27" t="s">
+        <v>106</v>
+      </c>
+      <c r="M27" t="s">
         <v>112</v>
       </c>
-      <c r="L27" t="s">
-        <v>97</v>
-      </c>
-      <c r="M27" t="s">
-        <v>106</v>
-      </c>
       <c r="N27" t="s">
+        <v>92</v>
+      </c>
+      <c r="O27" t="s">
         <v>96</v>
       </c>
-      <c r="O27" t="s">
-        <v>92</v>
-      </c>
       <c r="P27" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="Q27" t="s">
-        <v>92</v>
+        <v>112</v>
+      </c>
+      <c r="R27" t="s">
+        <v>88</v>
       </c>
       <c r="S27" t="s">
         <v>92</v>
       </c>
       <c r="T27" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="U27" t="s">
-        <v>112</v>
-      </c>
-      <c r="W27" t="s">
         <v>88</v>
       </c>
-      <c r="Y27" t="s">
+      <c r="V27" t="s">
         <v>92</v>
       </c>
-      <c r="AA27" t="s">
-        <v>115</v>
-      </c>
-      <c r="AB27" t="s">
-        <v>88</v>
-      </c>
-      <c r="AE27" t="s">
-        <v>61</v>
-      </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>95</v>
+      </c>
+      <c r="B28" t="s">
         <v>111</v>
-      </c>
-      <c r="B28" t="s">
-        <v>95</v>
       </c>
       <c r="C28" t="s">
         <v>113</v>
@@ -4733,7 +4703,7 @@
         <v>114</v>
       </c>
       <c r="F28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G28" t="s">
         <v>83</v>
@@ -4745,48 +4715,39 @@
         <v>106</v>
       </c>
       <c r="J28" t="s">
+        <v>92</v>
+      </c>
+      <c r="K28" t="s">
+        <v>92</v>
+      </c>
+      <c r="L28" t="s">
         <v>96</v>
       </c>
-      <c r="K28" t="s">
-        <v>88</v>
-      </c>
-      <c r="L28" t="s">
-        <v>112</v>
-      </c>
       <c r="M28" t="s">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="N28" t="s">
         <v>112</v>
       </c>
+      <c r="O28" t="s">
+        <v>112</v>
+      </c>
       <c r="P28" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="Q28" t="s">
-        <v>112</v>
-      </c>
-      <c r="S28" t="s">
-        <v>115</v>
+        <v>69</v>
       </c>
       <c r="T28" t="s">
-        <v>92</v>
-      </c>
-      <c r="U28" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA28" t="s">
-        <v>116</v>
-      </c>
-      <c r="AE28" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B29" t="s">
-        <v>67</v>
+        <v>109</v>
       </c>
       <c r="C29" t="s">
         <v>109</v>
@@ -4810,36 +4771,30 @@
         <v>92</v>
       </c>
       <c r="J29" t="s">
+        <v>97</v>
+      </c>
+      <c r="K29" t="s">
+        <v>97</v>
+      </c>
+      <c r="L29" t="s">
         <v>112</v>
       </c>
-      <c r="L29" t="s">
+      <c r="M29" t="s">
+        <v>88</v>
+      </c>
+      <c r="N29" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>103</v>
+      </c>
+      <c r="B30" t="s">
         <v>61</v>
       </c>
-      <c r="M29" t="s">
-        <v>97</v>
-      </c>
-      <c r="P29" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>88</v>
-      </c>
-      <c r="S29" t="s">
-        <v>116</v>
-      </c>
-      <c r="T29" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>109</v>
-      </c>
-      <c r="B30" t="s">
-        <v>103</v>
-      </c>
       <c r="C30" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="D30" t="s">
         <v>100</v>
@@ -4859,28 +4814,22 @@
       <c r="I30" t="s">
         <v>112</v>
       </c>
-      <c r="L30" t="s">
-        <v>62</v>
-      </c>
-      <c r="M30" t="s">
+      <c r="J30" t="s">
         <v>112</v>
       </c>
-      <c r="P30" t="s">
-        <v>116</v>
-      </c>
-      <c r="T30" t="s">
+      <c r="K30" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="B31" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="C31" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D31" t="s">
         <v>95</v>
@@ -4897,16 +4846,13 @@
       <c r="H31" t="s">
         <v>106</v>
       </c>
-      <c r="L31" t="s">
-        <v>88</v>
-      </c>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="B32" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="C32" t="s">
         <v>62</v>
@@ -4926,10 +4872,10 @@
     </row>
     <row r="33" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="B33" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="C33" t="s">
         <v>60</v>
@@ -4946,10 +4892,10 @@
     </row>
     <row r="34" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B34" t="s">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="C34" t="s">
         <v>91</v>
@@ -4960,10 +4906,10 @@
     </row>
     <row r="35" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="B35" t="s">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="C35" t="s">
         <v>104</v>
@@ -4974,10 +4920,10 @@
     </row>
     <row r="36" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="B36" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="C36" t="s">
         <v>100</v>
@@ -4988,10 +4934,10 @@
     </row>
     <row r="37" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B37" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="C37" t="s">
         <v>110</v>
@@ -5002,10 +4948,10 @@
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="B38" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C38" t="s">
         <v>83</v>
@@ -5016,10 +4962,10 @@
     </row>
     <row r="39" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="B39" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C39" t="s">
         <v>106</v>
@@ -5030,10 +4976,10 @@
     </row>
     <row r="40" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="B40" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="C40" t="s">
         <v>96</v>
@@ -5044,10 +4990,10 @@
     </row>
     <row r="41" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B41" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="C41" t="s">
         <v>92</v>
@@ -5055,10 +5001,10 @@
     </row>
     <row r="42" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="B42" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="C42" t="s">
         <v>97</v>
@@ -5066,10 +5012,10 @@
     </row>
     <row r="43" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="B43" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C43" t="s">
         <v>112</v>
@@ -5077,10 +5023,10 @@
     </row>
     <row r="44" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B44" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="C44" t="s">
         <v>115</v>
@@ -5088,10 +5034,10 @@
     </row>
     <row r="45" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="B45" t="s">
-        <v>69</v>
+        <v>112</v>
       </c>
       <c r="C45" t="s">
         <v>88</v>
@@ -5099,18 +5045,11 @@
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>92</v>
-      </c>
-      <c r="B46" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="47" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="48" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="49" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="50" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="51" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5243,16 +5182,16 @@
         <v>51</v>
       </c>
       <c r="B3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" t="s">
         <v>55</v>
-      </c>
-      <c r="C3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" t="s">
-        <v>54</v>
       </c>
       <c r="F3" t="s">
         <v>57</v>
@@ -5267,7 +5206,7 @@
         <v>70</v>
       </c>
       <c r="J3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K3" t="s">
         <v>71</v>
@@ -5330,7 +5269,7 @@
         <v>86</v>
       </c>
       <c r="AE3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AF3" t="s">
         <v>98</v>
@@ -5366,7 +5305,7 @@
         <v>111</v>
       </c>
       <c r="AQ3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AR3" t="s">
         <v>103</v>
@@ -5381,7 +5320,7 @@
         <v>75</v>
       </c>
       <c r="AV3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AW3" t="s">
         <v>62</v>
@@ -5446,43 +5385,43 @@
         <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="s">
         <v>117</v>
       </c>
       <c r="I4" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="s">
         <v>2</v>
       </c>
       <c r="K4" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="s">
         <v>36</v>
       </c>
       <c r="M4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N4" t="s">
         <v>117</v>
       </c>
       <c r="O4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Q4" t="s">
         <v>2</v>
@@ -5500,7 +5439,7 @@
         <v>117</v>
       </c>
       <c r="V4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W4" t="s">
         <v>5</v>
@@ -5518,7 +5457,7 @@
         <v>40</v>
       </c>
       <c r="AB4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AC4" t="s">
         <v>2</v>
@@ -5527,37 +5466,37 @@
         <v>2</v>
       </c>
       <c r="AE4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG4" t="s">
         <v>2</v>
       </c>
       <c r="AH4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ4" t="s">
         <v>2</v>
       </c>
       <c r="AK4" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL4" t="s">
+        <v>12</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN4" t="s">
         <v>11</v>
       </c>
-      <c r="AM4" t="s">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="s">
-        <v>9</v>
-      </c>
       <c r="AO4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP4" t="s">
         <v>2</v>
@@ -5566,19 +5505,19 @@
         <v>40</v>
       </c>
       <c r="AR4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS4" t="s">
         <v>2</v>
       </c>
       <c r="AT4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AU4" t="s">
         <v>6</v>
       </c>
       <c r="AV4" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="s">
         <v>50</v>
@@ -5593,10 +5532,10 @@
         <v>5</v>
       </c>
       <c r="BA4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BB4" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC4" t="s">
         <v>3</v>
@@ -5608,28 +5547,28 @@
         <v>33</v>
       </c>
       <c r="BF4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BG4" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BH4" t="s">
         <v>6</v>
       </c>
       <c r="BI4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BJ4" t="s">
         <v>48</v>
       </c>
       <c r="BK4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BL4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BM4" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
@@ -5637,13 +5576,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
@@ -5655,7 +5594,7 @@
         <v>35</v>
       </c>
       <c r="H5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I5" t="s">
         <v>3</v>
@@ -5664,19 +5603,19 @@
         <v>35</v>
       </c>
       <c r="K5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="M5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N5" t="s">
         <v>34</v>
       </c>
       <c r="O5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P5" t="s">
         <v>6</v>
@@ -5688,19 +5627,19 @@
         <v>3</v>
       </c>
       <c r="S5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T5" t="s">
+        <v>1</v>
+      </c>
+      <c r="U5" t="s">
         <v>0</v>
-      </c>
-      <c r="U5" t="s">
-        <v>1</v>
       </c>
       <c r="V5" t="s">
         <v>3</v>
       </c>
       <c r="W5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X5" t="s">
         <v>6</v>
@@ -5712,7 +5651,7 @@
         <v>3</v>
       </c>
       <c r="AA5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AB5" t="s">
         <v>35</v>
@@ -5727,46 +5666,46 @@
         <v>7</v>
       </c>
       <c r="AF5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="s">
         <v>3</v>
       </c>
       <c r="AH5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="s">
         <v>2</v>
       </c>
       <c r="AJ5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL5" t="s">
         <v>0</v>
-      </c>
-      <c r="AK5" t="s">
-        <v>9</v>
-      </c>
-      <c r="AL5" t="s">
-        <v>1</v>
       </c>
       <c r="AM5" t="s">
         <v>3</v>
       </c>
       <c r="AN5" t="s">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="s">
         <v>1</v>
       </c>
-      <c r="AO5" t="s">
-        <v>1</v>
-      </c>
-      <c r="AP5" t="s">
+      <c r="AQ5" t="s">
         <v>0</v>
       </c>
-      <c r="AQ5" t="s">
-        <v>1</v>
-      </c>
       <c r="AR5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AS5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="s">
         <v>6</v>
@@ -5781,19 +5720,19 @@
         <v>2</v>
       </c>
       <c r="AX5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY5" t="s">
         <v>3</v>
       </c>
       <c r="AZ5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC5" t="s">
         <v>7</v>
@@ -5811,10 +5750,10 @@
         <v>3</v>
       </c>
       <c r="BH5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BI5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="s">
         <v>35</v>
@@ -5826,57 +5765,57 @@
         <v>3</v>
       </c>
       <c r="BM5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
         <v>26</v>
       </c>
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F6" t="s">
         <v>30</v>
       </c>
       <c r="G6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H6" t="s">
         <v>38</v>
       </c>
       <c r="I6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J6" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="K6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="M6" t="s">
         <v>38</v>
       </c>
       <c r="N6" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="O6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P6" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="Q6" t="s">
         <v>8</v>
@@ -5885,25 +5824,25 @@
         <v>38</v>
       </c>
       <c r="S6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T6" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="U6" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="V6" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="W6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X6" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="Y6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Z6" t="s">
         <v>30</v>
@@ -5912,31 +5851,31 @@
         <v>30</v>
       </c>
       <c r="AB6" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>20</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>17</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>18</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>18</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>18</v>
+      </c>
+      <c r="AJ6" t="s">
         <v>26</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>14</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>14</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>26</v>
-      </c>
-      <c r="AH6" t="s">
-        <v>26</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>27</v>
       </c>
       <c r="AK6" t="s">
         <v>8</v>
@@ -5945,85 +5884,85 @@
         <v>30</v>
       </c>
       <c r="AM6" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AN6" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AO6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AP6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AQ6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AR6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AT6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AU6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AV6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW6" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AX6" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AY6" t="s">
         <v>30</v>
       </c>
       <c r="AZ6" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="BA6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BB6" t="s">
         <v>8</v>
       </c>
       <c r="BC6" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="BD6" t="s">
         <v>30</v>
       </c>
       <c r="BE6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BF6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BG6" t="s">
         <v>30</v>
       </c>
       <c r="BH6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BI6" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="BJ6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BK6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BL6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BM6" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
@@ -6031,10 +5970,10 @@
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
         <v>37</v>
@@ -6046,16 +5985,16 @@
         <v>39</v>
       </c>
       <c r="G7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H7" t="s">
         <v>30</v>
       </c>
       <c r="I7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K7" t="s">
         <v>15</v>
@@ -6064,16 +6003,16 @@
         <v>37</v>
       </c>
       <c r="M7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="N7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="O7" t="s">
         <v>15</v>
       </c>
       <c r="P7" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="Q7" t="s">
         <v>41</v>
@@ -6085,7 +6024,7 @@
         <v>15</v>
       </c>
       <c r="T7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="U7" t="s">
         <v>30</v>
@@ -6100,19 +6039,19 @@
         <v>4</v>
       </c>
       <c r="Y7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="Z7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AA7" t="s">
         <v>39</v>
       </c>
       <c r="AB7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="AC7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="AD7" t="s">
         <v>29</v>
@@ -6130,10 +6069,10 @@
         <v>15</v>
       </c>
       <c r="AI7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="AK7" t="s">
         <v>4</v>
@@ -6142,7 +6081,7 @@
         <v>37</v>
       </c>
       <c r="AM7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AN7" t="s">
         <v>29</v>
@@ -6154,7 +6093,7 @@
         <v>4</v>
       </c>
       <c r="AQ7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AR7" t="s">
         <v>15</v>
@@ -6166,7 +6105,7 @@
         <v>29</v>
       </c>
       <c r="AU7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AV7" t="s">
         <v>15</v>
@@ -6181,19 +6120,19 @@
         <v>41</v>
       </c>
       <c r="AZ7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BA7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB7" t="s">
         <v>4</v>
       </c>
       <c r="BC7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BD7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="BE7" t="s">
         <v>15</v>
@@ -6205,13 +6144,13 @@
         <v>4</v>
       </c>
       <c r="BH7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BI7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BJ7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="BK7" t="s">
         <v>15</v>
@@ -6220,7 +6159,7 @@
         <v>15</v>
       </c>
       <c r="BM7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
@@ -6228,25 +6167,25 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E8" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G8" t="s">
         <v>6</v>
       </c>
       <c r="H8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L8" t="s">
         <v>40</v>
@@ -6255,13 +6194,13 @@
         <v>35</v>
       </c>
       <c r="O8" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Q8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T8" t="s">
         <v>5</v>
@@ -6273,25 +6212,25 @@
         <v>35</v>
       </c>
       <c r="X8" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="Y8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AC8" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AE8" t="s">
         <v>43</v>
@@ -6300,10 +6239,10 @@
         <v>5</v>
       </c>
       <c r="AH8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI8" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AJ8" t="s">
         <v>36</v>
@@ -6312,13 +6251,13 @@
         <v>36</v>
       </c>
       <c r="AL8" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AN8" t="s">
         <v>5</v>
       </c>
       <c r="AO8" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AQ8" t="s">
         <v>6</v>
@@ -6327,28 +6266,28 @@
         <v>34</v>
       </c>
       <c r="AS8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU8" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="AV8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW8" t="s">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="s">
+        <v>19</v>
+      </c>
+      <c r="AY8" t="s">
         <v>1</v>
       </c>
-      <c r="AX8" t="s">
-        <v>18</v>
-      </c>
-      <c r="AY8" t="s">
-        <v>0</v>
-      </c>
       <c r="AZ8" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA8" t="s">
         <v>5</v>
@@ -6360,13 +6299,13 @@
         <v>43</v>
       </c>
       <c r="BE8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BF8" t="s">
         <v>34</v>
       </c>
       <c r="BG8" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BH8" t="s">
         <v>2</v>
@@ -6375,7 +6314,7 @@
         <v>36</v>
       </c>
       <c r="BJ8" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="s">
         <v>2</v>
@@ -6383,28 +6322,28 @@
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="s">
         <v>35</v>
       </c>
       <c r="F9" t="s">
+        <v>0</v>
+      </c>
+      <c r="G9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" t="s">
         <v>1</v>
       </c>
-      <c r="G9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" t="s">
-        <v>0</v>
-      </c>
       <c r="J9" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L9" t="s">
         <v>2</v>
@@ -6416,16 +6355,16 @@
         <v>6</v>
       </c>
       <c r="Q9" t="s">
+        <v>0</v>
+      </c>
+      <c r="R9" t="s">
         <v>1</v>
       </c>
-      <c r="R9" t="s">
-        <v>0</v>
-      </c>
       <c r="T9" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="V9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="W9" t="s">
         <v>3</v>
@@ -6440,16 +6379,16 @@
         <v>6</v>
       </c>
       <c r="AA9" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="s">
         <v>7</v>
       </c>
       <c r="AC9" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE9" t="s">
         <v>33</v>
@@ -6461,7 +6400,7 @@
         <v>35</v>
       </c>
       <c r="AI9" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="s">
         <v>35</v>
@@ -6470,28 +6409,28 @@
         <v>35</v>
       </c>
       <c r="AL9" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AN9" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AO9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AQ9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR9" t="s">
         <v>2</v>
       </c>
       <c r="AS9" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT9" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU9" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AV9" t="s">
         <v>36</v>
@@ -6500,25 +6439,25 @@
         <v>7</v>
       </c>
       <c r="AX9" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY9" t="s">
         <v>7</v>
       </c>
       <c r="AZ9" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="BA9" t="s">
         <v>35</v>
       </c>
       <c r="BC9" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BD9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BE9" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="s">
         <v>6</v>
@@ -6530,135 +6469,135 @@
         <v>3</v>
       </c>
       <c r="BI9" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BJ9" t="s">
         <v>3</v>
       </c>
       <c r="BM9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G10" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" t="s">
         <v>20</v>
       </c>
-      <c r="H10" t="s">
-        <v>22</v>
-      </c>
       <c r="J10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L10" t="s">
         <v>45</v>
       </c>
       <c r="M10" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="O10" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="Q10" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="R10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T10" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="V10" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="W10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="X10" t="s">
         <v>8</v>
       </c>
       <c r="Y10" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>20</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>22</v>
+      </c>
+      <c r="AF10" t="s">
         <v>26</v>
       </c>
-      <c r="Z10" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>22</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>22</v>
-      </c>
-      <c r="AE10" t="s">
+      <c r="AH10" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>20</v>
+      </c>
+      <c r="AJ10" t="s">
         <v>17</v>
       </c>
-      <c r="AF10" t="s">
-        <v>27</v>
-      </c>
-      <c r="AH10" t="s">
-        <v>32</v>
-      </c>
-      <c r="AI10" t="s">
-        <v>22</v>
-      </c>
-      <c r="AJ10" t="s">
-        <v>10</v>
-      </c>
       <c r="AK10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL10" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AN10" t="s">
         <v>30</v>
       </c>
       <c r="AO10" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AQ10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AR10" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AS10" t="s">
+        <v>25</v>
+      </c>
+      <c r="AT10" t="s">
         <v>26</v>
       </c>
-      <c r="AT10" t="s">
-        <v>27</v>
-      </c>
       <c r="AU10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AV10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AW10" t="s">
         <v>38</v>
       </c>
       <c r="AX10" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AY10" t="s">
         <v>8</v>
@@ -6667,34 +6606,34 @@
         <v>8</v>
       </c>
       <c r="BA10" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="BC10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BD10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BE10" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="BF10" t="s">
+        <v>16</v>
+      </c>
+      <c r="BG10" t="s">
+        <v>42</v>
+      </c>
+      <c r="BH10" t="s">
+        <v>42</v>
+      </c>
+      <c r="BI10" t="s">
+        <v>31</v>
+      </c>
+      <c r="BJ10" t="s">
+        <v>31</v>
+      </c>
+      <c r="BM10" t="s">
         <v>20</v>
-      </c>
-      <c r="BG10" t="s">
-        <v>44</v>
-      </c>
-      <c r="BH10" t="s">
-        <v>44</v>
-      </c>
-      <c r="BI10" t="s">
-        <v>32</v>
-      </c>
-      <c r="BJ10" t="s">
-        <v>32</v>
-      </c>
-      <c r="BM10" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
@@ -6702,10 +6641,10 @@
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F11" t="s">
         <v>4</v>
@@ -6720,31 +6659,31 @@
         <v>15</v>
       </c>
       <c r="K11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L11" t="s">
         <v>15</v>
       </c>
       <c r="M11" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="O11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q11" t="s">
         <v>30</v>
       </c>
       <c r="R11" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="T11" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="V11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="W11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="X11" t="s">
         <v>45</v>
@@ -6756,25 +6695,25 @@
         <v>15</v>
       </c>
       <c r="AA11" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="AB11" t="s">
         <v>4</v>
       </c>
       <c r="AC11" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AD11" t="s">
         <v>38</v>
       </c>
       <c r="AE11" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AF11" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="AH11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI11" t="s">
         <v>45</v>
@@ -6783,7 +6722,7 @@
         <v>29</v>
       </c>
       <c r="AK11" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AL11" t="s">
         <v>29</v>
@@ -6792,7 +6731,7 @@
         <v>37</v>
       </c>
       <c r="AO11" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AQ11" t="s">
         <v>39</v>
@@ -6804,13 +6743,13 @@
         <v>15</v>
       </c>
       <c r="AT11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AU11" t="s">
         <v>15</v>
       </c>
       <c r="AV11" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="AW11" t="s">
         <v>4</v>
@@ -6822,16 +6761,16 @@
         <v>4</v>
       </c>
       <c r="AZ11" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="BA11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC11" t="s">
         <v>37</v>
       </c>
       <c r="BD11" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="BE11" t="s">
         <v>4</v>
@@ -6840,10 +6779,10 @@
         <v>41</v>
       </c>
       <c r="BG11" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="BH11" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="BI11" t="s">
         <v>29</v>
@@ -6852,12 +6791,12 @@
         <v>29</v>
       </c>
       <c r="BM11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
@@ -6869,37 +6808,37 @@
         <v>2</v>
       </c>
       <c r="H12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K12" t="s">
+        <v>32</v>
+      </c>
+      <c r="M12" t="s">
+        <v>32</v>
+      </c>
+      <c r="O12" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>11</v>
+      </c>
+      <c r="R12" t="s">
         <v>28</v>
-      </c>
-      <c r="M12" t="s">
-        <v>28</v>
-      </c>
-      <c r="O12" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>9</v>
-      </c>
-      <c r="R12" t="s">
-        <v>23</v>
       </c>
       <c r="T12" t="s">
         <v>117</v>
       </c>
       <c r="V12" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W12" t="s">
         <v>2</v>
       </c>
       <c r="X12" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z12" t="s">
         <v>5</v>
@@ -6911,31 +6850,31 @@
         <v>5</v>
       </c>
       <c r="AD12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AE12" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AF12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI12" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AJ12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK12" t="s">
         <v>33</v>
       </c>
       <c r="AL12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AN12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO12" t="s">
         <v>34</v>
@@ -6944,19 +6883,19 @@
         <v>33</v>
       </c>
       <c r="AR12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT12" t="s">
         <v>2</v>
       </c>
       <c r="AU12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV12" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AW12" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AX12" t="s">
         <v>5</v>
@@ -6965,22 +6904,22 @@
         <v>36</v>
       </c>
       <c r="AZ12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA12" t="s">
         <v>36</v>
       </c>
       <c r="BC12" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="s">
         <v>40</v>
       </c>
       <c r="BE12" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BF12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BG12" t="s">
         <v>5</v>
@@ -6997,13 +6936,13 @@
         <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" t="s">
         <v>11</v>
-      </c>
-      <c r="F13" t="s">
-        <v>9</v>
       </c>
       <c r="H13" t="s">
         <v>36</v>
@@ -7024,67 +6963,67 @@
         <v>35</v>
       </c>
       <c r="R13" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V13" t="s">
         <v>7</v>
       </c>
       <c r="W13" t="s">
+        <v>1</v>
+      </c>
+      <c r="X13" t="s">
         <v>0</v>
       </c>
-      <c r="X13" t="s">
+      <c r="Z13" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF13" t="s">
         <v>1</v>
       </c>
-      <c r="Z13" t="s">
+      <c r="AH13" t="s">
         <v>1</v>
       </c>
-      <c r="AA13" t="s">
-        <v>24</v>
-      </c>
-      <c r="AB13" t="s">
-        <v>23</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE13" t="s">
-        <v>24</v>
-      </c>
-      <c r="AF13" t="s">
+      <c r="AI13" t="s">
+        <v>11</v>
+      </c>
+      <c r="AJ13" t="s">
         <v>0</v>
-      </c>
-      <c r="AH13" t="s">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ13" t="s">
-        <v>1</v>
       </c>
       <c r="AK13" t="s">
         <v>7</v>
       </c>
       <c r="AL13" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN13" t="s">
         <v>2</v>
       </c>
       <c r="AO13" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AQ13" t="s">
         <v>7</v>
       </c>
       <c r="AR13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU13" t="s">
         <v>7</v>
@@ -7093,7 +7032,7 @@
         <v>43</v>
       </c>
       <c r="AW13" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AX13" t="s">
         <v>35</v>
@@ -7102,10 +7041,10 @@
         <v>35</v>
       </c>
       <c r="AZ13" t="s">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="s">
         <v>1</v>
-      </c>
-      <c r="BA13" t="s">
-        <v>0</v>
       </c>
       <c r="BC13" t="s">
         <v>35</v>
@@ -7123,7 +7062,7 @@
         <v>2</v>
       </c>
       <c r="BI13" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ13" t="s">
         <v>34</v>
@@ -7134,118 +7073,118 @@
         <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J14" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K14" t="s">
         <v>30</v>
       </c>
       <c r="M14" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="O14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q14" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="R14" t="s">
         <v>8</v>
       </c>
       <c r="T14" t="s">
+        <v>22</v>
+      </c>
+      <c r="V14" t="s">
+        <v>18</v>
+      </c>
+      <c r="W14" t="s">
+        <v>24</v>
+      </c>
+      <c r="X14" t="s">
         <v>17</v>
-      </c>
-      <c r="V14" t="s">
-        <v>14</v>
-      </c>
-      <c r="W14" t="s">
-        <v>25</v>
-      </c>
-      <c r="X14" t="s">
-        <v>10</v>
       </c>
       <c r="Z14" t="s">
         <v>38</v>
       </c>
       <c r="AA14" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AB14" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AD14" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AE14" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AF14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AH14" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AI14" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AJ14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AK14" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AL14" t="s">
         <v>8</v>
       </c>
       <c r="AN14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AO14" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AQ14" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AR14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AT14" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AU14" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AV14" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AW14" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AX14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY14" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AZ14" t="s">
         <v>15</v>
       </c>
       <c r="BA14" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="BC14" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="BD14" t="s">
         <v>39</v>
@@ -7254,16 +7193,16 @@
         <v>30</v>
       </c>
       <c r="BF14" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BG14" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BI14" t="s">
         <v>8</v>
       </c>
       <c r="BJ14" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:62" x14ac:dyDescent="0.25">
@@ -7280,25 +7219,25 @@
         <v>37</v>
       </c>
       <c r="H15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J15" t="s">
         <v>8</v>
       </c>
       <c r="K15" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M15" t="s">
         <v>41</v>
       </c>
       <c r="O15" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="Q15" t="s">
         <v>38</v>
       </c>
       <c r="R15" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="T15" t="s">
         <v>39</v>
@@ -7313,19 +7252,19 @@
         <v>30</v>
       </c>
       <c r="Z15" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AA15" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AB15" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AD15" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF15" t="s">
         <v>8</v>
@@ -7340,72 +7279,72 @@
         <v>15</v>
       </c>
       <c r="AK15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL15" t="s">
         <v>4</v>
       </c>
       <c r="AN15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO15" t="s">
         <v>38</v>
       </c>
       <c r="AQ15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR15" t="s">
         <v>29</v>
       </c>
       <c r="AT15" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AU15" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AV15" t="s">
         <v>37</v>
       </c>
       <c r="AW15" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AX15" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="AY15" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="AZ15" t="s">
+        <v>26</v>
+      </c>
+      <c r="BA15" t="s">
         <v>27</v>
       </c>
-      <c r="BA15" t="s">
-        <v>31</v>
-      </c>
       <c r="BC15" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BD15" t="s">
         <v>29</v>
       </c>
       <c r="BE15" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BF15" t="s">
         <v>38</v>
       </c>
       <c r="BG15" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BI15" t="s">
         <v>4</v>
       </c>
       <c r="BJ15" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C16" t="s">
         <v>43</v>
@@ -7414,22 +7353,22 @@
         <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H16" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J16" t="s">
         <v>5</v>
       </c>
       <c r="K16" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M16" t="s">
         <v>5</v>
       </c>
       <c r="O16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q16" t="s">
         <v>34</v>
@@ -7438,19 +7377,19 @@
         <v>117</v>
       </c>
       <c r="T16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="V16" t="s">
         <v>36</v>
       </c>
       <c r="X16" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z16" t="s">
         <v>28</v>
       </c>
-      <c r="Z16" t="s">
-        <v>23</v>
-      </c>
       <c r="AA16" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB16" t="s">
         <v>2</v>
@@ -7474,7 +7413,7 @@
         <v>5</v>
       </c>
       <c r="AN16" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO16" t="s">
         <v>2</v>
@@ -7483,16 +7422,16 @@
         <v>36</v>
       </c>
       <c r="AR16" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="s">
         <v>34</v>
       </c>
       <c r="AV16" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX16" t="s">
         <v>6</v>
@@ -7501,25 +7440,25 @@
         <v>2</v>
       </c>
       <c r="AZ16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA16" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="BC16" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BD16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BE16" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF16" t="s">
         <v>33</v>
       </c>
       <c r="BG16" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="BI16" t="s">
         <v>2</v>
@@ -7527,7 +7466,7 @@
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17" t="s">
         <v>34</v>
@@ -7542,7 +7481,7 @@
         <v>43</v>
       </c>
       <c r="J17" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="K17" t="s">
         <v>7</v>
@@ -7554,10 +7493,10 @@
         <v>7</v>
       </c>
       <c r="Q17" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T17" t="s">
         <v>40</v>
@@ -7566,10 +7505,10 @@
         <v>2</v>
       </c>
       <c r="X17" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z17" t="s">
         <v>11</v>
-      </c>
-      <c r="Z17" t="s">
-        <v>9</v>
       </c>
       <c r="AA17" t="s">
         <v>7</v>
@@ -7581,7 +7520,7 @@
         <v>36</v>
       </c>
       <c r="AE17" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AF17" t="s">
         <v>2</v>
@@ -7593,108 +7532,108 @@
         <v>7</v>
       </c>
       <c r="AJ17" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AN17" t="s">
         <v>7</v>
       </c>
       <c r="AO17" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ17" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AR17" t="s">
         <v>7</v>
       </c>
       <c r="AU17" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AV17" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AW17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX17" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AY17" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="s">
         <v>3</v>
       </c>
       <c r="BA17" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="BC17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD17" t="s">
         <v>3</v>
       </c>
       <c r="BE17" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BF17" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C18" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" t="s">
         <v>17</v>
       </c>
-      <c r="E18" t="s">
-        <v>14</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="H18" t="s">
+        <v>22</v>
+      </c>
+      <c r="J18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K18" t="s">
         <v>10</v>
       </c>
-      <c r="H18" t="s">
-        <v>17</v>
-      </c>
-      <c r="J18" t="s">
-        <v>25</v>
-      </c>
-      <c r="K18" t="s">
-        <v>19</v>
-      </c>
       <c r="M18" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="O18" t="s">
         <v>37</v>
       </c>
       <c r="Q18" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R18" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="T18" t="s">
+        <v>25</v>
+      </c>
+      <c r="V18" t="s">
         <v>26</v>
       </c>
-      <c r="V18" t="s">
-        <v>27</v>
-      </c>
       <c r="X18" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z18" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AA18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB18" t="s">
         <v>15</v>
@@ -7706,7 +7645,7 @@
         <v>8</v>
       </c>
       <c r="AF18" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AH18" t="s">
         <v>8</v>
@@ -7715,58 +7654,58 @@
         <v>8</v>
       </c>
       <c r="AJ18" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AN18" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AO18" t="s">
         <v>30</v>
       </c>
       <c r="AQ18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR18" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AU18" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AV18" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AW18" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AX18" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AY18" t="s">
         <v>39</v>
       </c>
       <c r="AZ18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA18" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="BC18" t="s">
+        <v>24</v>
+      </c>
+      <c r="BD18" t="s">
         <v>25</v>
       </c>
-      <c r="BD18" t="s">
-        <v>26</v>
-      </c>
       <c r="BE18" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BF18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="BG18" t="s">
         <v>8</v>
       </c>
       <c r="BI18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" spans="1:61" x14ac:dyDescent="0.25">
@@ -7777,22 +7716,22 @@
         <v>29</v>
       </c>
       <c r="E19" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H19" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J19" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K19" t="s">
         <v>4</v>
       </c>
       <c r="M19" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="O19" t="s">
         <v>29</v>
@@ -7801,13 +7740,13 @@
         <v>4</v>
       </c>
       <c r="R19" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="T19" t="s">
         <v>29</v>
       </c>
       <c r="V19" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="X19" t="s">
         <v>29</v>
@@ -7822,37 +7761,37 @@
         <v>38</v>
       </c>
       <c r="AD19" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE19" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AF19" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AH19" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AI19" t="s">
         <v>4</v>
       </c>
       <c r="AJ19" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AN19" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AO19" t="s">
         <v>4</v>
       </c>
       <c r="AQ19" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="AR19" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AU19" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AV19" t="s">
         <v>30</v>
@@ -7861,7 +7800,7 @@
         <v>15</v>
       </c>
       <c r="AX19" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AY19" t="s">
         <v>29</v>
@@ -7870,10 +7809,10 @@
         <v>39</v>
       </c>
       <c r="BA19" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BC19" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BD19" t="s">
         <v>15</v>
@@ -7885,15 +7824,15 @@
         <v>30</v>
       </c>
       <c r="BG19" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BI19" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C20" t="s">
         <v>3</v>
@@ -7908,7 +7847,7 @@
         <v>34</v>
       </c>
       <c r="K20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O20" t="s">
         <v>34</v>
@@ -7923,22 +7862,22 @@
         <v>6</v>
       </c>
       <c r="X20" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA20" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AB20" t="s">
         <v>40</v>
       </c>
       <c r="AF20" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AH20" t="s">
         <v>33</v>
       </c>
       <c r="AI20" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AJ20" t="s">
         <v>34</v>
@@ -7952,23 +7891,20 @@
       <c r="AR20" t="s">
         <v>5</v>
       </c>
-      <c r="AU20" t="s">
-        <v>2</v>
-      </c>
       <c r="AV20" t="s">
         <v>6</v>
       </c>
       <c r="AW20" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX20" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY20" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AZ20" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BA20" t="s">
         <v>33</v>
@@ -7977,7 +7913,7 @@
         <v>33</v>
       </c>
       <c r="BD20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BE20" t="s">
         <v>36</v>
@@ -7986,7 +7922,7 @@
         <v>5</v>
       </c>
       <c r="BG20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BI20" t="s">
         <v>34</v>
@@ -8000,28 +7936,28 @@
         <v>7</v>
       </c>
       <c r="E21" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F21" t="s">
+        <v>1</v>
+      </c>
+      <c r="H21" t="s">
         <v>0</v>
       </c>
-      <c r="H21" t="s">
+      <c r="K21" t="s">
+        <v>0</v>
+      </c>
+      <c r="O21" t="s">
         <v>1</v>
       </c>
-      <c r="K21" t="s">
-        <v>1</v>
-      </c>
-      <c r="O21" t="s">
-        <v>0</v>
-      </c>
       <c r="Q21" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="R21" t="s">
         <v>7</v>
       </c>
       <c r="T21" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="X21" t="s">
         <v>7</v>
@@ -8033,16 +7969,16 @@
         <v>6</v>
       </c>
       <c r="AF21" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AH21" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI21" t="s">
         <v>3</v>
       </c>
       <c r="AJ21" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AO21" t="s">
         <v>7</v>
@@ -8051,22 +7987,19 @@
         <v>35</v>
       </c>
       <c r="AR21" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU21" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AV21" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW21" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AX21" t="s">
         <v>3</v>
       </c>
       <c r="AY21" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AZ21" t="s">
         <v>34</v>
@@ -8075,10 +8008,10 @@
         <v>2</v>
       </c>
       <c r="BC21" t="s">
+        <v>1</v>
+      </c>
+      <c r="BD21" t="s">
         <v>0</v>
-      </c>
-      <c r="BD21" t="s">
-        <v>1</v>
       </c>
       <c r="BE21" t="s">
         <v>3</v>
@@ -8095,55 +8028,55 @@
     </row>
     <row r="22" ht="15" customHeight="1" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C22" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E22" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F22" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H22" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K22" t="s">
+        <v>20</v>
+      </c>
+      <c r="O22" t="s">
         <v>22</v>
       </c>
-      <c r="O22" t="s">
-        <v>17</v>
-      </c>
       <c r="Q22" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="R22" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T22" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="X22" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AA22" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AB22" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AF22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH22" t="s">
         <v>30</v>
       </c>
       <c r="AI22" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AJ22" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AO22" t="s">
         <v>8</v>
@@ -8154,29 +8087,26 @@
       <c r="AR22" t="s">
         <v>8</v>
       </c>
-      <c r="AU22" t="s">
-        <v>21</v>
-      </c>
       <c r="AV22" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AW22" t="s">
         <v>8</v>
       </c>
       <c r="AX22" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AY22" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AZ22" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="BA22" t="s">
         <v>30</v>
       </c>
       <c r="BC22" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="BD22" t="s">
         <v>45</v>
@@ -8185,24 +8115,24 @@
         <v>8</v>
       </c>
       <c r="BF22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BG22" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="BI22" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E23" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F23" t="s">
         <v>29</v>
@@ -8214,25 +8144,25 @@
         <v>29</v>
       </c>
       <c r="O23" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="Q23" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="R23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T23" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="X23" t="s">
         <v>37</v>
       </c>
       <c r="AA23" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AB23" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AF23" t="s">
         <v>15</v>
@@ -8241,28 +8171,25 @@
         <v>41</v>
       </c>
       <c r="AI23" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AJ23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO23" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AQ23" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AR23" t="s">
         <v>4</v>
       </c>
-      <c r="AU23" t="s">
-        <v>25</v>
-      </c>
       <c r="AV23" t="s">
         <v>39</v>
       </c>
       <c r="AW23" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AX23" t="s">
         <v>29</v>
@@ -8271,28 +8198,28 @@
         <v>37</v>
       </c>
       <c r="AZ23" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BA23" t="s">
         <v>39</v>
       </c>
       <c r="BC23" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BD23" t="s">
         <v>4</v>
       </c>
       <c r="BE23" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BF23" t="s">
+        <v>27</v>
+      </c>
+      <c r="BG23" t="s">
         <v>31</v>
       </c>
-      <c r="BG23" t="s">
-        <v>32</v>
-      </c>
       <c r="BI23" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" spans="1:61" x14ac:dyDescent="0.25">
@@ -8300,25 +8227,25 @@
         <v>2</v>
       </c>
       <c r="E24" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F24" t="s">
         <v>40</v>
       </c>
       <c r="H24" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="O24" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="T24" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X24" t="s">
         <v>2</v>
       </c>
       <c r="AB24" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF24" t="s">
         <v>6</v>
@@ -8336,19 +8263,19 @@
         <v>5</v>
       </c>
       <c r="AW24" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX24" t="s">
         <v>2</v>
       </c>
       <c r="AY24" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="AZ24" t="s">
         <v>33</v>
       </c>
       <c r="BA24" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="BC24" t="s">
         <v>5</v>
@@ -8360,7 +8287,7 @@
         <v>5</v>
       </c>
       <c r="BF24" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG24" t="s">
         <v>6</v>
@@ -8368,10 +8295,10 @@
     </row>
     <row r="25" ht="15" customHeight="1" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E25" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="s">
         <v>7</v>
@@ -8380,16 +8307,16 @@
         <v>3</v>
       </c>
       <c r="O25" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="T25" t="s">
         <v>3</v>
       </c>
       <c r="X25" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB25" t="s">
         <v>0</v>
-      </c>
-      <c r="AB25" t="s">
-        <v>1</v>
       </c>
       <c r="AF25" t="s">
         <v>3</v>
@@ -8413,7 +8340,7 @@
         <v>7</v>
       </c>
       <c r="AY25" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="AZ25" t="s">
         <v>2</v>
@@ -8425,87 +8352,87 @@
         <v>2</v>
       </c>
       <c r="BD25" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE25" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="BF25" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BG25" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E26" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F26" t="s">
         <v>8</v>
       </c>
       <c r="H26" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="O26" t="s">
         <v>8</v>
       </c>
       <c r="T26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X26" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AB26" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AF26" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AI26" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AJ26" t="s">
         <v>39</v>
       </c>
       <c r="AO26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AV26" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AW26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX26" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AY26" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AZ26" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="BA26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC26" t="s">
         <v>8</v>
       </c>
       <c r="BD26" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="BE26" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BF26" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="BG26" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" spans="1:59" x14ac:dyDescent="0.25">
@@ -8513,70 +8440,70 @@
         <v>4</v>
       </c>
       <c r="E27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F27" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O27" t="s">
         <v>4</v>
       </c>
       <c r="T27" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="X27" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AB27" t="s">
+        <v>24</v>
+      </c>
+      <c r="AF27" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI27" t="s">
+        <v>24</v>
+      </c>
+      <c r="AJ27" t="s">
+        <v>16</v>
+      </c>
+      <c r="AO27" t="s">
         <v>25</v>
       </c>
-      <c r="AF27" t="s">
-        <v>20</v>
-      </c>
-      <c r="AI27" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ27" t="s">
-        <v>20</v>
-      </c>
-      <c r="AO27" t="s">
-        <v>26</v>
-      </c>
       <c r="AV27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW27" t="s">
         <v>30</v>
       </c>
       <c r="AX27" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AY27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ27" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA27" t="s">
         <v>4</v>
       </c>
       <c r="BC27" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="BD27" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BE27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BF27" t="s">
         <v>4</v>
       </c>
       <c r="BG27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" spans="48:59" x14ac:dyDescent="0.25"/>
@@ -8690,16 +8617,16 @@
         <v>51</v>
       </c>
       <c r="B3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" t="s">
         <v>55</v>
-      </c>
-      <c r="C3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" t="s">
-        <v>54</v>
       </c>
       <c r="F3" t="s">
         <v>57</v>
@@ -8714,7 +8641,7 @@
         <v>70</v>
       </c>
       <c r="J3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K3" t="s">
         <v>71</v>
@@ -8777,7 +8704,7 @@
         <v>86</v>
       </c>
       <c r="AE3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AF3" t="s">
         <v>98</v>
@@ -8813,7 +8740,7 @@
         <v>111</v>
       </c>
       <c r="AQ3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AR3" t="s">
         <v>103</v>
@@ -8828,7 +8755,7 @@
         <v>75</v>
       </c>
       <c r="AV3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AW3" t="s">
         <v>62</v>
@@ -9189,500 +9116,500 @@
         <v>216</v>
       </c>
       <c r="AU5" t="s">
+        <v>189</v>
+      </c>
+      <c r="AV5" t="s">
         <v>217</v>
       </c>
-      <c r="AV5" t="s">
+      <c r="AW5" t="s">
         <v>218</v>
       </c>
-      <c r="AW5" t="s">
+      <c r="AX5" t="s">
         <v>219</v>
       </c>
-      <c r="AX5" t="s">
+      <c r="AY5" t="s">
         <v>220</v>
       </c>
-      <c r="AY5" t="s">
+      <c r="AZ5" t="s">
         <v>221</v>
       </c>
-      <c r="AZ5" t="s">
+      <c r="BA5" t="s">
         <v>222</v>
       </c>
-      <c r="BA5" t="s">
+      <c r="BC5" t="s">
         <v>223</v>
       </c>
-      <c r="BC5" t="s">
+      <c r="BD5" t="s">
         <v>224</v>
       </c>
-      <c r="BD5" t="s">
+      <c r="BE5" t="s">
         <v>225</v>
       </c>
-      <c r="BE5" t="s">
+      <c r="BF5" t="s">
         <v>226</v>
       </c>
-      <c r="BF5" t="s">
+      <c r="BG5" t="s">
         <v>227</v>
       </c>
-      <c r="BG5" t="s">
+      <c r="BH5" t="s">
         <v>228</v>
       </c>
-      <c r="BH5" t="s">
+      <c r="BI5" t="s">
         <v>229</v>
       </c>
-      <c r="BI5" t="s">
+      <c r="BJ5" t="s">
         <v>230</v>
       </c>
-      <c r="BJ5" t="s">
+      <c r="BM5" t="s">
         <v>231</v>
-      </c>
-      <c r="BM5" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>232</v>
+      </c>
+      <c r="C6" t="s">
         <v>233</v>
       </c>
-      <c r="C6" t="s">
+      <c r="E6" t="s">
         <v>234</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>235</v>
       </c>
-      <c r="F6" t="s">
+      <c r="H6" t="s">
         <v>236</v>
       </c>
-      <c r="H6" t="s">
+      <c r="J6" t="s">
         <v>237</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>238</v>
       </c>
-      <c r="K6" t="s">
+      <c r="M6" t="s">
         <v>239</v>
       </c>
-      <c r="M6" t="s">
+      <c r="O6" t="s">
         <v>240</v>
       </c>
-      <c r="O6" t="s">
+      <c r="Q6" t="s">
         <v>241</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="R6" t="s">
         <v>242</v>
       </c>
-      <c r="R6" t="s">
+      <c r="T6" t="s">
         <v>243</v>
       </c>
-      <c r="T6" t="s">
+      <c r="V6" t="s">
         <v>244</v>
       </c>
-      <c r="V6" t="s">
+      <c r="W6" t="s">
         <v>245</v>
       </c>
-      <c r="W6" t="s">
+      <c r="X6" t="s">
         <v>246</v>
       </c>
-      <c r="X6" t="s">
+      <c r="Z6" t="s">
         <v>247</v>
       </c>
-      <c r="Z6" t="s">
+      <c r="AA6" t="s">
         <v>248</v>
       </c>
-      <c r="AA6" t="s">
+      <c r="AB6" t="s">
         <v>249</v>
       </c>
-      <c r="AB6" t="s">
+      <c r="AD6" t="s">
         <v>250</v>
       </c>
-      <c r="AD6" t="s">
+      <c r="AE6" t="s">
         <v>251</v>
       </c>
-      <c r="AE6" t="s">
+      <c r="AF6" t="s">
         <v>252</v>
       </c>
-      <c r="AF6" t="s">
+      <c r="AH6" t="s">
         <v>253</v>
       </c>
-      <c r="AH6" t="s">
+      <c r="AI6" t="s">
         <v>254</v>
       </c>
-      <c r="AI6" t="s">
+      <c r="AJ6" t="s">
         <v>255</v>
       </c>
-      <c r="AJ6" t="s">
+      <c r="AK6" t="s">
         <v>256</v>
       </c>
-      <c r="AK6" t="s">
+      <c r="AL6" t="s">
         <v>257</v>
       </c>
-      <c r="AL6" t="s">
+      <c r="AN6" t="s">
         <v>258</v>
       </c>
-      <c r="AN6" t="s">
+      <c r="AO6" t="s">
         <v>259</v>
       </c>
-      <c r="AO6" t="s">
+      <c r="AQ6" t="s">
         <v>260</v>
       </c>
-      <c r="AQ6" t="s">
+      <c r="AR6" t="s">
         <v>261</v>
       </c>
-      <c r="AR6" t="s">
+      <c r="AS6" t="s">
         <v>262</v>
       </c>
-      <c r="AS6" t="s">
+      <c r="AT6" t="s">
         <v>263</v>
       </c>
-      <c r="AT6" t="s">
+      <c r="AU6" t="s">
         <v>264</v>
       </c>
-      <c r="AU6" t="s">
+      <c r="AV6" t="s">
         <v>265</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>266</v>
       </c>
       <c r="AW6" t="s">
         <v>213</v>
       </c>
       <c r="AX6" t="s">
+        <v>266</v>
+      </c>
+      <c r="AY6" t="s">
         <v>267</v>
       </c>
-      <c r="AY6" t="s">
+      <c r="AZ6" t="s">
         <v>268</v>
       </c>
-      <c r="AZ6" t="s">
+      <c r="BA6" t="s">
         <v>269</v>
       </c>
-      <c r="BA6" t="s">
+      <c r="BC6" t="s">
         <v>270</v>
       </c>
-      <c r="BC6" t="s">
+      <c r="BD6" t="s">
         <v>271</v>
       </c>
-      <c r="BD6" t="s">
+      <c r="BE6" t="s">
         <v>272</v>
       </c>
-      <c r="BE6" t="s">
+      <c r="BF6" t="s">
         <v>273</v>
       </c>
-      <c r="BF6" t="s">
+      <c r="BG6" t="s">
         <v>274</v>
       </c>
-      <c r="BG6" t="s">
+      <c r="BI6" t="s">
         <v>275</v>
       </c>
-      <c r="BI6" t="s">
+      <c r="BJ6" t="s">
         <v>276</v>
-      </c>
-      <c r="BJ6" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>277</v>
+      </c>
+      <c r="C7" t="s">
         <v>278</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
         <v>279</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>280</v>
       </c>
-      <c r="F7" t="s">
+      <c r="H7" t="s">
         <v>281</v>
       </c>
-      <c r="H7" t="s">
+      <c r="J7" t="s">
         <v>282</v>
       </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
         <v>283</v>
       </c>
-      <c r="K7" t="s">
+      <c r="M7" t="s">
         <v>284</v>
       </c>
-      <c r="M7" t="s">
+      <c r="O7" t="s">
         <v>285</v>
       </c>
-      <c r="O7" t="s">
+      <c r="Q7" t="s">
         <v>286</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="R7" t="s">
         <v>287</v>
       </c>
-      <c r="R7" t="s">
+      <c r="T7" t="s">
         <v>288</v>
       </c>
-      <c r="T7" t="s">
+      <c r="V7" t="s">
         <v>289</v>
       </c>
-      <c r="V7" t="s">
+      <c r="X7" t="s">
         <v>290</v>
       </c>
-      <c r="X7" t="s">
+      <c r="Z7" t="s">
         <v>291</v>
       </c>
-      <c r="Z7" t="s">
+      <c r="AA7" t="s">
         <v>292</v>
       </c>
-      <c r="AA7" t="s">
+      <c r="AB7" t="s">
         <v>293</v>
       </c>
-      <c r="AB7" t="s">
+      <c r="AD7" t="s">
         <v>294</v>
       </c>
-      <c r="AD7" t="s">
+      <c r="AE7" t="s">
         <v>295</v>
       </c>
-      <c r="AE7" t="s">
+      <c r="AF7" t="s">
         <v>296</v>
       </c>
-      <c r="AF7" t="s">
+      <c r="AH7" t="s">
         <v>297</v>
       </c>
-      <c r="AH7" t="s">
+      <c r="AI7" t="s">
         <v>298</v>
       </c>
-      <c r="AI7" t="s">
+      <c r="AJ7" t="s">
         <v>299</v>
       </c>
-      <c r="AJ7" t="s">
+      <c r="AN7" t="s">
         <v>300</v>
       </c>
-      <c r="AN7" t="s">
+      <c r="AO7" t="s">
         <v>301</v>
       </c>
-      <c r="AO7" t="s">
+      <c r="AQ7" t="s">
         <v>302</v>
       </c>
-      <c r="AQ7" t="s">
+      <c r="AR7" t="s">
         <v>303</v>
       </c>
-      <c r="AR7" t="s">
+      <c r="AU7" t="s">
         <v>304</v>
       </c>
-      <c r="AU7" t="s">
+      <c r="AV7" t="s">
         <v>305</v>
       </c>
-      <c r="AV7" t="s">
+      <c r="AW7" t="s">
         <v>306</v>
       </c>
-      <c r="AW7" t="s">
+      <c r="AX7" t="s">
         <v>307</v>
       </c>
-      <c r="AX7" t="s">
+      <c r="AY7" t="s">
         <v>308</v>
       </c>
-      <c r="AY7" t="s">
+      <c r="AZ7" t="s">
         <v>309</v>
       </c>
-      <c r="AZ7" t="s">
+      <c r="BA7" t="s">
         <v>310</v>
       </c>
-      <c r="BA7" t="s">
+      <c r="BC7" t="s">
         <v>311</v>
       </c>
-      <c r="BC7" t="s">
+      <c r="BD7" t="s">
         <v>312</v>
       </c>
-      <c r="BD7" t="s">
+      <c r="BE7" t="s">
         <v>313</v>
       </c>
-      <c r="BE7" t="s">
+      <c r="BF7" t="s">
         <v>314</v>
       </c>
-      <c r="BF7" t="s">
+      <c r="BG7" t="s">
         <v>315</v>
       </c>
-      <c r="BG7" t="s">
+      <c r="BI7" t="s">
         <v>316</v>
-      </c>
-      <c r="BI7" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>317</v>
+      </c>
+      <c r="C8" t="s">
         <v>318</v>
       </c>
-      <c r="C8" t="s">
+      <c r="E8" t="s">
         <v>319</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>320</v>
       </c>
-      <c r="F8" t="s">
+      <c r="H8" t="s">
         <v>321</v>
       </c>
-      <c r="H8" t="s">
+      <c r="K8" t="s">
         <v>322</v>
       </c>
-      <c r="K8" t="s">
+      <c r="O8" t="s">
         <v>323</v>
       </c>
-      <c r="O8" t="s">
+      <c r="Q8" t="s">
         <v>324</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="R8" t="s">
         <v>325</v>
       </c>
-      <c r="R8" t="s">
+      <c r="T8" t="s">
         <v>326</v>
       </c>
-      <c r="T8" t="s">
+      <c r="X8" t="s">
         <v>327</v>
       </c>
-      <c r="X8" t="s">
+      <c r="AA8" t="s">
         <v>328</v>
       </c>
-      <c r="AA8" t="s">
+      <c r="AB8" t="s">
         <v>329</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>330</v>
       </c>
       <c r="AE8" t="s">
         <v>213</v>
       </c>
       <c r="AF8" t="s">
+        <v>330</v>
+      </c>
+      <c r="AH8" t="s">
         <v>331</v>
       </c>
-      <c r="AH8" t="s">
+      <c r="AI8" t="s">
         <v>332</v>
       </c>
-      <c r="AI8" t="s">
+      <c r="AJ8" t="s">
         <v>333</v>
       </c>
-      <c r="AJ8" t="s">
+      <c r="AN8" t="s">
         <v>334</v>
       </c>
-      <c r="AN8" t="s">
+      <c r="AO8" t="s">
         <v>335</v>
       </c>
-      <c r="AO8" t="s">
+      <c r="AQ8" t="s">
         <v>336</v>
       </c>
-      <c r="AQ8" t="s">
+      <c r="AR8" t="s">
         <v>337</v>
       </c>
-      <c r="AR8" t="s">
+      <c r="AU8" t="s">
+        <v>213</v>
+      </c>
+      <c r="AV8" t="s">
         <v>338</v>
       </c>
-      <c r="AU8" t="s">
+      <c r="AW8" t="s">
         <v>339</v>
       </c>
-      <c r="AV8" t="s">
+      <c r="AX8" t="s">
         <v>340</v>
       </c>
-      <c r="AW8" t="s">
+      <c r="AY8" t="s">
         <v>341</v>
       </c>
-      <c r="AX8" t="s">
+      <c r="AZ8" t="s">
         <v>342</v>
       </c>
-      <c r="AY8" t="s">
+      <c r="BA8" t="s">
         <v>343</v>
       </c>
-      <c r="AZ8" t="s">
+      <c r="BC8" t="s">
         <v>344</v>
       </c>
-      <c r="BA8" t="s">
+      <c r="BD8" t="s">
         <v>345</v>
       </c>
-      <c r="BC8" t="s">
+      <c r="BE8" t="s">
         <v>346</v>
       </c>
-      <c r="BD8" t="s">
+      <c r="BF8" t="s">
         <v>347</v>
       </c>
-      <c r="BE8" t="s">
+      <c r="BG8" t="s">
         <v>348</v>
       </c>
-      <c r="BF8" t="s">
+      <c r="BI8" t="s">
         <v>349</v>
-      </c>
-      <c r="BG8" t="s">
-        <v>350</v>
-      </c>
-      <c r="BI8" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>350</v>
+      </c>
+      <c r="E9" t="s">
+        <v>351</v>
+      </c>
+      <c r="F9" t="s">
         <v>352</v>
       </c>
-      <c r="E9" t="s">
+      <c r="H9" t="s">
         <v>353</v>
       </c>
-      <c r="F9" t="s">
+      <c r="O9" t="s">
         <v>354</v>
       </c>
-      <c r="H9" t="s">
+      <c r="T9" t="s">
         <v>355</v>
       </c>
-      <c r="O9" t="s">
+      <c r="X9" t="s">
         <v>356</v>
       </c>
-      <c r="T9" t="s">
+      <c r="AB9" t="s">
         <v>357</v>
       </c>
-      <c r="X9" t="s">
+      <c r="AF9" t="s">
         <v>358</v>
       </c>
-      <c r="AB9" t="s">
+      <c r="AI9" t="s">
         <v>359</v>
       </c>
-      <c r="AF9" t="s">
+      <c r="AJ9" t="s">
         <v>360</v>
       </c>
-      <c r="AI9" t="s">
+      <c r="AO9" t="s">
         <v>361</v>
       </c>
-      <c r="AJ9" t="s">
+      <c r="AV9" t="s">
         <v>362</v>
       </c>
-      <c r="AO9" t="s">
+      <c r="AW9" t="s">
         <v>363</v>
       </c>
-      <c r="AV9" t="s">
+      <c r="AX9" t="s">
         <v>364</v>
       </c>
-      <c r="AW9" t="s">
+      <c r="AY9" t="s">
         <v>365</v>
       </c>
-      <c r="AX9" t="s">
+      <c r="AZ9" t="s">
         <v>366</v>
       </c>
-      <c r="AY9" t="s">
+      <c r="BA9" t="s">
         <v>367</v>
       </c>
-      <c r="AZ9" t="s">
+      <c r="BC9" t="s">
         <v>368</v>
       </c>
-      <c r="BA9" t="s">
+      <c r="BD9" t="s">
         <v>369</v>
       </c>
-      <c r="BC9" t="s">
+      <c r="BE9" t="s">
         <v>370</v>
       </c>
-      <c r="BD9" t="s">
+      <c r="BF9" t="s">
         <v>371</v>
       </c>
-      <c r="BE9" t="s">
+      <c r="BG9" t="s">
         <v>372</v>
-      </c>
-      <c r="BF9" t="s">
-        <v>373</v>
-      </c>
-      <c r="BG9" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="41:59" x14ac:dyDescent="0.25">
       <c r="AO10" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="AW10" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" spans="49:49" x14ac:dyDescent="0.25"/>

--- a/data/ICEHLdelegacije.xlsx
+++ b/data/ICEHLdelegacije.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2506" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2508" uniqueCount="375">
   <si>
     <t>SmetanaLa</t>
   </si>
@@ -513,7 +513,7 @@
     <t>Tiroler Wasserkraft Arena;NikolicMa;SternatCh;PardatscherUl;SparerDa</t>
   </si>
   <si>
-    <t>Merkur Eisstadion Graz;SmetanaLa;SternatCh;JedlickaPe;KoncDa</t>
+    <t>Merkur Eisstadion Graz;FichtnerPa;SternatCh;JedlickaPe;KoncDa</t>
   </si>
   <si>
     <t>Eishalle Asiago;LazzeriAl;OfnerCh;MantovaniDa;WeissAl</t>
@@ -672,7 +672,7 @@
     <t>Gabor Ocskay Eisarena;HronskyTo;NagyAt;DurmisOt;VacziDa</t>
   </si>
   <si>
-    <t>Eishalle KagranEins;SmetanaLa;ZrnicMi;MoidlMa;ZgoncGa</t>
+    <t>Eishalle KagranEins;GroznikBo;ZrnicMi;MoidlMa;ZgoncGa</t>
   </si>
   <si>
     <t>Stadthalle Villach;HronskyTo;PiragicTr;BedynekSe;KoncDa</t>
@@ -1113,7 +1113,7 @@
     <t>Sparkasse Arena Bozen;OfnerCh;ZrnicMi;MantovaniDa;PardatscherUl</t>
   </si>
   <si>
-    <t>Eishalle Asiago;NikolicMa;NikolicKr;MantovaniDa;RigoniDa</t>
+    <t>Eishalle Asiago;NikolicKr;NikolicMa;MantovaniDa;RigoniDa</t>
   </si>
   <si>
     <t>Sparkasse Arena Bozen;Huber aAn;OfnerCh;MantovaniDa;PardatscherUl</t>
@@ -4785,8 +4785,11 @@
       <c r="N29" t="s">
         <v>88</v>
       </c>
+      <c r="O29" t="s">
+        <v>82</v>
+      </c>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>103</v>
       </c>
@@ -4872,7 +4875,7 @@
     </row>
     <row r="33" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="B33" t="s">
         <v>60</v>
@@ -4892,7 +4895,7 @@
     </row>
     <row r="34" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B34" t="s">
         <v>91</v>
@@ -4903,8 +4906,11 @@
       <c r="D34" t="s">
         <v>106</v>
       </c>
+      <c r="F34" t="s">
+        <v>62</v>
+      </c>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>60</v>
       </c>
@@ -5517,7 +5523,7 @@
         <v>6</v>
       </c>
       <c r="AV4" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AW4" t="s">
         <v>50</v>
@@ -6278,7 +6284,7 @@
         <v>19</v>
       </c>
       <c r="AW8" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AX8" t="s">
         <v>19</v>
@@ -8269,7 +8275,7 @@
         <v>2</v>
       </c>
       <c r="AY24" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="AZ24" t="s">
         <v>33</v>
@@ -8340,7 +8346,7 @@
         <v>7</v>
       </c>
       <c r="AY25" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="AZ25" t="s">
         <v>2</v>

--- a/data/ICEHLdelegacije.xlsx
+++ b/data/ICEHLdelegacije.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="ICEHL" state="visible" r:id="rId4"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2508" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2507" uniqueCount="374">
   <si>
     <t>SmetanaLa</t>
   </si>
@@ -165,9 +165,6 @@
     <t>HlavatyAl</t>
   </si>
   <si>
-    <t>HeadSc</t>
-  </si>
-  <si>
     <t>LazzeriAl</t>
   </si>
   <si>
@@ -201,168 +198,168 @@
     <t>2024-12-26</t>
   </si>
   <si>
+    <t>2024-12-22</t>
+  </si>
+  <si>
+    <t>2024-10-01</t>
+  </si>
+  <si>
+    <t>2024-10-25</t>
+  </si>
+  <si>
+    <t>2024-10-20</t>
+  </si>
+  <si>
+    <t>2024-12-08</t>
+  </si>
+  <si>
+    <t>2024-10-06</t>
+  </si>
+  <si>
+    <t>2024-11-01</t>
+  </si>
+  <si>
+    <t>2025-01-19</t>
+  </si>
+  <si>
+    <t>2024-10-05</t>
+  </si>
+  <si>
+    <t>2024-10-11</t>
+  </si>
+  <si>
+    <t>2024-10-02</t>
+  </si>
+  <si>
+    <t>2024-10-27</t>
+  </si>
+  <si>
+    <t>2024-10-22</t>
+  </si>
+  <si>
+    <t>2024-12-18</t>
+  </si>
+  <si>
+    <t>2024-11-27</t>
+  </si>
+  <si>
+    <t>2024-10-18</t>
+  </si>
+  <si>
+    <t>2024-11-13</t>
+  </si>
+  <si>
+    <t>2024-11-15</t>
+  </si>
+  <si>
+    <t>2024-11-24</t>
+  </si>
+  <si>
+    <t>2024-11-20</t>
+  </si>
+  <si>
+    <t>2024-12-20</t>
+  </si>
+  <si>
+    <t>2025-01-05</t>
+  </si>
+  <si>
+    <t>2024-10-19</t>
+  </si>
+  <si>
+    <t>2024-10-26</t>
+  </si>
+  <si>
+    <t>2024-11-17</t>
+  </si>
+  <si>
+    <t>2024-11-29</t>
+  </si>
+  <si>
+    <t>2025-01-18</t>
+  </si>
+  <si>
+    <t>2024-11-03</t>
+  </si>
+  <si>
+    <t>2024-11-02</t>
+  </si>
+  <si>
+    <t>2024-12-28</t>
+  </si>
+  <si>
+    <t>2025-01-03</t>
+  </si>
+  <si>
+    <t>2024-10-23</t>
+  </si>
+  <si>
+    <t>2024-10-29</t>
+  </si>
+  <si>
+    <t>2024-12-06</t>
+  </si>
+  <si>
+    <t>2025-01-10</t>
+  </si>
+  <si>
+    <t>2024-11-22</t>
+  </si>
+  <si>
+    <t>2024-12-01</t>
+  </si>
+  <si>
+    <t>2025-01-01</t>
+  </si>
+  <si>
+    <t>2024-11-16</t>
+  </si>
+  <si>
+    <t>2024-12-04</t>
+  </si>
+  <si>
+    <t>2024-12-13</t>
+  </si>
+  <si>
+    <t>2024-12-30</t>
+  </si>
+  <si>
     <t>zbrisano</t>
   </si>
   <si>
-    <t>2024-12-22</t>
-  </si>
-  <si>
-    <t>2024-10-01</t>
-  </si>
-  <si>
-    <t>2024-10-25</t>
-  </si>
-  <si>
-    <t>2024-10-20</t>
-  </si>
-  <si>
-    <t>2024-12-08</t>
-  </si>
-  <si>
-    <t>2024-10-06</t>
-  </si>
-  <si>
-    <t>2024-11-01</t>
-  </si>
-  <si>
-    <t>2025-01-19</t>
-  </si>
-  <si>
-    <t>2024-10-05</t>
-  </si>
-  <si>
-    <t>2024-10-11</t>
-  </si>
-  <si>
-    <t>2024-10-02</t>
-  </si>
-  <si>
-    <t>2024-10-27</t>
-  </si>
-  <si>
-    <t>2024-10-22</t>
-  </si>
-  <si>
-    <t>2024-12-18</t>
-  </si>
-  <si>
-    <t>2024-11-27</t>
-  </si>
-  <si>
-    <t>2024-10-18</t>
-  </si>
-  <si>
-    <t>2024-11-13</t>
-  </si>
-  <si>
-    <t>2024-11-15</t>
-  </si>
-  <si>
-    <t>2024-11-24</t>
-  </si>
-  <si>
-    <t>2024-11-20</t>
-  </si>
-  <si>
-    <t>2024-12-20</t>
-  </si>
-  <si>
-    <t>2025-01-05</t>
-  </si>
-  <si>
-    <t>2024-10-19</t>
-  </si>
-  <si>
-    <t>2024-10-26</t>
-  </si>
-  <si>
-    <t>2024-11-17</t>
-  </si>
-  <si>
-    <t>2024-11-29</t>
-  </si>
-  <si>
-    <t>2025-01-18</t>
-  </si>
-  <si>
-    <t>2024-11-03</t>
-  </si>
-  <si>
-    <t>2024-11-02</t>
-  </si>
-  <si>
-    <t>2024-12-28</t>
+    <t>2024-11-30</t>
+  </si>
+  <si>
+    <t>2025-01-08</t>
+  </si>
+  <si>
+    <t>2024-11-23</t>
   </si>
   <si>
     <t>2025-01-12</t>
   </si>
   <si>
-    <t>2024-10-23</t>
-  </si>
-  <si>
-    <t>2024-10-29</t>
-  </si>
-  <si>
-    <t>2024-12-06</t>
-  </si>
-  <si>
-    <t>2025-01-10</t>
+    <t>2024-12-03</t>
+  </si>
+  <si>
+    <t>2024-12-15</t>
+  </si>
+  <si>
+    <t>2024-12-07</t>
+  </si>
+  <si>
+    <t>2025-01-17</t>
+  </si>
+  <si>
+    <t>2024-12-14</t>
+  </si>
+  <si>
+    <t>2024-12-10</t>
   </si>
   <si>
     <t>2025-01-15</t>
   </si>
   <si>
-    <t>2024-11-22</t>
-  </si>
-  <si>
-    <t>2024-12-01</t>
-  </si>
-  <si>
-    <t>2025-01-01</t>
-  </si>
-  <si>
-    <t>2024-11-16</t>
-  </si>
-  <si>
-    <t>2024-12-04</t>
-  </si>
-  <si>
-    <t>2024-12-13</t>
-  </si>
-  <si>
-    <t>2024-12-30</t>
-  </si>
-  <si>
-    <t>2024-11-30</t>
-  </si>
-  <si>
-    <t>2025-01-08</t>
-  </si>
-  <si>
-    <t>2024-11-23</t>
-  </si>
-  <si>
-    <t>2024-12-03</t>
-  </si>
-  <si>
-    <t>2024-12-15</t>
-  </si>
-  <si>
-    <t>2025-01-03</t>
-  </si>
-  <si>
-    <t>2024-12-07</t>
-  </si>
-  <si>
-    <t>2025-01-17</t>
-  </si>
-  <si>
-    <t>2024-12-14</t>
-  </si>
-  <si>
-    <t>2024-12-10</t>
-  </si>
-  <si>
     <t>2025-01-21</t>
   </si>
   <si>
@@ -513,7 +510,7 @@
     <t>Tiroler Wasserkraft Arena;NikolicMa;SternatCh;PardatscherUl;SparerDa</t>
   </si>
   <si>
-    <t>Merkur Eisstadion Graz;FichtnerPa;SternatCh;JedlickaPe;KoncDa</t>
+    <t>Merkur Eisstadion Graz;FichtnerPa;ZrnicMi;JedlickaPe;KoncDa</t>
   </si>
   <si>
     <t>Eishalle Asiago;LazzeriAl;OfnerCh;MantovaniDa;WeissAl</t>
@@ -672,10 +669,10 @@
     <t>Gabor Ocskay Eisarena;HronskyTo;NagyAt;DurmisOt;VacziDa</t>
   </si>
   <si>
-    <t>Eishalle KagranEins;GroznikBo;ZrnicMi;MoidlMa;ZgoncGa</t>
-  </si>
-  <si>
-    <t>Stadthalle Villach;HronskyTo;PiragicTr;BedynekSe;KoncDa</t>
+    <t>Eishalle KagranEins;GroznikBo;ZrnicMi;ZacherlPa;ZgoncGa</t>
+  </si>
+  <si>
+    <t>Stadthalle Villach;HronskyTo;KainbergerJu;BedynekSe;KoncDa</t>
   </si>
   <si>
     <t>Gabor Ocskay Eisarena;PiragicTr;ZrnicMi;HribarMa;ZgoncGa</t>
@@ -696,13 +693,13 @@
     <t>Heidi Horten Arena Klagenfurt;FichtnerPa;SmetanaLa;BärnthalerCh;ZgoncGa</t>
   </si>
   <si>
-    <t>Tiroler Wasserkraft Arena;NikolicKr;NikolicMa;SparerDa;ZacherlPa</t>
-  </si>
-  <si>
-    <t>Eishalle Feldkirch;BernekerTh;NikolicKr;FleischmannLu;MartinFl</t>
-  </si>
-  <si>
-    <t>Sparkasse Arena Bozen;OfnerCh;SternatCh;FleischmannLu;MantovaniDa</t>
+    <t>Tiroler Wasserkraft Arena;NikolicMa;NikolicKr;SparerDa;ZacherlPa</t>
+  </si>
+  <si>
+    <t>Eishalle Feldkirch;BernekerTh;NikolicKr;MartinFl;SeewaldJe</t>
+  </si>
+  <si>
+    <t>Sparkasse Arena Bozen;OfnerCh;SternatCh;MantovaniDa;ZgoncGa</t>
   </si>
   <si>
     <t>Eishalle Wien-Kagran;NagyAt;SiegelSt;DurmisOt;WimmlerAl</t>
@@ -846,7 +843,7 @@
     <t>Stadthalle Villach;GroznikBo;PiragicTr;HribarMa;ZgoncGa</t>
   </si>
   <si>
-    <t>Eishalle Bruneck;NikolicMa;NikolicKr;MantovaniDa;SparerDa</t>
+    <t>Eishalle Bruneck;NikolicKr;NikolicMa;MantovaniDa;SparerDa</t>
   </si>
   <si>
     <t>Eishalle Wien-Kagran;HronskyTo;SmetanaLa;DurmisOt;WeissAl</t>
@@ -942,16 +939,16 @@
     <t>Eishalle Feldkirch;NikolicMa;SchauerJa;FleischmannLu;SparerDa</t>
   </si>
   <si>
-    <t>Eisarena Salzburg;OfnerCh;SmetanaLa;SeewaldJe;WimmlerAl</t>
+    <t>Eisarena Salzburg;OfnerCh;SmetanaLa;PuffWo;SeewaldJe</t>
   </si>
   <si>
     <t>Eisarena Salzburg;HronskyTo;SternatCh;JedlickaPe;SeewaldJe</t>
   </si>
   <si>
-    <t>Tiroler Wasserkraft Arena;NikolicKr;NikolicMa;MartinFl;SparerDa</t>
-  </si>
-  <si>
-    <t>Sparkasse Arena Bozen;BernekerTh;SeewaldEl;RigoniDa;SparerDa</t>
+    <t>Tiroler Wasserkraft Arena;NikolicMa;NikolicKr;MartinFl;SparerDa</t>
+  </si>
+  <si>
+    <t>Sparkasse Arena Bozen;BernekerTh;SeewaldEl;SeewaldJe;SparerDa</t>
   </si>
   <si>
     <t>Eishalle Wien-Kagran;HronskyTo;SternatCh;JedlickaPe;KoncDa</t>
@@ -1044,13 +1041,13 @@
     <t>Eishalle Bruneck;BernekerTh;SchauerJa;MartinFl;WeissAl</t>
   </si>
   <si>
-    <t>Eishalle Feldkirch;BernekerTh;NikolicKr;MartinFl;SparerDa</t>
+    <t>Eishalle Feldkirch;BernekerTh;NikolicMa;MartinFl;SparerDa</t>
   </si>
   <si>
     <t>Linz AG Eisarena;Huber aAn;OfnerCh;NotheggerDa;SeewaldJe</t>
   </si>
   <si>
-    <t>Eishalle Bruneck;Huber aAn;PiragicTr;MartinFl;PardatscherUl</t>
+    <t>Eishalle Bruneck;Huber aAn;PiragicTr;FleischmannLu;HribarMa</t>
   </si>
   <si>
     <t>Stadthalle Villach;FichtnerPa;SmetanaLa;JeramFi;ZgoncGa</t>
@@ -1110,7 +1107,7 @@
     <t>Hala Tivoli;PiragicTr;RezekGr;HribarMa;PuffWo</t>
   </si>
   <si>
-    <t>Sparkasse Arena Bozen;OfnerCh;ZrnicMi;MantovaniDa;PardatscherUl</t>
+    <t>Sparkasse Arena Bozen;PiragicTr;ZrnicMi;MantovaniDa;PardatscherUl</t>
   </si>
   <si>
     <t>Eishalle Asiago;NikolicKr;NikolicMa;MantovaniDa;RigoniDa</t>
@@ -1122,7 +1119,7 @@
     <t>Eishalle Bruneck;RezekGr;SternatCh;RigoniDa;ZgoncGa</t>
   </si>
   <si>
-    <t>Eishalle Asiago;GroznikBo;OfnerCh;HribarMa;MantovaniDa</t>
+    <t>Eishalle Asiago;GroznikBo;OfnerCh;MantovaniDa;RigoniDa</t>
   </si>
   <si>
     <t>Sparkasse Arena Bozen;NikolicKr;PiragicTr;MantovaniDa;PardatscherUl</t>
@@ -1458,7 +1455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:AZ134"/>
+  <dimension ref="A2:AY134"/>
   <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.28515625" customWidth="1"/>
@@ -1510,23 +1507,23 @@
     <col min="47" max="47" width="11.7109375" customWidth="1"/>
     <col min="48" max="48" width="15.140625" customWidth="1"/>
     <col min="49" max="49" width="14.140625" customWidth="1"/>
-    <col min="50" max="51" width="16" customWidth="1"/>
-    <col min="53" max="53" width="20.140625" customWidth="1"/>
-    <col min="55" max="55" width="10.140625" customWidth="1"/>
+    <col min="50" max="50" width="16" customWidth="1"/>
+    <col min="52" max="52" width="20.140625" customWidth="1"/>
+    <col min="54" max="54" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" ht="14.45" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A2">
-        <f>COUNTIF(A4:A100,"&lt;&gt;")</f>
-        <v>43</v>
+        <f>COUNTIF(A4:A97,"&lt;&gt;")</f>
+        <v>40</v>
       </c>
       <c r="B2">
-        <f>COUNTIF(B4:B96,"&lt;&gt;")</f>
-        <v>42</v>
+        <f>COUNTIF(B4:B95,"&lt;&gt;")</f>
+        <v>41</v>
       </c>
       <c r="C2">
-        <f>COUNTIF(C4:C98,"&lt;&gt;")</f>
-        <v>42</v>
+        <f>COUNTIF(C4:C97,"&lt;&gt;")</f>
+        <v>41</v>
       </c>
       <c r="D2">
         <f>COUNTIF(D4:D96,"&lt;&gt;")</f>
@@ -1534,11 +1531,11 @@
       </c>
       <c r="E2">
         <f>COUNTIF(E4:E98,"&lt;&gt;")</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F2">
         <f>COUNTIF(F4:F100,"&lt;&gt;")</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G2">
         <f>COUNTIF(G4:G100,"&lt;&gt;")</f>
@@ -1574,7 +1571,7 @@
       </c>
       <c r="O2">
         <f>COUNTIF(O4:O100,"&lt;&gt;")</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P2">
         <f>COUNTIF(P4:P98,"&lt;&gt;")</f>
@@ -1594,7 +1591,7 @@
       </c>
       <c r="T2">
         <f>COUNTIF(T4:T98,"&lt;&gt;")</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U2">
         <f>COUNTIF(U4:U100,"&lt;&gt;")</f>
@@ -1609,12 +1606,12 @@
         <v>23</v>
       </c>
       <c r="X2">
-        <f>COUNTIF(X4:X100,"&lt;&gt;")</f>
-        <v>23</v>
+        <f>COUNTIF(X4:X99,"&lt;&gt;")</f>
+        <v>22</v>
       </c>
       <c r="Y2">
-        <f>COUNTIF(Y4:Y100,"&lt;&gt;")</f>
-        <v>23</v>
+        <f>COUNTIF(Y4:Y99,"&lt;&gt;")</f>
+        <v>22</v>
       </c>
       <c r="Z2">
         <f>COUNTIF(Z4:Z95,"&lt;&gt;")</f>
@@ -1674,7 +1671,7 @@
       </c>
       <c r="AN2">
         <f>COUNTIF(AN4:AN100,"&lt;&gt;")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO2">
         <f>COUNTIF(AO4:AO98,"&lt;&gt;")</f>
@@ -1686,7 +1683,7 @@
       </c>
       <c r="AQ2">
         <f>COUNTIF(AQ4:AQ99,"&lt;&gt;")</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AR2">
         <f>COUNTIF(AR4:AR100,"&lt;&gt;")</f>
@@ -1705,7 +1702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -1856,3205 +1853,3200 @@
       <c r="AX3" t="s">
         <v>49</v>
       </c>
-      <c r="AY3" t="s">
+    </row>
+    <row r="4" ht="15" customHeight="1" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>50</v>
       </c>
+      <c r="B4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G4" t="s">
+        <v>50</v>
+      </c>
+      <c r="H4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J4" t="s">
+        <v>50</v>
+      </c>
+      <c r="K4" t="s">
+        <v>51</v>
+      </c>
+      <c r="L4" t="s">
+        <v>52</v>
+      </c>
+      <c r="M4" t="s">
+        <v>50</v>
+      </c>
+      <c r="N4" t="s">
+        <v>51</v>
+      </c>
+      <c r="O4" t="s">
+        <v>51</v>
+      </c>
+      <c r="P4" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>53</v>
+      </c>
+      <c r="R4" t="s">
+        <v>51</v>
+      </c>
+      <c r="S4" t="s">
+        <v>54</v>
+      </c>
+      <c r="T4" t="s">
+        <v>50</v>
+      </c>
+      <c r="U4" t="s">
+        <v>51</v>
+      </c>
+      <c r="V4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W4" t="s">
+        <v>50</v>
+      </c>
+      <c r="X4" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>58</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>60</v>
+      </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="5" ht="15" customHeight="1" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>51</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
         <v>51</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" t="s">
         <v>51</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E5" t="s">
         <v>51</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F5" t="s">
         <v>51</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G5" t="s">
+        <v>54</v>
+      </c>
+      <c r="H5" t="s">
         <v>51</v>
       </c>
-      <c r="G4" t="s">
+      <c r="I5" t="s">
+        <v>54</v>
+      </c>
+      <c r="J5" t="s">
+        <v>54</v>
+      </c>
+      <c r="K5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L5" t="s">
+        <v>56</v>
+      </c>
+      <c r="M5" t="s">
+        <v>54</v>
+      </c>
+      <c r="N5" t="s">
+        <v>55</v>
+      </c>
+      <c r="O5" t="s">
+        <v>52</v>
+      </c>
+      <c r="P5" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>61</v>
+      </c>
+      <c r="R5" t="s">
+        <v>52</v>
+      </c>
+      <c r="S5" t="s">
+        <v>56</v>
+      </c>
+      <c r="T5" t="s">
+        <v>54</v>
+      </c>
+      <c r="U5" t="s">
+        <v>54</v>
+      </c>
+      <c r="V5" t="s">
+        <v>54</v>
+      </c>
+      <c r="W5" t="s">
         <v>51</v>
       </c>
-      <c r="H4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I4" t="s">
-        <v>51</v>
-      </c>
-      <c r="J4" t="s">
-        <v>51</v>
-      </c>
-      <c r="K4" t="s">
+      <c r="X5" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>54</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>55</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AL5" t="s">
         <v>52</v>
       </c>
-      <c r="L4" t="s">
-        <v>53</v>
-      </c>
-      <c r="M4" t="s">
-        <v>51</v>
-      </c>
-      <c r="N4" t="s">
-        <v>52</v>
-      </c>
-      <c r="O4" t="s">
-        <v>52</v>
-      </c>
-      <c r="P4" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>54</v>
-      </c>
-      <c r="R4" t="s">
-        <v>52</v>
-      </c>
-      <c r="S4" t="s">
+      <c r="AM5" t="s">
+        <v>57</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>62</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>58</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>63</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AR5" t="s">
         <v>55</v>
       </c>
-      <c r="T4" t="s">
-        <v>51</v>
-      </c>
-      <c r="U4" t="s">
-        <v>52</v>
-      </c>
-      <c r="V4" t="s">
-        <v>54</v>
-      </c>
-      <c r="W4" t="s">
-        <v>51</v>
-      </c>
-      <c r="X4" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>52</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>52</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>52</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>52</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>55</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>52</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>56</v>
-      </c>
-      <c r="AN4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AO4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>58</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>52</v>
-      </c>
-      <c r="AS4" t="s">
-        <v>52</v>
-      </c>
-      <c r="AT4" t="s">
-        <v>59</v>
-      </c>
-      <c r="AU4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>56</v>
-      </c>
-      <c r="AW4" t="s">
-        <v>60</v>
-      </c>
-      <c r="AX4" t="s">
-        <v>61</v>
-      </c>
-      <c r="AY4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D5" t="s">
-        <v>52</v>
-      </c>
-      <c r="E5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G5" t="s">
-        <v>55</v>
-      </c>
-      <c r="H5" t="s">
-        <v>52</v>
-      </c>
-      <c r="I5" t="s">
-        <v>55</v>
-      </c>
-      <c r="J5" t="s">
-        <v>55</v>
-      </c>
-      <c r="K5" t="s">
-        <v>55</v>
-      </c>
-      <c r="L5" t="s">
-        <v>57</v>
-      </c>
-      <c r="M5" t="s">
-        <v>55</v>
-      </c>
-      <c r="N5" t="s">
-        <v>56</v>
-      </c>
-      <c r="O5" t="s">
-        <v>53</v>
-      </c>
-      <c r="P5" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>63</v>
-      </c>
-      <c r="R5" t="s">
-        <v>53</v>
-      </c>
-      <c r="S5" t="s">
-        <v>57</v>
-      </c>
-      <c r="T5" t="s">
-        <v>55</v>
-      </c>
-      <c r="U5" t="s">
-        <v>55</v>
-      </c>
-      <c r="V5" t="s">
-        <v>55</v>
-      </c>
-      <c r="W5" t="s">
-        <v>52</v>
-      </c>
-      <c r="X5" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>55</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>57</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>57</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>57</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>57</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>55</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>55</v>
-      </c>
-      <c r="AH5" t="s">
-        <v>56</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>55</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AK5" t="s">
-        <v>57</v>
-      </c>
-      <c r="AL5" t="s">
-        <v>53</v>
-      </c>
-      <c r="AM5" t="s">
-        <v>58</v>
-      </c>
-      <c r="AN5" t="s">
-        <v>64</v>
-      </c>
-      <c r="AO5" t="s">
-        <v>59</v>
-      </c>
-      <c r="AP5" t="s">
+      <c r="AS5" t="s">
         <v>65</v>
       </c>
-      <c r="AQ5" t="s">
+      <c r="AT5" t="s">
         <v>66</v>
       </c>
-      <c r="AR5" t="s">
-        <v>56</v>
-      </c>
-      <c r="AS5" t="s">
+      <c r="AW5" t="s">
         <v>67</v>
-      </c>
-      <c r="AT5" t="s">
-        <v>68</v>
-      </c>
-      <c r="AW5" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H6" t="s">
+        <v>56</v>
+      </c>
+      <c r="I6" t="s">
+        <v>56</v>
+      </c>
+      <c r="J6" t="s">
+        <v>56</v>
+      </c>
+      <c r="K6" t="s">
+        <v>56</v>
+      </c>
+      <c r="L6" t="s">
+        <v>65</v>
+      </c>
+      <c r="M6" t="s">
+        <v>56</v>
+      </c>
+      <c r="N6" t="s">
+        <v>68</v>
+      </c>
+      <c r="O6" t="s">
+        <v>56</v>
+      </c>
+      <c r="P6" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q6" t="s">
         <v>55</v>
       </c>
-      <c r="B6" t="s">
+      <c r="R6" t="s">
+        <v>56</v>
+      </c>
+      <c r="S6" t="s">
+        <v>65</v>
+      </c>
+      <c r="T6" t="s">
+        <v>55</v>
+      </c>
+      <c r="U6" t="s">
+        <v>55</v>
+      </c>
+      <c r="V6" t="s">
+        <v>55</v>
+      </c>
+      <c r="W6" t="s">
+        <v>55</v>
+      </c>
+      <c r="X6" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB6" t="s">
         <v>57</v>
       </c>
-      <c r="C6" t="s">
+      <c r="AC6" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>69</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF6" t="s">
         <v>55</v>
       </c>
-      <c r="D6" t="s">
+      <c r="AG6" t="s">
         <v>55</v>
       </c>
-      <c r="E6" t="s">
-        <v>57</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="AH6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AI6" t="s">
         <v>55</v>
       </c>
-      <c r="G6" t="s">
-        <v>57</v>
-      </c>
-      <c r="H6" t="s">
-        <v>57</v>
-      </c>
-      <c r="I6" t="s">
-        <v>57</v>
-      </c>
-      <c r="J6" t="s">
-        <v>57</v>
-      </c>
-      <c r="K6" t="s">
-        <v>57</v>
-      </c>
-      <c r="L6" t="s">
-        <v>67</v>
-      </c>
-      <c r="M6" t="s">
-        <v>57</v>
-      </c>
-      <c r="N6" t="s">
-        <v>70</v>
-      </c>
-      <c r="O6" t="s">
-        <v>57</v>
-      </c>
-      <c r="P6" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q6" t="s">
+      <c r="AJ6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AL6" t="s">
         <v>56</v>
       </c>
-      <c r="R6" t="s">
-        <v>57</v>
-      </c>
-      <c r="S6" t="s">
-        <v>67</v>
-      </c>
-      <c r="T6" t="s">
-        <v>56</v>
-      </c>
-      <c r="U6" t="s">
-        <v>56</v>
-      </c>
-      <c r="V6" t="s">
-        <v>56</v>
-      </c>
-      <c r="W6" t="s">
-        <v>56</v>
-      </c>
-      <c r="X6" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>56</v>
-      </c>
-      <c r="AA6" t="s">
+      <c r="AM6" t="s">
         <v>63</v>
       </c>
-      <c r="AB6" t="s">
-        <v>58</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD6" t="s">
+      <c r="AN6" t="s">
         <v>71</v>
       </c>
-      <c r="AE6" t="s">
-        <v>71</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>56</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>56</v>
-      </c>
-      <c r="AH6" t="s">
+      <c r="AO6" t="s">
+        <v>62</v>
+      </c>
+      <c r="AP6" t="s">
         <v>72</v>
       </c>
-      <c r="AI6" t="s">
-        <v>56</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>67</v>
-      </c>
-      <c r="AK6" t="s">
-        <v>56</v>
-      </c>
-      <c r="AL6" t="s">
-        <v>57</v>
-      </c>
-      <c r="AM6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AN6" t="s">
+      <c r="AQ6" t="s">
         <v>73</v>
       </c>
-      <c r="AO6" t="s">
-        <v>64</v>
-      </c>
-      <c r="AP6" t="s">
+      <c r="AR6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AT6" t="s">
         <v>74</v>
-      </c>
-      <c r="AQ6" t="s">
-        <v>75</v>
-      </c>
-      <c r="AR6" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS6" t="s">
-        <v>68</v>
-      </c>
-      <c r="AT6" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G7" t="s">
+        <v>61</v>
+      </c>
+      <c r="H7" t="s">
+        <v>65</v>
+      </c>
+      <c r="I7" t="s">
+        <v>65</v>
+      </c>
+      <c r="J7" t="s">
+        <v>55</v>
+      </c>
+      <c r="K7" t="s">
+        <v>69</v>
+      </c>
+      <c r="L7" t="s">
+        <v>69</v>
+      </c>
+      <c r="M7" t="s">
+        <v>55</v>
+      </c>
+      <c r="N7" t="s">
+        <v>58</v>
+      </c>
+      <c r="O7" t="s">
+        <v>55</v>
+      </c>
+      <c r="P7" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>68</v>
+      </c>
+      <c r="R7" t="s">
+        <v>65</v>
+      </c>
+      <c r="S7" t="s">
         <v>57</v>
       </c>
-      <c r="B7" t="s">
+      <c r="T7" t="s">
+        <v>65</v>
+      </c>
+      <c r="U7" t="s">
+        <v>69</v>
+      </c>
+      <c r="V7" t="s">
+        <v>69</v>
+      </c>
+      <c r="W7" t="s">
+        <v>57</v>
+      </c>
+      <c r="X7" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>65</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>75</v>
+      </c>
+      <c r="AE7" t="s">
         <v>63</v>
       </c>
-      <c r="C7" t="s">
+      <c r="AF7" t="s">
+        <v>65</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>69</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AI7" t="s">
         <v>57</v>
       </c>
-      <c r="D7" t="s">
+      <c r="AJ7" t="s">
         <v>57</v>
       </c>
-      <c r="E7" t="s">
-        <v>63</v>
-      </c>
-      <c r="F7" t="s">
-        <v>67</v>
-      </c>
-      <c r="G7" t="s">
-        <v>63</v>
-      </c>
-      <c r="H7" t="s">
-        <v>67</v>
-      </c>
-      <c r="I7" t="s">
-        <v>67</v>
-      </c>
-      <c r="J7" t="s">
-        <v>56</v>
-      </c>
-      <c r="K7" t="s">
-        <v>71</v>
-      </c>
-      <c r="L7" t="s">
-        <v>71</v>
-      </c>
-      <c r="M7" t="s">
-        <v>56</v>
-      </c>
-      <c r="N7" t="s">
+      <c r="AK7" t="s">
+        <v>58</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>58</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>76</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>77</v>
+      </c>
+      <c r="AP7" t="s">
+        <v>78</v>
+      </c>
+      <c r="AQ7" t="s">
         <v>59</v>
       </c>
-      <c r="O7" t="s">
-        <v>56</v>
-      </c>
-      <c r="P7" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>70</v>
-      </c>
-      <c r="R7" t="s">
-        <v>67</v>
-      </c>
-      <c r="S7" t="s">
-        <v>58</v>
-      </c>
-      <c r="T7" t="s">
-        <v>67</v>
-      </c>
-      <c r="U7" t="s">
-        <v>71</v>
-      </c>
-      <c r="V7" t="s">
-        <v>71</v>
-      </c>
-      <c r="W7" t="s">
-        <v>58</v>
-      </c>
-      <c r="X7" t="s">
-        <v>57</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>71</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>77</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>67</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>77</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>65</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>67</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>71</v>
-      </c>
-      <c r="AH7" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI7" t="s">
-        <v>58</v>
-      </c>
-      <c r="AJ7" t="s">
-        <v>58</v>
-      </c>
-      <c r="AK7" t="s">
-        <v>59</v>
-      </c>
-      <c r="AL7" t="s">
-        <v>59</v>
-      </c>
-      <c r="AM7" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN7" t="s">
-        <v>78</v>
-      </c>
-      <c r="AO7" t="s">
+      <c r="AR7" t="s">
         <v>79</v>
       </c>
-      <c r="AP7" t="s">
+      <c r="AS7" t="s">
         <v>80</v>
       </c>
-      <c r="AQ7" t="s">
-        <v>60</v>
-      </c>
-      <c r="AR7" t="s">
+      <c r="AT7" t="s">
         <v>81</v>
-      </c>
-      <c r="AS7" t="s">
-        <v>82</v>
-      </c>
-      <c r="AT7" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I8" t="s">
+        <v>75</v>
+      </c>
+      <c r="J8" t="s">
+        <v>57</v>
+      </c>
+      <c r="K8" t="s">
+        <v>57</v>
+      </c>
+      <c r="L8" t="s">
+        <v>57</v>
+      </c>
+      <c r="M8" t="s">
+        <v>57</v>
+      </c>
+      <c r="N8" t="s">
+        <v>57</v>
+      </c>
+      <c r="O8" t="s">
+        <v>69</v>
+      </c>
+      <c r="P8" t="s">
         <v>58</v>
       </c>
-      <c r="G8" t="s">
+      <c r="Q8" t="s">
+        <v>65</v>
+      </c>
+      <c r="R8" t="s">
+        <v>70</v>
+      </c>
+      <c r="S8" t="s">
+        <v>82</v>
+      </c>
+      <c r="T8" t="s">
+        <v>69</v>
+      </c>
+      <c r="U8" t="s">
+        <v>70</v>
+      </c>
+      <c r="V8" t="s">
         <v>58</v>
       </c>
-      <c r="H8" t="s">
-        <v>71</v>
-      </c>
-      <c r="I8" t="s">
-        <v>77</v>
-      </c>
-      <c r="J8" t="s">
-        <v>58</v>
-      </c>
-      <c r="K8" t="s">
-        <v>58</v>
-      </c>
-      <c r="L8" t="s">
-        <v>58</v>
-      </c>
-      <c r="M8" t="s">
-        <v>58</v>
-      </c>
-      <c r="N8" t="s">
-        <v>58</v>
-      </c>
-      <c r="O8" t="s">
-        <v>71</v>
-      </c>
-      <c r="P8" t="s">
+      <c r="W8" t="s">
+        <v>54</v>
+      </c>
+      <c r="X8" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>66</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>83</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>69</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>57</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>63</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>75</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>75</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>84</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>76</v>
+      </c>
+      <c r="AP8" t="s">
         <v>59</v>
       </c>
-      <c r="Q8" t="s">
-        <v>67</v>
-      </c>
-      <c r="R8" t="s">
-        <v>72</v>
-      </c>
-      <c r="S8" t="s">
-        <v>84</v>
-      </c>
-      <c r="T8" t="s">
-        <v>71</v>
-      </c>
-      <c r="U8" t="s">
-        <v>72</v>
-      </c>
-      <c r="V8" t="s">
-        <v>59</v>
-      </c>
-      <c r="W8" t="s">
-        <v>55</v>
-      </c>
-      <c r="X8" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>74</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>64</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>71</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC8" t="s">
-        <v>71</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>68</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>85</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>71</v>
-      </c>
-      <c r="AG8" t="s">
-        <v>58</v>
-      </c>
-      <c r="AH8" t="s">
-        <v>64</v>
-      </c>
-      <c r="AI8" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJ8" t="s">
-        <v>65</v>
-      </c>
-      <c r="AK8" t="s">
-        <v>77</v>
-      </c>
-      <c r="AL8" t="s">
-        <v>77</v>
-      </c>
-      <c r="AM8" t="s">
+      <c r="AQ8" t="s">
+        <v>81</v>
+      </c>
+      <c r="AR8" t="s">
+        <v>80</v>
+      </c>
+      <c r="AS8" t="s">
         <v>86</v>
-      </c>
-      <c r="AN8" t="s">
-        <v>87</v>
-      </c>
-      <c r="AO8" t="s">
-        <v>78</v>
-      </c>
-      <c r="AP8" t="s">
-        <v>60</v>
-      </c>
-      <c r="AQ8" t="s">
-        <v>83</v>
-      </c>
-      <c r="AR8" t="s">
-        <v>82</v>
-      </c>
-      <c r="AS8" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E9" t="s">
+        <v>69</v>
+      </c>
+      <c r="F9" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I9" t="s">
+        <v>63</v>
+      </c>
+      <c r="J9" t="s">
+        <v>63</v>
+      </c>
+      <c r="K9" t="s">
+        <v>63</v>
+      </c>
+      <c r="L9" t="s">
+        <v>75</v>
+      </c>
+      <c r="M9" t="s">
+        <v>75</v>
+      </c>
+      <c r="N9" t="s">
+        <v>72</v>
+      </c>
+      <c r="O9" t="s">
+        <v>75</v>
+      </c>
+      <c r="P9" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>75</v>
+      </c>
+      <c r="R9" t="s">
+        <v>82</v>
+      </c>
+      <c r="S9" t="s">
+        <v>63</v>
+      </c>
+      <c r="T9" t="s">
+        <v>75</v>
+      </c>
+      <c r="U9" t="s">
+        <v>75</v>
+      </c>
+      <c r="V9" t="s">
+        <v>75</v>
+      </c>
+      <c r="W9" t="s">
+        <v>75</v>
+      </c>
+      <c r="X9" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB9" t="s">
         <v>71</v>
       </c>
-      <c r="C9" t="s">
-        <v>59</v>
-      </c>
-      <c r="D9" t="s">
-        <v>70</v>
-      </c>
-      <c r="E9" t="s">
-        <v>71</v>
-      </c>
-      <c r="F9" t="s">
-        <v>65</v>
-      </c>
-      <c r="G9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H9" t="s">
-        <v>58</v>
-      </c>
-      <c r="I9" t="s">
-        <v>65</v>
-      </c>
-      <c r="J9" t="s">
-        <v>65</v>
-      </c>
-      <c r="K9" t="s">
-        <v>65</v>
-      </c>
-      <c r="L9" t="s">
-        <v>77</v>
-      </c>
-      <c r="M9" t="s">
-        <v>77</v>
-      </c>
-      <c r="N9" t="s">
-        <v>74</v>
-      </c>
-      <c r="O9" t="s">
-        <v>77</v>
-      </c>
-      <c r="P9" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>77</v>
-      </c>
-      <c r="R9" t="s">
-        <v>84</v>
-      </c>
-      <c r="S9" t="s">
-        <v>65</v>
-      </c>
-      <c r="T9" t="s">
-        <v>77</v>
-      </c>
-      <c r="U9" t="s">
-        <v>77</v>
-      </c>
-      <c r="V9" t="s">
-        <v>77</v>
-      </c>
-      <c r="W9" t="s">
-        <v>77</v>
-      </c>
-      <c r="X9" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y9" t="s">
+      <c r="AC9" t="s">
+        <v>75</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>87</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>75</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>75</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>88</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>88</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>79</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>80</v>
+      </c>
+      <c r="AO9" t="s">
         <v>64</v>
       </c>
-      <c r="Z9" t="s">
+      <c r="AP9" t="s">
         <v>89</v>
       </c>
-      <c r="AA9" t="s">
-        <v>77</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>73</v>
-      </c>
-      <c r="AC9" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>89</v>
-      </c>
-      <c r="AE9" t="s">
-        <v>68</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>77</v>
-      </c>
-      <c r="AG9" t="s">
-        <v>77</v>
-      </c>
-      <c r="AH9" t="s">
-        <v>85</v>
-      </c>
-      <c r="AI9" t="s">
-        <v>77</v>
-      </c>
-      <c r="AJ9" t="s">
+      <c r="AQ9" t="s">
         <v>90</v>
       </c>
-      <c r="AK9" t="s">
-        <v>90</v>
-      </c>
-      <c r="AL9" t="s">
-        <v>68</v>
-      </c>
-      <c r="AM9" t="s">
+      <c r="AR9" t="s">
         <v>81</v>
-      </c>
-      <c r="AN9" t="s">
-        <v>82</v>
-      </c>
-      <c r="AO9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AP9" t="s">
-        <v>91</v>
-      </c>
-      <c r="AQ9" t="s">
-        <v>92</v>
-      </c>
-      <c r="AR9" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" t="s">
+        <v>91</v>
+      </c>
+      <c r="G10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H10" t="s">
+        <v>75</v>
+      </c>
+      <c r="I10" t="s">
+        <v>72</v>
+      </c>
+      <c r="J10" t="s">
+        <v>72</v>
+      </c>
+      <c r="K10" t="s">
+        <v>62</v>
+      </c>
+      <c r="L10" t="s">
+        <v>63</v>
+      </c>
+      <c r="M10" t="s">
+        <v>72</v>
+      </c>
+      <c r="N10" t="s">
+        <v>62</v>
+      </c>
+      <c r="O10" t="s">
+        <v>63</v>
+      </c>
+      <c r="P10" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>72</v>
+      </c>
+      <c r="R10" t="s">
+        <v>63</v>
+      </c>
+      <c r="S10" t="s">
+        <v>62</v>
+      </c>
+      <c r="T10" t="s">
+        <v>91</v>
+      </c>
+      <c r="U10" t="s">
+        <v>92</v>
+      </c>
+      <c r="V10" t="s">
+        <v>63</v>
+      </c>
+      <c r="W10" t="s">
+        <v>72</v>
+      </c>
+      <c r="X10" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y10" t="s">
         <v>71</v>
       </c>
-      <c r="B10" t="s">
+      <c r="Z10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>84</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>87</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>82</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>92</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>71</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>78</v>
+      </c>
+      <c r="AM10" t="s">
+        <v>87</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>89</v>
+      </c>
+      <c r="AO10" t="s">
+        <v>93</v>
+      </c>
+      <c r="AP10" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" t="s">
+        <v>75</v>
+      </c>
+      <c r="F11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" t="s">
+        <v>82</v>
+      </c>
+      <c r="H11" t="s">
+        <v>63</v>
+      </c>
+      <c r="I11" t="s">
+        <v>92</v>
+      </c>
+      <c r="J11" t="s">
+        <v>62</v>
+      </c>
+      <c r="K11" t="s">
+        <v>83</v>
+      </c>
+      <c r="L11" t="s">
+        <v>62</v>
+      </c>
+      <c r="M11" t="s">
+        <v>62</v>
+      </c>
+      <c r="N11" t="s">
+        <v>66</v>
+      </c>
+      <c r="O11" t="s">
+        <v>72</v>
+      </c>
+      <c r="P11" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>62</v>
+      </c>
+      <c r="R11" t="s">
+        <v>62</v>
+      </c>
+      <c r="S11" t="s">
+        <v>71</v>
+      </c>
+      <c r="T11" t="s">
+        <v>62</v>
+      </c>
+      <c r="U11" t="s">
+        <v>66</v>
+      </c>
+      <c r="V11" t="s">
+        <v>62</v>
+      </c>
+      <c r="W11" t="s">
+        <v>62</v>
+      </c>
+      <c r="X11" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>95</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE11" t="s">
         <v>55</v>
       </c>
-      <c r="C10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="AF11" t="s">
+        <v>95</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>66</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>79</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>95</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>84</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>96</v>
+      </c>
+      <c r="AM11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>97</v>
+      </c>
+      <c r="AO11" t="s">
         <v>74</v>
       </c>
-      <c r="E10" t="s">
-        <v>55</v>
-      </c>
-      <c r="F10" t="s">
-        <v>93</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="AP11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" t="s">
+        <v>92</v>
+      </c>
+      <c r="G12" t="s">
+        <v>62</v>
+      </c>
+      <c r="H12" t="s">
+        <v>72</v>
+      </c>
+      <c r="I12" t="s">
+        <v>66</v>
+      </c>
+      <c r="J12" t="s">
+        <v>71</v>
+      </c>
+      <c r="K12" t="s">
+        <v>87</v>
+      </c>
+      <c r="L12" t="s">
+        <v>66</v>
+      </c>
+      <c r="M12" t="s">
+        <v>71</v>
+      </c>
+      <c r="N12" t="s">
+        <v>87</v>
+      </c>
+      <c r="O12" t="s">
+        <v>76</v>
+      </c>
+      <c r="P12" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>66</v>
+      </c>
+      <c r="R12" t="s">
+        <v>66</v>
+      </c>
+      <c r="S12" t="s">
+        <v>66</v>
+      </c>
+      <c r="T12" t="s">
+        <v>88</v>
+      </c>
+      <c r="U12" t="s">
         <v>77</v>
       </c>
-      <c r="H10" t="s">
-        <v>77</v>
-      </c>
-      <c r="I10" t="s">
-        <v>74</v>
-      </c>
-      <c r="J10" t="s">
-        <v>74</v>
-      </c>
-      <c r="K10" t="s">
-        <v>64</v>
-      </c>
-      <c r="L10" t="s">
-        <v>65</v>
-      </c>
-      <c r="M10" t="s">
-        <v>74</v>
-      </c>
-      <c r="N10" t="s">
-        <v>64</v>
-      </c>
-      <c r="O10" t="s">
-        <v>65</v>
-      </c>
-      <c r="P10" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>74</v>
-      </c>
-      <c r="R10" t="s">
-        <v>65</v>
-      </c>
-      <c r="S10" t="s">
-        <v>64</v>
-      </c>
-      <c r="T10" t="s">
-        <v>93</v>
-      </c>
-      <c r="U10" t="s">
-        <v>94</v>
-      </c>
-      <c r="V10" t="s">
-        <v>65</v>
-      </c>
-      <c r="W10" t="s">
-        <v>74</v>
-      </c>
-      <c r="X10" t="s">
-        <v>94</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>73</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>79</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>90</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>74</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>86</v>
-      </c>
-      <c r="AE10" t="s">
-        <v>89</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>74</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH10" t="s">
-        <v>90</v>
-      </c>
-      <c r="AI10" t="s">
-        <v>65</v>
-      </c>
-      <c r="AJ10" t="s">
-        <v>94</v>
-      </c>
-      <c r="AK10" t="s">
-        <v>73</v>
-      </c>
-      <c r="AL10" t="s">
-        <v>80</v>
-      </c>
-      <c r="AM10" t="s">
-        <v>89</v>
-      </c>
-      <c r="AN10" t="s">
-        <v>91</v>
-      </c>
-      <c r="AO10" t="s">
+      <c r="V12" t="s">
+        <v>71</v>
+      </c>
+      <c r="W12" t="s">
+        <v>71</v>
+      </c>
+      <c r="X12" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>76</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>76</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>85</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>78</v>
+      </c>
+      <c r="AK12" t="s">
         <v>95</v>
       </c>
-      <c r="AP10" t="s">
-        <v>96</v>
-      </c>
-      <c r="AQ10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>65</v>
-      </c>
-      <c r="B11" t="s">
-        <v>77</v>
-      </c>
-      <c r="C11" t="s">
-        <v>74</v>
-      </c>
-      <c r="D11" t="s">
-        <v>64</v>
-      </c>
-      <c r="E11" t="s">
-        <v>77</v>
-      </c>
-      <c r="F11" t="s">
-        <v>64</v>
-      </c>
-      <c r="G11" t="s">
-        <v>84</v>
-      </c>
-      <c r="H11" t="s">
-        <v>65</v>
-      </c>
-      <c r="I11" t="s">
-        <v>94</v>
-      </c>
-      <c r="J11" t="s">
-        <v>64</v>
-      </c>
-      <c r="K11" t="s">
-        <v>85</v>
-      </c>
-      <c r="L11" t="s">
-        <v>64</v>
-      </c>
-      <c r="M11" t="s">
-        <v>64</v>
-      </c>
-      <c r="N11" t="s">
-        <v>68</v>
-      </c>
-      <c r="O11" t="s">
-        <v>74</v>
-      </c>
-      <c r="P11" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>64</v>
-      </c>
-      <c r="R11" t="s">
-        <v>64</v>
-      </c>
-      <c r="S11" t="s">
-        <v>73</v>
-      </c>
-      <c r="T11" t="s">
-        <v>64</v>
-      </c>
-      <c r="U11" t="s">
-        <v>68</v>
-      </c>
-      <c r="V11" t="s">
-        <v>64</v>
-      </c>
-      <c r="W11" t="s">
-        <v>64</v>
-      </c>
-      <c r="X11" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>94</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>98</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>94</v>
-      </c>
-      <c r="AB11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AC11" t="s">
-        <v>68</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>76</v>
-      </c>
-      <c r="AE11" t="s">
-        <v>56</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>98</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>68</v>
-      </c>
-      <c r="AH11" t="s">
+      <c r="AL12" t="s">
+        <v>99</v>
+      </c>
+      <c r="AM12" t="s">
+        <v>100</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>101</v>
+      </c>
+      <c r="AO12" t="s">
         <v>81</v>
-      </c>
-      <c r="AI11" t="s">
-        <v>98</v>
-      </c>
-      <c r="AJ11" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK11" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL11" t="s">
-        <v>99</v>
-      </c>
-      <c r="AM11" t="s">
-        <v>79</v>
-      </c>
-      <c r="AN11" t="s">
-        <v>100</v>
-      </c>
-      <c r="AO11" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>74</v>
-      </c>
-      <c r="B12" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12" t="s">
-        <v>64</v>
-      </c>
-      <c r="D12" t="s">
-        <v>73</v>
-      </c>
-      <c r="E12" t="s">
-        <v>65</v>
-      </c>
-      <c r="F12" t="s">
-        <v>94</v>
-      </c>
-      <c r="G12" t="s">
-        <v>64</v>
-      </c>
-      <c r="H12" t="s">
-        <v>74</v>
-      </c>
-      <c r="I12" t="s">
-        <v>68</v>
-      </c>
-      <c r="J12" t="s">
-        <v>73</v>
-      </c>
-      <c r="K12" t="s">
-        <v>89</v>
-      </c>
-      <c r="L12" t="s">
-        <v>68</v>
-      </c>
-      <c r="M12" t="s">
-        <v>73</v>
-      </c>
-      <c r="N12" t="s">
-        <v>89</v>
-      </c>
-      <c r="O12" t="s">
-        <v>78</v>
-      </c>
-      <c r="P12" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>68</v>
-      </c>
-      <c r="R12" t="s">
-        <v>68</v>
-      </c>
-      <c r="S12" t="s">
-        <v>68</v>
-      </c>
-      <c r="T12" t="s">
-        <v>90</v>
-      </c>
-      <c r="U12" t="s">
-        <v>79</v>
-      </c>
-      <c r="V12" t="s">
-        <v>73</v>
-      </c>
-      <c r="W12" t="s">
-        <v>73</v>
-      </c>
-      <c r="X12" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>78</v>
-      </c>
-      <c r="Z12" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AB12" t="s">
-        <v>101</v>
-      </c>
-      <c r="AC12" t="s">
-        <v>89</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>87</v>
-      </c>
-      <c r="AE12" t="s">
-        <v>78</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>80</v>
-      </c>
-      <c r="AG12" t="s">
-        <v>78</v>
-      </c>
-      <c r="AH12" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI12" t="s">
-        <v>87</v>
-      </c>
-      <c r="AJ12" t="s">
-        <v>80</v>
-      </c>
-      <c r="AK12" t="s">
-        <v>98</v>
-      </c>
-      <c r="AL12" t="s">
-        <v>102</v>
-      </c>
-      <c r="AM12" t="s">
-        <v>103</v>
-      </c>
-      <c r="AN12" t="s">
-        <v>104</v>
-      </c>
-      <c r="AO12" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" t="s">
+        <v>92</v>
+      </c>
+      <c r="E13" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" t="s">
+        <v>66</v>
+      </c>
+      <c r="G13" t="s">
+        <v>66</v>
+      </c>
+      <c r="H13" t="s">
+        <v>71</v>
+      </c>
+      <c r="I13" t="s">
+        <v>84</v>
+      </c>
+      <c r="J13" t="s">
+        <v>76</v>
+      </c>
+      <c r="K13" t="s">
+        <v>77</v>
+      </c>
+      <c r="L13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M13" t="s">
+        <v>66</v>
+      </c>
+      <c r="N13" t="s">
+        <v>76</v>
+      </c>
+      <c r="O13" t="s">
+        <v>77</v>
+      </c>
+      <c r="P13" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>76</v>
+      </c>
+      <c r="R13" t="s">
+        <v>75</v>
+      </c>
+      <c r="S13" t="s">
+        <v>77</v>
+      </c>
+      <c r="T13" t="s">
+        <v>87</v>
+      </c>
+      <c r="U13" t="s">
+        <v>84</v>
+      </c>
+      <c r="V13" t="s">
+        <v>76</v>
+      </c>
+      <c r="W13" t="s">
+        <v>76</v>
+      </c>
+      <c r="X13" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>95</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>95</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>85</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>79</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>93</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>85</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>85</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>80</v>
+      </c>
+      <c r="AM13" t="s">
+        <v>102</v>
+      </c>
+      <c r="AN13" t="s">
         <v>64</v>
       </c>
-      <c r="B13" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" t="s">
-        <v>73</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="AO13" t="s">
         <v>94</v>
-      </c>
-      <c r="E13" t="s">
-        <v>73</v>
-      </c>
-      <c r="F13" t="s">
-        <v>68</v>
-      </c>
-      <c r="G13" t="s">
-        <v>68</v>
-      </c>
-      <c r="H13" t="s">
-        <v>73</v>
-      </c>
-      <c r="I13" t="s">
-        <v>86</v>
-      </c>
-      <c r="J13" t="s">
-        <v>78</v>
-      </c>
-      <c r="K13" t="s">
-        <v>79</v>
-      </c>
-      <c r="L13" t="s">
-        <v>89</v>
-      </c>
-      <c r="M13" t="s">
-        <v>68</v>
-      </c>
-      <c r="N13" t="s">
-        <v>78</v>
-      </c>
-      <c r="O13" t="s">
-        <v>79</v>
-      </c>
-      <c r="P13" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>78</v>
-      </c>
-      <c r="R13" t="s">
-        <v>77</v>
-      </c>
-      <c r="S13" t="s">
-        <v>79</v>
-      </c>
-      <c r="T13" t="s">
-        <v>89</v>
-      </c>
-      <c r="U13" t="s">
-        <v>86</v>
-      </c>
-      <c r="V13" t="s">
-        <v>78</v>
-      </c>
-      <c r="W13" t="s">
-        <v>78</v>
-      </c>
-      <c r="X13" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z13" t="s">
-        <v>76</v>
-      </c>
-      <c r="AA13" t="s">
-        <v>98</v>
-      </c>
-      <c r="AB13" t="s">
-        <v>98</v>
-      </c>
-      <c r="AC13" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>99</v>
-      </c>
-      <c r="AE13" t="s">
-        <v>80</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>87</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>81</v>
-      </c>
-      <c r="AH13" t="s">
-        <v>76</v>
-      </c>
-      <c r="AI13" t="s">
-        <v>95</v>
-      </c>
-      <c r="AJ13" t="s">
-        <v>87</v>
-      </c>
-      <c r="AK13" t="s">
-        <v>87</v>
-      </c>
-      <c r="AL13" t="s">
-        <v>82</v>
-      </c>
-      <c r="AM13" t="s">
-        <v>62</v>
-      </c>
-      <c r="AN13" t="s">
-        <v>66</v>
-      </c>
-      <c r="AO13" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>83</v>
+      </c>
+      <c r="B14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" t="s">
+        <v>92</v>
+      </c>
+      <c r="D14" t="s">
+        <v>66</v>
+      </c>
+      <c r="E14" t="s">
+        <v>92</v>
+      </c>
+      <c r="F14" t="s">
+        <v>87</v>
+      </c>
+      <c r="G14" t="s">
+        <v>87</v>
+      </c>
+      <c r="H14" t="s">
+        <v>66</v>
+      </c>
+      <c r="I14" t="s">
+        <v>95</v>
+      </c>
+      <c r="J14" t="s">
+        <v>98</v>
+      </c>
+      <c r="K14" t="s">
+        <v>95</v>
+      </c>
+      <c r="L14" t="s">
+        <v>77</v>
+      </c>
+      <c r="M14" t="s">
+        <v>76</v>
+      </c>
+      <c r="N14" t="s">
+        <v>77</v>
+      </c>
+      <c r="O14" t="s">
+        <v>84</v>
+      </c>
+      <c r="P14" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>79</v>
+      </c>
+      <c r="R14" t="s">
+        <v>77</v>
+      </c>
+      <c r="S14" t="s">
+        <v>79</v>
+      </c>
+      <c r="T14" t="s">
+        <v>95</v>
+      </c>
+      <c r="U14" t="s">
+        <v>74</v>
+      </c>
+      <c r="V14" t="s">
+        <v>79</v>
+      </c>
+      <c r="W14" t="s">
+        <v>77</v>
+      </c>
+      <c r="X14" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB14" t="s">
         <v>85</v>
       </c>
-      <c r="B14" t="s">
+      <c r="AC14" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>99</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>96</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>99</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>95</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>103</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>100</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>103</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>103</v>
+      </c>
+      <c r="AL14" t="s">
+        <v>60</v>
+      </c>
+      <c r="AM14" t="s">
+        <v>93</v>
+      </c>
+      <c r="AN14" t="s">
+        <v>104</v>
+      </c>
+      <c r="AO14" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>92</v>
+      </c>
+      <c r="B15" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" t="s">
+        <v>87</v>
+      </c>
+      <c r="E15" t="s">
+        <v>66</v>
+      </c>
+      <c r="F15" t="s">
+        <v>77</v>
+      </c>
+      <c r="G15" t="s">
+        <v>76</v>
+      </c>
+      <c r="H15" t="s">
+        <v>77</v>
+      </c>
+      <c r="I15" t="s">
+        <v>78</v>
+      </c>
+      <c r="J15" t="s">
+        <v>79</v>
+      </c>
+      <c r="K15" t="s">
+        <v>78</v>
+      </c>
+      <c r="L15" t="s">
+        <v>84</v>
+      </c>
+      <c r="M15" t="s">
+        <v>84</v>
+      </c>
+      <c r="N15" t="s">
+        <v>98</v>
+      </c>
+      <c r="O15" t="s">
+        <v>95</v>
+      </c>
+      <c r="P15" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>95</v>
+      </c>
+      <c r="R15" t="s">
+        <v>84</v>
+      </c>
+      <c r="S15" t="s">
+        <v>95</v>
+      </c>
+      <c r="T15" t="s">
+        <v>78</v>
+      </c>
+      <c r="U15" t="s">
+        <v>85</v>
+      </c>
+      <c r="V15" t="s">
+        <v>95</v>
+      </c>
+      <c r="W15" t="s">
+        <v>84</v>
+      </c>
+      <c r="X15" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>85</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF15" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>74</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>93</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>73</v>
+      </c>
+      <c r="AJ15" t="s">
         <v>64</v>
       </c>
-      <c r="C14" t="s">
+      <c r="AK15" t="s">
+        <v>64</v>
+      </c>
+      <c r="AL15" t="s">
+        <v>89</v>
+      </c>
+      <c r="AM15" t="s">
         <v>94</v>
       </c>
-      <c r="D14" t="s">
-        <v>68</v>
-      </c>
-      <c r="E14" t="s">
-        <v>94</v>
-      </c>
-      <c r="F14" t="s">
-        <v>89</v>
-      </c>
-      <c r="G14" t="s">
-        <v>89</v>
-      </c>
-      <c r="H14" t="s">
-        <v>68</v>
-      </c>
-      <c r="I14" t="s">
-        <v>98</v>
-      </c>
-      <c r="J14" t="s">
-        <v>101</v>
-      </c>
-      <c r="K14" t="s">
-        <v>98</v>
-      </c>
-      <c r="L14" t="s">
-        <v>79</v>
-      </c>
-      <c r="M14" t="s">
-        <v>78</v>
-      </c>
-      <c r="N14" t="s">
-        <v>79</v>
-      </c>
-      <c r="O14" t="s">
-        <v>86</v>
-      </c>
-      <c r="P14" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q14" t="s">
+      <c r="AN15" t="s">
         <v>81</v>
-      </c>
-      <c r="R14" t="s">
-        <v>79</v>
-      </c>
-      <c r="S14" t="s">
-        <v>81</v>
-      </c>
-      <c r="T14" t="s">
-        <v>98</v>
-      </c>
-      <c r="U14" t="s">
-        <v>76</v>
-      </c>
-      <c r="V14" t="s">
-        <v>81</v>
-      </c>
-      <c r="W14" t="s">
-        <v>79</v>
-      </c>
-      <c r="X14" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>81</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>102</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB14" t="s">
-        <v>87</v>
-      </c>
-      <c r="AC14" t="s">
-        <v>81</v>
-      </c>
-      <c r="AD14" t="s">
-        <v>102</v>
-      </c>
-      <c r="AE14" t="s">
-        <v>99</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>102</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>98</v>
-      </c>
-      <c r="AH14" t="s">
-        <v>105</v>
-      </c>
-      <c r="AI14" t="s">
-        <v>103</v>
-      </c>
-      <c r="AJ14" t="s">
-        <v>105</v>
-      </c>
-      <c r="AK14" t="s">
-        <v>105</v>
-      </c>
-      <c r="AL14" t="s">
-        <v>62</v>
-      </c>
-      <c r="AM14" t="s">
-        <v>95</v>
-      </c>
-      <c r="AN14" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>94</v>
-      </c>
-      <c r="B15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C15" t="s">
-        <v>68</v>
-      </c>
-      <c r="D15" t="s">
-        <v>89</v>
-      </c>
-      <c r="E15" t="s">
-        <v>68</v>
-      </c>
-      <c r="F15" t="s">
-        <v>79</v>
-      </c>
-      <c r="G15" t="s">
-        <v>78</v>
-      </c>
-      <c r="H15" t="s">
-        <v>79</v>
-      </c>
-      <c r="I15" t="s">
-        <v>80</v>
-      </c>
-      <c r="J15" t="s">
-        <v>81</v>
-      </c>
-      <c r="K15" t="s">
-        <v>80</v>
-      </c>
-      <c r="L15" t="s">
-        <v>86</v>
-      </c>
-      <c r="M15" t="s">
-        <v>86</v>
-      </c>
-      <c r="N15" t="s">
-        <v>101</v>
-      </c>
-      <c r="O15" t="s">
-        <v>98</v>
-      </c>
-      <c r="P15" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>98</v>
-      </c>
-      <c r="R15" t="s">
-        <v>86</v>
-      </c>
-      <c r="S15" t="s">
-        <v>98</v>
-      </c>
-      <c r="T15" t="s">
-        <v>80</v>
-      </c>
-      <c r="U15" t="s">
-        <v>87</v>
-      </c>
-      <c r="V15" t="s">
-        <v>98</v>
-      </c>
-      <c r="W15" t="s">
-        <v>86</v>
-      </c>
-      <c r="X15" t="s">
-        <v>86</v>
-      </c>
-      <c r="Y15" t="s">
-        <v>76</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>90</v>
-      </c>
-      <c r="AA15" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB15" t="s">
-        <v>79</v>
-      </c>
-      <c r="AC15" t="s">
-        <v>76</v>
-      </c>
-      <c r="AD15" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE15" t="s">
-        <v>102</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>93</v>
-      </c>
-      <c r="AG15" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH15" t="s">
-        <v>95</v>
-      </c>
-      <c r="AI15" t="s">
-        <v>75</v>
-      </c>
-      <c r="AJ15" t="s">
-        <v>66</v>
-      </c>
-      <c r="AK15" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM15" t="s">
-        <v>96</v>
-      </c>
-      <c r="AN15" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B16" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C16" t="s">
+        <v>87</v>
+      </c>
+      <c r="D16" t="s">
+        <v>76</v>
+      </c>
+      <c r="E16" t="s">
+        <v>76</v>
+      </c>
+      <c r="F16" t="s">
+        <v>84</v>
+      </c>
+      <c r="G16" t="s">
+        <v>77</v>
+      </c>
+      <c r="H16" t="s">
+        <v>79</v>
+      </c>
+      <c r="I16" t="s">
+        <v>74</v>
+      </c>
+      <c r="J16" t="s">
+        <v>78</v>
+      </c>
+      <c r="K16" t="s">
+        <v>103</v>
+      </c>
+      <c r="L16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M16" t="s">
+        <v>79</v>
+      </c>
+      <c r="N16" t="s">
+        <v>84</v>
+      </c>
+      <c r="O16" t="s">
+        <v>78</v>
+      </c>
+      <c r="P16" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>74</v>
+      </c>
+      <c r="R16" t="s">
+        <v>95</v>
+      </c>
+      <c r="S16" t="s">
+        <v>74</v>
+      </c>
+      <c r="T16" t="s">
+        <v>74</v>
+      </c>
+      <c r="U16" t="s">
+        <v>103</v>
+      </c>
+      <c r="V16" t="s">
+        <v>74</v>
+      </c>
+      <c r="W16" t="s">
+        <v>79</v>
+      </c>
+      <c r="X16" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>105</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>64</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>85</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>93</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>100</v>
+      </c>
+      <c r="AG16" t="s">
+        <v>96</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI16" t="s">
         <v>89</v>
       </c>
-      <c r="D16" t="s">
+      <c r="AJ16" t="s">
+        <v>59</v>
+      </c>
+      <c r="AK16" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL16" t="s">
+        <v>95</v>
+      </c>
+      <c r="AN16" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D17" t="s">
+        <v>77</v>
+      </c>
+      <c r="E17" t="s">
+        <v>77</v>
+      </c>
+      <c r="F17" t="s">
+        <v>95</v>
+      </c>
+      <c r="G17" t="s">
+        <v>95</v>
+      </c>
+      <c r="H17" t="s">
         <v>78</v>
       </c>
-      <c r="E16" t="s">
+      <c r="I17" t="s">
+        <v>103</v>
+      </c>
+      <c r="J17" t="s">
+        <v>74</v>
+      </c>
+      <c r="K17" t="s">
+        <v>107</v>
+      </c>
+      <c r="L17" t="s">
+        <v>103</v>
+      </c>
+      <c r="M17" t="s">
         <v>78</v>
       </c>
-      <c r="F16" t="s">
-        <v>86</v>
-      </c>
-      <c r="G16" t="s">
-        <v>79</v>
-      </c>
-      <c r="H16" t="s">
-        <v>81</v>
-      </c>
-      <c r="I16" t="s">
+      <c r="N17" t="s">
+        <v>74</v>
+      </c>
+      <c r="O17" t="s">
+        <v>85</v>
+      </c>
+      <c r="P17" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>85</v>
+      </c>
+      <c r="R17" t="s">
+        <v>85</v>
+      </c>
+      <c r="S17" t="s">
+        <v>99</v>
+      </c>
+      <c r="T17" t="s">
+        <v>96</v>
+      </c>
+      <c r="U17" t="s">
+        <v>98</v>
+      </c>
+      <c r="V17" t="s">
+        <v>85</v>
+      </c>
+      <c r="W17" t="s">
+        <v>95</v>
+      </c>
+      <c r="X17" t="s">
+        <v>107</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>108</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>99</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>100</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>108</v>
+      </c>
+      <c r="AG17" t="s">
+        <v>93</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI17" t="s">
+        <v>102</v>
+      </c>
+      <c r="AJ17" t="s">
+        <v>89</v>
+      </c>
+      <c r="AK17" t="s">
+        <v>89</v>
+      </c>
+      <c r="AL17" t="s">
+        <v>90</v>
+      </c>
+      <c r="AN17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>76</v>
       </c>
-      <c r="J16" t="s">
+      <c r="B18" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" t="s">
+        <v>98</v>
+      </c>
+      <c r="D18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E18" t="s">
+        <v>74</v>
+      </c>
+      <c r="F18" t="s">
+        <v>74</v>
+      </c>
+      <c r="G18" t="s">
+        <v>78</v>
+      </c>
+      <c r="H18" t="s">
+        <v>74</v>
+      </c>
+      <c r="I18" t="s">
+        <v>96</v>
+      </c>
+      <c r="J18" t="s">
+        <v>85</v>
+      </c>
+      <c r="K18" t="s">
+        <v>93</v>
+      </c>
+      <c r="L18" t="s">
+        <v>96</v>
+      </c>
+      <c r="M18" t="s">
+        <v>96</v>
+      </c>
+      <c r="N18" t="s">
+        <v>85</v>
+      </c>
+      <c r="O18" t="s">
+        <v>99</v>
+      </c>
+      <c r="P18" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>64</v>
+      </c>
+      <c r="R18" t="s">
+        <v>96</v>
+      </c>
+      <c r="S18" t="s">
+        <v>100</v>
+      </c>
+      <c r="T18" t="s">
+        <v>100</v>
+      </c>
+      <c r="U18" t="s">
+        <v>93</v>
+      </c>
+      <c r="V18" t="s">
+        <v>93</v>
+      </c>
+      <c r="W18" t="s">
+        <v>74</v>
+      </c>
+      <c r="X18" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z18" t="s">
         <v>80</v>
       </c>
-      <c r="K16" t="s">
-        <v>105</v>
-      </c>
-      <c r="L16" t="s">
-        <v>76</v>
-      </c>
-      <c r="M16" t="s">
-        <v>81</v>
-      </c>
-      <c r="N16" t="s">
-        <v>86</v>
-      </c>
-      <c r="O16" t="s">
-        <v>80</v>
-      </c>
-      <c r="P16" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>76</v>
-      </c>
-      <c r="R16" t="s">
-        <v>98</v>
-      </c>
-      <c r="S16" t="s">
-        <v>76</v>
-      </c>
-      <c r="T16" t="s">
-        <v>76</v>
-      </c>
-      <c r="U16" t="s">
-        <v>105</v>
-      </c>
-      <c r="V16" t="s">
-        <v>76</v>
-      </c>
-      <c r="W16" t="s">
-        <v>81</v>
-      </c>
-      <c r="X16" t="s">
-        <v>81</v>
-      </c>
-      <c r="Y16" t="s">
-        <v>87</v>
-      </c>
-      <c r="Z16" t="s">
-        <v>107</v>
-      </c>
-      <c r="AA16" t="s">
-        <v>66</v>
-      </c>
-      <c r="AB16" t="s">
-        <v>66</v>
-      </c>
-      <c r="AC16" t="s">
-        <v>87</v>
-      </c>
-      <c r="AD16" t="s">
-        <v>95</v>
-      </c>
-      <c r="AE16" t="s">
-        <v>95</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>103</v>
-      </c>
-      <c r="AG16" t="s">
-        <v>99</v>
-      </c>
-      <c r="AH16" t="s">
-        <v>66</v>
-      </c>
-      <c r="AI16" t="s">
-        <v>91</v>
-      </c>
-      <c r="AJ16" t="s">
-        <v>60</v>
-      </c>
-      <c r="AK16" t="s">
-        <v>82</v>
-      </c>
-      <c r="AL16" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="AA18" t="s">
+        <v>59</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>108</v>
+      </c>
+      <c r="AE18" t="s">
         <v>89</v>
       </c>
-      <c r="B17" t="s">
-        <v>68</v>
-      </c>
-      <c r="C17" t="s">
-        <v>79</v>
-      </c>
-      <c r="D17" t="s">
-        <v>79</v>
-      </c>
-      <c r="E17" t="s">
-        <v>79</v>
-      </c>
-      <c r="F17" t="s">
-        <v>98</v>
-      </c>
-      <c r="G17" t="s">
-        <v>98</v>
-      </c>
-      <c r="H17" t="s">
-        <v>80</v>
-      </c>
-      <c r="I17" t="s">
-        <v>105</v>
-      </c>
-      <c r="J17" t="s">
-        <v>76</v>
-      </c>
-      <c r="K17" t="s">
+      <c r="AF18" t="s">
+        <v>73</v>
+      </c>
+      <c r="AG18" t="s">
         <v>108</v>
       </c>
-      <c r="L17" t="s">
-        <v>105</v>
-      </c>
-      <c r="M17" t="s">
-        <v>80</v>
-      </c>
-      <c r="N17" t="s">
-        <v>76</v>
-      </c>
-      <c r="O17" t="s">
-        <v>87</v>
-      </c>
-      <c r="P17" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>87</v>
-      </c>
-      <c r="R17" t="s">
-        <v>87</v>
-      </c>
-      <c r="S17" t="s">
-        <v>102</v>
-      </c>
-      <c r="T17" t="s">
-        <v>99</v>
-      </c>
-      <c r="U17" t="s">
-        <v>101</v>
-      </c>
-      <c r="V17" t="s">
-        <v>87</v>
-      </c>
-      <c r="W17" t="s">
-        <v>98</v>
-      </c>
-      <c r="X17" t="s">
-        <v>108</v>
-      </c>
-      <c r="Y17" t="s">
-        <v>105</v>
-      </c>
-      <c r="Z17" t="s">
-        <v>103</v>
-      </c>
-      <c r="AA17" t="s">
-        <v>109</v>
-      </c>
-      <c r="AB17" t="s">
-        <v>82</v>
-      </c>
-      <c r="AC17" t="s">
-        <v>102</v>
-      </c>
-      <c r="AD17" t="s">
-        <v>103</v>
-      </c>
-      <c r="AE17" t="s">
-        <v>82</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>109</v>
-      </c>
-      <c r="AG17" t="s">
-        <v>95</v>
-      </c>
-      <c r="AH17" t="s">
-        <v>91</v>
-      </c>
-      <c r="AI17" t="s">
-        <v>104</v>
-      </c>
-      <c r="AJ17" t="s">
-        <v>91</v>
-      </c>
-      <c r="AK17" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL17" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>78</v>
-      </c>
-      <c r="B18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C18" t="s">
-        <v>101</v>
-      </c>
-      <c r="D18" t="s">
-        <v>101</v>
-      </c>
-      <c r="E18" t="s">
-        <v>76</v>
-      </c>
-      <c r="F18" t="s">
-        <v>76</v>
-      </c>
-      <c r="G18" t="s">
-        <v>80</v>
-      </c>
-      <c r="H18" t="s">
-        <v>76</v>
-      </c>
-      <c r="I18" t="s">
-        <v>99</v>
-      </c>
-      <c r="J18" t="s">
-        <v>87</v>
-      </c>
-      <c r="K18" t="s">
-        <v>95</v>
-      </c>
-      <c r="L18" t="s">
-        <v>99</v>
-      </c>
-      <c r="M18" t="s">
-        <v>99</v>
-      </c>
-      <c r="N18" t="s">
-        <v>87</v>
-      </c>
-      <c r="O18" t="s">
-        <v>102</v>
-      </c>
-      <c r="P18" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>66</v>
-      </c>
-      <c r="R18" t="s">
-        <v>99</v>
-      </c>
-      <c r="S18" t="s">
-        <v>103</v>
-      </c>
-      <c r="T18" t="s">
-        <v>103</v>
-      </c>
-      <c r="U18" t="s">
-        <v>95</v>
-      </c>
-      <c r="V18" t="s">
-        <v>95</v>
-      </c>
-      <c r="W18" t="s">
-        <v>76</v>
-      </c>
-      <c r="X18" t="s">
-        <v>111</v>
-      </c>
-      <c r="Y18" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z18" t="s">
-        <v>82</v>
-      </c>
-      <c r="AA18" t="s">
-        <v>60</v>
-      </c>
-      <c r="AB18" t="s">
-        <v>60</v>
-      </c>
-      <c r="AC18" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD18" t="s">
-        <v>109</v>
-      </c>
-      <c r="AE18" t="s">
-        <v>91</v>
-      </c>
-      <c r="AF18" t="s">
-        <v>75</v>
-      </c>
-      <c r="AG18" t="s">
-        <v>109</v>
-      </c>
       <c r="AH18" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="AI18" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="AJ18" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="AK18" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>77</v>
+      </c>
+      <c r="B19" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" t="s">
+        <v>84</v>
+      </c>
+      <c r="D19" t="s">
+        <v>84</v>
+      </c>
+      <c r="E19" t="s">
+        <v>103</v>
+      </c>
+      <c r="F19" t="s">
+        <v>85</v>
+      </c>
+      <c r="G19" t="s">
+        <v>85</v>
+      </c>
+      <c r="H19" t="s">
+        <v>103</v>
+      </c>
+      <c r="I19" t="s">
         <v>79</v>
       </c>
-      <c r="B19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C19" t="s">
-        <v>86</v>
-      </c>
-      <c r="D19" t="s">
-        <v>86</v>
-      </c>
-      <c r="E19" t="s">
-        <v>105</v>
-      </c>
-      <c r="F19" t="s">
-        <v>87</v>
-      </c>
-      <c r="G19" t="s">
-        <v>87</v>
-      </c>
-      <c r="H19" t="s">
-        <v>105</v>
-      </c>
-      <c r="I19" t="s">
+      <c r="J19" t="s">
+        <v>93</v>
+      </c>
+      <c r="K19" t="s">
+        <v>80</v>
+      </c>
+      <c r="L19" t="s">
+        <v>99</v>
+      </c>
+      <c r="M19" t="s">
+        <v>64</v>
+      </c>
+      <c r="N19" t="s">
+        <v>103</v>
+      </c>
+      <c r="O19" t="s">
+        <v>93</v>
+      </c>
+      <c r="P19" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>73</v>
+      </c>
+      <c r="R19" t="s">
+        <v>100</v>
+      </c>
+      <c r="S19" t="s">
+        <v>108</v>
+      </c>
+      <c r="T19" t="s">
+        <v>80</v>
+      </c>
+      <c r="U19" t="s">
+        <v>64</v>
+      </c>
+      <c r="V19" t="s">
+        <v>73</v>
+      </c>
+      <c r="W19" t="s">
+        <v>93</v>
+      </c>
+      <c r="X19" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>101</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>101</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>100</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>59</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG19" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>101</v>
+      </c>
+      <c r="AI19" t="s">
         <v>81</v>
       </c>
-      <c r="J19" t="s">
-        <v>95</v>
-      </c>
-      <c r="K19" t="s">
-        <v>82</v>
-      </c>
-      <c r="L19" t="s">
-        <v>102</v>
-      </c>
-      <c r="M19" t="s">
-        <v>66</v>
-      </c>
-      <c r="N19" t="s">
-        <v>105</v>
-      </c>
-      <c r="O19" t="s">
-        <v>95</v>
-      </c>
-      <c r="P19" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>75</v>
-      </c>
-      <c r="R19" t="s">
-        <v>103</v>
-      </c>
-      <c r="S19" t="s">
-        <v>109</v>
-      </c>
-      <c r="T19" t="s">
-        <v>82</v>
-      </c>
-      <c r="U19" t="s">
-        <v>66</v>
-      </c>
-      <c r="V19" t="s">
-        <v>75</v>
-      </c>
-      <c r="W19" t="s">
-        <v>95</v>
-      </c>
-      <c r="X19" t="s">
-        <v>109</v>
-      </c>
-      <c r="Y19" t="s">
-        <v>61</v>
-      </c>
-      <c r="Z19" t="s">
+      <c r="AJ19" t="s">
+        <v>90</v>
+      </c>
+      <c r="AK19" t="s">
         <v>104</v>
-      </c>
-      <c r="AA19" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB19" t="s">
-        <v>91</v>
-      </c>
-      <c r="AC19" t="s">
-        <v>103</v>
-      </c>
-      <c r="AD19" t="s">
-        <v>60</v>
-      </c>
-      <c r="AE19" t="s">
-        <v>100</v>
-      </c>
-      <c r="AF19" t="s">
-        <v>82</v>
-      </c>
-      <c r="AG19" t="s">
-        <v>82</v>
-      </c>
-      <c r="AH19" t="s">
-        <v>104</v>
-      </c>
-      <c r="AI19" t="s">
-        <v>83</v>
-      </c>
-      <c r="AJ19" t="s">
-        <v>110</v>
-      </c>
-      <c r="AK19" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>98</v>
+      </c>
+      <c r="B20" t="s">
+        <v>98</v>
+      </c>
+      <c r="C20" t="s">
+        <v>95</v>
+      </c>
+      <c r="D20" t="s">
+        <v>95</v>
+      </c>
+      <c r="E20" t="s">
+        <v>96</v>
+      </c>
+      <c r="F20" t="s">
+        <v>99</v>
+      </c>
+      <c r="G20" t="s">
+        <v>64</v>
+      </c>
+      <c r="H20" t="s">
+        <v>76</v>
+      </c>
+      <c r="I20" t="s">
+        <v>93</v>
+      </c>
+      <c r="J20" t="s">
+        <v>64</v>
+      </c>
+      <c r="K20" t="s">
+        <v>60</v>
+      </c>
+      <c r="L20" t="s">
+        <v>93</v>
+      </c>
+      <c r="M20" t="s">
+        <v>100</v>
+      </c>
+      <c r="N20" t="s">
+        <v>93</v>
+      </c>
+      <c r="O20" t="s">
+        <v>100</v>
+      </c>
+      <c r="P20" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>80</v>
+      </c>
+      <c r="R20" t="s">
+        <v>80</v>
+      </c>
+      <c r="S20" t="s">
+        <v>73</v>
+      </c>
+      <c r="T20" t="s">
+        <v>60</v>
+      </c>
+      <c r="U20" t="s">
+        <v>108</v>
+      </c>
+      <c r="V20" t="s">
+        <v>60</v>
+      </c>
+      <c r="W20" t="s">
+        <v>73</v>
+      </c>
+      <c r="X20" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>97</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>97</v>
+      </c>
+      <c r="AB20" t="s">
         <v>101</v>
       </c>
-      <c r="B20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C20" t="s">
-        <v>98</v>
-      </c>
-      <c r="D20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E20" t="s">
-        <v>99</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="AC20" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD20" t="s">
         <v>102</v>
       </c>
-      <c r="G20" t="s">
-        <v>66</v>
-      </c>
-      <c r="H20" t="s">
-        <v>78</v>
-      </c>
-      <c r="I20" t="s">
-        <v>95</v>
-      </c>
-      <c r="J20" t="s">
-        <v>66</v>
-      </c>
-      <c r="K20" t="s">
-        <v>62</v>
-      </c>
-      <c r="L20" t="s">
-        <v>95</v>
-      </c>
-      <c r="M20" t="s">
-        <v>103</v>
-      </c>
-      <c r="N20" t="s">
-        <v>95</v>
-      </c>
-      <c r="O20" t="s">
-        <v>103</v>
-      </c>
-      <c r="P20" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>82</v>
-      </c>
-      <c r="R20" t="s">
-        <v>82</v>
-      </c>
-      <c r="S20" t="s">
-        <v>75</v>
-      </c>
-      <c r="T20" t="s">
-        <v>62</v>
-      </c>
-      <c r="U20" t="s">
-        <v>109</v>
-      </c>
-      <c r="V20" t="s">
-        <v>62</v>
-      </c>
-      <c r="W20" t="s">
-        <v>75</v>
-      </c>
-      <c r="X20" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y20" t="s">
-        <v>82</v>
-      </c>
-      <c r="Z20" t="s">
-        <v>100</v>
-      </c>
-      <c r="AA20" t="s">
-        <v>100</v>
-      </c>
-      <c r="AB20" t="s">
+      <c r="AE20" t="s">
         <v>104</v>
       </c>
-      <c r="AC20" t="s">
-        <v>62</v>
-      </c>
-      <c r="AD20" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE20" t="s">
-        <v>106</v>
-      </c>
       <c r="AF20" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="AG20" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="AH20" t="s">
+        <v>90</v>
+      </c>
+      <c r="AI20" t="s">
+        <v>94</v>
+      </c>
+      <c r="AJ20" t="s">
+        <v>67</v>
+      </c>
+      <c r="AK20" t="s">
         <v>110</v>
-      </c>
-      <c r="AI20" t="s">
-        <v>96</v>
-      </c>
-      <c r="AJ20" t="s">
-        <v>69</v>
-      </c>
-      <c r="AK20" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B21" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C21" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D21" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E21" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F21" t="s">
+        <v>71</v>
+      </c>
+      <c r="G21" t="s">
+        <v>108</v>
+      </c>
+      <c r="H21" t="s">
+        <v>93</v>
+      </c>
+      <c r="I21" t="s">
+        <v>64</v>
+      </c>
+      <c r="J21" t="s">
         <v>73</v>
       </c>
-      <c r="G21" t="s">
-        <v>109</v>
-      </c>
-      <c r="H21" t="s">
-        <v>95</v>
-      </c>
-      <c r="I21" t="s">
-        <v>66</v>
-      </c>
-      <c r="J21" t="s">
-        <v>75</v>
-      </c>
       <c r="K21" t="s">
+        <v>59</v>
+      </c>
+      <c r="L21" t="s">
+        <v>100</v>
+      </c>
+      <c r="M21" t="s">
+        <v>108</v>
+      </c>
+      <c r="N21" t="s">
+        <v>64</v>
+      </c>
+      <c r="O21" t="s">
+        <v>108</v>
+      </c>
+      <c r="P21" t="s">
         <v>60</v>
       </c>
-      <c r="L21" t="s">
-        <v>103</v>
-      </c>
-      <c r="M21" t="s">
-        <v>109</v>
-      </c>
-      <c r="N21" t="s">
-        <v>66</v>
-      </c>
-      <c r="O21" t="s">
-        <v>109</v>
-      </c>
-      <c r="P21" t="s">
-        <v>62</v>
-      </c>
       <c r="Q21" t="s">
+        <v>59</v>
+      </c>
+      <c r="R21" t="s">
         <v>60</v>
       </c>
-      <c r="R21" t="s">
-        <v>62</v>
-      </c>
       <c r="S21" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="T21" t="s">
+        <v>59</v>
+      </c>
+      <c r="U21" t="s">
+        <v>73</v>
+      </c>
+      <c r="V21" t="s">
+        <v>59</v>
+      </c>
+      <c r="W21" t="s">
+        <v>89</v>
+      </c>
+      <c r="X21" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>93</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>97</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>101</v>
+      </c>
+      <c r="AD21" t="s">
+        <v>81</v>
+      </c>
+      <c r="AE21" t="s">
+        <v>94</v>
+      </c>
+      <c r="AF21" t="s">
+        <v>94</v>
+      </c>
+      <c r="AG21" t="s">
+        <v>101</v>
+      </c>
+      <c r="AH21" t="s">
+        <v>104</v>
+      </c>
+      <c r="AI21" t="s">
+        <v>106</v>
+      </c>
+      <c r="AJ21" t="s">
         <v>60</v>
-      </c>
-      <c r="U21" t="s">
-        <v>75</v>
-      </c>
-      <c r="V21" t="s">
-        <v>60</v>
-      </c>
-      <c r="W21" t="s">
-        <v>91</v>
-      </c>
-      <c r="X21" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y21" t="s">
-        <v>91</v>
-      </c>
-      <c r="Z21" t="s">
-        <v>95</v>
-      </c>
-      <c r="AA21" t="s">
-        <v>96</v>
-      </c>
-      <c r="AB21" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC21" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD21" t="s">
-        <v>83</v>
-      </c>
-      <c r="AE21" t="s">
-        <v>96</v>
-      </c>
-      <c r="AF21" t="s">
-        <v>96</v>
-      </c>
-      <c r="AG21" t="s">
-        <v>104</v>
-      </c>
-      <c r="AH21" t="s">
-        <v>106</v>
-      </c>
-      <c r="AI21" t="s">
-        <v>92</v>
-      </c>
-      <c r="AJ21" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B22" t="s">
+        <v>78</v>
+      </c>
+      <c r="C22" t="s">
+        <v>74</v>
+      </c>
+      <c r="D22" t="s">
+        <v>74</v>
+      </c>
+      <c r="E22" t="s">
+        <v>109</v>
+      </c>
+      <c r="F22" t="s">
+        <v>64</v>
+      </c>
+      <c r="G22" t="s">
+        <v>73</v>
+      </c>
+      <c r="H22" t="s">
+        <v>100</v>
+      </c>
+      <c r="I22" t="s">
+        <v>100</v>
+      </c>
+      <c r="J22" t="s">
         <v>80</v>
       </c>
-      <c r="C22" t="s">
-        <v>76</v>
-      </c>
-      <c r="D22" t="s">
-        <v>76</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="K22" t="s">
+        <v>89</v>
+      </c>
+      <c r="L22" t="s">
+        <v>73</v>
+      </c>
+      <c r="M22" t="s">
+        <v>59</v>
+      </c>
+      <c r="N22" t="s">
+        <v>100</v>
+      </c>
+      <c r="O22" t="s">
+        <v>73</v>
+      </c>
+      <c r="P22" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>101</v>
+      </c>
+      <c r="R22" t="s">
+        <v>59</v>
+      </c>
+      <c r="S22" t="s">
+        <v>59</v>
+      </c>
+      <c r="T22" t="s">
+        <v>101</v>
+      </c>
+      <c r="U22" t="s">
+        <v>60</v>
+      </c>
+      <c r="V22" t="s">
+        <v>89</v>
+      </c>
+      <c r="W22" t="s">
+        <v>101</v>
+      </c>
+      <c r="X22" t="s">
+        <v>101</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z22" t="s">
         <v>111</v>
       </c>
-      <c r="F22" t="s">
-        <v>66</v>
-      </c>
-      <c r="G22" t="s">
-        <v>75</v>
-      </c>
-      <c r="H22" t="s">
-        <v>103</v>
-      </c>
-      <c r="I22" t="s">
-        <v>103</v>
-      </c>
-      <c r="J22" t="s">
-        <v>82</v>
-      </c>
-      <c r="K22" t="s">
-        <v>91</v>
-      </c>
-      <c r="L22" t="s">
-        <v>75</v>
-      </c>
-      <c r="M22" t="s">
-        <v>60</v>
-      </c>
-      <c r="N22" t="s">
-        <v>103</v>
-      </c>
-      <c r="O22" t="s">
-        <v>75</v>
-      </c>
-      <c r="P22" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>104</v>
-      </c>
-      <c r="R22" t="s">
-        <v>60</v>
-      </c>
-      <c r="S22" t="s">
-        <v>60</v>
-      </c>
-      <c r="T22" t="s">
-        <v>104</v>
-      </c>
-      <c r="U22" t="s">
-        <v>62</v>
-      </c>
-      <c r="V22" t="s">
-        <v>91</v>
-      </c>
-      <c r="W22" t="s">
-        <v>104</v>
-      </c>
-      <c r="X22" t="s">
-        <v>60</v>
-      </c>
-      <c r="Y22" t="s">
-        <v>100</v>
-      </c>
-      <c r="Z22" t="s">
-        <v>113</v>
-      </c>
       <c r="AA22" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AB22" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AC22" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="AD22" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="AE22" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="AF22" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="AG22" t="s">
+        <v>90</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>94</v>
+      </c>
+      <c r="AI22" t="s">
         <v>110</v>
-      </c>
-      <c r="AH22" t="s">
-        <v>96</v>
-      </c>
-      <c r="AI22" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>78</v>
+      </c>
+      <c r="B23" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" t="s">
+        <v>85</v>
+      </c>
+      <c r="D23" t="s">
+        <v>85</v>
+      </c>
+      <c r="E23" t="s">
+        <v>100</v>
+      </c>
+      <c r="F23" t="s">
+        <v>100</v>
+      </c>
+      <c r="G23" t="s">
         <v>80</v>
       </c>
-      <c r="B23" t="s">
-        <v>87</v>
-      </c>
-      <c r="C23" t="s">
-        <v>87</v>
-      </c>
-      <c r="D23" t="s">
-        <v>87</v>
-      </c>
-      <c r="E23" t="s">
-        <v>103</v>
-      </c>
-      <c r="F23" t="s">
-        <v>103</v>
-      </c>
-      <c r="G23" t="s">
-        <v>82</v>
-      </c>
       <c r="H23" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I23" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J23" t="s">
+        <v>59</v>
+      </c>
+      <c r="K23" t="s">
+        <v>101</v>
+      </c>
+      <c r="L23" t="s">
         <v>60</v>
       </c>
-      <c r="K23" t="s">
+      <c r="M23" t="s">
+        <v>112</v>
+      </c>
+      <c r="N23" t="s">
+        <v>111</v>
+      </c>
+      <c r="O23" t="s">
+        <v>60</v>
+      </c>
+      <c r="P23" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>97</v>
+      </c>
+      <c r="R23" t="s">
+        <v>101</v>
+      </c>
+      <c r="S23" t="s">
+        <v>89</v>
+      </c>
+      <c r="T23" t="s">
+        <v>111</v>
+      </c>
+      <c r="U23" t="s">
+        <v>97</v>
+      </c>
+      <c r="V23" t="s">
+        <v>78</v>
+      </c>
+      <c r="W23" t="s">
+        <v>97</v>
+      </c>
+      <c r="X23" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y23" t="s">
         <v>104</v>
       </c>
-      <c r="L23" t="s">
-        <v>62</v>
-      </c>
-      <c r="M23" t="s">
-        <v>114</v>
-      </c>
-      <c r="N23" t="s">
-        <v>113</v>
-      </c>
-      <c r="O23" t="s">
-        <v>62</v>
-      </c>
-      <c r="P23" t="s">
+      <c r="Z23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC23" t="s">
         <v>104</v>
       </c>
-      <c r="Q23" t="s">
-        <v>100</v>
-      </c>
-      <c r="R23" t="s">
-        <v>104</v>
-      </c>
-      <c r="S23" t="s">
-        <v>91</v>
-      </c>
-      <c r="T23" t="s">
-        <v>113</v>
-      </c>
-      <c r="U23" t="s">
-        <v>100</v>
-      </c>
-      <c r="V23" t="s">
-        <v>80</v>
-      </c>
-      <c r="W23" t="s">
-        <v>100</v>
-      </c>
-      <c r="X23" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y23" t="s">
+      <c r="AD23" t="s">
         <v>110</v>
       </c>
-      <c r="Z23" t="s">
-        <v>83</v>
-      </c>
-      <c r="AA23" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB23" t="s">
-        <v>96</v>
-      </c>
-      <c r="AC23" t="s">
+      <c r="AE23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AF23" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG23" t="s">
         <v>106</v>
       </c>
-      <c r="AD23" t="s">
-        <v>112</v>
-      </c>
-      <c r="AE23" t="s">
-        <v>83</v>
-      </c>
-      <c r="AF23" t="s">
-        <v>112</v>
-      </c>
-      <c r="AG23" t="s">
-        <v>92</v>
-      </c>
       <c r="AH23" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="AI23" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B24" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C24" t="s">
+        <v>99</v>
+      </c>
+      <c r="D24" t="s">
+        <v>107</v>
+      </c>
+      <c r="E24" t="s">
+        <v>111</v>
+      </c>
+      <c r="F24" t="s">
+        <v>80</v>
+      </c>
+      <c r="G24" t="s">
+        <v>59</v>
+      </c>
+      <c r="H24" t="s">
+        <v>60</v>
+      </c>
+      <c r="I24" t="s">
+        <v>89</v>
+      </c>
+      <c r="J24" t="s">
+        <v>101</v>
+      </c>
+      <c r="K24" t="s">
+        <v>99</v>
+      </c>
+      <c r="L24" t="s">
+        <v>101</v>
+      </c>
+      <c r="M24" t="s">
+        <v>80</v>
+      </c>
+      <c r="N24" t="s">
+        <v>90</v>
+      </c>
+      <c r="O24" t="s">
+        <v>101</v>
+      </c>
+      <c r="P24" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>90</v>
+      </c>
+      <c r="R24" t="s">
+        <v>97</v>
+      </c>
+      <c r="S24" t="s">
+        <v>97</v>
+      </c>
+      <c r="T24" t="s">
+        <v>81</v>
+      </c>
+      <c r="U24" t="s">
+        <v>90</v>
+      </c>
+      <c r="V24" t="s">
+        <v>81</v>
+      </c>
+      <c r="W24" t="s">
         <v>102</v>
       </c>
-      <c r="D24" t="s">
-        <v>108</v>
-      </c>
-      <c r="E24" t="s">
-        <v>113</v>
-      </c>
-      <c r="F24" t="s">
-        <v>82</v>
-      </c>
-      <c r="G24" t="s">
-        <v>60</v>
-      </c>
-      <c r="H24" t="s">
-        <v>62</v>
-      </c>
-      <c r="I24" t="s">
-        <v>91</v>
-      </c>
-      <c r="J24" t="s">
-        <v>104</v>
-      </c>
-      <c r="K24" t="s">
-        <v>102</v>
-      </c>
-      <c r="L24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M24" t="s">
-        <v>82</v>
-      </c>
-      <c r="N24" t="s">
-        <v>110</v>
-      </c>
-      <c r="O24" t="s">
-        <v>104</v>
-      </c>
-      <c r="P24" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>110</v>
-      </c>
-      <c r="R24" t="s">
-        <v>100</v>
-      </c>
-      <c r="S24" t="s">
-        <v>100</v>
-      </c>
-      <c r="T24" t="s">
-        <v>83</v>
-      </c>
-      <c r="U24" t="s">
-        <v>110</v>
-      </c>
-      <c r="V24" t="s">
-        <v>83</v>
-      </c>
-      <c r="W24" t="s">
-        <v>110</v>
-      </c>
       <c r="X24" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="Y24" t="s">
         <v>106</v>
       </c>
       <c r="Z24" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>110</v>
+      </c>
+      <c r="AC24" t="s">
         <v>106</v>
       </c>
-      <c r="AA24" t="s">
-        <v>62</v>
-      </c>
-      <c r="AB24" t="s">
-        <v>112</v>
-      </c>
-      <c r="AC24" t="s">
-        <v>92</v>
-      </c>
       <c r="AD24" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="AE24" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="AF24" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B25" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C25" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D25" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E25" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G25" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I25" t="s">
+        <v>101</v>
+      </c>
+      <c r="J25" t="s">
+        <v>102</v>
+      </c>
+      <c r="K25" t="s">
+        <v>90</v>
+      </c>
+      <c r="L25" t="s">
+        <v>97</v>
+      </c>
+      <c r="M25" t="s">
+        <v>90</v>
+      </c>
+      <c r="N25" t="s">
         <v>104</v>
       </c>
-      <c r="J25" t="s">
-        <v>110</v>
-      </c>
-      <c r="K25" t="s">
-        <v>110</v>
-      </c>
-      <c r="L25" t="s">
-        <v>100</v>
-      </c>
-      <c r="M25" t="s">
-        <v>110</v>
-      </c>
-      <c r="N25" t="s">
+      <c r="O25" t="s">
+        <v>81</v>
+      </c>
+      <c r="P25" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>94</v>
+      </c>
+      <c r="R25" t="s">
+        <v>90</v>
+      </c>
+      <c r="S25" t="s">
+        <v>90</v>
+      </c>
+      <c r="T25" t="s">
         <v>106</v>
       </c>
-      <c r="O25" t="s">
-        <v>83</v>
-      </c>
-      <c r="P25" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>96</v>
-      </c>
-      <c r="R25" t="s">
-        <v>110</v>
-      </c>
-      <c r="S25" t="s">
-        <v>110</v>
-      </c>
-      <c r="T25" t="s">
-        <v>92</v>
-      </c>
       <c r="U25" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="V25" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="W25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="X25" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="Y25" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="Z25" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AA25" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AB25" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B26" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D26" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="E26" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F26" t="s">
+        <v>101</v>
+      </c>
+      <c r="G26" t="s">
+        <v>97</v>
+      </c>
+      <c r="H26" t="s">
+        <v>89</v>
+      </c>
+      <c r="I26" t="s">
+        <v>112</v>
+      </c>
+      <c r="J26" t="s">
+        <v>81</v>
+      </c>
+      <c r="K26" t="s">
+        <v>81</v>
+      </c>
+      <c r="L26" t="s">
+        <v>90</v>
+      </c>
+      <c r="M26" t="s">
+        <v>113</v>
+      </c>
+      <c r="N26" t="s">
+        <v>94</v>
+      </c>
+      <c r="O26" t="s">
         <v>104</v>
       </c>
-      <c r="G26" t="s">
-        <v>100</v>
-      </c>
-      <c r="H26" t="s">
-        <v>91</v>
-      </c>
-      <c r="I26" t="s">
+      <c r="P26" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>106</v>
+      </c>
+      <c r="R26" t="s">
+        <v>110</v>
+      </c>
+      <c r="S26" t="s">
+        <v>104</v>
+      </c>
+      <c r="T26" t="s">
         <v>114</v>
       </c>
-      <c r="J26" t="s">
-        <v>83</v>
-      </c>
-      <c r="K26" t="s">
-        <v>83</v>
-      </c>
-      <c r="L26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M26" t="s">
-        <v>97</v>
-      </c>
-      <c r="N26" t="s">
-        <v>96</v>
-      </c>
-      <c r="O26" t="s">
+      <c r="U26" t="s">
+        <v>94</v>
+      </c>
+      <c r="V26" t="s">
+        <v>94</v>
+      </c>
+      <c r="W26" t="s">
         <v>106</v>
       </c>
-      <c r="P26" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>92</v>
-      </c>
-      <c r="R26" t="s">
-        <v>112</v>
-      </c>
-      <c r="S26" t="s">
-        <v>106</v>
-      </c>
-      <c r="T26" t="s">
+      <c r="X26" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z26" t="s">
         <v>115</v>
-      </c>
-      <c r="U26" t="s">
-        <v>96</v>
-      </c>
-      <c r="V26" t="s">
-        <v>96</v>
-      </c>
-      <c r="W26" t="s">
-        <v>92</v>
-      </c>
-      <c r="X26" t="s">
-        <v>106</v>
-      </c>
-      <c r="Y26" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z26" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>99</v>
+      </c>
+      <c r="B27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C27" t="s">
+        <v>100</v>
+      </c>
+      <c r="D27" t="s">
+        <v>59</v>
+      </c>
+      <c r="E27" t="s">
+        <v>97</v>
+      </c>
+      <c r="F27" t="s">
+        <v>97</v>
+      </c>
+      <c r="G27" t="s">
+        <v>90</v>
+      </c>
+      <c r="H27" t="s">
+        <v>64</v>
+      </c>
+      <c r="I27" t="s">
         <v>102</v>
       </c>
-      <c r="B27" t="s">
-        <v>95</v>
-      </c>
-      <c r="C27" t="s">
-        <v>103</v>
-      </c>
-      <c r="D27" t="s">
-        <v>60</v>
-      </c>
-      <c r="E27" t="s">
-        <v>100</v>
-      </c>
-      <c r="F27" t="s">
-        <v>100</v>
-      </c>
-      <c r="G27" t="s">
+      <c r="J27" t="s">
+        <v>104</v>
+      </c>
+      <c r="K27" t="s">
+        <v>94</v>
+      </c>
+      <c r="L27" t="s">
+        <v>104</v>
+      </c>
+      <c r="M27" t="s">
         <v>110</v>
       </c>
-      <c r="H27" t="s">
-        <v>66</v>
-      </c>
-      <c r="I27" t="s">
+      <c r="N27" t="s">
+        <v>106</v>
+      </c>
+      <c r="O27" t="s">
+        <v>94</v>
+      </c>
+      <c r="P27" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q27" t="s">
         <v>110</v>
       </c>
-      <c r="J27" t="s">
+      <c r="R27" t="s">
+        <v>86</v>
+      </c>
+      <c r="S27" t="s">
         <v>106</v>
       </c>
-      <c r="K27" t="s">
-        <v>96</v>
-      </c>
-      <c r="L27" t="s">
+      <c r="T27" t="s">
+        <v>115</v>
+      </c>
+      <c r="U27" t="s">
+        <v>86</v>
+      </c>
+      <c r="V27" t="s">
         <v>106</v>
-      </c>
-      <c r="M27" t="s">
-        <v>112</v>
-      </c>
-      <c r="N27" t="s">
-        <v>92</v>
-      </c>
-      <c r="O27" t="s">
-        <v>96</v>
-      </c>
-      <c r="P27" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>112</v>
-      </c>
-      <c r="R27" t="s">
-        <v>88</v>
-      </c>
-      <c r="S27" t="s">
-        <v>92</v>
-      </c>
-      <c r="T27" t="s">
-        <v>116</v>
-      </c>
-      <c r="U27" t="s">
-        <v>88</v>
-      </c>
-      <c r="V27" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B28" t="s">
+        <v>109</v>
+      </c>
+      <c r="C28" t="s">
         <v>111</v>
       </c>
-      <c r="C28" t="s">
-        <v>113</v>
-      </c>
       <c r="D28" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E28" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F28" t="s">
+        <v>79</v>
+      </c>
+      <c r="G28" t="s">
         <v>81</v>
       </c>
-      <c r="G28" t="s">
-        <v>83</v>
-      </c>
       <c r="H28" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I28" t="s">
+        <v>104</v>
+      </c>
+      <c r="J28" t="s">
         <v>106</v>
       </c>
-      <c r="J28" t="s">
-        <v>92</v>
-      </c>
       <c r="K28" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="L28" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="M28" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="N28" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="O28" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q28" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="T28" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D29" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E29" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F29" t="s">
+        <v>90</v>
+      </c>
+      <c r="G29" t="s">
+        <v>94</v>
+      </c>
+      <c r="H29" t="s">
+        <v>90</v>
+      </c>
+      <c r="I29" t="s">
+        <v>106</v>
+      </c>
+      <c r="J29" t="s">
+        <v>113</v>
+      </c>
+      <c r="K29" t="s">
+        <v>113</v>
+      </c>
+      <c r="L29" t="s">
         <v>110</v>
       </c>
-      <c r="G29" t="s">
-        <v>96</v>
-      </c>
-      <c r="H29" t="s">
-        <v>110</v>
-      </c>
-      <c r="I29" t="s">
-        <v>92</v>
-      </c>
-      <c r="J29" t="s">
-        <v>97</v>
-      </c>
-      <c r="K29" t="s">
-        <v>97</v>
-      </c>
-      <c r="L29" t="s">
-        <v>112</v>
-      </c>
       <c r="M29" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="N29" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="O29" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B30" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="C30" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="D30" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E30" t="s">
+        <v>104</v>
+      </c>
+      <c r="F30" t="s">
+        <v>104</v>
+      </c>
+      <c r="G30" t="s">
         <v>106</v>
       </c>
-      <c r="F30" t="s">
-        <v>106</v>
-      </c>
-      <c r="G30" t="s">
-        <v>92</v>
-      </c>
       <c r="H30" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I30" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="J30" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="K30" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>111</v>
+      </c>
+      <c r="B31" t="s">
+        <v>60</v>
+      </c>
+      <c r="C31" t="s">
+        <v>60</v>
+      </c>
+      <c r="D31" t="s">
+        <v>93</v>
+      </c>
+      <c r="E31" t="s">
+        <v>94</v>
+      </c>
+      <c r="F31" t="s">
+        <v>94</v>
+      </c>
+      <c r="G31" t="s">
         <v>113</v>
       </c>
-      <c r="B31" t="s">
-        <v>82</v>
-      </c>
-      <c r="C31" t="s">
-        <v>82</v>
-      </c>
-      <c r="D31" t="s">
-        <v>95</v>
-      </c>
-      <c r="E31" t="s">
-        <v>96</v>
-      </c>
-      <c r="F31" t="s">
-        <v>96</v>
-      </c>
-      <c r="G31" t="s">
-        <v>97</v>
-      </c>
       <c r="H31" t="s">
+        <v>104</v>
+      </c>
+      <c r="I31" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>59</v>
+      </c>
+      <c r="B32" t="s">
+        <v>59</v>
+      </c>
+      <c r="C32" t="s">
+        <v>102</v>
+      </c>
+      <c r="D32" t="s">
+        <v>90</v>
+      </c>
+      <c r="E32" t="s">
         <v>106</v>
       </c>
+      <c r="F32" t="s">
+        <v>106</v>
+      </c>
+      <c r="G32" t="s">
+        <v>67</v>
+      </c>
+      <c r="H32" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>61</v>
-      </c>
-      <c r="B32" t="s">
-        <v>62</v>
-      </c>
-      <c r="C32" t="s">
-        <v>62</v>
-      </c>
-      <c r="D32" t="s">
+    <row r="33" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>89</v>
+      </c>
+      <c r="B33" t="s">
+        <v>89</v>
+      </c>
+      <c r="C33" t="s">
+        <v>89</v>
+      </c>
+      <c r="D33" t="s">
+        <v>81</v>
+      </c>
+      <c r="E33" t="s">
         <v>110</v>
       </c>
-      <c r="E32" t="s">
-        <v>92</v>
-      </c>
-      <c r="F32" t="s">
-        <v>92</v>
-      </c>
-      <c r="G32" t="s">
-        <v>69</v>
+      <c r="F33" t="s">
+        <v>110</v>
+      </c>
+      <c r="G33" t="s">
+        <v>101</v>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>61</v>
-      </c>
-      <c r="B33" t="s">
+    <row r="34" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>101</v>
+      </c>
+      <c r="B34" t="s">
+        <v>101</v>
+      </c>
+      <c r="C34" t="s">
+        <v>101</v>
+      </c>
+      <c r="D34" t="s">
+        <v>104</v>
+      </c>
+      <c r="E34" t="s">
+        <v>113</v>
+      </c>
+      <c r="F34" t="s">
         <v>60</v>
-      </c>
-      <c r="C33" t="s">
-        <v>60</v>
-      </c>
-      <c r="D33" t="s">
-        <v>83</v>
-      </c>
-      <c r="E33" t="s">
-        <v>112</v>
-      </c>
-      <c r="F33" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>61</v>
-      </c>
-      <c r="B34" t="s">
-        <v>91</v>
-      </c>
-      <c r="C34" t="s">
-        <v>91</v>
-      </c>
-      <c r="D34" t="s">
-        <v>106</v>
-      </c>
-      <c r="F34" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="B35" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C35" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="D35" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B36" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="C36" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D36" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="B37" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="C37" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="D37" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B38" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="C38" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="D38" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B39" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="C39" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="D39" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="B40" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="C40" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="D40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B41" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C41" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="B42" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="C42" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B43" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="C43" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>112</v>
-      </c>
       <c r="B44" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="C44" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>69</v>
-      </c>
-      <c r="B45" t="s">
-        <v>112</v>
-      </c>
-      <c r="C45" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="15" customHeight="1" spans="2:3" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="48" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="49" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="50" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5185,199 +5177,199 @@
   <sheetData>
     <row r="3" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" t="s">
         <v>51</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" t="s">
         <v>54</v>
       </c>
-      <c r="C3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H3" t="s">
         <v>55</v>
       </c>
-      <c r="F3" t="s">
+      <c r="I3" t="s">
+        <v>68</v>
+      </c>
+      <c r="J3" t="s">
+        <v>65</v>
+      </c>
+      <c r="K3" t="s">
+        <v>69</v>
+      </c>
+      <c r="L3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M3" t="s">
         <v>57</v>
       </c>
-      <c r="G3" t="s">
+      <c r="N3" t="s">
+        <v>70</v>
+      </c>
+      <c r="O3" t="s">
+        <v>75</v>
+      </c>
+      <c r="P3" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q3" t="s">
         <v>63</v>
       </c>
-      <c r="H3" t="s">
-        <v>56</v>
-      </c>
-      <c r="I3" t="s">
-        <v>70</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="R3" t="s">
+        <v>72</v>
+      </c>
+      <c r="S3" t="s">
+        <v>91</v>
+      </c>
+      <c r="T3" t="s">
+        <v>62</v>
+      </c>
+      <c r="U3" t="s">
+        <v>83</v>
+      </c>
+      <c r="V3" t="s">
+        <v>71</v>
+      </c>
+      <c r="W3" t="s">
+        <v>92</v>
+      </c>
+      <c r="X3" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>98</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>95</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>105</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>103</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>107</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>93</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>109</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>100</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>111</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>108</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>59</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>89</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>101</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>97</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>90</v>
+      </c>
+      <c r="BD3" t="s">
+        <v>81</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>104</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>94</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>106</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>110</v>
+      </c>
+      <c r="BJ3" t="s">
         <v>67</v>
       </c>
-      <c r="K3" t="s">
-        <v>71</v>
-      </c>
-      <c r="L3" t="s">
-        <v>59</v>
-      </c>
-      <c r="M3" t="s">
-        <v>58</v>
-      </c>
-      <c r="N3" t="s">
-        <v>72</v>
-      </c>
-      <c r="O3" t="s">
-        <v>77</v>
-      </c>
-      <c r="P3" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>65</v>
-      </c>
-      <c r="R3" t="s">
-        <v>74</v>
-      </c>
-      <c r="S3" t="s">
-        <v>93</v>
-      </c>
-      <c r="T3" t="s">
-        <v>64</v>
-      </c>
-      <c r="U3" t="s">
-        <v>85</v>
-      </c>
-      <c r="V3" t="s">
-        <v>73</v>
-      </c>
-      <c r="W3" t="s">
-        <v>94</v>
-      </c>
-      <c r="X3" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>90</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>89</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>101</v>
-      </c>
-      <c r="AD3" t="s">
+      <c r="BK3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>115</v>
+      </c>
+      <c r="BM3" t="s">
         <v>86</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>81</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>98</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>107</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>76</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>87</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>105</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>99</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>108</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>102</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>111</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>66</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>103</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>113</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>109</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>82</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>62</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>60</v>
-      </c>
-      <c r="AY3" t="s">
-        <v>91</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>104</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>100</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>114</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>110</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>83</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>106</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>96</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>92</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>97</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>112</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>69</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>115</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
@@ -5403,7 +5395,7 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I4" t="s">
         <v>0</v>
@@ -5421,7 +5413,7 @@
         <v>12</v>
       </c>
       <c r="N4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O4" t="s">
         <v>14</v>
@@ -5442,7 +5434,7 @@
         <v>2</v>
       </c>
       <c r="U4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="V4" t="s">
         <v>12</v>
@@ -5526,7 +5518,7 @@
         <v>14</v>
       </c>
       <c r="AW4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AX4" t="s">
         <v>48</v>
@@ -5720,7 +5712,7 @@
         <v>3</v>
       </c>
       <c r="AV5" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AW5" t="s">
         <v>2</v>
@@ -6308,7 +6300,7 @@
         <v>14</v>
       </c>
       <c r="BF8" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="BG8" t="s">
         <v>32</v>
@@ -6445,7 +6437,7 @@
         <v>7</v>
       </c>
       <c r="AX9" t="s">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="AY9" t="s">
         <v>7</v>
@@ -6466,7 +6458,7 @@
         <v>0</v>
       </c>
       <c r="BF9" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="BG9" t="s">
         <v>34</v>
@@ -6600,7 +6592,7 @@
         <v>31</v>
       </c>
       <c r="AW10" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="AX10" t="s">
         <v>17</v>
@@ -6627,10 +6619,10 @@
         <v>16</v>
       </c>
       <c r="BG10" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="BH10" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="BI10" t="s">
         <v>31</v>
@@ -6785,10 +6777,10 @@
         <v>41</v>
       </c>
       <c r="BG11" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="BH11" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="BI11" t="s">
         <v>29</v>
@@ -6835,7 +6827,7 @@
         <v>28</v>
       </c>
       <c r="T12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="V12" t="s">
         <v>1</v>
@@ -6934,7 +6926,7 @@
         <v>5</v>
       </c>
       <c r="BJ12" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:62" x14ac:dyDescent="0.25">
@@ -7071,7 +7063,7 @@
         <v>1</v>
       </c>
       <c r="BJ13" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:62" x14ac:dyDescent="0.25">
@@ -7380,7 +7372,7 @@
         <v>34</v>
       </c>
       <c r="R16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="T16" t="s">
         <v>19</v>
@@ -7449,7 +7441,7 @@
         <v>19</v>
       </c>
       <c r="BA16" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="BC16" t="s">
         <v>32</v>
@@ -7571,7 +7563,7 @@
         <v>3</v>
       </c>
       <c r="BA17" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="BC17" t="s">
         <v>12</v>
@@ -7687,7 +7679,7 @@
         <v>42</v>
       </c>
       <c r="AY18" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="AZ18" t="s">
         <v>25</v>
@@ -7696,7 +7688,7 @@
         <v>22</v>
       </c>
       <c r="BC18" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="BD18" t="s">
         <v>25</v>
@@ -7809,7 +7801,7 @@
         <v>16</v>
       </c>
       <c r="AY19" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="AZ19" t="s">
         <v>39</v>
@@ -7936,7 +7928,7 @@
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C21" t="s">
         <v>7</v>
@@ -8008,7 +8000,7 @@
         <v>21</v>
       </c>
       <c r="AZ21" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="BA21" t="s">
         <v>2</v>
@@ -8112,7 +8104,7 @@
         <v>30</v>
       </c>
       <c r="BC22" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="BD22" t="s">
         <v>45</v>
@@ -8210,7 +8202,7 @@
         <v>39</v>
       </c>
       <c r="BC23" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD23" t="s">
         <v>4</v>
@@ -8272,7 +8264,7 @@
         <v>12</v>
       </c>
       <c r="AX24" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY24" t="s">
         <v>34</v>
@@ -8426,7 +8418,7 @@
         <v>24</v>
       </c>
       <c r="BC26" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BD26" t="s">
         <v>10</v>
@@ -8497,7 +8489,7 @@
         <v>4</v>
       </c>
       <c r="BC27" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="BD27" t="s">
         <v>9</v>
@@ -8512,7 +8504,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="48:59" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="15" customHeight="1" spans="53:59" x14ac:dyDescent="0.25"/>
     <row r="29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -8620,1005 +8612,1005 @@
   <sheetData>
     <row r="3" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" t="s">
         <v>51</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" t="s">
         <v>54</v>
       </c>
-      <c r="C3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H3" t="s">
         <v>55</v>
       </c>
-      <c r="F3" t="s">
+      <c r="I3" t="s">
+        <v>68</v>
+      </c>
+      <c r="J3" t="s">
+        <v>65</v>
+      </c>
+      <c r="K3" t="s">
+        <v>69</v>
+      </c>
+      <c r="L3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M3" t="s">
         <v>57</v>
       </c>
-      <c r="G3" t="s">
+      <c r="N3" t="s">
+        <v>70</v>
+      </c>
+      <c r="O3" t="s">
+        <v>75</v>
+      </c>
+      <c r="P3" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q3" t="s">
         <v>63</v>
       </c>
-      <c r="H3" t="s">
-        <v>56</v>
-      </c>
-      <c r="I3" t="s">
-        <v>70</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="R3" t="s">
+        <v>72</v>
+      </c>
+      <c r="S3" t="s">
+        <v>91</v>
+      </c>
+      <c r="T3" t="s">
+        <v>62</v>
+      </c>
+      <c r="U3" t="s">
+        <v>83</v>
+      </c>
+      <c r="V3" t="s">
+        <v>71</v>
+      </c>
+      <c r="W3" t="s">
+        <v>92</v>
+      </c>
+      <c r="X3" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>98</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>95</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>105</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>103</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>107</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>93</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>109</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>100</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>111</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>108</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>59</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>89</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>101</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>97</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>90</v>
+      </c>
+      <c r="BD3" t="s">
+        <v>81</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>104</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>94</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>106</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>110</v>
+      </c>
+      <c r="BJ3" t="s">
         <v>67</v>
       </c>
-      <c r="K3" t="s">
-        <v>71</v>
-      </c>
-      <c r="L3" t="s">
-        <v>59</v>
-      </c>
-      <c r="M3" t="s">
-        <v>58</v>
-      </c>
-      <c r="N3" t="s">
-        <v>72</v>
-      </c>
-      <c r="O3" t="s">
-        <v>77</v>
-      </c>
-      <c r="P3" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>65</v>
-      </c>
-      <c r="R3" t="s">
-        <v>74</v>
-      </c>
-      <c r="S3" t="s">
-        <v>93</v>
-      </c>
-      <c r="T3" t="s">
-        <v>64</v>
-      </c>
-      <c r="U3" t="s">
-        <v>85</v>
-      </c>
-      <c r="V3" t="s">
-        <v>73</v>
-      </c>
-      <c r="W3" t="s">
-        <v>94</v>
-      </c>
-      <c r="X3" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>90</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>89</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>101</v>
-      </c>
-      <c r="AD3" t="s">
+      <c r="BK3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>115</v>
+      </c>
+      <c r="BM3" t="s">
         <v>86</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>81</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>98</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>107</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>76</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>87</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>105</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>99</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>108</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>102</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>111</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>66</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>103</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>113</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>109</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>82</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>62</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>60</v>
-      </c>
-      <c r="AY3" t="s">
-        <v>91</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>104</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>100</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>114</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>110</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>83</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>106</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>96</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>92</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>97</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>112</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>69</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>115</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B4" t="s">
         <v>118</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>119</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>120</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>121</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>122</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>123</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>124</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>125</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>126</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>127</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>128</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>129</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>130</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>131</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>132</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>133</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
         <v>134</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S4" t="s">
         <v>135</v>
       </c>
-      <c r="S4" t="s">
+      <c r="T4" t="s">
         <v>136</v>
       </c>
-      <c r="T4" t="s">
+      <c r="U4" t="s">
         <v>137</v>
       </c>
-      <c r="U4" t="s">
+      <c r="V4" t="s">
         <v>138</v>
       </c>
-      <c r="V4" t="s">
+      <c r="W4" t="s">
         <v>139</v>
       </c>
-      <c r="W4" t="s">
+      <c r="X4" t="s">
         <v>140</v>
       </c>
-      <c r="X4" t="s">
+      <c r="Y4" t="s">
         <v>141</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Z4" t="s">
         <v>142</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AA4" t="s">
         <v>143</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AB4" t="s">
         <v>144</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AC4" t="s">
         <v>145</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AD4" t="s">
         <v>146</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AE4" t="s">
         <v>147</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AF4" t="s">
         <v>148</v>
       </c>
-      <c r="AF4" t="s">
+      <c r="AG4" t="s">
         <v>149</v>
       </c>
-      <c r="AG4" t="s">
+      <c r="AH4" t="s">
         <v>150</v>
       </c>
-      <c r="AH4" t="s">
+      <c r="AI4" t="s">
         <v>151</v>
       </c>
-      <c r="AI4" t="s">
+      <c r="AJ4" t="s">
         <v>152</v>
       </c>
-      <c r="AJ4" t="s">
+      <c r="AK4" t="s">
         <v>153</v>
       </c>
-      <c r="AK4" t="s">
+      <c r="AL4" t="s">
         <v>154</v>
       </c>
-      <c r="AL4" t="s">
+      <c r="AM4" t="s">
         <v>155</v>
       </c>
-      <c r="AM4" t="s">
+      <c r="AN4" t="s">
         <v>156</v>
       </c>
-      <c r="AN4" t="s">
+      <c r="AO4" t="s">
         <v>157</v>
       </c>
-      <c r="AO4" t="s">
+      <c r="AP4" t="s">
         <v>158</v>
       </c>
-      <c r="AP4" t="s">
+      <c r="AQ4" t="s">
         <v>159</v>
       </c>
-      <c r="AQ4" t="s">
+      <c r="AR4" t="s">
         <v>160</v>
       </c>
-      <c r="AR4" t="s">
+      <c r="AS4" t="s">
         <v>161</v>
       </c>
-      <c r="AS4" t="s">
+      <c r="AT4" t="s">
         <v>162</v>
       </c>
-      <c r="AT4" t="s">
+      <c r="AU4" t="s">
         <v>163</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AV4" t="s">
         <v>164</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AW4" t="s">
         <v>165</v>
       </c>
-      <c r="AW4" t="s">
+      <c r="AX4" t="s">
         <v>166</v>
       </c>
-      <c r="AX4" t="s">
+      <c r="AY4" t="s">
         <v>167</v>
       </c>
-      <c r="AY4" t="s">
+      <c r="AZ4" t="s">
         <v>168</v>
       </c>
-      <c r="AZ4" t="s">
+      <c r="BA4" t="s">
         <v>169</v>
       </c>
-      <c r="BA4" t="s">
+      <c r="BB4" t="s">
         <v>170</v>
       </c>
-      <c r="BB4" t="s">
+      <c r="BC4" t="s">
         <v>171</v>
       </c>
-      <c r="BC4" t="s">
+      <c r="BD4" t="s">
         <v>172</v>
       </c>
-      <c r="BD4" t="s">
+      <c r="BE4" t="s">
         <v>173</v>
       </c>
-      <c r="BE4" t="s">
+      <c r="BF4" t="s">
         <v>174</v>
       </c>
-      <c r="BF4" t="s">
+      <c r="BG4" t="s">
         <v>175</v>
       </c>
-      <c r="BG4" t="s">
+      <c r="BH4" t="s">
         <v>176</v>
       </c>
-      <c r="BH4" t="s">
+      <c r="BI4" t="s">
         <v>177</v>
       </c>
-      <c r="BI4" t="s">
+      <c r="BJ4" t="s">
         <v>178</v>
       </c>
-      <c r="BJ4" t="s">
+      <c r="BK4" t="s">
         <v>179</v>
       </c>
-      <c r="BK4" t="s">
+      <c r="BL4" t="s">
         <v>180</v>
       </c>
-      <c r="BL4" t="s">
+      <c r="BM4" t="s">
         <v>181</v>
-      </c>
-      <c r="BM4" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>182</v>
+      </c>
+      <c r="C5" t="s">
         <v>183</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
         <v>184</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>185</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>186</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>187</v>
       </c>
-      <c r="H5" t="s">
+      <c r="J5" t="s">
         <v>188</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>189</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>190</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>191</v>
       </c>
-      <c r="M5" t="s">
+      <c r="O5" t="s">
         <v>192</v>
       </c>
-      <c r="O5" t="s">
+      <c r="Q5" t="s">
         <v>193</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="R5" t="s">
         <v>194</v>
       </c>
-      <c r="R5" t="s">
+      <c r="T5" t="s">
         <v>195</v>
       </c>
-      <c r="T5" t="s">
+      <c r="V5" t="s">
         <v>196</v>
       </c>
-      <c r="V5" t="s">
+      <c r="W5" t="s">
         <v>197</v>
       </c>
-      <c r="W5" t="s">
+      <c r="X5" t="s">
         <v>198</v>
       </c>
-      <c r="X5" t="s">
+      <c r="Y5" t="s">
         <v>199</v>
       </c>
-      <c r="Y5" t="s">
+      <c r="Z5" t="s">
         <v>200</v>
       </c>
-      <c r="Z5" t="s">
+      <c r="AA5" t="s">
         <v>201</v>
       </c>
-      <c r="AA5" t="s">
+      <c r="AB5" t="s">
         <v>202</v>
       </c>
-      <c r="AB5" t="s">
+      <c r="AC5" t="s">
         <v>203</v>
       </c>
-      <c r="AC5" t="s">
+      <c r="AD5" t="s">
         <v>204</v>
       </c>
-      <c r="AD5" t="s">
+      <c r="AE5" t="s">
         <v>205</v>
       </c>
-      <c r="AE5" t="s">
+      <c r="AF5" t="s">
         <v>206</v>
       </c>
-      <c r="AF5" t="s">
+      <c r="AH5" t="s">
         <v>207</v>
       </c>
-      <c r="AH5" t="s">
+      <c r="AI5" t="s">
         <v>208</v>
       </c>
-      <c r="AI5" t="s">
+      <c r="AJ5" t="s">
         <v>209</v>
       </c>
-      <c r="AJ5" t="s">
+      <c r="AK5" t="s">
         <v>210</v>
       </c>
-      <c r="AK5" t="s">
+      <c r="AL5" t="s">
         <v>211</v>
       </c>
-      <c r="AL5" t="s">
+      <c r="AN5" t="s">
         <v>212</v>
       </c>
-      <c r="AN5" t="s">
+      <c r="AO5" t="s">
+        <v>212</v>
+      </c>
+      <c r="AQ5" t="s">
         <v>213</v>
       </c>
-      <c r="AO5" t="s">
-        <v>213</v>
-      </c>
-      <c r="AQ5" t="s">
+      <c r="AR5" t="s">
         <v>214</v>
       </c>
-      <c r="AR5" t="s">
+      <c r="AS5" t="s">
+        <v>212</v>
+      </c>
+      <c r="AT5" t="s">
         <v>215</v>
       </c>
-      <c r="AS5" t="s">
-        <v>213</v>
-      </c>
-      <c r="AT5" t="s">
+      <c r="AU5" t="s">
+        <v>188</v>
+      </c>
+      <c r="AV5" t="s">
         <v>216</v>
       </c>
-      <c r="AU5" t="s">
-        <v>189</v>
-      </c>
-      <c r="AV5" t="s">
+      <c r="AW5" t="s">
         <v>217</v>
       </c>
-      <c r="AW5" t="s">
+      <c r="AX5" t="s">
         <v>218</v>
       </c>
-      <c r="AX5" t="s">
+      <c r="AY5" t="s">
         <v>219</v>
       </c>
-      <c r="AY5" t="s">
+      <c r="AZ5" t="s">
         <v>220</v>
       </c>
-      <c r="AZ5" t="s">
+      <c r="BA5" t="s">
         <v>221</v>
       </c>
-      <c r="BA5" t="s">
+      <c r="BC5" t="s">
         <v>222</v>
       </c>
-      <c r="BC5" t="s">
+      <c r="BD5" t="s">
         <v>223</v>
       </c>
-      <c r="BD5" t="s">
+      <c r="BE5" t="s">
         <v>224</v>
       </c>
-      <c r="BE5" t="s">
+      <c r="BF5" t="s">
         <v>225</v>
       </c>
-      <c r="BF5" t="s">
+      <c r="BG5" t="s">
         <v>226</v>
       </c>
-      <c r="BG5" t="s">
+      <c r="BH5" t="s">
         <v>227</v>
       </c>
-      <c r="BH5" t="s">
+      <c r="BI5" t="s">
         <v>228</v>
       </c>
-      <c r="BI5" t="s">
+      <c r="BJ5" t="s">
         <v>229</v>
       </c>
-      <c r="BJ5" t="s">
+      <c r="BM5" t="s">
         <v>230</v>
-      </c>
-      <c r="BM5" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C6" t="s">
         <v>232</v>
       </c>
-      <c r="C6" t="s">
+      <c r="E6" t="s">
         <v>233</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>234</v>
       </c>
-      <c r="F6" t="s">
+      <c r="H6" t="s">
         <v>235</v>
       </c>
-      <c r="H6" t="s">
+      <c r="J6" t="s">
         <v>236</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>237</v>
       </c>
-      <c r="K6" t="s">
+      <c r="M6" t="s">
         <v>238</v>
       </c>
-      <c r="M6" t="s">
+      <c r="O6" t="s">
         <v>239</v>
       </c>
-      <c r="O6" t="s">
+      <c r="Q6" t="s">
         <v>240</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="R6" t="s">
         <v>241</v>
       </c>
-      <c r="R6" t="s">
+      <c r="T6" t="s">
         <v>242</v>
       </c>
-      <c r="T6" t="s">
+      <c r="V6" t="s">
         <v>243</v>
       </c>
-      <c r="V6" t="s">
+      <c r="W6" t="s">
         <v>244</v>
       </c>
-      <c r="W6" t="s">
+      <c r="X6" t="s">
         <v>245</v>
       </c>
-      <c r="X6" t="s">
+      <c r="Z6" t="s">
         <v>246</v>
       </c>
-      <c r="Z6" t="s">
+      <c r="AA6" t="s">
         <v>247</v>
       </c>
-      <c r="AA6" t="s">
+      <c r="AB6" t="s">
         <v>248</v>
       </c>
-      <c r="AB6" t="s">
+      <c r="AD6" t="s">
         <v>249</v>
       </c>
-      <c r="AD6" t="s">
+      <c r="AE6" t="s">
         <v>250</v>
       </c>
-      <c r="AE6" t="s">
+      <c r="AF6" t="s">
         <v>251</v>
       </c>
-      <c r="AF6" t="s">
+      <c r="AH6" t="s">
         <v>252</v>
       </c>
-      <c r="AH6" t="s">
+      <c r="AI6" t="s">
         <v>253</v>
       </c>
-      <c r="AI6" t="s">
+      <c r="AJ6" t="s">
         <v>254</v>
       </c>
-      <c r="AJ6" t="s">
+      <c r="AK6" t="s">
         <v>255</v>
       </c>
-      <c r="AK6" t="s">
+      <c r="AL6" t="s">
         <v>256</v>
       </c>
-      <c r="AL6" t="s">
+      <c r="AN6" t="s">
         <v>257</v>
       </c>
-      <c r="AN6" t="s">
+      <c r="AO6" t="s">
         <v>258</v>
       </c>
-      <c r="AO6" t="s">
+      <c r="AQ6" t="s">
         <v>259</v>
       </c>
-      <c r="AQ6" t="s">
+      <c r="AR6" t="s">
         <v>260</v>
       </c>
-      <c r="AR6" t="s">
+      <c r="AS6" t="s">
         <v>261</v>
       </c>
-      <c r="AS6" t="s">
+      <c r="AT6" t="s">
         <v>262</v>
       </c>
-      <c r="AT6" t="s">
+      <c r="AU6" t="s">
         <v>263</v>
       </c>
-      <c r="AU6" t="s">
+      <c r="AV6" t="s">
         <v>264</v>
       </c>
-      <c r="AV6" t="s">
+      <c r="AW6" t="s">
+        <v>212</v>
+      </c>
+      <c r="AX6" t="s">
         <v>265</v>
       </c>
-      <c r="AW6" t="s">
-        <v>213</v>
-      </c>
-      <c r="AX6" t="s">
+      <c r="AY6" t="s">
         <v>266</v>
       </c>
-      <c r="AY6" t="s">
+      <c r="AZ6" t="s">
         <v>267</v>
       </c>
-      <c r="AZ6" t="s">
+      <c r="BA6" t="s">
         <v>268</v>
       </c>
-      <c r="BA6" t="s">
+      <c r="BC6" t="s">
         <v>269</v>
       </c>
-      <c r="BC6" t="s">
+      <c r="BD6" t="s">
         <v>270</v>
       </c>
-      <c r="BD6" t="s">
+      <c r="BE6" t="s">
         <v>271</v>
       </c>
-      <c r="BE6" t="s">
+      <c r="BF6" t="s">
         <v>272</v>
       </c>
-      <c r="BF6" t="s">
+      <c r="BG6" t="s">
         <v>273</v>
       </c>
-      <c r="BG6" t="s">
+      <c r="BI6" t="s">
         <v>274</v>
       </c>
-      <c r="BI6" t="s">
+      <c r="BJ6" t="s">
         <v>275</v>
-      </c>
-      <c r="BJ6" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>276</v>
+      </c>
+      <c r="C7" t="s">
         <v>277</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
         <v>278</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>279</v>
       </c>
-      <c r="F7" t="s">
+      <c r="H7" t="s">
         <v>280</v>
       </c>
-      <c r="H7" t="s">
+      <c r="J7" t="s">
         <v>281</v>
       </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
         <v>282</v>
       </c>
-      <c r="K7" t="s">
+      <c r="M7" t="s">
         <v>283</v>
       </c>
-      <c r="M7" t="s">
+      <c r="O7" t="s">
         <v>284</v>
       </c>
-      <c r="O7" t="s">
+      <c r="Q7" t="s">
         <v>285</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="R7" t="s">
         <v>286</v>
       </c>
-      <c r="R7" t="s">
+      <c r="T7" t="s">
         <v>287</v>
       </c>
-      <c r="T7" t="s">
+      <c r="V7" t="s">
         <v>288</v>
       </c>
-      <c r="V7" t="s">
+      <c r="X7" t="s">
         <v>289</v>
       </c>
-      <c r="X7" t="s">
+      <c r="Z7" t="s">
         <v>290</v>
       </c>
-      <c r="Z7" t="s">
+      <c r="AA7" t="s">
         <v>291</v>
       </c>
-      <c r="AA7" t="s">
+      <c r="AB7" t="s">
         <v>292</v>
       </c>
-      <c r="AB7" t="s">
+      <c r="AD7" t="s">
         <v>293</v>
       </c>
-      <c r="AD7" t="s">
+      <c r="AE7" t="s">
         <v>294</v>
       </c>
-      <c r="AE7" t="s">
+      <c r="AF7" t="s">
         <v>295</v>
       </c>
-      <c r="AF7" t="s">
+      <c r="AH7" t="s">
         <v>296</v>
       </c>
-      <c r="AH7" t="s">
+      <c r="AI7" t="s">
         <v>297</v>
       </c>
-      <c r="AI7" t="s">
+      <c r="AJ7" t="s">
         <v>298</v>
       </c>
-      <c r="AJ7" t="s">
+      <c r="AN7" t="s">
         <v>299</v>
       </c>
-      <c r="AN7" t="s">
+      <c r="AO7" t="s">
         <v>300</v>
       </c>
-      <c r="AO7" t="s">
+      <c r="AQ7" t="s">
         <v>301</v>
       </c>
-      <c r="AQ7" t="s">
+      <c r="AR7" t="s">
         <v>302</v>
       </c>
-      <c r="AR7" t="s">
+      <c r="AU7" t="s">
         <v>303</v>
       </c>
-      <c r="AU7" t="s">
+      <c r="AV7" t="s">
         <v>304</v>
       </c>
-      <c r="AV7" t="s">
+      <c r="AW7" t="s">
         <v>305</v>
       </c>
-      <c r="AW7" t="s">
+      <c r="AX7" t="s">
         <v>306</v>
       </c>
-      <c r="AX7" t="s">
+      <c r="AY7" t="s">
         <v>307</v>
       </c>
-      <c r="AY7" t="s">
+      <c r="AZ7" t="s">
         <v>308</v>
       </c>
-      <c r="AZ7" t="s">
+      <c r="BA7" t="s">
         <v>309</v>
       </c>
-      <c r="BA7" t="s">
+      <c r="BC7" t="s">
         <v>310</v>
       </c>
-      <c r="BC7" t="s">
+      <c r="BD7" t="s">
         <v>311</v>
       </c>
-      <c r="BD7" t="s">
+      <c r="BE7" t="s">
         <v>312</v>
       </c>
-      <c r="BE7" t="s">
+      <c r="BF7" t="s">
         <v>313</v>
       </c>
-      <c r="BF7" t="s">
+      <c r="BG7" t="s">
         <v>314</v>
       </c>
-      <c r="BG7" t="s">
+      <c r="BI7" t="s">
         <v>315</v>
-      </c>
-      <c r="BI7" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>316</v>
+      </c>
+      <c r="C8" t="s">
         <v>317</v>
       </c>
-      <c r="C8" t="s">
+      <c r="E8" t="s">
         <v>318</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>319</v>
       </c>
-      <c r="F8" t="s">
+      <c r="H8" t="s">
         <v>320</v>
       </c>
-      <c r="H8" t="s">
+      <c r="K8" t="s">
         <v>321</v>
       </c>
-      <c r="K8" t="s">
+      <c r="O8" t="s">
         <v>322</v>
       </c>
-      <c r="O8" t="s">
+      <c r="Q8" t="s">
         <v>323</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="R8" t="s">
         <v>324</v>
       </c>
-      <c r="R8" t="s">
+      <c r="T8" t="s">
         <v>325</v>
       </c>
-      <c r="T8" t="s">
+      <c r="X8" t="s">
         <v>326</v>
       </c>
-      <c r="X8" t="s">
+      <c r="AA8" t="s">
         <v>327</v>
       </c>
-      <c r="AA8" t="s">
+      <c r="AB8" t="s">
         <v>328</v>
       </c>
-      <c r="AB8" t="s">
+      <c r="AE8" t="s">
+        <v>212</v>
+      </c>
+      <c r="AF8" t="s">
         <v>329</v>
       </c>
-      <c r="AE8" t="s">
-        <v>213</v>
-      </c>
-      <c r="AF8" t="s">
+      <c r="AH8" t="s">
         <v>330</v>
       </c>
-      <c r="AH8" t="s">
+      <c r="AI8" t="s">
         <v>331</v>
       </c>
-      <c r="AI8" t="s">
+      <c r="AJ8" t="s">
         <v>332</v>
       </c>
-      <c r="AJ8" t="s">
+      <c r="AN8" t="s">
         <v>333</v>
       </c>
-      <c r="AN8" t="s">
+      <c r="AO8" t="s">
         <v>334</v>
       </c>
-      <c r="AO8" t="s">
+      <c r="AQ8" t="s">
         <v>335</v>
       </c>
-      <c r="AQ8" t="s">
+      <c r="AR8" t="s">
         <v>336</v>
       </c>
-      <c r="AR8" t="s">
+      <c r="AU8" t="s">
+        <v>212</v>
+      </c>
+      <c r="AV8" t="s">
         <v>337</v>
       </c>
-      <c r="AU8" t="s">
-        <v>213</v>
-      </c>
-      <c r="AV8" t="s">
+      <c r="AW8" t="s">
         <v>338</v>
       </c>
-      <c r="AW8" t="s">
+      <c r="AX8" t="s">
         <v>339</v>
       </c>
-      <c r="AX8" t="s">
+      <c r="AY8" t="s">
         <v>340</v>
       </c>
-      <c r="AY8" t="s">
+      <c r="AZ8" t="s">
         <v>341</v>
       </c>
-      <c r="AZ8" t="s">
+      <c r="BA8" t="s">
         <v>342</v>
       </c>
-      <c r="BA8" t="s">
+      <c r="BC8" t="s">
         <v>343</v>
       </c>
-      <c r="BC8" t="s">
+      <c r="BD8" t="s">
         <v>344</v>
       </c>
-      <c r="BD8" t="s">
+      <c r="BE8" t="s">
         <v>345</v>
       </c>
-      <c r="BE8" t="s">
+      <c r="BF8" t="s">
         <v>346</v>
       </c>
-      <c r="BF8" t="s">
+      <c r="BG8" t="s">
         <v>347</v>
       </c>
-      <c r="BG8" t="s">
+      <c r="BI8" t="s">
         <v>348</v>
-      </c>
-      <c r="BI8" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>349</v>
+      </c>
+      <c r="E9" t="s">
         <v>350</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>351</v>
       </c>
-      <c r="F9" t="s">
+      <c r="H9" t="s">
         <v>352</v>
       </c>
-      <c r="H9" t="s">
+      <c r="O9" t="s">
         <v>353</v>
       </c>
-      <c r="O9" t="s">
+      <c r="T9" t="s">
         <v>354</v>
       </c>
-      <c r="T9" t="s">
+      <c r="X9" t="s">
         <v>355</v>
       </c>
-      <c r="X9" t="s">
+      <c r="AB9" t="s">
         <v>356</v>
       </c>
-      <c r="AB9" t="s">
+      <c r="AF9" t="s">
         <v>357</v>
       </c>
-      <c r="AF9" t="s">
+      <c r="AI9" t="s">
         <v>358</v>
       </c>
-      <c r="AI9" t="s">
+      <c r="AJ9" t="s">
         <v>359</v>
       </c>
-      <c r="AJ9" t="s">
+      <c r="AO9" t="s">
         <v>360</v>
       </c>
-      <c r="AO9" t="s">
+      <c r="AV9" t="s">
         <v>361</v>
       </c>
-      <c r="AV9" t="s">
+      <c r="AW9" t="s">
         <v>362</v>
       </c>
-      <c r="AW9" t="s">
+      <c r="AX9" t="s">
         <v>363</v>
       </c>
-      <c r="AX9" t="s">
+      <c r="AY9" t="s">
         <v>364</v>
       </c>
-      <c r="AY9" t="s">
+      <c r="AZ9" t="s">
         <v>365</v>
       </c>
-      <c r="AZ9" t="s">
+      <c r="BA9" t="s">
         <v>366</v>
       </c>
-      <c r="BA9" t="s">
+      <c r="BC9" t="s">
         <v>367</v>
       </c>
-      <c r="BC9" t="s">
+      <c r="BD9" t="s">
         <v>368</v>
       </c>
-      <c r="BD9" t="s">
+      <c r="BE9" t="s">
         <v>369</v>
       </c>
-      <c r="BE9" t="s">
+      <c r="BF9" t="s">
         <v>370</v>
       </c>
-      <c r="BF9" t="s">
+      <c r="BG9" t="s">
         <v>371</v>
-      </c>
-      <c r="BG9" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="41:59" x14ac:dyDescent="0.25">
       <c r="AO10" t="s">
+        <v>372</v>
+      </c>
+      <c r="AW10" t="s">
         <v>373</v>
       </c>
-      <c r="AW10" t="s">
-        <v>374</v>
-      </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="49:49" x14ac:dyDescent="0.25"/>
+    <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="13" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="14" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/data/ICEHLdelegacije.xlsx
+++ b/data/ICEHLdelegacije.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="ICEHL" state="visible" r:id="rId4"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2507" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2681" uniqueCount="398">
   <si>
     <t>SmetanaLa</t>
   </si>
@@ -168,6 +168,9 @@
     <t>LazzeriAl</t>
   </si>
   <si>
+    <t>LinesmanEi</t>
+  </si>
+  <si>
     <t>2024-09-20</t>
   </si>
   <si>
@@ -201,6 +204,9 @@
     <t>2024-12-22</t>
   </si>
   <si>
+    <t>2025-01-19</t>
+  </si>
+  <si>
     <t>2024-10-01</t>
   </si>
   <si>
@@ -219,7 +225,7 @@
     <t>2024-11-01</t>
   </si>
   <si>
-    <t>2025-01-19</t>
+    <t>2025-01-01</t>
   </si>
   <si>
     <t>2024-10-05</t>
@@ -279,6 +285,9 @@
     <t>2025-01-18</t>
   </si>
   <si>
+    <t>2025-01-28</t>
+  </si>
+  <si>
     <t>2024-11-03</t>
   </si>
   <si>
@@ -303,15 +312,15 @@
     <t>2025-01-10</t>
   </si>
   <si>
+    <t>2025-01-26</t>
+  </si>
+  <si>
     <t>2024-11-22</t>
   </si>
   <si>
     <t>2024-12-01</t>
   </si>
   <si>
-    <t>2025-01-01</t>
-  </si>
-  <si>
     <t>2024-11-16</t>
   </si>
   <si>
@@ -324,7 +333,7 @@
     <t>2024-12-30</t>
   </si>
   <si>
-    <t>zbrisano</t>
+    <t>2025-01-12</t>
   </si>
   <si>
     <t>2024-11-30</t>
@@ -336,9 +345,6 @@
     <t>2024-11-23</t>
   </si>
   <si>
-    <t>2025-01-12</t>
-  </si>
-  <si>
     <t>2024-12-03</t>
   </si>
   <si>
@@ -354,6 +360,9 @@
     <t>2024-12-14</t>
   </si>
   <si>
+    <t>2025-01-24</t>
+  </si>
+  <si>
     <t>2024-12-10</t>
   </si>
   <si>
@@ -363,9 +372,15 @@
     <t>2025-01-21</t>
   </si>
   <si>
+    <t>2025-01-29</t>
+  </si>
+  <si>
     <t>2025-01-22</t>
   </si>
   <si>
+    <t>2025-01-25</t>
+  </si>
+  <si>
     <t>HuberAn</t>
   </si>
   <si>
@@ -564,6 +579,21 @@
     <t>Eishalle Wien-Kagran;SmetanaLa;VoicanCh;BedynekSe;RieckenSi</t>
   </si>
   <si>
+    <t>Eisarena Salzburg;HronskyTo;SmetanaLa;KoncDa;RieckenSi</t>
+  </si>
+  <si>
+    <t>Sparkasse Arena Bozen;FichtnerPa;SiegelSt;MantovaniDa;RigoniDa</t>
+  </si>
+  <si>
+    <t>Linz AG Eisarena;NagyAt;SmetanaLa;NotheggerDa;WimmlerAl</t>
+  </si>
+  <si>
+    <t>Merkur Eisstadion Graz;GroznikBo;SiegelSt;PuffWo;WimmlerAl</t>
+  </si>
+  <si>
+    <t>Eishalle Asiago;Huber aAn;PiragicTr;HribarMa;RigoniDa</t>
+  </si>
+  <si>
     <t>Tiroler Wasserkraft Arena;NikolicMa;SeewaldEl;FleischmannLu;NotheggerDa</t>
   </si>
   <si>
@@ -693,13 +723,13 @@
     <t>Heidi Horten Arena Klagenfurt;FichtnerPa;SmetanaLa;BärnthalerCh;ZgoncGa</t>
   </si>
   <si>
-    <t>Tiroler Wasserkraft Arena;NikolicMa;NikolicKr;SparerDa;ZacherlPa</t>
+    <t>Tiroler Wasserkraft Arena;NikolicKr;NikolicMa;PardatscherUl;ZacherlPa</t>
   </si>
   <si>
     <t>Eishalle Feldkirch;BernekerTh;NikolicKr;MartinFl;SeewaldJe</t>
   </si>
   <si>
-    <t>Sparkasse Arena Bozen;OfnerCh;SternatCh;MantovaniDa;ZgoncGa</t>
+    <t>Sparkasse Arena Bozen;OfnerCh;PiragicTr;MantovaniDa;ZgoncGa</t>
   </si>
   <si>
     <t>Eishalle Wien-Kagran;NagyAt;SiegelSt;DurmisOt;WimmlerAl</t>
@@ -711,6 +741,18 @@
     <t>Gabor Ocskay Eisarena;OfnerCh;SeewaldEl;Gatol-schafranekMa;MuzsikNo</t>
   </si>
   <si>
+    <t>Stadthalle Villach;NikolicMa;SchauerJa;BedynekSe;PuffWo</t>
+  </si>
+  <si>
+    <t>Eishalle Bruneck;OfnerCh;SternatCh;DurmisOt;JedlickaPe</t>
+  </si>
+  <si>
+    <t>Klagenfurter Stadthalle;GroznikBo;SoosDa;MuzsikNo;VacziDa</t>
+  </si>
+  <si>
+    <t>Eishalle KagranEins;SeewaldEl;SmetanaLa;BedynekSe;RieckenSi</t>
+  </si>
+  <si>
     <t>Hala Tivoli;PiragicTr;ZrnicMi;HribarMa;SnojTa</t>
   </si>
   <si>
@@ -837,13 +879,22 @@
     <t>Eishalle Wien-Kagran;FichtnerPa;KainbergerJu;Gatol-schafranekMa;MoidlMa</t>
   </si>
   <si>
-    <t>Eishalle Bruneck;GroznikBo;OfnerCh;PardatscherUl;SparerDa</t>
+    <t>Eishalle Bruneck;GroznikBo;OfnerCh;PardatscherUl;ZacherlPa</t>
   </si>
   <si>
     <t>Stadthalle Villach;GroznikBo;PiragicTr;HribarMa;ZgoncGa</t>
   </si>
   <si>
-    <t>Eishalle Bruneck;NikolicKr;NikolicMa;MantovaniDa;SparerDa</t>
+    <t>Eishalle Bruneck;NikolicMa;NikolicKr;LinesmanEi;MantovaniDa</t>
+  </si>
+  <si>
+    <t>Tiroler Wasserkraft Arena;FichtnerPa;SiegelSt;MartinFl;PardatscherUl</t>
+  </si>
+  <si>
+    <t>Eishalle Feldkirch;OfnerCh;SternatCh;FleischmannLu;PardatscherUl</t>
+  </si>
+  <si>
+    <t>Stadthalle Villach;HronskyTo;ZrnicMi;DurmisOt;KoncDa</t>
   </si>
   <si>
     <t>Eishalle Wien-Kagran;HronskyTo;SmetanaLa;DurmisOt;WeissAl</t>
@@ -945,10 +996,10 @@
     <t>Eisarena Salzburg;HronskyTo;SternatCh;JedlickaPe;SeewaldJe</t>
   </si>
   <si>
-    <t>Tiroler Wasserkraft Arena;NikolicMa;NikolicKr;MartinFl;SparerDa</t>
-  </si>
-  <si>
-    <t>Sparkasse Arena Bozen;BernekerTh;SeewaldEl;SeewaldJe;SparerDa</t>
+    <t>Tiroler Wasserkraft Arena;NikolicKr;NikolicMa;MartinFl;StrimitzerDa</t>
+  </si>
+  <si>
+    <t>Sparkasse Arena Bozen;BernekerTh;SeewaldEl;SeewaldJe;ZacherlPa</t>
   </si>
   <si>
     <t>Eishalle Wien-Kagran;HronskyTo;SternatCh;JedlickaPe;KoncDa</t>
@@ -966,6 +1017,15 @@
     <t>Gabor Ocskay Eisarena;OfnerCh;SeewaldEl;MuzsikNo;VacziDa</t>
   </si>
   <si>
+    <t>Eishalle Feldkirch;Huber aAn;NikolicKr;DurmisOt;JedlickaPe</t>
+  </si>
+  <si>
+    <t>Eishalle KagranEins;NikolicMa;SchauerJa;Gatol-schafranekMa;RieckenSi</t>
+  </si>
+  <si>
+    <t>Gabor Ocskay Eisarena;FichtnerPa;SternatCh;Gatol-schafranekMa;WeissAl</t>
+  </si>
+  <si>
     <t>Eishalle Bruneck;BernekerTh;HuberAn;MartinFl;PardatscherUl</t>
   </si>
   <si>
@@ -1062,7 +1122,13 @@
     <t>Heidi Horten Arena Klagenfurt;HronskyTo;Huber aAn;BärnthalerCh;DurmisOt</t>
   </si>
   <si>
-    <t>Eishalle Asiago;NikolicKr;SternatCh;PardatscherUl;SparerDa</t>
+    <t>Eishalle Asiago;SchauerJa;SternatCh;PardatscherUl;RigoniDa</t>
+  </si>
+  <si>
+    <t>Eishalle Asiago;OfnerCh;SternatCh;HribarMa;ZgoncGa</t>
+  </si>
+  <si>
+    <t>Tiroler Wasserkraft Arena;BernekerTh;OfnerCh;MartinFl;SeewaldJe</t>
   </si>
   <si>
     <t>Eiswelle Bozen;OfnerCh;RezekGr;PuffWo;ZgoncGa</t>
@@ -1132,6 +1198,12 @@
   </si>
   <si>
     <t>Eishalle Asiago;NikolicMa;SchauerJa;MantovaniDa;RigoniDa</t>
+  </si>
+  <si>
+    <t>Sparkasse Arena Bozen;SeewaldEl;ZrnicMi;MantovaniDa;NotheggerDa</t>
+  </si>
+  <si>
+    <t>Hala Tivoli;KainbergerJu;PiragicTr;JeramFi;ZgoncGa</t>
   </si>
   <si>
     <t>Stadthalle Villach;KainbergerJu;SternatCh;DurmisOt;JedlickaPe</t>
@@ -1455,7 +1527,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:AY134"/>
+  <dimension ref="A2:AZ134"/>
   <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.28515625" customWidth="1"/>
@@ -1515,75 +1587,75 @@
     <row r="2" ht="14.45" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A2">
         <f>COUNTIF(A4:A97,"&lt;&gt;")</f>
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B2">
         <f>COUNTIF(B4:B95,"&lt;&gt;")</f>
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C2">
-        <f>COUNTIF(C4:C97,"&lt;&gt;")</f>
-        <v>41</v>
+        <f>COUNTIF(C4:C96,"&lt;&gt;")</f>
+        <v>44</v>
       </c>
       <c r="D2">
-        <f>COUNTIF(D4:D96,"&lt;&gt;")</f>
-        <v>37</v>
+        <f>COUNTIF(D4:D94,"&lt;&gt;")</f>
+        <v>39</v>
       </c>
       <c r="E2">
         <f>COUNTIF(E4:E98,"&lt;&gt;")</f>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F2">
         <f>COUNTIF(F4:F100,"&lt;&gt;")</f>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G2">
         <f>COUNTIF(G4:G100,"&lt;&gt;")</f>
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H2">
         <f>COUNTIF(H4:H100,"&lt;&gt;")</f>
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I2">
-        <f>COUNTIF(I4:I99,"&lt;&gt;")</f>
-        <v>27</v>
+        <f>COUNTIF(I4:I98,"&lt;&gt;")</f>
+        <v>29</v>
       </c>
       <c r="J2">
-        <f>COUNTIF(J4:J100,"&lt;&gt;")</f>
-        <v>27</v>
+        <f>COUNTIF(J4:J99,"&lt;&gt;")</f>
+        <v>29</v>
       </c>
       <c r="K2">
         <f>COUNTIF(K4:K99,"&lt;&gt;")</f>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L2">
         <f>COUNTIF(L4:L100,"&lt;&gt;")</f>
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M2">
         <f>COUNTIF(M4:M97,"&lt;&gt;")</f>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="N2">
         <f>COUNTIF(N4:N99,"&lt;&gt;")</f>
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="O2">
         <f>COUNTIF(O4:O100,"&lt;&gt;")</f>
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="P2">
         <f>COUNTIF(P4:P98,"&lt;&gt;")</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q2">
         <f>COUNTIF(Q4:Q100,"&lt;&gt;")</f>
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="R2">
         <f>COUNTIF(R4:R98,"&lt;&gt;")</f>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="S2">
         <f>COUNTIF(S4:S100,"&lt;&gt;")</f>
@@ -1591,99 +1663,99 @@
       </c>
       <c r="T2">
         <f>COUNTIF(T4:T98,"&lt;&gt;")</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="U2">
         <f>COUNTIF(U4:U100,"&lt;&gt;")</f>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="V2">
         <f>COUNTIF(V4:V100,"&lt;&gt;")</f>
+        <v>27</v>
+      </c>
+      <c r="W2">
+        <f>COUNTIF(W4:W99,"&lt;&gt;")</f>
         <v>24</v>
-      </c>
-      <c r="W2">
-        <f>COUNTIF(W4:W100,"&lt;&gt;")</f>
-        <v>23</v>
       </c>
       <c r="X2">
         <f>COUNTIF(X4:X99,"&lt;&gt;")</f>
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Y2">
         <f>COUNTIF(Y4:Y99,"&lt;&gt;")</f>
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Z2">
         <f>COUNTIF(Z4:Z95,"&lt;&gt;")</f>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AA2">
         <f>COUNTIF(AA4:AA96,"&lt;&gt;")</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB2">
         <f>COUNTIF(AB4:AB100,"&lt;&gt;")</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AC2">
         <f>COUNTIF(AC4:AC100,"&lt;&gt;")</f>
         <v>21</v>
       </c>
       <c r="AD2">
-        <f>COUNTIF(AD4:AD95,"&lt;&gt;")</f>
-        <v>21</v>
+        <f>COUNTIF(AD4:AD94,"&lt;&gt;")</f>
+        <v>22</v>
       </c>
       <c r="AE2">
         <f>COUNTIF(AE4:AE95,"&lt;&gt;")</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AF2">
         <f>COUNTIF(AF4:AF93,"&lt;&gt;")</f>
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AG2">
         <f>COUNTIF(AG4:AG100,"&lt;&gt;")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH2">
         <f>COUNTIF(AH4:AH97,"&lt;&gt;")</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AI2">
-        <f>COUNTIF(AI4:AI96,"&lt;&gt;")</f>
-        <v>20</v>
+        <f>COUNTIF(AI4:AI94,"&lt;&gt;")</f>
+        <v>19</v>
       </c>
       <c r="AJ2">
         <f>COUNTIF(AJ4:AJ97,"&lt;&gt;")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK2">
         <f>COUNTIF(AK4:AK100,"&lt;&gt;")</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL2">
         <f>COUNTIF(AL4:AL100,"&lt;&gt;")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM2">
-        <f>COUNTIF(AM4:AM99,"&lt;&gt;")</f>
-        <v>12</v>
+        <f>COUNTIF(AM4:AM98,"&lt;&gt;")</f>
+        <v>11</v>
       </c>
       <c r="AN2">
         <f>COUNTIF(AN4:AN100,"&lt;&gt;")</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AO2">
         <f>COUNTIF(AO4:AO98,"&lt;&gt;")</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AP2">
         <f>COUNTIF(AP4:AP100,"&lt;&gt;")</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AQ2">
         <f>COUNTIF(AQ4:AQ99,"&lt;&gt;")</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AR2">
         <f>COUNTIF(AR4:AR100,"&lt;&gt;")</f>
@@ -1695,14 +1767,14 @@
       </c>
       <c r="AT2">
         <f>COUNTIF(AT4:AT100,"&lt;&gt;")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU2">
         <f>COUNTIF(AU4:AU100,"&lt;&gt;")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -1853,3201 +1925,3411 @@
       <c r="AX3" t="s">
         <v>49</v>
       </c>
+      <c r="AY3" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K4" t="s">
+        <v>52</v>
+      </c>
+      <c r="L4" t="s">
+        <v>53</v>
+      </c>
+      <c r="M4" t="s">
         <v>51</v>
       </c>
-      <c r="L4" t="s">
+      <c r="N4" t="s">
         <v>52</v>
       </c>
-      <c r="M4" t="s">
-        <v>50</v>
-      </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
+        <v>52</v>
+      </c>
+      <c r="P4" t="s">
         <v>51</v>
       </c>
-      <c r="O4" t="s">
+      <c r="Q4" t="s">
+        <v>54</v>
+      </c>
+      <c r="R4" t="s">
+        <v>52</v>
+      </c>
+      <c r="S4" t="s">
+        <v>55</v>
+      </c>
+      <c r="T4" t="s">
         <v>51</v>
       </c>
-      <c r="P4" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q4" t="s">
+      <c r="U4" t="s">
+        <v>52</v>
+      </c>
+      <c r="V4" t="s">
+        <v>54</v>
+      </c>
+      <c r="W4" t="s">
+        <v>51</v>
+      </c>
+      <c r="X4" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>58</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>61</v>
+      </c>
+      <c r="AY4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H5" t="s">
+        <v>52</v>
+      </c>
+      <c r="I5" t="s">
+        <v>55</v>
+      </c>
+      <c r="J5" t="s">
+        <v>55</v>
+      </c>
+      <c r="K5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L5" t="s">
+        <v>57</v>
+      </c>
+      <c r="M5" t="s">
+        <v>55</v>
+      </c>
+      <c r="N5" t="s">
+        <v>56</v>
+      </c>
+      <c r="O5" t="s">
         <v>53</v>
       </c>
-      <c r="R4" t="s">
-        <v>51</v>
-      </c>
-      <c r="S4" t="s">
+      <c r="P5" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>63</v>
+      </c>
+      <c r="R5" t="s">
+        <v>53</v>
+      </c>
+      <c r="S5" t="s">
+        <v>57</v>
+      </c>
+      <c r="T5" t="s">
+        <v>55</v>
+      </c>
+      <c r="U5" t="s">
+        <v>55</v>
+      </c>
+      <c r="V5" t="s">
+        <v>55</v>
+      </c>
+      <c r="W5" t="s">
+        <v>52</v>
+      </c>
+      <c r="X5" t="s">
         <v>54</v>
       </c>
-      <c r="T4" t="s">
-        <v>50</v>
-      </c>
-      <c r="U4" t="s">
-        <v>51</v>
-      </c>
-      <c r="V4" t="s">
+      <c r="Y5" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>63</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>57</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>57</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>55</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>55</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>55</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>63</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>57</v>
+      </c>
+      <c r="AL5" t="s">
         <v>53</v>
       </c>
-      <c r="W4" t="s">
-        <v>50</v>
-      </c>
-      <c r="X4" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>51</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>54</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>55</v>
-      </c>
-      <c r="AN4" t="s">
+      <c r="AM5" t="s">
+        <v>58</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>59</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>65</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AR5" t="s">
         <v>56</v>
       </c>
-      <c r="AO4" t="s">
-        <v>56</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AS4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AT4" t="s">
-        <v>58</v>
-      </c>
-      <c r="AU4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>55</v>
-      </c>
-      <c r="AW4" t="s">
-        <v>59</v>
-      </c>
-      <c r="AX4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G5" t="s">
-        <v>54</v>
-      </c>
-      <c r="H5" t="s">
-        <v>51</v>
-      </c>
-      <c r="I5" t="s">
-        <v>54</v>
-      </c>
-      <c r="J5" t="s">
-        <v>54</v>
-      </c>
-      <c r="K5" t="s">
-        <v>54</v>
-      </c>
-      <c r="L5" t="s">
-        <v>56</v>
-      </c>
-      <c r="M5" t="s">
-        <v>54</v>
-      </c>
-      <c r="N5" t="s">
-        <v>55</v>
-      </c>
-      <c r="O5" t="s">
-        <v>52</v>
-      </c>
-      <c r="P5" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>61</v>
-      </c>
-      <c r="R5" t="s">
-        <v>52</v>
-      </c>
-      <c r="S5" t="s">
-        <v>56</v>
-      </c>
-      <c r="T5" t="s">
-        <v>54</v>
-      </c>
-      <c r="U5" t="s">
-        <v>54</v>
-      </c>
-      <c r="V5" t="s">
-        <v>54</v>
-      </c>
-      <c r="W5" t="s">
-        <v>51</v>
-      </c>
-      <c r="X5" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>54</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>56</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>56</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>56</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>56</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>54</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>54</v>
-      </c>
-      <c r="AH5" t="s">
-        <v>55</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>54</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>61</v>
-      </c>
-      <c r="AK5" t="s">
-        <v>56</v>
-      </c>
-      <c r="AL5" t="s">
-        <v>52</v>
-      </c>
-      <c r="AM5" t="s">
-        <v>57</v>
-      </c>
-      <c r="AN5" t="s">
+      <c r="AS5" t="s">
+        <v>67</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>68</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AW5" t="s">
         <v>62</v>
-      </c>
-      <c r="AO5" t="s">
-        <v>58</v>
-      </c>
-      <c r="AP5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AQ5" t="s">
-        <v>64</v>
-      </c>
-      <c r="AR5" t="s">
-        <v>55</v>
-      </c>
-      <c r="AS5" t="s">
-        <v>65</v>
-      </c>
-      <c r="AT5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AW5" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" t="s">
+        <v>57</v>
+      </c>
+      <c r="F6" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6" t="s">
+        <v>57</v>
+      </c>
+      <c r="H6" t="s">
+        <v>57</v>
+      </c>
+      <c r="I6" t="s">
+        <v>57</v>
+      </c>
+      <c r="J6" t="s">
+        <v>57</v>
+      </c>
+      <c r="K6" t="s">
+        <v>57</v>
+      </c>
+      <c r="L6" t="s">
+        <v>67</v>
+      </c>
+      <c r="M6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N6" t="s">
+        <v>70</v>
+      </c>
+      <c r="O6" t="s">
+        <v>57</v>
+      </c>
+      <c r="P6" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q6" t="s">
         <v>56</v>
       </c>
-      <c r="C6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="R6" t="s">
+        <v>57</v>
+      </c>
+      <c r="S6" t="s">
+        <v>67</v>
+      </c>
+      <c r="T6" t="s">
         <v>56</v>
       </c>
-      <c r="F6" t="s">
-        <v>54</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="U6" t="s">
         <v>56</v>
       </c>
-      <c r="H6" t="s">
+      <c r="V6" t="s">
         <v>56</v>
       </c>
-      <c r="I6" t="s">
+      <c r="W6" t="s">
         <v>56</v>
       </c>
-      <c r="J6" t="s">
+      <c r="X6" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y6" t="s">
         <v>56</v>
       </c>
-      <c r="K6" t="s">
+      <c r="Z6" t="s">
         <v>56</v>
       </c>
-      <c r="L6" t="s">
+      <c r="AA6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>71</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>71</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>67</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AM6" t="s">
         <v>65</v>
       </c>
-      <c r="M6" t="s">
-        <v>56</v>
-      </c>
-      <c r="N6" t="s">
+      <c r="AN6" t="s">
+        <v>73</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS6" t="s">
         <v>68</v>
       </c>
-      <c r="O6" t="s">
-        <v>56</v>
-      </c>
-      <c r="P6" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>55</v>
-      </c>
-      <c r="R6" t="s">
-        <v>56</v>
-      </c>
-      <c r="S6" t="s">
-        <v>65</v>
-      </c>
-      <c r="T6" t="s">
-        <v>55</v>
-      </c>
-      <c r="U6" t="s">
-        <v>55</v>
-      </c>
-      <c r="V6" t="s">
-        <v>55</v>
-      </c>
-      <c r="W6" t="s">
-        <v>55</v>
-      </c>
-      <c r="X6" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>55</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>57</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>69</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>69</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>55</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>55</v>
-      </c>
-      <c r="AH6" t="s">
-        <v>70</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>55</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AK6" t="s">
-        <v>55</v>
-      </c>
-      <c r="AL6" t="s">
-        <v>56</v>
-      </c>
-      <c r="AM6" t="s">
-        <v>63</v>
-      </c>
-      <c r="AN6" t="s">
-        <v>71</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>62</v>
-      </c>
-      <c r="AP6" t="s">
-        <v>72</v>
-      </c>
-      <c r="AQ6" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR6" t="s">
-        <v>72</v>
-      </c>
-      <c r="AS6" t="s">
-        <v>66</v>
-      </c>
       <c r="AT6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G7" t="s">
+        <v>63</v>
+      </c>
+      <c r="H7" t="s">
+        <v>67</v>
+      </c>
+      <c r="I7" t="s">
+        <v>67</v>
+      </c>
+      <c r="J7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="K7" t="s">
+        <v>71</v>
+      </c>
+      <c r="L7" t="s">
+        <v>71</v>
+      </c>
+      <c r="M7" t="s">
         <v>56</v>
       </c>
-      <c r="D7" t="s">
+      <c r="N7" t="s">
+        <v>59</v>
+      </c>
+      <c r="O7" t="s">
         <v>56</v>
       </c>
-      <c r="E7" t="s">
-        <v>61</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="P7" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>70</v>
+      </c>
+      <c r="R7" t="s">
+        <v>67</v>
+      </c>
+      <c r="S7" t="s">
+        <v>58</v>
+      </c>
+      <c r="T7" t="s">
+        <v>67</v>
+      </c>
+      <c r="U7" t="s">
+        <v>71</v>
+      </c>
+      <c r="V7" t="s">
+        <v>71</v>
+      </c>
+      <c r="W7" t="s">
+        <v>58</v>
+      </c>
+      <c r="X7" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>71</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>67</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>77</v>
+      </c>
+      <c r="AE7" t="s">
         <v>65</v>
       </c>
-      <c r="G7" t="s">
-        <v>61</v>
-      </c>
-      <c r="H7" t="s">
-        <v>65</v>
-      </c>
-      <c r="I7" t="s">
-        <v>65</v>
-      </c>
-      <c r="J7" t="s">
-        <v>55</v>
-      </c>
-      <c r="K7" t="s">
-        <v>69</v>
-      </c>
-      <c r="L7" t="s">
-        <v>69</v>
-      </c>
-      <c r="M7" t="s">
-        <v>55</v>
-      </c>
-      <c r="N7" t="s">
+      <c r="AF7" t="s">
+        <v>67</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI7" t="s">
         <v>58</v>
       </c>
-      <c r="O7" t="s">
-        <v>55</v>
-      </c>
-      <c r="P7" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>68</v>
-      </c>
-      <c r="R7" t="s">
-        <v>65</v>
-      </c>
-      <c r="S7" t="s">
-        <v>57</v>
-      </c>
-      <c r="T7" t="s">
-        <v>65</v>
-      </c>
-      <c r="U7" t="s">
-        <v>69</v>
-      </c>
-      <c r="V7" t="s">
-        <v>69</v>
-      </c>
-      <c r="W7" t="s">
-        <v>57</v>
-      </c>
-      <c r="X7" t="s">
-        <v>56</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>65</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>65</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>75</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>65</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>75</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>63</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>65</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>69</v>
-      </c>
-      <c r="AH7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AI7" t="s">
-        <v>57</v>
-      </c>
       <c r="AJ7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AL7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AM7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AN7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AO7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AP7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AQ7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AR7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AS7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AT7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G8" t="s">
+        <v>58</v>
+      </c>
+      <c r="H8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I8" t="s">
+        <v>77</v>
+      </c>
+      <c r="J8" t="s">
+        <v>58</v>
+      </c>
+      <c r="K8" t="s">
+        <v>58</v>
+      </c>
+      <c r="L8" t="s">
+        <v>58</v>
+      </c>
+      <c r="M8" t="s">
+        <v>58</v>
+      </c>
+      <c r="N8" t="s">
+        <v>58</v>
+      </c>
+      <c r="O8" t="s">
+        <v>71</v>
+      </c>
+      <c r="P8" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>67</v>
+      </c>
+      <c r="R8" t="s">
+        <v>72</v>
+      </c>
+      <c r="S8" t="s">
+        <v>84</v>
+      </c>
+      <c r="T8" t="s">
+        <v>71</v>
+      </c>
+      <c r="U8" t="s">
+        <v>72</v>
+      </c>
+      <c r="V8" t="s">
+        <v>59</v>
+      </c>
+      <c r="W8" t="s">
         <v>55</v>
       </c>
-      <c r="B8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="X8" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>71</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>68</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>85</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>71</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>58</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>72</v>
+      </c>
+      <c r="AJ8" t="s">
         <v>65</v>
       </c>
-      <c r="D8" t="s">
-        <v>55</v>
-      </c>
-      <c r="E8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F8" t="s">
-        <v>57</v>
-      </c>
-      <c r="G8" t="s">
-        <v>57</v>
-      </c>
-      <c r="H8" t="s">
-        <v>69</v>
-      </c>
-      <c r="I8" t="s">
-        <v>75</v>
-      </c>
-      <c r="J8" t="s">
-        <v>57</v>
-      </c>
-      <c r="K8" t="s">
-        <v>57</v>
-      </c>
-      <c r="L8" t="s">
-        <v>57</v>
-      </c>
-      <c r="M8" t="s">
-        <v>57</v>
-      </c>
-      <c r="N8" t="s">
-        <v>57</v>
-      </c>
-      <c r="O8" t="s">
-        <v>69</v>
-      </c>
-      <c r="P8" t="s">
+      <c r="AK8" t="s">
+        <v>77</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>77</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>86</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AP8" t="s">
+        <v>60</v>
+      </c>
+      <c r="AQ8" t="s">
+        <v>83</v>
+      </c>
+      <c r="AR8" t="s">
+        <v>82</v>
+      </c>
+      <c r="AS8" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" t="s">
+        <v>71</v>
+      </c>
+      <c r="F9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9" t="s">
+        <v>71</v>
+      </c>
+      <c r="H9" t="s">
         <v>58</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="I9" t="s">
         <v>65</v>
       </c>
-      <c r="R8" t="s">
-        <v>70</v>
-      </c>
-      <c r="S8" t="s">
+      <c r="J9" t="s">
+        <v>65</v>
+      </c>
+      <c r="K9" t="s">
+        <v>65</v>
+      </c>
+      <c r="L9" t="s">
+        <v>77</v>
+      </c>
+      <c r="M9" t="s">
+        <v>77</v>
+      </c>
+      <c r="N9" t="s">
+        <v>74</v>
+      </c>
+      <c r="O9" t="s">
+        <v>77</v>
+      </c>
+      <c r="P9" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>77</v>
+      </c>
+      <c r="R9" t="s">
+        <v>84</v>
+      </c>
+      <c r="S9" t="s">
+        <v>65</v>
+      </c>
+      <c r="T9" t="s">
+        <v>77</v>
+      </c>
+      <c r="U9" t="s">
+        <v>77</v>
+      </c>
+      <c r="V9" t="s">
+        <v>77</v>
+      </c>
+      <c r="W9" t="s">
+        <v>77</v>
+      </c>
+      <c r="X9" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>73</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>68</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>77</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>85</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>77</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>91</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>68</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>81</v>
+      </c>
+      <c r="AN9" t="s">
         <v>82</v>
       </c>
-      <c r="T8" t="s">
-        <v>69</v>
-      </c>
-      <c r="U8" t="s">
-        <v>70</v>
-      </c>
-      <c r="V8" t="s">
-        <v>58</v>
-      </c>
-      <c r="W8" t="s">
-        <v>54</v>
-      </c>
-      <c r="X8" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>62</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC8" t="s">
-        <v>69</v>
-      </c>
-      <c r="AD8" t="s">
+      <c r="AO9" t="s">
         <v>66</v>
       </c>
-      <c r="AE8" t="s">
+      <c r="AP9" t="s">
+        <v>92</v>
+      </c>
+      <c r="AQ9" t="s">
+        <v>93</v>
+      </c>
+      <c r="AR9" t="s">
         <v>83</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>69</v>
-      </c>
-      <c r="AG8" t="s">
-        <v>57</v>
-      </c>
-      <c r="AH8" t="s">
-        <v>62</v>
-      </c>
-      <c r="AI8" t="s">
-        <v>70</v>
-      </c>
-      <c r="AJ8" t="s">
-        <v>63</v>
-      </c>
-      <c r="AK8" t="s">
-        <v>75</v>
-      </c>
-      <c r="AL8" t="s">
-        <v>75</v>
-      </c>
-      <c r="AM8" t="s">
-        <v>84</v>
-      </c>
-      <c r="AN8" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO8" t="s">
-        <v>76</v>
-      </c>
-      <c r="AP8" t="s">
-        <v>59</v>
-      </c>
-      <c r="AQ8" t="s">
-        <v>81</v>
-      </c>
-      <c r="AR8" t="s">
-        <v>80</v>
-      </c>
-      <c r="AS8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>68</v>
-      </c>
-      <c r="B9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" t="s">
-        <v>58</v>
-      </c>
-      <c r="D9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E9" t="s">
-        <v>69</v>
-      </c>
-      <c r="F9" t="s">
-        <v>63</v>
-      </c>
-      <c r="G9" t="s">
-        <v>69</v>
-      </c>
-      <c r="H9" t="s">
-        <v>57</v>
-      </c>
-      <c r="I9" t="s">
-        <v>63</v>
-      </c>
-      <c r="J9" t="s">
-        <v>63</v>
-      </c>
-      <c r="K9" t="s">
-        <v>63</v>
-      </c>
-      <c r="L9" t="s">
-        <v>75</v>
-      </c>
-      <c r="M9" t="s">
-        <v>75</v>
-      </c>
-      <c r="N9" t="s">
-        <v>72</v>
-      </c>
-      <c r="O9" t="s">
-        <v>75</v>
-      </c>
-      <c r="P9" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>75</v>
-      </c>
-      <c r="R9" t="s">
-        <v>82</v>
-      </c>
-      <c r="S9" t="s">
-        <v>63</v>
-      </c>
-      <c r="T9" t="s">
-        <v>75</v>
-      </c>
-      <c r="U9" t="s">
-        <v>75</v>
-      </c>
-      <c r="V9" t="s">
-        <v>75</v>
-      </c>
-      <c r="W9" t="s">
-        <v>75</v>
-      </c>
-      <c r="X9" t="s">
-        <v>63</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>75</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>71</v>
-      </c>
-      <c r="AC9" t="s">
-        <v>75</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>87</v>
-      </c>
-      <c r="AE9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>75</v>
-      </c>
-      <c r="AG9" t="s">
-        <v>75</v>
-      </c>
-      <c r="AH9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AI9" t="s">
-        <v>75</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>88</v>
-      </c>
-      <c r="AK9" t="s">
-        <v>88</v>
-      </c>
-      <c r="AL9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AM9" t="s">
-        <v>79</v>
-      </c>
-      <c r="AN9" t="s">
-        <v>80</v>
-      </c>
-      <c r="AO9" t="s">
-        <v>64</v>
-      </c>
-      <c r="AP9" t="s">
-        <v>89</v>
-      </c>
-      <c r="AQ9" t="s">
-        <v>90</v>
-      </c>
-      <c r="AR9" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" t="s">
+        <v>94</v>
+      </c>
+      <c r="G10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H10" t="s">
+        <v>77</v>
+      </c>
+      <c r="I10" t="s">
+        <v>74</v>
+      </c>
+      <c r="J10" t="s">
+        <v>74</v>
+      </c>
+      <c r="K10" t="s">
+        <v>64</v>
+      </c>
+      <c r="L10" t="s">
+        <v>65</v>
+      </c>
+      <c r="M10" t="s">
+        <v>74</v>
+      </c>
+      <c r="N10" t="s">
+        <v>64</v>
+      </c>
+      <c r="O10" t="s">
+        <v>65</v>
+      </c>
+      <c r="P10" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>74</v>
+      </c>
+      <c r="R10" t="s">
+        <v>65</v>
+      </c>
+      <c r="S10" t="s">
+        <v>64</v>
+      </c>
+      <c r="T10" t="s">
+        <v>94</v>
+      </c>
+      <c r="U10" t="s">
+        <v>95</v>
+      </c>
+      <c r="V10" t="s">
+        <v>65</v>
+      </c>
+      <c r="W10" t="s">
+        <v>74</v>
+      </c>
+      <c r="X10" t="s">
+        <v>95</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>86</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>74</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>91</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>95</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>80</v>
+      </c>
+      <c r="AM10" t="s">
+        <v>90</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>92</v>
+      </c>
+      <c r="AO10" t="s">
+        <v>96</v>
+      </c>
+      <c r="AP10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AQ10" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" t="s">
+        <v>77</v>
+      </c>
+      <c r="F11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G11" t="s">
+        <v>84</v>
+      </c>
+      <c r="H11" t="s">
+        <v>65</v>
+      </c>
+      <c r="I11" t="s">
+        <v>95</v>
+      </c>
+      <c r="J11" t="s">
+        <v>64</v>
+      </c>
+      <c r="K11" t="s">
+        <v>85</v>
+      </c>
+      <c r="L11" t="s">
+        <v>64</v>
+      </c>
+      <c r="M11" t="s">
+        <v>64</v>
+      </c>
+      <c r="N11" t="s">
+        <v>68</v>
+      </c>
+      <c r="O11" t="s">
+        <v>74</v>
+      </c>
+      <c r="P11" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>64</v>
+      </c>
+      <c r="R11" t="s">
+        <v>64</v>
+      </c>
+      <c r="S11" t="s">
+        <v>73</v>
+      </c>
+      <c r="T11" t="s">
+        <v>64</v>
+      </c>
+      <c r="U11" t="s">
+        <v>68</v>
+      </c>
+      <c r="V11" t="s">
+        <v>64</v>
+      </c>
+      <c r="W11" t="s">
+        <v>64</v>
+      </c>
+      <c r="X11" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>95</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>95</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>78</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>68</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>76</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>99</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>68</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>81</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>99</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>79</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>100</v>
+      </c>
+      <c r="AM11" t="s">
+        <v>79</v>
+      </c>
+      <c r="AN11" t="s">
         <v>69</v>
       </c>
-      <c r="B10" t="s">
-        <v>54</v>
-      </c>
-      <c r="C10" t="s">
-        <v>63</v>
-      </c>
-      <c r="D10" t="s">
-        <v>72</v>
-      </c>
-      <c r="E10" t="s">
-        <v>54</v>
-      </c>
-      <c r="F10" t="s">
-        <v>91</v>
-      </c>
-      <c r="G10" t="s">
-        <v>75</v>
-      </c>
-      <c r="H10" t="s">
-        <v>75</v>
-      </c>
-      <c r="I10" t="s">
-        <v>72</v>
-      </c>
-      <c r="J10" t="s">
-        <v>72</v>
-      </c>
-      <c r="K10" t="s">
-        <v>62</v>
-      </c>
-      <c r="L10" t="s">
-        <v>63</v>
-      </c>
-      <c r="M10" t="s">
-        <v>72</v>
-      </c>
-      <c r="N10" t="s">
-        <v>62</v>
-      </c>
-      <c r="O10" t="s">
-        <v>63</v>
-      </c>
-      <c r="P10" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>72</v>
-      </c>
-      <c r="R10" t="s">
-        <v>63</v>
-      </c>
-      <c r="S10" t="s">
-        <v>62</v>
-      </c>
-      <c r="T10" t="s">
-        <v>91</v>
-      </c>
-      <c r="U10" t="s">
-        <v>92</v>
-      </c>
-      <c r="V10" t="s">
-        <v>63</v>
-      </c>
-      <c r="W10" t="s">
-        <v>72</v>
-      </c>
-      <c r="X10" t="s">
-        <v>92</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>71</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>77</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>71</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>88</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>72</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>84</v>
-      </c>
-      <c r="AE10" t="s">
-        <v>87</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>72</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>82</v>
-      </c>
-      <c r="AH10" t="s">
-        <v>88</v>
-      </c>
-      <c r="AI10" t="s">
-        <v>63</v>
-      </c>
-      <c r="AJ10" t="s">
-        <v>92</v>
-      </c>
-      <c r="AK10" t="s">
-        <v>71</v>
-      </c>
-      <c r="AL10" t="s">
-        <v>78</v>
-      </c>
-      <c r="AM10" t="s">
-        <v>87</v>
-      </c>
-      <c r="AN10" t="s">
-        <v>89</v>
-      </c>
-      <c r="AO10" t="s">
-        <v>93</v>
-      </c>
-      <c r="AP10" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>63</v>
-      </c>
-      <c r="B11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" t="s">
-        <v>72</v>
-      </c>
-      <c r="D11" t="s">
-        <v>62</v>
-      </c>
-      <c r="E11" t="s">
-        <v>75</v>
-      </c>
-      <c r="F11" t="s">
-        <v>62</v>
-      </c>
-      <c r="G11" t="s">
-        <v>82</v>
-      </c>
-      <c r="H11" t="s">
-        <v>63</v>
-      </c>
-      <c r="I11" t="s">
-        <v>92</v>
-      </c>
-      <c r="J11" t="s">
-        <v>62</v>
-      </c>
-      <c r="K11" t="s">
-        <v>83</v>
-      </c>
-      <c r="L11" t="s">
-        <v>62</v>
-      </c>
-      <c r="M11" t="s">
-        <v>62</v>
-      </c>
-      <c r="N11" t="s">
-        <v>66</v>
-      </c>
-      <c r="O11" t="s">
-        <v>72</v>
-      </c>
-      <c r="P11" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>62</v>
-      </c>
-      <c r="R11" t="s">
-        <v>62</v>
-      </c>
-      <c r="S11" t="s">
-        <v>71</v>
-      </c>
-      <c r="T11" t="s">
-        <v>62</v>
-      </c>
-      <c r="U11" t="s">
-        <v>66</v>
-      </c>
-      <c r="V11" t="s">
-        <v>62</v>
-      </c>
-      <c r="W11" t="s">
-        <v>62</v>
-      </c>
-      <c r="X11" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>95</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB11" t="s">
+      <c r="AO11" t="s">
         <v>76</v>
       </c>
-      <c r="AC11" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>74</v>
-      </c>
-      <c r="AE11" t="s">
-        <v>55</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>95</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>66</v>
-      </c>
-      <c r="AH11" t="s">
-        <v>79</v>
-      </c>
-      <c r="AI11" t="s">
-        <v>95</v>
-      </c>
-      <c r="AJ11" t="s">
-        <v>77</v>
-      </c>
-      <c r="AK11" t="s">
-        <v>84</v>
-      </c>
-      <c r="AL11" t="s">
-        <v>96</v>
-      </c>
-      <c r="AM11" t="s">
-        <v>77</v>
-      </c>
-      <c r="AN11" t="s">
-        <v>97</v>
-      </c>
-      <c r="AO11" t="s">
-        <v>74</v>
-      </c>
       <c r="AP11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E12" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F12" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H12" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I12" t="s">
+        <v>68</v>
+      </c>
+      <c r="J12" t="s">
+        <v>73</v>
+      </c>
+      <c r="K12" t="s">
+        <v>90</v>
+      </c>
+      <c r="L12" t="s">
+        <v>68</v>
+      </c>
+      <c r="M12" t="s">
+        <v>73</v>
+      </c>
+      <c r="N12" t="s">
+        <v>90</v>
+      </c>
+      <c r="O12" t="s">
+        <v>78</v>
+      </c>
+      <c r="P12" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>68</v>
+      </c>
+      <c r="R12" t="s">
+        <v>68</v>
+      </c>
+      <c r="S12" t="s">
+        <v>68</v>
+      </c>
+      <c r="T12" t="s">
+        <v>91</v>
+      </c>
+      <c r="U12" t="s">
+        <v>79</v>
+      </c>
+      <c r="V12" t="s">
+        <v>73</v>
+      </c>
+      <c r="W12" t="s">
+        <v>73</v>
+      </c>
+      <c r="X12" t="s">
+        <v>90</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>91</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>90</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>87</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>78</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>99</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>102</v>
+      </c>
+      <c r="AM12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>104</v>
+      </c>
+      <c r="AO12" t="s">
+        <v>83</v>
+      </c>
+      <c r="AP12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" t="s">
+        <v>95</v>
+      </c>
+      <c r="E13" t="s">
+        <v>73</v>
+      </c>
+      <c r="F13" t="s">
+        <v>68</v>
+      </c>
+      <c r="G13" t="s">
+        <v>68</v>
+      </c>
+      <c r="H13" t="s">
+        <v>73</v>
+      </c>
+      <c r="I13" t="s">
+        <v>86</v>
+      </c>
+      <c r="J13" t="s">
+        <v>78</v>
+      </c>
+      <c r="K13" t="s">
+        <v>79</v>
+      </c>
+      <c r="L13" t="s">
+        <v>90</v>
+      </c>
+      <c r="M13" t="s">
+        <v>68</v>
+      </c>
+      <c r="N13" t="s">
+        <v>78</v>
+      </c>
+      <c r="O13" t="s">
+        <v>79</v>
+      </c>
+      <c r="P13" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>78</v>
+      </c>
+      <c r="R13" t="s">
+        <v>77</v>
+      </c>
+      <c r="S13" t="s">
+        <v>79</v>
+      </c>
+      <c r="T13" t="s">
+        <v>90</v>
+      </c>
+      <c r="U13" t="s">
+        <v>86</v>
+      </c>
+      <c r="V13" t="s">
+        <v>78</v>
+      </c>
+      <c r="W13" t="s">
+        <v>78</v>
+      </c>
+      <c r="X13" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>99</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>99</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>100</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>87</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>81</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>76</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>96</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>87</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>87</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>82</v>
+      </c>
+      <c r="AM13" t="s">
+        <v>96</v>
+      </c>
+      <c r="AN13" t="s">
         <v>66</v>
       </c>
-      <c r="J12" t="s">
-        <v>71</v>
-      </c>
-      <c r="K12" t="s">
+      <c r="AO13" t="s">
+        <v>97</v>
+      </c>
+      <c r="AP13" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" t="s">
+        <v>95</v>
+      </c>
+      <c r="D14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" t="s">
+        <v>95</v>
+      </c>
+      <c r="F14" t="s">
+        <v>90</v>
+      </c>
+      <c r="G14" t="s">
+        <v>90</v>
+      </c>
+      <c r="H14" t="s">
+        <v>68</v>
+      </c>
+      <c r="I14" t="s">
+        <v>99</v>
+      </c>
+      <c r="J14" t="s">
+        <v>101</v>
+      </c>
+      <c r="K14" t="s">
+        <v>99</v>
+      </c>
+      <c r="L14" t="s">
+        <v>79</v>
+      </c>
+      <c r="M14" t="s">
+        <v>78</v>
+      </c>
+      <c r="N14" t="s">
+        <v>79</v>
+      </c>
+      <c r="O14" t="s">
+        <v>86</v>
+      </c>
+      <c r="P14" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>81</v>
+      </c>
+      <c r="R14" t="s">
+        <v>79</v>
+      </c>
+      <c r="S14" t="s">
+        <v>81</v>
+      </c>
+      <c r="T14" t="s">
+        <v>99</v>
+      </c>
+      <c r="U14" t="s">
+        <v>76</v>
+      </c>
+      <c r="V14" t="s">
+        <v>81</v>
+      </c>
+      <c r="W14" t="s">
+        <v>79</v>
+      </c>
+      <c r="X14" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>81</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB14" t="s">
         <v>87</v>
       </c>
-      <c r="L12" t="s">
-        <v>66</v>
-      </c>
-      <c r="M12" t="s">
-        <v>71</v>
-      </c>
-      <c r="N12" t="s">
-        <v>87</v>
-      </c>
-      <c r="O12" t="s">
-        <v>76</v>
-      </c>
-      <c r="P12" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>66</v>
-      </c>
-      <c r="R12" t="s">
-        <v>66</v>
-      </c>
-      <c r="S12" t="s">
-        <v>66</v>
-      </c>
-      <c r="T12" t="s">
-        <v>88</v>
-      </c>
-      <c r="U12" t="s">
-        <v>77</v>
-      </c>
-      <c r="V12" t="s">
-        <v>71</v>
-      </c>
-      <c r="W12" t="s">
-        <v>71</v>
-      </c>
-      <c r="X12" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>76</v>
-      </c>
-      <c r="Z12" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA12" t="s">
-        <v>88</v>
-      </c>
-      <c r="AB12" t="s">
-        <v>98</v>
-      </c>
-      <c r="AC12" t="s">
-        <v>87</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AE12" t="s">
-        <v>76</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>78</v>
-      </c>
-      <c r="AG12" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH12" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AJ12" t="s">
-        <v>78</v>
-      </c>
-      <c r="AK12" t="s">
-        <v>95</v>
-      </c>
-      <c r="AL12" t="s">
+      <c r="AC14" t="s">
+        <v>81</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>102</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>100</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>102</v>
+      </c>
+      <c r="AG14" t="s">
         <v>99</v>
       </c>
-      <c r="AM12" t="s">
-        <v>100</v>
-      </c>
-      <c r="AN12" t="s">
-        <v>101</v>
-      </c>
-      <c r="AO12" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13" t="s">
-        <v>71</v>
-      </c>
-      <c r="D13" t="s">
-        <v>92</v>
-      </c>
-      <c r="E13" t="s">
-        <v>71</v>
-      </c>
-      <c r="F13" t="s">
-        <v>66</v>
-      </c>
-      <c r="G13" t="s">
-        <v>66</v>
-      </c>
-      <c r="H13" t="s">
-        <v>71</v>
-      </c>
-      <c r="I13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J13" t="s">
-        <v>76</v>
-      </c>
-      <c r="K13" t="s">
-        <v>77</v>
-      </c>
-      <c r="L13" t="s">
-        <v>87</v>
-      </c>
-      <c r="M13" t="s">
-        <v>66</v>
-      </c>
-      <c r="N13" t="s">
-        <v>76</v>
-      </c>
-      <c r="O13" t="s">
-        <v>77</v>
-      </c>
-      <c r="P13" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>76</v>
-      </c>
-      <c r="R13" t="s">
-        <v>75</v>
-      </c>
-      <c r="S13" t="s">
-        <v>77</v>
-      </c>
-      <c r="T13" t="s">
-        <v>87</v>
-      </c>
-      <c r="U13" t="s">
-        <v>84</v>
-      </c>
-      <c r="V13" t="s">
-        <v>76</v>
-      </c>
-      <c r="W13" t="s">
-        <v>76</v>
-      </c>
-      <c r="X13" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>77</v>
-      </c>
-      <c r="Z13" t="s">
-        <v>74</v>
-      </c>
-      <c r="AA13" t="s">
-        <v>95</v>
-      </c>
-      <c r="AB13" t="s">
-        <v>95</v>
-      </c>
-      <c r="AC13" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>96</v>
-      </c>
-      <c r="AE13" t="s">
-        <v>78</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>85</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>79</v>
-      </c>
-      <c r="AH13" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI13" t="s">
-        <v>93</v>
-      </c>
-      <c r="AJ13" t="s">
-        <v>85</v>
-      </c>
-      <c r="AK13" t="s">
-        <v>85</v>
-      </c>
-      <c r="AL13" t="s">
-        <v>80</v>
-      </c>
-      <c r="AM13" t="s">
-        <v>102</v>
-      </c>
-      <c r="AN13" t="s">
-        <v>64</v>
-      </c>
-      <c r="AO13" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>83</v>
-      </c>
-      <c r="B14" t="s">
-        <v>62</v>
-      </c>
-      <c r="C14" t="s">
-        <v>92</v>
-      </c>
-      <c r="D14" t="s">
-        <v>66</v>
-      </c>
-      <c r="E14" t="s">
-        <v>92</v>
-      </c>
-      <c r="F14" t="s">
-        <v>87</v>
-      </c>
-      <c r="G14" t="s">
-        <v>87</v>
-      </c>
-      <c r="H14" t="s">
-        <v>66</v>
-      </c>
-      <c r="I14" t="s">
-        <v>95</v>
-      </c>
-      <c r="J14" t="s">
-        <v>98</v>
-      </c>
-      <c r="K14" t="s">
-        <v>95</v>
-      </c>
-      <c r="L14" t="s">
-        <v>77</v>
-      </c>
-      <c r="M14" t="s">
-        <v>76</v>
-      </c>
-      <c r="N14" t="s">
-        <v>77</v>
-      </c>
-      <c r="O14" t="s">
-        <v>84</v>
-      </c>
-      <c r="P14" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>79</v>
-      </c>
-      <c r="R14" t="s">
-        <v>77</v>
-      </c>
-      <c r="S14" t="s">
-        <v>79</v>
-      </c>
-      <c r="T14" t="s">
-        <v>95</v>
-      </c>
-      <c r="U14" t="s">
-        <v>74</v>
-      </c>
-      <c r="V14" t="s">
-        <v>79</v>
-      </c>
-      <c r="W14" t="s">
-        <v>77</v>
-      </c>
-      <c r="X14" t="s">
-        <v>76</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>99</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>78</v>
-      </c>
-      <c r="AB14" t="s">
-        <v>85</v>
-      </c>
-      <c r="AC14" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD14" t="s">
-        <v>99</v>
-      </c>
-      <c r="AE14" t="s">
-        <v>96</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>99</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>95</v>
-      </c>
       <c r="AH14" t="s">
+        <v>106</v>
+      </c>
+      <c r="AI14" t="s">
         <v>103</v>
       </c>
-      <c r="AI14" t="s">
-        <v>100</v>
-      </c>
       <c r="AJ14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="AK14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="AL14" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM14" t="s">
+        <v>97</v>
+      </c>
+      <c r="AN14" t="s">
+        <v>107</v>
+      </c>
+      <c r="AO14" t="s">
         <v>60</v>
-      </c>
-      <c r="AM14" t="s">
-        <v>93</v>
-      </c>
-      <c r="AN14" t="s">
-        <v>104</v>
-      </c>
-      <c r="AO14" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>95</v>
+      </c>
+      <c r="B15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E15" t="s">
+        <v>68</v>
+      </c>
+      <c r="F15" t="s">
+        <v>79</v>
+      </c>
+      <c r="G15" t="s">
+        <v>78</v>
+      </c>
+      <c r="H15" t="s">
+        <v>79</v>
+      </c>
+      <c r="I15" t="s">
+        <v>80</v>
+      </c>
+      <c r="J15" t="s">
+        <v>81</v>
+      </c>
+      <c r="K15" t="s">
+        <v>80</v>
+      </c>
+      <c r="L15" t="s">
+        <v>86</v>
+      </c>
+      <c r="M15" t="s">
+        <v>86</v>
+      </c>
+      <c r="N15" t="s">
+        <v>101</v>
+      </c>
+      <c r="O15" t="s">
+        <v>99</v>
+      </c>
+      <c r="P15" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>99</v>
+      </c>
+      <c r="R15" t="s">
+        <v>86</v>
+      </c>
+      <c r="S15" t="s">
+        <v>99</v>
+      </c>
+      <c r="T15" t="s">
+        <v>80</v>
+      </c>
+      <c r="U15" t="s">
+        <v>87</v>
+      </c>
+      <c r="V15" t="s">
+        <v>99</v>
+      </c>
+      <c r="W15" t="s">
+        <v>86</v>
+      </c>
+      <c r="X15" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>102</v>
+      </c>
+      <c r="AF15" t="s">
+        <v>94</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>76</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>96</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>66</v>
+      </c>
+      <c r="AK15" t="s">
+        <v>66</v>
+      </c>
+      <c r="AL15" t="s">
         <v>92</v>
       </c>
-      <c r="B15" t="s">
-        <v>71</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="AN15" t="s">
+        <v>83</v>
+      </c>
+      <c r="AO15" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16" t="s">
+        <v>78</v>
+      </c>
+      <c r="E16" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" t="s">
+        <v>86</v>
+      </c>
+      <c r="G16" t="s">
+        <v>79</v>
+      </c>
+      <c r="H16" t="s">
+        <v>81</v>
+      </c>
+      <c r="I16" t="s">
+        <v>76</v>
+      </c>
+      <c r="J16" t="s">
+        <v>80</v>
+      </c>
+      <c r="K16" t="s">
+        <v>106</v>
+      </c>
+      <c r="L16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M16" t="s">
+        <v>81</v>
+      </c>
+      <c r="N16" t="s">
+        <v>86</v>
+      </c>
+      <c r="O16" t="s">
+        <v>80</v>
+      </c>
+      <c r="P16" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>76</v>
+      </c>
+      <c r="R16" t="s">
+        <v>99</v>
+      </c>
+      <c r="S16" t="s">
+        <v>76</v>
+      </c>
+      <c r="T16" t="s">
+        <v>76</v>
+      </c>
+      <c r="U16" t="s">
+        <v>106</v>
+      </c>
+      <c r="V16" t="s">
+        <v>76</v>
+      </c>
+      <c r="W16" t="s">
+        <v>81</v>
+      </c>
+      <c r="X16" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA16" t="s">
         <v>66</v>
       </c>
-      <c r="D15" t="s">
+      <c r="AB16" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC16" t="s">
         <v>87</v>
       </c>
-      <c r="E15" t="s">
+      <c r="AD16" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>96</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>103</v>
+      </c>
+      <c r="AG16" t="s">
+        <v>100</v>
+      </c>
+      <c r="AH16" t="s">
         <v>66</v>
       </c>
-      <c r="F15" t="s">
-        <v>77</v>
-      </c>
-      <c r="G15" t="s">
-        <v>76</v>
-      </c>
-      <c r="H15" t="s">
-        <v>77</v>
-      </c>
-      <c r="I15" t="s">
-        <v>78</v>
-      </c>
-      <c r="J15" t="s">
-        <v>79</v>
-      </c>
-      <c r="K15" t="s">
-        <v>78</v>
-      </c>
-      <c r="L15" t="s">
-        <v>84</v>
-      </c>
-      <c r="M15" t="s">
-        <v>84</v>
-      </c>
-      <c r="N15" t="s">
-        <v>98</v>
-      </c>
-      <c r="O15" t="s">
-        <v>95</v>
-      </c>
-      <c r="P15" t="s">
+      <c r="AI16" t="s">
+        <v>92</v>
+      </c>
+      <c r="AJ16" t="s">
+        <v>60</v>
+      </c>
+      <c r="AK16" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL16" t="s">
+        <v>99</v>
+      </c>
+      <c r="AN16" t="s">
         <v>105</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>95</v>
-      </c>
-      <c r="R15" t="s">
-        <v>84</v>
-      </c>
-      <c r="S15" t="s">
-        <v>95</v>
-      </c>
-      <c r="T15" t="s">
-        <v>78</v>
-      </c>
-      <c r="U15" t="s">
-        <v>85</v>
-      </c>
-      <c r="V15" t="s">
-        <v>95</v>
-      </c>
-      <c r="W15" t="s">
-        <v>84</v>
-      </c>
-      <c r="X15" t="s">
-        <v>84</v>
-      </c>
-      <c r="Y15" t="s">
-        <v>74</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>88</v>
-      </c>
-      <c r="AA15" t="s">
-        <v>85</v>
-      </c>
-      <c r="AB15" t="s">
-        <v>77</v>
-      </c>
-      <c r="AC15" t="s">
-        <v>74</v>
-      </c>
-      <c r="AD15" t="s">
-        <v>62</v>
-      </c>
-      <c r="AE15" t="s">
-        <v>99</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AG15" t="s">
-        <v>74</v>
-      </c>
-      <c r="AH15" t="s">
-        <v>93</v>
-      </c>
-      <c r="AI15" t="s">
-        <v>73</v>
-      </c>
-      <c r="AJ15" t="s">
-        <v>64</v>
-      </c>
-      <c r="AK15" t="s">
-        <v>64</v>
-      </c>
-      <c r="AL15" t="s">
-        <v>89</v>
-      </c>
-      <c r="AM15" t="s">
-        <v>94</v>
-      </c>
-      <c r="AN15" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>66</v>
-      </c>
-      <c r="B16" t="s">
-        <v>92</v>
-      </c>
-      <c r="C16" t="s">
-        <v>87</v>
-      </c>
-      <c r="D16" t="s">
-        <v>76</v>
-      </c>
-      <c r="E16" t="s">
-        <v>76</v>
-      </c>
-      <c r="F16" t="s">
-        <v>84</v>
-      </c>
-      <c r="G16" t="s">
-        <v>77</v>
-      </c>
-      <c r="H16" t="s">
-        <v>79</v>
-      </c>
-      <c r="I16" t="s">
-        <v>74</v>
-      </c>
-      <c r="J16" t="s">
-        <v>78</v>
-      </c>
-      <c r="K16" t="s">
-        <v>103</v>
-      </c>
-      <c r="L16" t="s">
-        <v>74</v>
-      </c>
-      <c r="M16" t="s">
-        <v>79</v>
-      </c>
-      <c r="N16" t="s">
-        <v>84</v>
-      </c>
-      <c r="O16" t="s">
-        <v>78</v>
-      </c>
-      <c r="P16" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>74</v>
-      </c>
-      <c r="R16" t="s">
-        <v>95</v>
-      </c>
-      <c r="S16" t="s">
-        <v>74</v>
-      </c>
-      <c r="T16" t="s">
-        <v>74</v>
-      </c>
-      <c r="U16" t="s">
-        <v>103</v>
-      </c>
-      <c r="V16" t="s">
-        <v>74</v>
-      </c>
-      <c r="W16" t="s">
-        <v>79</v>
-      </c>
-      <c r="X16" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y16" t="s">
-        <v>85</v>
-      </c>
-      <c r="Z16" t="s">
-        <v>105</v>
-      </c>
-      <c r="AA16" t="s">
-        <v>64</v>
-      </c>
-      <c r="AB16" t="s">
-        <v>64</v>
-      </c>
-      <c r="AC16" t="s">
-        <v>85</v>
-      </c>
-      <c r="AD16" t="s">
-        <v>93</v>
-      </c>
-      <c r="AE16" t="s">
-        <v>93</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>100</v>
-      </c>
-      <c r="AG16" t="s">
-        <v>96</v>
-      </c>
-      <c r="AH16" t="s">
-        <v>64</v>
-      </c>
-      <c r="AI16" t="s">
-        <v>89</v>
-      </c>
-      <c r="AJ16" t="s">
-        <v>59</v>
-      </c>
-      <c r="AK16" t="s">
-        <v>80</v>
-      </c>
-      <c r="AL16" t="s">
-        <v>95</v>
-      </c>
-      <c r="AN16" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17" t="s">
+        <v>79</v>
+      </c>
+      <c r="E17" t="s">
+        <v>79</v>
+      </c>
+      <c r="F17" t="s">
+        <v>99</v>
+      </c>
+      <c r="G17" t="s">
+        <v>99</v>
+      </c>
+      <c r="H17" t="s">
+        <v>80</v>
+      </c>
+      <c r="I17" t="s">
+        <v>106</v>
+      </c>
+      <c r="J17" t="s">
+        <v>76</v>
+      </c>
+      <c r="K17" t="s">
+        <v>109</v>
+      </c>
+      <c r="L17" t="s">
+        <v>106</v>
+      </c>
+      <c r="M17" t="s">
+        <v>80</v>
+      </c>
+      <c r="N17" t="s">
+        <v>76</v>
+      </c>
+      <c r="O17" t="s">
         <v>87</v>
       </c>
-      <c r="B17" t="s">
-        <v>66</v>
-      </c>
-      <c r="C17" t="s">
-        <v>77</v>
-      </c>
-      <c r="D17" t="s">
-        <v>77</v>
-      </c>
-      <c r="E17" t="s">
-        <v>77</v>
-      </c>
-      <c r="F17" t="s">
-        <v>95</v>
-      </c>
-      <c r="G17" t="s">
-        <v>95</v>
-      </c>
-      <c r="H17" t="s">
-        <v>78</v>
-      </c>
-      <c r="I17" t="s">
+      <c r="P17" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>87</v>
+      </c>
+      <c r="R17" t="s">
+        <v>87</v>
+      </c>
+      <c r="S17" t="s">
+        <v>102</v>
+      </c>
+      <c r="T17" t="s">
+        <v>100</v>
+      </c>
+      <c r="U17" t="s">
+        <v>101</v>
+      </c>
+      <c r="V17" t="s">
+        <v>87</v>
+      </c>
+      <c r="W17" t="s">
+        <v>99</v>
+      </c>
+      <c r="X17" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>106</v>
+      </c>
+      <c r="Z17" t="s">
         <v>103</v>
       </c>
-      <c r="J17" t="s">
-        <v>74</v>
-      </c>
-      <c r="K17" t="s">
-        <v>107</v>
-      </c>
-      <c r="L17" t="s">
+      <c r="AA17" t="s">
+        <v>110</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>82</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>102</v>
+      </c>
+      <c r="AD17" t="s">
         <v>103</v>
       </c>
-      <c r="M17" t="s">
-        <v>78</v>
-      </c>
-      <c r="N17" t="s">
-        <v>74</v>
-      </c>
-      <c r="O17" t="s">
-        <v>85</v>
-      </c>
-      <c r="P17" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>85</v>
-      </c>
-      <c r="R17" t="s">
-        <v>85</v>
-      </c>
-      <c r="S17" t="s">
-        <v>99</v>
-      </c>
-      <c r="T17" t="s">
+      <c r="AE17" t="s">
+        <v>82</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG17" t="s">
         <v>96</v>
       </c>
-      <c r="U17" t="s">
-        <v>98</v>
-      </c>
-      <c r="V17" t="s">
-        <v>85</v>
-      </c>
-      <c r="W17" t="s">
-        <v>95</v>
-      </c>
-      <c r="X17" t="s">
-        <v>107</v>
-      </c>
-      <c r="Y17" t="s">
-        <v>103</v>
-      </c>
-      <c r="Z17" t="s">
-        <v>100</v>
-      </c>
-      <c r="AA17" t="s">
-        <v>108</v>
-      </c>
-      <c r="AB17" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC17" t="s">
-        <v>99</v>
-      </c>
-      <c r="AD17" t="s">
-        <v>100</v>
-      </c>
-      <c r="AE17" t="s">
-        <v>80</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>108</v>
-      </c>
-      <c r="AG17" t="s">
+      <c r="AH17" t="s">
+        <v>92</v>
+      </c>
+      <c r="AI17" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ17" t="s">
+        <v>92</v>
+      </c>
+      <c r="AK17" t="s">
+        <v>92</v>
+      </c>
+      <c r="AL17" t="s">
         <v>93</v>
       </c>
-      <c r="AH17" t="s">
-        <v>89</v>
-      </c>
-      <c r="AI17" t="s">
-        <v>102</v>
-      </c>
-      <c r="AJ17" t="s">
-        <v>89</v>
-      </c>
-      <c r="AK17" t="s">
-        <v>89</v>
-      </c>
-      <c r="AL17" t="s">
-        <v>90</v>
-      </c>
       <c r="AN17" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>78</v>
+      </c>
+      <c r="B18" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" t="s">
+        <v>101</v>
+      </c>
+      <c r="D18" t="s">
+        <v>101</v>
+      </c>
+      <c r="E18" t="s">
         <v>76</v>
       </c>
-      <c r="B18" t="s">
+      <c r="F18" t="s">
         <v>76</v>
       </c>
-      <c r="C18" t="s">
-        <v>98</v>
-      </c>
-      <c r="D18" t="s">
-        <v>98</v>
-      </c>
-      <c r="E18" t="s">
-        <v>74</v>
-      </c>
-      <c r="F18" t="s">
-        <v>74</v>
-      </c>
       <c r="G18" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H18" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I18" t="s">
+        <v>100</v>
+      </c>
+      <c r="J18" t="s">
+        <v>87</v>
+      </c>
+      <c r="K18" t="s">
         <v>96</v>
       </c>
-      <c r="J18" t="s">
-        <v>85</v>
-      </c>
-      <c r="K18" t="s">
+      <c r="L18" t="s">
+        <v>100</v>
+      </c>
+      <c r="M18" t="s">
+        <v>100</v>
+      </c>
+      <c r="N18" t="s">
+        <v>87</v>
+      </c>
+      <c r="O18" t="s">
+        <v>102</v>
+      </c>
+      <c r="P18" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>66</v>
+      </c>
+      <c r="R18" t="s">
+        <v>100</v>
+      </c>
+      <c r="S18" t="s">
+        <v>103</v>
+      </c>
+      <c r="T18" t="s">
+        <v>103</v>
+      </c>
+      <c r="U18" t="s">
+        <v>96</v>
+      </c>
+      <c r="V18" t="s">
+        <v>96</v>
+      </c>
+      <c r="W18" t="s">
+        <v>76</v>
+      </c>
+      <c r="X18" t="s">
+        <v>111</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>82</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE18" t="s">
+        <v>92</v>
+      </c>
+      <c r="AF18" t="s">
+        <v>75</v>
+      </c>
+      <c r="AG18" t="s">
+        <v>110</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>69</v>
+      </c>
+      <c r="AI18" t="s">
+        <v>83</v>
+      </c>
+      <c r="AJ18" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK18" t="s">
+        <v>69</v>
+      </c>
+      <c r="AL18" t="s">
+        <v>89</v>
+      </c>
+      <c r="AN18" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>79</v>
+      </c>
+      <c r="B19" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" t="s">
+        <v>86</v>
+      </c>
+      <c r="D19" t="s">
+        <v>86</v>
+      </c>
+      <c r="E19" t="s">
+        <v>106</v>
+      </c>
+      <c r="F19" t="s">
+        <v>87</v>
+      </c>
+      <c r="G19" t="s">
+        <v>87</v>
+      </c>
+      <c r="H19" t="s">
+        <v>106</v>
+      </c>
+      <c r="I19" t="s">
+        <v>81</v>
+      </c>
+      <c r="J19" t="s">
+        <v>96</v>
+      </c>
+      <c r="K19" t="s">
+        <v>82</v>
+      </c>
+      <c r="L19" t="s">
+        <v>102</v>
+      </c>
+      <c r="M19" t="s">
+        <v>66</v>
+      </c>
+      <c r="N19" t="s">
+        <v>106</v>
+      </c>
+      <c r="O19" t="s">
+        <v>96</v>
+      </c>
+      <c r="P19" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>75</v>
+      </c>
+      <c r="R19" t="s">
+        <v>103</v>
+      </c>
+      <c r="S19" t="s">
+        <v>110</v>
+      </c>
+      <c r="T19" t="s">
+        <v>82</v>
+      </c>
+      <c r="U19" t="s">
+        <v>66</v>
+      </c>
+      <c r="V19" t="s">
+        <v>75</v>
+      </c>
+      <c r="W19" t="s">
+        <v>96</v>
+      </c>
+      <c r="X19" t="s">
+        <v>110</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>103</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>82</v>
+      </c>
+      <c r="AG19" t="s">
+        <v>82</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>104</v>
+      </c>
+      <c r="AI19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AJ19" t="s">
         <v>93</v>
       </c>
-      <c r="L18" t="s">
-        <v>96</v>
-      </c>
-      <c r="M18" t="s">
-        <v>96</v>
-      </c>
-      <c r="N18" t="s">
-        <v>85</v>
-      </c>
-      <c r="O18" t="s">
-        <v>99</v>
-      </c>
-      <c r="P18" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>64</v>
-      </c>
-      <c r="R18" t="s">
-        <v>96</v>
-      </c>
-      <c r="S18" t="s">
-        <v>100</v>
-      </c>
-      <c r="T18" t="s">
-        <v>100</v>
-      </c>
-      <c r="U18" t="s">
-        <v>93</v>
-      </c>
-      <c r="V18" t="s">
-        <v>93</v>
-      </c>
-      <c r="W18" t="s">
-        <v>74</v>
-      </c>
-      <c r="X18" t="s">
-        <v>109</v>
-      </c>
-      <c r="Y18" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z18" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA18" t="s">
-        <v>59</v>
-      </c>
-      <c r="AB18" t="s">
-        <v>59</v>
-      </c>
-      <c r="AC18" t="s">
-        <v>64</v>
-      </c>
-      <c r="AD18" t="s">
-        <v>108</v>
-      </c>
-      <c r="AE18" t="s">
-        <v>89</v>
-      </c>
-      <c r="AF18" t="s">
-        <v>73</v>
-      </c>
-      <c r="AG18" t="s">
-        <v>108</v>
-      </c>
-      <c r="AH18" t="s">
-        <v>97</v>
-      </c>
-      <c r="AI18" t="s">
-        <v>97</v>
-      </c>
-      <c r="AJ18" t="s">
-        <v>97</v>
-      </c>
-      <c r="AK18" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>77</v>
-      </c>
-      <c r="B19" t="s">
-        <v>77</v>
-      </c>
-      <c r="C19" t="s">
-        <v>84</v>
-      </c>
-      <c r="D19" t="s">
-        <v>84</v>
-      </c>
-      <c r="E19" t="s">
-        <v>103</v>
-      </c>
-      <c r="F19" t="s">
-        <v>85</v>
-      </c>
-      <c r="G19" t="s">
-        <v>85</v>
-      </c>
-      <c r="H19" t="s">
-        <v>103</v>
-      </c>
-      <c r="I19" t="s">
-        <v>79</v>
-      </c>
-      <c r="J19" t="s">
-        <v>93</v>
-      </c>
-      <c r="K19" t="s">
-        <v>80</v>
-      </c>
-      <c r="L19" t="s">
-        <v>99</v>
-      </c>
-      <c r="M19" t="s">
-        <v>64</v>
-      </c>
-      <c r="N19" t="s">
-        <v>103</v>
-      </c>
-      <c r="O19" t="s">
-        <v>93</v>
-      </c>
-      <c r="P19" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>73</v>
-      </c>
-      <c r="R19" t="s">
-        <v>100</v>
-      </c>
-      <c r="S19" t="s">
-        <v>108</v>
-      </c>
-      <c r="T19" t="s">
-        <v>80</v>
-      </c>
-      <c r="U19" t="s">
-        <v>64</v>
-      </c>
-      <c r="V19" t="s">
-        <v>73</v>
-      </c>
-      <c r="W19" t="s">
-        <v>93</v>
-      </c>
-      <c r="X19" t="s">
-        <v>108</v>
-      </c>
-      <c r="Y19" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z19" t="s">
-        <v>101</v>
-      </c>
-      <c r="AA19" t="s">
-        <v>101</v>
-      </c>
-      <c r="AB19" t="s">
-        <v>89</v>
-      </c>
-      <c r="AC19" t="s">
-        <v>100</v>
-      </c>
-      <c r="AD19" t="s">
-        <v>59</v>
-      </c>
-      <c r="AE19" t="s">
-        <v>97</v>
-      </c>
-      <c r="AF19" t="s">
-        <v>80</v>
-      </c>
-      <c r="AG19" t="s">
-        <v>80</v>
-      </c>
-      <c r="AH19" t="s">
-        <v>101</v>
-      </c>
-      <c r="AI19" t="s">
-        <v>81</v>
-      </c>
-      <c r="AJ19" t="s">
-        <v>90</v>
-      </c>
       <c r="AK19" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B20" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C20" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D20" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E20" t="s">
+        <v>100</v>
+      </c>
+      <c r="F20" t="s">
+        <v>102</v>
+      </c>
+      <c r="G20" t="s">
+        <v>66</v>
+      </c>
+      <c r="H20" t="s">
+        <v>78</v>
+      </c>
+      <c r="I20" t="s">
         <v>96</v>
       </c>
-      <c r="F20" t="s">
-        <v>99</v>
-      </c>
-      <c r="G20" t="s">
-        <v>64</v>
-      </c>
-      <c r="H20" t="s">
-        <v>76</v>
-      </c>
-      <c r="I20" t="s">
+      <c r="J20" t="s">
+        <v>66</v>
+      </c>
+      <c r="K20" t="s">
+        <v>61</v>
+      </c>
+      <c r="L20" t="s">
+        <v>96</v>
+      </c>
+      <c r="M20" t="s">
+        <v>103</v>
+      </c>
+      <c r="N20" t="s">
+        <v>96</v>
+      </c>
+      <c r="O20" t="s">
+        <v>103</v>
+      </c>
+      <c r="P20" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>82</v>
+      </c>
+      <c r="R20" t="s">
+        <v>82</v>
+      </c>
+      <c r="S20" t="s">
+        <v>75</v>
+      </c>
+      <c r="T20" t="s">
+        <v>61</v>
+      </c>
+      <c r="U20" t="s">
+        <v>110</v>
+      </c>
+      <c r="V20" t="s">
+        <v>61</v>
+      </c>
+      <c r="W20" t="s">
+        <v>75</v>
+      </c>
+      <c r="X20" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD20" t="s">
+        <v>83</v>
+      </c>
+      <c r="AE20" t="s">
+        <v>107</v>
+      </c>
+      <c r="AF20" t="s">
+        <v>96</v>
+      </c>
+      <c r="AG20" t="s">
+        <v>92</v>
+      </c>
+      <c r="AH20" t="s">
         <v>93</v>
       </c>
-      <c r="J20" t="s">
-        <v>64</v>
-      </c>
-      <c r="K20" t="s">
-        <v>60</v>
-      </c>
-      <c r="L20" t="s">
-        <v>93</v>
-      </c>
-      <c r="M20" t="s">
-        <v>100</v>
-      </c>
-      <c r="N20" t="s">
-        <v>93</v>
-      </c>
-      <c r="O20" t="s">
-        <v>100</v>
-      </c>
-      <c r="P20" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>80</v>
-      </c>
-      <c r="R20" t="s">
-        <v>80</v>
-      </c>
-      <c r="S20" t="s">
-        <v>73</v>
-      </c>
-      <c r="T20" t="s">
-        <v>60</v>
-      </c>
-      <c r="U20" t="s">
-        <v>108</v>
-      </c>
-      <c r="V20" t="s">
-        <v>60</v>
-      </c>
-      <c r="W20" t="s">
-        <v>73</v>
-      </c>
-      <c r="X20" t="s">
-        <v>60</v>
-      </c>
-      <c r="Y20" t="s">
-        <v>89</v>
-      </c>
-      <c r="Z20" t="s">
-        <v>97</v>
-      </c>
-      <c r="AA20" t="s">
-        <v>97</v>
-      </c>
-      <c r="AB20" t="s">
-        <v>101</v>
-      </c>
-      <c r="AC20" t="s">
-        <v>60</v>
-      </c>
-      <c r="AD20" t="s">
-        <v>102</v>
-      </c>
-      <c r="AE20" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF20" t="s">
-        <v>93</v>
-      </c>
-      <c r="AG20" t="s">
-        <v>89</v>
-      </c>
-      <c r="AH20" t="s">
-        <v>90</v>
-      </c>
       <c r="AI20" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="AJ20" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="AK20" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B21" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C21" t="s">
+        <v>108</v>
+      </c>
+      <c r="D21" t="s">
+        <v>108</v>
+      </c>
+      <c r="E21" t="s">
+        <v>96</v>
+      </c>
+      <c r="F21" t="s">
+        <v>73</v>
+      </c>
+      <c r="G21" t="s">
+        <v>110</v>
+      </c>
+      <c r="H21" t="s">
+        <v>96</v>
+      </c>
+      <c r="I21" t="s">
+        <v>66</v>
+      </c>
+      <c r="J21" t="s">
+        <v>75</v>
+      </c>
+      <c r="K21" t="s">
+        <v>60</v>
+      </c>
+      <c r="L21" t="s">
+        <v>103</v>
+      </c>
+      <c r="M21" t="s">
+        <v>110</v>
+      </c>
+      <c r="N21" t="s">
+        <v>66</v>
+      </c>
+      <c r="O21" t="s">
+        <v>110</v>
+      </c>
+      <c r="P21" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>60</v>
+      </c>
+      <c r="R21" t="s">
+        <v>61</v>
+      </c>
+      <c r="S21" t="s">
+        <v>61</v>
+      </c>
+      <c r="T21" t="s">
+        <v>60</v>
+      </c>
+      <c r="U21" t="s">
+        <v>75</v>
+      </c>
+      <c r="V21" t="s">
+        <v>60</v>
+      </c>
+      <c r="W21" t="s">
+        <v>92</v>
+      </c>
+      <c r="X21" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>96</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>97</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>104</v>
+      </c>
+      <c r="AD21" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE21" t="s">
+        <v>97</v>
+      </c>
+      <c r="AF21" t="s">
+        <v>97</v>
+      </c>
+      <c r="AG21" t="s">
+        <v>104</v>
+      </c>
+      <c r="AH21" t="s">
+        <v>107</v>
+      </c>
+      <c r="AI21" t="s">
+        <v>62</v>
+      </c>
+      <c r="AJ21" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK21" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>99</v>
+      </c>
+      <c r="B22" t="s">
+        <v>80</v>
+      </c>
+      <c r="C22" t="s">
+        <v>76</v>
+      </c>
+      <c r="D22" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" t="s">
+        <v>111</v>
+      </c>
+      <c r="F22" t="s">
+        <v>66</v>
+      </c>
+      <c r="G22" t="s">
+        <v>75</v>
+      </c>
+      <c r="H22" t="s">
+        <v>103</v>
+      </c>
+      <c r="I22" t="s">
+        <v>103</v>
+      </c>
+      <c r="J22" t="s">
+        <v>82</v>
+      </c>
+      <c r="K22" t="s">
+        <v>92</v>
+      </c>
+      <c r="L22" t="s">
+        <v>75</v>
+      </c>
+      <c r="M22" t="s">
+        <v>60</v>
+      </c>
+      <c r="N22" t="s">
+        <v>103</v>
+      </c>
+      <c r="O22" t="s">
+        <v>75</v>
+      </c>
+      <c r="P22" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>104</v>
+      </c>
+      <c r="R22" t="s">
+        <v>60</v>
+      </c>
+      <c r="S22" t="s">
+        <v>60</v>
+      </c>
+      <c r="T22" t="s">
+        <v>104</v>
+      </c>
+      <c r="U22" t="s">
+        <v>61</v>
+      </c>
+      <c r="V22" t="s">
+        <v>92</v>
+      </c>
+      <c r="W22" t="s">
+        <v>104</v>
+      </c>
+      <c r="X22" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>112</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD22" t="s">
+        <v>112</v>
+      </c>
+      <c r="AE22" t="s">
         <v>105</v>
       </c>
-      <c r="D21" t="s">
+      <c r="AF22" t="s">
         <v>105</v>
       </c>
-      <c r="E21" t="s">
+      <c r="AG22" t="s">
         <v>93</v>
       </c>
-      <c r="F21" t="s">
-        <v>71</v>
-      </c>
-      <c r="G21" t="s">
-        <v>108</v>
-      </c>
-      <c r="H21" t="s">
+      <c r="AH22" t="s">
+        <v>97</v>
+      </c>
+      <c r="AI22" t="s">
+        <v>114</v>
+      </c>
+      <c r="AJ22" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>80</v>
+      </c>
+      <c r="B23" t="s">
+        <v>87</v>
+      </c>
+      <c r="C23" t="s">
+        <v>87</v>
+      </c>
+      <c r="D23" t="s">
+        <v>87</v>
+      </c>
+      <c r="E23" t="s">
+        <v>103</v>
+      </c>
+      <c r="F23" t="s">
+        <v>103</v>
+      </c>
+      <c r="G23" t="s">
+        <v>82</v>
+      </c>
+      <c r="H23" t="s">
+        <v>75</v>
+      </c>
+      <c r="I23" t="s">
+        <v>61</v>
+      </c>
+      <c r="J23" t="s">
+        <v>60</v>
+      </c>
+      <c r="K23" t="s">
+        <v>104</v>
+      </c>
+      <c r="L23" t="s">
+        <v>61</v>
+      </c>
+      <c r="M23" t="s">
+        <v>115</v>
+      </c>
+      <c r="N23" t="s">
+        <v>113</v>
+      </c>
+      <c r="O23" t="s">
+        <v>61</v>
+      </c>
+      <c r="P23" t="s">
+        <v>104</v>
+      </c>
+      <c r="R23" t="s">
+        <v>104</v>
+      </c>
+      <c r="S23" t="s">
+        <v>92</v>
+      </c>
+      <c r="T23" t="s">
+        <v>113</v>
+      </c>
+      <c r="U23" t="s">
+        <v>69</v>
+      </c>
+      <c r="V23" t="s">
+        <v>80</v>
+      </c>
+      <c r="W23" t="s">
+        <v>69</v>
+      </c>
+      <c r="X23" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>107</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>83</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>62</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>97</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>107</v>
+      </c>
+      <c r="AD23" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE23" t="s">
+        <v>83</v>
+      </c>
+      <c r="AF23" t="s">
+        <v>112</v>
+      </c>
+      <c r="AG23" t="s">
+        <v>105</v>
+      </c>
+      <c r="AH23" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>76</v>
+      </c>
+      <c r="B24" t="s">
+        <v>106</v>
+      </c>
+      <c r="C24" t="s">
+        <v>102</v>
+      </c>
+      <c r="D24" t="s">
+        <v>109</v>
+      </c>
+      <c r="E24" t="s">
+        <v>113</v>
+      </c>
+      <c r="F24" t="s">
+        <v>82</v>
+      </c>
+      <c r="G24" t="s">
+        <v>60</v>
+      </c>
+      <c r="H24" t="s">
+        <v>61</v>
+      </c>
+      <c r="I24" t="s">
+        <v>92</v>
+      </c>
+      <c r="J24" t="s">
+        <v>104</v>
+      </c>
+      <c r="K24" t="s">
+        <v>102</v>
+      </c>
+      <c r="L24" t="s">
+        <v>104</v>
+      </c>
+      <c r="M24" t="s">
+        <v>82</v>
+      </c>
+      <c r="N24" t="s">
         <v>93</v>
       </c>
-      <c r="I21" t="s">
-        <v>64</v>
-      </c>
-      <c r="J21" t="s">
-        <v>73</v>
-      </c>
-      <c r="K21" t="s">
-        <v>59</v>
-      </c>
-      <c r="L21" t="s">
+      <c r="O24" t="s">
+        <v>104</v>
+      </c>
+      <c r="P24" t="s">
+        <v>113</v>
+      </c>
+      <c r="R24" t="s">
+        <v>69</v>
+      </c>
+      <c r="S24" t="s">
+        <v>69</v>
+      </c>
+      <c r="T24" t="s">
+        <v>83</v>
+      </c>
+      <c r="U24" t="s">
+        <v>93</v>
+      </c>
+      <c r="V24" t="s">
+        <v>83</v>
+      </c>
+      <c r="W24" t="s">
+        <v>83</v>
+      </c>
+      <c r="X24" t="s">
+        <v>93</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>105</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>107</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>105</v>
+      </c>
+      <c r="AD24" t="s">
+        <v>98</v>
+      </c>
+      <c r="AE24" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF24" t="s">
+        <v>62</v>
+      </c>
+      <c r="AG24" t="s">
+        <v>89</v>
+      </c>
+      <c r="AH24" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>87</v>
+      </c>
+      <c r="B25" t="s">
         <v>100</v>
       </c>
-      <c r="M21" t="s">
-        <v>108</v>
-      </c>
-      <c r="N21" t="s">
-        <v>64</v>
-      </c>
-      <c r="O21" t="s">
-        <v>108</v>
-      </c>
-      <c r="P21" t="s">
+      <c r="C25" t="s">
+        <v>96</v>
+      </c>
+      <c r="D25" t="s">
+        <v>75</v>
+      </c>
+      <c r="E25" t="s">
+        <v>61</v>
+      </c>
+      <c r="F25" t="s">
         <v>60</v>
       </c>
-      <c r="Q21" t="s">
-        <v>59</v>
-      </c>
-      <c r="R21" t="s">
+      <c r="G25" t="s">
+        <v>92</v>
+      </c>
+      <c r="H25" t="s">
         <v>60</v>
       </c>
-      <c r="S21" t="s">
+      <c r="I25" t="s">
+        <v>104</v>
+      </c>
+      <c r="J25" t="s">
+        <v>83</v>
+      </c>
+      <c r="K25" t="s">
+        <v>93</v>
+      </c>
+      <c r="L25" t="s">
+        <v>69</v>
+      </c>
+      <c r="M25" t="s">
+        <v>93</v>
+      </c>
+      <c r="N25" t="s">
+        <v>107</v>
+      </c>
+      <c r="O25" t="s">
+        <v>83</v>
+      </c>
+      <c r="P25" t="s">
+        <v>83</v>
+      </c>
+      <c r="R25" t="s">
+        <v>93</v>
+      </c>
+      <c r="S25" t="s">
+        <v>93</v>
+      </c>
+      <c r="T25" t="s">
+        <v>105</v>
+      </c>
+      <c r="U25" t="s">
+        <v>107</v>
+      </c>
+      <c r="V25" t="s">
+        <v>107</v>
+      </c>
+      <c r="W25" t="s">
+        <v>105</v>
+      </c>
+      <c r="X25" t="s">
+        <v>107</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>116</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>117</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>62</v>
+      </c>
+      <c r="AD25" t="s">
+        <v>89</v>
+      </c>
+      <c r="AE25" t="s">
+        <v>114</v>
+      </c>
+      <c r="AF25" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH25" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>100</v>
+      </c>
+      <c r="B26" t="s">
+        <v>109</v>
+      </c>
+      <c r="C26" t="s">
+        <v>111</v>
+      </c>
+      <c r="D26" t="s">
         <v>60</v>
       </c>
-      <c r="T21" t="s">
-        <v>59</v>
-      </c>
-      <c r="U21" t="s">
-        <v>73</v>
-      </c>
-      <c r="V21" t="s">
-        <v>59</v>
-      </c>
-      <c r="W21" t="s">
+      <c r="E26" t="s">
+        <v>92</v>
+      </c>
+      <c r="F26" t="s">
+        <v>104</v>
+      </c>
+      <c r="G26" t="s">
+        <v>69</v>
+      </c>
+      <c r="H26" t="s">
+        <v>92</v>
+      </c>
+      <c r="I26" t="s">
+        <v>115</v>
+      </c>
+      <c r="J26" t="s">
+        <v>107</v>
+      </c>
+      <c r="K26" t="s">
+        <v>83</v>
+      </c>
+      <c r="L26" t="s">
+        <v>93</v>
+      </c>
+      <c r="M26" t="s">
+        <v>116</v>
+      </c>
+      <c r="N26" t="s">
+        <v>97</v>
+      </c>
+      <c r="O26" t="s">
+        <v>107</v>
+      </c>
+      <c r="P26" t="s">
+        <v>107</v>
+      </c>
+      <c r="R26" t="s">
+        <v>112</v>
+      </c>
+      <c r="S26" t="s">
+        <v>107</v>
+      </c>
+      <c r="T26" t="s">
+        <v>117</v>
+      </c>
+      <c r="U26" t="s">
+        <v>97</v>
+      </c>
+      <c r="V26" t="s">
+        <v>97</v>
+      </c>
+      <c r="W26" t="s">
+        <v>114</v>
+      </c>
+      <c r="X26" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>119</v>
+      </c>
+      <c r="AA26" t="s">
+        <v>98</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>98</v>
+      </c>
+      <c r="AE26" t="s">
+        <v>98</v>
+      </c>
+      <c r="AF26" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>102</v>
+      </c>
+      <c r="B27" t="s">
+        <v>96</v>
+      </c>
+      <c r="C27" t="s">
+        <v>103</v>
+      </c>
+      <c r="D27" t="s">
+        <v>92</v>
+      </c>
+      <c r="E27" t="s">
+        <v>69</v>
+      </c>
+      <c r="F27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G27" t="s">
+        <v>93</v>
+      </c>
+      <c r="H27" t="s">
+        <v>66</v>
+      </c>
+      <c r="I27" t="s">
+        <v>107</v>
+      </c>
+      <c r="J27" t="s">
+        <v>105</v>
+      </c>
+      <c r="K27" t="s">
+        <v>97</v>
+      </c>
+      <c r="L27" t="s">
+        <v>107</v>
+      </c>
+      <c r="M27" t="s">
+        <v>112</v>
+      </c>
+      <c r="N27" t="s">
+        <v>105</v>
+      </c>
+      <c r="O27" t="s">
+        <v>97</v>
+      </c>
+      <c r="P27" t="s">
+        <v>117</v>
+      </c>
+      <c r="R27" t="s">
+        <v>88</v>
+      </c>
+      <c r="S27" t="s">
+        <v>105</v>
+      </c>
+      <c r="T27" t="s">
+        <v>119</v>
+      </c>
+      <c r="U27" t="s">
+        <v>88</v>
+      </c>
+      <c r="V27" t="s">
+        <v>105</v>
+      </c>
+      <c r="W27" t="s">
         <v>89</v>
       </c>
-      <c r="X21" t="s">
-        <v>59</v>
-      </c>
-      <c r="Y21" t="s">
+      <c r="X27" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>120</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>114</v>
+      </c>
+      <c r="AF27" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>96</v>
+      </c>
+      <c r="B28" t="s">
+        <v>111</v>
+      </c>
+      <c r="C28" t="s">
+        <v>113</v>
+      </c>
+      <c r="D28" t="s">
+        <v>104</v>
+      </c>
+      <c r="E28" t="s">
+        <v>115</v>
+      </c>
+      <c r="F28" t="s">
+        <v>81</v>
+      </c>
+      <c r="G28" t="s">
+        <v>83</v>
+      </c>
+      <c r="H28" t="s">
+        <v>102</v>
+      </c>
+      <c r="I28" t="s">
+        <v>105</v>
+      </c>
+      <c r="J28" t="s">
+        <v>116</v>
+      </c>
+      <c r="K28" t="s">
+        <v>105</v>
+      </c>
+      <c r="L28" t="s">
         <v>97</v>
       </c>
-      <c r="Z21" t="s">
+      <c r="M28" t="s">
+        <v>61</v>
+      </c>
+      <c r="N28" t="s">
+        <v>112</v>
+      </c>
+      <c r="O28" t="s">
+        <v>112</v>
+      </c>
+      <c r="P28" t="s">
+        <v>119</v>
+      </c>
+      <c r="R28" t="s">
+        <v>114</v>
+      </c>
+      <c r="T28" t="s">
+        <v>75</v>
+      </c>
+      <c r="U28" t="s">
+        <v>98</v>
+      </c>
+      <c r="V28" t="s">
+        <v>112</v>
+      </c>
+      <c r="X28" t="s">
+        <v>89</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>66</v>
+      </c>
+      <c r="B29" t="s">
+        <v>110</v>
+      </c>
+      <c r="C29" t="s">
+        <v>110</v>
+      </c>
+      <c r="D29" t="s">
+        <v>69</v>
+      </c>
+      <c r="E29" t="s">
+        <v>83</v>
+      </c>
+      <c r="F29" t="s">
         <v>93</v>
       </c>
-      <c r="AA21" t="s">
-        <v>94</v>
-      </c>
-      <c r="AB21" t="s">
+      <c r="G29" t="s">
         <v>97</v>
       </c>
-      <c r="AC21" t="s">
-        <v>101</v>
-      </c>
-      <c r="AD21" t="s">
-        <v>81</v>
-      </c>
-      <c r="AE21" t="s">
-        <v>94</v>
-      </c>
-      <c r="AF21" t="s">
-        <v>94</v>
-      </c>
-      <c r="AG21" t="s">
-        <v>101</v>
-      </c>
-      <c r="AH21" t="s">
-        <v>104</v>
-      </c>
-      <c r="AI21" t="s">
-        <v>106</v>
-      </c>
-      <c r="AJ21" t="s">
-        <v>60</v>
+      <c r="H29" t="s">
+        <v>93</v>
+      </c>
+      <c r="I29" t="s">
+        <v>112</v>
+      </c>
+      <c r="J29" t="s">
+        <v>112</v>
+      </c>
+      <c r="K29" t="s">
+        <v>116</v>
+      </c>
+      <c r="L29" t="s">
+        <v>112</v>
+      </c>
+      <c r="M29" t="s">
+        <v>88</v>
+      </c>
+      <c r="N29" t="s">
+        <v>88</v>
+      </c>
+      <c r="O29" t="s">
+        <v>82</v>
+      </c>
+      <c r="P29" t="s">
+        <v>114</v>
+      </c>
+      <c r="R29" t="s">
+        <v>89</v>
+      </c>
+      <c r="T29" t="s">
+        <v>114</v>
+      </c>
+      <c r="U29" t="s">
+        <v>89</v>
+      </c>
+      <c r="V29" t="s">
+        <v>114</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>95</v>
-      </c>
-      <c r="B22" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" t="s">
-        <v>74</v>
-      </c>
-      <c r="D22" t="s">
-        <v>74</v>
-      </c>
-      <c r="E22" t="s">
-        <v>109</v>
-      </c>
-      <c r="F22" t="s">
-        <v>64</v>
-      </c>
-      <c r="G22" t="s">
-        <v>73</v>
-      </c>
-      <c r="H22" t="s">
-        <v>100</v>
-      </c>
-      <c r="I22" t="s">
-        <v>100</v>
-      </c>
-      <c r="J22" t="s">
-        <v>80</v>
-      </c>
-      <c r="K22" t="s">
+    <row r="30" ht="15" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>103</v>
+      </c>
+      <c r="B30" t="s">
+        <v>82</v>
+      </c>
+      <c r="C30" t="s">
+        <v>82</v>
+      </c>
+      <c r="D30" t="s">
+        <v>96</v>
+      </c>
+      <c r="E30" t="s">
+        <v>107</v>
+      </c>
+      <c r="F30" t="s">
+        <v>107</v>
+      </c>
+      <c r="G30" t="s">
+        <v>105</v>
+      </c>
+      <c r="H30" t="s">
+        <v>83</v>
+      </c>
+      <c r="I30" t="s">
+        <v>93</v>
+      </c>
+      <c r="J30" t="s">
+        <v>97</v>
+      </c>
+      <c r="K30" t="s">
+        <v>62</v>
+      </c>
+      <c r="L30" t="s">
+        <v>114</v>
+      </c>
+      <c r="M30" t="s">
+        <v>114</v>
+      </c>
+      <c r="N30" t="s">
+        <v>114</v>
+      </c>
+      <c r="O30" t="s">
+        <v>114</v>
+      </c>
+      <c r="P30" t="s">
         <v>89</v>
       </c>
-      <c r="L22" t="s">
-        <v>73</v>
-      </c>
-      <c r="M22" t="s">
-        <v>59</v>
-      </c>
-      <c r="N22" t="s">
-        <v>100</v>
-      </c>
-      <c r="O22" t="s">
-        <v>73</v>
-      </c>
-      <c r="P22" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>101</v>
-      </c>
-      <c r="R22" t="s">
-        <v>59</v>
-      </c>
-      <c r="S22" t="s">
-        <v>59</v>
-      </c>
-      <c r="T22" t="s">
-        <v>101</v>
-      </c>
-      <c r="U22" t="s">
-        <v>60</v>
-      </c>
-      <c r="V22" t="s">
+      <c r="T30" t="s">
         <v>89</v>
       </c>
-      <c r="W22" t="s">
-        <v>101</v>
-      </c>
-      <c r="X22" t="s">
-        <v>101</v>
-      </c>
-      <c r="Y22" t="s">
-        <v>90</v>
-      </c>
-      <c r="Z22" t="s">
-        <v>111</v>
-      </c>
-      <c r="AA22" t="s">
-        <v>110</v>
-      </c>
-      <c r="AB22" t="s">
-        <v>81</v>
-      </c>
-      <c r="AC22" t="s">
-        <v>97</v>
-      </c>
-      <c r="AD22" t="s">
-        <v>94</v>
-      </c>
-      <c r="AE22" t="s">
-        <v>106</v>
-      </c>
-      <c r="AF22" t="s">
-        <v>106</v>
-      </c>
-      <c r="AG22" t="s">
-        <v>90</v>
-      </c>
-      <c r="AH22" t="s">
-        <v>94</v>
-      </c>
-      <c r="AI22" t="s">
-        <v>110</v>
+      <c r="V30" t="s">
+        <v>98</v>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>78</v>
-      </c>
-      <c r="B23" t="s">
-        <v>85</v>
-      </c>
-      <c r="C23" t="s">
-        <v>85</v>
-      </c>
-      <c r="D23" t="s">
-        <v>85</v>
-      </c>
-      <c r="E23" t="s">
-        <v>100</v>
-      </c>
-      <c r="F23" t="s">
-        <v>100</v>
-      </c>
-      <c r="G23" t="s">
-        <v>80</v>
-      </c>
-      <c r="H23" t="s">
-        <v>73</v>
-      </c>
-      <c r="I23" t="s">
-        <v>60</v>
-      </c>
-      <c r="J23" t="s">
-        <v>59</v>
-      </c>
-      <c r="K23" t="s">
-        <v>101</v>
-      </c>
-      <c r="L23" t="s">
-        <v>60</v>
-      </c>
-      <c r="M23" t="s">
-        <v>112</v>
-      </c>
-      <c r="N23" t="s">
-        <v>111</v>
-      </c>
-      <c r="O23" t="s">
-        <v>60</v>
-      </c>
-      <c r="P23" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>97</v>
-      </c>
-      <c r="R23" t="s">
-        <v>101</v>
-      </c>
-      <c r="S23" t="s">
-        <v>89</v>
-      </c>
-      <c r="T23" t="s">
-        <v>111</v>
-      </c>
-      <c r="U23" t="s">
-        <v>97</v>
-      </c>
-      <c r="V23" t="s">
-        <v>78</v>
-      </c>
-      <c r="W23" t="s">
-        <v>97</v>
-      </c>
-      <c r="X23" t="s">
-        <v>99</v>
-      </c>
-      <c r="Y23" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z23" t="s">
-        <v>81</v>
-      </c>
-      <c r="AA23" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB23" t="s">
-        <v>94</v>
-      </c>
-      <c r="AC23" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD23" t="s">
-        <v>110</v>
-      </c>
-      <c r="AE23" t="s">
-        <v>81</v>
-      </c>
-      <c r="AF23" t="s">
-        <v>110</v>
-      </c>
-      <c r="AG23" t="s">
-        <v>106</v>
-      </c>
-      <c r="AH23" t="s">
-        <v>106</v>
-      </c>
-      <c r="AI23" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>74</v>
-      </c>
-      <c r="B24" t="s">
-        <v>103</v>
-      </c>
-      <c r="C24" t="s">
-        <v>99</v>
-      </c>
-      <c r="D24" t="s">
-        <v>107</v>
-      </c>
-      <c r="E24" t="s">
-        <v>111</v>
-      </c>
-      <c r="F24" t="s">
-        <v>80</v>
-      </c>
-      <c r="G24" t="s">
-        <v>59</v>
-      </c>
-      <c r="H24" t="s">
-        <v>60</v>
-      </c>
-      <c r="I24" t="s">
-        <v>89</v>
-      </c>
-      <c r="J24" t="s">
-        <v>101</v>
-      </c>
-      <c r="K24" t="s">
-        <v>99</v>
-      </c>
-      <c r="L24" t="s">
-        <v>101</v>
-      </c>
-      <c r="M24" t="s">
-        <v>80</v>
-      </c>
-      <c r="N24" t="s">
-        <v>90</v>
-      </c>
-      <c r="O24" t="s">
-        <v>101</v>
-      </c>
-      <c r="P24" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>90</v>
-      </c>
-      <c r="R24" t="s">
-        <v>97</v>
-      </c>
-      <c r="S24" t="s">
-        <v>97</v>
-      </c>
-      <c r="T24" t="s">
-        <v>81</v>
-      </c>
-      <c r="U24" t="s">
-        <v>90</v>
-      </c>
-      <c r="V24" t="s">
-        <v>81</v>
-      </c>
-      <c r="W24" t="s">
-        <v>102</v>
-      </c>
-      <c r="X24" t="s">
-        <v>90</v>
-      </c>
-      <c r="Y24" t="s">
-        <v>106</v>
-      </c>
-      <c r="Z24" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA24" t="s">
-        <v>60</v>
-      </c>
-      <c r="AB24" t="s">
-        <v>110</v>
-      </c>
-      <c r="AC24" t="s">
-        <v>106</v>
-      </c>
-      <c r="AD24" t="s">
-        <v>67</v>
-      </c>
-      <c r="AE24" t="s">
-        <v>60</v>
-      </c>
-      <c r="AF24" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>85</v>
-      </c>
-      <c r="B25" t="s">
-        <v>96</v>
-      </c>
-      <c r="C25" t="s">
-        <v>93</v>
-      </c>
-      <c r="D25" t="s">
-        <v>73</v>
-      </c>
-      <c r="E25" t="s">
-        <v>60</v>
-      </c>
-      <c r="F25" t="s">
-        <v>59</v>
-      </c>
-      <c r="G25" t="s">
-        <v>89</v>
-      </c>
-      <c r="H25" t="s">
-        <v>59</v>
-      </c>
-      <c r="I25" t="s">
-        <v>101</v>
-      </c>
-      <c r="J25" t="s">
-        <v>102</v>
-      </c>
-      <c r="K25" t="s">
-        <v>90</v>
-      </c>
-      <c r="L25" t="s">
-        <v>97</v>
-      </c>
-      <c r="M25" t="s">
-        <v>90</v>
-      </c>
-      <c r="N25" t="s">
-        <v>104</v>
-      </c>
-      <c r="O25" t="s">
-        <v>81</v>
-      </c>
-      <c r="P25" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>94</v>
-      </c>
-      <c r="R25" t="s">
-        <v>90</v>
-      </c>
-      <c r="S25" t="s">
-        <v>90</v>
-      </c>
-      <c r="T25" t="s">
-        <v>106</v>
-      </c>
-      <c r="U25" t="s">
-        <v>104</v>
-      </c>
-      <c r="V25" t="s">
-        <v>104</v>
-      </c>
-      <c r="W25" t="s">
-        <v>81</v>
-      </c>
-      <c r="X25" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y25" t="s">
+    <row r="31" ht="15" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>113</v>
       </c>
-      <c r="Z25" t="s">
-        <v>114</v>
-      </c>
-      <c r="AA25" t="s">
-        <v>86</v>
-      </c>
-      <c r="AB25" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>96</v>
-      </c>
-      <c r="B26" t="s">
-        <v>107</v>
-      </c>
-      <c r="C26" t="s">
-        <v>109</v>
-      </c>
-      <c r="D26" t="s">
-        <v>102</v>
-      </c>
-      <c r="E26" t="s">
-        <v>89</v>
-      </c>
-      <c r="F26" t="s">
-        <v>101</v>
-      </c>
-      <c r="G26" t="s">
-        <v>97</v>
-      </c>
-      <c r="H26" t="s">
-        <v>89</v>
-      </c>
-      <c r="I26" t="s">
-        <v>112</v>
-      </c>
-      <c r="J26" t="s">
-        <v>81</v>
-      </c>
-      <c r="K26" t="s">
-        <v>81</v>
-      </c>
-      <c r="L26" t="s">
-        <v>90</v>
-      </c>
-      <c r="M26" t="s">
-        <v>113</v>
-      </c>
-      <c r="N26" t="s">
-        <v>94</v>
-      </c>
-      <c r="O26" t="s">
-        <v>104</v>
-      </c>
-      <c r="P26" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>106</v>
-      </c>
-      <c r="R26" t="s">
-        <v>110</v>
-      </c>
-      <c r="S26" t="s">
-        <v>104</v>
-      </c>
-      <c r="T26" t="s">
-        <v>114</v>
-      </c>
-      <c r="U26" t="s">
-        <v>94</v>
-      </c>
-      <c r="V26" t="s">
-        <v>94</v>
-      </c>
-      <c r="W26" t="s">
-        <v>106</v>
-      </c>
-      <c r="X26" t="s">
-        <v>89</v>
-      </c>
-      <c r="Z26" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>99</v>
-      </c>
-      <c r="B27" t="s">
-        <v>93</v>
-      </c>
-      <c r="C27" t="s">
-        <v>100</v>
-      </c>
-      <c r="D27" t="s">
-        <v>59</v>
-      </c>
-      <c r="E27" t="s">
-        <v>97</v>
-      </c>
-      <c r="F27" t="s">
-        <v>97</v>
-      </c>
-      <c r="G27" t="s">
-        <v>90</v>
-      </c>
-      <c r="H27" t="s">
-        <v>64</v>
-      </c>
-      <c r="I27" t="s">
-        <v>102</v>
-      </c>
-      <c r="J27" t="s">
-        <v>104</v>
-      </c>
-      <c r="K27" t="s">
-        <v>94</v>
-      </c>
-      <c r="L27" t="s">
-        <v>104</v>
-      </c>
-      <c r="M27" t="s">
-        <v>110</v>
-      </c>
-      <c r="N27" t="s">
-        <v>106</v>
-      </c>
-      <c r="O27" t="s">
-        <v>94</v>
-      </c>
-      <c r="P27" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>110</v>
-      </c>
-      <c r="R27" t="s">
-        <v>86</v>
-      </c>
-      <c r="S27" t="s">
-        <v>106</v>
-      </c>
-      <c r="T27" t="s">
-        <v>115</v>
-      </c>
-      <c r="U27" t="s">
-        <v>86</v>
-      </c>
-      <c r="V27" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>93</v>
-      </c>
-      <c r="B28" t="s">
-        <v>109</v>
-      </c>
-      <c r="C28" t="s">
-        <v>111</v>
-      </c>
-      <c r="D28" t="s">
-        <v>89</v>
-      </c>
-      <c r="E28" t="s">
-        <v>112</v>
-      </c>
-      <c r="F28" t="s">
-        <v>79</v>
-      </c>
-      <c r="G28" t="s">
-        <v>81</v>
-      </c>
-      <c r="H28" t="s">
-        <v>99</v>
-      </c>
-      <c r="I28" t="s">
-        <v>104</v>
-      </c>
-      <c r="J28" t="s">
-        <v>106</v>
-      </c>
-      <c r="K28" t="s">
-        <v>106</v>
-      </c>
-      <c r="L28" t="s">
-        <v>94</v>
-      </c>
-      <c r="M28" t="s">
-        <v>60</v>
-      </c>
-      <c r="N28" t="s">
-        <v>110</v>
-      </c>
-      <c r="O28" t="s">
-        <v>110</v>
-      </c>
-      <c r="P28" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>67</v>
-      </c>
-      <c r="T28" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>64</v>
-      </c>
-      <c r="B29" t="s">
-        <v>108</v>
-      </c>
-      <c r="C29" t="s">
-        <v>108</v>
-      </c>
-      <c r="D29" t="s">
-        <v>101</v>
-      </c>
-      <c r="E29" t="s">
-        <v>81</v>
-      </c>
-      <c r="F29" t="s">
-        <v>90</v>
-      </c>
-      <c r="G29" t="s">
-        <v>94</v>
-      </c>
-      <c r="H29" t="s">
-        <v>90</v>
-      </c>
-      <c r="I29" t="s">
-        <v>106</v>
-      </c>
-      <c r="J29" t="s">
-        <v>113</v>
-      </c>
-      <c r="K29" t="s">
-        <v>113</v>
-      </c>
-      <c r="L29" t="s">
-        <v>110</v>
-      </c>
-      <c r="M29" t="s">
-        <v>86</v>
-      </c>
-      <c r="N29" t="s">
-        <v>86</v>
-      </c>
-      <c r="O29" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>100</v>
-      </c>
-      <c r="B30" t="s">
-        <v>80</v>
-      </c>
-      <c r="C30" t="s">
-        <v>80</v>
-      </c>
-      <c r="D30" t="s">
-        <v>97</v>
-      </c>
-      <c r="E30" t="s">
-        <v>104</v>
-      </c>
-      <c r="F30" t="s">
-        <v>104</v>
-      </c>
-      <c r="G30" t="s">
-        <v>106</v>
-      </c>
-      <c r="H30" t="s">
-        <v>81</v>
-      </c>
-      <c r="I30" t="s">
-        <v>110</v>
-      </c>
-      <c r="J30" t="s">
-        <v>110</v>
-      </c>
-      <c r="K30" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>111</v>
-      </c>
       <c r="B31" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C31" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D31" t="s">
         <v>93</v>
       </c>
       <c r="E31" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F31" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G31" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="H31" t="s">
+        <v>107</v>
+      </c>
+      <c r="I31" t="s">
+        <v>114</v>
+      </c>
+      <c r="J31" t="s">
+        <v>114</v>
+      </c>
+      <c r="K31" t="s">
+        <v>114</v>
+      </c>
+      <c r="L31" t="s">
+        <v>120</v>
+      </c>
+      <c r="M31" t="s">
+        <v>89</v>
+      </c>
+      <c r="N31" t="s">
+        <v>98</v>
+      </c>
+      <c r="O31" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>60</v>
+      </c>
+      <c r="B32" t="s">
+        <v>60</v>
+      </c>
+      <c r="C32" t="s">
+        <v>92</v>
+      </c>
+      <c r="D32" t="s">
+        <v>83</v>
+      </c>
+      <c r="E32" t="s">
+        <v>105</v>
+      </c>
+      <c r="F32" t="s">
+        <v>105</v>
+      </c>
+      <c r="G32" t="s">
+        <v>62</v>
+      </c>
+      <c r="H32" t="s">
+        <v>82</v>
+      </c>
+      <c r="I32" t="s">
+        <v>118</v>
+      </c>
+      <c r="J32" t="s">
+        <v>98</v>
+      </c>
+      <c r="K32" t="s">
+        <v>120</v>
+      </c>
+      <c r="L32" t="s">
+        <v>89</v>
+      </c>
+      <c r="N32" t="s">
+        <v>89</v>
+      </c>
+      <c r="O32" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>92</v>
+      </c>
+      <c r="B33" t="s">
+        <v>92</v>
+      </c>
+      <c r="C33" t="s">
         <v>104</v>
       </c>
-      <c r="I31" t="s">
-        <v>90</v>
+      <c r="D33" t="s">
+        <v>107</v>
+      </c>
+      <c r="E33" t="s">
+        <v>112</v>
+      </c>
+      <c r="F33" t="s">
+        <v>112</v>
+      </c>
+      <c r="G33" t="s">
+        <v>104</v>
+      </c>
+      <c r="H33" t="s">
+        <v>114</v>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>59</v>
-      </c>
-      <c r="B32" t="s">
-        <v>59</v>
-      </c>
-      <c r="C32" t="s">
+    <row r="34" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>104</v>
+      </c>
+      <c r="B34" t="s">
+        <v>104</v>
+      </c>
+      <c r="C34" t="s">
+        <v>69</v>
+      </c>
+      <c r="D34" t="s">
+        <v>97</v>
+      </c>
+      <c r="E34" t="s">
+        <v>116</v>
+      </c>
+      <c r="F34" t="s">
+        <v>61</v>
+      </c>
+      <c r="G34" t="s">
+        <v>114</v>
+      </c>
+      <c r="H34" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>69</v>
+      </c>
+      <c r="B35" t="s">
+        <v>69</v>
+      </c>
+      <c r="C35" t="s">
+        <v>93</v>
+      </c>
+      <c r="D35" t="s">
+        <v>105</v>
+      </c>
+      <c r="E35" t="s">
+        <v>114</v>
+      </c>
+      <c r="F35" t="s">
+        <v>98</v>
+      </c>
+      <c r="G35" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>93</v>
+      </c>
+      <c r="B36" t="s">
+        <v>115</v>
+      </c>
+      <c r="C36" t="s">
+        <v>83</v>
+      </c>
+      <c r="D36" t="s">
+        <v>112</v>
+      </c>
+      <c r="E36" t="s">
+        <v>89</v>
+      </c>
+      <c r="F36" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>83</v>
+      </c>
+      <c r="B37" t="s">
         <v>102</v>
       </c>
-      <c r="D32" t="s">
-        <v>90</v>
-      </c>
-      <c r="E32" t="s">
-        <v>106</v>
-      </c>
-      <c r="F32" t="s">
-        <v>106</v>
-      </c>
-      <c r="G32" t="s">
-        <v>67</v>
-      </c>
-      <c r="H32" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>89</v>
-      </c>
-      <c r="B33" t="s">
-        <v>89</v>
-      </c>
-      <c r="C33" t="s">
-        <v>89</v>
-      </c>
-      <c r="D33" t="s">
-        <v>81</v>
-      </c>
-      <c r="E33" t="s">
-        <v>110</v>
-      </c>
-      <c r="F33" t="s">
-        <v>110</v>
-      </c>
-      <c r="G33" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>101</v>
-      </c>
-      <c r="B34" t="s">
-        <v>101</v>
-      </c>
-      <c r="C34" t="s">
-        <v>101</v>
-      </c>
-      <c r="D34" t="s">
-        <v>104</v>
-      </c>
-      <c r="E34" t="s">
-        <v>113</v>
-      </c>
-      <c r="F34" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>97</v>
-      </c>
-      <c r="B35" t="s">
-        <v>97</v>
-      </c>
-      <c r="C35" t="s">
-        <v>97</v>
-      </c>
-      <c r="D35" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>90</v>
-      </c>
-      <c r="B36" t="s">
-        <v>112</v>
-      </c>
-      <c r="C36" t="s">
-        <v>90</v>
-      </c>
-      <c r="D36" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>81</v>
-      </c>
-      <c r="B37" t="s">
-        <v>99</v>
-      </c>
       <c r="C37" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="D37" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B38" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C38" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="D38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B39" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C39" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="D39" t="s">
-        <v>67</v>
+        <v>114</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B40" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C40" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="D40" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B41" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C41" t="s">
-        <v>113</v>
+        <v>112</v>
+      </c>
+      <c r="D41" t="s">
+        <v>98</v>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B42" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C42" t="s">
-        <v>110</v>
+        <v>117</v>
+      </c>
+      <c r="D42" t="s">
+        <v>89</v>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B43" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C43" t="s">
-        <v>114</v>
+        <v>88</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>114</v>
+      </c>
       <c r="B44" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C44" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="2:3" x14ac:dyDescent="0.25"/>
-    <row r="46" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>98</v>
+      </c>
+      <c r="B45" t="s">
+        <v>116</v>
+      </c>
+      <c r="C45" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>89</v>
+      </c>
+      <c r="B46" t="s">
+        <v>89</v>
+      </c>
+      <c r="C46" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B47" t="s">
+        <v>118</v>
+      </c>
+      <c r="C47" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1" spans="2:3" x14ac:dyDescent="0.25"/>
     <row r="49" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="50" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="51" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5142,7 +5424,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:BM42"/>
+  <dimension ref="A3:BR42"/>
   <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="17.85546875" customWidth="1"/>
@@ -5175,204 +5457,219 @@
     <col min="98" max="98" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" t="s">
         <v>53</v>
       </c>
-      <c r="C3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" t="s">
-        <v>52</v>
-      </c>
       <c r="E3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H3" t="s">
         <v>56</v>
       </c>
-      <c r="G3" t="s">
+      <c r="I3" t="s">
+        <v>70</v>
+      </c>
+      <c r="J3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K3" t="s">
+        <v>71</v>
+      </c>
+      <c r="L3" t="s">
+        <v>59</v>
+      </c>
+      <c r="M3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N3" t="s">
+        <v>72</v>
+      </c>
+      <c r="O3" t="s">
+        <v>77</v>
+      </c>
+      <c r="P3" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>65</v>
+      </c>
+      <c r="R3" t="s">
+        <v>74</v>
+      </c>
+      <c r="S3" t="s">
+        <v>94</v>
+      </c>
+      <c r="T3" t="s">
+        <v>64</v>
+      </c>
+      <c r="U3" t="s">
+        <v>85</v>
+      </c>
+      <c r="V3" t="s">
+        <v>73</v>
+      </c>
+      <c r="W3" t="s">
+        <v>95</v>
+      </c>
+      <c r="X3" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>101</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>81</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>108</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>106</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>100</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>109</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>102</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>111</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>103</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>110</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>75</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>82</v>
+      </c>
+      <c r="AW3" t="s">
         <v>61</v>
       </c>
-      <c r="H3" t="s">
-        <v>55</v>
-      </c>
-      <c r="I3" t="s">
-        <v>68</v>
-      </c>
-      <c r="J3" t="s">
-        <v>65</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="AX3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>104</v>
+      </c>
+      <c r="BA3" t="s">
         <v>69</v>
       </c>
-      <c r="L3" t="s">
-        <v>58</v>
-      </c>
-      <c r="M3" t="s">
-        <v>57</v>
-      </c>
-      <c r="N3" t="s">
-        <v>70</v>
-      </c>
-      <c r="O3" t="s">
-        <v>75</v>
-      </c>
-      <c r="P3" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>63</v>
-      </c>
-      <c r="R3" t="s">
-        <v>72</v>
-      </c>
-      <c r="S3" t="s">
-        <v>91</v>
-      </c>
-      <c r="T3" t="s">
+      <c r="BB3" t="s">
+        <v>115</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>93</v>
+      </c>
+      <c r="BD3" t="s">
+        <v>83</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>107</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>97</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>105</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>116</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BJ3" t="s">
         <v>62</v>
       </c>
-      <c r="U3" t="s">
-        <v>83</v>
-      </c>
-      <c r="V3" t="s">
-        <v>71</v>
-      </c>
-      <c r="W3" t="s">
-        <v>92</v>
-      </c>
-      <c r="X3" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y3" t="s">
+      <c r="BK3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BM3" t="s">
         <v>88</v>
       </c>
-      <c r="Z3" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>77</v>
-      </c>
-      <c r="AC3" t="s">
+      <c r="BN3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BO3" t="s">
+        <v>120</v>
+      </c>
+      <c r="BP3" t="s">
         <v>98</v>
       </c>
-      <c r="AD3" t="s">
-        <v>84</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>105</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>85</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>103</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>96</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>107</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>99</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>93</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>109</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>64</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>100</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>111</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>108</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>73</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>60</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>59</v>
-      </c>
-      <c r="AY3" t="s">
+      <c r="BQ3" t="s">
         <v>89</v>
       </c>
-      <c r="AZ3" t="s">
-        <v>101</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>97</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>112</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>90</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>81</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>104</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>94</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>106</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>113</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>110</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>67</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>114</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>115</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>86</v>
+      <c r="BR3" t="s">
+        <v>118</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -5395,7 +5692,7 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="I4" t="s">
         <v>0</v>
@@ -5413,7 +5710,7 @@
         <v>12</v>
       </c>
       <c r="N4" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="O4" t="s">
         <v>14</v>
@@ -5434,7 +5731,7 @@
         <v>2</v>
       </c>
       <c r="U4" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="V4" t="s">
         <v>12</v>
@@ -5568,8 +5865,23 @@
       <c r="BM4" t="s">
         <v>0</v>
       </c>
+      <c r="BN4" t="s">
+        <v>19</v>
+      </c>
+      <c r="BO4" t="s">
+        <v>14</v>
+      </c>
+      <c r="BP4" t="s">
+        <v>36</v>
+      </c>
+      <c r="BQ4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BR4" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -5765,8 +6077,23 @@
       <c r="BM5" t="s">
         <v>44</v>
       </c>
+      <c r="BN5" t="s">
+        <v>0</v>
+      </c>
+      <c r="BO5" t="s">
+        <v>11</v>
+      </c>
+      <c r="BP5" t="s">
+        <v>0</v>
+      </c>
+      <c r="BQ5" t="s">
+        <v>11</v>
+      </c>
+      <c r="BR5" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -5962,8 +6289,23 @@
       <c r="BM6" t="s">
         <v>17</v>
       </c>
+      <c r="BN6" t="s">
+        <v>15</v>
+      </c>
+      <c r="BO6" t="s">
+        <v>10</v>
+      </c>
+      <c r="BP6" t="s">
+        <v>30</v>
+      </c>
+      <c r="BQ6" t="s">
+        <v>23</v>
+      </c>
+      <c r="BR6" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -6159,8 +6501,23 @@
       <c r="BM7" t="s">
         <v>13</v>
       </c>
+      <c r="BN7" t="s">
+        <v>13</v>
+      </c>
+      <c r="BO7" t="s">
+        <v>24</v>
+      </c>
+      <c r="BP7" t="s">
+        <v>29</v>
+      </c>
+      <c r="BQ7" t="s">
+        <v>29</v>
+      </c>
+      <c r="BR7" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -6300,7 +6657,7 @@
         <v>14</v>
       </c>
       <c r="BF8" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="BG8" t="s">
         <v>32</v>
@@ -6317,8 +6674,20 @@
       <c r="BM8" t="s">
         <v>2</v>
       </c>
+      <c r="BN8" t="s">
+        <v>6</v>
+      </c>
+      <c r="BO8" t="s">
+        <v>2</v>
+      </c>
+      <c r="BP8" t="s">
+        <v>5</v>
+      </c>
+      <c r="BQ8" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -6458,13 +6827,13 @@
         <v>0</v>
       </c>
       <c r="BF9" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="BG9" t="s">
         <v>34</v>
       </c>
       <c r="BH9" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BI9" t="s">
         <v>11</v>
@@ -6475,8 +6844,20 @@
       <c r="BM9" t="s">
         <v>12</v>
       </c>
+      <c r="BN9" t="s">
+        <v>21</v>
+      </c>
+      <c r="BO9" t="s">
+        <v>3</v>
+      </c>
+      <c r="BP9" t="s">
+        <v>35</v>
+      </c>
+      <c r="BQ9" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>42</v>
       </c>
@@ -6616,7 +6997,7 @@
         <v>18</v>
       </c>
       <c r="BF10" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="BG10" t="s">
         <v>22</v>
@@ -6633,8 +7014,20 @@
       <c r="BM10" t="s">
         <v>20</v>
       </c>
+      <c r="BN10" t="s">
+        <v>17</v>
+      </c>
+      <c r="BO10" t="s">
+        <v>31</v>
+      </c>
+      <c r="BP10" t="s">
+        <v>26</v>
+      </c>
+      <c r="BQ10" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -6791,8 +7184,20 @@
       <c r="BM11" t="s">
         <v>26</v>
       </c>
+      <c r="BN11" t="s">
+        <v>23</v>
+      </c>
+      <c r="BO11" t="s">
+        <v>25</v>
+      </c>
+      <c r="BP11" t="s">
+        <v>27</v>
+      </c>
+      <c r="BQ11" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>1</v>
       </c>
@@ -6827,7 +7232,7 @@
         <v>28</v>
       </c>
       <c r="T12" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="V12" t="s">
         <v>1</v>
@@ -6926,10 +7331,19 @@
         <v>5</v>
       </c>
       <c r="BJ12" t="s">
-        <v>34</v>
+        <v>6</v>
+      </c>
+      <c r="BN12" t="s">
+        <v>14</v>
+      </c>
+      <c r="BP12" t="s">
+        <v>2</v>
+      </c>
+      <c r="BQ12" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -7063,10 +7477,19 @@
         <v>1</v>
       </c>
       <c r="BJ13" t="s">
-        <v>6</v>
+        <v>34</v>
+      </c>
+      <c r="BN13" t="s">
+        <v>11</v>
+      </c>
+      <c r="BP13" t="s">
+        <v>3</v>
+      </c>
+      <c r="BQ13" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>8</v>
       </c>
@@ -7200,10 +7623,19 @@
         <v>8</v>
       </c>
       <c r="BJ14" t="s">
-        <v>10</v>
+        <v>50</v>
+      </c>
+      <c r="BN14" t="s">
+        <v>22</v>
+      </c>
+      <c r="BP14" t="s">
+        <v>42</v>
+      </c>
+      <c r="BQ14" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>46</v>
       </c>
@@ -7331,16 +7763,25 @@
         <v>38</v>
       </c>
       <c r="BG15" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="BI15" t="s">
         <v>4</v>
       </c>
       <c r="BJ15" t="s">
-        <v>16</v>
+        <v>10</v>
+      </c>
+      <c r="BN15" t="s">
+        <v>9</v>
+      </c>
+      <c r="BP15" t="s">
+        <v>9</v>
+      </c>
+      <c r="BQ15" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -7372,7 +7813,7 @@
         <v>34</v>
       </c>
       <c r="R16" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="T16" t="s">
         <v>19</v>
@@ -7441,7 +7882,7 @@
         <v>19</v>
       </c>
       <c r="BA16" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="BC16" t="s">
         <v>32</v>
@@ -7461,8 +7902,17 @@
       <c r="BI16" t="s">
         <v>2</v>
       </c>
+      <c r="BN16" t="s">
+        <v>33</v>
+      </c>
+      <c r="BP16" t="s">
+        <v>6</v>
+      </c>
+      <c r="BQ16" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>0</v>
       </c>
@@ -7563,7 +8013,7 @@
         <v>3</v>
       </c>
       <c r="BA17" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="BC17" t="s">
         <v>12</v>
@@ -7583,8 +8033,17 @@
       <c r="BI17" t="s">
         <v>12</v>
       </c>
+      <c r="BN17" t="s">
+        <v>34</v>
+      </c>
+      <c r="BP17" t="s">
+        <v>21</v>
+      </c>
+      <c r="BQ17" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -7705,8 +8164,17 @@
       <c r="BI18" t="s">
         <v>26</v>
       </c>
+      <c r="BN18" t="s">
+        <v>31</v>
+      </c>
+      <c r="BP18" t="s">
+        <v>20</v>
+      </c>
+      <c r="BQ18" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>37</v>
       </c>
@@ -7807,10 +8275,10 @@
         <v>39</v>
       </c>
       <c r="BA19" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="BC19" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="BD19" t="s">
         <v>15</v>
@@ -7827,8 +8295,17 @@
       <c r="BI19" t="s">
         <v>27</v>
       </c>
+      <c r="BN19" t="s">
+        <v>25</v>
+      </c>
+      <c r="BP19" t="s">
+        <v>13</v>
+      </c>
+      <c r="BQ19" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>32</v>
       </c>
@@ -7923,12 +8400,18 @@
         <v>19</v>
       </c>
       <c r="BI20" t="s">
-        <v>34</v>
+        <v>21</v>
+      </c>
+      <c r="BN20" t="s">
+        <v>2</v>
+      </c>
+      <c r="BQ20" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C21" t="s">
         <v>7</v>
@@ -8023,8 +8506,14 @@
       <c r="BI21" t="s">
         <v>3</v>
       </c>
+      <c r="BN21" t="s">
+        <v>3</v>
+      </c>
+      <c r="BQ21" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -8121,8 +8610,14 @@
       <c r="BI22" t="s">
         <v>9</v>
       </c>
+      <c r="BN22" t="s">
+        <v>8</v>
+      </c>
+      <c r="BQ22" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>9</v>
       </c>
@@ -8217,10 +8712,16 @@
         <v>31</v>
       </c>
       <c r="BI23" t="s">
-        <v>16</v>
+        <v>24</v>
+      </c>
+      <c r="BN23" t="s">
+        <v>4</v>
+      </c>
+      <c r="BQ23" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>2</v>
       </c>
@@ -8290,8 +8791,14 @@
       <c r="BG24" t="s">
         <v>6</v>
       </c>
+      <c r="BN24" t="s">
+        <v>12</v>
+      </c>
+      <c r="BQ24" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -8361,8 +8868,14 @@
       <c r="BG25" t="s">
         <v>21</v>
       </c>
+      <c r="BN25" t="s">
+        <v>7</v>
+      </c>
+      <c r="BQ25" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>23</v>
       </c>
@@ -8432,8 +8945,14 @@
       <c r="BG26" t="s">
         <v>10</v>
       </c>
+      <c r="BN26" t="s">
+        <v>10</v>
+      </c>
+      <c r="BQ26" t="s">
+        <v>45</v>
+      </c>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -8503,8 +9022,14 @@
       <c r="BG27" t="s">
         <v>24</v>
       </c>
+      <c r="BN27" t="s">
+        <v>30</v>
+      </c>
+      <c r="BQ27" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="53:59" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="15" customHeight="1" spans="57:69" x14ac:dyDescent="0.25"/>
     <row r="29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -8526,7 +9051,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:BM1898"/>
+  <dimension ref="A3:BR1898"/>
   <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="55.28515625" customWidth="1"/>
@@ -8610,1004 +9135,1076 @@
     <col min="99" max="99" width="47.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" t="s">
         <v>53</v>
       </c>
-      <c r="C3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" t="s">
-        <v>52</v>
-      </c>
       <c r="E3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H3" t="s">
         <v>56</v>
       </c>
-      <c r="G3" t="s">
+      <c r="I3" t="s">
+        <v>70</v>
+      </c>
+      <c r="J3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K3" t="s">
+        <v>71</v>
+      </c>
+      <c r="L3" t="s">
+        <v>59</v>
+      </c>
+      <c r="M3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N3" t="s">
+        <v>72</v>
+      </c>
+      <c r="O3" t="s">
+        <v>77</v>
+      </c>
+      <c r="P3" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>65</v>
+      </c>
+      <c r="R3" t="s">
+        <v>74</v>
+      </c>
+      <c r="S3" t="s">
+        <v>94</v>
+      </c>
+      <c r="T3" t="s">
+        <v>64</v>
+      </c>
+      <c r="U3" t="s">
+        <v>85</v>
+      </c>
+      <c r="V3" t="s">
+        <v>73</v>
+      </c>
+      <c r="W3" t="s">
+        <v>95</v>
+      </c>
+      <c r="X3" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>101</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>81</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>108</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>106</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>100</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>109</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>102</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>111</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>103</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>110</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>75</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>82</v>
+      </c>
+      <c r="AW3" t="s">
         <v>61</v>
       </c>
-      <c r="H3" t="s">
-        <v>55</v>
-      </c>
-      <c r="I3" t="s">
-        <v>68</v>
-      </c>
-      <c r="J3" t="s">
-        <v>65</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="AX3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>104</v>
+      </c>
+      <c r="BA3" t="s">
         <v>69</v>
       </c>
-      <c r="L3" t="s">
-        <v>58</v>
-      </c>
-      <c r="M3" t="s">
-        <v>57</v>
-      </c>
-      <c r="N3" t="s">
-        <v>70</v>
-      </c>
-      <c r="O3" t="s">
-        <v>75</v>
-      </c>
-      <c r="P3" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>63</v>
-      </c>
-      <c r="R3" t="s">
-        <v>72</v>
-      </c>
-      <c r="S3" t="s">
-        <v>91</v>
-      </c>
-      <c r="T3" t="s">
+      <c r="BB3" t="s">
+        <v>115</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>93</v>
+      </c>
+      <c r="BD3" t="s">
+        <v>83</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>107</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>97</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>105</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>116</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BJ3" t="s">
         <v>62</v>
       </c>
-      <c r="U3" t="s">
-        <v>83</v>
-      </c>
-      <c r="V3" t="s">
-        <v>71</v>
-      </c>
-      <c r="W3" t="s">
-        <v>92</v>
-      </c>
-      <c r="X3" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y3" t="s">
+      <c r="BK3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BM3" t="s">
         <v>88</v>
       </c>
-      <c r="Z3" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>77</v>
-      </c>
-      <c r="AC3" t="s">
+      <c r="BN3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BO3" t="s">
+        <v>120</v>
+      </c>
+      <c r="BP3" t="s">
         <v>98</v>
       </c>
-      <c r="AD3" t="s">
-        <v>84</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>105</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>85</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>103</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>96</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>107</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>99</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>93</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>109</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>64</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>100</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>111</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>108</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>73</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>60</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>59</v>
-      </c>
-      <c r="AY3" t="s">
+      <c r="BQ3" t="s">
         <v>89</v>
       </c>
-      <c r="AZ3" t="s">
-        <v>101</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>97</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>112</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>90</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>81</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>104</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>94</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>106</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>113</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>110</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>67</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>114</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>115</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>86</v>
+      <c r="BR3" t="s">
+        <v>118</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B4" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C4" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D4" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E4" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F4" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="H4" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="I4" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="J4" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="K4" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="L4" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="M4" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="N4" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="O4" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="P4" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="Q4" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="R4" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="S4" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="T4" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="U4" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="V4" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="W4" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="X4" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="Y4" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="Z4" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="AA4" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="AB4" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="AC4" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="AD4" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="AE4" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AF4" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="AG4" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="AH4" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="AI4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="AJ4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="AK4" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="AL4" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="AM4" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="AN4" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="AO4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="AP4" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="AQ4" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="AR4" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="AS4" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="AT4" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="AU4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="AV4" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="AW4" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="AX4" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="AY4" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="AZ4" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="BA4" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="BB4" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="BC4" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="BD4" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="BE4" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="BF4" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="BG4" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="BH4" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="BI4" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="BJ4" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="BK4" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="BL4" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="BM4" t="s">
-        <v>181</v>
+        <v>186</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>187</v>
+      </c>
+      <c r="BO4" t="s">
+        <v>188</v>
+      </c>
+      <c r="BP4" t="s">
+        <v>189</v>
+      </c>
+      <c r="BQ4" t="s">
+        <v>190</v>
+      </c>
+      <c r="BR4" t="s">
+        <v>191</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="C5" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="E5" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="F5" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="G5" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="H5" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="J5" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="K5" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="L5" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="M5" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="O5" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="Q5" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="R5" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="T5" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="V5" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="W5" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="X5" t="s">
+        <v>208</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>209</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>210</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>211</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>212</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>213</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>214</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>215</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>216</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>217</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>218</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>219</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>220</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>221</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>222</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>222</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>223</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>224</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>222</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>225</v>
+      </c>
+      <c r="AU5" t="s">
         <v>198</v>
       </c>
-      <c r="Y5" t="s">
-        <v>199</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>200</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>202</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>203</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>204</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>205</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>206</v>
-      </c>
-      <c r="AH5" t="s">
-        <v>207</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>208</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>209</v>
-      </c>
-      <c r="AK5" t="s">
-        <v>210</v>
-      </c>
-      <c r="AL5" t="s">
-        <v>211</v>
-      </c>
-      <c r="AN5" t="s">
-        <v>212</v>
-      </c>
-      <c r="AO5" t="s">
-        <v>212</v>
-      </c>
-      <c r="AQ5" t="s">
-        <v>213</v>
-      </c>
-      <c r="AR5" t="s">
-        <v>214</v>
-      </c>
-      <c r="AS5" t="s">
-        <v>212</v>
-      </c>
-      <c r="AT5" t="s">
-        <v>215</v>
-      </c>
-      <c r="AU5" t="s">
-        <v>188</v>
-      </c>
       <c r="AV5" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="AW5" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="AX5" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="AY5" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="AZ5" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="BA5" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="BC5" t="s">
+        <v>232</v>
+      </c>
+      <c r="BD5" t="s">
+        <v>233</v>
+      </c>
+      <c r="BE5" t="s">
+        <v>234</v>
+      </c>
+      <c r="BF5" t="s">
+        <v>235</v>
+      </c>
+      <c r="BG5" t="s">
+        <v>236</v>
+      </c>
+      <c r="BH5" t="s">
+        <v>237</v>
+      </c>
+      <c r="BI5" t="s">
+        <v>238</v>
+      </c>
+      <c r="BJ5" t="s">
+        <v>239</v>
+      </c>
+      <c r="BM5" t="s">
+        <v>240</v>
+      </c>
+      <c r="BN5" t="s">
+        <v>241</v>
+      </c>
+      <c r="BO5" t="s">
+        <v>242</v>
+      </c>
+      <c r="BP5" t="s">
+        <v>243</v>
+      </c>
+      <c r="BQ5" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>245</v>
+      </c>
+      <c r="C6" t="s">
+        <v>246</v>
+      </c>
+      <c r="E6" t="s">
+        <v>247</v>
+      </c>
+      <c r="F6" t="s">
+        <v>248</v>
+      </c>
+      <c r="H6" t="s">
+        <v>249</v>
+      </c>
+      <c r="J6" t="s">
+        <v>250</v>
+      </c>
+      <c r="K6" t="s">
+        <v>251</v>
+      </c>
+      <c r="M6" t="s">
+        <v>252</v>
+      </c>
+      <c r="O6" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>254</v>
+      </c>
+      <c r="R6" t="s">
+        <v>255</v>
+      </c>
+      <c r="T6" t="s">
+        <v>256</v>
+      </c>
+      <c r="V6" t="s">
+        <v>257</v>
+      </c>
+      <c r="W6" t="s">
+        <v>258</v>
+      </c>
+      <c r="X6" t="s">
+        <v>259</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>260</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>261</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>262</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>263</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>264</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>265</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>266</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>267</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>268</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>269</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>270</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>271</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>272</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>273</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>274</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>275</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>276</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>278</v>
+      </c>
+      <c r="AW6" t="s">
         <v>222</v>
       </c>
-      <c r="BD5" t="s">
-        <v>223</v>
-      </c>
-      <c r="BE5" t="s">
-        <v>224</v>
-      </c>
-      <c r="BF5" t="s">
-        <v>225</v>
-      </c>
-      <c r="BG5" t="s">
-        <v>226</v>
-      </c>
-      <c r="BH5" t="s">
-        <v>227</v>
-      </c>
-      <c r="BI5" t="s">
-        <v>228</v>
-      </c>
-      <c r="BJ5" t="s">
-        <v>229</v>
-      </c>
-      <c r="BM5" t="s">
-        <v>230</v>
+      <c r="AX6" t="s">
+        <v>279</v>
+      </c>
+      <c r="AY6" t="s">
+        <v>280</v>
+      </c>
+      <c r="AZ6" t="s">
+        <v>281</v>
+      </c>
+      <c r="BA6" t="s">
+        <v>282</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>283</v>
+      </c>
+      <c r="BD6" t="s">
+        <v>284</v>
+      </c>
+      <c r="BE6" t="s">
+        <v>285</v>
+      </c>
+      <c r="BF6" t="s">
+        <v>286</v>
+      </c>
+      <c r="BG6" t="s">
+        <v>287</v>
+      </c>
+      <c r="BI6" t="s">
+        <v>288</v>
+      </c>
+      <c r="BJ6" t="s">
+        <v>289</v>
+      </c>
+      <c r="BN6" t="s">
+        <v>290</v>
+      </c>
+      <c r="BP6" t="s">
+        <v>291</v>
+      </c>
+      <c r="BQ6" t="s">
+        <v>292</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>231</v>
-      </c>
-      <c r="C6" t="s">
-        <v>232</v>
-      </c>
-      <c r="E6" t="s">
-        <v>233</v>
-      </c>
-      <c r="F6" t="s">
-        <v>234</v>
-      </c>
-      <c r="H6" t="s">
-        <v>235</v>
-      </c>
-      <c r="J6" t="s">
-        <v>236</v>
-      </c>
-      <c r="K6" t="s">
-        <v>237</v>
-      </c>
-      <c r="M6" t="s">
-        <v>238</v>
-      </c>
-      <c r="O6" t="s">
-        <v>239</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>240</v>
-      </c>
-      <c r="R6" t="s">
-        <v>241</v>
-      </c>
-      <c r="T6" t="s">
-        <v>242</v>
-      </c>
-      <c r="V6" t="s">
-        <v>243</v>
-      </c>
-      <c r="W6" t="s">
-        <v>244</v>
-      </c>
-      <c r="X6" t="s">
-        <v>245</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>246</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>247</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>248</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>249</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>250</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>251</v>
-      </c>
-      <c r="AH6" t="s">
-        <v>252</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>253</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>254</v>
-      </c>
-      <c r="AK6" t="s">
-        <v>255</v>
-      </c>
-      <c r="AL6" t="s">
-        <v>256</v>
-      </c>
-      <c r="AN6" t="s">
-        <v>257</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>258</v>
-      </c>
-      <c r="AQ6" t="s">
-        <v>259</v>
-      </c>
-      <c r="AR6" t="s">
-        <v>260</v>
-      </c>
-      <c r="AS6" t="s">
-        <v>261</v>
-      </c>
-      <c r="AT6" t="s">
-        <v>262</v>
-      </c>
-      <c r="AU6" t="s">
-        <v>263</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>264</v>
-      </c>
-      <c r="AW6" t="s">
-        <v>212</v>
-      </c>
-      <c r="AX6" t="s">
-        <v>265</v>
-      </c>
-      <c r="AY6" t="s">
-        <v>266</v>
-      </c>
-      <c r="AZ6" t="s">
-        <v>267</v>
-      </c>
-      <c r="BA6" t="s">
-        <v>268</v>
-      </c>
-      <c r="BC6" t="s">
-        <v>269</v>
-      </c>
-      <c r="BD6" t="s">
-        <v>270</v>
-      </c>
-      <c r="BE6" t="s">
-        <v>271</v>
-      </c>
-      <c r="BF6" t="s">
-        <v>272</v>
-      </c>
-      <c r="BG6" t="s">
-        <v>273</v>
-      </c>
-      <c r="BI6" t="s">
-        <v>274</v>
-      </c>
-      <c r="BJ6" t="s">
-        <v>275</v>
+    <row r="7" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>293</v>
+      </c>
+      <c r="C7" t="s">
+        <v>294</v>
+      </c>
+      <c r="E7" t="s">
+        <v>295</v>
+      </c>
+      <c r="F7" t="s">
+        <v>296</v>
+      </c>
+      <c r="H7" t="s">
+        <v>297</v>
+      </c>
+      <c r="J7" t="s">
+        <v>298</v>
+      </c>
+      <c r="K7" t="s">
+        <v>299</v>
+      </c>
+      <c r="M7" t="s">
+        <v>300</v>
+      </c>
+      <c r="O7" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>302</v>
+      </c>
+      <c r="R7" t="s">
+        <v>303</v>
+      </c>
+      <c r="T7" t="s">
+        <v>304</v>
+      </c>
+      <c r="V7" t="s">
+        <v>305</v>
+      </c>
+      <c r="X7" t="s">
+        <v>306</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>307</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>308</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>309</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>310</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>311</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>312</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>313</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>314</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>315</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>316</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>317</v>
+      </c>
+      <c r="AQ7" t="s">
+        <v>318</v>
+      </c>
+      <c r="AR7" t="s">
+        <v>319</v>
+      </c>
+      <c r="AU7" t="s">
+        <v>320</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>321</v>
+      </c>
+      <c r="AW7" t="s">
+        <v>322</v>
+      </c>
+      <c r="AX7" t="s">
+        <v>323</v>
+      </c>
+      <c r="AY7" t="s">
+        <v>324</v>
+      </c>
+      <c r="AZ7" t="s">
+        <v>325</v>
+      </c>
+      <c r="BA7" t="s">
+        <v>326</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>327</v>
+      </c>
+      <c r="BD7" t="s">
+        <v>328</v>
+      </c>
+      <c r="BE7" t="s">
+        <v>329</v>
+      </c>
+      <c r="BF7" t="s">
+        <v>330</v>
+      </c>
+      <c r="BG7" t="s">
+        <v>331</v>
+      </c>
+      <c r="BI7" t="s">
+        <v>332</v>
+      </c>
+      <c r="BN7" t="s">
+        <v>333</v>
+      </c>
+      <c r="BP7" t="s">
+        <v>334</v>
+      </c>
+      <c r="BQ7" t="s">
+        <v>335</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>276</v>
-      </c>
-      <c r="C7" t="s">
-        <v>277</v>
-      </c>
-      <c r="E7" t="s">
-        <v>278</v>
-      </c>
-      <c r="F7" t="s">
-        <v>279</v>
-      </c>
-      <c r="H7" t="s">
-        <v>280</v>
-      </c>
-      <c r="J7" t="s">
-        <v>281</v>
-      </c>
-      <c r="K7" t="s">
-        <v>282</v>
-      </c>
-      <c r="M7" t="s">
-        <v>283</v>
-      </c>
-      <c r="O7" t="s">
-        <v>284</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>285</v>
-      </c>
-      <c r="R7" t="s">
-        <v>286</v>
-      </c>
-      <c r="T7" t="s">
-        <v>287</v>
-      </c>
-      <c r="V7" t="s">
-        <v>288</v>
-      </c>
-      <c r="X7" t="s">
-        <v>289</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>290</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>291</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>292</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>293</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>294</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>295</v>
-      </c>
-      <c r="AH7" t="s">
-        <v>296</v>
-      </c>
-      <c r="AI7" t="s">
-        <v>297</v>
-      </c>
-      <c r="AJ7" t="s">
-        <v>298</v>
-      </c>
-      <c r="AN7" t="s">
-        <v>299</v>
-      </c>
-      <c r="AO7" t="s">
-        <v>300</v>
-      </c>
-      <c r="AQ7" t="s">
-        <v>301</v>
-      </c>
-      <c r="AR7" t="s">
-        <v>302</v>
-      </c>
-      <c r="AU7" t="s">
-        <v>303</v>
-      </c>
-      <c r="AV7" t="s">
-        <v>304</v>
-      </c>
-      <c r="AW7" t="s">
-        <v>305</v>
-      </c>
-      <c r="AX7" t="s">
-        <v>306</v>
-      </c>
-      <c r="AY7" t="s">
-        <v>307</v>
-      </c>
-      <c r="AZ7" t="s">
-        <v>308</v>
-      </c>
-      <c r="BA7" t="s">
-        <v>309</v>
-      </c>
-      <c r="BC7" t="s">
-        <v>310</v>
-      </c>
-      <c r="BD7" t="s">
-        <v>311</v>
-      </c>
-      <c r="BE7" t="s">
-        <v>312</v>
-      </c>
-      <c r="BF7" t="s">
-        <v>313</v>
-      </c>
-      <c r="BG7" t="s">
-        <v>314</v>
-      </c>
-      <c r="BI7" t="s">
-        <v>315</v>
+    <row r="8" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>336</v>
+      </c>
+      <c r="C8" t="s">
+        <v>337</v>
+      </c>
+      <c r="E8" t="s">
+        <v>338</v>
+      </c>
+      <c r="F8" t="s">
+        <v>339</v>
+      </c>
+      <c r="H8" t="s">
+        <v>340</v>
+      </c>
+      <c r="K8" t="s">
+        <v>341</v>
+      </c>
+      <c r="O8" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>343</v>
+      </c>
+      <c r="R8" t="s">
+        <v>344</v>
+      </c>
+      <c r="T8" t="s">
+        <v>345</v>
+      </c>
+      <c r="X8" t="s">
+        <v>346</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>347</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>348</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>222</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>349</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>350</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>351</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>352</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>353</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>354</v>
+      </c>
+      <c r="AQ8" t="s">
+        <v>355</v>
+      </c>
+      <c r="AR8" t="s">
+        <v>356</v>
+      </c>
+      <c r="AU8" t="s">
+        <v>222</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>357</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>358</v>
+      </c>
+      <c r="AX8" t="s">
+        <v>359</v>
+      </c>
+      <c r="AY8" t="s">
+        <v>360</v>
+      </c>
+      <c r="AZ8" t="s">
+        <v>361</v>
+      </c>
+      <c r="BA8" t="s">
+        <v>362</v>
+      </c>
+      <c r="BC8" t="s">
+        <v>363</v>
+      </c>
+      <c r="BD8" t="s">
+        <v>364</v>
+      </c>
+      <c r="BE8" t="s">
+        <v>365</v>
+      </c>
+      <c r="BF8" t="s">
+        <v>366</v>
+      </c>
+      <c r="BG8" t="s">
+        <v>367</v>
+      </c>
+      <c r="BI8" t="s">
+        <v>368</v>
+      </c>
+      <c r="BN8" t="s">
+        <v>369</v>
+      </c>
+      <c r="BQ8" t="s">
+        <v>370</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:61" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>316</v>
-      </c>
-      <c r="C8" t="s">
-        <v>317</v>
-      </c>
-      <c r="E8" t="s">
-        <v>318</v>
-      </c>
-      <c r="F8" t="s">
-        <v>319</v>
-      </c>
-      <c r="H8" t="s">
-        <v>320</v>
-      </c>
-      <c r="K8" t="s">
-        <v>321</v>
-      </c>
-      <c r="O8" t="s">
-        <v>322</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>323</v>
-      </c>
-      <c r="R8" t="s">
-        <v>324</v>
-      </c>
-      <c r="T8" t="s">
-        <v>325</v>
-      </c>
-      <c r="X8" t="s">
-        <v>326</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>327</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>328</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>212</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>329</v>
-      </c>
-      <c r="AH8" t="s">
-        <v>330</v>
-      </c>
-      <c r="AI8" t="s">
-        <v>331</v>
-      </c>
-      <c r="AJ8" t="s">
-        <v>332</v>
-      </c>
-      <c r="AN8" t="s">
-        <v>333</v>
-      </c>
-      <c r="AO8" t="s">
-        <v>334</v>
-      </c>
-      <c r="AQ8" t="s">
-        <v>335</v>
-      </c>
-      <c r="AR8" t="s">
-        <v>336</v>
-      </c>
-      <c r="AU8" t="s">
-        <v>212</v>
-      </c>
-      <c r="AV8" t="s">
-        <v>337</v>
-      </c>
-      <c r="AW8" t="s">
-        <v>338</v>
-      </c>
-      <c r="AX8" t="s">
-        <v>339</v>
-      </c>
-      <c r="AY8" t="s">
-        <v>340</v>
-      </c>
-      <c r="AZ8" t="s">
-        <v>341</v>
-      </c>
-      <c r="BA8" t="s">
-        <v>342</v>
-      </c>
-      <c r="BC8" t="s">
-        <v>343</v>
-      </c>
-      <c r="BD8" t="s">
-        <v>344</v>
-      </c>
-      <c r="BE8" t="s">
-        <v>345</v>
-      </c>
-      <c r="BF8" t="s">
-        <v>346</v>
-      </c>
-      <c r="BG8" t="s">
-        <v>347</v>
-      </c>
-      <c r="BI8" t="s">
-        <v>348</v>
+    <row r="9" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>371</v>
+      </c>
+      <c r="E9" t="s">
+        <v>372</v>
+      </c>
+      <c r="F9" t="s">
+        <v>373</v>
+      </c>
+      <c r="H9" t="s">
+        <v>374</v>
+      </c>
+      <c r="O9" t="s">
+        <v>375</v>
+      </c>
+      <c r="T9" t="s">
+        <v>376</v>
+      </c>
+      <c r="X9" t="s">
+        <v>377</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>378</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>380</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>381</v>
+      </c>
+      <c r="AO9" t="s">
+        <v>382</v>
+      </c>
+      <c r="AV9" t="s">
+        <v>383</v>
+      </c>
+      <c r="AW9" t="s">
+        <v>384</v>
+      </c>
+      <c r="AX9" t="s">
+        <v>385</v>
+      </c>
+      <c r="AY9" t="s">
+        <v>386</v>
+      </c>
+      <c r="AZ9" t="s">
+        <v>387</v>
+      </c>
+      <c r="BA9" t="s">
+        <v>388</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>389</v>
+      </c>
+      <c r="BD9" t="s">
+        <v>390</v>
+      </c>
+      <c r="BE9" t="s">
+        <v>391</v>
+      </c>
+      <c r="BF9" t="s">
+        <v>392</v>
+      </c>
+      <c r="BG9" t="s">
+        <v>393</v>
+      </c>
+      <c r="BN9" t="s">
+        <v>394</v>
+      </c>
+      <c r="BQ9" t="s">
+        <v>395</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:61" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>349</v>
-      </c>
-      <c r="E9" t="s">
-        <v>350</v>
-      </c>
-      <c r="F9" t="s">
-        <v>351</v>
-      </c>
-      <c r="H9" t="s">
-        <v>352</v>
-      </c>
-      <c r="O9" t="s">
-        <v>353</v>
-      </c>
-      <c r="T9" t="s">
-        <v>354</v>
-      </c>
-      <c r="X9" t="s">
-        <v>355</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>356</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>357</v>
-      </c>
-      <c r="AI9" t="s">
-        <v>358</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>359</v>
-      </c>
-      <c r="AO9" t="s">
-        <v>360</v>
-      </c>
-      <c r="AV9" t="s">
-        <v>361</v>
-      </c>
-      <c r="AW9" t="s">
-        <v>362</v>
-      </c>
-      <c r="AX9" t="s">
-        <v>363</v>
-      </c>
-      <c r="AY9" t="s">
-        <v>364</v>
-      </c>
-      <c r="AZ9" t="s">
-        <v>365</v>
-      </c>
-      <c r="BA9" t="s">
-        <v>366</v>
-      </c>
-      <c r="BC9" t="s">
-        <v>367</v>
-      </c>
-      <c r="BD9" t="s">
-        <v>368</v>
-      </c>
-      <c r="BE9" t="s">
-        <v>369</v>
-      </c>
-      <c r="BF9" t="s">
-        <v>370</v>
-      </c>
-      <c r="BG9" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" spans="41:59" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="41:69" x14ac:dyDescent="0.25">
       <c r="AO10" t="s">
-        <v>372</v>
+        <v>396</v>
       </c>
       <c r="AW10" t="s">
-        <v>373</v>
+        <v>397</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/data/ICEHLdelegacije.xlsx
+++ b/data/ICEHLdelegacije.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2681" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2685" uniqueCount="399">
   <si>
     <t>SmetanaLa</t>
   </si>
@@ -300,6 +300,9 @@
     <t>2025-01-03</t>
   </si>
   <si>
+    <t>2025-01-24</t>
+  </si>
+  <si>
     <t>2024-10-23</t>
   </si>
   <si>
@@ -312,57 +315,57 @@
     <t>2025-01-10</t>
   </si>
   <si>
+    <t>zbrisano</t>
+  </si>
+  <si>
+    <t>2024-11-22</t>
+  </si>
+  <si>
+    <t>2024-12-01</t>
+  </si>
+  <si>
+    <t>2024-11-16</t>
+  </si>
+  <si>
+    <t>2024-12-04</t>
+  </si>
+  <si>
+    <t>2024-12-13</t>
+  </si>
+  <si>
+    <t>2024-12-30</t>
+  </si>
+  <si>
+    <t>2025-01-12</t>
+  </si>
+  <si>
+    <t>2024-11-30</t>
+  </si>
+  <si>
+    <t>2025-01-08</t>
+  </si>
+  <si>
+    <t>2024-11-23</t>
+  </si>
+  <si>
+    <t>2024-12-03</t>
+  </si>
+  <si>
+    <t>2024-12-15</t>
+  </si>
+  <si>
+    <t>2024-12-07</t>
+  </si>
+  <si>
+    <t>2025-01-17</t>
+  </si>
+  <si>
     <t>2025-01-26</t>
   </si>
   <si>
-    <t>2024-11-22</t>
-  </si>
-  <si>
-    <t>2024-12-01</t>
-  </si>
-  <si>
-    <t>2024-11-16</t>
-  </si>
-  <si>
-    <t>2024-12-04</t>
-  </si>
-  <si>
-    <t>2024-12-13</t>
-  </si>
-  <si>
-    <t>2024-12-30</t>
-  </si>
-  <si>
-    <t>2025-01-12</t>
-  </si>
-  <si>
-    <t>2024-11-30</t>
-  </si>
-  <si>
-    <t>2025-01-08</t>
-  </si>
-  <si>
-    <t>2024-11-23</t>
-  </si>
-  <si>
-    <t>2024-12-03</t>
-  </si>
-  <si>
-    <t>2024-12-15</t>
-  </si>
-  <si>
-    <t>2024-12-07</t>
-  </si>
-  <si>
-    <t>2025-01-17</t>
-  </si>
-  <si>
     <t>2024-12-14</t>
   </si>
   <si>
-    <t>2025-01-24</t>
-  </si>
-  <si>
     <t>2024-12-10</t>
   </si>
   <si>
@@ -723,7 +726,7 @@
     <t>Heidi Horten Arena Klagenfurt;FichtnerPa;SmetanaLa;BärnthalerCh;ZgoncGa</t>
   </si>
   <si>
-    <t>Tiroler Wasserkraft Arena;NikolicKr;NikolicMa;PardatscherUl;ZacherlPa</t>
+    <t>Tiroler Wasserkraft Arena;NikolicMa;NikolicKr;PardatscherUl;ZacherlPa</t>
   </si>
   <si>
     <t>Eishalle Feldkirch;BernekerTh;NikolicKr;MartinFl;SeewaldJe</t>
@@ -891,7 +894,7 @@
     <t>Tiroler Wasserkraft Arena;FichtnerPa;SiegelSt;MartinFl;PardatscherUl</t>
   </si>
   <si>
-    <t>Eishalle Feldkirch;OfnerCh;SternatCh;FleischmannLu;PardatscherUl</t>
+    <t>Eishalle Feldkirch;OfnerCh;SternatCh;PardatscherUl;SparerDa</t>
   </si>
   <si>
     <t>Stadthalle Villach;HronskyTo;ZrnicMi;DurmisOt;KoncDa</t>
@@ -1008,7 +1011,7 @@
     <t>Linz AG Eisarena;PiragicTr;SiegelSt;Gatol-schafranekMa;SeewaldJe</t>
   </si>
   <si>
-    <t>Linz AG Eisarena;Huber aAn;SmetanaLa;DurmisOt;NotheggerDa</t>
+    <t>Linz AG Eisarena;Huber aAn;SmetanaLa;NotheggerDa;WeissAl</t>
   </si>
   <si>
     <t>Stadthalle Villach;RezekGr;SmetanaLa;HribarMa;RieckenSi</t>
@@ -1119,13 +1122,13 @@
     <t>Hala Tivoli;GroznikBo;OfnerCh;MuzsikNo;VacziDa</t>
   </si>
   <si>
-    <t>Heidi Horten Arena Klagenfurt;HronskyTo;Huber aAn;BärnthalerCh;DurmisOt</t>
+    <t>Heidi Horten Arena Klagenfurt;HronskyTo;Huber aAn;BärnthalerCh;KoncDa</t>
   </si>
   <si>
     <t>Eishalle Asiago;SchauerJa;SternatCh;PardatscherUl;RigoniDa</t>
   </si>
   <si>
-    <t>Eishalle Asiago;OfnerCh;SternatCh;HribarMa;ZgoncGa</t>
+    <t>Eishalle Asiago;OfnerCh;SternatCh;JeramFi;ZgoncGa</t>
   </si>
   <si>
     <t>Tiroler Wasserkraft Arena;BernekerTh;OfnerCh;MartinFl;SeewaldJe</t>
@@ -2783,8 +2786,11 @@
       <c r="AR9" t="s">
         <v>83</v>
       </c>
+      <c r="AT9" t="s">
+        <v>94</v>
+      </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>71</v>
       </c>
@@ -2801,7 +2807,7 @@
         <v>55</v>
       </c>
       <c r="F10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G10" t="s">
         <v>77</v>
@@ -2831,7 +2837,7 @@
         <v>65</v>
       </c>
       <c r="P10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q10" t="s">
         <v>74</v>
@@ -2843,10 +2849,10 @@
         <v>64</v>
       </c>
       <c r="T10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="U10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="V10" t="s">
         <v>65</v>
@@ -2855,7 +2861,7 @@
         <v>74</v>
       </c>
       <c r="X10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Y10" t="s">
         <v>73</v>
@@ -2891,7 +2897,7 @@
         <v>65</v>
       </c>
       <c r="AJ10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK10" t="s">
         <v>73</v>
@@ -2906,13 +2912,13 @@
         <v>92</v>
       </c>
       <c r="AO10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AP10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AQ10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
@@ -2941,7 +2947,7 @@
         <v>65</v>
       </c>
       <c r="I11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J11" t="s">
         <v>64</v>
@@ -2989,13 +2995,13 @@
         <v>68</v>
       </c>
       <c r="Y11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Z11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AA11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AB11" t="s">
         <v>78</v>
@@ -3010,7 +3016,7 @@
         <v>56</v>
       </c>
       <c r="AF11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AG11" t="s">
         <v>68</v>
@@ -3019,7 +3025,7 @@
         <v>81</v>
       </c>
       <c r="AI11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AJ11" t="s">
         <v>79</v>
@@ -3028,7 +3034,7 @@
         <v>86</v>
       </c>
       <c r="AL11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AM11" t="s">
         <v>79</v>
@@ -3060,7 +3066,7 @@
         <v>65</v>
       </c>
       <c r="F12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G12" t="s">
         <v>64</v>
@@ -3126,7 +3132,7 @@
         <v>91</v>
       </c>
       <c r="AB12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AC12" t="s">
         <v>90</v>
@@ -3153,16 +3159,16 @@
         <v>80</v>
       </c>
       <c r="AK12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AL12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AM12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AN12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AO12" t="s">
         <v>83</v>
@@ -3182,7 +3188,7 @@
         <v>73</v>
       </c>
       <c r="D13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E13" t="s">
         <v>73</v>
@@ -3251,16 +3257,16 @@
         <v>76</v>
       </c>
       <c r="AA13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AB13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AC13" t="s">
         <v>79</v>
       </c>
       <c r="AD13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AE13" t="s">
         <v>80</v>
@@ -3275,7 +3281,7 @@
         <v>76</v>
       </c>
       <c r="AI13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AJ13" t="s">
         <v>87</v>
@@ -3287,16 +3293,16 @@
         <v>82</v>
       </c>
       <c r="AM13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AN13" t="s">
         <v>66</v>
       </c>
       <c r="AO13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AP13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
@@ -3307,13 +3313,13 @@
         <v>64</v>
       </c>
       <c r="C14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D14" t="s">
         <v>68</v>
       </c>
       <c r="E14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F14" t="s">
         <v>90</v>
@@ -3325,13 +3331,13 @@
         <v>68</v>
       </c>
       <c r="I14" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K14" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L14" t="s">
         <v>79</v>
@@ -3346,7 +3352,7 @@
         <v>86</v>
       </c>
       <c r="P14" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q14" t="s">
         <v>81</v>
@@ -3358,7 +3364,7 @@
         <v>81</v>
       </c>
       <c r="T14" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="U14" t="s">
         <v>76</v>
@@ -3376,7 +3382,7 @@
         <v>81</v>
       </c>
       <c r="Z14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AA14" t="s">
         <v>80</v>
@@ -3388,37 +3394,37 @@
         <v>81</v>
       </c>
       <c r="AD14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AE14" t="s">
+        <v>101</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>103</v>
+      </c>
+      <c r="AG14" t="s">
         <v>100</v>
       </c>
-      <c r="AF14" t="s">
-        <v>102</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>99</v>
-      </c>
       <c r="AH14" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AI14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AJ14" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK14" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AL14" t="s">
         <v>61</v>
       </c>
       <c r="AM14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AN14" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AO14" t="s">
         <v>60</v>
@@ -3426,7 +3432,7 @@
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B15" t="s">
         <v>73</v>
@@ -3465,22 +3471,22 @@
         <v>86</v>
       </c>
       <c r="N15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="R15" t="s">
         <v>86</v>
       </c>
       <c r="S15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T15" t="s">
         <v>80</v>
@@ -3489,7 +3495,7 @@
         <v>87</v>
       </c>
       <c r="V15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="W15" t="s">
         <v>86</v>
@@ -3516,16 +3522,16 @@
         <v>64</v>
       </c>
       <c r="AE15" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AF15" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AG15" t="s">
         <v>76</v>
       </c>
       <c r="AH15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AI15" t="s">
         <v>75</v>
@@ -3551,7 +3557,7 @@
         <v>68</v>
       </c>
       <c r="B16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C16" t="s">
         <v>90</v>
@@ -3578,7 +3584,7 @@
         <v>80</v>
       </c>
       <c r="K16" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L16" t="s">
         <v>76</v>
@@ -3599,7 +3605,7 @@
         <v>76</v>
       </c>
       <c r="R16" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="S16" t="s">
         <v>76</v>
@@ -3608,7 +3614,7 @@
         <v>76</v>
       </c>
       <c r="U16" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="V16" t="s">
         <v>76</v>
@@ -3623,7 +3629,7 @@
         <v>87</v>
       </c>
       <c r="Z16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AA16" t="s">
         <v>66</v>
@@ -3635,16 +3641,16 @@
         <v>87</v>
       </c>
       <c r="AD16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG16" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AH16" t="s">
         <v>66</v>
@@ -3659,10 +3665,10 @@
         <v>82</v>
       </c>
       <c r="AL16" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AN16" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
@@ -3682,25 +3688,25 @@
         <v>79</v>
       </c>
       <c r="F17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H17" t="s">
         <v>80</v>
       </c>
       <c r="I17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J17" t="s">
         <v>76</v>
       </c>
       <c r="K17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M17" t="s">
         <v>80</v>
@@ -3721,49 +3727,49 @@
         <v>87</v>
       </c>
       <c r="S17" t="s">
+        <v>103</v>
+      </c>
+      <c r="T17" t="s">
+        <v>101</v>
+      </c>
+      <c r="U17" t="s">
         <v>102</v>
-      </c>
-      <c r="T17" t="s">
-        <v>100</v>
-      </c>
-      <c r="U17" t="s">
-        <v>101</v>
       </c>
       <c r="V17" t="s">
         <v>87</v>
       </c>
       <c r="W17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="X17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Y17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Z17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AA17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB17" t="s">
         <v>82</v>
       </c>
       <c r="AC17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AD17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE17" t="s">
         <v>82</v>
       </c>
       <c r="AF17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH17" t="s">
         <v>92</v>
@@ -3792,10 +3798,10 @@
         <v>78</v>
       </c>
       <c r="C18" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D18" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E18" t="s">
         <v>76</v>
@@ -3810,52 +3816,52 @@
         <v>76</v>
       </c>
       <c r="I18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J18" t="s">
         <v>87</v>
       </c>
       <c r="K18" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N18" t="s">
         <v>87</v>
       </c>
       <c r="O18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q18" t="s">
         <v>66</v>
       </c>
       <c r="R18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="S18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="U18" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="V18" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="W18" t="s">
         <v>76</v>
       </c>
       <c r="X18" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Y18" t="s">
         <v>66</v>
@@ -3873,7 +3879,7 @@
         <v>66</v>
       </c>
       <c r="AD18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AE18" t="s">
         <v>92</v>
@@ -3882,7 +3888,7 @@
         <v>75</v>
       </c>
       <c r="AG18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH18" t="s">
         <v>69</v>
@@ -3917,7 +3923,7 @@
         <v>86</v>
       </c>
       <c r="E19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F19" t="s">
         <v>87</v>
@@ -3926,28 +3932,28 @@
         <v>87</v>
       </c>
       <c r="H19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I19" t="s">
         <v>81</v>
       </c>
       <c r="J19" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K19" t="s">
         <v>82</v>
       </c>
       <c r="L19" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M19" t="s">
         <v>66</v>
       </c>
       <c r="N19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O19" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P19" t="s">
         <v>75</v>
@@ -3956,10 +3962,10 @@
         <v>75</v>
       </c>
       <c r="R19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T19" t="s">
         <v>82</v>
@@ -3971,25 +3977,25 @@
         <v>75</v>
       </c>
       <c r="W19" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="X19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y19" t="s">
         <v>82</v>
       </c>
       <c r="Z19" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AA19" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AB19" t="s">
         <v>92</v>
       </c>
       <c r="AC19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AD19" t="s">
         <v>60</v>
@@ -4004,36 +4010,39 @@
         <v>82</v>
       </c>
       <c r="AH19" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AI19" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AJ19" t="s">
         <v>93</v>
       </c>
       <c r="AK19" t="s">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="AL19" t="s">
+        <v>98</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>102</v>
+      </c>
+      <c r="B20" t="s">
+        <v>102</v>
+      </c>
+      <c r="C20" t="s">
+        <v>100</v>
+      </c>
+      <c r="D20" t="s">
+        <v>100</v>
+      </c>
+      <c r="E20" t="s">
         <v>101</v>
       </c>
-      <c r="B20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C20" t="s">
-        <v>99</v>
-      </c>
-      <c r="D20" t="s">
-        <v>99</v>
-      </c>
-      <c r="E20" t="s">
-        <v>100</v>
-      </c>
       <c r="F20" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G20" t="s">
         <v>66</v>
@@ -4042,7 +4051,7 @@
         <v>78</v>
       </c>
       <c r="I20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J20" t="s">
         <v>66</v>
@@ -4051,16 +4060,16 @@
         <v>61</v>
       </c>
       <c r="L20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P20" t="s">
         <v>82</v>
@@ -4078,7 +4087,7 @@
         <v>61</v>
       </c>
       <c r="U20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="V20" t="s">
         <v>61</v>
@@ -4099,7 +4108,7 @@
         <v>69</v>
       </c>
       <c r="AB20" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AC20" t="s">
         <v>61</v>
@@ -4108,10 +4117,10 @@
         <v>83</v>
       </c>
       <c r="AE20" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AF20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG20" t="s">
         <v>92</v>
@@ -4120,13 +4129,13 @@
         <v>93</v>
       </c>
       <c r="AI20" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AJ20" t="s">
         <v>62</v>
       </c>
       <c r="AK20" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
@@ -4134,25 +4143,25 @@
         <v>86</v>
       </c>
       <c r="B21" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C21" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D21" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E21" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F21" t="s">
         <v>73</v>
       </c>
       <c r="G21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H21" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I21" t="s">
         <v>66</v>
@@ -4164,16 +4173,16 @@
         <v>60</v>
       </c>
       <c r="L21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N21" t="s">
         <v>66</v>
       </c>
       <c r="O21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P21" t="s">
         <v>61</v>
@@ -4206,31 +4215,31 @@
         <v>69</v>
       </c>
       <c r="Z21" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AA21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AB21" t="s">
         <v>69</v>
       </c>
       <c r="AC21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AD21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AE21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AF21" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AG21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AH21" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AI21" t="s">
         <v>62</v>
@@ -4239,12 +4248,12 @@
         <v>61</v>
       </c>
       <c r="AK21" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B22" t="s">
         <v>80</v>
@@ -4256,7 +4265,7 @@
         <v>76</v>
       </c>
       <c r="E22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F22" t="s">
         <v>66</v>
@@ -4265,10 +4274,10 @@
         <v>75</v>
       </c>
       <c r="H22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J22" t="s">
         <v>82</v>
@@ -4283,7 +4292,7 @@
         <v>60</v>
       </c>
       <c r="N22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O22" t="s">
         <v>75</v>
@@ -4292,7 +4301,7 @@
         <v>60</v>
       </c>
       <c r="Q22" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="R22" t="s">
         <v>60</v>
@@ -4301,7 +4310,7 @@
         <v>60</v>
       </c>
       <c r="T22" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="U22" t="s">
         <v>61</v>
@@ -4310,19 +4319,19 @@
         <v>92</v>
       </c>
       <c r="W22" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="X22" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Y22" t="s">
         <v>93</v>
       </c>
       <c r="Z22" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA22" t="s">
         <v>113</v>
-      </c>
-      <c r="AA22" t="s">
-        <v>112</v>
       </c>
       <c r="AB22" t="s">
         <v>83</v>
@@ -4331,25 +4340,25 @@
         <v>69</v>
       </c>
       <c r="AD22" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AE22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AF22" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="AG22" t="s">
         <v>93</v>
       </c>
       <c r="AH22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AI22" t="s">
+        <v>94</v>
+      </c>
+      <c r="AJ22" t="s">
         <v>114</v>
-      </c>
-      <c r="AJ22" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
@@ -4366,10 +4375,10 @@
         <v>87</v>
       </c>
       <c r="E23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G23" t="s">
         <v>82</v>
@@ -4384,31 +4393,34 @@
         <v>60</v>
       </c>
       <c r="K23" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L23" t="s">
         <v>61</v>
       </c>
       <c r="M23" t="s">
+        <v>116</v>
+      </c>
+      <c r="N23" t="s">
         <v>115</v>
-      </c>
-      <c r="N23" t="s">
-        <v>113</v>
       </c>
       <c r="O23" t="s">
         <v>61</v>
       </c>
       <c r="P23" t="s">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>114</v>
       </c>
       <c r="R23" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="S23" t="s">
         <v>92</v>
       </c>
       <c r="T23" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="U23" t="s">
         <v>69</v>
@@ -4420,10 +4432,10 @@
         <v>69</v>
       </c>
       <c r="X23" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Y23" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Z23" t="s">
         <v>83</v>
@@ -4432,10 +4444,10 @@
         <v>62</v>
       </c>
       <c r="AB23" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AC23" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AD23" t="s">
         <v>62</v>
@@ -4444,13 +4456,13 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AH23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
@@ -4458,16 +4470,16 @@
         <v>76</v>
       </c>
       <c r="B24" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C24" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E24" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F24" t="s">
         <v>82</v>
@@ -4482,13 +4494,13 @@
         <v>92</v>
       </c>
       <c r="J24" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K24" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L24" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M24" t="s">
         <v>82</v>
@@ -4497,10 +4509,10 @@
         <v>93</v>
       </c>
       <c r="O24" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="R24" t="s">
         <v>69</v>
@@ -4524,22 +4536,22 @@
         <v>93</v>
       </c>
       <c r="Y24" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Z24" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AA24" t="s">
         <v>61</v>
       </c>
       <c r="AB24" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AC24" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AD24" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AE24" t="s">
         <v>61</v>
@@ -4551,7 +4563,7 @@
         <v>89</v>
       </c>
       <c r="AH24" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
@@ -4559,10 +4571,10 @@
         <v>87</v>
       </c>
       <c r="B25" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D25" t="s">
         <v>75</v>
@@ -4580,7 +4592,7 @@
         <v>60</v>
       </c>
       <c r="I25" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J25" t="s">
         <v>83</v>
@@ -4595,7 +4607,7 @@
         <v>93</v>
       </c>
       <c r="N25" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O25" t="s">
         <v>83</v>
@@ -4610,25 +4622,25 @@
         <v>93</v>
       </c>
       <c r="T25" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="U25" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="V25" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="W25" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="X25" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Y25" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Z25" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AA25" t="s">
         <v>88</v>
@@ -4640,24 +4652,24 @@
         <v>89</v>
       </c>
       <c r="AE25" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="AF25" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="AH25" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B26" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C26" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D26" t="s">
         <v>60</v>
@@ -4666,7 +4678,7 @@
         <v>92</v>
       </c>
       <c r="F26" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G26" t="s">
         <v>69</v>
@@ -4675,10 +4687,10 @@
         <v>92</v>
       </c>
       <c r="I26" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J26" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K26" t="s">
         <v>83</v>
@@ -4687,66 +4699,66 @@
         <v>93</v>
       </c>
       <c r="M26" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O26" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="R26" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="S26" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T26" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="U26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="V26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="W26" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="X26" t="s">
         <v>92</v>
       </c>
       <c r="Y26" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Z26" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AA26" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AB26" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AE26" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AF26" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B27" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D27" t="s">
         <v>92</v>
@@ -4764,55 +4776,55 @@
         <v>66</v>
       </c>
       <c r="I27" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J27" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K27" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L27" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M27" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O27" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P27" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="R27" t="s">
         <v>88</v>
       </c>
       <c r="S27" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T27" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="U27" t="s">
         <v>88</v>
       </c>
       <c r="V27" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="W27" t="s">
         <v>89</v>
       </c>
       <c r="X27" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="Y27" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Z27" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="AF27" t="s">
         <v>89</v>
@@ -4820,19 +4832,19 @@
     </row>
     <row r="28" ht="15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B28" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C28" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D28" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E28" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F28" t="s">
         <v>81</v>
@@ -4841,52 +4853,52 @@
         <v>83</v>
       </c>
       <c r="H28" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I28" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J28" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K28" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L28" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M28" t="s">
         <v>61</v>
       </c>
       <c r="N28" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O28" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P28" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="R28" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="T28" t="s">
         <v>75</v>
       </c>
       <c r="U28" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="V28" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="X28" t="s">
         <v>89</v>
       </c>
       <c r="Y28" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Z28" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
@@ -4894,10 +4906,10 @@
         <v>66</v>
       </c>
       <c r="B29" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C29" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D29" t="s">
         <v>69</v>
@@ -4909,22 +4921,22 @@
         <v>93</v>
       </c>
       <c r="G29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H29" t="s">
         <v>93</v>
       </c>
       <c r="I29" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J29" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K29" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L29" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M29" t="s">
         <v>88</v>
@@ -4936,24 +4948,24 @@
         <v>82</v>
       </c>
       <c r="P29" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="R29" t="s">
         <v>89</v>
       </c>
       <c r="T29" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="U29" t="s">
         <v>89</v>
       </c>
       <c r="V29" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B30" t="s">
         <v>82</v>
@@ -4962,16 +4974,16 @@
         <v>82</v>
       </c>
       <c r="D30" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E30" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F30" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G30" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H30" t="s">
         <v>83</v>
@@ -4980,22 +4992,22 @@
         <v>93</v>
       </c>
       <c r="J30" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K30" t="s">
         <v>62</v>
       </c>
       <c r="L30" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="M30" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="N30" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="O30" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="P30" t="s">
         <v>89</v>
@@ -5004,12 +5016,12 @@
         <v>89</v>
       </c>
       <c r="V30" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B31" t="s">
         <v>61</v>
@@ -5021,40 +5033,43 @@
         <v>93</v>
       </c>
       <c r="E31" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F31" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G31" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H31" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I31" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="J31" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="K31" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="L31" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M31" t="s">
         <v>89</v>
       </c>
       <c r="N31" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="O31" t="s">
-        <v>120</v>
+        <v>121</v>
+      </c>
+      <c r="P31" t="s">
+        <v>106</v>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>60</v>
       </c>
@@ -5068,10 +5083,10 @@
         <v>83</v>
       </c>
       <c r="E32" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F32" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G32" t="s">
         <v>62</v>
@@ -5080,13 +5095,13 @@
         <v>82</v>
       </c>
       <c r="I32" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J32" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="K32" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L32" t="s">
         <v>89</v>
@@ -5106,45 +5121,45 @@
         <v>92</v>
       </c>
       <c r="C33" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D33" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E33" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F33" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G33" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H33" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C34" t="s">
         <v>69</v>
       </c>
       <c r="D34" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E34" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F34" t="s">
         <v>61</v>
       </c>
       <c r="G34" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="H34" t="s">
         <v>89</v>
@@ -5161,16 +5176,16 @@
         <v>93</v>
       </c>
       <c r="D35" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E35" t="s">
+        <v>94</v>
+      </c>
+      <c r="F35" t="s">
         <v>114</v>
       </c>
-      <c r="F35" t="s">
-        <v>98</v>
-      </c>
       <c r="G35" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5178,13 +5193,13 @@
         <v>93</v>
       </c>
       <c r="B36" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C36" t="s">
         <v>83</v>
       </c>
       <c r="D36" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E36" t="s">
         <v>89</v>
@@ -5198,10 +5213,10 @@
         <v>83</v>
       </c>
       <c r="B37" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C37" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D37" t="s">
         <v>62</v>
@@ -5209,58 +5224,58 @@
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B38" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C38" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D38" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B39" t="s">
         <v>93</v>
       </c>
       <c r="C39" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D39" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B40" t="s">
         <v>83</v>
       </c>
       <c r="C40" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D40" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B41" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C41" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D41" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -5268,10 +5283,10 @@
         <v>62</v>
       </c>
       <c r="B42" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C42" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D42" t="s">
         <v>89</v>
@@ -5282,7 +5297,7 @@
         <v>88</v>
       </c>
       <c r="B43" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C43" t="s">
         <v>88</v>
@@ -5290,24 +5305,24 @@
     </row>
     <row r="44" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="B44" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C44" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="B45" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C45" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -5318,12 +5333,12 @@
         <v>89</v>
       </c>
       <c r="C46" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C47" t="s">
         <v>89</v>
@@ -5513,7 +5528,7 @@
         <v>74</v>
       </c>
       <c r="S3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="T3" t="s">
         <v>64</v>
@@ -5525,7 +5540,7 @@
         <v>73</v>
       </c>
       <c r="W3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="X3" t="s">
         <v>68</v>
@@ -5543,7 +5558,7 @@
         <v>79</v>
       </c>
       <c r="AC3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AD3" t="s">
         <v>86</v>
@@ -5552,10 +5567,10 @@
         <v>81</v>
       </c>
       <c r="AF3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AG3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AH3" t="s">
         <v>80</v>
@@ -5567,34 +5582,34 @@
         <v>87</v>
       </c>
       <c r="AK3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AL3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AM3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AN3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AO3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AP3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AQ3" t="s">
         <v>66</v>
       </c>
       <c r="AR3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AS3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AT3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AU3" t="s">
         <v>75</v>
@@ -5612,13 +5627,13 @@
         <v>92</v>
       </c>
       <c r="AZ3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BA3" t="s">
         <v>69</v>
       </c>
       <c r="BB3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="BC3" t="s">
         <v>93</v>
@@ -5627,46 +5642,46 @@
         <v>83</v>
       </c>
       <c r="BE3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="BF3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="BG3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BH3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BI3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BJ3" t="s">
         <v>62</v>
       </c>
       <c r="BK3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BL3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BM3" t="s">
         <v>88</v>
       </c>
       <c r="BN3" t="s">
+        <v>94</v>
+      </c>
+      <c r="BO3" t="s">
+        <v>121</v>
+      </c>
+      <c r="BP3" t="s">
         <v>114</v>
-      </c>
-      <c r="BO3" t="s">
-        <v>120</v>
-      </c>
-      <c r="BP3" t="s">
-        <v>98</v>
       </c>
       <c r="BQ3" t="s">
         <v>89</v>
       </c>
       <c r="BR3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
@@ -5692,7 +5707,7 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I4" t="s">
         <v>0</v>
@@ -5710,7 +5725,7 @@
         <v>12</v>
       </c>
       <c r="N4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O4" t="s">
         <v>14</v>
@@ -5731,7 +5746,7 @@
         <v>2</v>
       </c>
       <c r="U4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="V4" t="s">
         <v>12</v>
@@ -6657,7 +6672,7 @@
         <v>14</v>
       </c>
       <c r="BF8" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="BG8" t="s">
         <v>32</v>
@@ -6827,7 +6842,7 @@
         <v>0</v>
       </c>
       <c r="BF9" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="BG9" t="s">
         <v>34</v>
@@ -7232,7 +7247,7 @@
         <v>28</v>
       </c>
       <c r="T12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="V12" t="s">
         <v>1</v>
@@ -7629,7 +7644,7 @@
         <v>22</v>
       </c>
       <c r="BP14" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="BQ14" t="s">
         <v>31</v>
@@ -7775,7 +7790,7 @@
         <v>9</v>
       </c>
       <c r="BP15" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="BQ15" t="s">
         <v>15</v>
@@ -7813,7 +7828,7 @@
         <v>34</v>
       </c>
       <c r="R16" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="T16" t="s">
         <v>19</v>
@@ -8156,7 +8171,7 @@
         <v>20</v>
       </c>
       <c r="BF18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="BG18" t="s">
         <v>8</v>
@@ -8287,7 +8302,7 @@
         <v>39</v>
       </c>
       <c r="BF19" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="BG19" t="s">
         <v>13</v>
@@ -8411,7 +8426,7 @@
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C21" t="s">
         <v>7</v>
@@ -8611,7 +8626,7 @@
         <v>9</v>
       </c>
       <c r="BN22" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="BQ22" t="s">
         <v>22</v>
@@ -8709,7 +8724,7 @@
         <v>27</v>
       </c>
       <c r="BG23" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="BI23" t="s">
         <v>24</v>
@@ -9191,7 +9206,7 @@
         <v>74</v>
       </c>
       <c r="S3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="T3" t="s">
         <v>64</v>
@@ -9203,7 +9218,7 @@
         <v>73</v>
       </c>
       <c r="W3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="X3" t="s">
         <v>68</v>
@@ -9221,7 +9236,7 @@
         <v>79</v>
       </c>
       <c r="AC3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AD3" t="s">
         <v>86</v>
@@ -9230,10 +9245,10 @@
         <v>81</v>
       </c>
       <c r="AF3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AG3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AH3" t="s">
         <v>80</v>
@@ -9245,34 +9260,34 @@
         <v>87</v>
       </c>
       <c r="AK3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AL3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AM3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AN3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AO3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AP3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AQ3" t="s">
         <v>66</v>
       </c>
       <c r="AR3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AS3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AT3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AU3" t="s">
         <v>75</v>
@@ -9290,13 +9305,13 @@
         <v>92</v>
       </c>
       <c r="AZ3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BA3" t="s">
         <v>69</v>
       </c>
       <c r="BB3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="BC3" t="s">
         <v>93</v>
@@ -9305,906 +9320,906 @@
         <v>83</v>
       </c>
       <c r="BE3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="BF3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="BG3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BH3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BI3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BJ3" t="s">
         <v>62</v>
       </c>
       <c r="BK3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BL3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BM3" t="s">
         <v>88</v>
       </c>
       <c r="BN3" t="s">
+        <v>94</v>
+      </c>
+      <c r="BO3" t="s">
+        <v>121</v>
+      </c>
+      <c r="BP3" t="s">
         <v>114</v>
-      </c>
-      <c r="BO3" t="s">
-        <v>120</v>
-      </c>
-      <c r="BP3" t="s">
-        <v>98</v>
       </c>
       <c r="BQ3" t="s">
         <v>89</v>
       </c>
       <c r="BR3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="R4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="S4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="T4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="U4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="V4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="W4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="X4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Y4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Z4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AA4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AB4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AC4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AD4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AE4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AF4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AH4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AI4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AJ4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AK4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AL4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AM4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AN4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AO4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AP4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AQ4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AR4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AS4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AT4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AU4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AV4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AW4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AX4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AY4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AZ4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="BA4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="BB4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="BC4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BD4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="BE4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="BF4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="BG4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="BH4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="BI4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="BJ4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="BK4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="BL4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="BM4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="BN4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="BO4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BP4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="BQ4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="BR4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K5" t="s">
+        <v>200</v>
+      </c>
+      <c r="L5" t="s">
+        <v>201</v>
+      </c>
+      <c r="M5" t="s">
+        <v>202</v>
+      </c>
+      <c r="O5" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>204</v>
+      </c>
+      <c r="R5" t="s">
+        <v>205</v>
+      </c>
+      <c r="T5" t="s">
+        <v>206</v>
+      </c>
+      <c r="V5" t="s">
+        <v>207</v>
+      </c>
+      <c r="W5" t="s">
+        <v>208</v>
+      </c>
+      <c r="X5" t="s">
+        <v>209</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>210</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>211</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>212</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>213</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>214</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>215</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>216</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>217</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>218</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>219</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>220</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>221</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>222</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>223</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>223</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>224</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>225</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>223</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>226</v>
+      </c>
+      <c r="AU5" t="s">
         <v>199</v>
       </c>
-      <c r="L5" t="s">
-        <v>200</v>
-      </c>
-      <c r="M5" t="s">
-        <v>201</v>
-      </c>
-      <c r="O5" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>203</v>
-      </c>
-      <c r="R5" t="s">
-        <v>204</v>
-      </c>
-      <c r="T5" t="s">
-        <v>205</v>
-      </c>
-      <c r="V5" t="s">
-        <v>206</v>
-      </c>
-      <c r="W5" t="s">
-        <v>207</v>
-      </c>
-      <c r="X5" t="s">
-        <v>208</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>209</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>210</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>211</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>212</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>213</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>214</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>215</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>216</v>
-      </c>
-      <c r="AH5" t="s">
-        <v>217</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>218</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>219</v>
-      </c>
-      <c r="AK5" t="s">
-        <v>220</v>
-      </c>
-      <c r="AL5" t="s">
-        <v>221</v>
-      </c>
-      <c r="AN5" t="s">
-        <v>222</v>
-      </c>
-      <c r="AO5" t="s">
-        <v>222</v>
-      </c>
-      <c r="AQ5" t="s">
-        <v>223</v>
-      </c>
-      <c r="AR5" t="s">
-        <v>224</v>
-      </c>
-      <c r="AS5" t="s">
-        <v>222</v>
-      </c>
-      <c r="AT5" t="s">
-        <v>225</v>
-      </c>
-      <c r="AU5" t="s">
-        <v>198</v>
-      </c>
       <c r="AV5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AW5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AX5" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AY5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AZ5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="BA5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="BC5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="BD5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="BE5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="BF5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="BG5" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="BH5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="BI5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="BJ5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="BM5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="BN5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="BO5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="BP5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="BQ5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="R6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="T6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="V6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="W6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="X6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Z6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AA6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AB6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AD6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AE6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AF6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AH6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AI6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AJ6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AK6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AL6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AN6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AO6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AQ6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AR6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AS6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AT6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AU6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AV6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AW6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AX6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AY6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AZ6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="BA6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="BC6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="BD6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="BE6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="BF6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="BG6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="BI6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="BJ6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="BN6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="BP6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="BQ6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H7" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="J7" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O7" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q7" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="R7" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="T7" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="V7" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="X7" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Z7" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AA7" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AB7" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AD7" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AE7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AF7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AH7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AI7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AJ7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AN7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AO7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AQ7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AR7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AU7" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AV7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AW7" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AX7" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AY7" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AZ7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="BA7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="BC7" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="BD7" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="BE7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="BF7" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="BG7" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="BI7" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="BN7" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="BP7" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="BQ7" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C8" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E8" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F8" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H8" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K8" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O8" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q8" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="R8" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="T8" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="X8" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AA8" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AB8" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AE8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AF8" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AH8" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI8" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AJ8" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AN8" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AO8" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AQ8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AR8" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AU8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AV8" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AW8" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AX8" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AY8" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AZ8" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="BA8" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="BC8" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="BD8" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="BE8" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="BF8" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="BG8" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="BI8" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="BN8" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="BQ8" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E9" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F9" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H9" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O9" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="T9" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="X9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AB9" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AF9" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI9" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AJ9" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AO9" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AV9" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AW9" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AX9" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AY9" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AZ9" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="BA9" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="BC9" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="BD9" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="BE9" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="BF9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="BG9" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="BN9" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="BQ9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="41:69" x14ac:dyDescent="0.25">
       <c r="AO10" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AW10" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/data/ICEHLdelegacije.xlsx
+++ b/data/ICEHLdelegacije.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2685" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2682" uniqueCount="399">
   <si>
     <t>SmetanaLa</t>
   </si>
@@ -204,30 +204,33 @@
     <t>2024-12-22</t>
   </si>
   <si>
+    <t>zbrisano</t>
+  </si>
+  <si>
+    <t>2024-10-01</t>
+  </si>
+  <si>
+    <t>2024-10-25</t>
+  </si>
+  <si>
+    <t>2024-10-20</t>
+  </si>
+  <si>
+    <t>2024-12-08</t>
+  </si>
+  <si>
+    <t>2024-10-06</t>
+  </si>
+  <si>
+    <t>2024-11-01</t>
+  </si>
+  <si>
+    <t>2025-01-01</t>
+  </si>
+  <si>
     <t>2025-01-19</t>
   </si>
   <si>
-    <t>2024-10-01</t>
-  </si>
-  <si>
-    <t>2024-10-25</t>
-  </si>
-  <si>
-    <t>2024-10-20</t>
-  </si>
-  <si>
-    <t>2024-12-08</t>
-  </si>
-  <si>
-    <t>2024-10-06</t>
-  </si>
-  <si>
-    <t>2024-11-01</t>
-  </si>
-  <si>
-    <t>2025-01-01</t>
-  </si>
-  <si>
     <t>2024-10-05</t>
   </si>
   <si>
@@ -315,9 +318,6 @@
     <t>2025-01-10</t>
   </si>
   <si>
-    <t>zbrisano</t>
-  </si>
-  <si>
     <t>2024-11-22</t>
   </si>
   <si>
@@ -558,10 +558,10 @@
     <t>Merkur Eisstadion Graz;Huber aAn;OfnerCh;JedlickaPe;KoncDa</t>
   </si>
   <si>
-    <t>Merkur Eisstadion Graz;SiegelSt;SternatCh;RieckenSi;WimmlerAl</t>
-  </si>
-  <si>
-    <t>Eisarena Salzburg;PiragicTr;SternatCh;NotheggerDa;ZgoncGa</t>
+    <t>Merkur Eisstadion Graz;SiegelSt;SternatCh;HribarMa;RieckenSi</t>
+  </si>
+  <si>
+    <t>Eisarena Salzburg;PiragicTr;SternatCh;WeissAl;ZgoncGa</t>
   </si>
   <si>
     <t>Eishalle Bruneck;NikolicMa;SeewaldEl;PardatscherUl;RigoniDa</t>
@@ -582,7 +582,7 @@
     <t>Eishalle Wien-Kagran;SmetanaLa;VoicanCh;BedynekSe;RieckenSi</t>
   </si>
   <si>
-    <t>Eisarena Salzburg;HronskyTo;SmetanaLa;KoncDa;RieckenSi</t>
+    <t>Eisarena Salzburg;HronskyTo;SmetanaLa;RieckenSi;WimmlerAl</t>
   </si>
   <si>
     <t>Sparkasse Arena Bozen;FichtnerPa;SiegelSt;MantovaniDa;RigoniDa</t>
@@ -735,10 +735,10 @@
     <t>Sparkasse Arena Bozen;OfnerCh;PiragicTr;MantovaniDa;ZgoncGa</t>
   </si>
   <si>
-    <t>Eishalle Wien-Kagran;NagyAt;SiegelSt;DurmisOt;WimmlerAl</t>
-  </si>
-  <si>
-    <t>Linz AG Eisarena;SmetanaLa;SternatCh;DurmisOt;WimmlerAl</t>
+    <t>Eishalle Wien-Kagran;NagyAt;SiegelSt;Gatol-schafranekMa;WimmlerAl</t>
+  </si>
+  <si>
+    <t>Linz AG Eisarena;SmetanaLa;SternatCh;NotheggerDa;WimmlerAl</t>
   </si>
   <si>
     <t>Gabor Ocskay Eisarena;OfnerCh;SeewaldEl;Gatol-schafranekMa;MuzsikNo</t>
@@ -747,7 +747,7 @@
     <t>Stadthalle Villach;NikolicMa;SchauerJa;BedynekSe;PuffWo</t>
   </si>
   <si>
-    <t>Eishalle Bruneck;OfnerCh;SternatCh;DurmisOt;JedlickaPe</t>
+    <t>Eishalle Bruneck;OfnerCh;SternatCh;JedlickaPe;KoncDa</t>
   </si>
   <si>
     <t>Klagenfurter Stadthalle;GroznikBo;SoosDa;MuzsikNo;VacziDa</t>
@@ -876,7 +876,7 @@
     <t>Tiroler Wasserkraft Arena;KainbergerJu;OfnerCh;SeewaldJe;WimmlerAl</t>
   </si>
   <si>
-    <t>Eisarena Salzburg;SchauerJa;ZrnicMi;NotheggerDa;RieckenSi</t>
+    <t>Eisarena Salzburg;SchauerJa;ZrnicMi;RieckenSi;ZacherlPa</t>
   </si>
   <si>
     <t>Eishalle Wien-Kagran;FichtnerPa;KainbergerJu;Gatol-schafranekMa;MoidlMa</t>
@@ -888,7 +888,7 @@
     <t>Stadthalle Villach;GroznikBo;PiragicTr;HribarMa;ZgoncGa</t>
   </si>
   <si>
-    <t>Eishalle Bruneck;NikolicMa;NikolicKr;LinesmanEi;MantovaniDa</t>
+    <t>Eishalle Bruneck;NikolicMa;NikolicKr;MantovaniDa;RigoniDa</t>
   </si>
   <si>
     <t>Tiroler Wasserkraft Arena;FichtnerPa;SiegelSt;MartinFl;PardatscherUl</t>
@@ -1011,7 +1011,7 @@
     <t>Linz AG Eisarena;PiragicTr;SiegelSt;Gatol-schafranekMa;SeewaldJe</t>
   </si>
   <si>
-    <t>Linz AG Eisarena;Huber aAn;SmetanaLa;NotheggerDa;WeissAl</t>
+    <t>Linz AG Eisarena;Huber aAn;SmetanaLa;WeissAl;WimmlerAl</t>
   </si>
   <si>
     <t>Stadthalle Villach;RezekGr;SmetanaLa;HribarMa;RieckenSi</t>
@@ -1020,7 +1020,7 @@
     <t>Gabor Ocskay Eisarena;OfnerCh;SeewaldEl;MuzsikNo;VacziDa</t>
   </si>
   <si>
-    <t>Eishalle Feldkirch;Huber aAn;NikolicKr;DurmisOt;JedlickaPe</t>
+    <t>Eishalle Feldkirch;Huber aAn;NikolicKr;JedlickaPe;KoncDa</t>
   </si>
   <si>
     <t>Eishalle KagranEins;NikolicMa;SchauerJa;Gatol-schafranekMa;RieckenSi</t>
@@ -1621,7 +1621,7 @@
         <v>31</v>
       </c>
       <c r="I2">
-        <f>COUNTIF(I4:I98,"&lt;&gt;")</f>
+        <f>COUNTIF(I4:I97,"&lt;&gt;")</f>
         <v>29</v>
       </c>
       <c r="J2">
@@ -1650,11 +1650,11 @@
       </c>
       <c r="P2">
         <f>COUNTIF(P4:P98,"&lt;&gt;")</f>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Q2">
         <f>COUNTIF(Q4:Q100,"&lt;&gt;")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R2">
         <f>COUNTIF(R4:R98,"&lt;&gt;")</f>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="U2">
         <f>COUNTIF(U4:U100,"&lt;&gt;")</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="V2">
         <f>COUNTIF(V4:V100,"&lt;&gt;")</f>
@@ -1706,15 +1706,15 @@
       </c>
       <c r="AD2">
         <f>COUNTIF(AD4:AD94,"&lt;&gt;")</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE2">
-        <f>COUNTIF(AE4:AE95,"&lt;&gt;")</f>
-        <v>23</v>
+        <f>COUNTIF(AE4:AE92,"&lt;&gt;")</f>
+        <v>21</v>
       </c>
       <c r="AF2">
-        <f>COUNTIF(AF4:AF93,"&lt;&gt;")</f>
-        <v>24</v>
+        <f>COUNTIF(AF4:AF87,"&lt;&gt;")</f>
+        <v>18</v>
       </c>
       <c r="AG2">
         <f>COUNTIF(AG4:AG100,"&lt;&gt;")</f>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="AL2">
         <f>COUNTIF(AL4:AL100,"&lt;&gt;")</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AM2">
         <f>COUNTIF(AM4:AM98,"&lt;&gt;")</f>
@@ -1754,11 +1754,11 @@
       </c>
       <c r="AP2">
         <f>COUNTIF(AP4:AP100,"&lt;&gt;")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ2">
         <f>COUNTIF(AQ4:AQ99,"&lt;&gt;")</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR2">
         <f>COUNTIF(AR4:AR100,"&lt;&gt;")</f>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="AT2">
         <f>COUNTIF(AT4:AT100,"&lt;&gt;")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU2">
         <f>COUNTIF(AU4:AU100,"&lt;&gt;")</f>
@@ -2230,7 +2230,7 @@
         <v>69</v>
       </c>
       <c r="AW5" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:49" x14ac:dyDescent="0.25">
@@ -2274,7 +2274,7 @@
         <v>57</v>
       </c>
       <c r="N6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O6" t="s">
         <v>57</v>
@@ -2322,10 +2322,10 @@
         <v>63</v>
       </c>
       <c r="AD6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF6" t="s">
         <v>56</v>
@@ -2334,7 +2334,7 @@
         <v>56</v>
       </c>
       <c r="AH6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AI6" t="s">
         <v>56</v>
@@ -2352,25 +2352,25 @@
         <v>65</v>
       </c>
       <c r="AN6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO6" t="s">
         <v>64</v>
       </c>
       <c r="AP6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AQ6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AR6" t="s">
         <v>75</v>
-      </c>
-      <c r="AR6" t="s">
-        <v>74</v>
       </c>
       <c r="AS6" t="s">
         <v>68</v>
       </c>
       <c r="AT6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
@@ -2405,10 +2405,10 @@
         <v>56</v>
       </c>
       <c r="K7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M7" t="s">
         <v>56</v>
@@ -2420,10 +2420,10 @@
         <v>56</v>
       </c>
       <c r="P7" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q7" t="s">
         <v>71</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>70</v>
       </c>
       <c r="R7" t="s">
         <v>67</v>
@@ -2435,10 +2435,10 @@
         <v>67</v>
       </c>
       <c r="U7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W7" t="s">
         <v>58</v>
@@ -2450,19 +2450,19 @@
         <v>67</v>
       </c>
       <c r="Z7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA7" t="s">
         <v>67</v>
       </c>
       <c r="AB7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC7" t="s">
         <v>67</v>
       </c>
       <c r="AD7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE7" t="s">
         <v>65</v>
@@ -2471,10 +2471,10 @@
         <v>67</v>
       </c>
       <c r="AG7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AH7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI7" t="s">
         <v>58</v>
@@ -2489,28 +2489,28 @@
         <v>59</v>
       </c>
       <c r="AM7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AN7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AO7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AQ7" t="s">
         <v>60</v>
       </c>
       <c r="AR7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AS7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AT7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
@@ -2536,10 +2536,10 @@
         <v>58</v>
       </c>
       <c r="H8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J8" t="s">
         <v>58</v>
@@ -2557,7 +2557,7 @@
         <v>58</v>
       </c>
       <c r="O8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P8" t="s">
         <v>59</v>
@@ -2566,16 +2566,16 @@
         <v>67</v>
       </c>
       <c r="R8" t="s">
+        <v>73</v>
+      </c>
+      <c r="S8" t="s">
+        <v>85</v>
+      </c>
+      <c r="T8" t="s">
         <v>72</v>
       </c>
-      <c r="S8" t="s">
-        <v>84</v>
-      </c>
-      <c r="T8" t="s">
-        <v>71</v>
-      </c>
       <c r="U8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="V8" t="s">
         <v>59</v>
@@ -2584,31 +2584,31 @@
         <v>55</v>
       </c>
       <c r="X8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Z8" t="s">
         <v>64</v>
       </c>
       <c r="AA8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AC8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD8" t="s">
         <v>68</v>
       </c>
       <c r="AE8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AF8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AG8" t="s">
         <v>58</v>
@@ -2617,63 +2617,63 @@
         <v>64</v>
       </c>
       <c r="AI8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AJ8" t="s">
         <v>65</v>
       </c>
       <c r="AK8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AL8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AM8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AN8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AO8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AP8" t="s">
         <v>60</v>
       </c>
       <c r="AQ8" t="s">
+        <v>84</v>
+      </c>
+      <c r="AR8" t="s">
         <v>83</v>
       </c>
-      <c r="AR8" t="s">
-        <v>82</v>
-      </c>
       <c r="AS8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AT8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
         <v>59</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F9" t="s">
         <v>65</v>
       </c>
       <c r="G9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H9" t="s">
         <v>58</v>
@@ -2688,40 +2688,40 @@
         <v>65</v>
       </c>
       <c r="L9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S9" t="s">
         <v>65</v>
       </c>
       <c r="T9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X9" t="s">
         <v>65</v>
@@ -2730,69 +2730,69 @@
         <v>64</v>
       </c>
       <c r="Z9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AA9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AE9" t="s">
         <v>68</v>
       </c>
       <c r="AF9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AG9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AK9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AL9" t="s">
         <v>68</v>
       </c>
       <c r="AM9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AN9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO9" t="s">
         <v>66</v>
       </c>
       <c r="AP9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AQ9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AR9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AT9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B10" t="s">
         <v>55</v>
@@ -2801,25 +2801,25 @@
         <v>65</v>
       </c>
       <c r="D10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E10" t="s">
         <v>55</v>
       </c>
       <c r="F10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K10" t="s">
         <v>64</v>
@@ -2828,7 +2828,7 @@
         <v>65</v>
       </c>
       <c r="M10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N10" t="s">
         <v>64</v>
@@ -2837,10 +2837,10 @@
         <v>65</v>
       </c>
       <c r="P10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="R10" t="s">
         <v>65</v>
@@ -2849,111 +2849,108 @@
         <v>64</v>
       </c>
       <c r="T10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="U10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="V10" t="s">
         <v>65</v>
       </c>
       <c r="W10" t="s">
+        <v>75</v>
+      </c>
+      <c r="X10" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y10" t="s">
         <v>74</v>
       </c>
-      <c r="X10" t="s">
-        <v>96</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>73</v>
-      </c>
       <c r="Z10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AB10" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>75</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>87</v>
+      </c>
+      <c r="AE10" t="s">
         <v>91</v>
       </c>
-      <c r="AC10" t="s">
-        <v>74</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>86</v>
-      </c>
-      <c r="AE10" t="s">
-        <v>90</v>
-      </c>
       <c r="AF10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AG10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AH10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI10" t="s">
         <v>65</v>
       </c>
       <c r="AJ10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AL10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AM10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AN10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AO10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AP10" t="s">
-        <v>98</v>
-      </c>
-      <c r="AQ10" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>65</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D11" t="s">
         <v>64</v>
       </c>
       <c r="E11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F11" t="s">
         <v>64</v>
       </c>
       <c r="G11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H11" t="s">
         <v>65</v>
       </c>
       <c r="I11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J11" t="s">
         <v>64</v>
       </c>
       <c r="K11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L11" t="s">
         <v>64</v>
@@ -2965,10 +2962,10 @@
         <v>68</v>
       </c>
       <c r="O11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q11" t="s">
         <v>64</v>
@@ -2977,7 +2974,7 @@
         <v>64</v>
       </c>
       <c r="S11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="T11" t="s">
         <v>64</v>
@@ -2995,22 +2992,22 @@
         <v>68</v>
       </c>
       <c r="Y11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Z11" t="s">
         <v>100</v>
       </c>
       <c r="AA11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AB11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AC11" t="s">
         <v>68</v>
       </c>
       <c r="AD11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AE11" t="s">
         <v>56</v>
@@ -3022,28 +3019,28 @@
         <v>68</v>
       </c>
       <c r="AH11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI11" t="s">
         <v>100</v>
       </c>
       <c r="AJ11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AL11" t="s">
         <v>101</v>
       </c>
       <c r="AM11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN11" t="s">
         <v>69</v>
       </c>
       <c r="AO11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AP11" t="s">
         <v>61</v>
@@ -3051,7 +3048,7 @@
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B12" t="s">
         <v>65</v>
@@ -3060,43 +3057,43 @@
         <v>64</v>
       </c>
       <c r="D12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E12" t="s">
         <v>65</v>
       </c>
       <c r="F12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G12" t="s">
         <v>64</v>
       </c>
       <c r="H12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I12" t="s">
         <v>68</v>
       </c>
       <c r="J12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L12" t="s">
         <v>68</v>
       </c>
       <c r="M12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q12" t="s">
         <v>68</v>
@@ -3108,55 +3105,55 @@
         <v>68</v>
       </c>
       <c r="T12" t="s">
+        <v>92</v>
+      </c>
+      <c r="U12" t="s">
+        <v>80</v>
+      </c>
+      <c r="V12" t="s">
+        <v>74</v>
+      </c>
+      <c r="W12" t="s">
+        <v>74</v>
+      </c>
+      <c r="X12" t="s">
         <v>91</v>
       </c>
-      <c r="U12" t="s">
+      <c r="Y12" t="s">
         <v>79</v>
       </c>
-      <c r="V12" t="s">
-        <v>73</v>
-      </c>
-      <c r="W12" t="s">
-        <v>73</v>
-      </c>
-      <c r="X12" t="s">
-        <v>90</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>78</v>
-      </c>
       <c r="Z12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AA12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AB12" t="s">
         <v>102</v>
       </c>
       <c r="AC12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AD12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AE12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AF12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AG12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AJ12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AK12" t="s">
         <v>100</v>
@@ -3171,10 +3168,10 @@
         <v>105</v>
       </c>
       <c r="AO12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AP12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
@@ -3182,16 +3179,16 @@
         <v>64</v>
       </c>
       <c r="B13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" t="s">
         <v>74</v>
       </c>
-      <c r="C13" t="s">
-        <v>73</v>
-      </c>
       <c r="D13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F13" t="s">
         <v>68</v>
@@ -3200,61 +3197,61 @@
         <v>68</v>
       </c>
       <c r="H13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M13" t="s">
         <v>68</v>
       </c>
       <c r="N13" t="s">
+        <v>79</v>
+      </c>
+      <c r="O13" t="s">
+        <v>80</v>
+      </c>
+      <c r="P13" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>79</v>
+      </c>
+      <c r="R13" t="s">
         <v>78</v>
       </c>
-      <c r="O13" t="s">
+      <c r="S13" t="s">
+        <v>80</v>
+      </c>
+      <c r="T13" t="s">
+        <v>91</v>
+      </c>
+      <c r="U13" t="s">
+        <v>87</v>
+      </c>
+      <c r="V13" t="s">
         <v>79</v>
       </c>
-      <c r="P13" t="s">
+      <c r="W13" t="s">
         <v>79</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>78</v>
-      </c>
-      <c r="R13" t="s">
-        <v>77</v>
-      </c>
-      <c r="S13" t="s">
-        <v>79</v>
-      </c>
-      <c r="T13" t="s">
-        <v>90</v>
-      </c>
-      <c r="U13" t="s">
-        <v>86</v>
-      </c>
-      <c r="V13" t="s">
-        <v>78</v>
-      </c>
-      <c r="W13" t="s">
-        <v>78</v>
       </c>
       <c r="X13" t="s">
         <v>64</v>
       </c>
       <c r="Y13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AA13" t="s">
         <v>100</v>
@@ -3263,43 +3260,43 @@
         <v>100</v>
       </c>
       <c r="AC13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD13" t="s">
         <v>101</v>
       </c>
       <c r="AE13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AF13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AG13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AJ13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AK13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AL13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AN13" t="s">
         <v>66</v>
       </c>
       <c r="AO13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AP13" t="s">
         <v>106</v>
@@ -3307,25 +3304,25 @@
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B14" t="s">
         <v>64</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D14" t="s">
         <v>68</v>
       </c>
       <c r="E14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H14" t="s">
         <v>68</v>
@@ -3340,58 +3337,58 @@
         <v>100</v>
       </c>
       <c r="L14" t="s">
+        <v>80</v>
+      </c>
+      <c r="M14" t="s">
         <v>79</v>
       </c>
-      <c r="M14" t="s">
-        <v>78</v>
-      </c>
       <c r="N14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P14" t="s">
         <v>100</v>
       </c>
       <c r="Q14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T14" t="s">
         <v>100</v>
       </c>
       <c r="U14" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W14" t="s">
+        <v>80</v>
+      </c>
+      <c r="X14" t="s">
         <v>79</v>
       </c>
-      <c r="X14" t="s">
-        <v>78</v>
-      </c>
       <c r="Y14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z14" t="s">
         <v>103</v>
       </c>
       <c r="AA14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AB14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AC14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD14" t="s">
         <v>103</v>
@@ -3421,7 +3418,7 @@
         <v>61</v>
       </c>
       <c r="AM14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AN14" t="s">
         <v>108</v>
@@ -3429,46 +3426,49 @@
       <c r="AO14" t="s">
         <v>60</v>
       </c>
+      <c r="AP14" t="s">
+        <v>108</v>
+      </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
         <v>68</v>
       </c>
       <c r="D15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E15" t="s">
         <v>68</v>
       </c>
       <c r="F15" t="s">
+        <v>80</v>
+      </c>
+      <c r="G15" t="s">
         <v>79</v>
       </c>
-      <c r="G15" t="s">
-        <v>78</v>
-      </c>
       <c r="H15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J15" t="s">
+        <v>82</v>
+      </c>
+      <c r="K15" t="s">
         <v>81</v>
       </c>
-      <c r="K15" t="s">
-        <v>80</v>
-      </c>
       <c r="L15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N15" t="s">
         <v>102</v>
@@ -3483,40 +3483,40 @@
         <v>100</v>
       </c>
       <c r="R15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="S15" t="s">
         <v>100</v>
       </c>
       <c r="T15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="U15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="V15" t="s">
         <v>100</v>
       </c>
       <c r="W15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="X15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Y15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Z15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AA15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AB15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD15" t="s">
         <v>64</v>
@@ -3525,16 +3525,16 @@
         <v>103</v>
       </c>
       <c r="AF15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG15" t="s">
+        <v>77</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI15" t="s">
         <v>76</v>
-      </c>
-      <c r="AH15" t="s">
-        <v>97</v>
-      </c>
-      <c r="AI15" t="s">
-        <v>75</v>
       </c>
       <c r="AJ15" t="s">
         <v>66</v>
@@ -3543,13 +3543,13 @@
         <v>66</v>
       </c>
       <c r="AL15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AN15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AO15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
@@ -3557,76 +3557,76 @@
         <v>68</v>
       </c>
       <c r="B16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H16" t="s">
+        <v>82</v>
+      </c>
+      <c r="I16" t="s">
+        <v>77</v>
+      </c>
+      <c r="J16" t="s">
         <v>81</v>
-      </c>
-      <c r="I16" t="s">
-        <v>76</v>
-      </c>
-      <c r="J16" t="s">
-        <v>80</v>
       </c>
       <c r="K16" t="s">
         <v>107</v>
       </c>
       <c r="L16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M16" t="s">
+        <v>82</v>
+      </c>
+      <c r="N16" t="s">
+        <v>87</v>
+      </c>
+      <c r="O16" t="s">
         <v>81</v>
       </c>
-      <c r="N16" t="s">
-        <v>86</v>
-      </c>
-      <c r="O16" t="s">
-        <v>80</v>
-      </c>
       <c r="P16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="R16" t="s">
         <v>100</v>
       </c>
       <c r="S16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U16" t="s">
         <v>107</v>
       </c>
       <c r="V16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="W16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Y16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Z16" t="s">
         <v>109</v>
@@ -3638,13 +3638,13 @@
         <v>66</v>
       </c>
       <c r="AC16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AD16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AE16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AF16" t="s">
         <v>104</v>
@@ -3656,13 +3656,13 @@
         <v>66</v>
       </c>
       <c r="AI16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AJ16" t="s">
         <v>60</v>
       </c>
       <c r="AK16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL16" t="s">
         <v>100</v>
@@ -3673,19 +3673,19 @@
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B17" t="s">
         <v>68</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F17" t="s">
         <v>100</v>
@@ -3694,13 +3694,13 @@
         <v>100</v>
       </c>
       <c r="H17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I17" t="s">
         <v>107</v>
       </c>
       <c r="J17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K17" t="s">
         <v>110</v>
@@ -3709,22 +3709,22 @@
         <v>107</v>
       </c>
       <c r="M17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="R17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="S17" t="s">
         <v>103</v>
@@ -3736,7 +3736,7 @@
         <v>102</v>
       </c>
       <c r="V17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="W17" t="s">
         <v>100</v>
@@ -3754,7 +3754,7 @@
         <v>111</v>
       </c>
       <c r="AB17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC17" t="s">
         <v>103</v>
@@ -3763,39 +3763,39 @@
         <v>104</v>
       </c>
       <c r="AE17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF17" t="s">
         <v>111</v>
       </c>
       <c r="AG17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AH17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI17" t="s">
         <v>69</v>
       </c>
       <c r="AJ17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AK17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AL17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C18" t="s">
         <v>102</v>
@@ -3804,25 +3804,25 @@
         <v>102</v>
       </c>
       <c r="E18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I18" t="s">
         <v>101</v>
       </c>
       <c r="J18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L18" t="s">
         <v>101</v>
@@ -3831,7 +3831,7 @@
         <v>101</v>
       </c>
       <c r="N18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O18" t="s">
         <v>103</v>
@@ -3852,13 +3852,13 @@
         <v>104</v>
       </c>
       <c r="U18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="V18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="W18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X18" t="s">
         <v>112</v>
@@ -3867,7 +3867,7 @@
         <v>66</v>
       </c>
       <c r="Z18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA18" t="s">
         <v>60</v>
@@ -3882,10 +3882,10 @@
         <v>111</v>
       </c>
       <c r="AE18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AF18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AG18" t="s">
         <v>111</v>
@@ -3894,7 +3894,7 @@
         <v>69</v>
       </c>
       <c r="AI18" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AJ18" t="s">
         <v>69</v>
@@ -3903,45 +3903,45 @@
         <v>69</v>
       </c>
       <c r="AL18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AN18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C19" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D19" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E19" t="s">
         <v>107</v>
       </c>
       <c r="F19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H19" t="s">
         <v>107</v>
       </c>
       <c r="I19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J19" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L19" t="s">
         <v>103</v>
@@ -3953,13 +3953,13 @@
         <v>107</v>
       </c>
       <c r="O19" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="R19" t="s">
         <v>104</v>
@@ -3968,22 +3968,22 @@
         <v>111</v>
       </c>
       <c r="T19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U19" t="s">
         <v>66</v>
       </c>
       <c r="V19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="W19" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="X19" t="s">
         <v>111</v>
       </c>
       <c r="Y19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z19" t="s">
         <v>105</v>
@@ -3992,7 +3992,7 @@
         <v>105</v>
       </c>
       <c r="AB19" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AC19" t="s">
         <v>104</v>
@@ -4004,25 +4004,25 @@
         <v>69</v>
       </c>
       <c r="AF19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AG19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH19" t="s">
         <v>105</v>
       </c>
       <c r="AI19" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AJ19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AK19" t="s">
         <v>108</v>
       </c>
       <c r="AL19" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
@@ -4048,10 +4048,10 @@
         <v>66</v>
       </c>
       <c r="H20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I20" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J20" t="s">
         <v>66</v>
@@ -4060,28 +4060,28 @@
         <v>61</v>
       </c>
       <c r="L20" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M20" t="s">
         <v>104</v>
       </c>
       <c r="N20" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O20" t="s">
         <v>104</v>
       </c>
       <c r="P20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="R20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T20" t="s">
         <v>61</v>
@@ -4093,13 +4093,13 @@
         <v>61</v>
       </c>
       <c r="W20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="X20" t="s">
         <v>61</v>
       </c>
       <c r="Y20" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Z20" t="s">
         <v>69</v>
@@ -4114,33 +4114,36 @@
         <v>61</v>
       </c>
       <c r="AD20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AE20" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="AF20" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG20" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH20" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI20" t="s">
         <v>106</v>
       </c>
       <c r="AJ20" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="AK20" t="s">
         <v>113</v>
       </c>
+      <c r="AL20" t="s">
+        <v>106</v>
+      </c>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B21" t="s">
         <v>100</v>
@@ -4152,22 +4155,22 @@
         <v>109</v>
       </c>
       <c r="E21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F21" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G21" t="s">
         <v>111</v>
       </c>
       <c r="H21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I21" t="s">
         <v>66</v>
       </c>
       <c r="J21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K21" t="s">
         <v>60</v>
@@ -4200,13 +4203,13 @@
         <v>60</v>
       </c>
       <c r="U21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="V21" t="s">
         <v>60</v>
       </c>
       <c r="W21" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="X21" t="s">
         <v>60</v>
@@ -4215,10 +4218,10 @@
         <v>69</v>
       </c>
       <c r="Z21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AA21" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AB21" t="s">
         <v>69</v>
@@ -4227,13 +4230,13 @@
         <v>105</v>
       </c>
       <c r="AD21" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AE21" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="AF21" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="AG21" t="s">
         <v>105</v>
@@ -4242,7 +4245,7 @@
         <v>108</v>
       </c>
       <c r="AI21" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="AJ21" t="s">
         <v>61</v>
@@ -4256,13 +4259,13 @@
         <v>100</v>
       </c>
       <c r="B22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C22" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D22" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E22" t="s">
         <v>112</v>
@@ -4271,7 +4274,7 @@
         <v>66</v>
       </c>
       <c r="G22" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H22" t="s">
         <v>104</v>
@@ -4280,13 +4283,13 @@
         <v>104</v>
       </c>
       <c r="J22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K22" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L22" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M22" t="s">
         <v>60</v>
@@ -4295,7 +4298,7 @@
         <v>104</v>
       </c>
       <c r="O22" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P22" t="s">
         <v>60</v>
@@ -4316,7 +4319,7 @@
         <v>61</v>
       </c>
       <c r="V22" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="W22" t="s">
         <v>105</v>
@@ -4325,7 +4328,7 @@
         <v>105</v>
       </c>
       <c r="Y22" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Z22" t="s">
         <v>115</v>
@@ -4334,7 +4337,7 @@
         <v>113</v>
       </c>
       <c r="AB22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AC22" t="s">
         <v>69</v>
@@ -4343,19 +4346,16 @@
         <v>113</v>
       </c>
       <c r="AE22" t="s">
-        <v>106</v>
-      </c>
-      <c r="AF22" t="s">
+        <v>95</v>
+      </c>
+      <c r="AG22" t="s">
+        <v>94</v>
+      </c>
+      <c r="AH22" t="s">
         <v>99</v>
       </c>
-      <c r="AG22" t="s">
-        <v>93</v>
-      </c>
-      <c r="AH22" t="s">
-        <v>98</v>
-      </c>
       <c r="AI22" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AJ22" t="s">
         <v>114</v>
@@ -4363,16 +4363,16 @@
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E23" t="s">
         <v>104</v>
@@ -4381,10 +4381,10 @@
         <v>104</v>
       </c>
       <c r="G23" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H23" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I23" t="s">
         <v>61</v>
@@ -4417,7 +4417,7 @@
         <v>105</v>
       </c>
       <c r="S23" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T23" t="s">
         <v>115</v>
@@ -4426,7 +4426,7 @@
         <v>69</v>
       </c>
       <c r="V23" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="W23" t="s">
         <v>69</v>
@@ -4438,25 +4438,22 @@
         <v>108</v>
       </c>
       <c r="Z23" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AA23" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="AB23" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AC23" t="s">
         <v>108</v>
       </c>
       <c r="AD23" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="AE23" t="s">
-        <v>83</v>
-      </c>
-      <c r="AF23" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG23" t="s">
         <v>106</v>
@@ -4467,7 +4464,7 @@
     </row>
     <row r="24" ht="15" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B24" t="s">
         <v>107</v>
@@ -4482,7 +4479,7 @@
         <v>115</v>
       </c>
       <c r="F24" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G24" t="s">
         <v>60</v>
@@ -4491,7 +4488,7 @@
         <v>61</v>
       </c>
       <c r="I24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J24" t="s">
         <v>105</v>
@@ -4503,10 +4500,10 @@
         <v>105</v>
       </c>
       <c r="M24" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="N24" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O24" t="s">
         <v>105</v>
@@ -4521,19 +4518,19 @@
         <v>69</v>
       </c>
       <c r="T24" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U24" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="V24" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="W24" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X24" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Y24" t="s">
         <v>106</v>
@@ -4554,30 +4551,27 @@
         <v>114</v>
       </c>
       <c r="AE24" t="s">
-        <v>61</v>
-      </c>
-      <c r="AF24" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="AG24" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AH24" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B25" t="s">
         <v>101</v>
       </c>
       <c r="C25" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D25" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E25" t="s">
         <v>61</v>
@@ -4586,7 +4580,7 @@
         <v>60</v>
       </c>
       <c r="G25" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H25" t="s">
         <v>60</v>
@@ -4595,31 +4589,31 @@
         <v>105</v>
       </c>
       <c r="J25" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K25" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L25" t="s">
         <v>69</v>
       </c>
       <c r="M25" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N25" t="s">
         <v>108</v>
       </c>
       <c r="O25" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P25" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="R25" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="S25" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T25" t="s">
         <v>106</v>
@@ -4643,19 +4637,13 @@
         <v>118</v>
       </c>
       <c r="AA25" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AB25" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="AD25" t="s">
-        <v>89</v>
-      </c>
-      <c r="AE25" t="s">
-        <v>94</v>
-      </c>
-      <c r="AF25" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="AH25" t="s">
         <v>119</v>
@@ -4675,7 +4663,7 @@
         <v>60</v>
       </c>
       <c r="E26" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F26" t="s">
         <v>105</v>
@@ -4684,7 +4672,7 @@
         <v>69</v>
       </c>
       <c r="H26" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I26" t="s">
         <v>116</v>
@@ -4693,16 +4681,16 @@
         <v>108</v>
       </c>
       <c r="K26" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L26" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M26" t="s">
         <v>117</v>
       </c>
       <c r="N26" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O26" t="s">
         <v>108</v>
@@ -4720,16 +4708,16 @@
         <v>118</v>
       </c>
       <c r="U26" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="V26" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="W26" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="X26" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Y26" t="s">
         <v>113</v>
@@ -4743,25 +4731,22 @@
       <c r="AB26" t="s">
         <v>114</v>
       </c>
-      <c r="AE26" t="s">
-        <v>114</v>
-      </c>
-      <c r="AF26" t="s">
-        <v>121</v>
+      <c r="AD26" t="s">
+        <v>95</v>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>103</v>
       </c>
       <c r="B27" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C27" t="s">
         <v>104</v>
       </c>
       <c r="D27" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E27" t="s">
         <v>69</v>
@@ -4770,7 +4755,7 @@
         <v>69</v>
       </c>
       <c r="G27" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H27" t="s">
         <v>66</v>
@@ -4782,7 +4767,7 @@
         <v>106</v>
       </c>
       <c r="K27" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L27" t="s">
         <v>108</v>
@@ -4794,13 +4779,13 @@
         <v>106</v>
       </c>
       <c r="O27" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P27" t="s">
         <v>118</v>
       </c>
       <c r="R27" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="S27" t="s">
         <v>106</v>
@@ -4809,30 +4794,27 @@
         <v>120</v>
       </c>
       <c r="U27" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="V27" t="s">
         <v>106</v>
       </c>
       <c r="W27" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="X27" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Y27" t="s">
         <v>121</v>
       </c>
       <c r="Z27" t="s">
-        <v>94</v>
-      </c>
-      <c r="AF27" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B28" t="s">
         <v>112</v>
@@ -4847,10 +4829,10 @@
         <v>116</v>
       </c>
       <c r="F28" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G28" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H28" t="s">
         <v>103</v>
@@ -4865,7 +4847,7 @@
         <v>106</v>
       </c>
       <c r="L28" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M28" t="s">
         <v>61</v>
@@ -4880,10 +4862,10 @@
         <v>120</v>
       </c>
       <c r="R28" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="T28" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U28" t="s">
         <v>114</v>
@@ -4892,7 +4874,7 @@
         <v>113</v>
       </c>
       <c r="X28" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Y28" t="s">
         <v>119</v>
@@ -4915,16 +4897,16 @@
         <v>69</v>
       </c>
       <c r="E29" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F29" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G29" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H29" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I29" t="s">
         <v>113</v>
@@ -4939,42 +4921,45 @@
         <v>113</v>
       </c>
       <c r="M29" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N29" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O29" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P29" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="R29" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="T29" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="U29" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="V29" t="s">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>70</v>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>104</v>
       </c>
       <c r="B30" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C30" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D30" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E30" t="s">
         <v>108</v>
@@ -4986,34 +4971,37 @@
         <v>106</v>
       </c>
       <c r="H30" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I30" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J30" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K30" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="L30" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M30" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N30" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O30" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P30" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="T30" t="s">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="U30" t="s">
+        <v>113</v>
       </c>
       <c r="V30" t="s">
         <v>114</v>
@@ -5030,13 +5018,13 @@
         <v>61</v>
       </c>
       <c r="D31" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E31" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F31" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G31" t="s">
         <v>117</v>
@@ -5045,19 +5033,19 @@
         <v>108</v>
       </c>
       <c r="I31" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="J31" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K31" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L31" t="s">
         <v>121</v>
       </c>
       <c r="M31" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N31" t="s">
         <v>114</v>
@@ -5077,10 +5065,10 @@
         <v>60</v>
       </c>
       <c r="C32" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D32" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E32" t="s">
         <v>106</v>
@@ -5089,13 +5077,13 @@
         <v>106</v>
       </c>
       <c r="G32" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="H32" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I32" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="J32" t="s">
         <v>114</v>
@@ -5104,21 +5092,24 @@
         <v>121</v>
       </c>
       <c r="L32" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N32" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O32" t="s">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="P32" t="s">
+        <v>121</v>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B33" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C33" t="s">
         <v>105</v>
@@ -5136,7 +5127,7 @@
         <v>105</v>
       </c>
       <c r="H33" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5150,7 +5141,7 @@
         <v>69</v>
       </c>
       <c r="D34" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E34" t="s">
         <v>117</v>
@@ -5159,10 +5150,10 @@
         <v>61</v>
       </c>
       <c r="G34" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H34" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5173,13 +5164,13 @@
         <v>69</v>
       </c>
       <c r="C35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D35" t="s">
         <v>106</v>
       </c>
       <c r="E35" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F35" t="s">
         <v>114</v>
@@ -5190,27 +5181,27 @@
     </row>
     <row r="36" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B36" t="s">
         <v>116</v>
       </c>
       <c r="C36" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D36" t="s">
         <v>113</v>
       </c>
       <c r="E36" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F36" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B37" t="s">
         <v>103</v>
@@ -5219,7 +5210,7 @@
         <v>108</v>
       </c>
       <c r="D37" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -5230,7 +5221,7 @@
         <v>115</v>
       </c>
       <c r="C38" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D38" t="s">
         <v>120</v>
@@ -5238,16 +5229,16 @@
     </row>
     <row r="39" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B39" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C39" t="s">
         <v>106</v>
       </c>
       <c r="D39" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -5255,7 +5246,7 @@
         <v>106</v>
       </c>
       <c r="B40" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C40" t="s">
         <v>117</v>
@@ -5280,38 +5271,38 @@
     </row>
     <row r="42" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="B42" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C42" t="s">
         <v>118</v>
       </c>
       <c r="D42" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B43" t="s">
         <v>106</v>
       </c>
       <c r="C43" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B44" t="s">
         <v>113</v>
       </c>
       <c r="C44" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -5327,10 +5318,10 @@
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B46" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C46" t="s">
         <v>114</v>
@@ -5341,7 +5332,7 @@
         <v>119</v>
       </c>
       <c r="C47" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" spans="2:3" x14ac:dyDescent="0.25"/>
@@ -5498,13 +5489,13 @@
         <v>56</v>
       </c>
       <c r="I3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J3" t="s">
         <v>67</v>
       </c>
       <c r="K3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L3" t="s">
         <v>59</v>
@@ -5513,58 +5504,58 @@
         <v>58</v>
       </c>
       <c r="N3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q3" t="s">
         <v>65</v>
       </c>
       <c r="R3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="S3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T3" t="s">
         <v>64</v>
       </c>
       <c r="U3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="V3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="W3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="X3" t="s">
         <v>68</v>
       </c>
       <c r="Y3" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z3" t="s">
         <v>91</v>
       </c>
-      <c r="Z3" t="s">
-        <v>90</v>
-      </c>
       <c r="AA3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AB3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC3" t="s">
         <v>102</v>
       </c>
       <c r="AD3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AE3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF3" t="s">
         <v>100</v>
@@ -5573,13 +5564,13 @@
         <v>109</v>
       </c>
       <c r="AH3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AJ3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AK3" t="s">
         <v>107</v>
@@ -5594,7 +5585,7 @@
         <v>103</v>
       </c>
       <c r="AO3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AP3" t="s">
         <v>112</v>
@@ -5612,10 +5603,10 @@
         <v>111</v>
       </c>
       <c r="AU3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AV3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW3" t="s">
         <v>61</v>
@@ -5624,7 +5615,7 @@
         <v>60</v>
       </c>
       <c r="AY3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AZ3" t="s">
         <v>105</v>
@@ -5636,16 +5627,16 @@
         <v>116</v>
       </c>
       <c r="BC3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="BD3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="BE3" t="s">
         <v>108</v>
       </c>
       <c r="BF3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="BG3" t="s">
         <v>106</v>
@@ -5657,7 +5648,7 @@
         <v>113</v>
       </c>
       <c r="BJ3" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="BK3" t="s">
         <v>118</v>
@@ -5666,10 +5657,10 @@
         <v>120</v>
       </c>
       <c r="BM3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="BN3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="BO3" t="s">
         <v>121</v>
@@ -5678,7 +5669,7 @@
         <v>114</v>
       </c>
       <c r="BQ3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="BR3" t="s">
         <v>119</v>
@@ -6281,10 +6272,10 @@
         <v>25</v>
       </c>
       <c r="BF6" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="BG6" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="BH6" t="s">
         <v>9</v>
@@ -6305,7 +6296,7 @@
         <v>17</v>
       </c>
       <c r="BN6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BO6" t="s">
         <v>10</v>
@@ -6493,7 +6484,7 @@
         <v>15</v>
       </c>
       <c r="BF7" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="BG7" t="s">
         <v>4</v>
@@ -6517,7 +6508,7 @@
         <v>13</v>
       </c>
       <c r="BN7" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="BO7" t="s">
         <v>24</v>
@@ -7021,10 +7012,10 @@
         <v>10</v>
       </c>
       <c r="BI10" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="BJ10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="BM10" t="s">
         <v>20</v>
@@ -7033,7 +7024,7 @@
         <v>17</v>
       </c>
       <c r="BO10" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="BP10" t="s">
         <v>26</v>
@@ -7203,7 +7194,7 @@
         <v>23</v>
       </c>
       <c r="BO11" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="BP11" t="s">
         <v>27</v>
@@ -7626,7 +7617,7 @@
         <v>39</v>
       </c>
       <c r="BE14" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="BF14" t="s">
         <v>20</v>
@@ -7638,7 +7629,7 @@
         <v>8</v>
       </c>
       <c r="BJ14" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="BN14" t="s">
         <v>22</v>
@@ -7772,7 +7763,7 @@
         <v>29</v>
       </c>
       <c r="BE15" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="BF15" t="s">
         <v>38</v>
@@ -7784,7 +7775,7 @@
         <v>4</v>
       </c>
       <c r="BJ15" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="BN15" t="s">
         <v>9</v>
@@ -8171,7 +8162,7 @@
         <v>20</v>
       </c>
       <c r="BF18" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="BG18" t="s">
         <v>8</v>
@@ -8180,7 +8171,7 @@
         <v>26</v>
       </c>
       <c r="BN18" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="BP18" t="s">
         <v>20</v>
@@ -8302,7 +8293,7 @@
         <v>39</v>
       </c>
       <c r="BF19" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="BG19" t="s">
         <v>13</v>
@@ -8311,7 +8302,7 @@
         <v>27</v>
       </c>
       <c r="BN19" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="BP19" t="s">
         <v>13</v>
@@ -9044,7 +9035,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="57:69" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="15" customHeight="1" spans="66:69" x14ac:dyDescent="0.25"/>
     <row r="29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9176,13 +9167,13 @@
         <v>56</v>
       </c>
       <c r="I3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J3" t="s">
         <v>67</v>
       </c>
       <c r="K3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L3" t="s">
         <v>59</v>
@@ -9191,58 +9182,58 @@
         <v>58</v>
       </c>
       <c r="N3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q3" t="s">
         <v>65</v>
       </c>
       <c r="R3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="S3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T3" t="s">
         <v>64</v>
       </c>
       <c r="U3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="V3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="W3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="X3" t="s">
         <v>68</v>
       </c>
       <c r="Y3" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z3" t="s">
         <v>91</v>
       </c>
-      <c r="Z3" t="s">
-        <v>90</v>
-      </c>
       <c r="AA3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AB3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC3" t="s">
         <v>102</v>
       </c>
       <c r="AD3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AE3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF3" t="s">
         <v>100</v>
@@ -9251,13 +9242,13 @@
         <v>109</v>
       </c>
       <c r="AH3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AJ3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AK3" t="s">
         <v>107</v>
@@ -9272,7 +9263,7 @@
         <v>103</v>
       </c>
       <c r="AO3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AP3" t="s">
         <v>112</v>
@@ -9290,10 +9281,10 @@
         <v>111</v>
       </c>
       <c r="AU3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AV3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW3" t="s">
         <v>61</v>
@@ -9302,7 +9293,7 @@
         <v>60</v>
       </c>
       <c r="AY3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AZ3" t="s">
         <v>105</v>
@@ -9314,16 +9305,16 @@
         <v>116</v>
       </c>
       <c r="BC3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="BD3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="BE3" t="s">
         <v>108</v>
       </c>
       <c r="BF3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="BG3" t="s">
         <v>106</v>
@@ -9335,7 +9326,7 @@
         <v>113</v>
       </c>
       <c r="BJ3" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="BK3" t="s">
         <v>118</v>
@@ -9344,10 +9335,10 @@
         <v>120</v>
       </c>
       <c r="BM3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="BN3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="BO3" t="s">
         <v>121</v>
@@ -9356,7 +9347,7 @@
         <v>114</v>
       </c>
       <c r="BQ3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="BR3" t="s">
         <v>119</v>

--- a/data/ICEHLdelegacije.xlsx
+++ b/data/ICEHLdelegacije.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2978" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2982" uniqueCount="441">
   <si>
     <t>SmetanaLa</t>
   </si>
@@ -330,90 +330,93 @@
     <t>2024-12-01</t>
   </si>
   <si>
+    <t>2025-02-12</t>
+  </si>
+  <si>
+    <t>2024-11-16</t>
+  </si>
+  <si>
+    <t>2024-12-04</t>
+  </si>
+  <si>
+    <t>2024-12-13</t>
+  </si>
+  <si>
+    <t>2024-12-30</t>
+  </si>
+  <si>
+    <t>2025-01-12</t>
+  </si>
+  <si>
+    <t>2024-11-30</t>
+  </si>
+  <si>
+    <t>2025-01-08</t>
+  </si>
+  <si>
+    <t>2024-11-23</t>
+  </si>
+  <si>
+    <t>2024-12-03</t>
+  </si>
+  <si>
+    <t>2024-12-15</t>
+  </si>
+  <si>
+    <t>2024-12-07</t>
+  </si>
+  <si>
+    <t>2025-02-14</t>
+  </si>
+  <si>
+    <t>2025-01-17</t>
+  </si>
+  <si>
+    <t>2025-01-26</t>
+  </si>
+  <si>
+    <t>2024-12-14</t>
+  </si>
+  <si>
+    <t>2025-02-02</t>
+  </si>
+  <si>
+    <t>2024-12-10</t>
+  </si>
+  <si>
+    <t>2025-01-15</t>
+  </si>
+  <si>
+    <t>2025-01-21</t>
+  </si>
+  <si>
+    <t>2025-01-18</t>
+  </si>
+  <si>
+    <t>2025-02-13</t>
+  </si>
+  <si>
+    <t>2025-01-29</t>
+  </si>
+  <si>
+    <t>2025-01-22</t>
+  </si>
+  <si>
+    <t>2025-01-25</t>
+  </si>
+  <si>
+    <t>2025-02-16</t>
+  </si>
+  <si>
+    <t>2025-02-11</t>
+  </si>
+  <si>
+    <t>2025-02-19</t>
+  </si>
+  <si>
     <t>zbrisano</t>
   </si>
   <si>
-    <t>2024-11-16</t>
-  </si>
-  <si>
-    <t>2024-12-04</t>
-  </si>
-  <si>
-    <t>2024-12-13</t>
-  </si>
-  <si>
-    <t>2024-12-30</t>
-  </si>
-  <si>
-    <t>2025-02-12</t>
-  </si>
-  <si>
-    <t>2025-01-12</t>
-  </si>
-  <si>
-    <t>2024-11-30</t>
-  </si>
-  <si>
-    <t>2025-01-08</t>
-  </si>
-  <si>
-    <t>2024-11-23</t>
-  </si>
-  <si>
-    <t>2024-12-03</t>
-  </si>
-  <si>
-    <t>2024-12-15</t>
-  </si>
-  <si>
-    <t>2024-12-07</t>
-  </si>
-  <si>
-    <t>2025-01-17</t>
-  </si>
-  <si>
-    <t>2025-02-14</t>
-  </si>
-  <si>
-    <t>2025-01-26</t>
-  </si>
-  <si>
-    <t>2024-12-14</t>
-  </si>
-  <si>
-    <t>2025-02-02</t>
-  </si>
-  <si>
-    <t>2024-12-10</t>
-  </si>
-  <si>
-    <t>2025-01-15</t>
-  </si>
-  <si>
-    <t>2025-01-21</t>
-  </si>
-  <si>
-    <t>2025-01-18</t>
-  </si>
-  <si>
-    <t>2025-02-13</t>
-  </si>
-  <si>
-    <t>2025-01-29</t>
-  </si>
-  <si>
-    <t>2025-01-22</t>
-  </si>
-  <si>
-    <t>2025-01-25</t>
-  </si>
-  <si>
-    <t>2025-02-16</t>
-  </si>
-  <si>
-    <t>2025-02-11</t>
-  </si>
-  <si>
     <t>HuberAn</t>
   </si>
   <si>
@@ -654,6 +657,9 @@
     <t>Gabor Ocskay Eisarena;GroznikBo;HronskyTo;PuffWo;ZgoncGa</t>
   </si>
   <si>
+    <t>Eisarena Salzburg;OfnerCh;SmetanaLa;JedlickaPe;KoncDa</t>
+  </si>
+  <si>
     <t>Tiroler Wasserkraft Arena;NikolicMa;SeewaldEl;FleischmannLu;NotheggerDa</t>
   </si>
   <si>
@@ -828,7 +834,7 @@
     <t>Tiroler Wasserkraft Arena;SmetanaLa;SternatCh;RieckenSi;SeewaldJe</t>
   </si>
   <si>
-    <t>Eisarena Salzburg;FichtnerPa;SiegelSt;BedynekSe;Gatol-schafranekMa</t>
+    <t>Eisarena Salzburg;FichtnerPa;SchauerJa;BedynekSe;Gatol-schafranekMa</t>
   </si>
   <si>
     <t>Hala Tivoli;PiragicTr;ZrnicMi;HribarMa;SnojTa</t>
@@ -1131,7 +1137,7 @@
     <t>Eishalle Feldkirch;NikolicMa;SchauerJa;PardatscherUl;SparerDa</t>
   </si>
   <si>
-    <t>Merkur Eisstadion Graz;SternatCh;ZrnicMi;BärnthalerCh;NotheggerDa</t>
+    <t>Merkur Eisstadion Graz;SiegelSt;SternatCh;BärnthalerCh;NotheggerDa</t>
   </si>
   <si>
     <t>Eishalle Bruneck;BernekerTh;HuberAn;MartinFl;PardatscherUl</t>
@@ -1248,7 +1254,7 @@
     <t>Eishalle Asiago;GroznikBo;RezekGr;HribarMa;PuffWo</t>
   </si>
   <si>
-    <t>Hala Tivoli;OfnerCh;RezekGr;MuzsikNo;VacziDa</t>
+    <t>Hala Tivoli;RezekGr;ZrnicMi;MuzsikNo;VacziDa</t>
   </si>
   <si>
     <t>Eiswelle Bozen;OfnerCh;RezekGr;PuffWo;ZgoncGa</t>
@@ -1704,105 +1710,106 @@
     <col min="49" max="49" width="14.140625" customWidth="1"/>
     <col min="50" max="50" width="16" customWidth="1"/>
     <col min="51" max="51" width="20.140625" customWidth="1"/>
+    <col min="52" max="52" width="12" customWidth="1"/>
     <col min="53" max="53" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="14.45" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="2" ht="14.45" customHeight="1" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A2">
         <f>COUNTIF(A4:A97,"&lt;&gt;")</f>
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B2">
         <f>COUNTIF(B4:B95,"&lt;&gt;")</f>
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C2">
         <f>COUNTIF(C4:C96,"&lt;&gt;")</f>
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D2">
         <f>COUNTIF(D4:D94,"&lt;&gt;")</f>
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E2">
         <f>COUNTIF(E4:E98,"&lt;&gt;")</f>
+        <v>38</v>
+      </c>
+      <c r="F2">
+        <f>COUNTIF(F4:F99,"&lt;&gt;")</f>
         <v>35</v>
-      </c>
-      <c r="F2">
-        <f>COUNTIF(F4:F100,"&lt;&gt;")</f>
-        <v>34</v>
       </c>
       <c r="G2">
         <f>COUNTIF(G4:G100,"&lt;&gt;")</f>
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H2">
         <f>COUNTIF(H4:H100,"&lt;&gt;")</f>
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I2">
         <f>COUNTIF(I4:I97,"&lt;&gt;")</f>
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J2">
-        <f>COUNTIF(J4:J99,"&lt;&gt;")</f>
-        <v>30</v>
+        <f>COUNTIF(J4:J98,"&lt;&gt;")</f>
+        <v>31</v>
       </c>
       <c r="K2">
         <f>COUNTIF(K4:K99,"&lt;&gt;")</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L2">
         <f>COUNTIF(L4:L100,"&lt;&gt;")</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M2">
         <f>COUNTIF(M4:M97,"&lt;&gt;")</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N2">
         <f>COUNTIF(N4:N99,"&lt;&gt;")</f>
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="O2">
         <f>COUNTIF(O4:O100,"&lt;&gt;")</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="P2">
         <f>COUNTIF(P4:P98,"&lt;&gt;")</f>
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="Q2">
         <f>COUNTIF(Q4:Q100,"&lt;&gt;")</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="R2">
         <f>COUNTIF(R4:R98,"&lt;&gt;")</f>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="S2">
         <f>COUNTIF(S4:S100,"&lt;&gt;")</f>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="T2">
         <f>COUNTIF(T4:T98,"&lt;&gt;")</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="U2">
         <f>COUNTIF(U4:U100,"&lt;&gt;")</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="V2">
         <f>COUNTIF(V4:V100,"&lt;&gt;")</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="W2">
         <f>COUNTIF(W4:W99,"&lt;&gt;")</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="X2">
         <f>COUNTIF(X4:X99,"&lt;&gt;")</f>
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="Y2">
         <f>COUNTIF(Y4:Y99,"&lt;&gt;")</f>
@@ -1810,43 +1817,43 @@
       </c>
       <c r="Z2">
         <f>COUNTIF(Z4:Z95,"&lt;&gt;")</f>
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AA2">
         <f>COUNTIF(AA4:AA96,"&lt;&gt;")</f>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AB2">
         <f>COUNTIF(AB4:AB100,"&lt;&gt;")</f>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AC2">
         <f>COUNTIF(AC4:AC100,"&lt;&gt;")</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AD2">
         <f>COUNTIF(AD4:AD93,"&lt;&gt;")</f>
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AE2">
         <f>COUNTIF(AE4:AE92,"&lt;&gt;")</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AF2">
         <f>COUNTIF(AF4:AF87,"&lt;&gt;")</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AG2">
         <f>COUNTIF(AG4:AG100,"&lt;&gt;")</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AH2">
         <f>COUNTIF(AH4:AH97,"&lt;&gt;")</f>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AI2">
         <f>COUNTIF(AI4:AI94,"&lt;&gt;")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ2">
         <f>COUNTIF(AJ4:AJ97,"&lt;&gt;")</f>
@@ -1862,11 +1869,11 @@
       </c>
       <c r="AM2">
         <f>COUNTIF(AM4:AM98,"&lt;&gt;")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN2">
-        <f>COUNTIF(AN4:AN100,"&lt;&gt;")</f>
-        <v>15</v>
+        <f>COUNTIF(AN4:AN99,"&lt;&gt;")</f>
+        <v>16</v>
       </c>
       <c r="AO2">
         <f>COUNTIF(AO4:AO98,"&lt;&gt;")</f>
@@ -1874,15 +1881,15 @@
       </c>
       <c r="AP2">
         <f>COUNTIF(AP4:AP100,"&lt;&gt;")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ2">
-        <f>COUNTIF(AQ4:AQ99,"&lt;&gt;")</f>
+        <f>COUNTIF(AQ4:AQ98,"&lt;&gt;")</f>
         <v>8</v>
       </c>
       <c r="AR2">
         <f>COUNTIF(AR4:AR100,"&lt;&gt;")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS2">
         <f>COUNTIF(AS4:AS99,"&lt;&gt;")</f>
@@ -1894,6 +1901,26 @@
       </c>
       <c r="AU2">
         <f>COUNTIF(AU4:AU100,"&lt;&gt;")</f>
+        <v>1</v>
+      </c>
+      <c r="AV2">
+        <f t="shared" ref="AV2:AZ2" si="0">COUNTIF(AV4:AV100,"&lt;&gt;")</f>
+        <v>2</v>
+      </c>
+      <c r="AW2">
+        <f t="shared" ref="AW2:AZ2" si="1">COUNTIF(AW4:AW99,"&lt;&gt;")</f>
+        <v>2</v>
+      </c>
+      <c r="AX2">
+        <f t="shared" ref="AX2:AZ2" si="2">COUNTIF(AX4:AX100,"&lt;&gt;")</f>
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AZ2">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3305,11 +3332,8 @@
       <c r="AP12" t="s">
         <v>95</v>
       </c>
-      <c r="AQ12" t="s">
-        <v>109</v>
-      </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>66</v>
       </c>
@@ -3434,7 +3458,7 @@
         <v>100</v>
       </c>
       <c r="AP13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
@@ -3538,16 +3562,16 @@
         <v>102</v>
       </c>
       <c r="AH14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AI14" t="s">
         <v>107</v>
       </c>
       <c r="AJ14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AK14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AL14" t="s">
         <v>62</v>
@@ -3556,13 +3580,13 @@
         <v>100</v>
       </c>
       <c r="AN14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AO14" t="s">
         <v>61</v>
       </c>
       <c r="AP14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
@@ -3612,7 +3636,7 @@
         <v>102</v>
       </c>
       <c r="P15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q15" t="s">
         <v>102</v>
@@ -3725,7 +3749,7 @@
         <v>83</v>
       </c>
       <c r="K16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L16" t="s">
         <v>79</v>
@@ -3755,7 +3779,7 @@
         <v>79</v>
       </c>
       <c r="U16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="V16" t="s">
         <v>79</v>
@@ -3770,7 +3794,7 @@
         <v>90</v>
       </c>
       <c r="Z16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AA16" t="s">
         <v>68</v>
@@ -3809,7 +3833,7 @@
         <v>102</v>
       </c>
       <c r="AN16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
@@ -3838,16 +3862,16 @@
         <v>83</v>
       </c>
       <c r="I17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J17" t="s">
         <v>79</v>
       </c>
       <c r="K17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M17" t="s">
         <v>83</v>
@@ -3883,16 +3907,16 @@
         <v>102</v>
       </c>
       <c r="X17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Y17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Z17" t="s">
         <v>107</v>
       </c>
       <c r="AA17" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AB17" t="s">
         <v>85</v>
@@ -3907,7 +3931,7 @@
         <v>85</v>
       </c>
       <c r="AF17" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AG17" t="s">
         <v>99</v>
@@ -4002,7 +4026,7 @@
         <v>79</v>
       </c>
       <c r="X18" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Y18" t="s">
         <v>68</v>
@@ -4020,7 +4044,7 @@
         <v>68</v>
       </c>
       <c r="AD18" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AE18" t="s">
         <v>94</v>
@@ -4029,7 +4053,7 @@
         <v>78</v>
       </c>
       <c r="AG18" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AH18" t="s">
         <v>71</v>
@@ -4064,7 +4088,7 @@
         <v>89</v>
       </c>
       <c r="E19" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F19" t="s">
         <v>90</v>
@@ -4073,7 +4097,7 @@
         <v>90</v>
       </c>
       <c r="H19" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I19" t="s">
         <v>84</v>
@@ -4091,7 +4115,7 @@
         <v>68</v>
       </c>
       <c r="N19" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O19" t="s">
         <v>99</v>
@@ -4106,7 +4130,7 @@
         <v>107</v>
       </c>
       <c r="S19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="T19" t="s">
         <v>85</v>
@@ -4121,7 +4145,7 @@
         <v>99</v>
       </c>
       <c r="X19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Y19" t="s">
         <v>85</v>
@@ -4160,13 +4184,13 @@
         <v>95</v>
       </c>
       <c r="AK19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AL19" t="s">
         <v>100</v>
       </c>
       <c r="AN19" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
@@ -4231,7 +4255,7 @@
         <v>62</v>
       </c>
       <c r="U20" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="V20" t="s">
         <v>62</v>
@@ -4273,7 +4297,7 @@
         <v>95</v>
       </c>
       <c r="AI20" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AJ20" t="s">
         <v>72</v>
@@ -4282,13 +4306,10 @@
         <v>117</v>
       </c>
       <c r="AL20" t="s">
-        <v>110</v>
-      </c>
-      <c r="AN20" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>89</v>
       </c>
@@ -4296,10 +4317,10 @@
         <v>102</v>
       </c>
       <c r="C21" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D21" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E21" t="s">
         <v>99</v>
@@ -4308,7 +4329,7 @@
         <v>76</v>
       </c>
       <c r="G21" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H21" t="s">
         <v>99</v>
@@ -4326,13 +4347,13 @@
         <v>107</v>
       </c>
       <c r="M21" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N21" t="s">
         <v>68</v>
       </c>
       <c r="O21" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P21" t="s">
         <v>62</v>
@@ -4389,7 +4410,7 @@
         <v>108</v>
       </c>
       <c r="AH21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AI21" t="s">
         <v>72</v>
@@ -4398,7 +4419,7 @@
         <v>62</v>
       </c>
       <c r="AK21" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AL21" t="s">
         <v>117</v>
@@ -4418,7 +4439,7 @@
         <v>79</v>
       </c>
       <c r="E22" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F22" t="s">
         <v>68</v>
@@ -4481,7 +4502,7 @@
         <v>95</v>
       </c>
       <c r="Z22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AA22" t="s">
         <v>117</v>
@@ -4492,14 +4513,11 @@
       <c r="AC22" t="s">
         <v>71</v>
       </c>
-      <c r="AD22" t="s">
-        <v>104</v>
-      </c>
       <c r="AE22" t="s">
         <v>96</v>
       </c>
       <c r="AF22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AG22" t="s">
         <v>95</v>
@@ -4511,7 +4529,7 @@
         <v>96</v>
       </c>
       <c r="AJ22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
@@ -4552,10 +4570,10 @@
         <v>62</v>
       </c>
       <c r="M23" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="N23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O23" t="s">
         <v>62</v>
@@ -4564,7 +4582,7 @@
         <v>108</v>
       </c>
       <c r="Q23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R23" t="s">
         <v>108</v>
@@ -4573,7 +4591,7 @@
         <v>94</v>
       </c>
       <c r="T23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="U23" t="s">
         <v>71</v>
@@ -4588,7 +4606,7 @@
         <v>106</v>
       </c>
       <c r="Y23" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Z23" t="s">
         <v>86</v>
@@ -4600,28 +4618,25 @@
         <v>100</v>
       </c>
       <c r="AC23" t="s">
-        <v>112</v>
-      </c>
-      <c r="AD23" t="s">
+        <v>111</v>
+      </c>
+      <c r="AE23" t="s">
+        <v>118</v>
+      </c>
+      <c r="AF23" t="s">
         <v>104</v>
       </c>
-      <c r="AE23" t="s">
-        <v>119</v>
-      </c>
-      <c r="AF23" t="s">
+      <c r="AG23" t="s">
         <v>109</v>
       </c>
-      <c r="AG23" t="s">
-        <v>110</v>
-      </c>
       <c r="AH23" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AI23" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AJ23" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
@@ -4629,16 +4644,16 @@
         <v>79</v>
       </c>
       <c r="B24" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C24" t="s">
         <v>106</v>
       </c>
       <c r="D24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E24" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F24" t="s">
         <v>85</v>
@@ -4671,7 +4686,7 @@
         <v>108</v>
       </c>
       <c r="P24" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q24" t="s">
         <v>96</v>
@@ -4698,10 +4713,10 @@
         <v>95</v>
       </c>
       <c r="Y24" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Z24" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AA24" t="s">
         <v>62</v>
@@ -4710,16 +4725,13 @@
         <v>117</v>
       </c>
       <c r="AC24" t="s">
-        <v>110</v>
-      </c>
-      <c r="AD24" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="AE24" t="s">
         <v>72</v>
       </c>
       <c r="AF24" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AG24" t="s">
         <v>91</v>
@@ -4728,7 +4740,7 @@
         <v>96</v>
       </c>
       <c r="AI24" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
@@ -4772,7 +4784,7 @@
         <v>95</v>
       </c>
       <c r="N25" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O25" t="s">
         <v>86</v>
@@ -4781,7 +4793,7 @@
         <v>86</v>
       </c>
       <c r="Q25" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="R25" t="s">
         <v>95</v>
@@ -4790,46 +4802,43 @@
         <v>95</v>
       </c>
       <c r="T25" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="U25" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="V25" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="W25" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="X25" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Y25" t="s">
+        <v>122</v>
+      </c>
+      <c r="Z25" t="s">
         <v>123</v>
       </c>
-      <c r="Z25" t="s">
+      <c r="AA25" t="s">
         <v>124</v>
-      </c>
-      <c r="AA25" t="s">
-        <v>125</v>
       </c>
       <c r="AB25" t="s">
         <v>72</v>
       </c>
       <c r="AC25" t="s">
-        <v>121</v>
-      </c>
-      <c r="AD25" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="AE25" t="s">
         <v>63</v>
       </c>
       <c r="AG25" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH25" t="s">
         <v>126</v>
-      </c>
-      <c r="AH25" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
@@ -4837,10 +4846,10 @@
         <v>103</v>
       </c>
       <c r="B26" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C26" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D26" t="s">
         <v>61</v>
@@ -4858,10 +4867,10 @@
         <v>94</v>
       </c>
       <c r="I26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J26" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K26" t="s">
         <v>86</v>
@@ -4870,25 +4879,25 @@
         <v>95</v>
       </c>
       <c r="M26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N26" t="s">
         <v>100</v>
       </c>
       <c r="O26" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P26" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="R26" t="s">
         <v>117</v>
       </c>
       <c r="S26" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="T26" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="U26" t="s">
         <v>100</v>
@@ -4906,19 +4915,19 @@
         <v>117</v>
       </c>
       <c r="Z26" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AA26" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AB26" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC26" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AE26" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AG26" t="s">
         <v>101</v>
@@ -4953,43 +4962,43 @@
         <v>68</v>
       </c>
       <c r="I27" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J27" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K27" t="s">
         <v>100</v>
       </c>
       <c r="L27" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="M27" t="s">
         <v>117</v>
       </c>
       <c r="N27" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="O27" t="s">
         <v>100</v>
       </c>
       <c r="P27" t="s">
+        <v>123</v>
+      </c>
+      <c r="R27" t="s">
         <v>124</v>
       </c>
-      <c r="R27" t="s">
-        <v>125</v>
-      </c>
       <c r="S27" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T27" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U27" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="V27" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="W27" t="s">
         <v>91</v>
@@ -4998,25 +5007,25 @@
         <v>96</v>
       </c>
       <c r="Y27" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Z27" t="s">
         <v>96</v>
       </c>
       <c r="AA27" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AB27" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AC27" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AE27" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AH27" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
@@ -5024,16 +5033,16 @@
         <v>99</v>
       </c>
       <c r="B28" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D28" t="s">
         <v>108</v>
       </c>
       <c r="E28" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F28" t="s">
         <v>84</v>
@@ -5045,13 +5054,13 @@
         <v>106</v>
       </c>
       <c r="I28" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J28" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K28" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L28" t="s">
         <v>100</v>
@@ -5066,7 +5075,7 @@
         <v>117</v>
       </c>
       <c r="P28" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="R28" t="s">
         <v>96</v>
@@ -5078,7 +5087,7 @@
         <v>78</v>
       </c>
       <c r="U28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="V28" t="s">
         <v>117</v>
@@ -5090,19 +5099,19 @@
         <v>91</v>
       </c>
       <c r="Y28" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Z28" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AA28" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AB28" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AH28" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
@@ -5110,10 +5119,10 @@
         <v>68</v>
       </c>
       <c r="B29" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C29" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D29" t="s">
         <v>71</v>
@@ -5137,16 +5146,16 @@
         <v>117</v>
       </c>
       <c r="K29" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L29" t="s">
         <v>117</v>
       </c>
       <c r="M29" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N29" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="O29" t="s">
         <v>85</v>
@@ -5158,7 +5167,7 @@
         <v>91</v>
       </c>
       <c r="S29" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="T29" t="s">
         <v>96</v>
@@ -5170,10 +5179,10 @@
         <v>96</v>
       </c>
       <c r="W29" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X29" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Y29" t="s">
         <v>72</v>
@@ -5182,10 +5191,10 @@
         <v>63</v>
       </c>
       <c r="AA29" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AB29" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -5202,13 +5211,13 @@
         <v>99</v>
       </c>
       <c r="E30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H30" t="s">
         <v>86</v>
@@ -5238,10 +5247,10 @@
         <v>91</v>
       </c>
       <c r="R30" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="S30" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="T30" t="s">
         <v>91</v>
@@ -5250,24 +5259,24 @@
         <v>117</v>
       </c>
       <c r="V30" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="W30" t="s">
         <v>101</v>
       </c>
       <c r="X30" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="Y30" t="s">
         <v>63</v>
       </c>
       <c r="Z30" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B31" t="s">
         <v>62</v>
@@ -5285,58 +5294,58 @@
         <v>100</v>
       </c>
       <c r="G31" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H31" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I31" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J31" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="K31" t="s">
         <v>96</v>
       </c>
       <c r="L31" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M31" t="s">
         <v>91</v>
       </c>
       <c r="N31" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O31" t="s">
+        <v>128</v>
+      </c>
+      <c r="P31" t="s">
+        <v>109</v>
+      </c>
+      <c r="R31" t="s">
+        <v>118</v>
+      </c>
+      <c r="S31" t="s">
         <v>129</v>
-      </c>
-      <c r="P31" t="s">
-        <v>110</v>
-      </c>
-      <c r="R31" t="s">
-        <v>119</v>
-      </c>
-      <c r="S31" t="s">
-        <v>130</v>
       </c>
       <c r="T31" t="s">
         <v>63</v>
       </c>
       <c r="U31" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V31" t="s">
         <v>64</v>
       </c>
       <c r="X31" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="Y31" t="s">
         <v>64</v>
       </c>
       <c r="Z31" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
@@ -5353,10 +5362,10 @@
         <v>86</v>
       </c>
       <c r="E32" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F32" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G32" t="s">
         <v>72</v>
@@ -5368,10 +5377,10 @@
         <v>100</v>
       </c>
       <c r="J32" t="s">
-        <v>119</v>
+        <v>63</v>
       </c>
       <c r="K32" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L32" t="s">
         <v>91</v>
@@ -5386,25 +5395,28 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
+        <v>128</v>
+      </c>
+      <c r="R32" t="s">
+        <v>104</v>
+      </c>
+      <c r="T32" t="s">
+        <v>120</v>
+      </c>
+      <c r="U32" t="s">
         <v>129</v>
       </c>
-      <c r="R32" t="s">
-        <v>109</v>
-      </c>
-      <c r="T32" t="s">
-        <v>121</v>
-      </c>
-      <c r="U32" t="s">
-        <v>130</v>
-      </c>
       <c r="V32" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="X32" t="s">
-        <v>130</v>
+        <v>129</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>131</v>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>94</v>
       </c>
@@ -5415,7 +5427,7 @@
         <v>108</v>
       </c>
       <c r="D33" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E33" t="s">
         <v>117</v>
@@ -5433,34 +5445,37 @@
         <v>91</v>
       </c>
       <c r="J33" t="s">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="K33" t="s">
         <v>63</v>
       </c>
       <c r="L33" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="M33" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="N33" t="s">
         <v>63</v>
       </c>
       <c r="O33" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="P33" t="s">
         <v>63</v>
       </c>
       <c r="R33" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="T33" t="s">
-        <v>125</v>
+        <v>124</v>
+      </c>
+      <c r="V33" t="s">
+        <v>129</v>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>108</v>
       </c>
@@ -5474,7 +5489,7 @@
         <v>100</v>
       </c>
       <c r="E34" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F34" t="s">
         <v>62</v>
@@ -5486,34 +5501,34 @@
         <v>91</v>
       </c>
       <c r="I34" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="J34" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="K34" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="L34" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="M34" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="N34" t="s">
         <v>64</v>
       </c>
       <c r="O34" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="P34" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="R34" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="T34" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -5527,34 +5542,31 @@
         <v>95</v>
       </c>
       <c r="D35" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E35" t="s">
         <v>96</v>
       </c>
       <c r="F35" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="G35" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H35" t="s">
         <v>63</v>
       </c>
       <c r="I35" t="s">
-        <v>118</v>
-      </c>
-      <c r="J35" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="N35" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="P35" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="T35" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -5562,7 +5574,7 @@
         <v>95</v>
       </c>
       <c r="B36" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C36" t="s">
         <v>86</v>
@@ -5574,19 +5586,19 @@
         <v>91</v>
       </c>
       <c r="F36" t="s">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="G36" t="s">
         <v>63</v>
       </c>
       <c r="H36" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N36" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="P36" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -5597,7 +5609,7 @@
         <v>106</v>
       </c>
       <c r="C37" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D37" t="s">
         <v>72</v>
@@ -5606,42 +5618,45 @@
         <v>63</v>
       </c>
       <c r="F37" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="G37" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H37" t="s">
+        <v>118</v>
+      </c>
+      <c r="N37" t="s">
+        <v>116</v>
+      </c>
+      <c r="P37" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>111</v>
+      </c>
+      <c r="B38" t="s">
         <v>119</v>
-      </c>
-      <c r="N37" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>112</v>
-      </c>
-      <c r="B38" t="s">
-        <v>120</v>
       </c>
       <c r="C38" t="s">
         <v>100</v>
       </c>
       <c r="D38" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E38" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F38" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="G38" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="H38" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5652,45 +5667,42 @@
         <v>95</v>
       </c>
       <c r="C39" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D39" t="s">
         <v>96</v>
       </c>
       <c r="E39" t="s">
-        <v>131</v>
-      </c>
-      <c r="F39" t="s">
         <v>130</v>
       </c>
       <c r="G39" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H39" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B40" t="s">
         <v>86</v>
       </c>
       <c r="C40" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D40" t="s">
+        <v>128</v>
+      </c>
+      <c r="E40" t="s">
+        <v>104</v>
+      </c>
+      <c r="G40" t="s">
         <v>129</v>
       </c>
-      <c r="E40" t="s">
-        <v>109</v>
-      </c>
-      <c r="G40" t="s">
-        <v>130</v>
-      </c>
       <c r="H40" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5698,19 +5710,19 @@
         <v>117</v>
       </c>
       <c r="B41" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C41" t="s">
         <v>117</v>
       </c>
       <c r="D41" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E41" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H41" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5721,7 +5733,7 @@
         <v>100</v>
       </c>
       <c r="C42" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D42" t="s">
         <v>91</v>
@@ -5729,13 +5741,13 @@
     </row>
     <row r="43" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B43" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C43" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D43" t="s">
         <v>63</v>
@@ -5757,16 +5769,16 @@
     </row>
     <row r="45" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B45" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C45" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D45" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -5777,10 +5789,10 @@
         <v>91</v>
       </c>
       <c r="C46" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D46" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -5788,13 +5800,13 @@
         <v>63</v>
       </c>
       <c r="B47" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C47" t="s">
         <v>91</v>
       </c>
       <c r="D47" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -5810,10 +5822,10 @@
     </row>
     <row r="49" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B49" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C49" t="s">
         <v>64</v>
@@ -5821,36 +5833,43 @@
     </row>
     <row r="50" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B50" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C50" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B51" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C51" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>131</v>
+      </c>
       <c r="B52" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C52" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
-    <row r="53" ht="15" customHeight="1" spans="2:3" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C53" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="54" ht="15" customHeight="1" spans="3:3" x14ac:dyDescent="0.25"/>
     <row r="55" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="56" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="57" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5939,7 +5958,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:CA42"/>
+  <dimension ref="A3:CB42"/>
   <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="17.85546875" customWidth="1"/>
@@ -5972,7 +5991,7 @@
     <col min="98" max="98" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>52</v>
       </c>
@@ -6070,7 +6089,7 @@
         <v>102</v>
       </c>
       <c r="AG3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AH3" t="s">
         <v>83</v>
@@ -6082,13 +6101,13 @@
         <v>90</v>
       </c>
       <c r="AK3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AL3" t="s">
         <v>103</v>
       </c>
       <c r="AM3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AN3" t="s">
         <v>106</v>
@@ -6097,7 +6116,7 @@
         <v>99</v>
       </c>
       <c r="AP3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AQ3" t="s">
         <v>68</v>
@@ -6106,10 +6125,10 @@
         <v>107</v>
       </c>
       <c r="AS3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AT3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AU3" t="s">
         <v>78</v>
@@ -6133,7 +6152,7 @@
         <v>71</v>
       </c>
       <c r="BB3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="BC3" t="s">
         <v>95</v>
@@ -6142,16 +6161,16 @@
         <v>86</v>
       </c>
       <c r="BE3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BF3" t="s">
         <v>100</v>
       </c>
       <c r="BG3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="BH3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BI3" t="s">
         <v>117</v>
@@ -6160,28 +6179,28 @@
         <v>72</v>
       </c>
       <c r="BK3" t="s">
+        <v>123</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BM3" t="s">
         <v>124</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>128</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>125</v>
       </c>
       <c r="BN3" t="s">
         <v>96</v>
       </c>
       <c r="BO3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="BP3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="BQ3" t="s">
         <v>91</v>
       </c>
       <c r="BR3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BS3" t="s">
         <v>63</v>
@@ -6190,28 +6209,31 @@
         <v>64</v>
       </c>
       <c r="BU3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="BV3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="BW3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="BX3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="BY3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="BZ3" t="s">
         <v>101</v>
       </c>
       <c r="CA3" t="s">
-        <v>130</v>
+        <v>129</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>131</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -6234,7 +6256,7 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I4" t="s">
         <v>0</v>
@@ -6252,7 +6274,7 @@
         <v>12</v>
       </c>
       <c r="N4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O4" t="s">
         <v>14</v>
@@ -6273,7 +6295,7 @@
         <v>2</v>
       </c>
       <c r="U4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="V4" t="s">
         <v>12</v>
@@ -6449,8 +6471,11 @@
       <c r="CA4" t="s">
         <v>5</v>
       </c>
+      <c r="CB4" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -6688,8 +6713,11 @@
       <c r="CA5" t="s">
         <v>19</v>
       </c>
+      <c r="CB5" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -6927,8 +6955,11 @@
       <c r="CA6" t="s">
         <v>23</v>
       </c>
+      <c r="CB6" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -7166,8 +7197,11 @@
       <c r="CA7" t="s">
         <v>4</v>
       </c>
+      <c r="CB7" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -7540,7 +7574,7 @@
         <v>3</v>
       </c>
       <c r="CA9" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:79" x14ac:dyDescent="0.25">
@@ -7954,7 +7988,7 @@
         <v>28</v>
       </c>
       <c r="T12" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="V12" t="s">
         <v>1</v>
@@ -8595,7 +8629,7 @@
         <v>34</v>
       </c>
       <c r="R16" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="T16" t="s">
         <v>19</v>
@@ -8706,7 +8740,7 @@
         <v>6</v>
       </c>
       <c r="CA16" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:79" x14ac:dyDescent="0.25">
@@ -8852,7 +8886,7 @@
         <v>21</v>
       </c>
       <c r="CA17" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:79" x14ac:dyDescent="0.25">
@@ -9260,12 +9294,12 @@
         <v>5</v>
       </c>
       <c r="CA20" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C21" t="s">
         <v>7</v>
@@ -9376,7 +9410,7 @@
         <v>28</v>
       </c>
       <c r="CA21" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" spans="1:79" x14ac:dyDescent="0.25">
@@ -9931,7 +9965,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="77:77" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9953,7 +9987,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:CA1898"/>
+  <dimension ref="A3:CB1898"/>
   <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="55.28515625" customWidth="1"/>
@@ -10037,7 +10071,7 @@
     <col min="99" max="99" width="47.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>52</v>
       </c>
@@ -10135,7 +10169,7 @@
         <v>102</v>
       </c>
       <c r="AG3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AH3" t="s">
         <v>83</v>
@@ -10147,13 +10181,13 @@
         <v>90</v>
       </c>
       <c r="AK3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AL3" t="s">
         <v>103</v>
       </c>
       <c r="AM3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AN3" t="s">
         <v>106</v>
@@ -10162,7 +10196,7 @@
         <v>99</v>
       </c>
       <c r="AP3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AQ3" t="s">
         <v>68</v>
@@ -10171,10 +10205,10 @@
         <v>107</v>
       </c>
       <c r="AS3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AT3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AU3" t="s">
         <v>78</v>
@@ -10198,7 +10232,7 @@
         <v>71</v>
       </c>
       <c r="BB3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="BC3" t="s">
         <v>95</v>
@@ -10207,16 +10241,16 @@
         <v>86</v>
       </c>
       <c r="BE3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BF3" t="s">
         <v>100</v>
       </c>
       <c r="BG3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="BH3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BI3" t="s">
         <v>117</v>
@@ -10225,28 +10259,28 @@
         <v>72</v>
       </c>
       <c r="BK3" t="s">
+        <v>123</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BM3" t="s">
         <v>124</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>128</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>125</v>
       </c>
       <c r="BN3" t="s">
         <v>96</v>
       </c>
       <c r="BO3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="BP3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="BQ3" t="s">
         <v>91</v>
       </c>
       <c r="BR3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BS3" t="s">
         <v>63</v>
@@ -10255,975 +10289,981 @@
         <v>64</v>
       </c>
       <c r="BU3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="BV3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="BW3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="BX3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="BY3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="BZ3" t="s">
         <v>101</v>
       </c>
       <c r="CA3" t="s">
-        <v>130</v>
+        <v>129</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>131</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="R4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="S4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="T4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="U4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="V4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="W4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="X4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Z4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AA4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AB4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AC4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AD4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AE4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AF4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AH4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AI4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AJ4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AK4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AL4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AM4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AN4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AO4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AP4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AQ4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AR4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AS4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AT4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AU4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AV4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AW4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AX4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AY4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AZ4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="BA4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="BB4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="BC4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="BD4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BE4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="BF4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="BG4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="BH4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BI4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="BJ4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="BK4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="BL4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="BM4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="BN4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="BO4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="BP4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="BQ4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="BR4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="BS4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="BT4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="BU4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="BV4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="BW4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="BX4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="BY4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="BZ4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="CA4" t="s">
-        <v>211</v>
+        <v>212</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>213</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="G5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="J5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="L5" t="s">
+        <v>222</v>
+      </c>
+      <c r="M5" t="s">
+        <v>223</v>
+      </c>
+      <c r="O5" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>225</v>
+      </c>
+      <c r="R5" t="s">
+        <v>226</v>
+      </c>
+      <c r="T5" t="s">
+        <v>227</v>
+      </c>
+      <c r="V5" t="s">
+        <v>228</v>
+      </c>
+      <c r="W5" t="s">
+        <v>229</v>
+      </c>
+      <c r="X5" t="s">
+        <v>230</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>231</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>234</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>235</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>236</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>237</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>238</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>239</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>240</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>241</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>242</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>243</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>244</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>244</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>245</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>246</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>244</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>247</v>
+      </c>
+      <c r="AU5" t="s">
         <v>220</v>
       </c>
-      <c r="M5" t="s">
-        <v>221</v>
-      </c>
-      <c r="O5" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>223</v>
-      </c>
-      <c r="R5" t="s">
-        <v>224</v>
-      </c>
-      <c r="T5" t="s">
-        <v>225</v>
-      </c>
-      <c r="V5" t="s">
-        <v>226</v>
-      </c>
-      <c r="W5" t="s">
-        <v>227</v>
-      </c>
-      <c r="X5" t="s">
-        <v>228</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>229</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>230</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>231</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>232</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>233</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>234</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>235</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>236</v>
-      </c>
-      <c r="AH5" t="s">
-        <v>237</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>238</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>239</v>
-      </c>
-      <c r="AK5" t="s">
-        <v>240</v>
-      </c>
-      <c r="AL5" t="s">
-        <v>241</v>
-      </c>
-      <c r="AN5" t="s">
-        <v>242</v>
-      </c>
-      <c r="AO5" t="s">
-        <v>242</v>
-      </c>
-      <c r="AQ5" t="s">
-        <v>243</v>
-      </c>
-      <c r="AR5" t="s">
-        <v>244</v>
-      </c>
-      <c r="AS5" t="s">
-        <v>242</v>
-      </c>
-      <c r="AT5" t="s">
-        <v>245</v>
-      </c>
-      <c r="AU5" t="s">
-        <v>218</v>
-      </c>
       <c r="AV5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AW5" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AX5" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AY5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AZ5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BA5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BC5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="BD5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="BE5" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="BF5" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="BG5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="BH5" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="BI5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="BJ5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="BM5" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="BN5" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="BO5" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="BP5" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="BQ5" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="BS5" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="BT5" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="BU5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="BW5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="BY5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="CA5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C6" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H6" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="J6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="K6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="M6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q6" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="R6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="T6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="V6" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="W6" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="X6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Z6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AA6" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AB6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AD6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AE6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AF6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AH6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AI6" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AJ6" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AK6" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AL6" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AN6" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AO6" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AQ6" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AR6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AS6" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AT6" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AU6" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AV6" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AW6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AX6" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AY6" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AZ6" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="BA6" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="BC6" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="BD6" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="BE6" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="BF6" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="BG6" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="BI6" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="BJ6" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="BN6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="BP6" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="BQ6" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="BS6" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="BU6" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="BW6" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="BY6" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="CA6" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C7" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E7" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F7" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H7" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="J7" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K7" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="M7" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="O7" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q7" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="R7" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="T7" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="V7" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="X7" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Z7" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AA7" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AB7" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AD7" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AE7" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AF7" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AH7" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AI7" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AJ7" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AN7" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AO7" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AQ7" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AR7" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AU7" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AV7" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AW7" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AX7" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AY7" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AZ7" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="BA7" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="BC7" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="BD7" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="BE7" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="BF7" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="BG7" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="BI7" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="BN7" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="BP7" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="BQ7" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="BS7" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="BU7" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="BW7" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="BY7" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="CA7" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C8" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F8" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H8" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="K8" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="O8" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Q8" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="R8" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="T8" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="X8" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AA8" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AB8" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AE8" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AF8" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AH8" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AI8" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AJ8" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AN8" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AO8" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AQ8" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AR8" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AU8" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AV8" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AW8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AX8" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AY8" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AZ8" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="BA8" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="BC8" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="BD8" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="BE8" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="BF8" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="BG8" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="BI8" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="BN8" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="BQ8" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="BS8" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="BW8" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="BY8" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="CA8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E9" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="F9" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="H9" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="O9" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="T9" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="X9" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AB9" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AF9" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AI9" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AJ9" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AO9" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AV9" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AW9" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AX9" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AY9" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AZ9" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="BA9" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="BC9" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="BD9" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="BE9" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="BF9" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="BG9" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="BN9" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="BQ9" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="BY9" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="41:77" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="41:49" x14ac:dyDescent="0.25">
       <c r="AO10" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AW10" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/data/ICEHLdelegacije.xlsx
+++ b/data/ICEHLdelegacije.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3078" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3283" uniqueCount="483">
   <si>
     <t>SmetanaLa</t>
   </si>
@@ -417,12 +417,36 @@
     <t>2025-02-16</t>
   </si>
   <si>
+    <t>2025-03-02</t>
+  </si>
+  <si>
     <t>2025-02-19</t>
   </si>
   <si>
+    <t>2025-02-28</t>
+  </si>
+  <si>
+    <t>2025-03-09</t>
+  </si>
+  <si>
     <t>2025-02-11</t>
   </si>
   <si>
+    <t>2025-03-04</t>
+  </si>
+  <si>
+    <t>2025-03-11</t>
+  </si>
+  <si>
+    <t>2025-03-07</t>
+  </si>
+  <si>
+    <t>2025-03-06</t>
+  </si>
+  <si>
+    <t>2025-03-08</t>
+  </si>
+  <si>
     <t>zbrisano</t>
   </si>
   <si>
@@ -678,6 +702,30 @@
     <t>Eishalle Wien-Kagran;PiragicTr;SmetanaLa;BedynekSe;DurmisOt</t>
   </si>
   <si>
+    <t>Gabor Ocskay Eisarena;OfnerCh;SternatCh;DurmisOt;RieckenSi</t>
+  </si>
+  <si>
+    <t>Eisarena Salzburg;PiragicTr;ZrnicMi;NotheggerDa;ZgoncGa</t>
+  </si>
+  <si>
+    <t>Merkur Eisstadion Graz;SeewaldEl;SternatCh;BedynekSe;RieckenSi</t>
+  </si>
+  <si>
+    <t>Linz AG Eisarena;FichtnerPa;ZrnicMi;NotheggerDa;ZgoncGa</t>
+  </si>
+  <si>
+    <t>Eisarena Salzburg;HronskyTo;SternatCh;DurmisOt;KoncDa</t>
+  </si>
+  <si>
+    <t>Merkur Eisstadion Graz;Huber aAn;NikolicMa;NotheggerDa;PuffWo</t>
+  </si>
+  <si>
+    <t>Stadthalle Villach;FichtnerPa;ZrnicMi;BärnthalerCh;RieckenSi</t>
+  </si>
+  <si>
+    <t>Heidi Horten Arena Klagenfurt;FichtnerPa;SmetanaLa;BärnthalerCh;RieckenSi</t>
+  </si>
+  <si>
     <t>Tiroler Wasserkraft Arena;NikolicMa;SeewaldEl;FleischmannLu;NotheggerDa</t>
   </si>
   <si>
@@ -864,6 +912,21 @@
     <t>Eishalle Bruneck;Huber aAn;NikolicKr;MantovaniDa;PardatscherUl</t>
   </si>
   <si>
+    <t>Linz AG Eisarena;HronskyTo;SmetanaLa;KoncDa;PuffWo</t>
+  </si>
+  <si>
+    <t>Stadthalle Villach;Huber aAn;NikolicMa;BärnthalerCh;PuffWo</t>
+  </si>
+  <si>
+    <t>Heidi Horten Arena Klagenfurt;Huber aAn;NikolicMa;BedynekSe;MantovaniDa</t>
+  </si>
+  <si>
+    <t>Gabor Ocskay Eisarena;SmetanaLa;SternatCh;DurmisOt;MuzsikNo</t>
+  </si>
+  <si>
+    <t>Linz AG Eisarena;HronskyTo;OfnerCh;DurmisOt;KoncDa</t>
+  </si>
+  <si>
     <t>Hala Tivoli;PiragicTr;ZrnicMi;HribarMa;SnojTa</t>
   </si>
   <si>
@@ -1026,6 +1089,21 @@
     <t>Heidi Horten Arena Klagenfurt;OfnerCh;ZrnicMi;PuffWo;ZgoncGa</t>
   </si>
   <si>
+    <t>Heidi Horten Arena Klagenfurt;OfnerCh;SternatCh;BärnthalerCh;MuzsikNo</t>
+  </si>
+  <si>
+    <t>Gabor Ocskay Eisarena;FichtnerPa;OfnerCh;DurmisOt;MuzsikNo</t>
+  </si>
+  <si>
+    <t>Sparkasse Arena Bozen;OfnerCh;SmetanaLa;PardatscherUl;RieckenSi</t>
+  </si>
+  <si>
+    <t>Eishalle Bruneck;NikolicKr;OfnerCh;MantovaniDa;PardatscherUl</t>
+  </si>
+  <si>
+    <t>Eisarena Salzburg;NikolicMa;NikolicKr;BedynekSe;NotheggerDa</t>
+  </si>
+  <si>
     <t>Eishalle Wien-Kagran;HronskyTo;SmetanaLa;DurmisOt;WeissAl</t>
   </si>
   <si>
@@ -1171,6 +1249,15 @@
   </si>
   <si>
     <t>Stadthalle Villach;NikolicMa;PiragicTr;MuzsikNo;VacziDa</t>
+  </si>
+  <si>
+    <t>Sparkasse Arena Bozen;NikolicKr;SeewaldEl;MantovaniDa;PardatscherUl</t>
+  </si>
+  <si>
+    <t>Eishalle Bruneck;PiragicTr;ZrnicMi;PardatscherUl;ZgoncGa</t>
+  </si>
+  <si>
+    <t>Sparkasse Arena Bozen;PiragicTr;SternatCh;MantovaniDa;ZgoncGa</t>
   </si>
   <si>
     <t>Eishalle Bruneck;BernekerTh;HuberAn;MartinFl;PardatscherUl</t>
@@ -5087,8 +5174,11 @@
       <c r="AG27" t="s">
         <v>130</v>
       </c>
+      <c r="AH27" t="s">
+        <v>133</v>
+      </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>100</v>
       </c>
@@ -5171,13 +5261,19 @@
         <v>117</v>
       </c>
       <c r="AB28" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AC28" t="s">
         <v>117</v>
       </c>
+      <c r="AG28" t="s">
+        <v>135</v>
+      </c>
+      <c r="AH28" t="s">
+        <v>136</v>
+      </c>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -5239,7 +5335,7 @@
         <v>91</v>
       </c>
       <c r="U29" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="V29" t="s">
         <v>63</v>
@@ -5265,8 +5361,14 @@
       <c r="AC29" t="s">
         <v>130</v>
       </c>
+      <c r="AG29" t="s">
+        <v>138</v>
+      </c>
+      <c r="AH29" t="s">
+        <v>139</v>
+      </c>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>108</v>
       </c>
@@ -5348,8 +5450,17 @@
       <c r="AA30" t="s">
         <v>109</v>
       </c>
+      <c r="AB30" t="s">
+        <v>133</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG30" t="s">
+        <v>140</v>
+      </c>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>120</v>
       </c>
@@ -5422,8 +5533,20 @@
       <c r="X31" t="s">
         <v>64</v>
       </c>
+      <c r="Z31" t="s">
+        <v>133</v>
+      </c>
+      <c r="AB31" t="s">
+        <v>141</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>140</v>
+      </c>
+      <c r="AG31" t="s">
+        <v>136</v>
+      </c>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>61</v>
       </c>
@@ -5488,13 +5611,25 @@
         <v>132</v>
       </c>
       <c r="V32" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="W32" t="s">
         <v>109</v>
       </c>
+      <c r="Z32" t="s">
+        <v>138</v>
+      </c>
+      <c r="AB32" t="s">
+        <v>142</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>142</v>
+      </c>
+      <c r="AG32" t="s">
+        <v>139</v>
+      </c>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>94</v>
       </c>
@@ -5561,8 +5696,17 @@
       <c r="V33" t="s">
         <v>109</v>
       </c>
+      <c r="W33" t="s">
+        <v>133</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>136</v>
+      </c>
+      <c r="AB33" t="s">
+        <v>139</v>
+      </c>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>107</v>
       </c>
@@ -5620,8 +5764,14 @@
       <c r="S34" t="s">
         <v>109</v>
       </c>
+      <c r="U34" t="s">
+        <v>133</v>
+      </c>
+      <c r="W34" t="s">
+        <v>138</v>
+      </c>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>71</v>
       </c>
@@ -5650,7 +5800,7 @@
         <v>104</v>
       </c>
       <c r="J35" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K35" t="s">
         <v>104</v>
@@ -5665,7 +5815,7 @@
         <v>109</v>
       </c>
       <c r="O35" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="P35" t="s">
         <v>109</v>
@@ -5676,8 +5826,14 @@
       <c r="R35" t="s">
         <v>109</v>
       </c>
+      <c r="U35" t="s">
+        <v>138</v>
+      </c>
+      <c r="W35" t="s">
+        <v>136</v>
+      </c>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>95</v>
       </c>
@@ -5720,11 +5876,20 @@
       <c r="O36" t="s">
         <v>130</v>
       </c>
+      <c r="Q36" t="s">
+        <v>138</v>
+      </c>
       <c r="R36" t="s">
         <v>130</v>
       </c>
+      <c r="U36" t="s">
+        <v>142</v>
+      </c>
+      <c r="W36" t="s">
+        <v>139</v>
+      </c>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>85</v>
       </c>
@@ -5752,11 +5917,29 @@
       <c r="I37" t="s">
         <v>117</v>
       </c>
+      <c r="J37" t="s">
+        <v>133</v>
+      </c>
+      <c r="K37" t="s">
+        <v>133</v>
+      </c>
       <c r="L37" t="s">
         <v>129</v>
       </c>
+      <c r="N37" t="s">
+        <v>133</v>
+      </c>
+      <c r="O37" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>141</v>
+      </c>
+      <c r="R37" t="s">
+        <v>138</v>
+      </c>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>112</v>
       </c>
@@ -5773,7 +5956,7 @@
         <v>121</v>
       </c>
       <c r="F38" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G38" t="s">
         <v>104</v>
@@ -5784,8 +5967,29 @@
       <c r="I38" t="s">
         <v>129</v>
       </c>
+      <c r="J38" t="s">
+        <v>138</v>
+      </c>
+      <c r="K38" t="s">
+        <v>140</v>
+      </c>
+      <c r="L38" t="s">
+        <v>133</v>
+      </c>
+      <c r="N38" t="s">
+        <v>138</v>
+      </c>
+      <c r="O38" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>136</v>
+      </c>
+      <c r="R38" t="s">
+        <v>140</v>
+      </c>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>99</v>
       </c>
@@ -5799,7 +6003,7 @@
         <v>96</v>
       </c>
       <c r="E39" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F39" t="s">
         <v>104</v>
@@ -5807,8 +6011,29 @@
       <c r="G39" t="s">
         <v>117</v>
       </c>
+      <c r="I39" t="s">
+        <v>135</v>
+      </c>
+      <c r="K39" t="s">
+        <v>139</v>
+      </c>
+      <c r="L39" t="s">
+        <v>140</v>
+      </c>
+      <c r="N39" t="s">
+        <v>140</v>
+      </c>
+      <c r="O39" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>139</v>
+      </c>
+      <c r="R39" t="s">
+        <v>139</v>
+      </c>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>110</v>
       </c>
@@ -5830,8 +6055,20 @@
       <c r="G40" t="s">
         <v>132</v>
       </c>
+      <c r="I40" t="s">
+        <v>138</v>
+      </c>
+      <c r="L40" t="s">
+        <v>139</v>
+      </c>
+      <c r="N40" t="s">
+        <v>136</v>
+      </c>
+      <c r="O40" t="s">
+        <v>139</v>
+      </c>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>118</v>
       </c>
@@ -5853,8 +6090,11 @@
       <c r="G41" t="s">
         <v>109</v>
       </c>
+      <c r="I41" t="s">
+        <v>140</v>
+      </c>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>72</v>
       </c>
@@ -5876,8 +6116,11 @@
       <c r="G42" t="s">
         <v>129</v>
       </c>
+      <c r="I42" t="s">
+        <v>136</v>
+      </c>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>125</v>
       </c>
@@ -5893,8 +6136,17 @@
       <c r="E43" t="s">
         <v>129</v>
       </c>
+      <c r="F43" t="s">
+        <v>133</v>
+      </c>
+      <c r="G43" t="s">
+        <v>138</v>
+      </c>
+      <c r="I43" t="s">
+        <v>139</v>
+      </c>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>96</v>
       </c>
@@ -5907,8 +6159,17 @@
       <c r="D44" t="s">
         <v>64</v>
       </c>
+      <c r="E44" t="s">
+        <v>133</v>
+      </c>
+      <c r="F44" t="s">
+        <v>138</v>
+      </c>
+      <c r="G44" t="s">
+        <v>140</v>
+      </c>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>119</v>
       </c>
@@ -5921,8 +6182,17 @@
       <c r="D45" t="s">
         <v>104</v>
       </c>
+      <c r="E45" t="s">
+        <v>138</v>
+      </c>
+      <c r="F45" t="s">
+        <v>141</v>
+      </c>
+      <c r="G45" t="s">
+        <v>142</v>
+      </c>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>91</v>
       </c>
@@ -5935,8 +6205,17 @@
       <c r="D46" t="s">
         <v>117</v>
       </c>
+      <c r="E46" t="s">
+        <v>141</v>
+      </c>
+      <c r="F46" t="s">
+        <v>136</v>
+      </c>
+      <c r="G46" t="s">
+        <v>139</v>
+      </c>
     </row>
-    <row r="47" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>63</v>
       </c>
@@ -5949,8 +6228,11 @@
       <c r="D47" t="s">
         <v>132</v>
       </c>
+      <c r="E47" t="s">
+        <v>139</v>
+      </c>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>64</v>
       </c>
@@ -5983,13 +6265,16 @@
         <v>127</v>
       </c>
       <c r="B50" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C50" t="s">
         <v>104</v>
       </c>
+      <c r="D50" t="s">
+        <v>135</v>
+      </c>
     </row>
-    <row r="51" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>117</v>
       </c>
@@ -5999,10 +6284,13 @@
       <c r="C51" t="s">
         <v>117</v>
       </c>
+      <c r="D51" t="s">
+        <v>133</v>
+      </c>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B52" t="s">
         <v>117</v>
@@ -6010,8 +6298,11 @@
       <c r="C52" t="s">
         <v>109</v>
       </c>
+      <c r="D52" t="s">
+        <v>138</v>
+      </c>
     </row>
-    <row r="53" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>109</v>
       </c>
@@ -6021,21 +6312,74 @@
       <c r="C53" t="s">
         <v>129</v>
       </c>
+      <c r="D53" t="s">
+        <v>140</v>
+      </c>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>130</v>
       </c>
       <c r="B54" t="s">
         <v>130</v>
       </c>
+      <c r="C54" t="s">
+        <v>135</v>
+      </c>
+      <c r="D54" t="s">
+        <v>136</v>
+      </c>
     </row>
-    <row r="55" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>133</v>
+      </c>
+      <c r="B55" t="s">
+        <v>133</v>
+      </c>
+      <c r="C55" t="s">
+        <v>133</v>
+      </c>
+      <c r="D55" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="56" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>140</v>
+      </c>
+      <c r="B56" t="s">
+        <v>138</v>
+      </c>
+      <c r="C56" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="57" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>136</v>
+      </c>
+      <c r="B57" t="s">
+        <v>139</v>
+      </c>
+      <c r="C57" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>139</v>
+      </c>
+      <c r="C58" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="59" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C59" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="60" ht="15" customHeight="1" spans="3:3" x14ac:dyDescent="0.25"/>
     <row r="61" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="62" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="63" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6118,7 +6462,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:CE42"/>
+  <dimension ref="A3:CM42"/>
   <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="17.85546875" customWidth="1"/>
@@ -6151,7 +6495,7 @@
     <col min="98" max="98" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>52</v>
       </c>
@@ -6372,7 +6716,7 @@
         <v>121</v>
       </c>
       <c r="BV3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="BW3" t="s">
         <v>104</v>
@@ -6390,7 +6734,7 @@
         <v>132</v>
       </c>
       <c r="CB3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="CC3" t="s">
         <v>109</v>
@@ -6401,8 +6745,32 @@
       <c r="CE3" t="s">
         <v>130</v>
       </c>
+      <c r="CF3" t="s">
+        <v>135</v>
+      </c>
+      <c r="CG3" t="s">
+        <v>133</v>
+      </c>
+      <c r="CH3" t="s">
+        <v>138</v>
+      </c>
+      <c r="CI3" t="s">
+        <v>141</v>
+      </c>
+      <c r="CJ3" t="s">
+        <v>140</v>
+      </c>
+      <c r="CK3" t="s">
+        <v>142</v>
+      </c>
+      <c r="CL3" t="s">
+        <v>136</v>
+      </c>
+      <c r="CM3" t="s">
+        <v>139</v>
+      </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -6425,7 +6793,7 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="I4" t="s">
         <v>0</v>
@@ -6443,7 +6811,7 @@
         <v>9</v>
       </c>
       <c r="N4" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="O4" t="s">
         <v>16</v>
@@ -6464,7 +6832,7 @@
         <v>2</v>
       </c>
       <c r="U4" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="V4" t="s">
         <v>9</v>
@@ -6652,8 +7020,32 @@
       <c r="CE4" t="s">
         <v>1</v>
       </c>
+      <c r="CF4" t="s">
+        <v>2</v>
+      </c>
+      <c r="CG4" t="s">
+        <v>1</v>
+      </c>
+      <c r="CH4" t="s">
+        <v>9</v>
+      </c>
+      <c r="CI4" t="s">
+        <v>16</v>
+      </c>
+      <c r="CJ4" t="s">
+        <v>11</v>
+      </c>
+      <c r="CK4" t="s">
+        <v>28</v>
+      </c>
+      <c r="CL4" t="s">
+        <v>16</v>
+      </c>
+      <c r="CM4" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -6903,8 +7295,32 @@
       <c r="CE5" t="s">
         <v>0</v>
       </c>
+      <c r="CF5" t="s">
+        <v>3</v>
+      </c>
+      <c r="CG5" t="s">
+        <v>5</v>
+      </c>
+      <c r="CH5" t="s">
+        <v>3</v>
+      </c>
+      <c r="CI5" t="s">
+        <v>5</v>
+      </c>
+      <c r="CJ5" t="s">
+        <v>3</v>
+      </c>
+      <c r="CK5" t="s">
+        <v>6</v>
+      </c>
+      <c r="CL5" t="s">
+        <v>5</v>
+      </c>
+      <c r="CM5" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -7154,8 +7570,32 @@
       <c r="CE6" t="s">
         <v>17</v>
       </c>
+      <c r="CF6" t="s">
+        <v>32</v>
+      </c>
+      <c r="CG6" t="s">
+        <v>27</v>
+      </c>
+      <c r="CH6" t="s">
+        <v>17</v>
+      </c>
+      <c r="CI6" t="s">
+        <v>27</v>
+      </c>
+      <c r="CJ6" t="s">
+        <v>32</v>
+      </c>
+      <c r="CK6" t="s">
+        <v>27</v>
+      </c>
+      <c r="CL6" t="s">
+        <v>22</v>
+      </c>
+      <c r="CM6" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -7405,8 +7845,32 @@
       <c r="CE7" t="s">
         <v>32</v>
       </c>
+      <c r="CF7" t="s">
+        <v>8</v>
+      </c>
+      <c r="CG7" t="s">
+        <v>4</v>
+      </c>
+      <c r="CH7" t="s">
+        <v>8</v>
+      </c>
+      <c r="CI7" t="s">
+        <v>4</v>
+      </c>
+      <c r="CJ7" t="s">
+        <v>10</v>
+      </c>
+      <c r="CK7" t="s">
+        <v>20</v>
+      </c>
+      <c r="CL7" t="s">
+        <v>8</v>
+      </c>
+      <c r="CM7" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -7602,8 +8066,23 @@
       <c r="CE8" t="s">
         <v>28</v>
       </c>
+      <c r="CG8" t="s">
+        <v>11</v>
+      </c>
+      <c r="CH8" t="s">
+        <v>28</v>
+      </c>
+      <c r="CJ8" t="s">
+        <v>28</v>
+      </c>
+      <c r="CL8" t="s">
+        <v>0</v>
+      </c>
+      <c r="CM8" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -7799,8 +8278,23 @@
       <c r="CE9" t="s">
         <v>33</v>
       </c>
+      <c r="CG9" t="s">
+        <v>0</v>
+      </c>
+      <c r="CH9" t="s">
+        <v>6</v>
+      </c>
+      <c r="CJ9" t="s">
+        <v>6</v>
+      </c>
+      <c r="CL9" t="s">
+        <v>3</v>
+      </c>
+      <c r="CM9" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>42</v>
       </c>
@@ -7996,8 +8490,23 @@
       <c r="CE10" t="s">
         <v>14</v>
       </c>
+      <c r="CG10" t="s">
+        <v>10</v>
+      </c>
+      <c r="CH10" t="s">
+        <v>22</v>
+      </c>
+      <c r="CJ10" t="s">
+        <v>17</v>
+      </c>
+      <c r="CL10" t="s">
+        <v>32</v>
+      </c>
+      <c r="CM10" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -8193,8 +8702,23 @@
       <c r="CE11" t="s">
         <v>13</v>
       </c>
+      <c r="CG11" t="s">
+        <v>20</v>
+      </c>
+      <c r="CH11" t="s">
+        <v>20</v>
+      </c>
+      <c r="CJ11" t="s">
+        <v>14</v>
+      </c>
+      <c r="CL11" t="s">
+        <v>25</v>
+      </c>
+      <c r="CM11" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>1</v>
       </c>
@@ -8229,7 +8753,7 @@
         <v>29</v>
       </c>
       <c r="T12" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="V12" t="s">
         <v>1</v>
@@ -8357,8 +8881,23 @@
       <c r="CC12" t="s">
         <v>2</v>
       </c>
+      <c r="CG12" t="s">
+        <v>2</v>
+      </c>
+      <c r="CH12" t="s">
+        <v>16</v>
+      </c>
+      <c r="CJ12" t="s">
+        <v>2</v>
+      </c>
+      <c r="CL12" t="s">
+        <v>33</v>
+      </c>
+      <c r="CM12" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -8521,8 +9060,23 @@
       <c r="CC13" t="s">
         <v>5</v>
       </c>
+      <c r="CG13" t="s">
+        <v>3</v>
+      </c>
+      <c r="CH13" t="s">
+        <v>2</v>
+      </c>
+      <c r="CJ13" t="s">
+        <v>0</v>
+      </c>
+      <c r="CL13" t="s">
+        <v>2</v>
+      </c>
+      <c r="CM13" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -8685,8 +9239,23 @@
       <c r="CC14" t="s">
         <v>20</v>
       </c>
+      <c r="CG14" t="s">
+        <v>22</v>
+      </c>
+      <c r="CH14" t="s">
+        <v>32</v>
+      </c>
+      <c r="CJ14" t="s">
+        <v>13</v>
+      </c>
+      <c r="CL14" t="s">
+        <v>14</v>
+      </c>
+      <c r="CM14" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>48</v>
       </c>
@@ -8849,8 +9418,23 @@
       <c r="CC15" t="s">
         <v>4</v>
       </c>
+      <c r="CG15" t="s">
+        <v>25</v>
+      </c>
+      <c r="CH15" t="s">
+        <v>25</v>
+      </c>
+      <c r="CJ15" t="s">
+        <v>8</v>
+      </c>
+      <c r="CL15" t="s">
+        <v>13</v>
+      </c>
+      <c r="CM15" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -8882,7 +9466,7 @@
         <v>33</v>
       </c>
       <c r="R16" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="T16" t="s">
         <v>11</v>
@@ -8998,8 +9582,17 @@
       <c r="CC16" t="s">
         <v>6</v>
       </c>
+      <c r="CG16" t="s">
+        <v>33</v>
+      </c>
+      <c r="CH16" t="s">
+        <v>1</v>
+      </c>
+      <c r="CM16" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>0</v>
       </c>
@@ -9147,8 +9740,17 @@
       <c r="CC17" t="s">
         <v>1</v>
       </c>
+      <c r="CG17" t="s">
+        <v>9</v>
+      </c>
+      <c r="CH17" t="s">
+        <v>5</v>
+      </c>
+      <c r="CM17" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>32</v>
       </c>
@@ -9296,8 +9898,17 @@
       <c r="CC18" t="s">
         <v>25</v>
       </c>
+      <c r="CG18" t="s">
+        <v>14</v>
+      </c>
+      <c r="CH18" t="s">
+        <v>13</v>
+      </c>
+      <c r="CM18" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>37</v>
       </c>
@@ -9445,8 +10056,17 @@
       <c r="CC19" t="s">
         <v>26</v>
       </c>
+      <c r="CG19" t="s">
+        <v>13</v>
+      </c>
+      <c r="CH19" t="s">
+        <v>4</v>
+      </c>
+      <c r="CM19" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>30</v>
       </c>
@@ -9567,7 +10187,7 @@
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="C21" t="s">
         <v>5</v>
@@ -10276,7 +10896,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:CE1898"/>
+  <dimension ref="A3:CM1898"/>
   <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="55.28515625" customWidth="1"/>
@@ -10360,7 +10980,7 @@
     <col min="99" max="99" width="47.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>52</v>
       </c>
@@ -10581,7 +11201,7 @@
         <v>121</v>
       </c>
       <c r="BV3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="BW3" t="s">
         <v>104</v>
@@ -10599,7 +11219,7 @@
         <v>132</v>
       </c>
       <c r="CB3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="CC3" t="s">
         <v>109</v>
@@ -10610,988 +11230,1075 @@
       <c r="CE3" t="s">
         <v>130</v>
       </c>
+      <c r="CF3" t="s">
+        <v>135</v>
+      </c>
+      <c r="CG3" t="s">
+        <v>133</v>
+      </c>
+      <c r="CH3" t="s">
+        <v>138</v>
+      </c>
+      <c r="CI3" t="s">
+        <v>141</v>
+      </c>
+      <c r="CJ3" t="s">
+        <v>140</v>
+      </c>
+      <c r="CK3" t="s">
+        <v>142</v>
+      </c>
+      <c r="CL3" t="s">
+        <v>136</v>
+      </c>
+      <c r="CM3" t="s">
+        <v>139</v>
+      </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B4" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="C4" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="D4" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="E4" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="F4" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="G4" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="H4" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="I4" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="J4" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="K4" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="L4" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="M4" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="N4" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="O4" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="P4" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="Q4" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="R4" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="S4" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="T4" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="U4" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="V4" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="W4" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="X4" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="Y4" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="Z4" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="AA4" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="AB4" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="AC4" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="AD4" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="AE4" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="AF4" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="AG4" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="AH4" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="AI4" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="AJ4" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="AK4" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="AL4" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="AM4" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="AN4" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="AO4" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="AP4" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="AQ4" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="AR4" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="AS4" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="AT4" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="AU4" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="AV4" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="AW4" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="AX4" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="AY4" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="AZ4" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="BA4" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="BB4" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="BC4" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="BD4" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="BE4" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="BF4" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="BG4" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="BH4" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="BI4" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="BJ4" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="BK4" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="BL4" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="BM4" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="BN4" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="BO4" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="BP4" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="BQ4" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="BR4" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="BS4" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="BT4" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="BU4" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="BV4" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="BW4" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="BX4" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="BY4" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="BZ4" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="CA4" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="CB4" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="CC4" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="CD4" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="CE4" t="s">
-        <v>219</v>
+        <v>227</v>
+      </c>
+      <c r="CF4" t="s">
+        <v>228</v>
+      </c>
+      <c r="CG4" t="s">
+        <v>229</v>
+      </c>
+      <c r="CH4" t="s">
+        <v>230</v>
+      </c>
+      <c r="CI4" t="s">
+        <v>231</v>
+      </c>
+      <c r="CJ4" t="s">
+        <v>232</v>
+      </c>
+      <c r="CK4" t="s">
+        <v>233</v>
+      </c>
+      <c r="CL4" t="s">
+        <v>234</v>
+      </c>
+      <c r="CM4" t="s">
+        <v>235</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="C5" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="E5" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="F5" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="G5" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="H5" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="J5" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="K5" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="L5" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="M5" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="O5" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="Q5" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="R5" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="T5" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="V5" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="W5" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="X5" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="Y5" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="Z5" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="AA5" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="AB5" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="AC5" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="AD5" t="s">
+        <v>258</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>259</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>260</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>261</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>262</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>263</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>264</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>265</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>266</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>266</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>267</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>268</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>266</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>269</v>
+      </c>
+      <c r="AU5" t="s">
         <v>242</v>
       </c>
-      <c r="AE5" t="s">
-        <v>243</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>244</v>
-      </c>
-      <c r="AH5" t="s">
-        <v>245</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>246</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>247</v>
-      </c>
-      <c r="AK5" t="s">
-        <v>248</v>
-      </c>
-      <c r="AL5" t="s">
-        <v>249</v>
-      </c>
-      <c r="AN5" t="s">
-        <v>250</v>
-      </c>
-      <c r="AO5" t="s">
-        <v>250</v>
-      </c>
-      <c r="AQ5" t="s">
-        <v>251</v>
-      </c>
-      <c r="AR5" t="s">
-        <v>252</v>
-      </c>
-      <c r="AS5" t="s">
-        <v>250</v>
-      </c>
-      <c r="AT5" t="s">
-        <v>253</v>
-      </c>
-      <c r="AU5" t="s">
-        <v>226</v>
-      </c>
       <c r="AV5" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="AW5" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="AX5" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="AY5" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="AZ5" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="BA5" t="s">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="BC5" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="BD5" t="s">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="BE5" t="s">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="BF5" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="BG5" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="BH5" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="BI5" t="s">
+        <v>282</v>
+      </c>
+      <c r="BJ5" t="s">
+        <v>283</v>
+      </c>
+      <c r="BM5" t="s">
+        <v>284</v>
+      </c>
+      <c r="BN5" t="s">
+        <v>285</v>
+      </c>
+      <c r="BO5" t="s">
+        <v>286</v>
+      </c>
+      <c r="BP5" t="s">
+        <v>287</v>
+      </c>
+      <c r="BQ5" t="s">
+        <v>288</v>
+      </c>
+      <c r="BS5" t="s">
+        <v>289</v>
+      </c>
+      <c r="BT5" t="s">
+        <v>290</v>
+      </c>
+      <c r="BU5" t="s">
+        <v>291</v>
+      </c>
+      <c r="BW5" t="s">
+        <v>292</v>
+      </c>
+      <c r="BY5" t="s">
+        <v>293</v>
+      </c>
+      <c r="CA5" t="s">
+        <v>294</v>
+      </c>
+      <c r="CC5" t="s">
+        <v>295</v>
+      </c>
+      <c r="CD5" t="s">
+        <v>296</v>
+      </c>
+      <c r="CE5" t="s">
+        <v>297</v>
+      </c>
+      <c r="CG5" t="s">
+        <v>298</v>
+      </c>
+      <c r="CH5" t="s">
+        <v>299</v>
+      </c>
+      <c r="CJ5" t="s">
+        <v>300</v>
+      </c>
+      <c r="CL5" t="s">
+        <v>301</v>
+      </c>
+      <c r="CM5" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>303</v>
+      </c>
+      <c r="C6" t="s">
+        <v>304</v>
+      </c>
+      <c r="E6" t="s">
+        <v>305</v>
+      </c>
+      <c r="F6" t="s">
+        <v>306</v>
+      </c>
+      <c r="H6" t="s">
+        <v>307</v>
+      </c>
+      <c r="J6" t="s">
+        <v>308</v>
+      </c>
+      <c r="K6" t="s">
+        <v>309</v>
+      </c>
+      <c r="M6" t="s">
+        <v>310</v>
+      </c>
+      <c r="O6" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>312</v>
+      </c>
+      <c r="R6" t="s">
+        <v>313</v>
+      </c>
+      <c r="T6" t="s">
+        <v>314</v>
+      </c>
+      <c r="V6" t="s">
+        <v>315</v>
+      </c>
+      <c r="W6" t="s">
+        <v>316</v>
+      </c>
+      <c r="X6" t="s">
+        <v>317</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>318</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>319</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>320</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>321</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>322</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>323</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>324</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>325</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>326</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>327</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>328</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>329</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>330</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>331</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>332</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>333</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>334</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>335</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>336</v>
+      </c>
+      <c r="AW6" t="s">
         <v>266</v>
       </c>
-      <c r="BJ5" t="s">
-        <v>267</v>
-      </c>
-      <c r="BM5" t="s">
-        <v>268</v>
-      </c>
-      <c r="BN5" t="s">
-        <v>269</v>
-      </c>
-      <c r="BO5" t="s">
-        <v>270</v>
-      </c>
-      <c r="BP5" t="s">
-        <v>271</v>
-      </c>
-      <c r="BQ5" t="s">
-        <v>272</v>
-      </c>
-      <c r="BS5" t="s">
-        <v>273</v>
-      </c>
-      <c r="BT5" t="s">
-        <v>274</v>
-      </c>
-      <c r="BU5" t="s">
-        <v>275</v>
-      </c>
-      <c r="BW5" t="s">
-        <v>276</v>
-      </c>
-      <c r="BY5" t="s">
-        <v>277</v>
-      </c>
-      <c r="CA5" t="s">
-        <v>278</v>
-      </c>
-      <c r="CC5" t="s">
-        <v>279</v>
-      </c>
-      <c r="CD5" t="s">
-        <v>280</v>
-      </c>
-      <c r="CE5" t="s">
-        <v>281</v>
+      <c r="AX6" t="s">
+        <v>337</v>
+      </c>
+      <c r="AY6" t="s">
+        <v>338</v>
+      </c>
+      <c r="AZ6" t="s">
+        <v>339</v>
+      </c>
+      <c r="BA6" t="s">
+        <v>340</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>341</v>
+      </c>
+      <c r="BD6" t="s">
+        <v>342</v>
+      </c>
+      <c r="BE6" t="s">
+        <v>343</v>
+      </c>
+      <c r="BF6" t="s">
+        <v>344</v>
+      </c>
+      <c r="BG6" t="s">
+        <v>345</v>
+      </c>
+      <c r="BI6" t="s">
+        <v>346</v>
+      </c>
+      <c r="BJ6" t="s">
+        <v>347</v>
+      </c>
+      <c r="BN6" t="s">
+        <v>348</v>
+      </c>
+      <c r="BP6" t="s">
+        <v>349</v>
+      </c>
+      <c r="BQ6" t="s">
+        <v>350</v>
+      </c>
+      <c r="BS6" t="s">
+        <v>351</v>
+      </c>
+      <c r="BU6" t="s">
+        <v>352</v>
+      </c>
+      <c r="BW6" t="s">
+        <v>353</v>
+      </c>
+      <c r="BY6" t="s">
+        <v>354</v>
+      </c>
+      <c r="CA6" t="s">
+        <v>355</v>
+      </c>
+      <c r="CC6" t="s">
+        <v>356</v>
+      </c>
+      <c r="CG6" t="s">
+        <v>357</v>
+      </c>
+      <c r="CH6" t="s">
+        <v>358</v>
+      </c>
+      <c r="CJ6" t="s">
+        <v>359</v>
+      </c>
+      <c r="CL6" t="s">
+        <v>360</v>
+      </c>
+      <c r="CM6" t="s">
+        <v>361</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:83" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>282</v>
-      </c>
-      <c r="C6" t="s">
-        <v>283</v>
-      </c>
-      <c r="E6" t="s">
-        <v>284</v>
-      </c>
-      <c r="F6" t="s">
-        <v>285</v>
-      </c>
-      <c r="H6" t="s">
-        <v>286</v>
-      </c>
-      <c r="J6" t="s">
-        <v>287</v>
-      </c>
-      <c r="K6" t="s">
-        <v>288</v>
-      </c>
-      <c r="M6" t="s">
-        <v>289</v>
-      </c>
-      <c r="O6" t="s">
-        <v>290</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>291</v>
-      </c>
-      <c r="R6" t="s">
-        <v>292</v>
-      </c>
-      <c r="T6" t="s">
-        <v>293</v>
-      </c>
-      <c r="V6" t="s">
-        <v>294</v>
-      </c>
-      <c r="W6" t="s">
-        <v>295</v>
-      </c>
-      <c r="X6" t="s">
-        <v>296</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>297</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>298</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>299</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>300</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>301</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>302</v>
-      </c>
-      <c r="AH6" t="s">
-        <v>303</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>304</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>305</v>
-      </c>
-      <c r="AK6" t="s">
-        <v>306</v>
-      </c>
-      <c r="AL6" t="s">
-        <v>307</v>
-      </c>
-      <c r="AN6" t="s">
-        <v>308</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>309</v>
-      </c>
-      <c r="AQ6" t="s">
-        <v>310</v>
-      </c>
-      <c r="AR6" t="s">
-        <v>311</v>
-      </c>
-      <c r="AS6" t="s">
-        <v>312</v>
-      </c>
-      <c r="AT6" t="s">
-        <v>313</v>
-      </c>
-      <c r="AU6" t="s">
-        <v>314</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>315</v>
-      </c>
-      <c r="AW6" t="s">
-        <v>250</v>
-      </c>
-      <c r="AX6" t="s">
-        <v>316</v>
-      </c>
-      <c r="AY6" t="s">
-        <v>317</v>
-      </c>
-      <c r="AZ6" t="s">
-        <v>318</v>
-      </c>
-      <c r="BA6" t="s">
-        <v>319</v>
-      </c>
-      <c r="BC6" t="s">
-        <v>320</v>
-      </c>
-      <c r="BD6" t="s">
-        <v>321</v>
-      </c>
-      <c r="BE6" t="s">
-        <v>322</v>
-      </c>
-      <c r="BF6" t="s">
-        <v>323</v>
-      </c>
-      <c r="BG6" t="s">
-        <v>324</v>
-      </c>
-      <c r="BI6" t="s">
-        <v>325</v>
-      </c>
-      <c r="BJ6" t="s">
-        <v>326</v>
-      </c>
-      <c r="BN6" t="s">
-        <v>327</v>
-      </c>
-      <c r="BP6" t="s">
-        <v>328</v>
-      </c>
-      <c r="BQ6" t="s">
-        <v>329</v>
-      </c>
-      <c r="BS6" t="s">
-        <v>330</v>
-      </c>
-      <c r="BU6" t="s">
-        <v>331</v>
-      </c>
-      <c r="BW6" t="s">
-        <v>332</v>
-      </c>
-      <c r="BY6" t="s">
-        <v>333</v>
-      </c>
-      <c r="CA6" t="s">
-        <v>334</v>
-      </c>
-      <c r="CC6" t="s">
-        <v>335</v>
+    <row r="7" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>362</v>
+      </c>
+      <c r="C7" t="s">
+        <v>363</v>
+      </c>
+      <c r="E7" t="s">
+        <v>364</v>
+      </c>
+      <c r="F7" t="s">
+        <v>365</v>
+      </c>
+      <c r="H7" t="s">
+        <v>366</v>
+      </c>
+      <c r="J7" t="s">
+        <v>367</v>
+      </c>
+      <c r="K7" t="s">
+        <v>368</v>
+      </c>
+      <c r="M7" t="s">
+        <v>369</v>
+      </c>
+      <c r="O7" t="s">
+        <v>370</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>371</v>
+      </c>
+      <c r="R7" t="s">
+        <v>372</v>
+      </c>
+      <c r="T7" t="s">
+        <v>373</v>
+      </c>
+      <c r="V7" t="s">
+        <v>374</v>
+      </c>
+      <c r="X7" t="s">
+        <v>375</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>376</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>377</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>378</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>379</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>380</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>381</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>382</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>383</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>384</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>385</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>386</v>
+      </c>
+      <c r="AQ7" t="s">
+        <v>387</v>
+      </c>
+      <c r="AR7" t="s">
+        <v>388</v>
+      </c>
+      <c r="AU7" t="s">
+        <v>389</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>390</v>
+      </c>
+      <c r="AW7" t="s">
+        <v>391</v>
+      </c>
+      <c r="AX7" t="s">
+        <v>392</v>
+      </c>
+      <c r="AY7" t="s">
+        <v>393</v>
+      </c>
+      <c r="AZ7" t="s">
+        <v>394</v>
+      </c>
+      <c r="BA7" t="s">
+        <v>395</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>396</v>
+      </c>
+      <c r="BD7" t="s">
+        <v>397</v>
+      </c>
+      <c r="BE7" t="s">
+        <v>398</v>
+      </c>
+      <c r="BF7" t="s">
+        <v>399</v>
+      </c>
+      <c r="BG7" t="s">
+        <v>400</v>
+      </c>
+      <c r="BI7" t="s">
+        <v>401</v>
+      </c>
+      <c r="BN7" t="s">
+        <v>402</v>
+      </c>
+      <c r="BP7" t="s">
+        <v>403</v>
+      </c>
+      <c r="BQ7" t="s">
+        <v>404</v>
+      </c>
+      <c r="BS7" t="s">
+        <v>405</v>
+      </c>
+      <c r="BU7" t="s">
+        <v>406</v>
+      </c>
+      <c r="BW7" t="s">
+        <v>407</v>
+      </c>
+      <c r="BY7" t="s">
+        <v>408</v>
+      </c>
+      <c r="CA7" t="s">
+        <v>409</v>
+      </c>
+      <c r="CC7" t="s">
+        <v>410</v>
+      </c>
+      <c r="CG7" t="s">
+        <v>411</v>
+      </c>
+      <c r="CH7" t="s">
+        <v>412</v>
+      </c>
+      <c r="CM7" t="s">
+        <v>413</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>336</v>
-      </c>
-      <c r="C7" t="s">
-        <v>337</v>
-      </c>
-      <c r="E7" t="s">
-        <v>338</v>
-      </c>
-      <c r="F7" t="s">
-        <v>339</v>
-      </c>
-      <c r="H7" t="s">
-        <v>340</v>
-      </c>
-      <c r="J7" t="s">
-        <v>341</v>
-      </c>
-      <c r="K7" t="s">
-        <v>342</v>
-      </c>
-      <c r="M7" t="s">
-        <v>343</v>
-      </c>
-      <c r="O7" t="s">
-        <v>344</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>345</v>
-      </c>
-      <c r="R7" t="s">
-        <v>346</v>
-      </c>
-      <c r="T7" t="s">
-        <v>347</v>
-      </c>
-      <c r="V7" t="s">
-        <v>348</v>
-      </c>
-      <c r="X7" t="s">
-        <v>349</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>350</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>351</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>352</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>353</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>354</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>355</v>
-      </c>
-      <c r="AH7" t="s">
-        <v>356</v>
-      </c>
-      <c r="AI7" t="s">
-        <v>357</v>
-      </c>
-      <c r="AJ7" t="s">
-        <v>358</v>
-      </c>
-      <c r="AN7" t="s">
-        <v>359</v>
-      </c>
-      <c r="AO7" t="s">
-        <v>360</v>
-      </c>
-      <c r="AQ7" t="s">
-        <v>361</v>
-      </c>
-      <c r="AR7" t="s">
-        <v>362</v>
-      </c>
-      <c r="AU7" t="s">
-        <v>363</v>
-      </c>
-      <c r="AV7" t="s">
-        <v>364</v>
-      </c>
-      <c r="AW7" t="s">
-        <v>365</v>
-      </c>
-      <c r="AX7" t="s">
-        <v>366</v>
-      </c>
-      <c r="AY7" t="s">
-        <v>367</v>
-      </c>
-      <c r="AZ7" t="s">
-        <v>368</v>
-      </c>
-      <c r="BA7" t="s">
-        <v>369</v>
-      </c>
-      <c r="BC7" t="s">
-        <v>370</v>
-      </c>
-      <c r="BD7" t="s">
-        <v>371</v>
-      </c>
-      <c r="BE7" t="s">
-        <v>372</v>
-      </c>
-      <c r="BF7" t="s">
-        <v>373</v>
-      </c>
-      <c r="BG7" t="s">
-        <v>374</v>
-      </c>
-      <c r="BI7" t="s">
-        <v>375</v>
-      </c>
-      <c r="BN7" t="s">
-        <v>376</v>
-      </c>
-      <c r="BP7" t="s">
-        <v>377</v>
-      </c>
-      <c r="BQ7" t="s">
-        <v>378</v>
-      </c>
-      <c r="BS7" t="s">
-        <v>379</v>
-      </c>
-      <c r="BU7" t="s">
-        <v>380</v>
-      </c>
-      <c r="BW7" t="s">
-        <v>381</v>
-      </c>
-      <c r="BY7" t="s">
-        <v>382</v>
-      </c>
-      <c r="CA7" t="s">
-        <v>383</v>
-      </c>
-      <c r="CC7" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>385</v>
+        <v>414</v>
       </c>
       <c r="C8" t="s">
-        <v>386</v>
+        <v>415</v>
       </c>
       <c r="E8" t="s">
-        <v>387</v>
+        <v>416</v>
       </c>
       <c r="F8" t="s">
-        <v>388</v>
+        <v>417</v>
       </c>
       <c r="H8" t="s">
-        <v>389</v>
+        <v>418</v>
       </c>
       <c r="K8" t="s">
-        <v>390</v>
+        <v>419</v>
       </c>
       <c r="O8" t="s">
-        <v>391</v>
+        <v>420</v>
       </c>
       <c r="Q8" t="s">
-        <v>392</v>
+        <v>421</v>
       </c>
       <c r="R8" t="s">
-        <v>393</v>
+        <v>422</v>
       </c>
       <c r="T8" t="s">
-        <v>394</v>
+        <v>423</v>
       </c>
       <c r="X8" t="s">
-        <v>395</v>
+        <v>424</v>
       </c>
       <c r="AA8" t="s">
-        <v>396</v>
+        <v>425</v>
       </c>
       <c r="AB8" t="s">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="AE8" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="AF8" t="s">
-        <v>398</v>
+        <v>427</v>
       </c>
       <c r="AH8" t="s">
-        <v>399</v>
+        <v>428</v>
       </c>
       <c r="AI8" t="s">
-        <v>400</v>
+        <v>429</v>
       </c>
       <c r="AJ8" t="s">
-        <v>401</v>
+        <v>430</v>
       </c>
       <c r="AN8" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="AO8" t="s">
-        <v>403</v>
+        <v>432</v>
       </c>
       <c r="AQ8" t="s">
-        <v>404</v>
+        <v>433</v>
       </c>
       <c r="AR8" t="s">
-        <v>405</v>
+        <v>434</v>
       </c>
       <c r="AU8" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="AV8" t="s">
-        <v>406</v>
+        <v>435</v>
       </c>
       <c r="AW8" t="s">
-        <v>407</v>
+        <v>436</v>
       </c>
       <c r="AX8" t="s">
-        <v>408</v>
+        <v>437</v>
       </c>
       <c r="AY8" t="s">
-        <v>409</v>
+        <v>438</v>
       </c>
       <c r="AZ8" t="s">
-        <v>410</v>
+        <v>439</v>
       </c>
       <c r="BA8" t="s">
-        <v>411</v>
+        <v>440</v>
       </c>
       <c r="BC8" t="s">
-        <v>412</v>
+        <v>441</v>
       </c>
       <c r="BD8" t="s">
-        <v>413</v>
+        <v>442</v>
       </c>
       <c r="BE8" t="s">
-        <v>414</v>
+        <v>443</v>
       </c>
       <c r="BF8" t="s">
-        <v>415</v>
+        <v>444</v>
       </c>
       <c r="BG8" t="s">
-        <v>416</v>
+        <v>445</v>
       </c>
       <c r="BI8" t="s">
-        <v>417</v>
+        <v>446</v>
       </c>
       <c r="BN8" t="s">
-        <v>418</v>
+        <v>447</v>
       </c>
       <c r="BQ8" t="s">
-        <v>419</v>
+        <v>448</v>
       </c>
       <c r="BS8" t="s">
-        <v>420</v>
+        <v>449</v>
       </c>
       <c r="BW8" t="s">
-        <v>421</v>
+        <v>450</v>
       </c>
       <c r="BY8" t="s">
-        <v>422</v>
+        <v>451</v>
       </c>
       <c r="CA8" t="s">
-        <v>423</v>
+        <v>452</v>
       </c>
       <c r="CC8" t="s">
-        <v>424</v>
+        <v>453</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>425</v>
+        <v>454</v>
       </c>
       <c r="E9" t="s">
-        <v>426</v>
+        <v>455</v>
       </c>
       <c r="F9" t="s">
-        <v>427</v>
+        <v>456</v>
       </c>
       <c r="H9" t="s">
-        <v>428</v>
+        <v>457</v>
       </c>
       <c r="O9" t="s">
-        <v>429</v>
+        <v>458</v>
       </c>
       <c r="T9" t="s">
-        <v>430</v>
+        <v>459</v>
       </c>
       <c r="X9" t="s">
-        <v>431</v>
+        <v>460</v>
       </c>
       <c r="AB9" t="s">
-        <v>432</v>
+        <v>461</v>
       </c>
       <c r="AF9" t="s">
-        <v>433</v>
+        <v>462</v>
       </c>
       <c r="AI9" t="s">
-        <v>434</v>
+        <v>463</v>
       </c>
       <c r="AJ9" t="s">
-        <v>435</v>
+        <v>464</v>
       </c>
       <c r="AO9" t="s">
-        <v>436</v>
+        <v>465</v>
       </c>
       <c r="AV9" t="s">
-        <v>437</v>
+        <v>466</v>
       </c>
       <c r="AW9" t="s">
-        <v>438</v>
+        <v>467</v>
       </c>
       <c r="AX9" t="s">
-        <v>439</v>
+        <v>468</v>
       </c>
       <c r="AY9" t="s">
-        <v>440</v>
+        <v>469</v>
       </c>
       <c r="AZ9" t="s">
-        <v>441</v>
+        <v>470</v>
       </c>
       <c r="BA9" t="s">
-        <v>442</v>
+        <v>471</v>
       </c>
       <c r="BC9" t="s">
-        <v>443</v>
+        <v>472</v>
       </c>
       <c r="BD9" t="s">
-        <v>444</v>
+        <v>473</v>
       </c>
       <c r="BE9" t="s">
-        <v>445</v>
+        <v>474</v>
       </c>
       <c r="BF9" t="s">
-        <v>446</v>
+        <v>475</v>
       </c>
       <c r="BG9" t="s">
-        <v>447</v>
+        <v>476</v>
       </c>
       <c r="BN9" t="s">
-        <v>448</v>
+        <v>477</v>
       </c>
       <c r="BQ9" t="s">
-        <v>449</v>
+        <v>478</v>
       </c>
       <c r="BY9" t="s">
-        <v>450</v>
+        <v>479</v>
       </c>
       <c r="CC9" t="s">
-        <v>451</v>
+        <v>480</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="41:49" x14ac:dyDescent="0.25">
       <c r="AO10" t="s">
-        <v>452</v>
+        <v>481</v>
       </c>
       <c r="AW10" t="s">
-        <v>453</v>
+        <v>482</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/data/ICEHLdelegacije.xlsx
+++ b/data/ICEHLdelegacije.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3283" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3280" uniqueCount="482">
   <si>
     <t>SmetanaLa</t>
   </si>
@@ -435,21 +435,21 @@
     <t>2025-03-04</t>
   </si>
   <si>
+    <t>zbrisano</t>
+  </si>
+  <si>
+    <t>2025-03-07</t>
+  </si>
+  <si>
+    <t>2025-03-06</t>
+  </si>
+  <si>
+    <t>2025-03-08</t>
+  </si>
+  <si>
     <t>2025-03-11</t>
   </si>
   <si>
-    <t>2025-03-07</t>
-  </si>
-  <si>
-    <t>2025-03-06</t>
-  </si>
-  <si>
-    <t>2025-03-08</t>
-  </si>
-  <si>
-    <t>zbrisano</t>
-  </si>
-  <si>
     <t>HuberAn</t>
   </si>
   <si>
@@ -720,7 +720,7 @@
     <t>Merkur Eisstadion Graz;Huber aAn;NikolicMa;NotheggerDa;PuffWo</t>
   </si>
   <si>
-    <t>Stadthalle Villach;FichtnerPa;ZrnicMi;BärnthalerCh;RieckenSi</t>
+    <t>Stadthalle Villach;SeewaldEl;ZrnicMi;BärnthalerCh;RieckenSi</t>
   </si>
   <si>
     <t>Heidi Horten Arena Klagenfurt;FichtnerPa;SmetanaLa;BärnthalerCh;RieckenSi</t>
@@ -921,7 +921,7 @@
     <t>Heidi Horten Arena Klagenfurt;Huber aAn;NikolicMa;BedynekSe;MantovaniDa</t>
   </si>
   <si>
-    <t>Gabor Ocskay Eisarena;SmetanaLa;SternatCh;DurmisOt;MuzsikNo</t>
+    <t>Gabor Ocskay Eisarena;FichtnerPa;SmetanaLa;DurmisOt;MuzsikNo</t>
   </si>
   <si>
     <t>Linz AG Eisarena;HronskyTo;OfnerCh;DurmisOt;KoncDa</t>
@@ -1099,9 +1099,6 @@
   </si>
   <si>
     <t>Eishalle Bruneck;NikolicKr;OfnerCh;MantovaniDa;PardatscherUl</t>
-  </si>
-  <si>
-    <t>Eisarena Salzburg;NikolicMa;NikolicKr;BedynekSe;NotheggerDa</t>
   </si>
   <si>
     <t>Eishalle Wien-Kagran;HronskyTo;SmetanaLa;DurmisOt;WeissAl</t>
@@ -1782,7 +1779,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:BA134"/>
+  <dimension ref="A2:AZ134"/>
   <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.28515625" customWidth="1"/>
@@ -2050,7 +2047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -2366,7 +2363,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>53</v>
       </c>
@@ -2512,7 +2509,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>56</v>
       </c>
@@ -2792,7 +2789,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>59</v>
       </c>
@@ -3066,7 +3063,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>74</v>
       </c>
@@ -3200,7 +3197,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>67</v>
       </c>
@@ -3462,7 +3459,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>66</v>
       </c>
@@ -3846,7 +3843,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>69</v>
       </c>
@@ -3968,7 +3965,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>92</v>
       </c>
@@ -4325,7 +4322,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>105</v>
       </c>
@@ -4557,7 +4554,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>102</v>
       </c>
@@ -4771,7 +4768,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>79</v>
       </c>
@@ -5368,7 +5365,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>108</v>
       </c>
@@ -5626,10 +5623,10 @@
         <v>142</v>
       </c>
       <c r="AG32" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>94</v>
       </c>
@@ -5706,7 +5703,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>107</v>
       </c>
@@ -5815,7 +5812,7 @@
         <v>109</v>
       </c>
       <c r="O35" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="P35" t="s">
         <v>109</v>
@@ -5886,10 +5883,10 @@
         <v>142</v>
       </c>
       <c r="W36" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>85</v>
       </c>
@@ -6014,8 +6011,11 @@
       <c r="I39" t="s">
         <v>135</v>
       </c>
+      <c r="J39" t="s">
+        <v>136</v>
+      </c>
       <c r="K39" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="L39" t="s">
         <v>140</v>
@@ -6027,13 +6027,13 @@
         <v>136</v>
       </c>
       <c r="Q39" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="R39" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>110</v>
       </c>
@@ -6059,16 +6059,16 @@
         <v>138</v>
       </c>
       <c r="L40" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="N40" t="s">
         <v>136</v>
       </c>
       <c r="O40" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>118</v>
       </c>
@@ -6143,10 +6143,10 @@
         <v>138</v>
       </c>
       <c r="I43" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>96</v>
       </c>
@@ -6215,7 +6215,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="47" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>63</v>
       </c>
@@ -6229,10 +6229,10 @@
         <v>132</v>
       </c>
       <c r="E47" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>64</v>
       </c>
@@ -6327,7 +6327,7 @@
         <v>135</v>
       </c>
       <c r="D54" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6341,10 +6341,10 @@
         <v>133</v>
       </c>
       <c r="D55" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>140</v>
       </c>
@@ -6360,7 +6360,7 @@
         <v>136</v>
       </c>
       <c r="B57" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C57" t="s">
         <v>140</v>
@@ -6368,18 +6368,18 @@
     </row>
     <row r="58" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C58" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="59" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" ht="15" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C59" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="61" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="62" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="63" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6767,7 +6767,7 @@
         <v>136</v>
       </c>
       <c r="CM3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
@@ -7039,7 +7039,7 @@
         <v>28</v>
       </c>
       <c r="CL4" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="CM4" t="s">
         <v>16</v>
@@ -8076,7 +8076,7 @@
         <v>28</v>
       </c>
       <c r="CL8" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="CM8" t="s">
         <v>11</v>
@@ -8288,7 +8288,7 @@
         <v>6</v>
       </c>
       <c r="CL9" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CM9" t="s">
         <v>2</v>
@@ -8894,7 +8894,7 @@
         <v>33</v>
       </c>
       <c r="CM12" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
@@ -9073,7 +9073,7 @@
         <v>2</v>
       </c>
       <c r="CM13" t="s">
-        <v>33</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
@@ -9252,7 +9252,7 @@
         <v>14</v>
       </c>
       <c r="CM14" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
@@ -9431,10 +9431,10 @@
         <v>13</v>
       </c>
       <c r="CM15" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -9588,11 +9588,8 @@
       <c r="CH16" t="s">
         <v>1</v>
       </c>
-      <c r="CM16" t="s">
-        <v>1</v>
-      </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>0</v>
       </c>
@@ -9746,11 +9743,8 @@
       <c r="CH17" t="s">
         <v>5</v>
       </c>
-      <c r="CM17" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>32</v>
       </c>
@@ -9904,11 +9898,8 @@
       <c r="CH18" t="s">
         <v>13</v>
       </c>
-      <c r="CM18" t="s">
-        <v>14</v>
-      </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>37</v>
       </c>
@@ -10062,11 +10053,8 @@
       <c r="CH19" t="s">
         <v>4</v>
       </c>
-      <c r="CM19" t="s">
-        <v>4</v>
-      </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>30</v>
       </c>
@@ -11252,7 +11240,7 @@
         <v>136</v>
       </c>
       <c r="CM3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
@@ -11921,384 +11909,384 @@
         <v>360</v>
       </c>
       <c r="CM6" t="s">
-        <v>361</v>
+        <v>266</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>361</v>
+      </c>
+      <c r="C7" t="s">
         <v>362</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
         <v>363</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>364</v>
       </c>
-      <c r="F7" t="s">
+      <c r="H7" t="s">
         <v>365</v>
       </c>
-      <c r="H7" t="s">
+      <c r="J7" t="s">
         <v>366</v>
       </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
         <v>367</v>
       </c>
-      <c r="K7" t="s">
+      <c r="M7" t="s">
         <v>368</v>
       </c>
-      <c r="M7" t="s">
+      <c r="O7" t="s">
         <v>369</v>
       </c>
-      <c r="O7" t="s">
+      <c r="Q7" t="s">
         <v>370</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="R7" t="s">
         <v>371</v>
       </c>
-      <c r="R7" t="s">
+      <c r="T7" t="s">
         <v>372</v>
       </c>
-      <c r="T7" t="s">
+      <c r="V7" t="s">
         <v>373</v>
       </c>
-      <c r="V7" t="s">
+      <c r="X7" t="s">
         <v>374</v>
       </c>
-      <c r="X7" t="s">
+      <c r="Z7" t="s">
         <v>375</v>
       </c>
-      <c r="Z7" t="s">
+      <c r="AA7" t="s">
         <v>376</v>
       </c>
-      <c r="AA7" t="s">
+      <c r="AB7" t="s">
         <v>377</v>
       </c>
-      <c r="AB7" t="s">
+      <c r="AD7" t="s">
         <v>378</v>
       </c>
-      <c r="AD7" t="s">
+      <c r="AE7" t="s">
         <v>379</v>
       </c>
-      <c r="AE7" t="s">
+      <c r="AF7" t="s">
         <v>380</v>
       </c>
-      <c r="AF7" t="s">
+      <c r="AH7" t="s">
         <v>381</v>
       </c>
-      <c r="AH7" t="s">
+      <c r="AI7" t="s">
         <v>382</v>
       </c>
-      <c r="AI7" t="s">
+      <c r="AJ7" t="s">
         <v>383</v>
       </c>
-      <c r="AJ7" t="s">
+      <c r="AN7" t="s">
         <v>384</v>
       </c>
-      <c r="AN7" t="s">
+      <c r="AO7" t="s">
         <v>385</v>
       </c>
-      <c r="AO7" t="s">
+      <c r="AQ7" t="s">
         <v>386</v>
       </c>
-      <c r="AQ7" t="s">
+      <c r="AR7" t="s">
         <v>387</v>
       </c>
-      <c r="AR7" t="s">
+      <c r="AU7" t="s">
         <v>388</v>
       </c>
-      <c r="AU7" t="s">
+      <c r="AV7" t="s">
         <v>389</v>
       </c>
-      <c r="AV7" t="s">
+      <c r="AW7" t="s">
         <v>390</v>
       </c>
-      <c r="AW7" t="s">
+      <c r="AX7" t="s">
         <v>391</v>
       </c>
-      <c r="AX7" t="s">
+      <c r="AY7" t="s">
         <v>392</v>
       </c>
-      <c r="AY7" t="s">
+      <c r="AZ7" t="s">
         <v>393</v>
       </c>
-      <c r="AZ7" t="s">
+      <c r="BA7" t="s">
         <v>394</v>
       </c>
-      <c r="BA7" t="s">
+      <c r="BC7" t="s">
         <v>395</v>
       </c>
-      <c r="BC7" t="s">
+      <c r="BD7" t="s">
         <v>396</v>
       </c>
-      <c r="BD7" t="s">
+      <c r="BE7" t="s">
         <v>397</v>
       </c>
-      <c r="BE7" t="s">
+      <c r="BF7" t="s">
         <v>398</v>
       </c>
-      <c r="BF7" t="s">
+      <c r="BG7" t="s">
         <v>399</v>
       </c>
-      <c r="BG7" t="s">
+      <c r="BI7" t="s">
         <v>400</v>
       </c>
-      <c r="BI7" t="s">
+      <c r="BN7" t="s">
         <v>401</v>
       </c>
-      <c r="BN7" t="s">
+      <c r="BP7" t="s">
         <v>402</v>
       </c>
-      <c r="BP7" t="s">
+      <c r="BQ7" t="s">
         <v>403</v>
       </c>
-      <c r="BQ7" t="s">
+      <c r="BS7" t="s">
         <v>404</v>
       </c>
-      <c r="BS7" t="s">
+      <c r="BU7" t="s">
         <v>405</v>
       </c>
-      <c r="BU7" t="s">
+      <c r="BW7" t="s">
         <v>406</v>
       </c>
-      <c r="BW7" t="s">
+      <c r="BY7" t="s">
         <v>407</v>
       </c>
-      <c r="BY7" t="s">
+      <c r="CA7" t="s">
         <v>408</v>
       </c>
-      <c r="CA7" t="s">
+      <c r="CC7" t="s">
         <v>409</v>
       </c>
-      <c r="CC7" t="s">
+      <c r="CG7" t="s">
         <v>410</v>
       </c>
-      <c r="CG7" t="s">
+      <c r="CH7" t="s">
         <v>411</v>
       </c>
-      <c r="CH7" t="s">
+      <c r="CM7" t="s">
         <v>412</v>
       </c>
-      <c r="CM7" t="s">
+    </row>
+    <row r="8" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="C8" t="s">
         <v>414</v>
       </c>
-      <c r="C8" t="s">
+      <c r="E8" t="s">
         <v>415</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>416</v>
       </c>
-      <c r="F8" t="s">
+      <c r="H8" t="s">
         <v>417</v>
       </c>
-      <c r="H8" t="s">
+      <c r="K8" t="s">
         <v>418</v>
       </c>
-      <c r="K8" t="s">
+      <c r="O8" t="s">
         <v>419</v>
       </c>
-      <c r="O8" t="s">
+      <c r="Q8" t="s">
         <v>420</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="R8" t="s">
         <v>421</v>
       </c>
-      <c r="R8" t="s">
+      <c r="T8" t="s">
         <v>422</v>
       </c>
-      <c r="T8" t="s">
+      <c r="X8" t="s">
         <v>423</v>
       </c>
-      <c r="X8" t="s">
+      <c r="AA8" t="s">
         <v>424</v>
       </c>
-      <c r="AA8" t="s">
+      <c r="AB8" t="s">
         <v>425</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>426</v>
       </c>
       <c r="AE8" t="s">
         <v>266</v>
       </c>
       <c r="AF8" t="s">
+        <v>426</v>
+      </c>
+      <c r="AH8" t="s">
         <v>427</v>
       </c>
-      <c r="AH8" t="s">
+      <c r="AI8" t="s">
         <v>428</v>
       </c>
-      <c r="AI8" t="s">
+      <c r="AJ8" t="s">
         <v>429</v>
       </c>
-      <c r="AJ8" t="s">
+      <c r="AN8" t="s">
         <v>430</v>
       </c>
-      <c r="AN8" t="s">
+      <c r="AO8" t="s">
         <v>431</v>
       </c>
-      <c r="AO8" t="s">
+      <c r="AQ8" t="s">
         <v>432</v>
       </c>
-      <c r="AQ8" t="s">
+      <c r="AR8" t="s">
         <v>433</v>
-      </c>
-      <c r="AR8" t="s">
-        <v>434</v>
       </c>
       <c r="AU8" t="s">
         <v>266</v>
       </c>
       <c r="AV8" t="s">
+        <v>434</v>
+      </c>
+      <c r="AW8" t="s">
         <v>435</v>
       </c>
-      <c r="AW8" t="s">
+      <c r="AX8" t="s">
         <v>436</v>
       </c>
-      <c r="AX8" t="s">
+      <c r="AY8" t="s">
         <v>437</v>
       </c>
-      <c r="AY8" t="s">
+      <c r="AZ8" t="s">
         <v>438</v>
       </c>
-      <c r="AZ8" t="s">
+      <c r="BA8" t="s">
         <v>439</v>
       </c>
-      <c r="BA8" t="s">
+      <c r="BC8" t="s">
         <v>440</v>
       </c>
-      <c r="BC8" t="s">
+      <c r="BD8" t="s">
         <v>441</v>
       </c>
-      <c r="BD8" t="s">
+      <c r="BE8" t="s">
         <v>442</v>
       </c>
-      <c r="BE8" t="s">
+      <c r="BF8" t="s">
         <v>443</v>
       </c>
-      <c r="BF8" t="s">
+      <c r="BG8" t="s">
         <v>444</v>
       </c>
-      <c r="BG8" t="s">
+      <c r="BI8" t="s">
         <v>445</v>
       </c>
-      <c r="BI8" t="s">
+      <c r="BN8" t="s">
         <v>446</v>
       </c>
-      <c r="BN8" t="s">
+      <c r="BQ8" t="s">
         <v>447</v>
       </c>
-      <c r="BQ8" t="s">
+      <c r="BS8" t="s">
         <v>448</v>
       </c>
-      <c r="BS8" t="s">
+      <c r="BW8" t="s">
         <v>449</v>
       </c>
-      <c r="BW8" t="s">
+      <c r="BY8" t="s">
         <v>450</v>
       </c>
-      <c r="BY8" t="s">
+      <c r="CA8" t="s">
         <v>451</v>
       </c>
-      <c r="CA8" t="s">
+      <c r="CC8" t="s">
         <v>452</v>
-      </c>
-      <c r="CC8" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>453</v>
+      </c>
+      <c r="E9" t="s">
         <v>454</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>455</v>
       </c>
-      <c r="F9" t="s">
+      <c r="H9" t="s">
         <v>456</v>
       </c>
-      <c r="H9" t="s">
+      <c r="O9" t="s">
         <v>457</v>
       </c>
-      <c r="O9" t="s">
+      <c r="T9" t="s">
         <v>458</v>
       </c>
-      <c r="T9" t="s">
+      <c r="X9" t="s">
         <v>459</v>
       </c>
-      <c r="X9" t="s">
+      <c r="AB9" t="s">
         <v>460</v>
       </c>
-      <c r="AB9" t="s">
+      <c r="AF9" t="s">
         <v>461</v>
       </c>
-      <c r="AF9" t="s">
+      <c r="AI9" t="s">
         <v>462</v>
       </c>
-      <c r="AI9" t="s">
+      <c r="AJ9" t="s">
         <v>463</v>
       </c>
-      <c r="AJ9" t="s">
+      <c r="AO9" t="s">
         <v>464</v>
       </c>
-      <c r="AO9" t="s">
+      <c r="AV9" t="s">
         <v>465</v>
       </c>
-      <c r="AV9" t="s">
+      <c r="AW9" t="s">
         <v>466</v>
       </c>
-      <c r="AW9" t="s">
+      <c r="AX9" t="s">
         <v>467</v>
       </c>
-      <c r="AX9" t="s">
+      <c r="AY9" t="s">
         <v>468</v>
       </c>
-      <c r="AY9" t="s">
+      <c r="AZ9" t="s">
         <v>469</v>
       </c>
-      <c r="AZ9" t="s">
+      <c r="BA9" t="s">
         <v>470</v>
       </c>
-      <c r="BA9" t="s">
+      <c r="BC9" t="s">
         <v>471</v>
       </c>
-      <c r="BC9" t="s">
+      <c r="BD9" t="s">
         <v>472</v>
       </c>
-      <c r="BD9" t="s">
+      <c r="BE9" t="s">
         <v>473</v>
       </c>
-      <c r="BE9" t="s">
+      <c r="BF9" t="s">
         <v>474</v>
       </c>
-      <c r="BF9" t="s">
+      <c r="BG9" t="s">
         <v>475</v>
       </c>
-      <c r="BG9" t="s">
+      <c r="BN9" t="s">
         <v>476</v>
       </c>
-      <c r="BN9" t="s">
+      <c r="BQ9" t="s">
         <v>477</v>
       </c>
-      <c r="BQ9" t="s">
+      <c r="BY9" t="s">
         <v>478</v>
       </c>
-      <c r="BY9" t="s">
+      <c r="CC9" t="s">
         <v>479</v>
-      </c>
-      <c r="CC9" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="41:49" x14ac:dyDescent="0.25">
       <c r="AO10" t="s">
+        <v>480</v>
+      </c>
+      <c r="AW10" t="s">
         <v>481</v>
-      </c>
-      <c r="AW10" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/data/ICEHLdelegacije.xlsx
+++ b/data/ICEHLdelegacije.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3280" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3431" uniqueCount="505">
   <si>
     <t>SmetanaLa</t>
   </si>
@@ -441,15 +441,39 @@
     <t>2025-03-07</t>
   </si>
   <si>
+    <t>2025-03-14</t>
+  </si>
+  <si>
     <t>2025-03-06</t>
   </si>
   <si>
+    <t>2025-03-18</t>
+  </si>
+  <si>
     <t>2025-03-08</t>
   </si>
   <si>
     <t>2025-03-11</t>
   </si>
   <si>
+    <t>2025-03-23</t>
+  </si>
+  <si>
+    <t>2025-03-16</t>
+  </si>
+  <si>
+    <t>2025-03-28</t>
+  </si>
+  <si>
+    <t>2025-03-21</t>
+  </si>
+  <si>
+    <t>2025-03-25</t>
+  </si>
+  <si>
+    <t>2025-03-30</t>
+  </si>
+  <si>
     <t>HuberAn</t>
   </si>
   <si>
@@ -726,6 +750,30 @@
     <t>Heidi Horten Arena Klagenfurt;FichtnerPa;SmetanaLa;BärnthalerCh;RieckenSi</t>
   </si>
   <si>
+    <t>Stadthalle Villach;HronskyTo;Huber aAn;BedynekSe;KoncDa</t>
+  </si>
+  <si>
+    <t>Linz AG Eisarena;SmetanaLa;SternatCh;DurmisOt;RieckenSi</t>
+  </si>
+  <si>
+    <t>Klagenfurter Stadthalle;HronskyTo;OfnerCh;KoncDa;ZgoncGa</t>
+  </si>
+  <si>
+    <t>Linz AG Eisarena;NikolicMa;SternatCh;BedynekSe;DurmisOt</t>
+  </si>
+  <si>
+    <t>Eisarena Salzburg;HronskyTo;OfnerCh;DurmisOt;KoncDa</t>
+  </si>
+  <si>
+    <t>Linz AG Eisarena;PiragicTr;SmetanaLa;BedynekSe;RieckenSi</t>
+  </si>
+  <si>
+    <t>Eisarena Salzburg;HronskyTo;NikolicKr;DurmisOt;KoncDa</t>
+  </si>
+  <si>
+    <t>Linz AG Eisarena;HronskyTo;NikolicMa;BedynekSe;RieckenSi</t>
+  </si>
+  <si>
     <t>Tiroler Wasserkraft Arena;NikolicMa;SeewaldEl;FleischmannLu;NotheggerDa</t>
   </si>
   <si>
@@ -927,6 +975,24 @@
     <t>Linz AG Eisarena;HronskyTo;OfnerCh;DurmisOt;KoncDa</t>
   </si>
   <si>
+    <t>Merkur Eisstadion Graz;NikolicMa;NikolicKr;NotheggerDa;PuffWo</t>
+  </si>
+  <si>
+    <t>Eisarena Salzburg;Huber aAn;NikolicKr;NotheggerDa;PuffWo</t>
+  </si>
+  <si>
+    <t>Sparkasse Arena Bozen;PiragicTr;SmetanaLa;MantovaniDa;RieckenSi</t>
+  </si>
+  <si>
+    <t>Heidi Horten Arena Klagenfurt;Huber aAn;NikolicKr;PuffWo;ZgoncGa</t>
+  </si>
+  <si>
+    <t>Sparkasse Arena Bozen;NikolicMa;SternatCh;MantovaniDa;NotheggerDa</t>
+  </si>
+  <si>
+    <t>Heidi Horten Arena Klagenfurt;OfnerCh;SternatCh;NotheggerDa;ZgoncGa</t>
+  </si>
+  <si>
     <t>Hala Tivoli;PiragicTr;ZrnicMi;HribarMa;SnojTa</t>
   </si>
   <si>
@@ -1099,6 +1165,9 @@
   </si>
   <si>
     <t>Eishalle Bruneck;NikolicKr;OfnerCh;MantovaniDa;PardatscherUl</t>
+  </si>
+  <si>
+    <t>Eishalle Bruneck;PiragicTr;ZrnicMi;MantovaniDa;ZgoncGa</t>
   </si>
   <si>
     <t>Eishalle Wien-Kagran;HronskyTo;SmetanaLa;DurmisOt;WeissAl</t>
@@ -1779,7 +1848,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:AZ134"/>
+  <dimension ref="A2:BA134"/>
   <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.28515625" customWidth="1"/>
@@ -2047,7 +2116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -2363,7 +2432,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>53</v>
       </c>
@@ -2509,7 +2578,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>56</v>
       </c>
@@ -2789,7 +2858,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>59</v>
       </c>
@@ -3063,7 +3132,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>74</v>
       </c>
@@ -3197,7 +3266,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>67</v>
       </c>
@@ -3459,7 +3528,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>66</v>
       </c>
@@ -3843,7 +3912,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>69</v>
       </c>
@@ -3965,7 +4034,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>92</v>
       </c>
@@ -4322,7 +4391,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>105</v>
       </c>
@@ -4554,7 +4623,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>102</v>
       </c>
@@ -4768,7 +4837,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>79</v>
       </c>
@@ -5365,7 +5434,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>108</v>
       </c>
@@ -5456,8 +5525,11 @@
       <c r="AG30" t="s">
         <v>140</v>
       </c>
+      <c r="AH30" t="s">
+        <v>141</v>
+      </c>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>120</v>
       </c>
@@ -5534,7 +5606,7 @@
         <v>133</v>
       </c>
       <c r="AB31" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AC31" t="s">
         <v>140</v>
@@ -5542,8 +5614,11 @@
       <c r="AG31" t="s">
         <v>136</v>
       </c>
+      <c r="AH31" t="s">
+        <v>143</v>
+      </c>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>61</v>
       </c>
@@ -5617,16 +5692,19 @@
         <v>138</v>
       </c>
       <c r="AB32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AC32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AG32" t="s">
-        <v>143</v>
+        <v>145</v>
+      </c>
+      <c r="AH32" t="s">
+        <v>146</v>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>94</v>
       </c>
@@ -5702,8 +5780,17 @@
       <c r="AB33" t="s">
         <v>139</v>
       </c>
+      <c r="AC33" t="s">
+        <v>141</v>
+      </c>
+      <c r="AG33" t="s">
+        <v>147</v>
+      </c>
+      <c r="AH33" t="s">
+        <v>148</v>
+      </c>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>107</v>
       </c>
@@ -5767,8 +5854,17 @@
       <c r="W34" t="s">
         <v>138</v>
       </c>
+      <c r="AB34" t="s">
+        <v>141</v>
+      </c>
+      <c r="AC34" t="s">
+        <v>143</v>
+      </c>
+      <c r="AG34" t="s">
+        <v>149</v>
+      </c>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>71</v>
       </c>
@@ -5829,8 +5925,17 @@
       <c r="W35" t="s">
         <v>136</v>
       </c>
+      <c r="AB35" t="s">
+        <v>143</v>
+      </c>
+      <c r="AC35" t="s">
+        <v>146</v>
+      </c>
+      <c r="AG35" t="s">
+        <v>146</v>
+      </c>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>95</v>
       </c>
@@ -5880,13 +5985,19 @@
         <v>130</v>
       </c>
       <c r="U36" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="W36" t="s">
-        <v>143</v>
+        <v>145</v>
+      </c>
+      <c r="AB36" t="s">
+        <v>150</v>
+      </c>
+      <c r="AG36" t="s">
+        <v>148</v>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>85</v>
       </c>
@@ -5930,13 +6041,19 @@
         <v>133</v>
       </c>
       <c r="Q37" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="R37" t="s">
         <v>138</v>
       </c>
+      <c r="U37" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB37" t="s">
+        <v>148</v>
+      </c>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>112</v>
       </c>
@@ -5985,8 +6102,11 @@
       <c r="R38" t="s">
         <v>140</v>
       </c>
+      <c r="U38" t="s">
+        <v>143</v>
+      </c>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>99</v>
       </c>
@@ -6015,7 +6135,7 @@
         <v>136</v>
       </c>
       <c r="K39" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="L39" t="s">
         <v>140</v>
@@ -6027,13 +6147,16 @@
         <v>136</v>
       </c>
       <c r="Q39" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="R39" t="s">
         <v>139</v>
       </c>
+      <c r="U39" t="s">
+        <v>146</v>
+      </c>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>110</v>
       </c>
@@ -6058,17 +6181,23 @@
       <c r="I40" t="s">
         <v>138</v>
       </c>
+      <c r="K40" t="s">
+        <v>141</v>
+      </c>
       <c r="L40" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="N40" t="s">
         <v>136</v>
       </c>
       <c r="O40" t="s">
-        <v>143</v>
+        <v>145</v>
+      </c>
+      <c r="R40" t="s">
+        <v>141</v>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>118</v>
       </c>
@@ -6093,8 +6222,20 @@
       <c r="I41" t="s">
         <v>140</v>
       </c>
+      <c r="K41" t="s">
+        <v>143</v>
+      </c>
+      <c r="L41" t="s">
+        <v>141</v>
+      </c>
+      <c r="O41" t="s">
+        <v>141</v>
+      </c>
+      <c r="R41" t="s">
+        <v>149</v>
+      </c>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>72</v>
       </c>
@@ -6119,8 +6260,20 @@
       <c r="I42" t="s">
         <v>136</v>
       </c>
+      <c r="K42" t="s">
+        <v>146</v>
+      </c>
+      <c r="L42" t="s">
+        <v>143</v>
+      </c>
+      <c r="O42" t="s">
+        <v>149</v>
+      </c>
+      <c r="R42" t="s">
+        <v>150</v>
+      </c>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>125</v>
       </c>
@@ -6143,10 +6296,22 @@
         <v>138</v>
       </c>
       <c r="I43" t="s">
-        <v>143</v>
+        <v>145</v>
+      </c>
+      <c r="K43" t="s">
+        <v>148</v>
+      </c>
+      <c r="L43" t="s">
+        <v>146</v>
+      </c>
+      <c r="O43" t="s">
+        <v>150</v>
+      </c>
+      <c r="R43" t="s">
+        <v>151</v>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>96</v>
       </c>
@@ -6168,8 +6333,14 @@
       <c r="G44" t="s">
         <v>140</v>
       </c>
+      <c r="I44" t="s">
+        <v>147</v>
+      </c>
+      <c r="L44" t="s">
+        <v>148</v>
+      </c>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>119</v>
       </c>
@@ -6186,13 +6357,19 @@
         <v>138</v>
       </c>
       <c r="F45" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G45" t="s">
-        <v>142</v>
+        <v>144</v>
+      </c>
+      <c r="I45" t="s">
+        <v>149</v>
+      </c>
+      <c r="L45" t="s">
+        <v>151</v>
       </c>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>91</v>
       </c>
@@ -6206,7 +6383,7 @@
         <v>117</v>
       </c>
       <c r="E46" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F46" t="s">
         <v>136</v>
@@ -6214,8 +6391,11 @@
       <c r="G46" t="s">
         <v>139</v>
       </c>
+      <c r="I46" t="s">
+        <v>150</v>
+      </c>
     </row>
-    <row r="47" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>63</v>
       </c>
@@ -6229,10 +6409,19 @@
         <v>132</v>
       </c>
       <c r="E47" t="s">
-        <v>143</v>
+        <v>145</v>
+      </c>
+      <c r="F47" t="s">
+        <v>141</v>
+      </c>
+      <c r="G47" t="s">
+        <v>141</v>
+      </c>
+      <c r="I47" t="s">
+        <v>151</v>
       </c>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>64</v>
       </c>
@@ -6245,8 +6434,14 @@
       <c r="D48" t="s">
         <v>109</v>
       </c>
+      <c r="E48" t="s">
+        <v>141</v>
+      </c>
+      <c r="G48" t="s">
+        <v>149</v>
+      </c>
     </row>
-    <row r="49" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>104</v>
       </c>
@@ -6259,8 +6454,14 @@
       <c r="D49" t="s">
         <v>129</v>
       </c>
+      <c r="E49" t="s">
+        <v>143</v>
+      </c>
+      <c r="G49" t="s">
+        <v>150</v>
+      </c>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>127</v>
       </c>
@@ -6273,8 +6474,14 @@
       <c r="D50" t="s">
         <v>135</v>
       </c>
+      <c r="E50" t="s">
+        <v>146</v>
+      </c>
+      <c r="G50" t="s">
+        <v>151</v>
+      </c>
     </row>
-    <row r="51" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>117</v>
       </c>
@@ -6287,8 +6494,11 @@
       <c r="D51" t="s">
         <v>133</v>
       </c>
+      <c r="E51" t="s">
+        <v>148</v>
+      </c>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>134</v>
       </c>
@@ -6341,10 +6551,10 @@
         <v>133</v>
       </c>
       <c r="D55" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>140</v>
       </c>
@@ -6354,35 +6564,77 @@
       <c r="C56" t="s">
         <v>138</v>
       </c>
+      <c r="D56" t="s">
+        <v>147</v>
+      </c>
     </row>
-    <row r="57" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>136</v>
       </c>
       <c r="B57" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C57" t="s">
         <v>140</v>
       </c>
+      <c r="D57" t="s">
+        <v>149</v>
+      </c>
     </row>
-    <row r="58" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>143</v>
+        <v>145</v>
+      </c>
+      <c r="B58" t="s">
+        <v>141</v>
       </c>
       <c r="C58" t="s">
         <v>136</v>
       </c>
+      <c r="D58" t="s">
+        <v>150</v>
+      </c>
     </row>
-    <row r="59" ht="15" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="59" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>147</v>
+      </c>
+      <c r="B59" t="s">
+        <v>149</v>
+      </c>
       <c r="C59" t="s">
+        <v>145</v>
+      </c>
+      <c r="D59" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="60" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>149</v>
+      </c>
+      <c r="B60" t="s">
+        <v>150</v>
+      </c>
+      <c r="C60" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="60" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>150</v>
+      </c>
+      <c r="C61" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="62" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C62" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="63" ht="15" customHeight="1" spans="3:3" x14ac:dyDescent="0.25"/>
     <row r="64" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="65" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="66" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6462,7 +6714,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:CM42"/>
+  <dimension ref="A3:CU42"/>
   <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="17.85546875" customWidth="1"/>
@@ -6495,7 +6747,7 @@
     <col min="98" max="98" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>52</v>
       </c>
@@ -6755,22 +7007,46 @@
         <v>138</v>
       </c>
       <c r="CI3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="CJ3" t="s">
         <v>140</v>
       </c>
       <c r="CK3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="CL3" t="s">
         <v>136</v>
       </c>
       <c r="CM3" t="s">
+        <v>145</v>
+      </c>
+      <c r="CN3" t="s">
+        <v>141</v>
+      </c>
+      <c r="CO3" t="s">
+        <v>147</v>
+      </c>
+      <c r="CP3" t="s">
         <v>143</v>
       </c>
+      <c r="CQ3" t="s">
+        <v>149</v>
+      </c>
+      <c r="CR3" t="s">
+        <v>146</v>
+      </c>
+      <c r="CS3" t="s">
+        <v>150</v>
+      </c>
+      <c r="CT3" t="s">
+        <v>148</v>
+      </c>
+      <c r="CU3" t="s">
+        <v>151</v>
+      </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -6793,7 +7069,7 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="I4" t="s">
         <v>0</v>
@@ -6811,7 +7087,7 @@
         <v>9</v>
       </c>
       <c r="N4" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="O4" t="s">
         <v>16</v>
@@ -6832,7 +7108,7 @@
         <v>2</v>
       </c>
       <c r="U4" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="V4" t="s">
         <v>9</v>
@@ -7044,8 +7320,32 @@
       <c r="CM4" t="s">
         <v>16</v>
       </c>
+      <c r="CN4" t="s">
+        <v>11</v>
+      </c>
+      <c r="CO4" t="s">
+        <v>0</v>
+      </c>
+      <c r="CP4" t="s">
+        <v>11</v>
+      </c>
+      <c r="CQ4" t="s">
+        <v>6</v>
+      </c>
+      <c r="CR4" t="s">
+        <v>11</v>
+      </c>
+      <c r="CS4" t="s">
+        <v>1</v>
+      </c>
+      <c r="CT4" t="s">
+        <v>11</v>
+      </c>
+      <c r="CU4" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -7319,8 +7619,32 @@
       <c r="CM5" t="s">
         <v>0</v>
       </c>
+      <c r="CN5" t="s">
+        <v>28</v>
+      </c>
+      <c r="CO5" t="s">
+        <v>3</v>
+      </c>
+      <c r="CP5" t="s">
+        <v>2</v>
+      </c>
+      <c r="CQ5" t="s">
+        <v>3</v>
+      </c>
+      <c r="CR5" t="s">
+        <v>2</v>
+      </c>
+      <c r="CS5" t="s">
+        <v>0</v>
+      </c>
+      <c r="CT5" t="s">
+        <v>33</v>
+      </c>
+      <c r="CU5" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -7594,8 +7918,32 @@
       <c r="CM6" t="s">
         <v>22</v>
       </c>
+      <c r="CN6" t="s">
+        <v>17</v>
+      </c>
+      <c r="CO6" t="s">
+        <v>32</v>
+      </c>
+      <c r="CP6" t="s">
+        <v>10</v>
+      </c>
+      <c r="CQ6" t="s">
+        <v>17</v>
+      </c>
+      <c r="CR6" t="s">
+        <v>32</v>
+      </c>
+      <c r="CS6" t="s">
+        <v>17</v>
+      </c>
+      <c r="CT6" t="s">
+        <v>32</v>
+      </c>
+      <c r="CU6" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -7869,8 +8217,32 @@
       <c r="CM7" t="s">
         <v>8</v>
       </c>
+      <c r="CN7" t="s">
+        <v>10</v>
+      </c>
+      <c r="CO7" t="s">
+        <v>8</v>
+      </c>
+      <c r="CP7" t="s">
+        <v>4</v>
+      </c>
+      <c r="CQ7" t="s">
+        <v>32</v>
+      </c>
+      <c r="CR7" t="s">
+        <v>10</v>
+      </c>
+      <c r="CS7" t="s">
+        <v>8</v>
+      </c>
+      <c r="CT7" t="s">
+        <v>10</v>
+      </c>
+      <c r="CU7" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -8081,8 +8453,26 @@
       <c r="CM8" t="s">
         <v>11</v>
       </c>
+      <c r="CN8" t="s">
+        <v>6</v>
+      </c>
+      <c r="CP8" t="s">
+        <v>28</v>
+      </c>
+      <c r="CQ8" t="s">
+        <v>1</v>
+      </c>
+      <c r="CR8" t="s">
+        <v>28</v>
+      </c>
+      <c r="CS8" t="s">
+        <v>6</v>
+      </c>
+      <c r="CT8" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -8293,8 +8683,26 @@
       <c r="CM9" t="s">
         <v>2</v>
       </c>
+      <c r="CN9" t="s">
+        <v>33</v>
+      </c>
+      <c r="CP9" t="s">
+        <v>33</v>
+      </c>
+      <c r="CQ9" t="s">
+        <v>0</v>
+      </c>
+      <c r="CR9" t="s">
+        <v>33</v>
+      </c>
+      <c r="CS9" t="s">
+        <v>3</v>
+      </c>
+      <c r="CT9" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>42</v>
       </c>
@@ -8505,8 +8913,26 @@
       <c r="CM10" t="s">
         <v>32</v>
       </c>
+      <c r="CN10" t="s">
+        <v>27</v>
+      </c>
+      <c r="CP10" t="s">
+        <v>27</v>
+      </c>
+      <c r="CQ10" t="s">
+        <v>14</v>
+      </c>
+      <c r="CR10" t="s">
+        <v>20</v>
+      </c>
+      <c r="CS10" t="s">
+        <v>14</v>
+      </c>
+      <c r="CT10" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -8717,8 +9143,26 @@
       <c r="CM11" t="s">
         <v>10</v>
       </c>
+      <c r="CN11" t="s">
+        <v>20</v>
+      </c>
+      <c r="CP11" t="s">
+        <v>20</v>
+      </c>
+      <c r="CQ11" t="s">
+        <v>8</v>
+      </c>
+      <c r="CR11" t="s">
+        <v>4</v>
+      </c>
+      <c r="CS11" t="s">
+        <v>27</v>
+      </c>
+      <c r="CT11" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:92" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>1</v>
       </c>
@@ -8753,7 +9197,7 @@
         <v>29</v>
       </c>
       <c r="T12" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="V12" t="s">
         <v>1</v>
@@ -8896,8 +9340,11 @@
       <c r="CM12" t="s">
         <v>1</v>
       </c>
+      <c r="CN12" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:92" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -9075,8 +9522,11 @@
       <c r="CM13" t="s">
         <v>3</v>
       </c>
+      <c r="CN13" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:92" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -9254,8 +9704,11 @@
       <c r="CM14" t="s">
         <v>14</v>
       </c>
+      <c r="CN14" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:92" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>48</v>
       </c>
@@ -9431,6 +9884,9 @@
         <v>13</v>
       </c>
       <c r="CM15" t="s">
+        <v>4</v>
+      </c>
+      <c r="CN15" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9466,7 +9922,7 @@
         <v>33</v>
       </c>
       <c r="R16" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="T16" t="s">
         <v>11</v>
@@ -10175,7 +10631,7 @@
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="C21" t="s">
         <v>5</v>
@@ -10884,7 +11340,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:CM1898"/>
+  <dimension ref="A3:CU1898"/>
   <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="55.28515625" customWidth="1"/>
@@ -10968,7 +11424,7 @@
     <col min="99" max="99" width="47.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>52</v>
       </c>
@@ -11228,1065 +11684,1134 @@
         <v>138</v>
       </c>
       <c r="CI3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="CJ3" t="s">
         <v>140</v>
       </c>
       <c r="CK3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="CL3" t="s">
         <v>136</v>
       </c>
       <c r="CM3" t="s">
+        <v>145</v>
+      </c>
+      <c r="CN3" t="s">
+        <v>141</v>
+      </c>
+      <c r="CO3" t="s">
+        <v>147</v>
+      </c>
+      <c r="CP3" t="s">
         <v>143</v>
       </c>
+      <c r="CQ3" t="s">
+        <v>149</v>
+      </c>
+      <c r="CR3" t="s">
+        <v>146</v>
+      </c>
+      <c r="CS3" t="s">
+        <v>150</v>
+      </c>
+      <c r="CT3" t="s">
+        <v>148</v>
+      </c>
+      <c r="CU3" t="s">
+        <v>151</v>
+      </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="B4" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="C4" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="D4" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="E4" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="F4" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="G4" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="H4" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="I4" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="J4" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="K4" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="L4" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="M4" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="N4" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="O4" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="P4" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="Q4" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="R4" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="S4" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="T4" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="U4" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="V4" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="W4" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="X4" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="Y4" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="Z4" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="AA4" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="AB4" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="AC4" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="AD4" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="AE4" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="AF4" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="AG4" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="AH4" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="AI4" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="AJ4" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="AK4" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="AL4" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="AM4" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="AN4" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="AO4" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="AP4" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="AQ4" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="AR4" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="AS4" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="AT4" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="AU4" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="AV4" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="AW4" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="AX4" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="AY4" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="AZ4" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="BA4" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="BB4" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="BC4" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="BD4" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="BE4" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="BF4" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="BG4" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="BH4" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="BI4" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="BJ4" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="BK4" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="BL4" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="BM4" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="BN4" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="BO4" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="BP4" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="BQ4" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="BR4" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="BS4" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="BT4" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="BU4" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="BV4" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="BW4" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="BX4" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="BY4" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="BZ4" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="CA4" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="CB4" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="CC4" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="CD4" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="CE4" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="CF4" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="CG4" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="CH4" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="CI4" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="CJ4" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="CK4" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="CL4" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="CM4" t="s">
-        <v>235</v>
+        <v>243</v>
+      </c>
+      <c r="CN4" t="s">
+        <v>244</v>
+      </c>
+      <c r="CO4" t="s">
+        <v>245</v>
+      </c>
+      <c r="CP4" t="s">
+        <v>246</v>
+      </c>
+      <c r="CQ4" t="s">
+        <v>247</v>
+      </c>
+      <c r="CR4" t="s">
+        <v>248</v>
+      </c>
+      <c r="CS4" t="s">
+        <v>249</v>
+      </c>
+      <c r="CT4" t="s">
+        <v>250</v>
+      </c>
+      <c r="CU4" t="s">
+        <v>251</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="C5" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="E5" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="F5" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="G5" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="H5" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="J5" t="s">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="K5" t="s">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="L5" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="M5" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="O5" t="s">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="Q5" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="R5" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="T5" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="V5" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="W5" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="X5" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="Y5" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="Z5" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="AA5" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="AB5" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="AC5" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="AD5" t="s">
+        <v>274</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>275</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>276</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>277</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>278</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>279</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>280</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>281</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>282</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>282</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>283</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>284</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>282</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>285</v>
+      </c>
+      <c r="AU5" t="s">
         <v>258</v>
       </c>
-      <c r="AE5" t="s">
-        <v>259</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>260</v>
-      </c>
-      <c r="AH5" t="s">
-        <v>261</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>262</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>263</v>
-      </c>
-      <c r="AK5" t="s">
-        <v>264</v>
-      </c>
-      <c r="AL5" t="s">
-        <v>265</v>
-      </c>
-      <c r="AN5" t="s">
-        <v>266</v>
-      </c>
-      <c r="AO5" t="s">
-        <v>266</v>
-      </c>
-      <c r="AQ5" t="s">
-        <v>267</v>
-      </c>
-      <c r="AR5" t="s">
-        <v>268</v>
-      </c>
-      <c r="AS5" t="s">
-        <v>266</v>
-      </c>
-      <c r="AT5" t="s">
-        <v>269</v>
-      </c>
-      <c r="AU5" t="s">
-        <v>242</v>
-      </c>
       <c r="AV5" t="s">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="AW5" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="AX5" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="AY5" t="s">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="AZ5" t="s">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="BA5" t="s">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="BC5" t="s">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="BD5" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="BE5" t="s">
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="BF5" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="BG5" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="BH5" t="s">
-        <v>281</v>
+        <v>297</v>
       </c>
       <c r="BI5" t="s">
+        <v>298</v>
+      </c>
+      <c r="BJ5" t="s">
+        <v>299</v>
+      </c>
+      <c r="BM5" t="s">
+        <v>300</v>
+      </c>
+      <c r="BN5" t="s">
+        <v>301</v>
+      </c>
+      <c r="BO5" t="s">
+        <v>302</v>
+      </c>
+      <c r="BP5" t="s">
+        <v>303</v>
+      </c>
+      <c r="BQ5" t="s">
+        <v>304</v>
+      </c>
+      <c r="BS5" t="s">
+        <v>305</v>
+      </c>
+      <c r="BT5" t="s">
+        <v>306</v>
+      </c>
+      <c r="BU5" t="s">
+        <v>307</v>
+      </c>
+      <c r="BW5" t="s">
+        <v>308</v>
+      </c>
+      <c r="BY5" t="s">
+        <v>309</v>
+      </c>
+      <c r="CA5" t="s">
+        <v>310</v>
+      </c>
+      <c r="CC5" t="s">
+        <v>311</v>
+      </c>
+      <c r="CD5" t="s">
+        <v>312</v>
+      </c>
+      <c r="CE5" t="s">
+        <v>313</v>
+      </c>
+      <c r="CG5" t="s">
+        <v>314</v>
+      </c>
+      <c r="CH5" t="s">
+        <v>315</v>
+      </c>
+      <c r="CJ5" t="s">
+        <v>316</v>
+      </c>
+      <c r="CL5" t="s">
+        <v>317</v>
+      </c>
+      <c r="CM5" t="s">
+        <v>318</v>
+      </c>
+      <c r="CN5" t="s">
+        <v>319</v>
+      </c>
+      <c r="CP5" t="s">
+        <v>320</v>
+      </c>
+      <c r="CQ5" t="s">
+        <v>321</v>
+      </c>
+      <c r="CR5" t="s">
+        <v>322</v>
+      </c>
+      <c r="CS5" t="s">
+        <v>323</v>
+      </c>
+      <c r="CT5" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" spans="1:92" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>325</v>
+      </c>
+      <c r="C6" t="s">
+        <v>326</v>
+      </c>
+      <c r="E6" t="s">
+        <v>327</v>
+      </c>
+      <c r="F6" t="s">
+        <v>328</v>
+      </c>
+      <c r="H6" t="s">
+        <v>329</v>
+      </c>
+      <c r="J6" t="s">
+        <v>330</v>
+      </c>
+      <c r="K6" t="s">
+        <v>331</v>
+      </c>
+      <c r="M6" t="s">
+        <v>332</v>
+      </c>
+      <c r="O6" t="s">
+        <v>333</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>334</v>
+      </c>
+      <c r="R6" t="s">
+        <v>335</v>
+      </c>
+      <c r="T6" t="s">
+        <v>336</v>
+      </c>
+      <c r="V6" t="s">
+        <v>337</v>
+      </c>
+      <c r="W6" t="s">
+        <v>338</v>
+      </c>
+      <c r="X6" t="s">
+        <v>339</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>341</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>342</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>343</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>344</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>345</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>346</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>347</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>348</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>349</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>350</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>351</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>352</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>353</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>354</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>355</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>356</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>357</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>358</v>
+      </c>
+      <c r="AW6" t="s">
         <v>282</v>
       </c>
-      <c r="BJ5" t="s">
-        <v>283</v>
-      </c>
-      <c r="BM5" t="s">
-        <v>284</v>
-      </c>
-      <c r="BN5" t="s">
-        <v>285</v>
-      </c>
-      <c r="BO5" t="s">
-        <v>286</v>
-      </c>
-      <c r="BP5" t="s">
-        <v>287</v>
-      </c>
-      <c r="BQ5" t="s">
-        <v>288</v>
-      </c>
-      <c r="BS5" t="s">
-        <v>289</v>
-      </c>
-      <c r="BT5" t="s">
-        <v>290</v>
-      </c>
-      <c r="BU5" t="s">
-        <v>291</v>
-      </c>
-      <c r="BW5" t="s">
-        <v>292</v>
-      </c>
-      <c r="BY5" t="s">
-        <v>293</v>
-      </c>
-      <c r="CA5" t="s">
-        <v>294</v>
-      </c>
-      <c r="CC5" t="s">
-        <v>295</v>
-      </c>
-      <c r="CD5" t="s">
-        <v>296</v>
-      </c>
-      <c r="CE5" t="s">
-        <v>297</v>
-      </c>
-      <c r="CG5" t="s">
-        <v>298</v>
-      </c>
-      <c r="CH5" t="s">
-        <v>299</v>
-      </c>
-      <c r="CJ5" t="s">
-        <v>300</v>
-      </c>
-      <c r="CL5" t="s">
-        <v>301</v>
-      </c>
-      <c r="CM5" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>303</v>
-      </c>
-      <c r="C6" t="s">
-        <v>304</v>
-      </c>
-      <c r="E6" t="s">
-        <v>305</v>
-      </c>
-      <c r="F6" t="s">
-        <v>306</v>
-      </c>
-      <c r="H6" t="s">
-        <v>307</v>
-      </c>
-      <c r="J6" t="s">
-        <v>308</v>
-      </c>
-      <c r="K6" t="s">
-        <v>309</v>
-      </c>
-      <c r="M6" t="s">
-        <v>310</v>
-      </c>
-      <c r="O6" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>312</v>
-      </c>
-      <c r="R6" t="s">
-        <v>313</v>
-      </c>
-      <c r="T6" t="s">
-        <v>314</v>
-      </c>
-      <c r="V6" t="s">
-        <v>315</v>
-      </c>
-      <c r="W6" t="s">
-        <v>316</v>
-      </c>
-      <c r="X6" t="s">
-        <v>317</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>318</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>319</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>320</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>321</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>322</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>323</v>
-      </c>
-      <c r="AH6" t="s">
-        <v>324</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>325</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>326</v>
-      </c>
-      <c r="AK6" t="s">
-        <v>327</v>
-      </c>
-      <c r="AL6" t="s">
-        <v>328</v>
-      </c>
-      <c r="AN6" t="s">
-        <v>329</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>330</v>
-      </c>
-      <c r="AQ6" t="s">
-        <v>331</v>
-      </c>
-      <c r="AR6" t="s">
-        <v>332</v>
-      </c>
-      <c r="AS6" t="s">
-        <v>333</v>
-      </c>
-      <c r="AT6" t="s">
-        <v>334</v>
-      </c>
-      <c r="AU6" t="s">
-        <v>335</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>336</v>
-      </c>
-      <c r="AW6" t="s">
-        <v>266</v>
-      </c>
       <c r="AX6" t="s">
-        <v>337</v>
+        <v>359</v>
       </c>
       <c r="AY6" t="s">
-        <v>338</v>
+        <v>360</v>
       </c>
       <c r="AZ6" t="s">
-        <v>339</v>
+        <v>361</v>
       </c>
       <c r="BA6" t="s">
-        <v>340</v>
+        <v>362</v>
       </c>
       <c r="BC6" t="s">
-        <v>341</v>
+        <v>363</v>
       </c>
       <c r="BD6" t="s">
-        <v>342</v>
+        <v>364</v>
       </c>
       <c r="BE6" t="s">
-        <v>343</v>
+        <v>365</v>
       </c>
       <c r="BF6" t="s">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="BG6" t="s">
-        <v>345</v>
+        <v>367</v>
       </c>
       <c r="BI6" t="s">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="BJ6" t="s">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="BN6" t="s">
-        <v>348</v>
+        <v>370</v>
       </c>
       <c r="BP6" t="s">
-        <v>349</v>
+        <v>371</v>
       </c>
       <c r="BQ6" t="s">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="BS6" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="BU6" t="s">
-        <v>352</v>
+        <v>374</v>
       </c>
       <c r="BW6" t="s">
-        <v>353</v>
+        <v>375</v>
       </c>
       <c r="BY6" t="s">
-        <v>354</v>
+        <v>376</v>
       </c>
       <c r="CA6" t="s">
-        <v>355</v>
+        <v>377</v>
       </c>
       <c r="CC6" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="CG6" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="CH6" t="s">
-        <v>358</v>
+        <v>380</v>
       </c>
       <c r="CJ6" t="s">
-        <v>359</v>
+        <v>381</v>
       </c>
       <c r="CL6" t="s">
-        <v>360</v>
+        <v>382</v>
       </c>
       <c r="CM6" t="s">
-        <v>266</v>
+        <v>282</v>
+      </c>
+      <c r="CN6" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>361</v>
+        <v>384</v>
       </c>
       <c r="C7" t="s">
-        <v>362</v>
+        <v>385</v>
       </c>
       <c r="E7" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="F7" t="s">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="H7" t="s">
-        <v>365</v>
+        <v>388</v>
       </c>
       <c r="J7" t="s">
-        <v>366</v>
+        <v>389</v>
       </c>
       <c r="K7" t="s">
-        <v>367</v>
+        <v>390</v>
       </c>
       <c r="M7" t="s">
-        <v>368</v>
+        <v>391</v>
       </c>
       <c r="O7" t="s">
-        <v>369</v>
+        <v>392</v>
       </c>
       <c r="Q7" t="s">
-        <v>370</v>
+        <v>393</v>
       </c>
       <c r="R7" t="s">
-        <v>371</v>
+        <v>394</v>
       </c>
       <c r="T7" t="s">
-        <v>372</v>
+        <v>395</v>
       </c>
       <c r="V7" t="s">
-        <v>373</v>
+        <v>396</v>
       </c>
       <c r="X7" t="s">
-        <v>374</v>
+        <v>397</v>
       </c>
       <c r="Z7" t="s">
-        <v>375</v>
+        <v>398</v>
       </c>
       <c r="AA7" t="s">
-        <v>376</v>
+        <v>399</v>
       </c>
       <c r="AB7" t="s">
-        <v>377</v>
+        <v>400</v>
       </c>
       <c r="AD7" t="s">
-        <v>378</v>
+        <v>401</v>
       </c>
       <c r="AE7" t="s">
-        <v>379</v>
+        <v>402</v>
       </c>
       <c r="AF7" t="s">
-        <v>380</v>
+        <v>403</v>
       </c>
       <c r="AH7" t="s">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="AI7" t="s">
-        <v>382</v>
+        <v>405</v>
       </c>
       <c r="AJ7" t="s">
-        <v>383</v>
+        <v>406</v>
       </c>
       <c r="AN7" t="s">
-        <v>384</v>
+        <v>407</v>
       </c>
       <c r="AO7" t="s">
-        <v>385</v>
+        <v>408</v>
       </c>
       <c r="AQ7" t="s">
-        <v>386</v>
+        <v>409</v>
       </c>
       <c r="AR7" t="s">
-        <v>387</v>
+        <v>410</v>
       </c>
       <c r="AU7" t="s">
-        <v>388</v>
+        <v>411</v>
       </c>
       <c r="AV7" t="s">
-        <v>389</v>
+        <v>412</v>
       </c>
       <c r="AW7" t="s">
-        <v>390</v>
+        <v>413</v>
       </c>
       <c r="AX7" t="s">
-        <v>391</v>
+        <v>414</v>
       </c>
       <c r="AY7" t="s">
-        <v>392</v>
+        <v>415</v>
       </c>
       <c r="AZ7" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="BA7" t="s">
-        <v>394</v>
+        <v>417</v>
       </c>
       <c r="BC7" t="s">
-        <v>395</v>
+        <v>418</v>
       </c>
       <c r="BD7" t="s">
-        <v>396</v>
+        <v>419</v>
       </c>
       <c r="BE7" t="s">
-        <v>397</v>
+        <v>420</v>
       </c>
       <c r="BF7" t="s">
-        <v>398</v>
+        <v>421</v>
       </c>
       <c r="BG7" t="s">
-        <v>399</v>
+        <v>422</v>
       </c>
       <c r="BI7" t="s">
-        <v>400</v>
+        <v>423</v>
       </c>
       <c r="BN7" t="s">
-        <v>401</v>
+        <v>424</v>
       </c>
       <c r="BP7" t="s">
-        <v>402</v>
+        <v>425</v>
       </c>
       <c r="BQ7" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="BS7" t="s">
-        <v>404</v>
+        <v>427</v>
       </c>
       <c r="BU7" t="s">
-        <v>405</v>
+        <v>428</v>
       </c>
       <c r="BW7" t="s">
-        <v>406</v>
+        <v>429</v>
       </c>
       <c r="BY7" t="s">
-        <v>407</v>
+        <v>430</v>
       </c>
       <c r="CA7" t="s">
-        <v>408</v>
+        <v>431</v>
       </c>
       <c r="CC7" t="s">
-        <v>409</v>
+        <v>432</v>
       </c>
       <c r="CG7" t="s">
-        <v>410</v>
+        <v>433</v>
       </c>
       <c r="CH7" t="s">
-        <v>411</v>
+        <v>434</v>
       </c>
       <c r="CM7" t="s">
-        <v>412</v>
+        <v>435</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>413</v>
+        <v>436</v>
       </c>
       <c r="C8" t="s">
-        <v>414</v>
+        <v>437</v>
       </c>
       <c r="E8" t="s">
-        <v>415</v>
+        <v>438</v>
       </c>
       <c r="F8" t="s">
-        <v>416</v>
+        <v>439</v>
       </c>
       <c r="H8" t="s">
-        <v>417</v>
+        <v>440</v>
       </c>
       <c r="K8" t="s">
-        <v>418</v>
+        <v>441</v>
       </c>
       <c r="O8" t="s">
-        <v>419</v>
+        <v>442</v>
       </c>
       <c r="Q8" t="s">
-        <v>420</v>
+        <v>443</v>
       </c>
       <c r="R8" t="s">
-        <v>421</v>
+        <v>444</v>
       </c>
       <c r="T8" t="s">
-        <v>422</v>
+        <v>445</v>
       </c>
       <c r="X8" t="s">
-        <v>423</v>
+        <v>446</v>
       </c>
       <c r="AA8" t="s">
-        <v>424</v>
+        <v>447</v>
       </c>
       <c r="AB8" t="s">
-        <v>425</v>
+        <v>448</v>
       </c>
       <c r="AE8" t="s">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="AF8" t="s">
-        <v>426</v>
+        <v>449</v>
       </c>
       <c r="AH8" t="s">
-        <v>427</v>
+        <v>450</v>
       </c>
       <c r="AI8" t="s">
-        <v>428</v>
+        <v>451</v>
       </c>
       <c r="AJ8" t="s">
-        <v>429</v>
+        <v>452</v>
       </c>
       <c r="AN8" t="s">
-        <v>430</v>
+        <v>453</v>
       </c>
       <c r="AO8" t="s">
-        <v>431</v>
+        <v>454</v>
       </c>
       <c r="AQ8" t="s">
-        <v>432</v>
+        <v>455</v>
       </c>
       <c r="AR8" t="s">
-        <v>433</v>
+        <v>456</v>
       </c>
       <c r="AU8" t="s">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="AV8" t="s">
-        <v>434</v>
+        <v>457</v>
       </c>
       <c r="AW8" t="s">
-        <v>435</v>
+        <v>458</v>
       </c>
       <c r="AX8" t="s">
-        <v>436</v>
+        <v>459</v>
       </c>
       <c r="AY8" t="s">
-        <v>437</v>
+        <v>460</v>
       </c>
       <c r="AZ8" t="s">
-        <v>438</v>
+        <v>461</v>
       </c>
       <c r="BA8" t="s">
-        <v>439</v>
+        <v>462</v>
       </c>
       <c r="BC8" t="s">
-        <v>440</v>
+        <v>463</v>
       </c>
       <c r="BD8" t="s">
-        <v>441</v>
+        <v>464</v>
       </c>
       <c r="BE8" t="s">
-        <v>442</v>
+        <v>465</v>
       </c>
       <c r="BF8" t="s">
-        <v>443</v>
+        <v>466</v>
       </c>
       <c r="BG8" t="s">
-        <v>444</v>
+        <v>467</v>
       </c>
       <c r="BI8" t="s">
-        <v>445</v>
+        <v>468</v>
       </c>
       <c r="BN8" t="s">
-        <v>446</v>
+        <v>469</v>
       </c>
       <c r="BQ8" t="s">
-        <v>447</v>
+        <v>470</v>
       </c>
       <c r="BS8" t="s">
-        <v>448</v>
+        <v>471</v>
       </c>
       <c r="BW8" t="s">
-        <v>449</v>
+        <v>472</v>
       </c>
       <c r="BY8" t="s">
-        <v>450</v>
+        <v>473</v>
       </c>
       <c r="CA8" t="s">
-        <v>451</v>
+        <v>474</v>
       </c>
       <c r="CC8" t="s">
-        <v>452</v>
+        <v>475</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>453</v>
+        <v>476</v>
       </c>
       <c r="E9" t="s">
-        <v>454</v>
+        <v>477</v>
       </c>
       <c r="F9" t="s">
-        <v>455</v>
+        <v>478</v>
       </c>
       <c r="H9" t="s">
-        <v>456</v>
+        <v>479</v>
       </c>
       <c r="O9" t="s">
-        <v>457</v>
+        <v>480</v>
       </c>
       <c r="T9" t="s">
-        <v>458</v>
+        <v>481</v>
       </c>
       <c r="X9" t="s">
-        <v>459</v>
+        <v>482</v>
       </c>
       <c r="AB9" t="s">
-        <v>460</v>
+        <v>483</v>
       </c>
       <c r="AF9" t="s">
-        <v>461</v>
+        <v>484</v>
       </c>
       <c r="AI9" t="s">
-        <v>462</v>
+        <v>485</v>
       </c>
       <c r="AJ9" t="s">
-        <v>463</v>
+        <v>486</v>
       </c>
       <c r="AO9" t="s">
-        <v>464</v>
+        <v>487</v>
       </c>
       <c r="AV9" t="s">
-        <v>465</v>
+        <v>488</v>
       </c>
       <c r="AW9" t="s">
-        <v>466</v>
+        <v>489</v>
       </c>
       <c r="AX9" t="s">
-        <v>467</v>
+        <v>490</v>
       </c>
       <c r="AY9" t="s">
-        <v>468</v>
+        <v>491</v>
       </c>
       <c r="AZ9" t="s">
-        <v>469</v>
+        <v>492</v>
       </c>
       <c r="BA9" t="s">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="BC9" t="s">
-        <v>471</v>
+        <v>494</v>
       </c>
       <c r="BD9" t="s">
-        <v>472</v>
+        <v>495</v>
       </c>
       <c r="BE9" t="s">
-        <v>473</v>
+        <v>496</v>
       </c>
       <c r="BF9" t="s">
-        <v>474</v>
+        <v>497</v>
       </c>
       <c r="BG9" t="s">
-        <v>475</v>
+        <v>498</v>
       </c>
       <c r="BN9" t="s">
-        <v>476</v>
+        <v>499</v>
       </c>
       <c r="BQ9" t="s">
-        <v>477</v>
+        <v>500</v>
       </c>
       <c r="BY9" t="s">
-        <v>478</v>
+        <v>501</v>
       </c>
       <c r="CC9" t="s">
-        <v>479</v>
+        <v>502</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="41:49" x14ac:dyDescent="0.25">
       <c r="AO10" t="s">
-        <v>480</v>
+        <v>503</v>
       </c>
       <c r="AW10" t="s">
-        <v>481</v>
+        <v>504</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/data/ICEHLdelegacije.xlsx
+++ b/data/ICEHLdelegacije.xlsx
@@ -1,47 +1,310 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FC0EB7B-8288-4865-9566-0B504CD5FABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
-    <sheet name="ICEHL" sheetId="1" r:id="rId1"/>
-    <sheet name="ICEHL_DAT" sheetId="3" r:id="rId2"/>
-    <sheet name="ICEHL_DAT_STRING" sheetId="4" r:id="rId3"/>
+    <sheet sheetId="1" name="ICEHL" state="visible" r:id="rId4"/>
+    <sheet sheetId="3" name="ICEHL_DAT" state="visible" r:id="rId5"/>
+    <sheet sheetId="4" name="ICEHL_DAT_STRING" state="visible" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="92">
+  <si>
+    <t>SternatCh</t>
+  </si>
+  <si>
+    <t>SmetanaLa</t>
+  </si>
+  <si>
+    <t>OfnerCh</t>
+  </si>
+  <si>
+    <t>NikolicMa</t>
+  </si>
+  <si>
+    <t>DurmisOt</t>
+  </si>
+  <si>
+    <t>KoncDa</t>
+  </si>
+  <si>
+    <t>PiragicTr</t>
+  </si>
+  <si>
+    <t>SeewaldEl</t>
+  </si>
+  <si>
+    <t>ZrnicMi</t>
+  </si>
+  <si>
+    <t>BärnthalerCh</t>
+  </si>
+  <si>
+    <t>BedynekSe</t>
+  </si>
+  <si>
+    <t>PuffWo</t>
+  </si>
+  <si>
+    <t>RezekGr</t>
+  </si>
+  <si>
+    <t>RieckenSi</t>
+  </si>
+  <si>
+    <t>HronskyTo</t>
+  </si>
+  <si>
+    <t>JedlickaPe</t>
+  </si>
+  <si>
+    <t>SoosDa</t>
+  </si>
+  <si>
+    <t>ZgoncGa</t>
+  </si>
+  <si>
+    <t>NikolicKr</t>
+  </si>
+  <si>
+    <t>FleischmannLu</t>
+  </si>
+  <si>
+    <t>HribarMa</t>
+  </si>
+  <si>
+    <t>KainbergerJu</t>
+  </si>
+  <si>
+    <t>NagyAt</t>
+  </si>
+  <si>
+    <t>GroznikBo</t>
+  </si>
+  <si>
+    <t>SchauerJa</t>
+  </si>
+  <si>
+    <t>MartinFl</t>
+  </si>
+  <si>
+    <t>HolzerTo</t>
+  </si>
+  <si>
+    <t>WeissAl</t>
+  </si>
+  <si>
+    <t>FichtnerPa</t>
+  </si>
+  <si>
+    <t>Gatol-schafranekMa</t>
+  </si>
+  <si>
+    <t>SeewaldJe</t>
+  </si>
+  <si>
+    <t>MuzsikNo</t>
+  </si>
+  <si>
+    <t>VacziDa</t>
+  </si>
+  <si>
+    <t>PardatscherUl</t>
+  </si>
+  <si>
+    <t>HlavatyAl</t>
+  </si>
+  <si>
+    <t>MoidlMa</t>
+  </si>
+  <si>
+    <t>MantovaniDa</t>
+  </si>
+  <si>
+    <t>SparerDa</t>
+  </si>
+  <si>
+    <t>RigoniDa</t>
+  </si>
+  <si>
+    <t>JeramFi</t>
+  </si>
+  <si>
+    <t>VoicanCh</t>
+  </si>
+  <si>
+    <t>WimmlerAl</t>
+  </si>
+  <si>
+    <t>ZacherlPa</t>
+  </si>
+  <si>
+    <t>NotheggerDa</t>
+  </si>
+  <si>
+    <t>Huber aAn</t>
+  </si>
+  <si>
+    <t>LinesmanZw</t>
+  </si>
+  <si>
+    <t>2025-09-12</t>
+  </si>
+  <si>
+    <t>2025-09-14</t>
+  </si>
+  <si>
+    <t>zbrisano</t>
+  </si>
+  <si>
+    <t>2025-09-19</t>
+  </si>
+  <si>
+    <t>2025-09-21</t>
+  </si>
+  <si>
+    <t>2025-09-26</t>
+  </si>
+  <si>
+    <t>2025-09-27</t>
+  </si>
+  <si>
+    <t>2025-09-28</t>
+  </si>
+  <si>
+    <t>2025-09-20</t>
+  </si>
+  <si>
+    <t>2025-09-23</t>
+  </si>
+  <si>
+    <t>FTC-Telekom Rink;HronskyTo;SmetanaLa;JedlickaPe;MuzsikNo</t>
+  </si>
+  <si>
+    <t>Eishalle Feldkirch;NikolicKr;SchauerJa;MartinFl;SparerDa</t>
+  </si>
+  <si>
+    <t>FTC-Telekom Rink;PiragicTr;ZrnicMi;DurmisOt;KoncDa</t>
+  </si>
+  <si>
+    <t>Gabor Ocskay Eisarena;PiragicTr;ZrnicMi;DurmisOt;KoncDa</t>
+  </si>
+  <si>
+    <t>ZBRISANO</t>
+  </si>
+  <si>
+    <t>Heidi Horten Arena Klagenfurt;FichtnerPa;GroznikBo;HribarMa;PuffWo</t>
+  </si>
+  <si>
+    <t>Tiroler Wasserkraft Arena;HolzerTo;OfnerCh;SparerDa;WeissAl</t>
+  </si>
+  <si>
+    <t>Merkur Eisstadion Graz;NagyAt;SoosDa;BärnthalerCh;BedynekSe</t>
+  </si>
+  <si>
+    <t>Merkur Eisstadion Graz;NikolicMa;VoicanCh;BärnthalerCh;Gatol-schafranekMa</t>
+  </si>
+  <si>
+    <t>Hala Tivoli;SoosDa;SternatCh;VacziDa;ZgoncGa</t>
+  </si>
+  <si>
+    <t>Gabor Ocskay Eisarena;GroznikBo;RezekGr;DurmisOt;KoncDa</t>
+  </si>
+  <si>
+    <t>Merkur Eisstadion Graz;HronskyTo;KainbergerJu;JedlickaPe;ZgoncGa</t>
+  </si>
+  <si>
+    <t>Heidi Horten Arena Klagenfurt;Huber aAn;SeewaldEl;MantovaniDa;NotheggerDa</t>
+  </si>
+  <si>
+    <t>Linz AG Eisarena;SmetanaLa;SoosDa;BedynekSe;SeewaldJe</t>
+  </si>
+  <si>
+    <t>Eishalle Bruneck;NikolicMa;SternatCh;DurmisOt;KoncDa</t>
+  </si>
+  <si>
+    <t>Eisarena Salzburg;SeewaldEl;SmetanaLa;MoidlMa;SeewaldJe</t>
+  </si>
+  <si>
+    <t>Tiroler Wasserkraft Arena;NikolicKr;NikolicMa;FleischmannLu;PardatscherUl</t>
+  </si>
+  <si>
+    <t>Eisarena Salzburg;OfnerCh;SternatCh;BedynekSe;PuffWo</t>
+  </si>
+  <si>
+    <t>Eishalle Wien-Kagran;OfnerCh;VoicanCh;BärnthalerCh;WimmlerAl</t>
+  </si>
+  <si>
+    <t>Eishalle Wien-Kagran;HronskyTo;SternatCh;BedynekSe;JedlickaPe</t>
+  </si>
+  <si>
+    <t>Eishalle Feldkirch;HlavatyAl;PiragicTr;FleischmannLu;WimmlerAl</t>
+  </si>
+  <si>
+    <t>Sparkasse Arena Bozen;NikolicMa;SternatCh;FleischmannLu;WeissAl</t>
+  </si>
+  <si>
+    <t>Heidi Horten Arena Klagenfurt;HlavatyAl;ZrnicMi;BärnthalerCh;HribarMa</t>
+  </si>
+  <si>
+    <t>Eishalle Bruneck;HolzerTo;NikolicMa;RigoniDa;WeissAl</t>
+  </si>
+  <si>
+    <t>Eishalle Feldkirch;HolzerTo;SmetanaLa;MartinFl;RieckenSi</t>
+  </si>
+  <si>
+    <t>Stadthalle Villach;SchauerJa;SmetanaLa;JeramFi;ZgoncGa</t>
+  </si>
+  <si>
+    <t>Tiroler Wasserkraft Arena;KainbergerJu;OfnerCh;MantovaniDa;MartinFl</t>
+  </si>
+  <si>
+    <t>Hala Tivoli;PiragicTr;RezekGr;Gatol-schafranekMa;RieckenSi</t>
+  </si>
+  <si>
+    <t>Linz AG Eisarena;KainbergerJu;NagyAt;BedynekSe;Gatol-schafranekMa</t>
+  </si>
+  <si>
+    <t>Eishalle Wien-Kagran;FichtnerPa;SmetanaLa;Gatol-schafranekMa;RieckenSi</t>
+  </si>
+  <si>
+    <t>Eisarena Salzburg;NikolicMa;SternatCh;NotheggerDa;SeewaldEl</t>
+  </si>
+  <si>
+    <t>FTC-Telekom Rink;FichtnerPa;RezekGr;HribarMa;VacziDa</t>
+  </si>
+  <si>
+    <t>Sparkasse Arena Bozen;NikolicKr;SchauerJa;PardatscherUl;RigoniDa</t>
+  </si>
+  <si>
+    <t>Sparkasse Arena Bozen;GroznikBo;OfnerCh;MantovaniDa;PuffWo</t>
+  </si>
+  <si>
+    <t>Hala Tivoli;PiragicTr;ZrnicMi;HribarMa;JeramFi</t>
+  </si>
+  <si>
+    <t>Hala Tivoli;NagyAt;OfnerCh;MuzsikNo;PuffWo</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -345,9 +608,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A3:A134"/>
-  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A2:AU134"/>
+  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.28515625" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -404,16 +667,814 @@
     <col min="53" max="53" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" ht="14.45" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <f>COUNTIF(A4:A118,"&lt;&gt;")</f>
+        <v>7</v>
+      </c>
+      <c r="B2">
+        <f>COUNTIF(B4:B118,"&lt;&gt;")</f>
+        <v>6</v>
+      </c>
+      <c r="C2">
+        <f>COUNTIF(C4:C118,"&lt;&gt;")</f>
+        <v>6</v>
+      </c>
+      <c r="D2">
+        <f>COUNTIF(D4:D118,"&lt;&gt;")</f>
+        <v>6</v>
+      </c>
+      <c r="E2">
+        <f>COUNTIF(E4:E118,"&lt;&gt;")</f>
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <f>COUNTIF(F4:F118,"&lt;&gt;")</f>
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <f>COUNTIF(G4:G118,"&lt;&gt;")</f>
+        <v>5</v>
+      </c>
+      <c r="H2">
+        <f>COUNTIF(H4:H118,"&lt;&gt;")</f>
+        <v>4</v>
+      </c>
+      <c r="I2">
+        <f>COUNTIF(I4:I118,"&lt;&gt;")</f>
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <f>COUNTIF(J4:J118,"&lt;&gt;")</f>
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <f>COUNTIF(K4:K118,"&lt;&gt;")</f>
+        <v>4</v>
+      </c>
+      <c r="L2">
+        <f>COUNTIF(L4:L118,"&lt;&gt;")</f>
+        <v>4</v>
+      </c>
+      <c r="M2">
+        <f>COUNTIF(M4:M117,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="N2">
+        <f>COUNTIF(N4:N118,"&lt;&gt;")</f>
+        <v>4</v>
+      </c>
+      <c r="O2">
+        <f>COUNTIF(O4:O118,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="P2">
+        <f>COUNTIF(P4:P118,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="Q2">
+        <f>COUNTIF(Q4:Q118,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="R2">
+        <f>COUNTIF(R4:R118,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="S2">
+        <f>COUNTIF(S4:S118,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="T2">
+        <f>COUNTIF(T4:T118,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="U2">
+        <f>COUNTIF(U4:U118,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="V2">
+        <f>COUNTIF(V4:V118,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="W2">
+        <f>COUNTIF(W4:W118,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="X2">
+        <f>COUNTIF(X4:X118,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="Y2">
+        <f>COUNTIF(Y4:Y118,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="Z2">
+        <f>COUNTIF(Z4:Z118,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="AA2">
+        <f>COUNTIF(AA4:AA118,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="AB2">
+        <f>COUNTIF(AB4:AB118,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="AC2">
+        <f>COUNTIF(AC4:AC118,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="AD2">
+        <f>COUNTIF(AD4:AD118,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="AE2">
+        <f>COUNTIF(AE4:AE118,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="AF2">
+        <f>COUNTIF(AF4:AF118,"&lt;&gt;")</f>
+        <v>2</v>
+      </c>
+      <c r="AG2">
+        <f>COUNTIF(AG4:AG118,"&lt;&gt;")</f>
+        <v>2</v>
+      </c>
+      <c r="AH2">
+        <f>COUNTIF(AH4:AH118,"&lt;&gt;")</f>
+        <v>2</v>
+      </c>
+      <c r="AI2">
+        <f>COUNTIF(AI4:AI118,"&lt;&gt;")</f>
+        <v>2</v>
+      </c>
+      <c r="AJ2">
+        <f>COUNTIF(AJ4:AJ118,"&lt;&gt;")</f>
+        <v>2</v>
+      </c>
+      <c r="AK2">
+        <f>COUNTIF(AK4:AK118,"&lt;&gt;")</f>
+        <v>2</v>
+      </c>
+      <c r="AL2">
+        <f>COUNTIF(AL4:AL118,"&lt;&gt;")</f>
+        <v>2</v>
+      </c>
+      <c r="AM2">
+        <f>COUNTIF(AM4:AM118,"&lt;&gt;")</f>
+        <v>2</v>
+      </c>
+      <c r="AN2">
+        <f>COUNTIF(AN4:AN118,"&lt;&gt;")</f>
+        <v>2</v>
+      </c>
+      <c r="AO2">
+        <f>COUNTIF(AO4:AO118,"&lt;&gt;")</f>
+        <v>2</v>
+      </c>
+      <c r="AP2">
+        <f>COUNTIF(AP4:AP118,"&lt;&gt;")</f>
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <f>COUNTIF(AQ4:AQ118,"&lt;&gt;")</f>
+        <v>2</v>
+      </c>
+      <c r="AR2">
+        <f>COUNTIF(AR4:AR118,"&lt;&gt;")</f>
+        <v>2</v>
+      </c>
+      <c r="AS2">
+        <f>COUNTIF(AS4:AS118,"&lt;&gt;")</f>
+        <v>1</v>
+      </c>
+      <c r="AT2">
+        <f>COUNTIF(AT4:AT118,"&lt;&gt;")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R3" t="s">
+        <v>17</v>
+      </c>
+      <c r="S3" t="s">
+        <v>18</v>
+      </c>
+      <c r="T3" t="s">
+        <v>19</v>
+      </c>
+      <c r="U3" t="s">
+        <v>20</v>
+      </c>
+      <c r="V3" t="s">
+        <v>21</v>
+      </c>
+      <c r="W3" t="s">
+        <v>22</v>
+      </c>
+      <c r="X3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I4" t="s">
+        <v>46</v>
+      </c>
+      <c r="J4" t="s">
+        <v>46</v>
+      </c>
+      <c r="K4" t="s">
+        <v>46</v>
+      </c>
+      <c r="L4" t="s">
+        <v>46</v>
+      </c>
+      <c r="M4" t="s">
+        <v>47</v>
+      </c>
+      <c r="N4" t="s">
+        <v>47</v>
+      </c>
+      <c r="O4" t="s">
+        <v>46</v>
+      </c>
+      <c r="P4" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>46</v>
+      </c>
+      <c r="R4" t="s">
+        <v>46</v>
+      </c>
+      <c r="S4" t="s">
+        <v>46</v>
+      </c>
+      <c r="T4" t="s">
+        <v>46</v>
+      </c>
+      <c r="U4" t="s">
+        <v>46</v>
+      </c>
+      <c r="V4" t="s">
+        <v>46</v>
+      </c>
+      <c r="W4" t="s">
+        <v>46</v>
+      </c>
+      <c r="X4" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" t="s">
+        <v>49</v>
+      </c>
+      <c r="H5" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J5" t="s">
+        <v>49</v>
+      </c>
+      <c r="K5" t="s">
+        <v>47</v>
+      </c>
+      <c r="L5" t="s">
+        <v>47</v>
+      </c>
+      <c r="M5" t="s">
+        <v>50</v>
+      </c>
+      <c r="N5" t="s">
+        <v>49</v>
+      </c>
+      <c r="O5" t="s">
+        <v>49</v>
+      </c>
+      <c r="P5" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>51</v>
+      </c>
+      <c r="R5" t="s">
+        <v>49</v>
+      </c>
+      <c r="S5" t="s">
+        <v>47</v>
+      </c>
+      <c r="T5" t="s">
+        <v>51</v>
+      </c>
+      <c r="U5" t="s">
+        <v>47</v>
+      </c>
+      <c r="V5" t="s">
+        <v>49</v>
+      </c>
+      <c r="W5" t="s">
+        <v>50</v>
+      </c>
+      <c r="X5" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>51</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>53</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>52</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>51</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>51</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G6" t="s">
+        <v>54</v>
+      </c>
+      <c r="H6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I6" t="s">
+        <v>49</v>
+      </c>
+      <c r="J6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K6" t="s">
+        <v>50</v>
+      </c>
+      <c r="L6" t="s">
+        <v>50</v>
+      </c>
+      <c r="M6" t="s">
+        <v>53</v>
+      </c>
+      <c r="N6" t="s">
+        <v>48</v>
+      </c>
+      <c r="O6" t="s">
+        <v>50</v>
+      </c>
+      <c r="P6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>53</v>
+      </c>
+      <c r="R6" t="s">
+        <v>50</v>
+      </c>
+      <c r="S6" t="s">
+        <v>51</v>
+      </c>
+      <c r="T6" t="s">
+        <v>53</v>
+      </c>
+      <c r="U6" t="s">
+        <v>50</v>
+      </c>
+      <c r="V6" t="s">
+        <v>51</v>
+      </c>
+      <c r="W6" t="s">
+        <v>53</v>
+      </c>
+      <c r="X6" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>51</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>51</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H7" t="s">
+        <v>53</v>
+      </c>
+      <c r="I7" t="s">
+        <v>54</v>
+      </c>
+      <c r="J7" t="s">
+        <v>53</v>
+      </c>
+      <c r="K7" t="s">
+        <v>53</v>
+      </c>
+      <c r="L7" t="s">
+        <v>51</v>
+      </c>
+      <c r="N7" t="s">
+        <v>53</v>
+      </c>
+      <c r="U7" t="s">
+        <v>51</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J8" t="s">
+        <v>55</v>
+      </c>
+      <c r="K8" t="s">
+        <v>51</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" spans="4:4" x14ac:dyDescent="0.25"/>
     <row r="13" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="14" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="15" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -538,14 +1599,14 @@
     <row r="134" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A3:A42"/>
-  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A3:I42"/>
+  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="17.85546875" customWidth="1"/>
     <col min="2" max="2" width="12.85546875" customWidth="1"/>
@@ -577,32 +1638,516 @@
     <col min="98" max="98" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" t="s">
+        <v>0</v>
+      </c>
+      <c r="F9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" t="s">
+        <v>0</v>
+      </c>
+      <c r="H9" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" t="s">
+        <v>4</v>
+      </c>
+      <c r="H10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" t="s">
+        <v>5</v>
+      </c>
+      <c r="H11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" t="s">
+        <v>34</v>
+      </c>
+      <c r="H12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" t="s">
+        <v>6</v>
+      </c>
+      <c r="H13" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" t="s">
+        <v>41</v>
+      </c>
+      <c r="H15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" t="s">
+        <v>21</v>
+      </c>
+      <c r="H16" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H17" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" t="s">
+        <v>36</v>
+      </c>
+      <c r="H18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
+        <v>0</v>
+      </c>
+      <c r="E21" t="s">
+        <v>2</v>
+      </c>
+      <c r="F21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>10</v>
+      </c>
+      <c r="B22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" t="s">
+        <v>31</v>
+      </c>
+      <c r="F22" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>2</v>
+      </c>
+      <c r="B25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26" t="s">
+        <v>20</v>
+      </c>
+      <c r="F26" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" t="s">
+        <v>39</v>
+      </c>
+      <c r="F27" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25"/>
     <row r="29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -622,10 +2167,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A3:A1898"/>
-  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A3:I1898"/>
+  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="55.28515625" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -708,14 +2253,159 @@
     <col min="99" max="99" width="47.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H4" t="s">
+        <v>63</v>
+      </c>
+      <c r="I4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" t="s">
+        <v>69</v>
+      </c>
+      <c r="G5" t="s">
+        <v>70</v>
+      </c>
+      <c r="H5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F7" t="s">
+        <v>82</v>
+      </c>
+      <c r="H7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" t="s">
+        <v>86</v>
+      </c>
+      <c r="E8" t="s">
+        <v>87</v>
+      </c>
+      <c r="F8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E9" t="s">
+        <v>91</v>
+      </c>
+      <c r="F9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25"/>
     <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="13" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2606,6 +4296,6 @@
     <row r="1898" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/data/ICEHLdelegacije.xlsx
+++ b/data/ICEHLdelegacije.xlsx
@@ -16,20 +16,20 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="121">
   <si>
     <t>SternatCh</t>
   </si>
   <si>
+    <t>NikolicMa</t>
+  </si>
+  <si>
     <t>SmetanaLa</t>
   </si>
   <si>
     <t>OfnerCh</t>
   </si>
   <si>
-    <t>NikolicMa</t>
-  </si>
-  <si>
     <t>DurmisOt</t>
   </si>
   <si>
@@ -39,78 +39,87 @@
     <t>PiragicTr</t>
   </si>
   <si>
+    <t>PuffWo</t>
+  </si>
+  <si>
+    <t>JedlickaPe</t>
+  </si>
+  <si>
     <t>SeewaldEl</t>
   </si>
   <si>
     <t>ZrnicMi</t>
   </si>
   <si>
+    <t>BedynekSe</t>
+  </si>
+  <si>
+    <t>HronskyTo</t>
+  </si>
+  <si>
+    <t>ZgoncGa</t>
+  </si>
+  <si>
+    <t>HribarMa</t>
+  </si>
+  <si>
+    <t>KainbergerJu</t>
+  </si>
+  <si>
+    <t>HolzerTo</t>
+  </si>
+  <si>
+    <t>Gatol-schafranekMa</t>
+  </si>
+  <si>
+    <t>VoicanCh</t>
+  </si>
+  <si>
     <t>BärnthalerCh</t>
   </si>
   <si>
-    <t>BedynekSe</t>
-  </si>
-  <si>
-    <t>PuffWo</t>
+    <t>RieckenSi</t>
+  </si>
+  <si>
+    <t>NikolicKr</t>
+  </si>
+  <si>
+    <t>GroznikBo</t>
+  </si>
+  <si>
+    <t>MartinFl</t>
+  </si>
+  <si>
+    <t>WeissAl</t>
+  </si>
+  <si>
+    <t>FichtnerPa</t>
+  </si>
+  <si>
+    <t>SeewaldJe</t>
+  </si>
+  <si>
+    <t>HlavatyAl</t>
+  </si>
+  <si>
+    <t>MantovaniDa</t>
   </si>
   <si>
     <t>RezekGr</t>
   </si>
   <si>
-    <t>RieckenSi</t>
-  </si>
-  <si>
-    <t>HronskyTo</t>
-  </si>
-  <si>
-    <t>JedlickaPe</t>
-  </si>
-  <si>
     <t>SoosDa</t>
   </si>
   <si>
-    <t>ZgoncGa</t>
-  </si>
-  <si>
-    <t>NikolicKr</t>
-  </si>
-  <si>
     <t>FleischmannLu</t>
   </si>
   <si>
-    <t>HribarMa</t>
-  </si>
-  <si>
-    <t>KainbergerJu</t>
-  </si>
-  <si>
     <t>NagyAt</t>
   </si>
   <si>
-    <t>GroznikBo</t>
-  </si>
-  <si>
     <t>SchauerJa</t>
   </si>
   <si>
-    <t>MartinFl</t>
-  </si>
-  <si>
-    <t>HolzerTo</t>
-  </si>
-  <si>
-    <t>WeissAl</t>
-  </si>
-  <si>
-    <t>FichtnerPa</t>
-  </si>
-  <si>
-    <t>Gatol-schafranekMa</t>
-  </si>
-  <si>
-    <t>SeewaldJe</t>
-  </si>
-  <si>
     <t>MuzsikNo</t>
   </si>
   <si>
@@ -120,64 +129,58 @@
     <t>PardatscherUl</t>
   </si>
   <si>
-    <t>HlavatyAl</t>
+    <t>RigoniDa</t>
+  </si>
+  <si>
+    <t>JeramFi</t>
+  </si>
+  <si>
+    <t>NotheggerDa</t>
+  </si>
+  <si>
+    <t>Huber aAn</t>
+  </si>
+  <si>
+    <t>SparerDa</t>
+  </si>
+  <si>
+    <t>WimmlerAl</t>
   </si>
   <si>
     <t>MoidlMa</t>
   </si>
   <si>
-    <t>MantovaniDa</t>
-  </si>
-  <si>
-    <t>SparerDa</t>
-  </si>
-  <si>
-    <t>RigoniDa</t>
-  </si>
-  <si>
-    <t>JeramFi</t>
-  </si>
-  <si>
-    <t>VoicanCh</t>
-  </si>
-  <si>
-    <t>WimmlerAl</t>
-  </si>
-  <si>
     <t>ZacherlPa</t>
   </si>
   <si>
-    <t>NotheggerDa</t>
-  </si>
-  <si>
-    <t>Huber aAn</t>
-  </si>
-  <si>
-    <t>LinesmanZw</t>
-  </si>
-  <si>
     <t>2025-09-12</t>
   </si>
   <si>
     <t>2025-09-14</t>
   </si>
   <si>
+    <t>2025-09-19</t>
+  </si>
+  <si>
     <t>zbrisano</t>
   </si>
   <si>
-    <t>2025-09-19</t>
-  </si>
-  <si>
     <t>2025-09-21</t>
   </si>
   <si>
+    <t>2025-10-12</t>
+  </si>
+  <si>
+    <t>2025-09-28</t>
+  </si>
+  <si>
+    <t>2025-09-27</t>
+  </si>
+  <si>
     <t>2025-09-26</t>
   </si>
   <si>
-    <t>2025-09-27</t>
-  </si>
-  <si>
-    <t>2025-09-28</t>
+    <t>2025-10-03</t>
   </si>
   <si>
     <t>2025-09-20</t>
@@ -186,6 +189,18 @@
     <t>2025-09-23</t>
   </si>
   <si>
+    <t>2025-10-10</t>
+  </si>
+  <si>
+    <t>2025-10-05</t>
+  </si>
+  <si>
+    <t>2025-10-04</t>
+  </si>
+  <si>
+    <t>2025-10-11</t>
+  </si>
+  <si>
     <t>FTC-Telekom Rink;HronskyTo;SmetanaLa;JedlickaPe;MuzsikNo</t>
   </si>
   <si>
@@ -213,6 +228,24 @@
     <t>Merkur Eisstadion Graz;NikolicMa;VoicanCh;BärnthalerCh;Gatol-schafranekMa</t>
   </si>
   <si>
+    <t>Stadthalle Villach;HlavatyAl;KainbergerJu;JeramFi;WimmlerAl</t>
+  </si>
+  <si>
+    <t>Eishalle Wien-Kagran;PiragicTr;SmetanaLa;HribarMa;JedlickaPe</t>
+  </si>
+  <si>
+    <t>Eishalle Feldkirch;HolzerTo;NikolicMa;MartinFl;SparerDa</t>
+  </si>
+  <si>
+    <t>Merkur Eisstadion Graz;HlavatyAl;HronskyTo;DurmisOt;VacziDa</t>
+  </si>
+  <si>
+    <t>Stadthalle Villach;KainbergerJu;ZrnicMi;BedynekSe;ZgoncGa</t>
+  </si>
+  <si>
+    <t>FTC-Telekom Rink;HlavatyAl;SmetanaLa;Gatol-schafranekMa;JedlickaPe</t>
+  </si>
+  <si>
     <t>Hala Tivoli;SoosDa;SternatCh;VacziDa;ZgoncGa</t>
   </si>
   <si>
@@ -234,6 +267,24 @@
     <t>Eisarena Salzburg;SeewaldEl;SmetanaLa;MoidlMa;SeewaldJe</t>
   </si>
   <si>
+    <t>Eishalle Wien-Kagran;OfnerCh;SoosDa;Gatol-schafranekMa;JedlickaPe</t>
+  </si>
+  <si>
+    <t>Tiroler Wasserkraft Arena;HolzerTo;NikolicKr;FleischmannLu;MartinFl</t>
+  </si>
+  <si>
+    <t>Heidi Horten Arena Klagenfurt;RezekGr;SeewaldEl;JeramFi;ZgoncGa</t>
+  </si>
+  <si>
+    <t>Eisarena Salzburg;PiragicTr;SternatCh;JedlickaPe;KoncDa</t>
+  </si>
+  <si>
+    <t>Gabor Ocskay Eisarena;OfnerCh;SeewaldEl;KoncDa;PuffWo</t>
+  </si>
+  <si>
+    <t>Gabor Ocskay Eisarena;OfnerCh;SeewaldEl;MuzsikNo;PuffWo</t>
+  </si>
+  <si>
     <t>Tiroler Wasserkraft Arena;NikolicKr;NikolicMa;FleischmannLu;PardatscherUl</t>
   </si>
   <si>
@@ -252,6 +303,18 @@
     <t>Sparkasse Arena Bozen;NikolicMa;SternatCh;FleischmannLu;WeissAl</t>
   </si>
   <si>
+    <t>Eisarena Salzburg;Huber aAn;NikolicMa;NotheggerDa;SeewaldJe</t>
+  </si>
+  <si>
+    <t>Linz AG Eisarena;FichtnerPa;HronskyTo;DurmisOt;KoncDa</t>
+  </si>
+  <si>
+    <t>Hala Tivoli;SmetanaLa;VoicanCh;HribarMa;RieckenSi</t>
+  </si>
+  <si>
+    <t>Sparkasse Arena Bozen;Huber aAn;NikolicMa;PardatscherUl;RigoniDa</t>
+  </si>
+  <si>
     <t>Heidi Horten Arena Klagenfurt;HlavatyAl;ZrnicMi;BärnthalerCh;HribarMa</t>
   </si>
   <si>
@@ -270,6 +333,18 @@
     <t>Hala Tivoli;PiragicTr;RezekGr;Gatol-schafranekMa;RieckenSi</t>
   </si>
   <si>
+    <t>Gabor Ocskay Eisarena;NagyAt;SternatCh;MuzsikNo;PuffWo</t>
+  </si>
+  <si>
+    <t>Sparkasse Arena Bozen;KainbergerJu;NikolicKr;MantovaniDa;RigoniDa</t>
+  </si>
+  <si>
+    <t>Eishalle Bruneck;GroznikBo;SchauerJa;MantovaniDa;PardatscherUl</t>
+  </si>
+  <si>
+    <t>Eishalle Wien-Kagran;FichtnerPa;HronskyTo;VacziDa;ZacherlPa</t>
+  </si>
+  <si>
     <t>Linz AG Eisarena;KainbergerJu;NagyAt;BedynekSe;Gatol-schafranekMa</t>
   </si>
   <si>
@@ -285,6 +360,15 @@
     <t>Sparkasse Arena Bozen;NikolicKr;SchauerJa;PardatscherUl;RigoniDa</t>
   </si>
   <si>
+    <t>Linz AG Eisarena;VoicanCh;ZrnicMi;WeissAl;ZgoncGa</t>
+  </si>
+  <si>
+    <t>Stadthalle Villach;GroznikBo;Huber aAn;NotheggerDa;SeewaldJe</t>
+  </si>
+  <si>
+    <t>Heidi Horten Arena Klagenfurt;HolzerTo;SternatCh;DurmisOt;WeissAl</t>
+  </si>
+  <si>
     <t>Sparkasse Arena Bozen;GroznikBo;OfnerCh;MantovaniDa;PuffWo</t>
   </si>
   <si>
@@ -292,13 +376,16 @@
   </si>
   <si>
     <t>Hala Tivoli;NagyAt;OfnerCh;MuzsikNo;PuffWo</t>
+  </si>
+  <si>
+    <t>Hala Tivoli;PiragicTr;VoicanCh;BärnthalerCh;RieckenSi</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -306,13 +393,26 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <charset val="238"/>
+      <color rgb="FF006100"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -327,8 +427,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -609,7 +710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:AU134"/>
+  <dimension ref="A2:AT134"/>
   <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.28515625" customWidth="1"/>
@@ -667,193 +768,189 @@
     <col min="53" max="53" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="14.45" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="2" ht="14.45" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A2">
         <f>COUNTIF(A4:A118,"&lt;&gt;")</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
-        <f>COUNTIF(B4:B118,"&lt;&gt;")</f>
-        <v>6</v>
+        <f>COUNTIF(B4:B117,"&lt;&gt;")</f>
+        <v>10</v>
       </c>
       <c r="C2">
         <f>COUNTIF(C4:C118,"&lt;&gt;")</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D2">
         <f>COUNTIF(D4:D118,"&lt;&gt;")</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E2">
         <f>COUNTIF(E4:E118,"&lt;&gt;")</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F2">
         <f>COUNTIF(F4:F118,"&lt;&gt;")</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G2">
         <f>COUNTIF(G4:G118,"&lt;&gt;")</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H2">
         <f>COUNTIF(H4:H118,"&lt;&gt;")</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I2">
         <f>COUNTIF(I4:I118,"&lt;&gt;")</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J2">
-        <f>COUNTIF(J4:J118,"&lt;&gt;")</f>
-        <v>4</v>
+        <f>COUNTIF(J4:J117,"&lt;&gt;")</f>
+        <v>6</v>
       </c>
       <c r="K2">
         <f>COUNTIF(K4:K118,"&lt;&gt;")</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L2">
         <f>COUNTIF(L4:L118,"&lt;&gt;")</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M2">
-        <f>COUNTIF(M4:M117,"&lt;&gt;")</f>
-        <v>3</v>
+        <f>COUNTIF(M4:M118,"&lt;&gt;")</f>
+        <v>6</v>
       </c>
       <c r="N2">
         <f>COUNTIF(N4:N118,"&lt;&gt;")</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O2">
         <f>COUNTIF(O4:O118,"&lt;&gt;")</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P2">
         <f>COUNTIF(P4:P118,"&lt;&gt;")</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q2">
         <f>COUNTIF(Q4:Q118,"&lt;&gt;")</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R2">
-        <f>COUNTIF(R4:R118,"&lt;&gt;")</f>
-        <v>3</v>
+        <f>COUNTIF(R4:R117,"&lt;&gt;")</f>
+        <v>6</v>
       </c>
       <c r="S2">
         <f>COUNTIF(S4:S118,"&lt;&gt;")</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T2">
-        <f>COUNTIF(T4:T118,"&lt;&gt;")</f>
-        <v>3</v>
+        <f>COUNTIF(T4:T117,"&lt;&gt;")</f>
+        <v>5</v>
       </c>
       <c r="U2">
-        <f>COUNTIF(U4:U118,"&lt;&gt;")</f>
-        <v>3</v>
+        <f>COUNTIF(U4:U117,"&lt;&gt;")</f>
+        <v>5</v>
       </c>
       <c r="V2">
         <f>COUNTIF(V4:V118,"&lt;&gt;")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W2">
         <f>COUNTIF(W4:W118,"&lt;&gt;")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X2">
         <f>COUNTIF(X4:X118,"&lt;&gt;")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Y2">
         <f>COUNTIF(Y4:Y118,"&lt;&gt;")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z2">
         <f>COUNTIF(Z4:Z118,"&lt;&gt;")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AA2">
         <f>COUNTIF(AA4:AA118,"&lt;&gt;")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB2">
         <f>COUNTIF(AB4:AB118,"&lt;&gt;")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AC2">
         <f>COUNTIF(AC4:AC118,"&lt;&gt;")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AD2">
-        <f>COUNTIF(AD4:AD118,"&lt;&gt;")</f>
-        <v>3</v>
+        <f>COUNTIF(AD4:AD117,"&lt;&gt;")</f>
+        <v>4</v>
       </c>
       <c r="AE2">
         <f>COUNTIF(AE4:AE118,"&lt;&gt;")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF2">
         <f>COUNTIF(AF4:AF118,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG2">
         <f>COUNTIF(AG4:AG118,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AH2">
         <f>COUNTIF(AH4:AH118,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AI2">
         <f>COUNTIF(AI4:AI118,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AJ2">
         <f>COUNTIF(AJ4:AJ118,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AK2">
         <f>COUNTIF(AK4:AK118,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AL2">
         <f>COUNTIF(AL4:AL118,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AM2">
         <f>COUNTIF(AM4:AM118,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AN2">
         <f>COUNTIF(AN4:AN118,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AO2">
         <f>COUNTIF(AO4:AO118,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AP2">
         <f>COUNTIF(AP4:AP118,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ2">
         <f>COUNTIF(AQ4:AQ118,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR2">
         <f>COUNTIF(AR4:AR118,"&lt;&gt;")</f>
         <v>2</v>
       </c>
       <c r="AS2">
-        <f>COUNTIF(AS4:AS118,"&lt;&gt;")</f>
+        <f>COUNTIF(AS4:AS116,"&lt;&gt;")</f>
         <v>1</v>
       </c>
-      <c r="AT2">
-        <f>COUNTIF(AT4:AT118,"&lt;&gt;")</f>
-        <v>1</v>
-      </c>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -872,7 +969,7 @@
       <c r="F3" t="s">
         <v>5</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="H3" t="s">
@@ -884,7 +981,7 @@
       <c r="J3" t="s">
         <v>9</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L3" t="s">
@@ -893,10 +990,10 @@
       <c r="M3" t="s">
         <v>12</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O3" t="s">
+      <c r="O3" s="1" t="s">
         <v>14</v>
       </c>
       <c r="P3" t="s">
@@ -920,7 +1017,7 @@
       <c r="V3" t="s">
         <v>21</v>
       </c>
-      <c r="W3" t="s">
+      <c r="W3" s="1" t="s">
         <v>22</v>
       </c>
       <c r="X3" t="s">
@@ -941,7 +1038,7 @@
       <c r="AC3" t="s">
         <v>28</v>
       </c>
-      <c r="AD3" t="s">
+      <c r="AD3" s="1" t="s">
         <v>29</v>
       </c>
       <c r="AE3" t="s">
@@ -968,7 +1065,7 @@
       <c r="AL3" t="s">
         <v>37</v>
       </c>
-      <c r="AM3" t="s">
+      <c r="AM3" s="1" t="s">
         <v>38</v>
       </c>
       <c r="AN3" t="s">
@@ -989,58 +1086,55 @@
       <c r="AS3" t="s">
         <v>44</v>
       </c>
-      <c r="AT3" t="s">
+    </row>
+    <row r="4" ht="15" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>46</v>
       </c>
       <c r="B4" t="s">
         <v>46</v>
       </c>
       <c r="C4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" t="s">
         <v>46</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J4" t="s">
         <v>47</v>
       </c>
-      <c r="E4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G4" t="s">
-        <v>47</v>
-      </c>
-      <c r="H4" t="s">
-        <v>48</v>
-      </c>
-      <c r="I4" t="s">
-        <v>46</v>
-      </c>
-      <c r="J4" t="s">
-        <v>46</v>
-      </c>
       <c r="K4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="O4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q4" t="s">
         <v>46</v>
@@ -1049,67 +1143,67 @@
         <v>46</v>
       </c>
       <c r="S4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
       </c>
       <c r="V4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="W4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="X4" t="s">
         <v>46</v>
       </c>
       <c r="Y4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Z4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AA4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AB4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AC4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AD4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AE4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AF4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AG4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AH4" t="s">
         <v>46</v>
       </c>
       <c r="AI4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL4" t="s">
         <v>46</v>
       </c>
-      <c r="AJ4" t="s">
-        <v>48</v>
-      </c>
-      <c r="AK4" t="s">
+      <c r="AM4" t="s">
         <v>46</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>47</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>47</v>
       </c>
       <c r="AN4" t="s">
         <v>47</v>
@@ -1118,45 +1212,42 @@
         <v>49</v>
       </c>
       <c r="AP4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="AQ4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AR4" t="s">
         <v>48</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>49</v>
       </c>
       <c r="AS4" t="s">
         <v>50</v>
       </c>
-      <c r="AT4" t="s">
-        <v>48</v>
-      </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B5" t="s">
         <v>47</v>
       </c>
       <c r="C5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" t="s">
         <v>47</v>
       </c>
-      <c r="D5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E5" t="s">
-        <v>49</v>
-      </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I5" t="s">
         <v>47</v>
@@ -1165,230 +1256,260 @@
         <v>49</v>
       </c>
       <c r="K5" t="s">
+        <v>46</v>
+      </c>
+      <c r="L5" t="s">
+        <v>46</v>
+      </c>
+      <c r="M5" t="s">
         <v>47</v>
       </c>
-      <c r="L5" t="s">
+      <c r="N5" t="s">
         <v>47</v>
       </c>
-      <c r="M5" t="s">
-        <v>50</v>
-      </c>
-      <c r="N5" t="s">
-        <v>49</v>
-      </c>
       <c r="O5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="P5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q5" t="s">
+        <v>47</v>
+      </c>
+      <c r="R5" t="s">
         <v>51</v>
       </c>
-      <c r="R5" t="s">
-        <v>49</v>
-      </c>
       <c r="S5" t="s">
+        <v>48</v>
+      </c>
+      <c r="T5" t="s">
         <v>47</v>
-      </c>
-      <c r="T5" t="s">
-        <v>51</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
       </c>
       <c r="V5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="W5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="X5" t="s">
         <v>47</v>
       </c>
       <c r="Y5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Z5" t="s">
         <v>49</v>
       </c>
       <c r="AA5" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>53</v>
+      </c>
+      <c r="AC5" t="s">
         <v>49</v>
       </c>
-      <c r="AB5" t="s">
+      <c r="AD5" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>53</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>49</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>49</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>49</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>49</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>53</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>53</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>49</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>54</v>
+      </c>
+      <c r="AP5" t="s">
         <v>52</v>
       </c>
-      <c r="AC5" t="s">
-        <v>50</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE5" t="s">
+      <c r="AQ5" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR5" t="s">
         <v>51</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>50</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>50</v>
-      </c>
-      <c r="AH5" t="s">
-        <v>51</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>53</v>
-      </c>
-      <c r="AK5" t="s">
-        <v>50</v>
-      </c>
-      <c r="AL5" t="s">
-        <v>52</v>
-      </c>
-      <c r="AM5" t="s">
-        <v>51</v>
-      </c>
-      <c r="AN5" t="s">
-        <v>50</v>
-      </c>
-      <c r="AO5" t="s">
-        <v>48</v>
-      </c>
-      <c r="AP5" t="s">
-        <v>51</v>
-      </c>
-      <c r="AQ5" t="s">
-        <v>48</v>
-      </c>
-      <c r="AR5" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F6" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6" t="s">
+        <v>55</v>
+      </c>
+      <c r="H6" t="s">
         <v>49</v>
-      </c>
-      <c r="B6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" t="s">
-        <v>54</v>
-      </c>
-      <c r="F6" t="s">
-        <v>54</v>
-      </c>
-      <c r="G6" t="s">
-        <v>54</v>
-      </c>
-      <c r="H6" t="s">
-        <v>50</v>
       </c>
       <c r="I6" t="s">
         <v>49</v>
       </c>
       <c r="J6" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="L6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M6" t="s">
+        <v>49</v>
+      </c>
+      <c r="N6" t="s">
+        <v>49</v>
+      </c>
+      <c r="O6" t="s">
+        <v>49</v>
+      </c>
+      <c r="P6" t="s">
         <v>53</v>
       </c>
-      <c r="N6" t="s">
-        <v>48</v>
-      </c>
-      <c r="O6" t="s">
-        <v>50</v>
-      </c>
-      <c r="P6" t="s">
-        <v>50</v>
-      </c>
       <c r="Q6" t="s">
+        <v>52</v>
+      </c>
+      <c r="R6" t="s">
+        <v>56</v>
+      </c>
+      <c r="S6" t="s">
+        <v>56</v>
+      </c>
+      <c r="T6" t="s">
+        <v>51</v>
+      </c>
+      <c r="U6" t="s">
+        <v>51</v>
+      </c>
+      <c r="V6" t="s">
         <v>53</v>
-      </c>
-      <c r="R6" t="s">
-        <v>50</v>
-      </c>
-      <c r="S6" t="s">
-        <v>51</v>
-      </c>
-      <c r="T6" t="s">
-        <v>53</v>
-      </c>
-      <c r="U6" t="s">
-        <v>50</v>
-      </c>
-      <c r="V6" t="s">
-        <v>51</v>
       </c>
       <c r="W6" t="s">
         <v>53</v>
       </c>
       <c r="X6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="Y6" t="s">
         <v>51</v>
       </c>
       <c r="Z6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA6" t="s">
         <v>51</v>
       </c>
-      <c r="AA6" t="s">
+      <c r="AB6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>51</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>51</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>51</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" t="s">
         <v>52</v>
       </c>
-      <c r="AB6" t="s">
+      <c r="C7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" t="s">
         <v>53</v>
       </c>
-      <c r="AC6" t="s">
-        <v>51</v>
-      </c>
-      <c r="AD6" t="s">
+      <c r="F7" t="s">
         <v>53</v>
       </c>
-      <c r="AE6" t="s">
+      <c r="G7" t="s">
         <v>53</v>
-      </c>
-      <c r="AK6" t="s">
-        <v>51</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C7" t="s">
-        <v>50</v>
-      </c>
-      <c r="D7" t="s">
-        <v>51</v>
-      </c>
-      <c r="E7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F7" t="s">
-        <v>51</v>
-      </c>
-      <c r="G7" t="s">
-        <v>51</v>
       </c>
       <c r="H7" t="s">
         <v>53</v>
@@ -1397,36 +1518,114 @@
         <v>54</v>
       </c>
       <c r="J7" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="K7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L7" t="s">
         <v>51</v>
       </c>
+      <c r="M7" t="s">
+        <v>58</v>
+      </c>
       <c r="N7" t="s">
+        <v>54</v>
+      </c>
+      <c r="O7" t="s">
         <v>53</v>
       </c>
+      <c r="P7" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>59</v>
+      </c>
+      <c r="R7" t="s">
+        <v>45</v>
+      </c>
+      <c r="S7" t="s">
+        <v>54</v>
+      </c>
+      <c r="T7" t="s">
+        <v>56</v>
+      </c>
       <c r="U7" t="s">
-        <v>51</v>
+        <v>57</v>
+      </c>
+      <c r="V7" t="s">
+        <v>59</v>
+      </c>
+      <c r="W7" t="s">
+        <v>58</v>
+      </c>
+      <c r="X7" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>58</v>
       </c>
       <c r="AD7" t="s">
-        <v>55</v>
+        <v>58</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>54</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>59</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>50</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>50</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>50</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>50</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>58</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>58</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>50</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B8" t="s">
         <v>51</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E8" t="s">
         <v>52</v>
@@ -1435,48 +1634,209 @@
         <v>52</v>
       </c>
       <c r="G8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I8" t="s">
+        <v>59</v>
+      </c>
+      <c r="J8" t="s">
+        <v>60</v>
+      </c>
+      <c r="K8" t="s">
+        <v>54</v>
+      </c>
+      <c r="L8" t="s">
         <v>53</v>
       </c>
-      <c r="J8" t="s">
-        <v>55</v>
-      </c>
-      <c r="K8" t="s">
-        <v>51</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>46</v>
+      <c r="M8" t="s">
+        <v>57</v>
+      </c>
+      <c r="N8" t="s">
+        <v>58</v>
+      </c>
+      <c r="O8" t="s">
+        <v>59</v>
+      </c>
+      <c r="P8" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>58</v>
+      </c>
+      <c r="R8" t="s">
+        <v>54</v>
+      </c>
+      <c r="S8" t="s">
+        <v>57</v>
+      </c>
+      <c r="T8" t="s">
+        <v>50</v>
+      </c>
+      <c r="U8" t="s">
+        <v>50</v>
+      </c>
+      <c r="V8" t="s">
+        <v>58</v>
+      </c>
+      <c r="W8" t="s">
+        <v>57</v>
+      </c>
+      <c r="X8" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>57</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>52</v>
       </c>
       <c r="B9" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" t="s">
         <v>52</v>
       </c>
-      <c r="D9" t="s">
-        <v>53</v>
+      <c r="E9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" t="s">
+        <v>60</v>
+      </c>
+      <c r="I9" t="s">
+        <v>57</v>
+      </c>
+      <c r="J9" t="s">
+        <v>50</v>
+      </c>
+      <c r="K9" t="s">
+        <v>60</v>
+      </c>
+      <c r="L9" t="s">
+        <v>60</v>
+      </c>
+      <c r="M9" t="s">
+        <v>50</v>
+      </c>
+      <c r="N9" t="s">
+        <v>60</v>
+      </c>
+      <c r="O9" t="s">
+        <v>57</v>
+      </c>
+      <c r="P9" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>50</v>
+      </c>
+      <c r="R9" t="s">
+        <v>50</v>
+      </c>
+      <c r="S9" t="s">
+        <v>50</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>53</v>
+        <v>51</v>
+      </c>
+      <c r="B10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" t="s">
+        <v>59</v>
       </c>
       <c r="D10" t="s">
-        <v>55</v>
+        <v>54</v>
+      </c>
+      <c r="E10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I10" t="s">
+        <v>50</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" t="s">
+        <v>57</v>
+      </c>
       <c r="D11" t="s">
-        <v>46</v>
+        <v>60</v>
+      </c>
+      <c r="E11" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" t="s">
+        <v>50</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="13" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25"/>
     <row r="15" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="16" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1605,7 +1965,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:I42"/>
+  <dimension ref="A3:O42"/>
   <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="17.85546875" customWidth="1"/>
@@ -1638,41 +1998,59 @@
     <col min="98" max="98" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" t="s">
         <v>46</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>47</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" t="s">
         <v>49</v>
       </c>
-      <c r="D3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E3" t="s">
-        <v>50</v>
-      </c>
       <c r="F3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G3" t="s">
         <v>52</v>
       </c>
       <c r="H3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I3" t="s">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="J3" t="s">
+        <v>54</v>
+      </c>
+      <c r="K3" t="s">
+        <v>59</v>
+      </c>
+      <c r="L3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M3" t="s">
+        <v>57</v>
+      </c>
+      <c r="N3" t="s">
+        <v>60</v>
+      </c>
+      <c r="O3" t="s">
+        <v>50</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -1681,56 +2059,92 @@
         <v>6</v>
       </c>
       <c r="E4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="H4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4" t="s">
+        <v>15</v>
+      </c>
+      <c r="O4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
         <v>22</v>
       </c>
-      <c r="I4" t="s">
+      <c r="G5" t="s">
         <v>3</v>
       </c>
+      <c r="H5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" t="s">
+        <v>2</v>
+      </c>
+      <c r="L5" t="s">
+        <v>1</v>
+      </c>
+      <c r="M5" t="s">
+        <v>12</v>
+      </c>
+      <c r="N5" t="s">
+        <v>10</v>
+      </c>
+      <c r="O5" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
+    <row r="6" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="D5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="B6" t="s">
         <v>23</v>
-      </c>
-      <c r="G5" t="s">
-        <v>2</v>
-      </c>
-      <c r="H5" t="s">
-        <v>16</v>
-      </c>
-      <c r="I5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
       </c>
       <c r="C6" t="s">
         <v>4</v>
@@ -1739,27 +2153,45 @@
         <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F6" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H6" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I6" t="s">
-        <v>9</v>
+        <v>19</v>
+      </c>
+      <c r="J6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K6" t="s">
+        <v>14</v>
+      </c>
+      <c r="L6" t="s">
+        <v>23</v>
+      </c>
+      <c r="M6" t="s">
+        <v>4</v>
+      </c>
+      <c r="N6" t="s">
+        <v>11</v>
+      </c>
+      <c r="O6" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
@@ -1768,145 +2200,247 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" t="s">
         <v>11</v>
       </c>
-      <c r="G7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H7" t="s">
-        <v>10</v>
-      </c>
       <c r="I7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" t="s">
+        <v>42</v>
+      </c>
+      <c r="K7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L7" t="s">
+        <v>41</v>
+      </c>
+      <c r="M7" t="s">
+        <v>35</v>
+      </c>
+      <c r="N7" t="s">
+        <v>13</v>
+      </c>
+      <c r="O7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
+        <v>2</v>
+      </c>
+      <c r="G8" t="s">
+        <v>1</v>
+      </c>
+      <c r="H8" t="s">
+        <v>9</v>
+      </c>
+      <c r="J8" t="s">
+        <v>3</v>
+      </c>
+      <c r="K8" t="s">
+        <v>16</v>
+      </c>
+      <c r="L8" t="s">
         <v>29</v>
       </c>
+      <c r="M8" t="s">
+        <v>6</v>
+      </c>
+      <c r="N8" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" t="s">
-        <v>1</v>
-      </c>
-      <c r="G8" t="s">
-        <v>3</v>
-      </c>
-      <c r="H8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E9" t="s">
         <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="G9" t="s">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="J9" t="s">
+        <v>30</v>
+      </c>
+      <c r="K9" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" t="s">
+        <v>9</v>
+      </c>
+      <c r="M9" t="s">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>9</v>
+      </c>
+      <c r="O9" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B10" t="s">
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G10" t="s">
         <v>4</v>
       </c>
       <c r="H10" t="s">
-        <v>35</v>
+        <v>43</v>
+      </c>
+      <c r="J10" t="s">
+        <v>17</v>
+      </c>
+      <c r="K10" t="s">
+        <v>31</v>
+      </c>
+      <c r="L10" t="s">
+        <v>38</v>
+      </c>
+      <c r="M10" t="s">
+        <v>8</v>
+      </c>
+      <c r="N10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O10" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E11" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G11" t="s">
         <v>5</v>
       </c>
       <c r="H11" t="s">
-        <v>30</v>
+        <v>26</v>
+      </c>
+      <c r="J11" t="s">
+        <v>8</v>
+      </c>
+      <c r="K11" t="s">
+        <v>23</v>
+      </c>
+      <c r="L11" t="s">
+        <v>13</v>
+      </c>
+      <c r="M11" t="s">
+        <v>5</v>
+      </c>
+      <c r="N11" t="s">
+        <v>7</v>
+      </c>
+      <c r="O11" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H12" t="s">
+        <v>1</v>
+      </c>
+      <c r="J12" t="s">
+        <v>40</v>
+      </c>
+      <c r="L12" t="s">
+        <v>25</v>
+      </c>
+      <c r="M12" t="s">
         <v>2</v>
       </c>
-      <c r="C12" t="s">
-        <v>2</v>
-      </c>
-      <c r="E12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F12" t="s">
-        <v>34</v>
-      </c>
-      <c r="H12" t="s">
-        <v>3</v>
+      <c r="O12" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B13" t="s">
         <v>0</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E13" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" t="s">
         <v>6</v>
@@ -1914,240 +2448,372 @@
       <c r="H13" t="s">
         <v>0</v>
       </c>
+      <c r="J13" t="s">
+        <v>1</v>
+      </c>
+      <c r="L13" t="s">
+        <v>12</v>
+      </c>
+      <c r="M13" t="s">
+        <v>18</v>
+      </c>
+      <c r="O13" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" t="s">
         <v>19</v>
       </c>
-      <c r="B14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" t="s">
-        <v>9</v>
-      </c>
       <c r="E14" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J14" t="s">
         <v>39</v>
       </c>
-      <c r="F14" t="s">
-        <v>19</v>
-      </c>
-      <c r="H14" t="s">
-        <v>19</v>
+      <c r="L14" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" t="s">
+        <v>14</v>
+      </c>
+      <c r="O14" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J15" t="s">
+        <v>26</v>
+      </c>
+      <c r="L15" t="s">
+        <v>5</v>
+      </c>
+      <c r="M15" t="s">
+        <v>20</v>
+      </c>
+      <c r="O15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>34</v>
-      </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E16" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F16" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H16" t="s">
         <v>6</v>
       </c>
+      <c r="J16" t="s">
+        <v>32</v>
+      </c>
+      <c r="L16" t="s">
+        <v>15</v>
+      </c>
+      <c r="M16" t="s">
+        <v>22</v>
+      </c>
+      <c r="O16" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E17" t="s">
+        <v>29</v>
+      </c>
+      <c r="F17" t="s">
         <v>3</v>
       </c>
-      <c r="C17" t="s">
+      <c r="H17" t="s">
+        <v>29</v>
+      </c>
+      <c r="J17" t="s">
+        <v>0</v>
+      </c>
+      <c r="L17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M17" t="s">
+        <v>33</v>
+      </c>
+      <c r="O17" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" t="s">
+        <v>28</v>
+      </c>
+      <c r="H18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" t="s">
+        <v>34</v>
+      </c>
+      <c r="L18" t="s">
+        <v>28</v>
+      </c>
+      <c r="M18" t="s">
+        <v>28</v>
+      </c>
+      <c r="O18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" t="s">
+        <v>35</v>
+      </c>
+      <c r="F19" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" t="s">
+        <v>7</v>
+      </c>
+      <c r="L19" t="s">
+        <v>37</v>
+      </c>
+      <c r="M19" t="s">
+        <v>36</v>
+      </c>
+      <c r="O19" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" t="s">
         <v>1</v>
       </c>
-      <c r="E17" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="E20" t="s">
+        <v>32</v>
+      </c>
+      <c r="F20" t="s">
+        <v>21</v>
+      </c>
+      <c r="J20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L20" t="s">
+        <v>22</v>
+      </c>
+      <c r="O20" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" t="s">
         <v>2</v>
-      </c>
-      <c r="H17" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" t="s">
-        <v>20</v>
-      </c>
-      <c r="F18" t="s">
-        <v>36</v>
-      </c>
-      <c r="H18" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" t="s">
-        <v>32</v>
-      </c>
-      <c r="F19" t="s">
-        <v>25</v>
-      </c>
-      <c r="H19" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F20" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" t="s">
-        <v>1</v>
       </c>
       <c r="C21" t="s">
         <v>0</v>
       </c>
       <c r="E21" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21" t="s">
+        <v>33</v>
+      </c>
+      <c r="J21" t="s">
+        <v>10</v>
+      </c>
+      <c r="L21" t="s">
+        <v>40</v>
+      </c>
+      <c r="O21" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" t="s">
+        <v>34</v>
+      </c>
+      <c r="F22" t="s">
+        <v>36</v>
+      </c>
+      <c r="J22" t="s">
         <v>24</v>
       </c>
+      <c r="L22" t="s">
+        <v>39</v>
+      </c>
+      <c r="O22" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>10</v>
-      </c>
-      <c r="B22" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" t="s">
-        <v>43</v>
-      </c>
-      <c r="E22" t="s">
-        <v>31</v>
-      </c>
-      <c r="F22" t="s">
-        <v>33</v>
+    <row r="23" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F23" t="s">
+        <v>37</v>
+      </c>
+      <c r="J23" t="s">
+        <v>13</v>
+      </c>
+      <c r="L23" t="s">
+        <v>26</v>
+      </c>
+      <c r="O23" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" t="s">
-        <v>13</v>
-      </c>
-      <c r="C23" t="s">
-        <v>7</v>
-      </c>
-      <c r="E23" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
         <v>6</v>
       </c>
       <c r="F24" t="s">
+        <v>1</v>
+      </c>
+      <c r="O24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>2</v>
-      </c>
       <c r="B25" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F25" t="s">
         <v>0</v>
       </c>
+      <c r="O25" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F26" t="s">
         <v>4</v>
       </c>
+      <c r="O26" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F27" t="s">
         <v>5</v>
       </c>
+      <c r="O27" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="15" customHeight="1" spans="6:15" x14ac:dyDescent="0.25"/>
     <row r="29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2169,7 +2835,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:I1898"/>
+  <dimension ref="A3:O1898"/>
   <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="55.28515625" customWidth="1"/>
@@ -2253,159 +2919,249 @@
     <col min="99" max="99" width="47.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" t="s">
         <v>46</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>47</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" t="s">
         <v>49</v>
       </c>
-      <c r="D3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E3" t="s">
-        <v>50</v>
-      </c>
       <c r="F3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G3" t="s">
         <v>52</v>
       </c>
       <c r="H3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I3" t="s">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="J3" t="s">
+        <v>54</v>
+      </c>
+      <c r="K3" t="s">
+        <v>59</v>
+      </c>
+      <c r="L3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M3" t="s">
+        <v>57</v>
+      </c>
+      <c r="N3" t="s">
+        <v>60</v>
+      </c>
+      <c r="O3" t="s">
+        <v>50</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E4" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F4" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H4" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="I4" t="s">
-        <v>64</v>
+        <v>69</v>
+      </c>
+      <c r="J4" t="s">
+        <v>70</v>
+      </c>
+      <c r="K4" t="s">
+        <v>71</v>
+      </c>
+      <c r="L4" t="s">
+        <v>72</v>
+      </c>
+      <c r="M4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N4" t="s">
+        <v>74</v>
+      </c>
+      <c r="O4" t="s">
+        <v>75</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="E5" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="F5" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="G5" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="H5" t="s">
-        <v>71</v>
+        <v>82</v>
+      </c>
+      <c r="J5" t="s">
+        <v>83</v>
+      </c>
+      <c r="K5" t="s">
+        <v>84</v>
+      </c>
+      <c r="L5" t="s">
+        <v>85</v>
+      </c>
+      <c r="M5" t="s">
+        <v>86</v>
+      </c>
+      <c r="N5" t="s">
+        <v>87</v>
+      </c>
+      <c r="O5" t="s">
+        <v>88</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="E6" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="F6" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="H6" t="s">
-        <v>77</v>
+        <v>94</v>
+      </c>
+      <c r="J6" t="s">
+        <v>95</v>
+      </c>
+      <c r="L6" t="s">
+        <v>96</v>
+      </c>
+      <c r="M6" t="s">
+        <v>97</v>
+      </c>
+      <c r="O6" t="s">
+        <v>98</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="E7" t="s">
+        <v>102</v>
+      </c>
+      <c r="F7" t="s">
+        <v>103</v>
+      </c>
+      <c r="H7" t="s">
+        <v>104</v>
+      </c>
+      <c r="J7" t="s">
+        <v>105</v>
+      </c>
+      <c r="L7" t="s">
+        <v>106</v>
+      </c>
+      <c r="M7" t="s">
+        <v>107</v>
+      </c>
+      <c r="O7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>109</v>
+      </c>
+      <c r="B8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C8" t="s">
+        <v>111</v>
+      </c>
+      <c r="E8" t="s">
+        <v>112</v>
+      </c>
+      <c r="F8" t="s">
+        <v>113</v>
+      </c>
+      <c r="J8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L8" t="s">
+        <v>115</v>
+      </c>
+      <c r="O8" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>117</v>
+      </c>
+      <c r="B9" t="s">
+        <v>118</v>
+      </c>
+      <c r="E9" t="s">
+        <v>119</v>
+      </c>
+      <c r="F9" t="s">
         <v>81</v>
       </c>
-      <c r="F7" t="s">
-        <v>82</v>
-      </c>
-      <c r="H7" t="s">
-        <v>83</v>
+      <c r="O9" t="s">
+        <v>120</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>84</v>
-      </c>
-      <c r="B8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C8" t="s">
-        <v>86</v>
-      </c>
-      <c r="E8" t="s">
-        <v>87</v>
-      </c>
-      <c r="F8" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>89</v>
-      </c>
-      <c r="B9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E9" t="s">
-        <v>91</v>
-      </c>
-      <c r="F9" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25"/>
+    <row r="10" ht="15" customHeight="1" spans="5:15" x14ac:dyDescent="0.25"/>
     <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="13" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/data/ICEHLdelegacije.xlsx
+++ b/data/ICEHLdelegacije.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="121">
   <si>
     <t>SternatCh</t>
   </si>
@@ -324,7 +324,7 @@
     <t>Eishalle Feldkirch;HolzerTo;SmetanaLa;MartinFl;RieckenSi</t>
   </si>
   <si>
-    <t>Stadthalle Villach;SchauerJa;SmetanaLa;JeramFi;ZgoncGa</t>
+    <t>Stadthalle Villach;GroznikBo;SmetanaLa;JeramFi;ZgoncGa</t>
   </si>
   <si>
     <t>Tiroler Wasserkraft Arena;KainbergerJu;OfnerCh;MantovaniDa;MartinFl</t>
@@ -333,7 +333,7 @@
     <t>Hala Tivoli;PiragicTr;RezekGr;Gatol-schafranekMa;RieckenSi</t>
   </si>
   <si>
-    <t>Gabor Ocskay Eisarena;NagyAt;SternatCh;MuzsikNo;PuffWo</t>
+    <t>Gabor Ocskay Eisarena;FichtnerPa;SternatCh;MuzsikNo;PuffWo</t>
   </si>
   <si>
     <t>Sparkasse Arena Bozen;KainbergerJu;NikolicKr;MantovaniDa;RigoniDa</t>
@@ -1325,7 +1325,7 @@
         <v>49</v>
       </c>
       <c r="AH5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AI5" t="s">
         <v>49</v>
@@ -1587,7 +1587,7 @@
         <v>59</v>
       </c>
       <c r="AG7" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="AH7" t="s">
         <v>57</v>
@@ -1761,8 +1761,14 @@
       <c r="S9" t="s">
         <v>50</v>
       </c>
+      <c r="W9" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>54</v>
+      </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>51</v>
       </c>
@@ -2408,7 +2414,7 @@
         <v>3</v>
       </c>
       <c r="E12" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F12" t="s">
         <v>27</v>
@@ -2545,7 +2551,7 @@
         <v>6</v>
       </c>
       <c r="J16" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="L16" t="s">
         <v>15</v>

--- a/data/ICEHLdelegacije.xlsx
+++ b/data/ICEHLdelegacije.xlsx
@@ -1,22 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9E56E00-DD9F-4A8F-849E-98EB99B4B320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="ICEHL" state="visible" r:id="rId4"/>
-    <sheet sheetId="3" name="ICEHL_DAT" state="visible" r:id="rId5"/>
-    <sheet sheetId="4" name="ICEHL_DAT_STRING" state="visible" r:id="rId6"/>
+    <sheet name="ICEHL" sheetId="1" r:id="rId1"/>
+    <sheet name="ICEHL_DAT" sheetId="3" r:id="rId2"/>
+    <sheet name="ICEHL_DAT_STRING" sheetId="4" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1016" uniqueCount="174">
   <si>
     <t>SternatCh</t>
   </si>
@@ -153,6 +167,12 @@
     <t>ZacherlPa</t>
   </si>
   <si>
+    <t>SiegelSt</t>
+  </si>
+  <si>
+    <t>LinesmanZw</t>
+  </si>
+  <si>
     <t>2025-09-12</t>
   </si>
   <si>
@@ -162,15 +182,18 @@
     <t>2025-09-19</t>
   </si>
   <si>
-    <t>zbrisano</t>
-  </si>
-  <si>
     <t>2025-09-21</t>
   </si>
   <si>
     <t>2025-10-12</t>
   </si>
   <si>
+    <t>2025-10-17</t>
+  </si>
+  <si>
+    <t>2025-10-29</t>
+  </si>
+  <si>
     <t>2025-09-28</t>
   </si>
   <si>
@@ -183,6 +206,9 @@
     <t>2025-10-03</t>
   </si>
   <si>
+    <t>2025-10-19</t>
+  </si>
+  <si>
     <t>2025-09-20</t>
   </si>
   <si>
@@ -195,12 +221,33 @@
     <t>2025-10-05</t>
   </si>
   <si>
+    <t>2025-10-26</t>
+  </si>
+  <si>
+    <t>2025-10-24</t>
+  </si>
+  <si>
     <t>2025-10-04</t>
   </si>
   <si>
     <t>2025-10-11</t>
   </si>
   <si>
+    <t>2025-10-25</t>
+  </si>
+  <si>
+    <t>2025-10-31</t>
+  </si>
+  <si>
+    <t>2025-11-02</t>
+  </si>
+  <si>
+    <t>2025-10-18</t>
+  </si>
+  <si>
+    <t>2025-11-01</t>
+  </si>
+  <si>
     <t>FTC-Telekom Rink;HronskyTo;SmetanaLa;JedlickaPe;MuzsikNo</t>
   </si>
   <si>
@@ -246,6 +293,36 @@
     <t>FTC-Telekom Rink;HlavatyAl;SmetanaLa;Gatol-schafranekMa;JedlickaPe</t>
   </si>
   <si>
+    <t>FTC-Telekom Rink;HronskyTo;SiegelSt;VacziDa;WeissAl</t>
+  </si>
+  <si>
+    <t>Sparkasse Arena Bozen;OfnerCh;SternatCh;MantovaniDa;RigoniDa</t>
+  </si>
+  <si>
+    <t>Eisarena Salzburg;KainbergerJu;PiragicTr;BärnthalerCh;WimmlerAl</t>
+  </si>
+  <si>
+    <t>Gabor Ocskay Eisarena;HronskyTo;SiegelSt;JedlickaPe;MuzsikNo</t>
+  </si>
+  <si>
+    <t>Tiroler Wasserkraft Arena;SmetanaLa;VoicanCh;DurmisOt;KoncDa</t>
+  </si>
+  <si>
+    <t>Linz AG Eisarena;SiegelSt;ZrnicMi;SeewaldJe;ZacherlPa</t>
+  </si>
+  <si>
+    <t>Merkur Eisstadion Graz;SeewaldEl;SternatCh;JeramFi;LinesmanZw</t>
+  </si>
+  <si>
+    <t>FTC-Telekom Rink;SiegelSt;SoosDa;BärnthalerCh;RieckenSi</t>
+  </si>
+  <si>
+    <t>Eishalle Feldkirch;HolzerTo;HronskyTo;JedlickaPe;MartinFl</t>
+  </si>
+  <si>
+    <t>Linz AG Eisarena;NagyAt;SmetanaLa;BedynekSe;NotheggerDa</t>
+  </si>
+  <si>
     <t>Hala Tivoli;SoosDa;SternatCh;VacziDa;ZgoncGa</t>
   </si>
   <si>
@@ -285,6 +362,33 @@
     <t>Gabor Ocskay Eisarena;OfnerCh;SeewaldEl;MuzsikNo;PuffWo</t>
   </si>
   <si>
+    <t>Stadthalle Villach;PiragicTr;ZrnicMi;MuzsikNo;RieckenSi</t>
+  </si>
+  <si>
+    <t>Eishalle Feldkirch;HolzerTo;SeewaldEl;FleischmannLu;MartinFl</t>
+  </si>
+  <si>
+    <t>Eisarena Salzburg;NagyAt;ZrnicMi;BärnthalerCh;Gatol-schafranekMa</t>
+  </si>
+  <si>
+    <t>Eishalle Wien-Kagran;FichtnerPa;NagyAt;RieckenSi;WimmlerAl</t>
+  </si>
+  <si>
+    <t>FTC-Telekom Rink;HlavatyAl;NagyAt;MuzsikNo;VacziDa</t>
+  </si>
+  <si>
+    <t>FTC-Telekom Rink;PiragicTr;VoicanCh;BedynekSe;MoidlMa</t>
+  </si>
+  <si>
+    <t>Linz AG Eisarena;KainbergerJu;PiragicTr;SparerDa;ZgoncGa</t>
+  </si>
+  <si>
+    <t>Hala Tivoli;RezekGr;SeewaldEl;HribarMa;JeramFi</t>
+  </si>
+  <si>
+    <t>Eishalle Feldkirch;HronskyTo;NikolicKr;FleischmannLu;JedlickaPe</t>
+  </si>
+  <si>
     <t>Tiroler Wasserkraft Arena;NikolicKr;NikolicMa;FleischmannLu;PardatscherUl</t>
   </si>
   <si>
@@ -315,6 +419,27 @@
     <t>Sparkasse Arena Bozen;Huber aAn;NikolicMa;PardatscherUl;RigoniDa</t>
   </si>
   <si>
+    <t>Tiroler Wasserkraft Arena;NikolicKr;SchauerJa;FleischmannLu;RigoniDa</t>
+  </si>
+  <si>
+    <t>Stadthalle Villach;SiegelSt;SmetanaLa;Gatol-schafranekMa;JeramFi</t>
+  </si>
+  <si>
+    <t>Linz AG Eisarena;NikolicMa;SchauerJa;BedynekSe;WeissAl</t>
+  </si>
+  <si>
+    <t>Merkur Eisstadion Graz;PiragicTr;SoosDa;JedlickaPe;KoncDa</t>
+  </si>
+  <si>
+    <t>Tiroler Wasserkraft Arena;NikolicKr;SchauerJa;MartinFl;ZacherlPa</t>
+  </si>
+  <si>
+    <t>Heidi Horten Arena Klagenfurt;NagyAt;SmetanaLa;PuffWo;VacziDa</t>
+  </si>
+  <si>
+    <t>Sparkasse Arena Bozen;OfnerCh;SchauerJa;MantovaniDa;SparerDa</t>
+  </si>
+  <si>
     <t>Heidi Horten Arena Klagenfurt;HlavatyAl;ZrnicMi;BärnthalerCh;HribarMa</t>
   </si>
   <si>
@@ -345,6 +470,27 @@
     <t>Eishalle Wien-Kagran;FichtnerPa;HronskyTo;VacziDa;ZacherlPa</t>
   </si>
   <si>
+    <t>Eishalle Wien-Kagran;GroznikBo;Huber aAn;BedynekSe;ZgoncGa</t>
+  </si>
+  <si>
+    <t>Merkur Eisstadion Graz;Huber aAn;ZrnicMi;MoidlMa;ZacherlPa</t>
+  </si>
+  <si>
+    <t>Tiroler Wasserkraft Arena;HlavatyAl;SmetanaLa;DurmisOt;KoncDa</t>
+  </si>
+  <si>
+    <t>Eisarena Salzburg;NikolicKr;SternatCh;MantovaniDa;NotheggerDa</t>
+  </si>
+  <si>
+    <t>Gabor Ocskay Eisarena;SiegelSt;SmetanaLa;BärnthalerCh;WeissAl</t>
+  </si>
+  <si>
+    <t>Eisarena Salzburg;FichtnerPa;SternatCh;MuzsikNo;RigoniDa</t>
+  </si>
+  <si>
+    <t>Eishalle Wien-Kagran;HlavatyAl;PiragicTr;MoidlMa;RieckenSi</t>
+  </si>
+  <si>
     <t>Linz AG Eisarena;KainbergerJu;NagyAt;BedynekSe;Gatol-schafranekMa</t>
   </si>
   <si>
@@ -369,6 +515,27 @@
     <t>Heidi Horten Arena Klagenfurt;HolzerTo;SternatCh;DurmisOt;WeissAl</t>
   </si>
   <si>
+    <t>Hala Tivoli;RezekGr;SoosDa;HribarMa;SeewaldJe</t>
+  </si>
+  <si>
+    <t>Eishalle Bruneck;NikolicMa;SchauerJa;PardatscherUl;PuffWo</t>
+  </si>
+  <si>
+    <t>Eishalle Bruneck;GroznikBo;PiragicTr;HribarMa;RigoniDa</t>
+  </si>
+  <si>
+    <t>Heidi Horten Arena Klagenfurt;KainbergerJu;OfnerCh;PuffWo;ZgoncGa</t>
+  </si>
+  <si>
+    <t>Eishalle Feldkirch;KainbergerJu;OfnerCh;PardatscherUl;WimmlerAl</t>
+  </si>
+  <si>
+    <t>Sparkasse Arena Bozen;GroznikBo;Huber aAn;MantovaniDa;PardatscherUl</t>
+  </si>
+  <si>
+    <t>Eishalle Bruneck;Huber aAn;VoicanCh;RigoniDa;ZacherlPa</t>
+  </si>
+  <si>
     <t>Sparkasse Arena Bozen;GroznikBo;OfnerCh;MantovaniDa;PuffWo</t>
   </si>
   <si>
@@ -379,27 +546,33 @@
   </si>
   <si>
     <t>Hala Tivoli;PiragicTr;VoicanCh;BärnthalerCh;RieckenSi</t>
+  </si>
+  <si>
+    <t>Eishalle Feldkirch;OfnerCh;SternatCh;PardatscherUl;SparerDa</t>
+  </si>
+  <si>
+    <t>Sparkasse Arena Bozen;NikolicMa;ZrnicMi;FleischmannLu;LinesmanZw</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="238"/>
-      <color rgb="FF006100"/>
-      <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -709,9 +882,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:AT134"/>
-  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A2:AU134"/>
+  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.28515625" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -768,311 +941,315 @@
     <col min="53" max="53" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="14.45" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <f>COUNTIF(A4:A118,"&lt;&gt;")</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B2">
-        <f>COUNTIF(B4:B117,"&lt;&gt;")</f>
-        <v>10</v>
+        <f>COUNTIF(B4:B118,"&lt;&gt;")</f>
+        <v>15</v>
       </c>
       <c r="C2">
         <f>COUNTIF(C4:C118,"&lt;&gt;")</f>
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D2">
         <f>COUNTIF(D4:D118,"&lt;&gt;")</f>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E2">
-        <f>COUNTIF(E4:E118,"&lt;&gt;")</f>
-        <v>8</v>
+        <f>COUNTIF(E4:E117,"&lt;&gt;")</f>
+        <v>13</v>
       </c>
       <c r="F2">
         <f>COUNTIF(F4:F118,"&lt;&gt;")</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <f>COUNTIF(G4:G118,"&lt;&gt;")</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H2">
         <f>COUNTIF(H4:H118,"&lt;&gt;")</f>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I2">
         <f>COUNTIF(I4:I118,"&lt;&gt;")</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J2">
-        <f>COUNTIF(J4:J117,"&lt;&gt;")</f>
-        <v>6</v>
+        <f>COUNTIF(J4:J118,"&lt;&gt;")</f>
+        <v>10</v>
       </c>
       <c r="K2">
         <f>COUNTIF(K4:K118,"&lt;&gt;")</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L2">
         <f>COUNTIF(L4:L118,"&lt;&gt;")</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M2">
         <f>COUNTIF(M4:M118,"&lt;&gt;")</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N2">
-        <f>COUNTIF(N4:N118,"&lt;&gt;")</f>
-        <v>6</v>
+        <f>COUNTIF(N4:N117,"&lt;&gt;")</f>
+        <v>9</v>
       </c>
       <c r="O2">
         <f>COUNTIF(O4:O118,"&lt;&gt;")</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P2">
         <f>COUNTIF(P4:P118,"&lt;&gt;")</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Q2">
-        <f>COUNTIF(Q4:Q118,"&lt;&gt;")</f>
-        <v>6</v>
+        <f>COUNTIF(Q4:Q117,"&lt;&gt;")</f>
+        <v>8</v>
       </c>
       <c r="R2">
         <f>COUNTIF(R4:R117,"&lt;&gt;")</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="S2">
-        <f>COUNTIF(S4:S118,"&lt;&gt;")</f>
-        <v>6</v>
+        <f>COUNTIF(S4:S117,"&lt;&gt;")</f>
+        <v>9</v>
       </c>
       <c r="T2">
-        <f>COUNTIF(T4:T117,"&lt;&gt;")</f>
-        <v>5</v>
+        <f>COUNTIF(T4:T118,"&lt;&gt;")</f>
+        <v>9</v>
       </c>
       <c r="U2">
-        <f>COUNTIF(U4:U117,"&lt;&gt;")</f>
-        <v>5</v>
+        <f>COUNTIF(U4:U118,"&lt;&gt;")</f>
+        <v>9</v>
       </c>
       <c r="V2">
         <f>COUNTIF(V4:V118,"&lt;&gt;")</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W2">
-        <f>COUNTIF(W4:W118,"&lt;&gt;")</f>
-        <v>5</v>
+        <f>COUNTIF(W4:W117,"&lt;&gt;")</f>
+        <v>8</v>
       </c>
       <c r="X2">
         <f>COUNTIF(X4:X118,"&lt;&gt;")</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Y2">
         <f>COUNTIF(Y4:Y118,"&lt;&gt;")</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z2">
-        <f>COUNTIF(Z4:Z118,"&lt;&gt;")</f>
-        <v>5</v>
+        <f>COUNTIF(Z4:Z117,"&lt;&gt;")</f>
+        <v>8</v>
       </c>
       <c r="AA2">
         <f>COUNTIF(AA4:AA118,"&lt;&gt;")</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB2">
         <f>COUNTIF(AB4:AB118,"&lt;&gt;")</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC2">
         <f>COUNTIF(AC4:AC118,"&lt;&gt;")</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AD2">
-        <f>COUNTIF(AD4:AD117,"&lt;&gt;")</f>
-        <v>4</v>
+        <f>COUNTIF(AD4:AD118,"&lt;&gt;")</f>
+        <v>8</v>
       </c>
       <c r="AE2">
         <f>COUNTIF(AE4:AE118,"&lt;&gt;")</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AF2">
         <f>COUNTIF(AF4:AF118,"&lt;&gt;")</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AG2">
         <f>COUNTIF(AG4:AG118,"&lt;&gt;")</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AH2">
         <f>COUNTIF(AH4:AH118,"&lt;&gt;")</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AI2">
         <f>COUNTIF(AI4:AI118,"&lt;&gt;")</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AJ2">
-        <f>COUNTIF(AJ4:AJ118,"&lt;&gt;")</f>
-        <v>4</v>
+        <f>COUNTIF(AJ4:AJ117,"&lt;&gt;")</f>
+        <v>6</v>
       </c>
       <c r="AK2">
         <f>COUNTIF(AK4:AK118,"&lt;&gt;")</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AL2">
         <f>COUNTIF(AL4:AL118,"&lt;&gt;")</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AM2">
         <f>COUNTIF(AM4:AM118,"&lt;&gt;")</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AN2">
-        <f>COUNTIF(AN4:AN118,"&lt;&gt;")</f>
-        <v>4</v>
+        <f>COUNTIF(AN4:AN117,"&lt;&gt;")</f>
+        <v>6</v>
       </c>
       <c r="AO2">
         <f>COUNTIF(AO4:AO118,"&lt;&gt;")</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AP2">
         <f>COUNTIF(AP4:AP118,"&lt;&gt;")</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AQ2">
         <f>COUNTIF(AQ4:AQ118,"&lt;&gt;")</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AR2">
-        <f>COUNTIF(AR4:AR118,"&lt;&gt;")</f>
-        <v>2</v>
+        <f>COUNTIF(AR4:AR117,"&lt;&gt;")</f>
+        <v>4</v>
       </c>
       <c r="AS2">
         <f>COUNTIF(AS4:AS116,"&lt;&gt;")</f>
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="AT2">
+        <f>COUNTIF(AT4:AT118,"&lt;&gt;")</f>
+        <v>6</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
         <v>2</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="D3" t="s">
         <v>3</v>
       </c>
       <c r="E3" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F3" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="G3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J3" t="s">
         <v>7</v>
       </c>
-      <c r="I3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M3" t="s">
+        <v>15</v>
+      </c>
+      <c r="N3" t="s">
         <v>9</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L3" t="s">
-        <v>11</v>
-      </c>
-      <c r="M3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P3" t="s">
-        <v>15</v>
-      </c>
       <c r="Q3" t="s">
+        <v>18</v>
+      </c>
+      <c r="R3" t="s">
+        <v>19</v>
+      </c>
+      <c r="S3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T3" t="s">
+        <v>21</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="V3" t="s">
+        <v>28</v>
+      </c>
+      <c r="W3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X3" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y3" t="s">
         <v>16</v>
       </c>
-      <c r="R3" t="s">
+      <c r="Z3" t="s">
         <v>17</v>
       </c>
-      <c r="S3" t="s">
-        <v>18</v>
-      </c>
-      <c r="T3" t="s">
-        <v>19</v>
-      </c>
-      <c r="U3" t="s">
-        <v>20</v>
-      </c>
-      <c r="V3" t="s">
-        <v>21</v>
-      </c>
-      <c r="W3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X3" t="s">
+      <c r="AA3" t="s">
         <v>23</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="AB3" t="s">
         <v>24</v>
       </c>
-      <c r="Z3" t="s">
+      <c r="AC3" t="s">
         <v>25</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AD3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AJ3" t="s">
         <v>26</v>
       </c>
-      <c r="AB3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE3" t="s">
+      <c r="AK3" t="s">
         <v>30</v>
       </c>
-      <c r="AF3" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>33</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>34</v>
-      </c>
-      <c r="AJ3" t="s">
+      <c r="AL3" t="s">
         <v>35</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>37</v>
       </c>
       <c r="AM3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AN3" t="s">
+      <c r="AN3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AO3" t="s">
         <v>39</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>40</v>
       </c>
       <c r="AP3" t="s">
         <v>41</v>
@@ -1086,781 +1263,1281 @@
       <c r="AS3" t="s">
         <v>44</v>
       </c>
+      <c r="AT3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>46</v>
+      </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J4" t="s">
         <v>47</v>
       </c>
       <c r="K4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N4" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="O4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="P4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="Q4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="R4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S4" t="s">
+        <v>48</v>
+      </c>
+      <c r="T4" t="s">
         <v>47</v>
       </c>
-      <c r="T4" t="s">
-        <v>45</v>
-      </c>
       <c r="U4" t="s">
-        <v>46</v>
+